--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Base Formatos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Base Formatos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M355"/>
+  <dimension ref="A1:M382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="18.08984375" customWidth="1" style="2" min="1" max="1"/>
@@ -13838,7 +13838,6 @@
           <t>ZIP com HTML5 e pastas de imagens/scripts, ou JPEG/GIF; enviar sempre uma imagem de backup incluída no ZIP da criatividade.</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
       <c r="L252" t="inlineStr">
         <is>
           <t>Não há template para peças servidas em Google — inserir sempre a clicktag do Google (GWD: inserida no editor; outros programas: colocar no código, ver guidelines). Não pode ter vídeo (passaria a Rich Media, com specs diferentes). Animação: máx. 30 segundos. Fundo branco: usar border para destacar a peça. Validação: usar o validador de asset DCM (todos os pontos têm de estar OK).</t>
@@ -15609,7 +15608,6 @@
           <t>Lens assets conforme Lens Studio/Lens Web Builder</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
       <c r="L282" t="inlineStr">
         <is>
           <t>Logótipo ou nome da marca visível obrigatório em Face e World Lenses, de preferência no canto superior esquerdo ou direito, fora da zona coberta pela UI/carrossel; etiqueta 'SPONSORED' acrescentada automaticamente pelo Snapchat (visível 2 seg, não aparece no Snap do utilizador).</t>
@@ -16009,7 +16007,6 @@
           <t>Configurado e lançado via Arrow (plataforma de terceiros, IC Group + X Next)</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
       <c r="L289" t="inlineStr">
         <is>
           <t>3 formatos de campanha: Scheduled (post de opt-in + 1 post agendado); Subscription (post de opt-in + vários posts agendados); Instant (1 post instantâneo por pessoa que fez opt-in). Requer conta X pública e verificada, e autorização via X OAuth à Arrow.</t>
@@ -16208,7 +16205,6 @@
           <t>Suporta Spark Ads e Non-Spark Ads (recomendado 1-2 criativos por campanha); Duet/Stitch: Spark Ads segue os toggles do vídeo original, Non-Spark Ads não suportado.</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
       <c r="L293" t="inlineStr">
         <is>
           <t>Objetivo: Reach. Targeting disponível: idade (18+) e localização (país). Tracking de terceiros suportado (impressões e cliques). Landing page: webview standard (HTTPS) ou páginas internas TikTok (Branded Hashtag Challenge, Effect, TikTok Shop) — não suporta redirecionamento automático para app store nem link de TopView para LIVE. Música: mesma política dos in-feed ads reservation (Commercial Music Library ou faixas próprias autorizadas). Permite desativar comentários e download do vídeo. Add-ons: só os disponíveis em ambos os placements (TopView + Top Feed). Som: sempre ativo. Watermark: pode pedir vídeo descarregável sem marca de água.</t>
@@ -18572,7 +18568,6 @@
           <t>JPG (formato estático).</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
       <c r="L337" t="inlineStr">
         <is>
           <t>Só suporta tag de clicks (não é possível usar tag de impressões).</t>
@@ -18630,7 +18625,6 @@
           <t>PSD</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
       <c r="L338" t="inlineStr">
         <is>
           <t>Opções de layout: fundo com copy (base); + CTA à esquerda ou à direita (opcional); + logo no topo, à esquerda ou à direita. Suporte com tracking DCM. Ver ficha técnica adicional fornecida pelo meio ("We Transfer", não disponibilizada aqui).</t>
@@ -18683,7 +18677,6 @@
           <t>PNG, JPG ou BMP (também aceite em GIF, redimensionado automaticamente pela Anzu).</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
       <c r="L339" t="inlineStr">
         <is>
           <t>Suporte com tracking DCM. Até 10 criativos por deal. Todos os criativos são moderados pela equipa Roblox e podem sofrer alterações para cumprir as regras de compliance da Roblox. Ver ficheiro técnico adicional fornecido pelo meio (não disponibilizado aqui).</t>
@@ -18778,7 +18771,6 @@
           <t>PSD</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
       <c r="L341" t="inlineStr">
         <is>
           <t>Os banners laterais podem ser iguais ou diferentes, ao critério do cliente. Suporte com tracking DCM. O meio ajuda a produzir a versão final — se houver elementos extra com que possa trabalhar para enriquecer o formato, enviar os ficheiros editáveis. As dimensões exatas dos banners laterais constam numa folha técnica adicional fornecida pelo meio (não disponibilizada aqui).</t>
@@ -19145,7 +19137,6 @@
           <t>Responsive (All) — adapta-se ao layout do site.</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
       <c r="L349" t="inlineStr">
         <is>
           <t>Formatos nativos personalizados, específicos por site. Consultar as specs próprias de cada site (ex.: Bauer Native — All Site) através do link fornecido pelo meio (não disponibilizado aqui).</t>
@@ -19188,7 +19179,6 @@
           <t>300x600px (Mobile)</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
       <c r="L350" t="inlineStr">
         <is>
           <t>Servido via tag de terceiros (Mobkoi).</t>
@@ -19231,7 +19221,6 @@
           <t>Multi — formato construído internamente pela Illuminate (Mobile).</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
       <c r="L351" t="inlineStr">
         <is>
           <t>Solução de rich media interativa, otimizada mobile-first, com formatos inspirados em redes sociais, para alcançar utilizadores durante a leitura de conteúdo editorial. Specs técnicas completas num documento à parte ("Social Display RMF Specifications"), não disponibilizado aqui.</t>
@@ -19279,7 +19268,6 @@
           <t>Skin/hero images em formato estático: JPG ou PNG.</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
       <c r="L352" t="inlineStr">
         <is>
           <t>Não são aceites tags de criativos de terceiros (viewability, conversão, engagement) — apenas trackers de impressão e clique.</t>
@@ -19327,7 +19315,6 @@
           <t>Skin/hero images em formato estático: JPG ou PNG.</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
       <c r="L353" t="inlineStr">
         <is>
           <t>Não são aceites tags de criativos de terceiros (viewability, conversão, engagement) — apenas trackers de impressão e clique.</t>
@@ -19380,7 +19367,6 @@
           <t>MP4, 3GPP ou MOV (H264, vídeo MPEG4, áudio AAC); AVI (vídeo MJPEG, áudio PCM); MPEG-PS (vídeo MPEG2, áudio MP2); WMV. Bitrate mín. 1500 kbit/s. Duração máx. 30s. Sem autoplay de áudio (som off por defeito). Tags VAST 2.0 a 4.2 (sem suporte a VPAID).</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
       <c r="L354" t="inlineStr">
         <is>
           <t>Anúncio de vídeo autónomo entre parágrafos de conteúdo editorial (mobile, tablet e desktop). Reproduz automaticamente quando 50% do anúncio está visível; som desligado por defeito; botão "Learn More" no fundo do anúncio (único elemento clicável).</t>
@@ -19433,12 +19419,1440 @@
           <t>MP4, 3GPP ou MOV (H264, vídeo MPEG4, áudio AAC); AVI (vídeo MJPEG, áudio PCM); MPEG-PS (vídeo MPEG2, áudio MP2); WMV. Bitrate mín. 1500 kbit/s. Duração máx. 30s. Sem autoplay de áudio (som off por defeito). Tags VAST 2.0 a 4.2 (sem suporte a VPAID).</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
       <c r="L355" t="inlineStr">
         <is>
           <t>Pre-roll único, reproduzido no arranque do stream de áudio iniciado pelo utilizador (ex.: Radio Players como Kiss). Vendido como parte do Radio Player Takeover ou via programática. Não disponível atualmente nos canais de YouTube da Bauer.</t>
         </is>
       </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>Billboard</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>High Impact</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>Desenho técnico à escala 1/10 + 3 mm de bleed (ou na escala fornecida, no caso de veículos) — formato genérico, sem dimensão fixa.</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr"/>
+      <c r="I356" t="inlineStr"/>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>PDF (qualidade de impressão), JPEG (visualização) e ficheiro editável (para ajustes menores)</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr"/>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>Fontes convertidas em curvas; imagens finalizadas a 300 dpi; ficheiro gravado em versão anterior à utilizada para o criar; sempre em CMYK (Pantone e RGB não aceites); sem elementos de informação relevante junto às margens de corte. Envio via WeTransfer/Hightail/Dropbox ou FTP do cliente (com utilizador e password); CD/DVD sempre com prova de cor.</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>Billboard</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>Outdoor 8x3</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>Arte final: 784x300mm (escala reduzida). Medida real: 8000x3000mm. Área visível: 7950x2950mm.</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr"/>
+      <c r="I357" t="inlineStr"/>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>Papel cartaz 120g blueback ou AFC 120g; impressão em tintas U.V.; PDF (qualidade de impressão), JPEG (visualização) e ficheiro editável.</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr"/>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão anterior do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Prazo de entrega: até 5 dias úteis antes do início da campanha. Cartazes entregues alceados (ordenados) e dobrados — cartaz de 14 folhas, ordem da última para a primeira folha, com a imagem voltada para cima; miras de sobreposição obrigatórias, com margens de sobreposição de 4cm do lado direito e 12,5cm no fundo das folhas inferiores (o papel tem distensão variável). Quantidades: Abril a Setembro, +15% do nº de faces; Outubro a Março, +25%. Cartazes entregues e identificados à unidade, e alceados. Nota: imagens com fundos escuros ou que necessitem de muita tinta reduzem a qualidade da afixação. Envio via WeTransfer/Hightail/Dropbox ou FTP do cliente; CD/DVD sempre com prova de cor.</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>Multibanco</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>Multibanco - Imagem</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>3 tamanhos disponíveis: 640x417px, 800x522px ou 1024x667px. 3 momentos distintos: 1º momento 10s, 2º momento 3s, 3º momento 10s (pode usar 1, 2 ou 3 imagens diferentes, ou combinar com vídeo nos vários momentos).</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr"/>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>JPG ou PNG, resolução igual ou superior a 72 dpi</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr"/>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>Não é possível apresentar conteúdos que mostrem, de forma explícita e não contextualizada, partes do corpo habitualmente resguardadas; mencionem instituições financeiras monetárias e de pagamento, partidos/associações políticas ou sindicais, organizações religiosas; usem símbolos/linguagem que se possam confundir com o funcionamento do caixa automático; ou que, no primeiro momento publicitário, mostrem qualquer preço sem identificação clara de que é um preço do anunciante, produto ou serviço. Para todos os outros princípios aplica-se o código da publicidade.</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>Multibanco</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>Multibanco - Vídeo</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>2 tamanhos disponíveis: 640x392px ou 800x496px. 3 momentos distintos: 1º momento 5s, 2º momento 2s, 3º momento 5s (pode usar 1, 2 ou 3 vídeos diferentes, ou combinar com imagens nos vários momentos; sugestão: terminar com a imagem estática do último frame).</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr"/>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>MPEG-1 ou MP4</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr"/>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>Sem canal áudio. Frame rate: 24 frames/s. Profundidade de cor: 24 bits/pixel. Mesmos princípios de conteúdo do formato "Multibanco - Imagem".</t>
+        </is>
+      </c>
+      <c r="M359" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>Decoração</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>Decorações Integrais e Grande Formato</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>Desenho técnico à escala 1/10 + 3 mm de bleed (ou na escala fornecida, no caso de veículos).</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr"/>
+      <c r="I360" t="inlineStr"/>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>PDF (qualidade de impressão), JPEG (visualização) e ficheiro editável (para ajustes menores)</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr"/>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>Fontes convertidas em curvas; imagens finalizadas a 300 dpi; ficheiro gravado em versão anterior do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Envio via WeTransfer/Hightail/Dropbox ou FTP do cliente; CD/DVD sempre com prova de cor.</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>LED Indoor</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>Grande Formato Digital Indoor 16x9</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>1920x1080px. Pode ser utilizado em suporte LED 16x9, ecrã triplo (3 ecrãs) ou Tomi Spot TV.</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>Máx. 100 MB</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>MP4, codec H264</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr"/>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>Duração: 10 segundos (obrigatório). Bitrate máx. 6 Mbps. Framerate 24 frames/s. No suporte de 3 ecrãs existe uma separação real de 2,5cm entre ecrãs, que divide/corta a imagem — deve ser tido em conta para não deformar frases ou elementos relevantes (zonas de quebra).</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>Mupi</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>Mupi Digital</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>1080x1920px.</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>Máx. 100 MB</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>MP4, codec H264</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr"/>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>Duração: 10 segundos (obrigatório). Bitrate máx. 6 Mbps. Framerate 24 frames/s.</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>Mupi</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>Mupi</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>Arte final: 234x348mm + 1mm de bleed. Medida real: 1185x1750mm. Área visível: 1131x1667mm.</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr"/>
+      <c r="I363" t="inlineStr"/>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>PDF (qualidade de impressão), JPEG (visualização) e ficheiro editável</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr"/>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão anterior do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Envio via WeTransfer/Hightail/Dropbox ou FTP do cliente; CD/DVD sempre com prova de cor.</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>DreamMedia</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>DreamMedia</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>Billboard</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>Outdoor 8x3</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>8000x3000mm (área de mancha publicitária = área visível).</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr"/>
+      <c r="I364" t="inlineStr"/>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>Ficheiro fechado: JPG, TIFF ou PDF, a 10% do tamanho real, a 300 dpi. Formato editável: textos convertidos em curvas (outlines) ou fontes fornecidas.</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr"/>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>Bleed: 10cm a toda a volta (não deve conter informação importante). Ficheiros fornecidos em CMYK prontos para impressão — ficheiros em RGB são convertidos para CMYK, podendo as cores sofrer alterações.</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr"/>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>BIG Outdoors</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>BIG Outdoors</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>Billboard</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>Monoposte 10x5</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>Área de mancha publicitária: 10000x5000mm.</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr"/>
+      <c r="I365" t="inlineStr"/>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>Ficheiro fechado: JPG, TIFF ou PDF, a 10% do tamanho real, a 300 dpi. Formato editável: textos convertidos em curvas (outlines) ou fontes fornecidas.</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr"/>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>Bleed: 10cm a toda a volta (não deve conter informação importante). Ficheiros fornecidos em CMYK prontos para impressão — ficheiros em RGB são convertidos para CMYK, podendo as cores sofrer alterações. Importante: a arte final não deve conter letras de tamanho inferior a 30cm (110 pontos); dar maior destaque ao produto, logótipo, telefone e site para melhores resultados de comunicação.</t>
+        </is>
+      </c>
+      <c r="M365" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>BIG Outdoors</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>BIG Outdoors</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>Billboard</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>Monoposte 11x5</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>Área de mancha publicitária: 11000x5000mm.</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr"/>
+      <c r="I366" t="inlineStr"/>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>Ficheiro fechado: JPG, TIFF ou PDF, a 10% do tamanho real, a 300 dpi. Formato editável: textos convertidos em curvas (outlines) ou fontes fornecidas.</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr"/>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>Bleed: 10cm a toda a volta (não deve conter informação importante). Ficheiros fornecidos em CMYK prontos para impressão — ficheiros em RGB são convertidos para CMYK, podendo as cores sofrer alterações. Importante: a arte final não deve conter letras de tamanho inferior a 30cm (110 pontos); dar maior destaque ao produto, logótipo, telefone e site para melhores resultados de comunicação.</t>
+        </is>
+      </c>
+      <c r="M366" t="inlineStr"/>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>BIG Outdoors</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>BIG Outdoors</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>Billboard</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>Monoposte 12x5</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>Área de mancha publicitária: 12000x5000mm.</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr"/>
+      <c r="I367" t="inlineStr"/>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>Ficheiro fechado: JPG, TIFF ou PDF, a 10% do tamanho real, a 300 dpi. Formato editável: textos convertidos em curvas (outlines) ou fontes fornecidas.</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr"/>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>Bleed: 10cm a toda a volta (não deve conter informação importante). Ficheiros fornecidos em CMYK prontos para impressão — ficheiros em RGB são convertidos para CMYK, podendo as cores sofrer alterações. Importante: a arte final não deve conter letras de tamanho inferior a 30cm (110 pontos); dar maior destaque ao produto, logótipo, telefone e site para melhores resultados de comunicação.</t>
+        </is>
+      </c>
+      <c r="M367" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>JCDecaux</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>JCDecaux</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>Mupi</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>Mupi Papel</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>Área total: 1185x1750mm. Área visível: 1160x1710mm.</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr"/>
+      <c r="I368" t="inlineStr"/>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>Papel, gramagem 130g, verso do cartaz com fundo branco. Ficheiro: Illustrator, Photoshop, PDF, EPS ou TIFF.</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr"/>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>Prazo: 7 dias úteis após aprovação da Arte Final. Se enviar PDF, atenção a cores/perfis embebidos/resolução de imagens; enviar fontes; texto convertido em curvas, aberto e editável. Impressão offset: CMYK, mín. 300 dpi, máx. 400 dpi. Impressão digital: CMYK, mín. 150 dpi, máx. 200 dpi. Ficheiro na medida indicada + 3cm de bleed (3mm se a AF for elaborada à escala de 10%); respeitar área de segurança virtual para evitar corte de elementos na afixação; sempre que possível, enviar com prova de cor. Após receção, a JCDecaux envia um JPG para validação final antes de imprimir; após aprovação, declina responsabilidade por desformatações/falhas na imagem. Critérios de qualidade: opacidade ≥88%, brancura 91-93 ISO, absorção de água (cobb60) 15-30g/m², absorção de água (cobb300) &lt;70g/m², distensão máx. ±2%/m, resistência à rutura por tração (húmido) &gt;0,6kN/m — materiais fora destes requisitos podem não ser afixados. Especificações ambientais: papel com certificação PEFC/FSC (ou equivalente); tintas conformes REACH/GreenGuard, isentas de metais pesados; papel reciclado, sem cloro (ECF/TCF).</t>
+        </is>
+      </c>
+      <c r="M368" t="inlineStr"/>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>JCDecaux</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>JCDecaux</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>Billboard</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>Impressão Senior</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>Área visível: 3020x2230mm. Área total: 3200x2350mm.</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr"/>
+      <c r="I369" t="inlineStr"/>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>Papel, gramagem 150g, verso do cartaz com fundo branco. Ficheiro: Illustrator, Photoshop, PDF, EPS ou TIFF.</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr"/>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>Impressão em 1, 2 ou 4 folhas, entregues alceadas por ordem de colagem (a começar na folha 1, com o verso para baixo). Impressão em 2 folhas: folha 1 3200x1200mm (aparada 3130x1150mm) + folha 2 idêntica, margem de sobreposição 25mm/35mm. Impressão em 4 folhas: 1600x1200mm por folha (aparada 1530x1175mm), aparadas à medida sem margem entre si. Prazo: 7 dias úteis após aprovação da Arte Final. Ficheiro: Illustrator/Photoshop (incluir fontes e respetivos links) ou PDF (cores/perfis embebidos/resolução de imagens, texto em curvas); impressão offset CMYK 300-400 dpi, digital CMYK 150-200 dpi; medida indicada + 3cm de bleed (3mm à escala de 10%); respeitar área de segurança virtual; enviar com prova de cor sempre que possível. Entrega nas instalações da JCDecaux 5 dias úteis antes do início da campanha, com impressão da campanha e guia de transporte certificada; horário de entrega 07h-12h e 13h30-16h (Portão 2), Beco da Aviação nº1, Granja do Alpriate, Vialonga. Após receção, a JCDecaux envia JPG para validação; após aprovação, declina responsabilidade por falhas na imagem. Critérios de qualidade: opacidade ≥88%, brancura 91-93 ISO, absorção água (cobb60) 15-30g/m², (cobb300) &lt;70g/m², distensão máx. ±2%/m, resistência à rutura (húmido) &gt;0,6kN/m.</t>
+        </is>
+      </c>
+      <c r="M369" t="inlineStr"/>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>JCDecaux</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>JCDecaux</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>Mupi</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>Mupi Digital</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>1080x1920px.</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr"/>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000.</t>
+        </is>
+      </c>
+      <c r="K370" t="inlineStr"/>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Após envio, a JCDecaux declina responsabilidade por falhas no vídeo apresentado. Alterações ao vídeo carecem de aprovação final do cliente; a JCDecaux não se responsabiliza por atraso na entrega (sem compensação de airing).</t>
+        </is>
+      </c>
+      <c r="M370" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>JCDecaux</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>JCDecaux</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>Mupi</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>Mupi Digital (Shopping)</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>Ficheiro entregue em 1920x1080px (paisagem, para ecrãs de 63''), rodado automaticamente pelo sistema para exibição vertical 1080x1920px.</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>16:9 (ficheiro) / 9:16 (exibição)</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr"/>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>Ficheiro nativo (compressão nativa), bitrate máx. 20.000.</t>
+        </is>
+      </c>
+      <c r="K371" t="inlineStr"/>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>Duração do spot: 10 segundos, dentro de um loop de 60 segundos com outros anunciantes. Enviar o vídeo 2 dias antes do início da campanha, por e-mail para o contacto JCDecaux. Alterações carecem de aprovação final do cliente; a JCDecaux declina responsabilidade por falhas no vídeo após o envio, e não se responsabiliza por atraso na entrega.</t>
+        </is>
+      </c>
+      <c r="M371" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>JCDecaux</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>JCDecaux</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>Billboard</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>Painel 8x3 - Papel</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>Área total: 8000x3000mm. Área visível: 7500x2750mm.</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr"/>
+      <c r="I372" t="inlineStr"/>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>Papel, gramagem entre 120g e 170g, verso do cartaz com fundo azul. Ficheiro: Illustrator, Photoshop, PDF, EPS ou TIFF.</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr"/>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>Prazo: 7 dias úteis após aprovação da Arte Final. Impressão em 12, 14 ou 16 folhas, entregues alceadas (a começar na folha 1, verso para baixo), numeradas no canto superior direito. Impressão em 14 folhas: folhas superiores 1-6 (997mm cada) + folha 7 (997mm), folhas inferiores 9-13 (1135mm cada) + folha 14 (1135mm); margem de sobreposição 25mm à direita nas folhas superiores (exceto a última) e 25mm à direita + no topo nas inferiores (exceto a última, só no topo); áreas de sobreposição isentas de impressão. Impressão em 16 folhas: superiores 1-7 (997mm) + folha 8 (997mm), inferiores 9-15 (997mm) + folha 16 (997mm), mesmas regras de margem. Se PDF: cores/perfis embebidos/resolução de imagens, texto em curvas; impressão offset CMYK 300-400 dpi, digital CMYK 150-200 dpi; medida indicada + 3cm de bleed (3mm à escala de 10%); área de segurança virtual; prova de cor recomendada. Entrega nas instalações JCDecaux, Portão 1, Beco da Aviação nº1, Granja do Alpriate, Vialonga, 07h-12h/13h30-16h. Após receção, JCDecaux envia JPG para validação; após aprovação, declina responsabilidade por falhas na imagem.</t>
+        </is>
+      </c>
+      <c r="M372" t="inlineStr"/>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>JCDecaux</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>JCDecaux</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>Billboard</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>Painel 8x3 - Vinil</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>Área total: 8000x3000mm. Área visível: 8000x3000mm (sem margem).</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr"/>
+      <c r="I373" t="inlineStr"/>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>Vinil PVC branco ou transparente, superfície brilhante ou mate, polyacrylate removível e transparente; base em papel revestido a silicone 135g/m². Ficheiro: Illustrator, Photoshop, PDF, EPS ou TIFF.</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr"/>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>Uso recomendado: outdoors de curta e média duração. Método de impressão: tintas de base solvente, UV ou látex. Prazo: 7 dias úteis após aprovação da Arte Final. Impressão em 8 folhas de 1000mm cada, enroladas por ordem (folha 1 a 8), numeradas no canto superior direito; margem de sobreposição 25mm à direita em todas as folhas (áreas de sobreposição isentas de impressão). Se PDF: cores/perfis embebidos/resolução de imagens, texto em curvas; impressão offset CMYK 300-400 dpi, digital CMYK 150-200 dpi; medida indicada + 5cm de bleed (5mm à escala de 10%); área de segurança virtual; prova de cor recomendada. Entrega nas instalações JCDecaux, Portão 1, Beco da Aviação nº1, Granja do Alpriate, Vialonga, 5 dias úteis antes do início da campanha, com impressão da campanha e guia de transporte certificada, 07h-12h/13h30-16h. Após receção, JCDecaux envia JPG para validação; após aprovação, declina responsabilidade por falhas na imagem.</t>
+        </is>
+      </c>
+      <c r="M373" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>JCDecaux</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>JCDecaux</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>Billboard</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>Premium LED 6m²</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>328x492px.</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr"/>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000.</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr"/>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 4 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
+        </is>
+      </c>
+      <c r="M374" t="inlineStr"/>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>JCDecaux</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>JCDecaux</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>Billboard</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>Premium LED 8m²</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>370x656px.</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr"/>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000.</t>
+        </is>
+      </c>
+      <c r="K375" t="inlineStr"/>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
+        </is>
+      </c>
+      <c r="M375" t="inlineStr"/>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>JCDecaux</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>JCDecaux</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>Billboard</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>Premium LED 12m²</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>1520x800px.</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>1.91:1</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr"/>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000.</t>
+        </is>
+      </c>
+      <c r="K376" t="inlineStr"/>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
+        </is>
+      </c>
+      <c r="M376" t="inlineStr"/>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>JCDecaux</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>JCDecaux</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>Billboard</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>Premium LED 15m²</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>720x1296px.</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr"/>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000.</t>
+        </is>
+      </c>
+      <c r="K377" t="inlineStr"/>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
+        </is>
+      </c>
+      <c r="M377" t="inlineStr"/>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>JCDecaux</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>JCDecaux</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>Billboard</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>Premium LED 18m²</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>640x1152px.</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr"/>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000.</t>
+        </is>
+      </c>
+      <c r="K378" t="inlineStr"/>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
+        </is>
+      </c>
+      <c r="M378" t="inlineStr"/>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>JCDecaux</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>JCDecaux</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>Billboard</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>Premium LED 22m²</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>1248x800px.</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr"/>
+      <c r="I379" t="inlineStr"/>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000.</t>
+        </is>
+      </c>
+      <c r="K379" t="inlineStr"/>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. Vídeo em estilo "Subtle Motion" recomendado: movimento lento e gradual dos elementos criativos (slow motion sem cortes bruscos; fundos deslocados/ampliados lentamente em vez de intermitentes; texto a desvanecer gradualmente em vez de deslizar/pulsar; luzes a brilhar em vez de piscar); marca visível em pelo menos 80% da criatividade. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
+        </is>
+      </c>
+      <c r="M379" t="inlineStr"/>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>JCDecaux</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>JCDecaux</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>Billboard</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>Premium LED 25m²</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>480x810px.</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr"/>
+      <c r="I380" t="inlineStr"/>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000.</t>
+        </is>
+      </c>
+      <c r="K380" t="inlineStr"/>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
+        </is>
+      </c>
+      <c r="M380" t="inlineStr"/>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>JCDecaux</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>JCDecaux</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>Billboard</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>Premium LED 37m²</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>480x738px.</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr"/>
+      <c r="I381" t="inlineStr"/>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000.</t>
+        </is>
+      </c>
+      <c r="K381" t="inlineStr"/>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 16,7%. Vídeo em estilo "Subtle Motion" recomendado (ver formato "Premium LED 22m²" para guidelines completas). A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
+        </is>
+      </c>
+      <c r="M381" t="inlineStr"/>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Táxi Advertising</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Táxi Advertising</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>Decoração</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>Decoração de Táxi</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>Manter o tamanho original do template (ficheiros vetoriais reais fornecidos pelo fornecedor, com o desenho do lado esquerdo e do lado direito do táxi).</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr"/>
+      <c r="I382" t="inlineStr"/>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>Ficheiros de trabalho em Illustrator (vetoriais). Entrega: JPG ou PDF.</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr"/>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>O texto deve manter-se dentro da linha amarela de segurança (para não ser cortado). O fundo atrás do texto deve ultrapassar a linha branca em pelo menos 50mm de bleed. Impressão em CMYK, resolução 150 pixels/polegada. É obrigatório enviar também um PDF com a maqueta da decoração do táxi, para orientação da colagem do vinil.</t>
+        </is>
+      </c>
+      <c r="M382" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -19446,11 +19446,6 @@
           <t>MOP</t>
         </is>
       </c>
-      <c r="E356" t="inlineStr">
-        <is>
-          <t>Billboard</t>
-        </is>
-      </c>
       <c r="F356" t="inlineStr">
         <is>
           <t>High Impact</t>
@@ -19461,20 +19456,16 @@
           <t>Desenho técnico à escala 1/10 + 3 mm de bleed (ou na escala fornecida, no caso de veículos) — formato genérico, sem dimensão fixa.</t>
         </is>
       </c>
-      <c r="H356" t="inlineStr"/>
-      <c r="I356" t="inlineStr"/>
       <c r="J356" t="inlineStr">
         <is>
           <t>PDF (qualidade de impressão), JPEG (visualização) e ficheiro editável (para ajustes menores)</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
       <c r="L356" t="inlineStr">
         <is>
           <t>Fontes convertidas em curvas; imagens finalizadas a 300 dpi; ficheiro gravado em versão anterior à utilizada para o criar; sempre em CMYK (Pantone e RGB não aceites); sem elementos de informação relevante junto às margens de corte. Envio via WeTransfer/Hightail/Dropbox ou FTP do cliente (com utilizador e password); CD/DVD sempre com prova de cor.</t>
         </is>
       </c>
-      <c r="M356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -19497,11 +19488,6 @@
           <t>MOP</t>
         </is>
       </c>
-      <c r="E357" t="inlineStr">
-        <is>
-          <t>Billboard</t>
-        </is>
-      </c>
       <c r="F357" t="inlineStr">
         <is>
           <t>Outdoor 8x3</t>
@@ -19512,20 +19498,16 @@
           <t>Arte final: 784x300mm (escala reduzida). Medida real: 8000x3000mm. Área visível: 7950x2950mm.</t>
         </is>
       </c>
-      <c r="H357" t="inlineStr"/>
-      <c r="I357" t="inlineStr"/>
       <c r="J357" t="inlineStr">
         <is>
           <t>Papel cartaz 120g blueback ou AFC 120g; impressão em tintas U.V.; PDF (qualidade de impressão), JPEG (visualização) e ficheiro editável.</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
       <c r="L357" t="inlineStr">
         <is>
           <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão anterior do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Prazo de entrega: até 5 dias úteis antes do início da campanha. Cartazes entregues alceados (ordenados) e dobrados — cartaz de 14 folhas, ordem da última para a primeira folha, com a imagem voltada para cima; miras de sobreposição obrigatórias, com margens de sobreposição de 4cm do lado direito e 12,5cm no fundo das folhas inferiores (o papel tem distensão variável). Quantidades: Abril a Setembro, +15% do nº de faces; Outubro a Março, +25%. Cartazes entregues e identificados à unidade, e alceados. Nota: imagens com fundos escuros ou que necessitem de muita tinta reduzem a qualidade da afixação. Envio via WeTransfer/Hightail/Dropbox ou FTP do cliente; CD/DVD sempre com prova de cor.</t>
         </is>
       </c>
-      <c r="M357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -19548,11 +19530,6 @@
           <t>MOP</t>
         </is>
       </c>
-      <c r="E358" t="inlineStr">
-        <is>
-          <t>Multibanco</t>
-        </is>
-      </c>
       <c r="F358" t="inlineStr">
         <is>
           <t>Multibanco - Imagem</t>
@@ -19563,7 +19540,6 @@
           <t>3 tamanhos disponíveis: 640x417px, 800x522px ou 1024x667px. 3 momentos distintos: 1º momento 10s, 2º momento 3s, 3º momento 10s (pode usar 1, 2 ou 3 imagens diferentes, ou combinar com vídeo nos vários momentos).</t>
         </is>
       </c>
-      <c r="H358" t="inlineStr"/>
       <c r="I358" t="inlineStr">
         <is>
           <t>Máx. 1 MB</t>
@@ -19574,13 +19550,11 @@
           <t>JPG ou PNG, resolução igual ou superior a 72 dpi</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
       <c r="L358" t="inlineStr">
         <is>
           <t>Não é possível apresentar conteúdos que mostrem, de forma explícita e não contextualizada, partes do corpo habitualmente resguardadas; mencionem instituições financeiras monetárias e de pagamento, partidos/associações políticas ou sindicais, organizações religiosas; usem símbolos/linguagem que se possam confundir com o funcionamento do caixa automático; ou que, no primeiro momento publicitário, mostrem qualquer preço sem identificação clara de que é um preço do anunciante, produto ou serviço. Para todos os outros princípios aplica-se o código da publicidade.</t>
         </is>
       </c>
-      <c r="M358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -19603,11 +19577,6 @@
           <t>MOP</t>
         </is>
       </c>
-      <c r="E359" t="inlineStr">
-        <is>
-          <t>Multibanco</t>
-        </is>
-      </c>
       <c r="F359" t="inlineStr">
         <is>
           <t>Multibanco - Vídeo</t>
@@ -19618,7 +19587,6 @@
           <t>2 tamanhos disponíveis: 640x392px ou 800x496px. 3 momentos distintos: 1º momento 5s, 2º momento 2s, 3º momento 5s (pode usar 1, 2 ou 3 vídeos diferentes, ou combinar com imagens nos vários momentos; sugestão: terminar com a imagem estática do último frame).</t>
         </is>
       </c>
-      <c r="H359" t="inlineStr"/>
       <c r="I359" t="inlineStr">
         <is>
           <t>Máx. 1 MB</t>
@@ -19629,13 +19597,11 @@
           <t>MPEG-1 ou MP4</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
       <c r="L359" t="inlineStr">
         <is>
           <t>Sem canal áudio. Frame rate: 24 frames/s. Profundidade de cor: 24 bits/pixel. Mesmos princípios de conteúdo do formato "Multibanco - Imagem".</t>
         </is>
       </c>
-      <c r="M359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -19658,11 +19624,6 @@
           <t>MOP</t>
         </is>
       </c>
-      <c r="E360" t="inlineStr">
-        <is>
-          <t>Decoração</t>
-        </is>
-      </c>
       <c r="F360" t="inlineStr">
         <is>
           <t>Decorações Integrais e Grande Formato</t>
@@ -19673,20 +19634,16 @@
           <t>Desenho técnico à escala 1/10 + 3 mm de bleed (ou na escala fornecida, no caso de veículos).</t>
         </is>
       </c>
-      <c r="H360" t="inlineStr"/>
-      <c r="I360" t="inlineStr"/>
       <c r="J360" t="inlineStr">
         <is>
           <t>PDF (qualidade de impressão), JPEG (visualização) e ficheiro editável (para ajustes menores)</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
       <c r="L360" t="inlineStr">
         <is>
           <t>Fontes convertidas em curvas; imagens finalizadas a 300 dpi; ficheiro gravado em versão anterior do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Envio via WeTransfer/Hightail/Dropbox ou FTP do cliente; CD/DVD sempre com prova de cor.</t>
         </is>
       </c>
-      <c r="M360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -19709,11 +19666,6 @@
           <t>MOP</t>
         </is>
       </c>
-      <c r="E361" t="inlineStr">
-        <is>
-          <t>LED Indoor</t>
-        </is>
-      </c>
       <c r="F361" t="inlineStr">
         <is>
           <t>Grande Formato Digital Indoor 16x9</t>
@@ -19739,13 +19691,11 @@
           <t>MP4, codec H264</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
       <c r="L361" t="inlineStr">
         <is>
           <t>Duração: 10 segundos (obrigatório). Bitrate máx. 6 Mbps. Framerate 24 frames/s. No suporte de 3 ecrãs existe uma separação real de 2,5cm entre ecrãs, que divide/corta a imagem — deve ser tido em conta para não deformar frases ou elementos relevantes (zonas de quebra).</t>
         </is>
       </c>
-      <c r="M361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -19768,11 +19718,6 @@
           <t>MOP</t>
         </is>
       </c>
-      <c r="E362" t="inlineStr">
-        <is>
-          <t>Mupi</t>
-        </is>
-      </c>
       <c r="F362" t="inlineStr">
         <is>
           <t>Mupi Digital</t>
@@ -19798,13 +19743,11 @@
           <t>MP4, codec H264</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
       <c r="L362" t="inlineStr">
         <is>
           <t>Duração: 10 segundos (obrigatório). Bitrate máx. 6 Mbps. Framerate 24 frames/s.</t>
         </is>
       </c>
-      <c r="M362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -19827,35 +19770,26 @@
           <t>MOP</t>
         </is>
       </c>
-      <c r="E363" t="inlineStr">
+      <c r="F363" t="inlineStr">
         <is>
           <t>Mupi</t>
         </is>
       </c>
-      <c r="F363" t="inlineStr">
-        <is>
-          <t>Mupi</t>
-        </is>
-      </c>
       <c r="G363" t="inlineStr">
         <is>
           <t>Arte final: 234x348mm + 1mm de bleed. Medida real: 1185x1750mm. Área visível: 1131x1667mm.</t>
         </is>
       </c>
-      <c r="H363" t="inlineStr"/>
-      <c r="I363" t="inlineStr"/>
       <c r="J363" t="inlineStr">
         <is>
           <t>PDF (qualidade de impressão), JPEG (visualização) e ficheiro editável</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
       <c r="L363" t="inlineStr">
         <is>
           <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão anterior do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Envio via WeTransfer/Hightail/Dropbox ou FTP do cliente; CD/DVD sempre com prova de cor.</t>
         </is>
       </c>
-      <c r="M363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -19878,11 +19812,6 @@
           <t>DreamMedia</t>
         </is>
       </c>
-      <c r="E364" t="inlineStr">
-        <is>
-          <t>Billboard</t>
-        </is>
-      </c>
       <c r="F364" t="inlineStr">
         <is>
           <t>Outdoor 8x3</t>
@@ -19893,20 +19822,16 @@
           <t>8000x3000mm (área de mancha publicitária = área visível).</t>
         </is>
       </c>
-      <c r="H364" t="inlineStr"/>
-      <c r="I364" t="inlineStr"/>
       <c r="J364" t="inlineStr">
         <is>
           <t>Ficheiro fechado: JPG, TIFF ou PDF, a 10% do tamanho real, a 300 dpi. Formato editável: textos convertidos em curvas (outlines) ou fontes fornecidas.</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
       <c r="L364" t="inlineStr">
         <is>
           <t>Bleed: 10cm a toda a volta (não deve conter informação importante). Ficheiros fornecidos em CMYK prontos para impressão — ficheiros em RGB são convertidos para CMYK, podendo as cores sofrer alterações.</t>
         </is>
       </c>
-      <c r="M364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -19929,11 +19854,6 @@
           <t>BIG Outdoors</t>
         </is>
       </c>
-      <c r="E365" t="inlineStr">
-        <is>
-          <t>Billboard</t>
-        </is>
-      </c>
       <c r="F365" t="inlineStr">
         <is>
           <t>Monoposte 10x5</t>
@@ -19944,20 +19864,16 @@
           <t>Área de mancha publicitária: 10000x5000mm.</t>
         </is>
       </c>
-      <c r="H365" t="inlineStr"/>
-      <c r="I365" t="inlineStr"/>
       <c r="J365" t="inlineStr">
         <is>
           <t>Ficheiro fechado: JPG, TIFF ou PDF, a 10% do tamanho real, a 300 dpi. Formato editável: textos convertidos em curvas (outlines) ou fontes fornecidas.</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
       <c r="L365" t="inlineStr">
         <is>
           <t>Bleed: 10cm a toda a volta (não deve conter informação importante). Ficheiros fornecidos em CMYK prontos para impressão — ficheiros em RGB são convertidos para CMYK, podendo as cores sofrer alterações. Importante: a arte final não deve conter letras de tamanho inferior a 30cm (110 pontos); dar maior destaque ao produto, logótipo, telefone e site para melhores resultados de comunicação.</t>
         </is>
       </c>
-      <c r="M365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -19980,11 +19896,6 @@
           <t>BIG Outdoors</t>
         </is>
       </c>
-      <c r="E366" t="inlineStr">
-        <is>
-          <t>Billboard</t>
-        </is>
-      </c>
       <c r="F366" t="inlineStr">
         <is>
           <t>Monoposte 11x5</t>
@@ -19995,20 +19906,16 @@
           <t>Área de mancha publicitária: 11000x5000mm.</t>
         </is>
       </c>
-      <c r="H366" t="inlineStr"/>
-      <c r="I366" t="inlineStr"/>
       <c r="J366" t="inlineStr">
         <is>
           <t>Ficheiro fechado: JPG, TIFF ou PDF, a 10% do tamanho real, a 300 dpi. Formato editável: textos convertidos em curvas (outlines) ou fontes fornecidas.</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
       <c r="L366" t="inlineStr">
         <is>
           <t>Bleed: 10cm a toda a volta (não deve conter informação importante). Ficheiros fornecidos em CMYK prontos para impressão — ficheiros em RGB são convertidos para CMYK, podendo as cores sofrer alterações. Importante: a arte final não deve conter letras de tamanho inferior a 30cm (110 pontos); dar maior destaque ao produto, logótipo, telefone e site para melhores resultados de comunicação.</t>
         </is>
       </c>
-      <c r="M366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -20031,11 +19938,6 @@
           <t>BIG Outdoors</t>
         </is>
       </c>
-      <c r="E367" t="inlineStr">
-        <is>
-          <t>Billboard</t>
-        </is>
-      </c>
       <c r="F367" t="inlineStr">
         <is>
           <t>Monoposte 12x5</t>
@@ -20046,20 +19948,16 @@
           <t>Área de mancha publicitária: 12000x5000mm.</t>
         </is>
       </c>
-      <c r="H367" t="inlineStr"/>
-      <c r="I367" t="inlineStr"/>
       <c r="J367" t="inlineStr">
         <is>
           <t>Ficheiro fechado: JPG, TIFF ou PDF, a 10% do tamanho real, a 300 dpi. Formato editável: textos convertidos em curvas (outlines) ou fontes fornecidas.</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
       <c r="L367" t="inlineStr">
         <is>
           <t>Bleed: 10cm a toda a volta (não deve conter informação importante). Ficheiros fornecidos em CMYK prontos para impressão — ficheiros em RGB são convertidos para CMYK, podendo as cores sofrer alterações. Importante: a arte final não deve conter letras de tamanho inferior a 30cm (110 pontos); dar maior destaque ao produto, logótipo, telefone e site para melhores resultados de comunicação.</t>
         </is>
       </c>
-      <c r="M367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -20082,11 +19980,6 @@
           <t>JCDecaux</t>
         </is>
       </c>
-      <c r="E368" t="inlineStr">
-        <is>
-          <t>Mupi</t>
-        </is>
-      </c>
       <c r="F368" t="inlineStr">
         <is>
           <t>Mupi Papel</t>
@@ -20097,20 +19990,16 @@
           <t>Área total: 1185x1750mm. Área visível: 1160x1710mm.</t>
         </is>
       </c>
-      <c r="H368" t="inlineStr"/>
-      <c r="I368" t="inlineStr"/>
       <c r="J368" t="inlineStr">
         <is>
           <t>Papel, gramagem 130g, verso do cartaz com fundo branco. Ficheiro: Illustrator, Photoshop, PDF, EPS ou TIFF.</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
       <c r="L368" t="inlineStr">
         <is>
           <t>Prazo: 7 dias úteis após aprovação da Arte Final. Se enviar PDF, atenção a cores/perfis embebidos/resolução de imagens; enviar fontes; texto convertido em curvas, aberto e editável. Impressão offset: CMYK, mín. 300 dpi, máx. 400 dpi. Impressão digital: CMYK, mín. 150 dpi, máx. 200 dpi. Ficheiro na medida indicada + 3cm de bleed (3mm se a AF for elaborada à escala de 10%); respeitar área de segurança virtual para evitar corte de elementos na afixação; sempre que possível, enviar com prova de cor. Após receção, a JCDecaux envia um JPG para validação final antes de imprimir; após aprovação, declina responsabilidade por desformatações/falhas na imagem. Critérios de qualidade: opacidade ≥88%, brancura 91-93 ISO, absorção de água (cobb60) 15-30g/m², absorção de água (cobb300) &lt;70g/m², distensão máx. ±2%/m, resistência à rutura por tração (húmido) &gt;0,6kN/m — materiais fora destes requisitos podem não ser afixados. Especificações ambientais: papel com certificação PEFC/FSC (ou equivalente); tintas conformes REACH/GreenGuard, isentas de metais pesados; papel reciclado, sem cloro (ECF/TCF).</t>
         </is>
       </c>
-      <c r="M368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -20133,11 +20022,6 @@
           <t>JCDecaux</t>
         </is>
       </c>
-      <c r="E369" t="inlineStr">
-        <is>
-          <t>Billboard</t>
-        </is>
-      </c>
       <c r="F369" t="inlineStr">
         <is>
           <t>Impressão Senior</t>
@@ -20148,20 +20032,16 @@
           <t>Área visível: 3020x2230mm. Área total: 3200x2350mm.</t>
         </is>
       </c>
-      <c r="H369" t="inlineStr"/>
-      <c r="I369" t="inlineStr"/>
       <c r="J369" t="inlineStr">
         <is>
           <t>Papel, gramagem 150g, verso do cartaz com fundo branco. Ficheiro: Illustrator, Photoshop, PDF, EPS ou TIFF.</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
       <c r="L369" t="inlineStr">
         <is>
           <t>Impressão em 1, 2 ou 4 folhas, entregues alceadas por ordem de colagem (a começar na folha 1, com o verso para baixo). Impressão em 2 folhas: folha 1 3200x1200mm (aparada 3130x1150mm) + folha 2 idêntica, margem de sobreposição 25mm/35mm. Impressão em 4 folhas: 1600x1200mm por folha (aparada 1530x1175mm), aparadas à medida sem margem entre si. Prazo: 7 dias úteis após aprovação da Arte Final. Ficheiro: Illustrator/Photoshop (incluir fontes e respetivos links) ou PDF (cores/perfis embebidos/resolução de imagens, texto em curvas); impressão offset CMYK 300-400 dpi, digital CMYK 150-200 dpi; medida indicada + 3cm de bleed (3mm à escala de 10%); respeitar área de segurança virtual; enviar com prova de cor sempre que possível. Entrega nas instalações da JCDecaux 5 dias úteis antes do início da campanha, com impressão da campanha e guia de transporte certificada; horário de entrega 07h-12h e 13h30-16h (Portão 2), Beco da Aviação nº1, Granja do Alpriate, Vialonga. Após receção, a JCDecaux envia JPG para validação; após aprovação, declina responsabilidade por falhas na imagem. Critérios de qualidade: opacidade ≥88%, brancura 91-93 ISO, absorção água (cobb60) 15-30g/m², (cobb300) &lt;70g/m², distensão máx. ±2%/m, resistência à rutura (húmido) &gt;0,6kN/m.</t>
         </is>
       </c>
-      <c r="M369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -20184,11 +20064,6 @@
           <t>JCDecaux</t>
         </is>
       </c>
-      <c r="E370" t="inlineStr">
-        <is>
-          <t>Mupi</t>
-        </is>
-      </c>
       <c r="F370" t="inlineStr">
         <is>
           <t>Mupi Digital</t>
@@ -20204,19 +20079,16 @@
           <t>9:16</t>
         </is>
       </c>
-      <c r="I370" t="inlineStr"/>
       <c r="J370" t="inlineStr">
         <is>
           <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000.</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
       <c r="L370" t="inlineStr">
         <is>
           <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Após envio, a JCDecaux declina responsabilidade por falhas no vídeo apresentado. Alterações ao vídeo carecem de aprovação final do cliente; a JCDecaux não se responsabiliza por atraso na entrega (sem compensação de airing).</t>
         </is>
       </c>
-      <c r="M370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -20239,11 +20111,6 @@
           <t>JCDecaux</t>
         </is>
       </c>
-      <c r="E371" t="inlineStr">
-        <is>
-          <t>Mupi</t>
-        </is>
-      </c>
       <c r="F371" t="inlineStr">
         <is>
           <t>Mupi Digital (Shopping)</t>
@@ -20259,19 +20126,16 @@
           <t>16:9 (ficheiro) / 9:16 (exibição)</t>
         </is>
       </c>
-      <c r="I371" t="inlineStr"/>
       <c r="J371" t="inlineStr">
         <is>
           <t>Ficheiro nativo (compressão nativa), bitrate máx. 20.000.</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
       <c r="L371" t="inlineStr">
         <is>
           <t>Duração do spot: 10 segundos, dentro de um loop de 60 segundos com outros anunciantes. Enviar o vídeo 2 dias antes do início da campanha, por e-mail para o contacto JCDecaux. Alterações carecem de aprovação final do cliente; a JCDecaux declina responsabilidade por falhas no vídeo após o envio, e não se responsabiliza por atraso na entrega.</t>
         </is>
       </c>
-      <c r="M371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -20294,11 +20158,6 @@
           <t>JCDecaux</t>
         </is>
       </c>
-      <c r="E372" t="inlineStr">
-        <is>
-          <t>Billboard</t>
-        </is>
-      </c>
       <c r="F372" t="inlineStr">
         <is>
           <t>Painel 8x3 - Papel</t>
@@ -20309,20 +20168,16 @@
           <t>Área total: 8000x3000mm. Área visível: 7500x2750mm.</t>
         </is>
       </c>
-      <c r="H372" t="inlineStr"/>
-      <c r="I372" t="inlineStr"/>
       <c r="J372" t="inlineStr">
         <is>
           <t>Papel, gramagem entre 120g e 170g, verso do cartaz com fundo azul. Ficheiro: Illustrator, Photoshop, PDF, EPS ou TIFF.</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
       <c r="L372" t="inlineStr">
         <is>
           <t>Prazo: 7 dias úteis após aprovação da Arte Final. Impressão em 12, 14 ou 16 folhas, entregues alceadas (a começar na folha 1, verso para baixo), numeradas no canto superior direito. Impressão em 14 folhas: folhas superiores 1-6 (997mm cada) + folha 7 (997mm), folhas inferiores 9-13 (1135mm cada) + folha 14 (1135mm); margem de sobreposição 25mm à direita nas folhas superiores (exceto a última) e 25mm à direita + no topo nas inferiores (exceto a última, só no topo); áreas de sobreposição isentas de impressão. Impressão em 16 folhas: superiores 1-7 (997mm) + folha 8 (997mm), inferiores 9-15 (997mm) + folha 16 (997mm), mesmas regras de margem. Se PDF: cores/perfis embebidos/resolução de imagens, texto em curvas; impressão offset CMYK 300-400 dpi, digital CMYK 150-200 dpi; medida indicada + 3cm de bleed (3mm à escala de 10%); área de segurança virtual; prova de cor recomendada. Entrega nas instalações JCDecaux, Portão 1, Beco da Aviação nº1, Granja do Alpriate, Vialonga, 07h-12h/13h30-16h. Após receção, JCDecaux envia JPG para validação; após aprovação, declina responsabilidade por falhas na imagem.</t>
         </is>
       </c>
-      <c r="M372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -20345,11 +20200,6 @@
           <t>JCDecaux</t>
         </is>
       </c>
-      <c r="E373" t="inlineStr">
-        <is>
-          <t>Billboard</t>
-        </is>
-      </c>
       <c r="F373" t="inlineStr">
         <is>
           <t>Painel 8x3 - Vinil</t>
@@ -20360,20 +20210,16 @@
           <t>Área total: 8000x3000mm. Área visível: 8000x3000mm (sem margem).</t>
         </is>
       </c>
-      <c r="H373" t="inlineStr"/>
-      <c r="I373" t="inlineStr"/>
       <c r="J373" t="inlineStr">
         <is>
           <t>Vinil PVC branco ou transparente, superfície brilhante ou mate, polyacrylate removível e transparente; base em papel revestido a silicone 135g/m². Ficheiro: Illustrator, Photoshop, PDF, EPS ou TIFF.</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr"/>
       <c r="L373" t="inlineStr">
         <is>
           <t>Uso recomendado: outdoors de curta e média duração. Método de impressão: tintas de base solvente, UV ou látex. Prazo: 7 dias úteis após aprovação da Arte Final. Impressão em 8 folhas de 1000mm cada, enroladas por ordem (folha 1 a 8), numeradas no canto superior direito; margem de sobreposição 25mm à direita em todas as folhas (áreas de sobreposição isentas de impressão). Se PDF: cores/perfis embebidos/resolução de imagens, texto em curvas; impressão offset CMYK 300-400 dpi, digital CMYK 150-200 dpi; medida indicada + 5cm de bleed (5mm à escala de 10%); área de segurança virtual; prova de cor recomendada. Entrega nas instalações JCDecaux, Portão 1, Beco da Aviação nº1, Granja do Alpriate, Vialonga, 5 dias úteis antes do início da campanha, com impressão da campanha e guia de transporte certificada, 07h-12h/13h30-16h. Após receção, JCDecaux envia JPG para validação; após aprovação, declina responsabilidade por falhas na imagem.</t>
         </is>
       </c>
-      <c r="M373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -20396,11 +20242,6 @@
           <t>JCDecaux</t>
         </is>
       </c>
-      <c r="E374" t="inlineStr">
-        <is>
-          <t>Billboard</t>
-        </is>
-      </c>
       <c r="F374" t="inlineStr">
         <is>
           <t>Premium LED 6m²</t>
@@ -20416,19 +20257,16 @@
           <t>2:3</t>
         </is>
       </c>
-      <c r="I374" t="inlineStr"/>
       <c r="J374" t="inlineStr">
         <is>
           <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000.</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
       <c r="L374" t="inlineStr">
         <is>
           <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 4 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
         </is>
       </c>
-      <c r="M374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -20451,11 +20289,6 @@
           <t>JCDecaux</t>
         </is>
       </c>
-      <c r="E375" t="inlineStr">
-        <is>
-          <t>Billboard</t>
-        </is>
-      </c>
       <c r="F375" t="inlineStr">
         <is>
           <t>Premium LED 8m²</t>
@@ -20471,19 +20304,16 @@
           <t>9:16</t>
         </is>
       </c>
-      <c r="I375" t="inlineStr"/>
       <c r="J375" t="inlineStr">
         <is>
           <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000.</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
       <c r="L375" t="inlineStr">
         <is>
           <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
         </is>
       </c>
-      <c r="M375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -20506,11 +20336,6 @@
           <t>JCDecaux</t>
         </is>
       </c>
-      <c r="E376" t="inlineStr">
-        <is>
-          <t>Billboard</t>
-        </is>
-      </c>
       <c r="F376" t="inlineStr">
         <is>
           <t>Premium LED 12m²</t>
@@ -20526,19 +20351,16 @@
           <t>1.91:1</t>
         </is>
       </c>
-      <c r="I376" t="inlineStr"/>
       <c r="J376" t="inlineStr">
         <is>
           <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000.</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
       <c r="L376" t="inlineStr">
         <is>
           <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
         </is>
       </c>
-      <c r="M376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -20561,11 +20383,6 @@
           <t>JCDecaux</t>
         </is>
       </c>
-      <c r="E377" t="inlineStr">
-        <is>
-          <t>Billboard</t>
-        </is>
-      </c>
       <c r="F377" t="inlineStr">
         <is>
           <t>Premium LED 15m²</t>
@@ -20581,19 +20398,16 @@
           <t>9:16</t>
         </is>
       </c>
-      <c r="I377" t="inlineStr"/>
       <c r="J377" t="inlineStr">
         <is>
           <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000.</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
       <c r="L377" t="inlineStr">
         <is>
           <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
         </is>
       </c>
-      <c r="M377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -20616,11 +20430,6 @@
           <t>JCDecaux</t>
         </is>
       </c>
-      <c r="E378" t="inlineStr">
-        <is>
-          <t>Billboard</t>
-        </is>
-      </c>
       <c r="F378" t="inlineStr">
         <is>
           <t>Premium LED 18m²</t>
@@ -20636,19 +20445,16 @@
           <t>9:16</t>
         </is>
       </c>
-      <c r="I378" t="inlineStr"/>
       <c r="J378" t="inlineStr">
         <is>
           <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000.</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
       <c r="L378" t="inlineStr">
         <is>
           <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
         </is>
       </c>
-      <c r="M378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -20671,11 +20477,6 @@
           <t>JCDecaux</t>
         </is>
       </c>
-      <c r="E379" t="inlineStr">
-        <is>
-          <t>Billboard</t>
-        </is>
-      </c>
       <c r="F379" t="inlineStr">
         <is>
           <t>Premium LED 22m²</t>
@@ -20686,20 +20487,16 @@
           <t>1248x800px.</t>
         </is>
       </c>
-      <c r="H379" t="inlineStr"/>
-      <c r="I379" t="inlineStr"/>
       <c r="J379" t="inlineStr">
         <is>
           <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000.</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
       <c r="L379" t="inlineStr">
         <is>
           <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. Vídeo em estilo "Subtle Motion" recomendado: movimento lento e gradual dos elementos criativos (slow motion sem cortes bruscos; fundos deslocados/ampliados lentamente em vez de intermitentes; texto a desvanecer gradualmente em vez de deslizar/pulsar; luzes a brilhar em vez de piscar); marca visível em pelo menos 80% da criatividade. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
         </is>
       </c>
-      <c r="M379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -20722,11 +20519,6 @@
           <t>JCDecaux</t>
         </is>
       </c>
-      <c r="E380" t="inlineStr">
-        <is>
-          <t>Billboard</t>
-        </is>
-      </c>
       <c r="F380" t="inlineStr">
         <is>
           <t>Premium LED 25m²</t>
@@ -20737,20 +20529,16 @@
           <t>480x810px.</t>
         </is>
       </c>
-      <c r="H380" t="inlineStr"/>
-      <c r="I380" t="inlineStr"/>
       <c r="J380" t="inlineStr">
         <is>
           <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000.</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
       <c r="L380" t="inlineStr">
         <is>
           <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
         </is>
       </c>
-      <c r="M380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -20773,11 +20561,6 @@
           <t>JCDecaux</t>
         </is>
       </c>
-      <c r="E381" t="inlineStr">
-        <is>
-          <t>Billboard</t>
-        </is>
-      </c>
       <c r="F381" t="inlineStr">
         <is>
           <t>Premium LED 37m²</t>
@@ -20788,20 +20571,16 @@
           <t>480x738px.</t>
         </is>
       </c>
-      <c r="H381" t="inlineStr"/>
-      <c r="I381" t="inlineStr"/>
       <c r="J381" t="inlineStr">
         <is>
           <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000.</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
       <c r="L381" t="inlineStr">
         <is>
           <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 16,7%. Vídeo em estilo "Subtle Motion" recomendado (ver formato "Premium LED 22m²" para guidelines completas). A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
         </is>
       </c>
-      <c r="M381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -20824,11 +20603,6 @@
           <t>Táxi Advertising</t>
         </is>
       </c>
-      <c r="E382" t="inlineStr">
-        <is>
-          <t>Decoração</t>
-        </is>
-      </c>
       <c r="F382" t="inlineStr">
         <is>
           <t>Decoração de Táxi</t>
@@ -20839,20 +20613,16 @@
           <t>Manter o tamanho original do template (ficheiros vetoriais reais fornecidos pelo fornecedor, com o desenho do lado esquerdo e do lado direito do táxi).</t>
         </is>
       </c>
-      <c r="H382" t="inlineStr"/>
-      <c r="I382" t="inlineStr"/>
       <c r="J382" t="inlineStr">
         <is>
           <t>Ficheiros de trabalho em Illustrator (vetoriais). Entrega: JPG ou PDF.</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr"/>
       <c r="L382" t="inlineStr">
         <is>
           <t>O texto deve manter-se dentro da linha amarela de segurança (para não ser cortado). O fundo atrás do texto deve ultrapassar a linha branca em pelo menos 50mm de bleed. Impressão em CMYK, resolução 150 pixels/polegada. É obrigatório enviar também um PDF com a maqueta da decoração do táxi, para orientação da colagem do vinil.</t>
         </is>
       </c>
-      <c r="M382" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M382"/>
+  <dimension ref="A1:M506"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="18.08984375" customWidth="1" style="2" min="1" max="1"/>
@@ -20624,6 +20624,5834 @@
         </is>
       </c>
     </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Correio da Manhã</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Correio da Manhã</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr"/>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>Página</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>257x320mm (80 módulos, 5 col. x 16 mód.)</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr"/>
+      <c r="I383" t="inlineStr"/>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K383" t="inlineStr"/>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 colunas x 16 módulos); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M383" t="inlineStr"/>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Correio da Manhã</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Correio da Manhã</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr"/>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>Meia Página</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>204x240mm (48 módulos, 4 col. x 12 mód.)</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr"/>
+      <c r="I384" t="inlineStr"/>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K384" t="inlineStr"/>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 colunas x 16 módulos); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M384" t="inlineStr"/>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Correio da Manhã</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Correio da Manhã</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr"/>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>1/2 Página Alto (3 Col.)</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>153x320mm (48 módulos, 3 col. x 16 mód.)</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr"/>
+      <c r="I385" t="inlineStr"/>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K385" t="inlineStr"/>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 colunas x 16 módulos); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M385" t="inlineStr"/>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Correio da Manhã</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Correio da Manhã</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr"/>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>1/3 Página Alto (2 Col.)</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>100x320mm (32 módulos, 2 col. x 16 mód.)</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr"/>
+      <c r="I386" t="inlineStr"/>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K386" t="inlineStr"/>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 colunas x 16 módulos); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M386" t="inlineStr"/>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Correio da Manhã</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Correio da Manhã</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr"/>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>1/2 Página Baixo</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>257x160mm (40 módulos, 5 col. x 8 mód.)</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr"/>
+      <c r="I387" t="inlineStr"/>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K387" t="inlineStr"/>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 colunas x 16 módulos); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M387" t="inlineStr"/>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Correio da Manhã</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Correio da Manhã</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr"/>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>1/4 Página (3 Col.)</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>153x160mm (24 módulos, 3 col. x 8 mód.)</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr"/>
+      <c r="I388" t="inlineStr"/>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K388" t="inlineStr"/>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 colunas x 16 módulos); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M388" t="inlineStr"/>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Correio da Manhã</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Correio da Manhã</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr"/>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>1/4 Página (2 Col.)</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>100x160mm (16 módulos, 2 col. x 8 mód.)</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr"/>
+      <c r="I389" t="inlineStr"/>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K389" t="inlineStr"/>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 colunas x 16 módulos); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M389" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Correio da Manhã</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Correio da Manhã</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr"/>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>Rodapé</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>257x61mm (15 módulos, 5 col. x 3 mód.)</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr"/>
+      <c r="I390" t="inlineStr"/>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K390" t="inlineStr"/>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 colunas x 16 módulos); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M390" t="inlineStr"/>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Correio da Manhã</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Mais Sport</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr"/>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>Página</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>257x320mm (80 módulos, 5 col. x 16 mód.)</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr"/>
+      <c r="I391" t="inlineStr"/>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr"/>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 257x320mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M391" t="inlineStr"/>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Correio da Manhã</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Boa Onda</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr"/>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>Página Dupla</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>400x295mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr"/>
+      <c r="I392" t="inlineStr"/>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr"/>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>Periodicidade semanal (sexta-feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M392" t="inlineStr"/>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Correio da Manhã</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Boa Onda</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr"/>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>Página</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>200x295mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr"/>
+      <c r="I393" t="inlineStr"/>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K393" t="inlineStr"/>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>Periodicidade semanal (sexta-feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M393" t="inlineStr"/>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Correio da Manhã</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Boa Onda</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr"/>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>1/2 Página Dupla</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>400x147mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr"/>
+      <c r="I394" t="inlineStr"/>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K394" t="inlineStr"/>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>Periodicidade semanal (sexta-feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M394" t="inlineStr"/>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Correio da Manhã</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Boa Onda</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr"/>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>1/2 Página Alto</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>100x295mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr"/>
+      <c r="I395" t="inlineStr"/>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K395" t="inlineStr"/>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>Periodicidade semanal (sexta-feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M395" t="inlineStr"/>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Correio da Manhã</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Boa Onda</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr"/>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>1/2 Página Baixo</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>200x147mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr"/>
+      <c r="I396" t="inlineStr"/>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K396" t="inlineStr"/>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>Periodicidade semanal (sexta-feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M396" t="inlineStr"/>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Correio da Manhã</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>Boa Onda</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr"/>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>1/3 Página Alto</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>72x295mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr"/>
+      <c r="I397" t="inlineStr"/>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K397" t="inlineStr"/>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>Periodicidade semanal (sexta-feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M397" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Correio da Manhã</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Boa Onda</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr"/>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>1/3 Página Baixo</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>200x105mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr"/>
+      <c r="I398" t="inlineStr"/>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K398" t="inlineStr"/>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>Periodicidade semanal (sexta-feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M398" t="inlineStr"/>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Correio da Manhã</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Boa Onda</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr"/>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>1/4 Página</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>100x147mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr"/>
+      <c r="I399" t="inlineStr"/>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K399" t="inlineStr"/>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>Periodicidade semanal (sexta-feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M399" t="inlineStr"/>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Correio da Manhã</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Boa Onda</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr"/>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>Rodapé</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>200x78mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr"/>
+      <c r="I400" t="inlineStr"/>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K400" t="inlineStr"/>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>Periodicidade semanal (sexta-feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M400" t="inlineStr"/>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Correio da Manhã</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>VIDAS</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr"/>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>Página Dupla</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>400x295mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr"/>
+      <c r="I401" t="inlineStr"/>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K401" t="inlineStr"/>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M401" t="inlineStr"/>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Correio da Manhã</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>VIDAS</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr"/>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>Página</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>200x295mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr"/>
+      <c r="I402" t="inlineStr"/>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K402" t="inlineStr"/>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M402" t="inlineStr"/>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Correio da Manhã</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>VIDAS</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr"/>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>1/2 Página Dupla</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>400x147mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr"/>
+      <c r="I403" t="inlineStr"/>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K403" t="inlineStr"/>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M403" t="inlineStr"/>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Correio da Manhã</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>VIDAS</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr"/>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>1/2 Página Alto</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>100x295mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr"/>
+      <c r="I404" t="inlineStr"/>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K404" t="inlineStr"/>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M404" t="inlineStr"/>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Correio da Manhã</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>VIDAS</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr"/>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>1/2 Página Baixo</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>200x147mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr"/>
+      <c r="I405" t="inlineStr"/>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K405" t="inlineStr"/>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M405" t="inlineStr"/>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Correio da Manhã</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>VIDAS</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr"/>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>1/3 Página Alto</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>72x295mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr"/>
+      <c r="I406" t="inlineStr"/>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K406" t="inlineStr"/>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M406" t="inlineStr"/>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Correio da Manhã</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>VIDAS</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr"/>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>1/3 Página Baixo</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>200x105mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr"/>
+      <c r="I407" t="inlineStr"/>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K407" t="inlineStr"/>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M407" t="inlineStr"/>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Correio da Manhã</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>VIDAS</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr"/>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>1/4 Página</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>100x147mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr"/>
+      <c r="I408" t="inlineStr"/>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K408" t="inlineStr"/>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M408" t="inlineStr"/>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Correio da Manhã</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>VIDAS</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr"/>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>Rodapé</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>200x78mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr"/>
+      <c r="I409" t="inlineStr"/>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K409" t="inlineStr"/>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M409" t="inlineStr"/>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Correio da Manhã</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Domingo</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr"/>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>Página Dupla</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>400x295mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr"/>
+      <c r="I410" t="inlineStr"/>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr"/>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>Periodicidade semanal (domingo); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M410" t="inlineStr"/>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Correio da Manhã</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Domingo</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr"/>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>Página</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>200x295mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr"/>
+      <c r="I411" t="inlineStr"/>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K411" t="inlineStr"/>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>Periodicidade semanal (domingo); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M411" t="inlineStr"/>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Correio da Manhã</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Domingo</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr"/>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>1/2 Página Dupla</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>400x147mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr"/>
+      <c r="I412" t="inlineStr"/>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr"/>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>Periodicidade semanal (domingo); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M412" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Correio da Manhã</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Domingo</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr"/>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>1/2 Página Alto</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>100x295mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr"/>
+      <c r="I413" t="inlineStr"/>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K413" t="inlineStr"/>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>Periodicidade semanal (domingo); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M413" t="inlineStr"/>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Correio da Manhã</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Domingo</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr"/>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>1/2 Página Baixo</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>200x147mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr"/>
+      <c r="I414" t="inlineStr"/>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr"/>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>Periodicidade semanal (domingo); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M414" t="inlineStr"/>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Correio da Manhã</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Domingo</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr"/>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>1/3 Página Alto</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>72x295mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr"/>
+      <c r="I415" t="inlineStr"/>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr"/>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>Periodicidade semanal (domingo); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M415" t="inlineStr"/>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Correio da Manhã</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Domingo</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr"/>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>1/3 Página Baixo</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>200x105mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr"/>
+      <c r="I416" t="inlineStr"/>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K416" t="inlineStr"/>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>Periodicidade semanal (domingo); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M416" t="inlineStr"/>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Correio da Manhã</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Domingo</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr"/>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>1/4 Página</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>100x147mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr"/>
+      <c r="I417" t="inlineStr"/>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr"/>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>Periodicidade semanal (domingo); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M417" t="inlineStr"/>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Correio da Manhã</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Domingo</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr"/>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>Rodapé</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>200x78mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr"/>
+      <c r="I418" t="inlineStr"/>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr"/>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>Periodicidade semanal (domingo); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr"/>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Destak</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Destak</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr"/>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>Capa Falsa</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>210x280mm | 230x300mm (corte)</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr"/>
+      <c r="I419" t="inlineStr"/>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
+        </is>
+      </c>
+      <c r="K419" t="inlineStr"/>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M419" t="inlineStr"/>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Destak</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Destak</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr"/>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>Rodapé 1ª Página</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>210x42mm</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr"/>
+      <c r="I420" t="inlineStr"/>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
+        </is>
+      </c>
+      <c r="K420" t="inlineStr"/>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M420" t="inlineStr"/>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Destak</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Destak</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr"/>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>Janela Premium</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>49,5x78,5mm</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr"/>
+      <c r="I421" t="inlineStr"/>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr"/>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M421" t="inlineStr"/>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Destak</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Destak</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr"/>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>Página Dupla</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>440x280mm | 460x300mm (corte)</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr"/>
+      <c r="I422" t="inlineStr"/>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
+        </is>
+      </c>
+      <c r="K422" t="inlineStr"/>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M422" t="inlineStr"/>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Destak</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Destak</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr"/>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>Página</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>210x280mm | 230x300mm (corte)</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr"/>
+      <c r="I423" t="inlineStr"/>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
+        </is>
+      </c>
+      <c r="K423" t="inlineStr"/>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M423" t="inlineStr"/>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Destak</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Destak</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr"/>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>Contracapa</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>210x280mm | 230x300mm (corte)</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr"/>
+      <c r="I424" t="inlineStr"/>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
+        </is>
+      </c>
+      <c r="K424" t="inlineStr"/>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M424" t="inlineStr"/>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Destak</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Destak</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr"/>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>1/2 Página Alto</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>103x280mm</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr"/>
+      <c r="I425" t="inlineStr"/>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
+        </is>
+      </c>
+      <c r="K425" t="inlineStr"/>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M425" t="inlineStr"/>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Destak</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>Destak</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr"/>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>1/2 Página Baixo</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>210x138mm</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr"/>
+      <c r="I426" t="inlineStr"/>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
+        </is>
+      </c>
+      <c r="K426" t="inlineStr"/>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M426" t="inlineStr"/>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Destak</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>Destak</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr"/>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>3/4 Página</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>103x138mm</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr"/>
+      <c r="I427" t="inlineStr"/>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
+        </is>
+      </c>
+      <c r="K427" t="inlineStr"/>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M427" t="inlineStr"/>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>Destak</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Destak</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr"/>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>Rodapé</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>210x42mm</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr"/>
+      <c r="I428" t="inlineStr"/>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
+        </is>
+      </c>
+      <c r="K428" t="inlineStr"/>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M428" t="inlineStr"/>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Jornal de Negócios</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>Jornal de Negócios</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr"/>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>Página</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>257x320mm (80 módulos, 5 col. x 16 mód.)</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr"/>
+      <c r="I429" t="inlineStr"/>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K429" t="inlineStr"/>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>Periodicidade diária (2ª feira a 6ª feira); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M429" t="inlineStr"/>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Jornal de Negócios</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>Jornal de Negócios</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr"/>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>Meia Página</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>204x240mm (48 módulos, 4 col. x 12 mód.)</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr"/>
+      <c r="I430" t="inlineStr"/>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K430" t="inlineStr"/>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>Periodicidade diária (2ª feira a 6ª feira); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M430" t="inlineStr"/>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Jornal de Negócios</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Jornal de Negócios</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr"/>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>1/2 Página Alto (3 Col.)</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>153x320mm (48 módulos, 3 col. x 16 mód.)</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr"/>
+      <c r="I431" t="inlineStr"/>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K431" t="inlineStr"/>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>Periodicidade diária (2ª feira a 6ª feira); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M431" t="inlineStr"/>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Jornal de Negócios</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>Jornal de Negócios</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr"/>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>1/3 Página Alto (2 Col.)</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>100x320mm (32 módulos, 2 col. x 16 mód.)</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr"/>
+      <c r="I432" t="inlineStr"/>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K432" t="inlineStr"/>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>Periodicidade diária (2ª feira a 6ª feira); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M432" t="inlineStr"/>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Jornal de Negócios</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>Jornal de Negócios</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr"/>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>1/2 Página Baixo</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>257x160mm (40 módulos, 5 col. x 8 mód.)</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr"/>
+      <c r="I433" t="inlineStr"/>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K433" t="inlineStr"/>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>Periodicidade diária (2ª feira a 6ª feira); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M433" t="inlineStr"/>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Jornal de Negócios</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>Jornal de Negócios</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr"/>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>1/4 Página (3 Col.)</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>153x160mm (24 módulos, 3 col. x 8 mód.)</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr"/>
+      <c r="I434" t="inlineStr"/>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K434" t="inlineStr"/>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>Periodicidade diária (2ª feira a 6ª feira); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M434" t="inlineStr"/>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Jornal de Negócios</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>Jornal de Negócios</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr"/>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>1/4 Página (2 Col.)</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>100x160mm (16 módulos, 2 col. x 8 mód.)</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr"/>
+      <c r="I435" t="inlineStr"/>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K435" t="inlineStr"/>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>Periodicidade diária (2ª feira a 6ª feira); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M435" t="inlineStr"/>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Jornal de Negócios</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>Jornal de Negócios</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr"/>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>Rodapé</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>257x61mm (15 módulos, 5 col. x 3 mód.)</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr"/>
+      <c r="I436" t="inlineStr"/>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K436" t="inlineStr"/>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>Periodicidade diária (2ª feira a 6ª feira); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M436" t="inlineStr"/>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>Jornal de Negócios</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Jornal de Negócios</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr"/>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>Janela de Primeira Página</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>55x96mm</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr"/>
+      <c r="I437" t="inlineStr"/>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K437" t="inlineStr"/>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>Formato especial na 1ª página ou última página do 1º Caderno. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M437" t="inlineStr"/>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>Jornal de Negócios</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Jornal de Negócios</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr"/>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>Orelha de Primeira Página</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>55x45mm</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr"/>
+      <c r="I438" t="inlineStr"/>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K438" t="inlineStr"/>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>Formato especial na 1ª página ou última página do 1º Caderno. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M438" t="inlineStr"/>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>Jornal de Negócios</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Jornal de Negócios</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr"/>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>Rodapé de Primeira Página</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>195x25mm</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr"/>
+      <c r="I439" t="inlineStr"/>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K439" t="inlineStr"/>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>Formato especial na 1ª página ou última página do 1º Caderno. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M439" t="inlineStr"/>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>Jornal de Negócios</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Jornal de Negócios</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr"/>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>Home Page (Quadrado 2ª Página)</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>150x130mm</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr"/>
+      <c r="I440" t="inlineStr"/>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K440" t="inlineStr"/>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>Formato especial na 1ª página ou última página do 1º Caderno. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M440" t="inlineStr"/>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>Jornal de Negócios</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>Jornal de Negócios</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr"/>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>Rodapé Última Página</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>205x61mm</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr"/>
+      <c r="I441" t="inlineStr"/>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr"/>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>Formato especial na 1ª página ou última página do 1º Caderno. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M441" t="inlineStr"/>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr"/>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>Página</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>257x320mm (80 módulos, 5 col. x 16 mód.)</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr"/>
+      <c r="I442" t="inlineStr"/>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr"/>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M442" t="inlineStr"/>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr"/>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>Meia Página</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>204x240mm (48 módulos, 4 col. x 12 mód.)</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr"/>
+      <c r="I443" t="inlineStr"/>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr"/>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M443" t="inlineStr"/>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr"/>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>1/2 Página Alto (3 Col.)</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>153x320mm (48 módulos, 3 col. x 16 mód.)</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr"/>
+      <c r="I444" t="inlineStr"/>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr"/>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M444" t="inlineStr"/>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr"/>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>1/3 Página Alto (2 Col.)</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>100x320mm (32 módulos, 2 col. x 16 mód.)</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr"/>
+      <c r="I445" t="inlineStr"/>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K445" t="inlineStr"/>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M445" t="inlineStr"/>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr"/>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>1/2 Página Baixo</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>257x160mm (40 módulos, 5 col. x 8 mód.)</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr"/>
+      <c r="I446" t="inlineStr"/>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K446" t="inlineStr"/>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M446" t="inlineStr"/>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr"/>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>1/4 Página (3 Col.)</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>153x160mm (24 módulos, 3 col. x 8 mód.)</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr"/>
+      <c r="I447" t="inlineStr"/>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K447" t="inlineStr"/>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M447" t="inlineStr"/>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr"/>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>1/4 Página (2 Col.)</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>100x160mm (16 módulos, 2 col. x 8 mód.)</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr"/>
+      <c r="I448" t="inlineStr"/>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K448" t="inlineStr"/>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M448" t="inlineStr"/>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr"/>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>Rodapé</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>257x61mm (15 módulos, 5 col. x 3 mód.)</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr"/>
+      <c r="I449" t="inlineStr"/>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K449" t="inlineStr"/>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M449" t="inlineStr"/>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr"/>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>Página Dupla</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>410x275mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr"/>
+      <c r="I450" t="inlineStr"/>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K450" t="inlineStr"/>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>Periodicidade semanal (5ª feira); distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M450" t="inlineStr"/>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr"/>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>Página</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>205x275mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr"/>
+      <c r="I451" t="inlineStr"/>
+      <c r="J451" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K451" t="inlineStr"/>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>Periodicidade semanal (5ª feira); distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M451" t="inlineStr"/>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr"/>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>1/2 Página Dupla</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>410x137mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr"/>
+      <c r="I452" t="inlineStr"/>
+      <c r="J452" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K452" t="inlineStr"/>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>Periodicidade semanal (5ª feira); distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M452" t="inlineStr"/>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr"/>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>1/2 Página Alto</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>102x275mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr"/>
+      <c r="I453" t="inlineStr"/>
+      <c r="J453" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K453" t="inlineStr"/>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>Periodicidade semanal (5ª feira); distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M453" t="inlineStr"/>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr"/>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>1/2 Página Baixo</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>205x137mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr"/>
+      <c r="I454" t="inlineStr"/>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K454" t="inlineStr"/>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>Periodicidade semanal (5ª feira); distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M454" t="inlineStr"/>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr"/>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>1/3 Página Alto</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>72x275mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr"/>
+      <c r="I455" t="inlineStr"/>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K455" t="inlineStr"/>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>Periodicidade semanal (5ª feira); distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M455" t="inlineStr"/>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr"/>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>1/3 Página Baixo</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>205x91mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr"/>
+      <c r="I456" t="inlineStr"/>
+      <c r="J456" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K456" t="inlineStr"/>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>Periodicidade semanal (5ª feira); distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M456" t="inlineStr"/>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>Sábado Viajante</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr"/>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>Página Dupla</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>410x275mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr"/>
+      <c r="I457" t="inlineStr"/>
+      <c r="J457" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K457" t="inlineStr"/>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>Periodicidade trimestral; distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M457" t="inlineStr"/>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>Sábado Viajante</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr"/>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>Página</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>205x275mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr"/>
+      <c r="I458" t="inlineStr"/>
+      <c r="J458" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K458" t="inlineStr"/>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t>Periodicidade trimestral; distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M458" t="inlineStr"/>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>Sábado Viajante</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr"/>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>1/2 Página Dupla</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>410x137mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr"/>
+      <c r="I459" t="inlineStr"/>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K459" t="inlineStr"/>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t>Periodicidade trimestral; distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M459" t="inlineStr"/>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>Sábado Viajante</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr"/>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>1/2 Página Alto</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>102x275mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr"/>
+      <c r="I460" t="inlineStr"/>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K460" t="inlineStr"/>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>Periodicidade trimestral; distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M460" t="inlineStr"/>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>Sábado Viajante</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr"/>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>1/2 Página Baixo</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>205x137mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr"/>
+      <c r="I461" t="inlineStr"/>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K461" t="inlineStr"/>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t>Periodicidade trimestral; distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M461" t="inlineStr"/>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>Sábado Viajante</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr"/>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>1/3 Página Alto</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>72x275mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr"/>
+      <c r="I462" t="inlineStr"/>
+      <c r="J462" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K462" t="inlineStr"/>
+      <c r="L462" t="inlineStr">
+        <is>
+          <t>Periodicidade trimestral; distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M462" t="inlineStr"/>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>Sábado Viajante</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr"/>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>1/3 Página Baixo</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>205x91mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr"/>
+      <c r="I463" t="inlineStr"/>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K463" t="inlineStr"/>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t>Periodicidade trimestral; distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M463" t="inlineStr"/>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>TV Guia</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>TV Guia</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr"/>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>Página Dupla</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>400x295mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr"/>
+      <c r="I464" t="inlineStr"/>
+      <c r="J464" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K464" t="inlineStr"/>
+      <c r="L464" t="inlineStr">
+        <is>
+          <t>Periodicidade semanal (6ª feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo LWC 57g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M464" t="inlineStr"/>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>TV Guia</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>TV Guia</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr"/>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>Página</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>200x295mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr"/>
+      <c r="I465" t="inlineStr"/>
+      <c r="J465" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K465" t="inlineStr"/>
+      <c r="L465" t="inlineStr">
+        <is>
+          <t>Periodicidade semanal (6ª feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo LWC 57g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M465" t="inlineStr"/>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>TV Guia</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>TV Guia</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr"/>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>1/2 Página Dupla</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>400x147mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr"/>
+      <c r="I466" t="inlineStr"/>
+      <c r="J466" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K466" t="inlineStr"/>
+      <c r="L466" t="inlineStr">
+        <is>
+          <t>Periodicidade semanal (6ª feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo LWC 57g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M466" t="inlineStr"/>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>TV Guia</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>TV Guia</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr"/>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>1/2 Página Alto</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>100x295mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr"/>
+      <c r="I467" t="inlineStr"/>
+      <c r="J467" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K467" t="inlineStr"/>
+      <c r="L467" t="inlineStr">
+        <is>
+          <t>Periodicidade semanal (6ª feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo LWC 57g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M467" t="inlineStr"/>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>TV Guia</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>TV Guia</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr"/>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>1/2 Página Baixo</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>200x147mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr"/>
+      <c r="I468" t="inlineStr"/>
+      <c r="J468" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K468" t="inlineStr"/>
+      <c r="L468" t="inlineStr">
+        <is>
+          <t>Periodicidade semanal (6ª feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo LWC 57g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M468" t="inlineStr"/>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>TV Guia</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>TV Guia</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr"/>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>1/3 Página Alto</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>72x295mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr"/>
+      <c r="I469" t="inlineStr"/>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K469" t="inlineStr"/>
+      <c r="L469" t="inlineStr">
+        <is>
+          <t>Periodicidade semanal (6ª feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo LWC 57g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M469" t="inlineStr"/>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>TV Guia</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>TV Guia</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr"/>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>1/3 Página Baixo</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>200x105mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr"/>
+      <c r="I470" t="inlineStr"/>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+        </is>
+      </c>
+      <c r="K470" t="inlineStr"/>
+      <c r="L470" t="inlineStr">
+        <is>
+          <t>Periodicidade semanal (6ª feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo LWC 57g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M470" t="inlineStr"/>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>Expresso</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>Expresso</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr"/>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>Página Dupla</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>548x408mm</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr"/>
+      <c r="I471" t="inlineStr"/>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
+        </is>
+      </c>
+      <c r="K471" t="inlineStr"/>
+      <c r="L471" t="inlineStr">
+        <is>
+          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M471" t="inlineStr"/>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>Expresso</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>Expresso</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr"/>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>Página</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>264x408mm</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr"/>
+      <c r="I472" t="inlineStr"/>
+      <c r="J472" t="inlineStr">
+        <is>
+          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
+        </is>
+      </c>
+      <c r="K472" t="inlineStr"/>
+      <c r="L472" t="inlineStr">
+        <is>
+          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M472" t="inlineStr"/>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>Expresso</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>Expresso</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr"/>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>1/2 Página Baixo</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>264x201,8mm</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr"/>
+      <c r="I473" t="inlineStr"/>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
+        </is>
+      </c>
+      <c r="K473" t="inlineStr"/>
+      <c r="L473" t="inlineStr">
+        <is>
+          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M473" t="inlineStr"/>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>Expresso</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>Expresso</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr"/>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>1/2 Página Alto</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>130x408mm</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr"/>
+      <c r="I474" t="inlineStr"/>
+      <c r="J474" t="inlineStr">
+        <is>
+          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
+        </is>
+      </c>
+      <c r="K474" t="inlineStr"/>
+      <c r="L474" t="inlineStr">
+        <is>
+          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M474" t="inlineStr"/>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>Expresso</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>Expresso</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr"/>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>1/2 Página Dupla</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>548x201,8mm</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr"/>
+      <c r="I475" t="inlineStr"/>
+      <c r="J475" t="inlineStr">
+        <is>
+          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
+        </is>
+      </c>
+      <c r="K475" t="inlineStr"/>
+      <c r="L475" t="inlineStr">
+        <is>
+          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M475" t="inlineStr"/>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>Expresso</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>Expresso</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr"/>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>Júnior Page</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>174,8x277mm</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr"/>
+      <c r="I476" t="inlineStr"/>
+      <c r="J476" t="inlineStr">
+        <is>
+          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
+        </is>
+      </c>
+      <c r="K476" t="inlineStr"/>
+      <c r="L476" t="inlineStr">
+        <is>
+          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M476" t="inlineStr"/>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>Expresso</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>Expresso</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr"/>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>1/4 Página</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>130x201,8mm</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr"/>
+      <c r="I477" t="inlineStr"/>
+      <c r="J477" t="inlineStr">
+        <is>
+          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
+        </is>
+      </c>
+      <c r="K477" t="inlineStr"/>
+      <c r="L477" t="inlineStr">
+        <is>
+          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M477" t="inlineStr"/>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>Expresso</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>Expresso</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr"/>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>1/4 Página Landscape</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>264x92,2mm</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr"/>
+      <c r="I478" t="inlineStr"/>
+      <c r="J478" t="inlineStr">
+        <is>
+          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
+        </is>
+      </c>
+      <c r="K478" t="inlineStr"/>
+      <c r="L478" t="inlineStr">
+        <is>
+          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M478" t="inlineStr"/>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>Expresso</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>Expresso</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr"/>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>1/8 Página</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>130x101mm</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr"/>
+      <c r="I479" t="inlineStr"/>
+      <c r="J479" t="inlineStr">
+        <is>
+          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
+        </is>
+      </c>
+      <c r="K479" t="inlineStr"/>
+      <c r="L479" t="inlineStr">
+        <is>
+          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M479" t="inlineStr"/>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>Expresso</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>Expresso</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr"/>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>Orelha de Capa</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>450x60mm</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr"/>
+      <c r="I480" t="inlineStr"/>
+      <c r="J480" t="inlineStr">
+        <is>
+          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
+        </is>
+      </c>
+      <c r="K480" t="inlineStr"/>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t>Formato especial de capa do 1º Caderno. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M480" t="inlineStr"/>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>Expresso</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>Expresso</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr"/>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>Sanca de Capa</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>240x264mm</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr"/>
+      <c r="I481" t="inlineStr"/>
+      <c r="J481" t="inlineStr">
+        <is>
+          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
+        </is>
+      </c>
+      <c r="K481" t="inlineStr"/>
+      <c r="L481" t="inlineStr">
+        <is>
+          <t>Formato especial de capa do 1º Caderno. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M481" t="inlineStr"/>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>Expresso</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>Expresso</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr"/>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>Saco Expresso</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>450x360mm (área útil do cliente: 450x278mm)</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr"/>
+      <c r="I482" t="inlineStr"/>
+      <c r="J482" t="inlineStr">
+        <is>
+          <t>PDF em alta definição (elementos de desenho em vetorial, imagens à parte + JPEG para visualização)</t>
+        </is>
+      </c>
+      <c r="K482" t="inlineStr"/>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t>Saco em papel liso impresso a CMYK + 2 cores; a tarja com a informação é sempre na cor do Expresso (Pantone 315C).</t>
+        </is>
+      </c>
+      <c r="M482" t="inlineStr"/>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>Expresso</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>Expresso Economia</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr"/>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>Página Dupla</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>548x408mm</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr"/>
+      <c r="I483" t="inlineStr"/>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
+        </is>
+      </c>
+      <c r="K483" t="inlineStr"/>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M483" t="inlineStr"/>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>Expresso</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Expresso Economia</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr"/>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>Página</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>264x408mm</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr"/>
+      <c r="I484" t="inlineStr"/>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
+        </is>
+      </c>
+      <c r="K484" t="inlineStr"/>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M484" t="inlineStr"/>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>Expresso</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Expresso Economia</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr"/>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>1/2 Página Baixo</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>264x201,8mm</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr"/>
+      <c r="I485" t="inlineStr"/>
+      <c r="J485" t="inlineStr">
+        <is>
+          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
+        </is>
+      </c>
+      <c r="K485" t="inlineStr"/>
+      <c r="L485" t="inlineStr">
+        <is>
+          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M485" t="inlineStr"/>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>Expresso</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>Expresso Economia</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr"/>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>1/2 Página Alto</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>130x408mm</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr"/>
+      <c r="I486" t="inlineStr"/>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
+        </is>
+      </c>
+      <c r="K486" t="inlineStr"/>
+      <c r="L486" t="inlineStr">
+        <is>
+          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M486" t="inlineStr"/>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>Expresso</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>Expresso Economia</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr"/>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>1/2 Página Dupla</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>548x201,8mm</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr"/>
+      <c r="I487" t="inlineStr"/>
+      <c r="J487" t="inlineStr">
+        <is>
+          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
+        </is>
+      </c>
+      <c r="K487" t="inlineStr"/>
+      <c r="L487" t="inlineStr">
+        <is>
+          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M487" t="inlineStr"/>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>Expresso</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>Expresso Economia</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr"/>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>Júnior Page</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>174,8x277mm</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr"/>
+      <c r="I488" t="inlineStr"/>
+      <c r="J488" t="inlineStr">
+        <is>
+          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
+        </is>
+      </c>
+      <c r="K488" t="inlineStr"/>
+      <c r="L488" t="inlineStr">
+        <is>
+          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M488" t="inlineStr"/>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>Expresso</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>Expresso Economia</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr"/>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>1/4 Página</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>130x201,8mm</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr"/>
+      <c r="I489" t="inlineStr"/>
+      <c r="J489" t="inlineStr">
+        <is>
+          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
+        </is>
+      </c>
+      <c r="K489" t="inlineStr"/>
+      <c r="L489" t="inlineStr">
+        <is>
+          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M489" t="inlineStr"/>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>Expresso</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>Expresso Economia</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr"/>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>1/4 Página Landscape</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>264x92,2mm</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr"/>
+      <c r="I490" t="inlineStr"/>
+      <c r="J490" t="inlineStr">
+        <is>
+          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
+        </is>
+      </c>
+      <c r="K490" t="inlineStr"/>
+      <c r="L490" t="inlineStr">
+        <is>
+          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M490" t="inlineStr"/>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>Expresso</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>Expresso Economia</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr"/>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>1/8 Página</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>130x101mm</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr"/>
+      <c r="I491" t="inlineStr"/>
+      <c r="J491" t="inlineStr">
+        <is>
+          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
+        </is>
+      </c>
+      <c r="K491" t="inlineStr"/>
+      <c r="L491" t="inlineStr">
+        <is>
+          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M491" t="inlineStr"/>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>Expresso</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>Expresso Economia</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr"/>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>Orelha (Janela na Primeira Página)</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>41x32mm</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr"/>
+      <c r="I492" t="inlineStr"/>
+      <c r="J492" t="inlineStr">
+        <is>
+          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
+        </is>
+      </c>
+      <c r="K492" t="inlineStr"/>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M492" t="inlineStr"/>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>Expresso</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>Expresso Economia</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr"/>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>Orelha Grande (Janela na Primeira Página)</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>41x87mm</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr"/>
+      <c r="I493" t="inlineStr"/>
+      <c r="J493" t="inlineStr">
+        <is>
+          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
+        </is>
+      </c>
+      <c r="K493" t="inlineStr"/>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M493" t="inlineStr"/>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>Expresso</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>Revista E</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr"/>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>Página Dupla</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>530x337mm</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr"/>
+      <c r="I494" t="inlineStr"/>
+      <c r="J494" t="inlineStr">
+        <is>
+          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
+        </is>
+      </c>
+      <c r="K494" t="inlineStr"/>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t>Impressão offset quadricromia — papel jornal melhorado 55g, capa couché mate 130g, lombada colada; localização obrigatória: +30%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M494" t="inlineStr"/>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>Expresso</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>Revista E</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr"/>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>Página</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>265x337mm</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr"/>
+      <c r="I495" t="inlineStr"/>
+      <c r="J495" t="inlineStr">
+        <is>
+          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
+        </is>
+      </c>
+      <c r="K495" t="inlineStr"/>
+      <c r="L495" t="inlineStr">
+        <is>
+          <t>Impressão offset quadricromia — papel jornal melhorado 55g, capa couché mate 130g, lombada colada; localização obrigatória: +30%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M495" t="inlineStr"/>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>Expresso</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>Revista E</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr"/>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>1/2 Página Baixo</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>265x167mm</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr"/>
+      <c r="I496" t="inlineStr"/>
+      <c r="J496" t="inlineStr">
+        <is>
+          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
+        </is>
+      </c>
+      <c r="K496" t="inlineStr"/>
+      <c r="L496" t="inlineStr">
+        <is>
+          <t>Impressão offset quadricromia — papel jornal melhorado 55g, capa couché mate 130g, lombada colada; localização obrigatória: +30%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M496" t="inlineStr"/>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>Expresso</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>Revista E</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr"/>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>1/2 Página Alto</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>130x337mm</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr"/>
+      <c r="I497" t="inlineStr"/>
+      <c r="J497" t="inlineStr">
+        <is>
+          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
+        </is>
+      </c>
+      <c r="K497" t="inlineStr"/>
+      <c r="L497" t="inlineStr">
+        <is>
+          <t>Impressão offset quadricromia — papel jornal melhorado 55g, capa couché mate 130g, lombada colada; localização obrigatória: +30%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M497" t="inlineStr"/>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>Expresso</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>Revista E</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr"/>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>1/3 Página Alto</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>90x337mm</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr"/>
+      <c r="I498" t="inlineStr"/>
+      <c r="J498" t="inlineStr">
+        <is>
+          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
+        </is>
+      </c>
+      <c r="K498" t="inlineStr"/>
+      <c r="L498" t="inlineStr">
+        <is>
+          <t>Impressão offset quadricromia — papel jornal melhorado 55g, capa couché mate 130g, lombada colada; localização obrigatória: +30%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M498" t="inlineStr"/>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>Expresso</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>Revista E</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr"/>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>Rodapé</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>265x108mm</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr"/>
+      <c r="I499" t="inlineStr"/>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
+        </is>
+      </c>
+      <c r="K499" t="inlineStr"/>
+      <c r="L499" t="inlineStr">
+        <is>
+          <t>Impressão offset quadricromia — papel jornal melhorado 55g, capa couché mate 130g, lombada colada; localização obrigatória: +30%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M499" t="inlineStr"/>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>Expresso</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>Revista E</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr"/>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>1/4 Página</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>115x147mm</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr"/>
+      <c r="I500" t="inlineStr"/>
+      <c r="J500" t="inlineStr">
+        <is>
+          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
+        </is>
+      </c>
+      <c r="K500" t="inlineStr"/>
+      <c r="L500" t="inlineStr">
+        <is>
+          <t>Impressão offset quadricromia — papel jornal melhorado 55g, capa couché mate 130g, lombada colada; localização obrigatória: +30%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M500" t="inlineStr"/>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>Expresso</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>Revista E</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr"/>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>1/6 Página</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>75x147mm</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr"/>
+      <c r="I501" t="inlineStr"/>
+      <c r="J501" t="inlineStr">
+        <is>
+          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
+        </is>
+      </c>
+      <c r="K501" t="inlineStr"/>
+      <c r="L501" t="inlineStr">
+        <is>
+          <t>Impressão offset quadricromia — papel jornal melhorado 55g, capa couché mate 130g, lombada colada; localização obrigatória: +30%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M501" t="inlineStr"/>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>Expresso</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>Revista E</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr"/>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>1/8 Página</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>115x71mm</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr"/>
+      <c r="I502" t="inlineStr"/>
+      <c r="J502" t="inlineStr">
+        <is>
+          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
+        </is>
+      </c>
+      <c r="K502" t="inlineStr"/>
+      <c r="L502" t="inlineStr">
+        <is>
+          <t>Impressão offset quadricromia — papel jornal melhorado 55g, capa couché mate 130g, lombada colada; localização obrigatória: +30%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M502" t="inlineStr"/>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>Attitude</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>Attitude</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr"/>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>Página (Par/Ímpar)</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>215x278mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr"/>
+      <c r="I503" t="inlineStr"/>
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF em alta resolução de 400 DPI (mínimo 300 DPI), CMYK, sem atribuição de perfil final</t>
+        </is>
+      </c>
+      <c r="K503" t="inlineStr"/>
+      <c r="L503" t="inlineStr">
+        <is>
+          <t>Periodicidade bimestral (janeiro, março, maio, julho, setembro, novembro); revista bilingue (português + inglês); distribuição em Portugal e mais 22 países; páginas duplas com desvio de 6mm ao centro (3mm para a esquerda e 3mm para a direita) para garantir o acerto central. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M503" t="inlineStr"/>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>Attitude</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>Attitude</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr"/>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>1/2 Página Vertical</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>106,25x278mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr"/>
+      <c r="I504" t="inlineStr"/>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF em alta resolução de 400 DPI (mínimo 300 DPI), CMYK, sem atribuição de perfil final</t>
+        </is>
+      </c>
+      <c r="K504" t="inlineStr"/>
+      <c r="L504" t="inlineStr">
+        <is>
+          <t>Periodicidade bimestral (janeiro, março, maio, julho, setembro, novembro); revista bilingue (português + inglês); distribuição em Portugal e mais 22 países; páginas duplas com desvio de 6mm ao centro (3mm para a esquerda e 3mm para a direita) para garantir o acerto central. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M504" t="inlineStr"/>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>Attitude</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>Attitude</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr"/>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>1/2 Página Horizontal</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>215x143mm (+3mm bleed)</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr"/>
+      <c r="I505" t="inlineStr"/>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF em alta resolução de 400 DPI (mínimo 300 DPI), CMYK, sem atribuição de perfil final</t>
+        </is>
+      </c>
+      <c r="K505" t="inlineStr"/>
+      <c r="L505" t="inlineStr">
+        <is>
+          <t>Periodicidade bimestral (janeiro, março, maio, julho, setembro, novembro); revista bilingue (português + inglês); distribuição em Portugal e mais 22 países; páginas duplas com desvio de 6mm ao centro (3mm para a esquerda e 3mm para a direita) para garantir o acerto central. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M505" t="inlineStr"/>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>Imprensa</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>Attitude</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>Attitude</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr"/>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>Página Dupla</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>430x278mm (+3mm bleed, +6mm massa central)</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr"/>
+      <c r="I506" t="inlineStr"/>
+      <c r="J506" t="inlineStr">
+        <is>
+          <t>PDF, EPS ou TIFF em alta resolução de 400 DPI (mínimo 300 DPI), CMYK, sem atribuição de perfil final</t>
+        </is>
+      </c>
+      <c r="K506" t="inlineStr"/>
+      <c r="L506" t="inlineStr">
+        <is>
+          <t>Periodicidade bimestral (janeiro, março, maio, julho, setembro, novembro); revista bilingue (português + inglês); distribuição em Portugal e mais 22 países; páginas duplas com desvio de 6mm ao centro (3mm para a esquerda e 3mm para a direita) para garantir o acerto central. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+        </is>
+      </c>
+      <c r="M506" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M506"/>
+  <dimension ref="A1:M509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="18.08984375" customWidth="1" style="2" min="1" max="1"/>
@@ -20645,7 +20645,6 @@
           <t>Correio da Manhã</t>
         </is>
       </c>
-      <c r="E383" t="inlineStr"/>
       <c r="F383" t="inlineStr">
         <is>
           <t>Página</t>
@@ -20656,20 +20655,16 @@
           <t>257x320mm (80 módulos, 5 col. x 16 mód.)</t>
         </is>
       </c>
-      <c r="H383" t="inlineStr"/>
-      <c r="I383" t="inlineStr"/>
       <c r="J383" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
       <c r="L383" t="inlineStr">
         <is>
           <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 colunas x 16 módulos); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -20692,7 +20687,6 @@
           <t>Correio da Manhã</t>
         </is>
       </c>
-      <c r="E384" t="inlineStr"/>
       <c r="F384" t="inlineStr">
         <is>
           <t>Meia Página</t>
@@ -20703,20 +20697,16 @@
           <t>204x240mm (48 módulos, 4 col. x 12 mód.)</t>
         </is>
       </c>
-      <c r="H384" t="inlineStr"/>
-      <c r="I384" t="inlineStr"/>
       <c r="J384" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
       <c r="L384" t="inlineStr">
         <is>
           <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 colunas x 16 módulos); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -20739,7 +20729,6 @@
           <t>Correio da Manhã</t>
         </is>
       </c>
-      <c r="E385" t="inlineStr"/>
       <c r="F385" t="inlineStr">
         <is>
           <t>1/2 Página Alto (3 Col.)</t>
@@ -20750,20 +20739,16 @@
           <t>153x320mm (48 módulos, 3 col. x 16 mód.)</t>
         </is>
       </c>
-      <c r="H385" t="inlineStr"/>
-      <c r="I385" t="inlineStr"/>
       <c r="J385" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
       <c r="L385" t="inlineStr">
         <is>
           <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 colunas x 16 módulos); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -20786,7 +20771,6 @@
           <t>Correio da Manhã</t>
         </is>
       </c>
-      <c r="E386" t="inlineStr"/>
       <c r="F386" t="inlineStr">
         <is>
           <t>1/3 Página Alto (2 Col.)</t>
@@ -20797,20 +20781,16 @@
           <t>100x320mm (32 módulos, 2 col. x 16 mód.)</t>
         </is>
       </c>
-      <c r="H386" t="inlineStr"/>
-      <c r="I386" t="inlineStr"/>
       <c r="J386" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
       <c r="L386" t="inlineStr">
         <is>
           <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 colunas x 16 módulos); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -20833,7 +20813,6 @@
           <t>Correio da Manhã</t>
         </is>
       </c>
-      <c r="E387" t="inlineStr"/>
       <c r="F387" t="inlineStr">
         <is>
           <t>1/2 Página Baixo</t>
@@ -20844,20 +20823,16 @@
           <t>257x160mm (40 módulos, 5 col. x 8 mód.)</t>
         </is>
       </c>
-      <c r="H387" t="inlineStr"/>
-      <c r="I387" t="inlineStr"/>
       <c r="J387" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
       <c r="L387" t="inlineStr">
         <is>
           <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 colunas x 16 módulos); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -20880,7 +20855,6 @@
           <t>Correio da Manhã</t>
         </is>
       </c>
-      <c r="E388" t="inlineStr"/>
       <c r="F388" t="inlineStr">
         <is>
           <t>1/4 Página (3 Col.)</t>
@@ -20891,20 +20865,16 @@
           <t>153x160mm (24 módulos, 3 col. x 8 mód.)</t>
         </is>
       </c>
-      <c r="H388" t="inlineStr"/>
-      <c r="I388" t="inlineStr"/>
       <c r="J388" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
       <c r="L388" t="inlineStr">
         <is>
           <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 colunas x 16 módulos); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -20927,7 +20897,6 @@
           <t>Correio da Manhã</t>
         </is>
       </c>
-      <c r="E389" t="inlineStr"/>
       <c r="F389" t="inlineStr">
         <is>
           <t>1/4 Página (2 Col.)</t>
@@ -20938,20 +20907,16 @@
           <t>100x160mm (16 módulos, 2 col. x 8 mód.)</t>
         </is>
       </c>
-      <c r="H389" t="inlineStr"/>
-      <c r="I389" t="inlineStr"/>
       <c r="J389" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
       <c r="L389" t="inlineStr">
         <is>
           <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 colunas x 16 módulos); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -20974,7 +20939,6 @@
           <t>Correio da Manhã</t>
         </is>
       </c>
-      <c r="E390" t="inlineStr"/>
       <c r="F390" t="inlineStr">
         <is>
           <t>Rodapé</t>
@@ -20985,20 +20949,16 @@
           <t>257x61mm (15 módulos, 5 col. x 3 mód.)</t>
         </is>
       </c>
-      <c r="H390" t="inlineStr"/>
-      <c r="I390" t="inlineStr"/>
       <c r="J390" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
       <c r="L390" t="inlineStr">
         <is>
           <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 colunas x 16 módulos); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -21021,7 +20981,6 @@
           <t>Mais Sport</t>
         </is>
       </c>
-      <c r="E391" t="inlineStr"/>
       <c r="F391" t="inlineStr">
         <is>
           <t>Página</t>
@@ -21032,20 +20991,16 @@
           <t>257x320mm (80 módulos, 5 col. x 16 mód.)</t>
         </is>
       </c>
-      <c r="H391" t="inlineStr"/>
-      <c r="I391" t="inlineStr"/>
       <c r="J391" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
       <c r="L391" t="inlineStr">
         <is>
           <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 257x320mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -21068,7 +21023,6 @@
           <t>Boa Onda</t>
         </is>
       </c>
-      <c r="E392" t="inlineStr"/>
       <c r="F392" t="inlineStr">
         <is>
           <t>Página Dupla</t>
@@ -21079,20 +21033,16 @@
           <t>400x295mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H392" t="inlineStr"/>
-      <c r="I392" t="inlineStr"/>
       <c r="J392" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
       <c r="L392" t="inlineStr">
         <is>
           <t>Periodicidade semanal (sexta-feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -21115,7 +21065,6 @@
           <t>Boa Onda</t>
         </is>
       </c>
-      <c r="E393" t="inlineStr"/>
       <c r="F393" t="inlineStr">
         <is>
           <t>Página</t>
@@ -21126,20 +21075,16 @@
           <t>200x295mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H393" t="inlineStr"/>
-      <c r="I393" t="inlineStr"/>
       <c r="J393" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
       <c r="L393" t="inlineStr">
         <is>
           <t>Periodicidade semanal (sexta-feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -21162,7 +21107,6 @@
           <t>Boa Onda</t>
         </is>
       </c>
-      <c r="E394" t="inlineStr"/>
       <c r="F394" t="inlineStr">
         <is>
           <t>1/2 Página Dupla</t>
@@ -21173,20 +21117,16 @@
           <t>400x147mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H394" t="inlineStr"/>
-      <c r="I394" t="inlineStr"/>
       <c r="J394" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
       <c r="L394" t="inlineStr">
         <is>
           <t>Periodicidade semanal (sexta-feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -21209,7 +21149,6 @@
           <t>Boa Onda</t>
         </is>
       </c>
-      <c r="E395" t="inlineStr"/>
       <c r="F395" t="inlineStr">
         <is>
           <t>1/2 Página Alto</t>
@@ -21220,20 +21159,16 @@
           <t>100x295mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H395" t="inlineStr"/>
-      <c r="I395" t="inlineStr"/>
       <c r="J395" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
       <c r="L395" t="inlineStr">
         <is>
           <t>Periodicidade semanal (sexta-feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -21256,7 +21191,6 @@
           <t>Boa Onda</t>
         </is>
       </c>
-      <c r="E396" t="inlineStr"/>
       <c r="F396" t="inlineStr">
         <is>
           <t>1/2 Página Baixo</t>
@@ -21267,20 +21201,16 @@
           <t>200x147mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H396" t="inlineStr"/>
-      <c r="I396" t="inlineStr"/>
       <c r="J396" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
       <c r="L396" t="inlineStr">
         <is>
           <t>Periodicidade semanal (sexta-feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -21303,7 +21233,6 @@
           <t>Boa Onda</t>
         </is>
       </c>
-      <c r="E397" t="inlineStr"/>
       <c r="F397" t="inlineStr">
         <is>
           <t>1/3 Página Alto</t>
@@ -21314,20 +21243,16 @@
           <t>72x295mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H397" t="inlineStr"/>
-      <c r="I397" t="inlineStr"/>
       <c r="J397" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
       <c r="L397" t="inlineStr">
         <is>
           <t>Periodicidade semanal (sexta-feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -21350,7 +21275,6 @@
           <t>Boa Onda</t>
         </is>
       </c>
-      <c r="E398" t="inlineStr"/>
       <c r="F398" t="inlineStr">
         <is>
           <t>1/3 Página Baixo</t>
@@ -21361,20 +21285,16 @@
           <t>200x105mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H398" t="inlineStr"/>
-      <c r="I398" t="inlineStr"/>
       <c r="J398" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
       <c r="L398" t="inlineStr">
         <is>
           <t>Periodicidade semanal (sexta-feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -21397,7 +21317,6 @@
           <t>Boa Onda</t>
         </is>
       </c>
-      <c r="E399" t="inlineStr"/>
       <c r="F399" t="inlineStr">
         <is>
           <t>1/4 Página</t>
@@ -21408,20 +21327,16 @@
           <t>100x147mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H399" t="inlineStr"/>
-      <c r="I399" t="inlineStr"/>
       <c r="J399" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
       <c r="L399" t="inlineStr">
         <is>
           <t>Periodicidade semanal (sexta-feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -21444,7 +21359,6 @@
           <t>Boa Onda</t>
         </is>
       </c>
-      <c r="E400" t="inlineStr"/>
       <c r="F400" t="inlineStr">
         <is>
           <t>Rodapé</t>
@@ -21455,20 +21369,16 @@
           <t>200x78mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H400" t="inlineStr"/>
-      <c r="I400" t="inlineStr"/>
       <c r="J400" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
       <c r="L400" t="inlineStr">
         <is>
           <t>Periodicidade semanal (sexta-feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -21491,7 +21401,6 @@
           <t>VIDAS</t>
         </is>
       </c>
-      <c r="E401" t="inlineStr"/>
       <c r="F401" t="inlineStr">
         <is>
           <t>Página Dupla</t>
@@ -21502,20 +21411,16 @@
           <t>400x295mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H401" t="inlineStr"/>
-      <c r="I401" t="inlineStr"/>
       <c r="J401" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
       <c r="L401" t="inlineStr">
         <is>
           <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -21538,7 +21443,6 @@
           <t>VIDAS</t>
         </is>
       </c>
-      <c r="E402" t="inlineStr"/>
       <c r="F402" t="inlineStr">
         <is>
           <t>Página</t>
@@ -21549,20 +21453,16 @@
           <t>200x295mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H402" t="inlineStr"/>
-      <c r="I402" t="inlineStr"/>
       <c r="J402" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
       <c r="L402" t="inlineStr">
         <is>
           <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -21585,7 +21485,6 @@
           <t>VIDAS</t>
         </is>
       </c>
-      <c r="E403" t="inlineStr"/>
       <c r="F403" t="inlineStr">
         <is>
           <t>1/2 Página Dupla</t>
@@ -21596,20 +21495,16 @@
           <t>400x147mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H403" t="inlineStr"/>
-      <c r="I403" t="inlineStr"/>
       <c r="J403" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
       <c r="L403" t="inlineStr">
         <is>
           <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -21632,7 +21527,6 @@
           <t>VIDAS</t>
         </is>
       </c>
-      <c r="E404" t="inlineStr"/>
       <c r="F404" t="inlineStr">
         <is>
           <t>1/2 Página Alto</t>
@@ -21643,20 +21537,16 @@
           <t>100x295mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H404" t="inlineStr"/>
-      <c r="I404" t="inlineStr"/>
       <c r="J404" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
       <c r="L404" t="inlineStr">
         <is>
           <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -21679,7 +21569,6 @@
           <t>VIDAS</t>
         </is>
       </c>
-      <c r="E405" t="inlineStr"/>
       <c r="F405" t="inlineStr">
         <is>
           <t>1/2 Página Baixo</t>
@@ -21690,20 +21579,16 @@
           <t>200x147mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H405" t="inlineStr"/>
-      <c r="I405" t="inlineStr"/>
       <c r="J405" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr"/>
       <c r="L405" t="inlineStr">
         <is>
           <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -21726,7 +21611,6 @@
           <t>VIDAS</t>
         </is>
       </c>
-      <c r="E406" t="inlineStr"/>
       <c r="F406" t="inlineStr">
         <is>
           <t>1/3 Página Alto</t>
@@ -21737,20 +21621,16 @@
           <t>72x295mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H406" t="inlineStr"/>
-      <c r="I406" t="inlineStr"/>
       <c r="J406" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
       <c r="L406" t="inlineStr">
         <is>
           <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -21773,7 +21653,6 @@
           <t>VIDAS</t>
         </is>
       </c>
-      <c r="E407" t="inlineStr"/>
       <c r="F407" t="inlineStr">
         <is>
           <t>1/3 Página Baixo</t>
@@ -21784,20 +21663,16 @@
           <t>200x105mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H407" t="inlineStr"/>
-      <c r="I407" t="inlineStr"/>
       <c r="J407" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr"/>
       <c r="L407" t="inlineStr">
         <is>
           <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -21820,7 +21695,6 @@
           <t>VIDAS</t>
         </is>
       </c>
-      <c r="E408" t="inlineStr"/>
       <c r="F408" t="inlineStr">
         <is>
           <t>1/4 Página</t>
@@ -21831,20 +21705,16 @@
           <t>100x147mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H408" t="inlineStr"/>
-      <c r="I408" t="inlineStr"/>
       <c r="J408" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
       <c r="L408" t="inlineStr">
         <is>
           <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -21867,7 +21737,6 @@
           <t>VIDAS</t>
         </is>
       </c>
-      <c r="E409" t="inlineStr"/>
       <c r="F409" t="inlineStr">
         <is>
           <t>Rodapé</t>
@@ -21878,20 +21747,16 @@
           <t>200x78mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H409" t="inlineStr"/>
-      <c r="I409" t="inlineStr"/>
       <c r="J409" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
       <c r="L409" t="inlineStr">
         <is>
           <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -21914,7 +21779,6 @@
           <t>Domingo</t>
         </is>
       </c>
-      <c r="E410" t="inlineStr"/>
       <c r="F410" t="inlineStr">
         <is>
           <t>Página Dupla</t>
@@ -21925,20 +21789,16 @@
           <t>400x295mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H410" t="inlineStr"/>
-      <c r="I410" t="inlineStr"/>
       <c r="J410" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
       <c r="L410" t="inlineStr">
         <is>
           <t>Periodicidade semanal (domingo); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -21961,7 +21821,6 @@
           <t>Domingo</t>
         </is>
       </c>
-      <c r="E411" t="inlineStr"/>
       <c r="F411" t="inlineStr">
         <is>
           <t>Página</t>
@@ -21972,20 +21831,16 @@
           <t>200x295mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H411" t="inlineStr"/>
-      <c r="I411" t="inlineStr"/>
       <c r="J411" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
       <c r="L411" t="inlineStr">
         <is>
           <t>Periodicidade semanal (domingo); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -22008,7 +21863,6 @@
           <t>Domingo</t>
         </is>
       </c>
-      <c r="E412" t="inlineStr"/>
       <c r="F412" t="inlineStr">
         <is>
           <t>1/2 Página Dupla</t>
@@ -22019,20 +21873,16 @@
           <t>400x147mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H412" t="inlineStr"/>
-      <c r="I412" t="inlineStr"/>
       <c r="J412" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K412" t="inlineStr"/>
       <c r="L412" t="inlineStr">
         <is>
           <t>Periodicidade semanal (domingo); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -22055,7 +21905,6 @@
           <t>Domingo</t>
         </is>
       </c>
-      <c r="E413" t="inlineStr"/>
       <c r="F413" t="inlineStr">
         <is>
           <t>1/2 Página Alto</t>
@@ -22066,20 +21915,16 @@
           <t>100x295mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H413" t="inlineStr"/>
-      <c r="I413" t="inlineStr"/>
       <c r="J413" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
       <c r="L413" t="inlineStr">
         <is>
           <t>Periodicidade semanal (domingo); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -22102,7 +21947,6 @@
           <t>Domingo</t>
         </is>
       </c>
-      <c r="E414" t="inlineStr"/>
       <c r="F414" t="inlineStr">
         <is>
           <t>1/2 Página Baixo</t>
@@ -22113,20 +21957,16 @@
           <t>200x147mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H414" t="inlineStr"/>
-      <c r="I414" t="inlineStr"/>
       <c r="J414" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr"/>
       <c r="L414" t="inlineStr">
         <is>
           <t>Periodicidade semanal (domingo); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -22149,7 +21989,6 @@
           <t>Domingo</t>
         </is>
       </c>
-      <c r="E415" t="inlineStr"/>
       <c r="F415" t="inlineStr">
         <is>
           <t>1/3 Página Alto</t>
@@ -22160,20 +21999,16 @@
           <t>72x295mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H415" t="inlineStr"/>
-      <c r="I415" t="inlineStr"/>
       <c r="J415" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr"/>
       <c r="L415" t="inlineStr">
         <is>
           <t>Periodicidade semanal (domingo); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -22196,7 +22031,6 @@
           <t>Domingo</t>
         </is>
       </c>
-      <c r="E416" t="inlineStr"/>
       <c r="F416" t="inlineStr">
         <is>
           <t>1/3 Página Baixo</t>
@@ -22207,20 +22041,16 @@
           <t>200x105mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H416" t="inlineStr"/>
-      <c r="I416" t="inlineStr"/>
       <c r="J416" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
       <c r="L416" t="inlineStr">
         <is>
           <t>Periodicidade semanal (domingo); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -22243,7 +22073,6 @@
           <t>Domingo</t>
         </is>
       </c>
-      <c r="E417" t="inlineStr"/>
       <c r="F417" t="inlineStr">
         <is>
           <t>1/4 Página</t>
@@ -22254,20 +22083,16 @@
           <t>100x147mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H417" t="inlineStr"/>
-      <c r="I417" t="inlineStr"/>
       <c r="J417" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K417" t="inlineStr"/>
       <c r="L417" t="inlineStr">
         <is>
           <t>Periodicidade semanal (domingo); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -22290,7 +22115,6 @@
           <t>Domingo</t>
         </is>
       </c>
-      <c r="E418" t="inlineStr"/>
       <c r="F418" t="inlineStr">
         <is>
           <t>Rodapé</t>
@@ -22301,20 +22125,16 @@
           <t>200x78mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H418" t="inlineStr"/>
-      <c r="I418" t="inlineStr"/>
       <c r="J418" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
       <c r="L418" t="inlineStr">
         <is>
           <t>Periodicidade semanal (domingo); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -22337,7 +22157,6 @@
           <t>Destak</t>
         </is>
       </c>
-      <c r="E419" t="inlineStr"/>
       <c r="F419" t="inlineStr">
         <is>
           <t>Capa Falsa</t>
@@ -22348,20 +22167,16 @@
           <t>210x280mm | 230x300mm (corte)</t>
         </is>
       </c>
-      <c r="H419" t="inlineStr"/>
-      <c r="I419" t="inlineStr"/>
       <c r="J419" t="inlineStr">
         <is>
           <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
       <c r="L419" t="inlineStr">
         <is>
           <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -22384,7 +22199,6 @@
           <t>Destak</t>
         </is>
       </c>
-      <c r="E420" t="inlineStr"/>
       <c r="F420" t="inlineStr">
         <is>
           <t>Rodapé 1ª Página</t>
@@ -22395,20 +22209,16 @@
           <t>210x42mm</t>
         </is>
       </c>
-      <c r="H420" t="inlineStr"/>
-      <c r="I420" t="inlineStr"/>
       <c r="J420" t="inlineStr">
         <is>
           <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr"/>
       <c r="L420" t="inlineStr">
         <is>
           <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -22431,7 +22241,6 @@
           <t>Destak</t>
         </is>
       </c>
-      <c r="E421" t="inlineStr"/>
       <c r="F421" t="inlineStr">
         <is>
           <t>Janela Premium</t>
@@ -22442,20 +22251,16 @@
           <t>49,5x78,5mm</t>
         </is>
       </c>
-      <c r="H421" t="inlineStr"/>
-      <c r="I421" t="inlineStr"/>
       <c r="J421" t="inlineStr">
         <is>
           <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
       <c r="L421" t="inlineStr">
         <is>
           <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -22478,7 +22283,6 @@
           <t>Destak</t>
         </is>
       </c>
-      <c r="E422" t="inlineStr"/>
       <c r="F422" t="inlineStr">
         <is>
           <t>Página Dupla</t>
@@ -22489,20 +22293,16 @@
           <t>440x280mm | 460x300mm (corte)</t>
         </is>
       </c>
-      <c r="H422" t="inlineStr"/>
-      <c r="I422" t="inlineStr"/>
       <c r="J422" t="inlineStr">
         <is>
           <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
       <c r="L422" t="inlineStr">
         <is>
           <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -22525,7 +22325,6 @@
           <t>Destak</t>
         </is>
       </c>
-      <c r="E423" t="inlineStr"/>
       <c r="F423" t="inlineStr">
         <is>
           <t>Página</t>
@@ -22536,20 +22335,16 @@
           <t>210x280mm | 230x300mm (corte)</t>
         </is>
       </c>
-      <c r="H423" t="inlineStr"/>
-      <c r="I423" t="inlineStr"/>
       <c r="J423" t="inlineStr">
         <is>
           <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr"/>
       <c r="L423" t="inlineStr">
         <is>
           <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -22572,7 +22367,6 @@
           <t>Destak</t>
         </is>
       </c>
-      <c r="E424" t="inlineStr"/>
       <c r="F424" t="inlineStr">
         <is>
           <t>Contracapa</t>
@@ -22583,20 +22377,16 @@
           <t>210x280mm | 230x300mm (corte)</t>
         </is>
       </c>
-      <c r="H424" t="inlineStr"/>
-      <c r="I424" t="inlineStr"/>
       <c r="J424" t="inlineStr">
         <is>
           <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr"/>
       <c r="L424" t="inlineStr">
         <is>
           <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -22619,7 +22409,6 @@
           <t>Destak</t>
         </is>
       </c>
-      <c r="E425" t="inlineStr"/>
       <c r="F425" t="inlineStr">
         <is>
           <t>1/2 Página Alto</t>
@@ -22630,20 +22419,16 @@
           <t>103x280mm</t>
         </is>
       </c>
-      <c r="H425" t="inlineStr"/>
-      <c r="I425" t="inlineStr"/>
       <c r="J425" t="inlineStr">
         <is>
           <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
       <c r="L425" t="inlineStr">
         <is>
           <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -22666,7 +22451,6 @@
           <t>Destak</t>
         </is>
       </c>
-      <c r="E426" t="inlineStr"/>
       <c r="F426" t="inlineStr">
         <is>
           <t>1/2 Página Baixo</t>
@@ -22677,20 +22461,16 @@
           <t>210x138mm</t>
         </is>
       </c>
-      <c r="H426" t="inlineStr"/>
-      <c r="I426" t="inlineStr"/>
       <c r="J426" t="inlineStr">
         <is>
           <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
         </is>
       </c>
-      <c r="K426" t="inlineStr"/>
       <c r="L426" t="inlineStr">
         <is>
           <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -22713,7 +22493,6 @@
           <t>Destak</t>
         </is>
       </c>
-      <c r="E427" t="inlineStr"/>
       <c r="F427" t="inlineStr">
         <is>
           <t>3/4 Página</t>
@@ -22724,20 +22503,16 @@
           <t>103x138mm</t>
         </is>
       </c>
-      <c r="H427" t="inlineStr"/>
-      <c r="I427" t="inlineStr"/>
       <c r="J427" t="inlineStr">
         <is>
           <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr"/>
       <c r="L427" t="inlineStr">
         <is>
           <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -22760,7 +22535,6 @@
           <t>Destak</t>
         </is>
       </c>
-      <c r="E428" t="inlineStr"/>
       <c r="F428" t="inlineStr">
         <is>
           <t>Rodapé</t>
@@ -22771,20 +22545,16 @@
           <t>210x42mm</t>
         </is>
       </c>
-      <c r="H428" t="inlineStr"/>
-      <c r="I428" t="inlineStr"/>
       <c r="J428" t="inlineStr">
         <is>
           <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
       <c r="L428" t="inlineStr">
         <is>
           <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -22807,7 +22577,6 @@
           <t>Jornal de Negócios</t>
         </is>
       </c>
-      <c r="E429" t="inlineStr"/>
       <c r="F429" t="inlineStr">
         <is>
           <t>Página</t>
@@ -22818,20 +22587,16 @@
           <t>257x320mm (80 módulos, 5 col. x 16 mód.)</t>
         </is>
       </c>
-      <c r="H429" t="inlineStr"/>
-      <c r="I429" t="inlineStr"/>
       <c r="J429" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
       <c r="L429" t="inlineStr">
         <is>
           <t>Periodicidade diária (2ª feira a 6ª feira); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -22854,7 +22619,6 @@
           <t>Jornal de Negócios</t>
         </is>
       </c>
-      <c r="E430" t="inlineStr"/>
       <c r="F430" t="inlineStr">
         <is>
           <t>Meia Página</t>
@@ -22865,20 +22629,16 @@
           <t>204x240mm (48 módulos, 4 col. x 12 mód.)</t>
         </is>
       </c>
-      <c r="H430" t="inlineStr"/>
-      <c r="I430" t="inlineStr"/>
       <c r="J430" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
       <c r="L430" t="inlineStr">
         <is>
           <t>Periodicidade diária (2ª feira a 6ª feira); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -22901,7 +22661,6 @@
           <t>Jornal de Negócios</t>
         </is>
       </c>
-      <c r="E431" t="inlineStr"/>
       <c r="F431" t="inlineStr">
         <is>
           <t>1/2 Página Alto (3 Col.)</t>
@@ -22912,20 +22671,16 @@
           <t>153x320mm (48 módulos, 3 col. x 16 mód.)</t>
         </is>
       </c>
-      <c r="H431" t="inlineStr"/>
-      <c r="I431" t="inlineStr"/>
       <c r="J431" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
       <c r="L431" t="inlineStr">
         <is>
           <t>Periodicidade diária (2ª feira a 6ª feira); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -22948,7 +22703,6 @@
           <t>Jornal de Negócios</t>
         </is>
       </c>
-      <c r="E432" t="inlineStr"/>
       <c r="F432" t="inlineStr">
         <is>
           <t>1/3 Página Alto (2 Col.)</t>
@@ -22959,20 +22713,16 @@
           <t>100x320mm (32 módulos, 2 col. x 16 mód.)</t>
         </is>
       </c>
-      <c r="H432" t="inlineStr"/>
-      <c r="I432" t="inlineStr"/>
       <c r="J432" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
       <c r="L432" t="inlineStr">
         <is>
           <t>Periodicidade diária (2ª feira a 6ª feira); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -22995,7 +22745,6 @@
           <t>Jornal de Negócios</t>
         </is>
       </c>
-      <c r="E433" t="inlineStr"/>
       <c r="F433" t="inlineStr">
         <is>
           <t>1/2 Página Baixo</t>
@@ -23006,20 +22755,16 @@
           <t>257x160mm (40 módulos, 5 col. x 8 mód.)</t>
         </is>
       </c>
-      <c r="H433" t="inlineStr"/>
-      <c r="I433" t="inlineStr"/>
       <c r="J433" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
       <c r="L433" t="inlineStr">
         <is>
           <t>Periodicidade diária (2ª feira a 6ª feira); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -23042,7 +22787,6 @@
           <t>Jornal de Negócios</t>
         </is>
       </c>
-      <c r="E434" t="inlineStr"/>
       <c r="F434" t="inlineStr">
         <is>
           <t>1/4 Página (3 Col.)</t>
@@ -23053,20 +22797,16 @@
           <t>153x160mm (24 módulos, 3 col. x 8 mód.)</t>
         </is>
       </c>
-      <c r="H434" t="inlineStr"/>
-      <c r="I434" t="inlineStr"/>
       <c r="J434" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr"/>
       <c r="L434" t="inlineStr">
         <is>
           <t>Periodicidade diária (2ª feira a 6ª feira); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -23089,7 +22829,6 @@
           <t>Jornal de Negócios</t>
         </is>
       </c>
-      <c r="E435" t="inlineStr"/>
       <c r="F435" t="inlineStr">
         <is>
           <t>1/4 Página (2 Col.)</t>
@@ -23100,20 +22839,16 @@
           <t>100x160mm (16 módulos, 2 col. x 8 mód.)</t>
         </is>
       </c>
-      <c r="H435" t="inlineStr"/>
-      <c r="I435" t="inlineStr"/>
       <c r="J435" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
       <c r="L435" t="inlineStr">
         <is>
           <t>Periodicidade diária (2ª feira a 6ª feira); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -23136,7 +22871,6 @@
           <t>Jornal de Negócios</t>
         </is>
       </c>
-      <c r="E436" t="inlineStr"/>
       <c r="F436" t="inlineStr">
         <is>
           <t>Rodapé</t>
@@ -23147,20 +22881,16 @@
           <t>257x61mm (15 módulos, 5 col. x 3 mód.)</t>
         </is>
       </c>
-      <c r="H436" t="inlineStr"/>
-      <c r="I436" t="inlineStr"/>
       <c r="J436" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
       <c r="L436" t="inlineStr">
         <is>
           <t>Periodicidade diária (2ª feira a 6ª feira); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -23183,7 +22913,6 @@
           <t>Jornal de Negócios</t>
         </is>
       </c>
-      <c r="E437" t="inlineStr"/>
       <c r="F437" t="inlineStr">
         <is>
           <t>Janela de Primeira Página</t>
@@ -23194,20 +22923,16 @@
           <t>55x96mm</t>
         </is>
       </c>
-      <c r="H437" t="inlineStr"/>
-      <c r="I437" t="inlineStr"/>
       <c r="J437" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
       <c r="L437" t="inlineStr">
         <is>
           <t>Formato especial na 1ª página ou última página do 1º Caderno. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -23230,7 +22955,6 @@
           <t>Jornal de Negócios</t>
         </is>
       </c>
-      <c r="E438" t="inlineStr"/>
       <c r="F438" t="inlineStr">
         <is>
           <t>Orelha de Primeira Página</t>
@@ -23241,20 +22965,16 @@
           <t>55x45mm</t>
         </is>
       </c>
-      <c r="H438" t="inlineStr"/>
-      <c r="I438" t="inlineStr"/>
       <c r="J438" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
       <c r="L438" t="inlineStr">
         <is>
           <t>Formato especial na 1ª página ou última página do 1º Caderno. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -23277,7 +22997,6 @@
           <t>Jornal de Negócios</t>
         </is>
       </c>
-      <c r="E439" t="inlineStr"/>
       <c r="F439" t="inlineStr">
         <is>
           <t>Rodapé de Primeira Página</t>
@@ -23288,20 +23007,16 @@
           <t>195x25mm</t>
         </is>
       </c>
-      <c r="H439" t="inlineStr"/>
-      <c r="I439" t="inlineStr"/>
       <c r="J439" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr"/>
       <c r="L439" t="inlineStr">
         <is>
           <t>Formato especial na 1ª página ou última página do 1º Caderno. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -23324,7 +23039,6 @@
           <t>Jornal de Negócios</t>
         </is>
       </c>
-      <c r="E440" t="inlineStr"/>
       <c r="F440" t="inlineStr">
         <is>
           <t>Home Page (Quadrado 2ª Página)</t>
@@ -23335,20 +23049,16 @@
           <t>150x130mm</t>
         </is>
       </c>
-      <c r="H440" t="inlineStr"/>
-      <c r="I440" t="inlineStr"/>
       <c r="J440" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
       <c r="L440" t="inlineStr">
         <is>
           <t>Formato especial na 1ª página ou última página do 1º Caderno. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -23371,7 +23081,6 @@
           <t>Jornal de Negócios</t>
         </is>
       </c>
-      <c r="E441" t="inlineStr"/>
       <c r="F441" t="inlineStr">
         <is>
           <t>Rodapé Última Página</t>
@@ -23382,20 +23091,16 @@
           <t>205x61mm</t>
         </is>
       </c>
-      <c r="H441" t="inlineStr"/>
-      <c r="I441" t="inlineStr"/>
       <c r="J441" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
       <c r="L441" t="inlineStr">
         <is>
           <t>Formato especial na 1ª página ou última página do 1º Caderno. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -23418,7 +23123,6 @@
           <t>Record</t>
         </is>
       </c>
-      <c r="E442" t="inlineStr"/>
       <c r="F442" t="inlineStr">
         <is>
           <t>Página</t>
@@ -23429,20 +23133,16 @@
           <t>257x320mm (80 módulos, 5 col. x 16 mód.)</t>
         </is>
       </c>
-      <c r="H442" t="inlineStr"/>
-      <c r="I442" t="inlineStr"/>
       <c r="J442" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K442" t="inlineStr"/>
       <c r="L442" t="inlineStr">
         <is>
           <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -23465,7 +23165,6 @@
           <t>Record</t>
         </is>
       </c>
-      <c r="E443" t="inlineStr"/>
       <c r="F443" t="inlineStr">
         <is>
           <t>Meia Página</t>
@@ -23476,20 +23175,16 @@
           <t>204x240mm (48 módulos, 4 col. x 12 mód.)</t>
         </is>
       </c>
-      <c r="H443" t="inlineStr"/>
-      <c r="I443" t="inlineStr"/>
       <c r="J443" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr"/>
       <c r="L443" t="inlineStr">
         <is>
           <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -23512,7 +23207,6 @@
           <t>Record</t>
         </is>
       </c>
-      <c r="E444" t="inlineStr"/>
       <c r="F444" t="inlineStr">
         <is>
           <t>1/2 Página Alto (3 Col.)</t>
@@ -23523,20 +23217,16 @@
           <t>153x320mm (48 módulos, 3 col. x 16 mód.)</t>
         </is>
       </c>
-      <c r="H444" t="inlineStr"/>
-      <c r="I444" t="inlineStr"/>
       <c r="J444" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr"/>
       <c r="L444" t="inlineStr">
         <is>
           <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -23559,7 +23249,6 @@
           <t>Record</t>
         </is>
       </c>
-      <c r="E445" t="inlineStr"/>
       <c r="F445" t="inlineStr">
         <is>
           <t>1/3 Página Alto (2 Col.)</t>
@@ -23570,20 +23259,16 @@
           <t>100x320mm (32 módulos, 2 col. x 16 mód.)</t>
         </is>
       </c>
-      <c r="H445" t="inlineStr"/>
-      <c r="I445" t="inlineStr"/>
       <c r="J445" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K445" t="inlineStr"/>
       <c r="L445" t="inlineStr">
         <is>
           <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -23606,7 +23291,6 @@
           <t>Record</t>
         </is>
       </c>
-      <c r="E446" t="inlineStr"/>
       <c r="F446" t="inlineStr">
         <is>
           <t>1/2 Página Baixo</t>
@@ -23617,20 +23301,16 @@
           <t>257x160mm (40 módulos, 5 col. x 8 mód.)</t>
         </is>
       </c>
-      <c r="H446" t="inlineStr"/>
-      <c r="I446" t="inlineStr"/>
       <c r="J446" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr"/>
       <c r="L446" t="inlineStr">
         <is>
           <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M446" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -23653,7 +23333,6 @@
           <t>Record</t>
         </is>
       </c>
-      <c r="E447" t="inlineStr"/>
       <c r="F447" t="inlineStr">
         <is>
           <t>1/4 Página (3 Col.)</t>
@@ -23664,20 +23343,16 @@
           <t>153x160mm (24 módulos, 3 col. x 8 mód.)</t>
         </is>
       </c>
-      <c r="H447" t="inlineStr"/>
-      <c r="I447" t="inlineStr"/>
       <c r="J447" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr"/>
       <c r="L447" t="inlineStr">
         <is>
           <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M447" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -23700,7 +23375,6 @@
           <t>Record</t>
         </is>
       </c>
-      <c r="E448" t="inlineStr"/>
       <c r="F448" t="inlineStr">
         <is>
           <t>1/4 Página (2 Col.)</t>
@@ -23711,20 +23385,16 @@
           <t>100x160mm (16 módulos, 2 col. x 8 mód.)</t>
         </is>
       </c>
-      <c r="H448" t="inlineStr"/>
-      <c r="I448" t="inlineStr"/>
       <c r="J448" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr"/>
       <c r="L448" t="inlineStr">
         <is>
           <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M448" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -23747,7 +23417,6 @@
           <t>Record</t>
         </is>
       </c>
-      <c r="E449" t="inlineStr"/>
       <c r="F449" t="inlineStr">
         <is>
           <t>Rodapé</t>
@@ -23758,20 +23427,16 @@
           <t>257x61mm (15 módulos, 5 col. x 3 mód.)</t>
         </is>
       </c>
-      <c r="H449" t="inlineStr"/>
-      <c r="I449" t="inlineStr"/>
       <c r="J449" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
       <c r="L449" t="inlineStr">
         <is>
           <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M449" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -23794,7 +23459,6 @@
           <t>Sábado</t>
         </is>
       </c>
-      <c r="E450" t="inlineStr"/>
       <c r="F450" t="inlineStr">
         <is>
           <t>Página Dupla</t>
@@ -23805,20 +23469,16 @@
           <t>410x275mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H450" t="inlineStr"/>
-      <c r="I450" t="inlineStr"/>
       <c r="J450" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
       <c r="L450" t="inlineStr">
         <is>
           <t>Periodicidade semanal (5ª feira); distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M450" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -23841,7 +23501,6 @@
           <t>Sábado</t>
         </is>
       </c>
-      <c r="E451" t="inlineStr"/>
       <c r="F451" t="inlineStr">
         <is>
           <t>Página</t>
@@ -23852,20 +23511,16 @@
           <t>205x275mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H451" t="inlineStr"/>
-      <c r="I451" t="inlineStr"/>
       <c r="J451" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
       <c r="L451" t="inlineStr">
         <is>
           <t>Periodicidade semanal (5ª feira); distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M451" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -23888,7 +23543,6 @@
           <t>Sábado</t>
         </is>
       </c>
-      <c r="E452" t="inlineStr"/>
       <c r="F452" t="inlineStr">
         <is>
           <t>1/2 Página Dupla</t>
@@ -23899,20 +23553,16 @@
           <t>410x137mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H452" t="inlineStr"/>
-      <c r="I452" t="inlineStr"/>
       <c r="J452" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
       <c r="L452" t="inlineStr">
         <is>
           <t>Periodicidade semanal (5ª feira); distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M452" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -23935,7 +23585,6 @@
           <t>Sábado</t>
         </is>
       </c>
-      <c r="E453" t="inlineStr"/>
       <c r="F453" t="inlineStr">
         <is>
           <t>1/2 Página Alto</t>
@@ -23946,20 +23595,16 @@
           <t>102x275mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H453" t="inlineStr"/>
-      <c r="I453" t="inlineStr"/>
       <c r="J453" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
       <c r="L453" t="inlineStr">
         <is>
           <t>Periodicidade semanal (5ª feira); distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M453" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -23982,7 +23627,6 @@
           <t>Sábado</t>
         </is>
       </c>
-      <c r="E454" t="inlineStr"/>
       <c r="F454" t="inlineStr">
         <is>
           <t>1/2 Página Baixo</t>
@@ -23993,20 +23637,16 @@
           <t>205x137mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H454" t="inlineStr"/>
-      <c r="I454" t="inlineStr"/>
       <c r="J454" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
       <c r="L454" t="inlineStr">
         <is>
           <t>Periodicidade semanal (5ª feira); distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M454" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -24029,7 +23669,6 @@
           <t>Sábado</t>
         </is>
       </c>
-      <c r="E455" t="inlineStr"/>
       <c r="F455" t="inlineStr">
         <is>
           <t>1/3 Página Alto</t>
@@ -24040,20 +23679,16 @@
           <t>72x275mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H455" t="inlineStr"/>
-      <c r="I455" t="inlineStr"/>
       <c r="J455" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
       <c r="L455" t="inlineStr">
         <is>
           <t>Periodicidade semanal (5ª feira); distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M455" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -24076,7 +23711,6 @@
           <t>Sábado</t>
         </is>
       </c>
-      <c r="E456" t="inlineStr"/>
       <c r="F456" t="inlineStr">
         <is>
           <t>1/3 Página Baixo</t>
@@ -24087,20 +23721,16 @@
           <t>205x91mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H456" t="inlineStr"/>
-      <c r="I456" t="inlineStr"/>
       <c r="J456" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
       <c r="L456" t="inlineStr">
         <is>
           <t>Periodicidade semanal (5ª feira); distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M456" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -24123,7 +23753,6 @@
           <t>Sábado Viajante</t>
         </is>
       </c>
-      <c r="E457" t="inlineStr"/>
       <c r="F457" t="inlineStr">
         <is>
           <t>Página Dupla</t>
@@ -24134,20 +23763,16 @@
           <t>410x275mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H457" t="inlineStr"/>
-      <c r="I457" t="inlineStr"/>
       <c r="J457" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K457" t="inlineStr"/>
       <c r="L457" t="inlineStr">
         <is>
           <t>Periodicidade trimestral; distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -24170,7 +23795,6 @@
           <t>Sábado Viajante</t>
         </is>
       </c>
-      <c r="E458" t="inlineStr"/>
       <c r="F458" t="inlineStr">
         <is>
           <t>Página</t>
@@ -24181,20 +23805,16 @@
           <t>205x275mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H458" t="inlineStr"/>
-      <c r="I458" t="inlineStr"/>
       <c r="J458" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
       <c r="L458" t="inlineStr">
         <is>
           <t>Periodicidade trimestral; distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M458" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -24217,7 +23837,6 @@
           <t>Sábado Viajante</t>
         </is>
       </c>
-      <c r="E459" t="inlineStr"/>
       <c r="F459" t="inlineStr">
         <is>
           <t>1/2 Página Dupla</t>
@@ -24228,20 +23847,16 @@
           <t>410x137mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H459" t="inlineStr"/>
-      <c r="I459" t="inlineStr"/>
       <c r="J459" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
       <c r="L459" t="inlineStr">
         <is>
           <t>Periodicidade trimestral; distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -24264,7 +23879,6 @@
           <t>Sábado Viajante</t>
         </is>
       </c>
-      <c r="E460" t="inlineStr"/>
       <c r="F460" t="inlineStr">
         <is>
           <t>1/2 Página Alto</t>
@@ -24275,20 +23889,16 @@
           <t>102x275mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H460" t="inlineStr"/>
-      <c r="I460" t="inlineStr"/>
       <c r="J460" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
       <c r="L460" t="inlineStr">
         <is>
           <t>Periodicidade trimestral; distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -24311,7 +23921,6 @@
           <t>Sábado Viajante</t>
         </is>
       </c>
-      <c r="E461" t="inlineStr"/>
       <c r="F461" t="inlineStr">
         <is>
           <t>1/2 Página Baixo</t>
@@ -24322,20 +23931,16 @@
           <t>205x137mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H461" t="inlineStr"/>
-      <c r="I461" t="inlineStr"/>
       <c r="J461" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
       <c r="L461" t="inlineStr">
         <is>
           <t>Periodicidade trimestral; distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M461" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -24358,7 +23963,6 @@
           <t>Sábado Viajante</t>
         </is>
       </c>
-      <c r="E462" t="inlineStr"/>
       <c r="F462" t="inlineStr">
         <is>
           <t>1/3 Página Alto</t>
@@ -24369,20 +23973,16 @@
           <t>72x275mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H462" t="inlineStr"/>
-      <c r="I462" t="inlineStr"/>
       <c r="J462" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K462" t="inlineStr"/>
       <c r="L462" t="inlineStr">
         <is>
           <t>Periodicidade trimestral; distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M462" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -24405,7 +24005,6 @@
           <t>Sábado Viajante</t>
         </is>
       </c>
-      <c r="E463" t="inlineStr"/>
       <c r="F463" t="inlineStr">
         <is>
           <t>1/3 Página Baixo</t>
@@ -24416,20 +24015,16 @@
           <t>205x91mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H463" t="inlineStr"/>
-      <c r="I463" t="inlineStr"/>
       <c r="J463" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
       <c r="L463" t="inlineStr">
         <is>
           <t>Periodicidade trimestral; distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M463" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -24452,7 +24047,6 @@
           <t>TV Guia</t>
         </is>
       </c>
-      <c r="E464" t="inlineStr"/>
       <c r="F464" t="inlineStr">
         <is>
           <t>Página Dupla</t>
@@ -24463,20 +24057,16 @@
           <t>400x295mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H464" t="inlineStr"/>
-      <c r="I464" t="inlineStr"/>
       <c r="J464" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr"/>
       <c r="L464" t="inlineStr">
         <is>
           <t>Periodicidade semanal (6ª feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo LWC 57g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M464" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -24499,7 +24089,6 @@
           <t>TV Guia</t>
         </is>
       </c>
-      <c r="E465" t="inlineStr"/>
       <c r="F465" t="inlineStr">
         <is>
           <t>Página</t>
@@ -24510,20 +24099,16 @@
           <t>200x295mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H465" t="inlineStr"/>
-      <c r="I465" t="inlineStr"/>
       <c r="J465" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr"/>
       <c r="L465" t="inlineStr">
         <is>
           <t>Periodicidade semanal (6ª feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo LWC 57g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -24546,7 +24131,6 @@
           <t>TV Guia</t>
         </is>
       </c>
-      <c r="E466" t="inlineStr"/>
       <c r="F466" t="inlineStr">
         <is>
           <t>1/2 Página Dupla</t>
@@ -24557,20 +24141,16 @@
           <t>400x147mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H466" t="inlineStr"/>
-      <c r="I466" t="inlineStr"/>
       <c r="J466" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
       <c r="L466" t="inlineStr">
         <is>
           <t>Periodicidade semanal (6ª feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo LWC 57g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M466" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -24593,7 +24173,6 @@
           <t>TV Guia</t>
         </is>
       </c>
-      <c r="E467" t="inlineStr"/>
       <c r="F467" t="inlineStr">
         <is>
           <t>1/2 Página Alto</t>
@@ -24604,20 +24183,16 @@
           <t>100x295mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H467" t="inlineStr"/>
-      <c r="I467" t="inlineStr"/>
       <c r="J467" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K467" t="inlineStr"/>
       <c r="L467" t="inlineStr">
         <is>
           <t>Periodicidade semanal (6ª feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo LWC 57g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M467" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -24640,7 +24215,6 @@
           <t>TV Guia</t>
         </is>
       </c>
-      <c r="E468" t="inlineStr"/>
       <c r="F468" t="inlineStr">
         <is>
           <t>1/2 Página Baixo</t>
@@ -24651,20 +24225,16 @@
           <t>200x147mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H468" t="inlineStr"/>
-      <c r="I468" t="inlineStr"/>
       <c r="J468" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
       <c r="L468" t="inlineStr">
         <is>
           <t>Periodicidade semanal (6ª feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo LWC 57g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M468" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -24687,7 +24257,6 @@
           <t>TV Guia</t>
         </is>
       </c>
-      <c r="E469" t="inlineStr"/>
       <c r="F469" t="inlineStr">
         <is>
           <t>1/3 Página Alto</t>
@@ -24698,20 +24267,16 @@
           <t>72x295mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H469" t="inlineStr"/>
-      <c r="I469" t="inlineStr"/>
       <c r="J469" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
       <c r="L469" t="inlineStr">
         <is>
           <t>Periodicidade semanal (6ª feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo LWC 57g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M469" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -24734,7 +24299,6 @@
           <t>TV Guia</t>
         </is>
       </c>
-      <c r="E470" t="inlineStr"/>
       <c r="F470" t="inlineStr">
         <is>
           <t>1/3 Página Baixo</t>
@@ -24745,20 +24309,16 @@
           <t>200x105mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H470" t="inlineStr"/>
-      <c r="I470" t="inlineStr"/>
       <c r="J470" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="K470" t="inlineStr"/>
       <c r="L470" t="inlineStr">
         <is>
           <t>Periodicidade semanal (6ª feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo LWC 57g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M470" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -24781,7 +24341,6 @@
           <t>Expresso</t>
         </is>
       </c>
-      <c r="E471" t="inlineStr"/>
       <c r="F471" t="inlineStr">
         <is>
           <t>Página Dupla</t>
@@ -24792,20 +24351,16 @@
           <t>548x408mm</t>
         </is>
       </c>
-      <c r="H471" t="inlineStr"/>
-      <c r="I471" t="inlineStr"/>
       <c r="J471" t="inlineStr">
         <is>
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr"/>
       <c r="L471" t="inlineStr">
         <is>
           <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M471" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -24828,7 +24383,6 @@
           <t>Expresso</t>
         </is>
       </c>
-      <c r="E472" t="inlineStr"/>
       <c r="F472" t="inlineStr">
         <is>
           <t>Página</t>
@@ -24839,20 +24393,16 @@
           <t>264x408mm</t>
         </is>
       </c>
-      <c r="H472" t="inlineStr"/>
-      <c r="I472" t="inlineStr"/>
       <c r="J472" t="inlineStr">
         <is>
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr"/>
       <c r="L472" t="inlineStr">
         <is>
           <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -24875,7 +24425,6 @@
           <t>Expresso</t>
         </is>
       </c>
-      <c r="E473" t="inlineStr"/>
       <c r="F473" t="inlineStr">
         <is>
           <t>1/2 Página Baixo</t>
@@ -24886,20 +24435,16 @@
           <t>264x201,8mm</t>
         </is>
       </c>
-      <c r="H473" t="inlineStr"/>
-      <c r="I473" t="inlineStr"/>
       <c r="J473" t="inlineStr">
         <is>
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="K473" t="inlineStr"/>
       <c r="L473" t="inlineStr">
         <is>
           <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -24922,7 +24467,6 @@
           <t>Expresso</t>
         </is>
       </c>
-      <c r="E474" t="inlineStr"/>
       <c r="F474" t="inlineStr">
         <is>
           <t>1/2 Página Alto</t>
@@ -24933,20 +24477,16 @@
           <t>130x408mm</t>
         </is>
       </c>
-      <c r="H474" t="inlineStr"/>
-      <c r="I474" t="inlineStr"/>
       <c r="J474" t="inlineStr">
         <is>
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="K474" t="inlineStr"/>
       <c r="L474" t="inlineStr">
         <is>
           <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M474" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -24969,7 +24509,6 @@
           <t>Expresso</t>
         </is>
       </c>
-      <c r="E475" t="inlineStr"/>
       <c r="F475" t="inlineStr">
         <is>
           <t>1/2 Página Dupla</t>
@@ -24980,20 +24519,16 @@
           <t>548x201,8mm</t>
         </is>
       </c>
-      <c r="H475" t="inlineStr"/>
-      <c r="I475" t="inlineStr"/>
       <c r="J475" t="inlineStr">
         <is>
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="K475" t="inlineStr"/>
       <c r="L475" t="inlineStr">
         <is>
           <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M475" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -25016,7 +24551,6 @@
           <t>Expresso</t>
         </is>
       </c>
-      <c r="E476" t="inlineStr"/>
       <c r="F476" t="inlineStr">
         <is>
           <t>Júnior Page</t>
@@ -25027,20 +24561,16 @@
           <t>174,8x277mm</t>
         </is>
       </c>
-      <c r="H476" t="inlineStr"/>
-      <c r="I476" t="inlineStr"/>
       <c r="J476" t="inlineStr">
         <is>
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="K476" t="inlineStr"/>
       <c r="L476" t="inlineStr">
         <is>
           <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M476" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -25063,7 +24593,6 @@
           <t>Expresso</t>
         </is>
       </c>
-      <c r="E477" t="inlineStr"/>
       <c r="F477" t="inlineStr">
         <is>
           <t>1/4 Página</t>
@@ -25074,20 +24603,16 @@
           <t>130x201,8mm</t>
         </is>
       </c>
-      <c r="H477" t="inlineStr"/>
-      <c r="I477" t="inlineStr"/>
       <c r="J477" t="inlineStr">
         <is>
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
       <c r="L477" t="inlineStr">
         <is>
           <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M477" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -25110,7 +24635,6 @@
           <t>Expresso</t>
         </is>
       </c>
-      <c r="E478" t="inlineStr"/>
       <c r="F478" t="inlineStr">
         <is>
           <t>1/4 Página Landscape</t>
@@ -25121,20 +24645,16 @@
           <t>264x92,2mm</t>
         </is>
       </c>
-      <c r="H478" t="inlineStr"/>
-      <c r="I478" t="inlineStr"/>
       <c r="J478" t="inlineStr">
         <is>
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
       <c r="L478" t="inlineStr">
         <is>
           <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M478" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -25157,7 +24677,6 @@
           <t>Expresso</t>
         </is>
       </c>
-      <c r="E479" t="inlineStr"/>
       <c r="F479" t="inlineStr">
         <is>
           <t>1/8 Página</t>
@@ -25168,20 +24687,16 @@
           <t>130x101mm</t>
         </is>
       </c>
-      <c r="H479" t="inlineStr"/>
-      <c r="I479" t="inlineStr"/>
       <c r="J479" t="inlineStr">
         <is>
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
       <c r="L479" t="inlineStr">
         <is>
           <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M479" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -25204,7 +24719,6 @@
           <t>Expresso</t>
         </is>
       </c>
-      <c r="E480" t="inlineStr"/>
       <c r="F480" t="inlineStr">
         <is>
           <t>Orelha de Capa</t>
@@ -25215,20 +24729,16 @@
           <t>450x60mm</t>
         </is>
       </c>
-      <c r="H480" t="inlineStr"/>
-      <c r="I480" t="inlineStr"/>
       <c r="J480" t="inlineStr">
         <is>
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
       <c r="L480" t="inlineStr">
         <is>
           <t>Formato especial de capa do 1º Caderno. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M480" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -25251,7 +24761,6 @@
           <t>Expresso</t>
         </is>
       </c>
-      <c r="E481" t="inlineStr"/>
       <c r="F481" t="inlineStr">
         <is>
           <t>Sanca de Capa</t>
@@ -25262,20 +24771,16 @@
           <t>240x264mm</t>
         </is>
       </c>
-      <c r="H481" t="inlineStr"/>
-      <c r="I481" t="inlineStr"/>
       <c r="J481" t="inlineStr">
         <is>
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="K481" t="inlineStr"/>
       <c r="L481" t="inlineStr">
         <is>
           <t>Formato especial de capa do 1º Caderno. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M481" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -25298,7 +24803,6 @@
           <t>Expresso</t>
         </is>
       </c>
-      <c r="E482" t="inlineStr"/>
       <c r="F482" t="inlineStr">
         <is>
           <t>Saco Expresso</t>
@@ -25309,20 +24813,16 @@
           <t>450x360mm (área útil do cliente: 450x278mm)</t>
         </is>
       </c>
-      <c r="H482" t="inlineStr"/>
-      <c r="I482" t="inlineStr"/>
       <c r="J482" t="inlineStr">
         <is>
           <t>PDF em alta definição (elementos de desenho em vetorial, imagens à parte + JPEG para visualização)</t>
         </is>
       </c>
-      <c r="K482" t="inlineStr"/>
       <c r="L482" t="inlineStr">
         <is>
           <t>Saco em papel liso impresso a CMYK + 2 cores; a tarja com a informação é sempre na cor do Expresso (Pantone 315C).</t>
         </is>
       </c>
-      <c r="M482" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -25345,7 +24845,6 @@
           <t>Expresso Economia</t>
         </is>
       </c>
-      <c r="E483" t="inlineStr"/>
       <c r="F483" t="inlineStr">
         <is>
           <t>Página Dupla</t>
@@ -25356,20 +24855,16 @@
           <t>548x408mm</t>
         </is>
       </c>
-      <c r="H483" t="inlineStr"/>
-      <c r="I483" t="inlineStr"/>
       <c r="J483" t="inlineStr">
         <is>
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="K483" t="inlineStr"/>
       <c r="L483" t="inlineStr">
         <is>
           <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M483" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -25392,7 +24887,6 @@
           <t>Expresso Economia</t>
         </is>
       </c>
-      <c r="E484" t="inlineStr"/>
       <c r="F484" t="inlineStr">
         <is>
           <t>Página</t>
@@ -25403,20 +24897,16 @@
           <t>264x408mm</t>
         </is>
       </c>
-      <c r="H484" t="inlineStr"/>
-      <c r="I484" t="inlineStr"/>
       <c r="J484" t="inlineStr">
         <is>
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="K484" t="inlineStr"/>
       <c r="L484" t="inlineStr">
         <is>
           <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M484" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -25439,7 +24929,6 @@
           <t>Expresso Economia</t>
         </is>
       </c>
-      <c r="E485" t="inlineStr"/>
       <c r="F485" t="inlineStr">
         <is>
           <t>1/2 Página Baixo</t>
@@ -25450,20 +24939,16 @@
           <t>264x201,8mm</t>
         </is>
       </c>
-      <c r="H485" t="inlineStr"/>
-      <c r="I485" t="inlineStr"/>
       <c r="J485" t="inlineStr">
         <is>
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
       <c r="L485" t="inlineStr">
         <is>
           <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M485" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -25486,7 +24971,6 @@
           <t>Expresso Economia</t>
         </is>
       </c>
-      <c r="E486" t="inlineStr"/>
       <c r="F486" t="inlineStr">
         <is>
           <t>1/2 Página Alto</t>
@@ -25497,20 +24981,16 @@
           <t>130x408mm</t>
         </is>
       </c>
-      <c r="H486" t="inlineStr"/>
-      <c r="I486" t="inlineStr"/>
       <c r="J486" t="inlineStr">
         <is>
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="K486" t="inlineStr"/>
       <c r="L486" t="inlineStr">
         <is>
           <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M486" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -25533,7 +25013,6 @@
           <t>Expresso Economia</t>
         </is>
       </c>
-      <c r="E487" t="inlineStr"/>
       <c r="F487" t="inlineStr">
         <is>
           <t>1/2 Página Dupla</t>
@@ -25544,20 +25023,16 @@
           <t>548x201,8mm</t>
         </is>
       </c>
-      <c r="H487" t="inlineStr"/>
-      <c r="I487" t="inlineStr"/>
       <c r="J487" t="inlineStr">
         <is>
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
       <c r="L487" t="inlineStr">
         <is>
           <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M487" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -25580,7 +25055,6 @@
           <t>Expresso Economia</t>
         </is>
       </c>
-      <c r="E488" t="inlineStr"/>
       <c r="F488" t="inlineStr">
         <is>
           <t>Júnior Page</t>
@@ -25591,20 +25065,16 @@
           <t>174,8x277mm</t>
         </is>
       </c>
-      <c r="H488" t="inlineStr"/>
-      <c r="I488" t="inlineStr"/>
       <c r="J488" t="inlineStr">
         <is>
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
       <c r="L488" t="inlineStr">
         <is>
           <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M488" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -25627,7 +25097,6 @@
           <t>Expresso Economia</t>
         </is>
       </c>
-      <c r="E489" t="inlineStr"/>
       <c r="F489" t="inlineStr">
         <is>
           <t>1/4 Página</t>
@@ -25638,20 +25107,16 @@
           <t>130x201,8mm</t>
         </is>
       </c>
-      <c r="H489" t="inlineStr"/>
-      <c r="I489" t="inlineStr"/>
       <c r="J489" t="inlineStr">
         <is>
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="K489" t="inlineStr"/>
       <c r="L489" t="inlineStr">
         <is>
           <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M489" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -25674,7 +25139,6 @@
           <t>Expresso Economia</t>
         </is>
       </c>
-      <c r="E490" t="inlineStr"/>
       <c r="F490" t="inlineStr">
         <is>
           <t>1/4 Página Landscape</t>
@@ -25685,20 +25149,16 @@
           <t>264x92,2mm</t>
         </is>
       </c>
-      <c r="H490" t="inlineStr"/>
-      <c r="I490" t="inlineStr"/>
       <c r="J490" t="inlineStr">
         <is>
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr"/>
       <c r="L490" t="inlineStr">
         <is>
           <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M490" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -25721,7 +25181,6 @@
           <t>Expresso Economia</t>
         </is>
       </c>
-      <c r="E491" t="inlineStr"/>
       <c r="F491" t="inlineStr">
         <is>
           <t>1/8 Página</t>
@@ -25732,20 +25191,16 @@
           <t>130x101mm</t>
         </is>
       </c>
-      <c r="H491" t="inlineStr"/>
-      <c r="I491" t="inlineStr"/>
       <c r="J491" t="inlineStr">
         <is>
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr"/>
       <c r="L491" t="inlineStr">
         <is>
           <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M491" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -25768,7 +25223,6 @@
           <t>Expresso Economia</t>
         </is>
       </c>
-      <c r="E492" t="inlineStr"/>
       <c r="F492" t="inlineStr">
         <is>
           <t>Orelha (Janela na Primeira Página)</t>
@@ -25779,20 +25233,16 @@
           <t>41x32mm</t>
         </is>
       </c>
-      <c r="H492" t="inlineStr"/>
-      <c r="I492" t="inlineStr"/>
       <c r="J492" t="inlineStr">
         <is>
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="K492" t="inlineStr"/>
       <c r="L492" t="inlineStr">
         <is>
           <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M492" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -25815,7 +25265,6 @@
           <t>Expresso Economia</t>
         </is>
       </c>
-      <c r="E493" t="inlineStr"/>
       <c r="F493" t="inlineStr">
         <is>
           <t>Orelha Grande (Janela na Primeira Página)</t>
@@ -25826,20 +25275,16 @@
           <t>41x87mm</t>
         </is>
       </c>
-      <c r="H493" t="inlineStr"/>
-      <c r="I493" t="inlineStr"/>
       <c r="J493" t="inlineStr">
         <is>
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="K493" t="inlineStr"/>
       <c r="L493" t="inlineStr">
         <is>
           <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M493" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -25862,7 +25307,6 @@
           <t>Revista E</t>
         </is>
       </c>
-      <c r="E494" t="inlineStr"/>
       <c r="F494" t="inlineStr">
         <is>
           <t>Página Dupla</t>
@@ -25873,20 +25317,16 @@
           <t>530x337mm</t>
         </is>
       </c>
-      <c r="H494" t="inlineStr"/>
-      <c r="I494" t="inlineStr"/>
       <c r="J494" t="inlineStr">
         <is>
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
       <c r="L494" t="inlineStr">
         <is>
           <t>Impressão offset quadricromia — papel jornal melhorado 55g, capa couché mate 130g, lombada colada; localização obrigatória: +30%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M494" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -25909,7 +25349,6 @@
           <t>Revista E</t>
         </is>
       </c>
-      <c r="E495" t="inlineStr"/>
       <c r="F495" t="inlineStr">
         <is>
           <t>Página</t>
@@ -25920,20 +25359,16 @@
           <t>265x337mm</t>
         </is>
       </c>
-      <c r="H495" t="inlineStr"/>
-      <c r="I495" t="inlineStr"/>
       <c r="J495" t="inlineStr">
         <is>
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="K495" t="inlineStr"/>
       <c r="L495" t="inlineStr">
         <is>
           <t>Impressão offset quadricromia — papel jornal melhorado 55g, capa couché mate 130g, lombada colada; localização obrigatória: +30%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -25956,7 +25391,6 @@
           <t>Revista E</t>
         </is>
       </c>
-      <c r="E496" t="inlineStr"/>
       <c r="F496" t="inlineStr">
         <is>
           <t>1/2 Página Baixo</t>
@@ -25967,20 +25401,16 @@
           <t>265x167mm</t>
         </is>
       </c>
-      <c r="H496" t="inlineStr"/>
-      <c r="I496" t="inlineStr"/>
       <c r="J496" t="inlineStr">
         <is>
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="K496" t="inlineStr"/>
       <c r="L496" t="inlineStr">
         <is>
           <t>Impressão offset quadricromia — papel jornal melhorado 55g, capa couché mate 130g, lombada colada; localização obrigatória: +30%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -26003,7 +25433,6 @@
           <t>Revista E</t>
         </is>
       </c>
-      <c r="E497" t="inlineStr"/>
       <c r="F497" t="inlineStr">
         <is>
           <t>1/2 Página Alto</t>
@@ -26014,20 +25443,16 @@
           <t>130x337mm</t>
         </is>
       </c>
-      <c r="H497" t="inlineStr"/>
-      <c r="I497" t="inlineStr"/>
       <c r="J497" t="inlineStr">
         <is>
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
       <c r="L497" t="inlineStr">
         <is>
           <t>Impressão offset quadricromia — papel jornal melhorado 55g, capa couché mate 130g, lombada colada; localização obrigatória: +30%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M497" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -26050,7 +25475,6 @@
           <t>Revista E</t>
         </is>
       </c>
-      <c r="E498" t="inlineStr"/>
       <c r="F498" t="inlineStr">
         <is>
           <t>1/3 Página Alto</t>
@@ -26061,20 +25485,16 @@
           <t>90x337mm</t>
         </is>
       </c>
-      <c r="H498" t="inlineStr"/>
-      <c r="I498" t="inlineStr"/>
       <c r="J498" t="inlineStr">
         <is>
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="K498" t="inlineStr"/>
       <c r="L498" t="inlineStr">
         <is>
           <t>Impressão offset quadricromia — papel jornal melhorado 55g, capa couché mate 130g, lombada colada; localização obrigatória: +30%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -26097,7 +25517,6 @@
           <t>Revista E</t>
         </is>
       </c>
-      <c r="E499" t="inlineStr"/>
       <c r="F499" t="inlineStr">
         <is>
           <t>Rodapé</t>
@@ -26108,20 +25527,16 @@
           <t>265x108mm</t>
         </is>
       </c>
-      <c r="H499" t="inlineStr"/>
-      <c r="I499" t="inlineStr"/>
       <c r="J499" t="inlineStr">
         <is>
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
       <c r="L499" t="inlineStr">
         <is>
           <t>Impressão offset quadricromia — papel jornal melhorado 55g, capa couché mate 130g, lombada colada; localização obrigatória: +30%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -26144,7 +25559,6 @@
           <t>Revista E</t>
         </is>
       </c>
-      <c r="E500" t="inlineStr"/>
       <c r="F500" t="inlineStr">
         <is>
           <t>1/4 Página</t>
@@ -26155,20 +25569,16 @@
           <t>115x147mm</t>
         </is>
       </c>
-      <c r="H500" t="inlineStr"/>
-      <c r="I500" t="inlineStr"/>
       <c r="J500" t="inlineStr">
         <is>
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="K500" t="inlineStr"/>
       <c r="L500" t="inlineStr">
         <is>
           <t>Impressão offset quadricromia — papel jornal melhorado 55g, capa couché mate 130g, lombada colada; localização obrigatória: +30%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M500" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -26191,7 +25601,6 @@
           <t>Revista E</t>
         </is>
       </c>
-      <c r="E501" t="inlineStr"/>
       <c r="F501" t="inlineStr">
         <is>
           <t>1/6 Página</t>
@@ -26202,20 +25611,16 @@
           <t>75x147mm</t>
         </is>
       </c>
-      <c r="H501" t="inlineStr"/>
-      <c r="I501" t="inlineStr"/>
       <c r="J501" t="inlineStr">
         <is>
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="K501" t="inlineStr"/>
       <c r="L501" t="inlineStr">
         <is>
           <t>Impressão offset quadricromia — papel jornal melhorado 55g, capa couché mate 130g, lombada colada; localização obrigatória: +30%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M501" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -26238,7 +25643,6 @@
           <t>Revista E</t>
         </is>
       </c>
-      <c r="E502" t="inlineStr"/>
       <c r="F502" t="inlineStr">
         <is>
           <t>1/8 Página</t>
@@ -26249,20 +25653,16 @@
           <t>115x71mm</t>
         </is>
       </c>
-      <c r="H502" t="inlineStr"/>
-      <c r="I502" t="inlineStr"/>
       <c r="J502" t="inlineStr">
         <is>
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="K502" t="inlineStr"/>
       <c r="L502" t="inlineStr">
         <is>
           <t>Impressão offset quadricromia — papel jornal melhorado 55g, capa couché mate 130g, lombada colada; localização obrigatória: +30%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -26285,7 +25685,6 @@
           <t>Attitude</t>
         </is>
       </c>
-      <c r="E503" t="inlineStr"/>
       <c r="F503" t="inlineStr">
         <is>
           <t>Página (Par/Ímpar)</t>
@@ -26296,20 +25695,16 @@
           <t>215x278mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H503" t="inlineStr"/>
-      <c r="I503" t="inlineStr"/>
       <c r="J503" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF em alta resolução de 400 DPI (mínimo 300 DPI), CMYK, sem atribuição de perfil final</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr"/>
       <c r="L503" t="inlineStr">
         <is>
           <t>Periodicidade bimestral (janeiro, março, maio, julho, setembro, novembro); revista bilingue (português + inglês); distribuição em Portugal e mais 22 países; páginas duplas com desvio de 6mm ao centro (3mm para a esquerda e 3mm para a direita) para garantir o acerto central. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M503" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -26332,7 +25727,6 @@
           <t>Attitude</t>
         </is>
       </c>
-      <c r="E504" t="inlineStr"/>
       <c r="F504" t="inlineStr">
         <is>
           <t>1/2 Página Vertical</t>
@@ -26343,20 +25737,16 @@
           <t>106,25x278mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H504" t="inlineStr"/>
-      <c r="I504" t="inlineStr"/>
       <c r="J504" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF em alta resolução de 400 DPI (mínimo 300 DPI), CMYK, sem atribuição de perfil final</t>
         </is>
       </c>
-      <c r="K504" t="inlineStr"/>
       <c r="L504" t="inlineStr">
         <is>
           <t>Periodicidade bimestral (janeiro, março, maio, julho, setembro, novembro); revista bilingue (português + inglês); distribuição em Portugal e mais 22 países; páginas duplas com desvio de 6mm ao centro (3mm para a esquerda e 3mm para a direita) para garantir o acerto central. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M504" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -26379,7 +25769,6 @@
           <t>Attitude</t>
         </is>
       </c>
-      <c r="E505" t="inlineStr"/>
       <c r="F505" t="inlineStr">
         <is>
           <t>1/2 Página Horizontal</t>
@@ -26390,20 +25779,16 @@
           <t>215x143mm (+3mm bleed)</t>
         </is>
       </c>
-      <c r="H505" t="inlineStr"/>
-      <c r="I505" t="inlineStr"/>
       <c r="J505" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF em alta resolução de 400 DPI (mínimo 300 DPI), CMYK, sem atribuição de perfil final</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr"/>
       <c r="L505" t="inlineStr">
         <is>
           <t>Periodicidade bimestral (janeiro, março, maio, julho, setembro, novembro); revista bilingue (português + inglês); distribuição em Portugal e mais 22 países; páginas duplas com desvio de 6mm ao centro (3mm para a esquerda e 3mm para a direita) para garantir o acerto central. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M505" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -26426,7 +25811,6 @@
           <t>Attitude</t>
         </is>
       </c>
-      <c r="E506" t="inlineStr"/>
       <c r="F506" t="inlineStr">
         <is>
           <t>Página Dupla</t>
@@ -26437,20 +25821,161 @@
           <t>430x278mm (+3mm bleed, +6mm massa central)</t>
         </is>
       </c>
-      <c r="H506" t="inlineStr"/>
-      <c r="I506" t="inlineStr"/>
       <c r="J506" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF em alta resolução de 400 DPI (mínimo 300 DPI), CMYK, sem atribuição de perfil final</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
       <c r="L506" t="inlineStr">
         <is>
           <t>Periodicidade bimestral (janeiro, março, maio, julho, setembro, novembro); revista bilingue (português + inglês); distribuição em Portugal e mais 22 países; páginas duplas com desvio de 6mm ao centro (3mm para a esquerda e 3mm para a direita) para garantir o acerto central. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
-      <c r="M506" t="inlineStr"/>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>GoFastWay</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>GoFastWay</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr"/>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>Spot TV (SD — IMX50)</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>720x576px, 25 fps</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr"/>
+      <c r="J507" t="inlineStr">
+        <is>
+          <t>MXF (OP-1a), codec IMX50, 50 Mb/s (CBR), croma 4:2:2, entrelaçado (Interlaced UFF, 16:9FHA), extensão .mxf</t>
+        </is>
+      </c>
+      <c r="K507" t="inlineStr"/>
+      <c r="L507" t="inlineStr">
+        <is>
+          <t>Estrutura obrigatória do ficheiro: o conteúdo publicitário deve começar no primeiro frame de vídeo e terminar no último — pre-roll e post-roll de 0 frames, duração do ficheiro = duração do spot x 25 frames. Áudio: PCM, 2 canais (stereo), 24 bit, 48 KHz, peak level -3dB TP máx., loudness (integrado) -23 LUFS. Nomenclatura sugerida para o ficheiro: &lt;Pub ID&gt;_&lt;Nome do Spot&gt;_&lt;Duração&gt;.mxf (ex.: PUB-2015-000345_Fiat 500X Sport Edition_30.mxf) — não é obrigatória, mas recomendada sempre que possível. Entrega exclusivamente por utilizador registado através do Portal GoFastWay (www.gofastway.tv). Todos os ficheiros passam por controlo automático de qualidade (conformidade técnica com estas specs + análise subjetiva de vídeo e áudio); em caso de inconsistência, a GoFastWay pode pedir a entrega de um novo ficheiro corrigido.</t>
+        </is>
+      </c>
+      <c r="M507" t="inlineStr"/>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>GoFastWay</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>GoFastWay</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr"/>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>Spot TV (HD — XDCAM HD422)</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>1920x1080px, 25 fps</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr"/>
+      <c r="J508" t="inlineStr">
+        <is>
+          <t>MXF (OP-1a), codec XDCAM HD422, 50 Mb/s mín. (CBR), croma 4:2:2, entrelaçado (Interlaced UFF), extensão .mxf</t>
+        </is>
+      </c>
+      <c r="K508" t="inlineStr"/>
+      <c r="L508" t="inlineStr">
+        <is>
+          <t>Estrutura obrigatória do ficheiro: o conteúdo publicitário deve começar no primeiro frame de vídeo e terminar no último — pre-roll e post-roll de 0 frames, duração do ficheiro = duração do spot x 25 frames. Áudio: PCM, 2 canais (stereo), 24 bit, 48 KHz, peak level -3dB TP máx., loudness (integrado) -23 LUFS. Nomenclatura sugerida para o ficheiro: &lt;Pub ID&gt;_&lt;Nome do Spot&gt;_&lt;Duração&gt;.mxf (ex.: PUB-2015-000345_Fiat 500X Sport Edition_30.mxf) — não é obrigatória, mas recomendada sempre que possível. Entrega exclusivamente por utilizador registado através do Portal GoFastWay (www.gofastway.tv). Todos os ficheiros passam por controlo automático de qualidade (conformidade técnica com estas specs + análise subjetiva de vídeo e áudio); em caso de inconsistência, a GoFastWay pode pedir a entrega de um novo ficheiro corrigido.</t>
+        </is>
+      </c>
+      <c r="M508" t="inlineStr"/>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>Rádio</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>Rádio</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>Rádio</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>Rádio</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr"/>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>Spot Rádio</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr"/>
+      <c r="H509" t="inlineStr"/>
+      <c r="I509" t="inlineStr"/>
+      <c r="J509" t="inlineStr">
+        <is>
+          <t>MP4 (áudio AAC)</t>
+        </is>
+      </c>
+      <c r="K509" t="inlineStr"/>
+      <c r="L509" t="inlineStr">
+        <is>
+          <t>Não foi indicada nenhuma plataforma de distribuição nem rádio específica — specs genéricas de entrega, a confirmar sempre junto da rádio ou da central de meios antes de entregar. Áudio AAC, 2 canais (stereo) ou mono consoante o spot, 48 KHz, bit rate mínimo recomendado 320 kbps (CBR), loudness (integrado) -23 LUFS e peak level -3dB TP máx. — o mesmo padrão de loudness broadcast já usado para TV.</t>
+        </is>
+      </c>
+      <c r="M509" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M509"/>
+  <dimension ref="A1:M524"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="18.08984375" customWidth="1" style="2" min="1" max="1"/>
@@ -19495,7 +19495,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>Arte final: 784x300mm (escala reduzida). Medida real: 8000x3000mm. Área visível: 7950x2950mm.</t>
+          <t>Arte final: 784x300mm (escala reduzida) + 1mm de bleed. Medida real: 8000x3000mm. Área visível: 7950x2950mm.</t>
         </is>
       </c>
       <c r="J357" t="inlineStr">
@@ -19537,7 +19537,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>3 tamanhos disponíveis: 640x417px, 800x522px ou 1024x667px. 3 momentos distintos: 1º momento 10s, 2º momento 3s, 3º momento 10s (pode usar 1, 2 ou 3 imagens diferentes, ou combinar com vídeo nos vários momentos).</t>
+          <t>3 tamanhos disponíveis (obrigatórios os três): 640x417px, 800x522px ou 1024x668px. 3 momentos distintos: 1º momento 10s, 2º momento 3s, 3º momento 10s (pode usar 1, 2 ou 3 imagens diferentes, ou combinar com vídeo nos vários momentos).</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -19547,12 +19547,12 @@
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>JPG ou PNG, resolução igual ou superior a 72 dpi</t>
+          <t>JPG ou PNG, resolução entre 72 e 100 DPI</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t>Não é possível apresentar conteúdos que mostrem, de forma explícita e não contextualizada, partes do corpo habitualmente resguardadas; mencionem instituições financeiras monetárias e de pagamento, partidos/associações políticas ou sindicais, organizações religiosas; usem símbolos/linguagem que se possam confundir com o funcionamento do caixa automático; ou que, no primeiro momento publicitário, mostrem qualquer preço sem identificação clara de que é um preço do anunciante, produto ou serviço. Para todos os outros princípios aplica-se o código da publicidade.</t>
+          <t>Tamanho até 1000kB/s (125KB/s). Profundidade de cor: 24 bits/pixel. Não é possível apresentar conteúdos que mostrem, de forma explícita e não contextualizada, partes do corpo habitualmente resguardadas; mencionem instituições financeiras monetárias e de pagamento, partidos/associações políticas ou sindicais, organizações religiosas; usem símbolos/linguagem que se possam confundir com o funcionamento do caixa automático; ou que, no primeiro momento publicitário, mostrem qualquer preço sem identificação clara de que é um preço do anunciante, produto ou serviço. Para todos os outros princípios aplica-se o código da publicidade.</t>
         </is>
       </c>
     </row>
@@ -19584,7 +19584,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>2 tamanhos disponíveis: 640x392px ou 800x496px. 3 momentos distintos: 1º momento 5s, 2º momento 2s, 3º momento 5s (pode usar 1, 2 ou 3 vídeos diferentes, ou combinar com imagens nos vários momentos; sugestão: terminar com a imagem estática do último frame).</t>
+          <t>3 tamanhos disponíveis (obrigatórios os três): 640x417px, 800x522px ou 1024x668px. 3 momentos distintos: 1º momento 10s, 2º momento 3s, 3º momento 10s (pode usar 1, 2 ou 3 vídeos diferentes, ou combinar com imagens nos vários momentos; sugestão: terminar com a imagem estática do último frame).</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -19594,12 +19594,12 @@
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>MPEG-1 ou MP4</t>
+          <t>MP4, resolução entre 72 e 100 DPI</t>
         </is>
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t>Sem canal áudio. Frame rate: 24 frames/s. Profundidade de cor: 24 bits/pixel. Mesmos princípios de conteúdo do formato "Multibanco - Imagem".</t>
+          <t>Sem canal áudio. Bitrate médio 1 Mb/s, máximo 8 Mb/s. Tamanho até 1000kB/s (125KB/s). Frame rate: 24 ou 30 frames/s. Profundidade de cor: 24 bits/pixel. Mesmos princípios de conteúdo do formato "Multibanco - Imagem".</t>
         </is>
       </c>
     </row>
@@ -19688,12 +19688,12 @@
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>MP4, codec H264</t>
+          <t>Vídeo: MP4/MOV; Imagem: qualquer formato; Web: HTML/URL — codec H264</t>
         </is>
       </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t>Duração: 10 segundos (obrigatório). Bitrate máx. 6 Mbps. Framerate 24 frames/s. No suporte de 3 ecrãs existe uma separação real de 2,5cm entre ecrãs, que divide/corta a imagem — deve ser tido em conta para não deformar frases ou elementos relevantes (zonas de quebra).</t>
+          <t>Duração: múltiplos de 10 segundos, com um máximo de 1 minuto. Bitrate máx. 6 Mbps. Framerate 30 frames/s. Tamanho máximo: 100MB. No suporte de 3 ecrãs existe uma separação real de 2,5cm entre ecrãs, que divide/corta a imagem — deve ser tido em conta para não deformar frases ou elementos relevantes (zonas de quebra). Este ficheiro pode também ser utilizado no suporte LED 16x9, ecrã triplo (3 ecrãs) ou Tomi Spot TV.</t>
         </is>
       </c>
     </row>
@@ -19740,12 +19740,12 @@
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>MP4, codec H264</t>
+          <t>Vídeo: MP4/MOV; Imagem: qualquer formato; Web: HTML/URL — codec H264</t>
         </is>
       </c>
       <c r="L362" t="inlineStr">
         <is>
-          <t>Duração: 10 segundos (obrigatório). Bitrate máx. 6 Mbps. Framerate 24 frames/s.</t>
+          <t>Duração: múltiplos de 10 segundos, com um máximo de 1 minuto. Bitrate máx. 6 Mbps. Framerate 30 frames/s. Tamanho máximo: 100MB. Este ficheiro pode ser utilizado no suporte dos formatos digitais verticais: Mupi Digital ou Tomi OOH.</t>
         </is>
       </c>
     </row>
@@ -19787,7 +19787,7 @@
       </c>
       <c r="L363" t="inlineStr">
         <is>
-          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão anterior do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Envio via WeTransfer/Hightail/Dropbox ou FTP do cliente; CD/DVD sempre com prova de cor.</t>
+          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Papel Couché mate (COM) ou Sunrise entre 130-140g/m2; densidade até 117µm. Prazo de entrega: até 5 dias úteis antes do início da campanha. Quantidades requeridas: +25% além da quantidade contratada. Impressão em serigrafia ou offset; impressão digital (tintas térmicas, UV ou semelhantes) só aceite até redes de 50 unidades. Cartazes entregues em rolos, separados por tema e sem misturas — cada rolo só pode ter um tema, com o maior número possível de cartazes; por tema, entrega em 6 rolos de 50 cartazes ou, em alternativa, 4 rolos de 38 + 4 rolos de 37. Rolos identificados com o nome da Campanha, Tema e Quantidade. Envio via WeTransfer/Hightail/Dropbox ou FTP do cliente (com utilizador e password); CD/DVD sempre com prova de cor.</t>
         </is>
       </c>
     </row>
@@ -25853,7 +25853,6 @@
           <t>GoFastWay</t>
         </is>
       </c>
-      <c r="E507" t="inlineStr"/>
       <c r="F507" t="inlineStr">
         <is>
           <t>Spot TV (SD — IMX50)</t>
@@ -25869,19 +25868,16 @@
           <t>16:9</t>
         </is>
       </c>
-      <c r="I507" t="inlineStr"/>
       <c r="J507" t="inlineStr">
         <is>
           <t>MXF (OP-1a), codec IMX50, 50 Mb/s (CBR), croma 4:2:2, entrelaçado (Interlaced UFF, 16:9FHA), extensão .mxf</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
       <c r="L507" t="inlineStr">
         <is>
           <t>Estrutura obrigatória do ficheiro: o conteúdo publicitário deve começar no primeiro frame de vídeo e terminar no último — pre-roll e post-roll de 0 frames, duração do ficheiro = duração do spot x 25 frames. Áudio: PCM, 2 canais (stereo), 24 bit, 48 KHz, peak level -3dB TP máx., loudness (integrado) -23 LUFS. Nomenclatura sugerida para o ficheiro: &lt;Pub ID&gt;_&lt;Nome do Spot&gt;_&lt;Duração&gt;.mxf (ex.: PUB-2015-000345_Fiat 500X Sport Edition_30.mxf) — não é obrigatória, mas recomendada sempre que possível. Entrega exclusivamente por utilizador registado através do Portal GoFastWay (www.gofastway.tv). Todos os ficheiros passam por controlo automático de qualidade (conformidade técnica com estas specs + análise subjetiva de vídeo e áudio); em caso de inconsistência, a GoFastWay pode pedir a entrega de um novo ficheiro corrigido.</t>
         </is>
       </c>
-      <c r="M507" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -25904,7 +25900,6 @@
           <t>GoFastWay</t>
         </is>
       </c>
-      <c r="E508" t="inlineStr"/>
       <c r="F508" t="inlineStr">
         <is>
           <t>Spot TV (HD — XDCAM HD422)</t>
@@ -25920,19 +25915,16 @@
           <t>16:9</t>
         </is>
       </c>
-      <c r="I508" t="inlineStr"/>
       <c r="J508" t="inlineStr">
         <is>
           <t>MXF (OP-1a), codec XDCAM HD422, 50 Mb/s mín. (CBR), croma 4:2:2, entrelaçado (Interlaced UFF), extensão .mxf</t>
         </is>
       </c>
-      <c r="K508" t="inlineStr"/>
       <c r="L508" t="inlineStr">
         <is>
           <t>Estrutura obrigatória do ficheiro: o conteúdo publicitário deve começar no primeiro frame de vídeo e terminar no último — pre-roll e post-roll de 0 frames, duração do ficheiro = duração do spot x 25 frames. Áudio: PCM, 2 canais (stereo), 24 bit, 48 KHz, peak level -3dB TP máx., loudness (integrado) -23 LUFS. Nomenclatura sugerida para o ficheiro: &lt;Pub ID&gt;_&lt;Nome do Spot&gt;_&lt;Duração&gt;.mxf (ex.: PUB-2015-000345_Fiat 500X Sport Edition_30.mxf) — não é obrigatória, mas recomendada sempre que possível. Entrega exclusivamente por utilizador registado através do Portal GoFastWay (www.gofastway.tv). Todos os ficheiros passam por controlo automático de qualidade (conformidade técnica com estas specs + análise subjetiva de vídeo e áudio); em caso de inconsistência, a GoFastWay pode pedir a entrega de um novo ficheiro corrigido.</t>
         </is>
       </c>
-      <c r="M508" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -25955,27 +25947,742 @@
           <t>Rádio</t>
         </is>
       </c>
-      <c r="E509" t="inlineStr"/>
       <c r="F509" t="inlineStr">
         <is>
           <t>Spot Rádio</t>
         </is>
       </c>
-      <c r="G509" t="inlineStr"/>
-      <c r="H509" t="inlineStr"/>
-      <c r="I509" t="inlineStr"/>
       <c r="J509" t="inlineStr">
         <is>
           <t>MP4 (áudio AAC)</t>
         </is>
       </c>
-      <c r="K509" t="inlineStr"/>
       <c r="L509" t="inlineStr">
         <is>
           <t>Não foi indicada nenhuma plataforma de distribuição nem rádio específica — specs genéricas de entrega, a confirmar sempre junto da rádio ou da central de meios antes de entregar. Áudio AAC, 2 canais (stereo) ou mono consoante o spot, 48 KHz, bit rate mínimo recomendado 320 kbps (CBR), loudness (integrado) -23 LUFS e peak level -3dB TP máx. — o mesmo padrão de loudness broadcast já usado para TV.</t>
         </is>
       </c>
-      <c r="M509" t="inlineStr"/>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr"/>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>4Plus</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>Arte final: 394x140mm. Medida real: 4000x1500mm. Área visível: 3860x1360mm.</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr"/>
+      <c r="I510" t="inlineStr"/>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>PDF (qualidade de impressão), JPEG (visualização) e ficheiro editável</t>
+        </is>
+      </c>
+      <c r="K510" t="inlineStr"/>
+      <c r="L510" t="inlineStr">
+        <is>
+          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Imagens a 100%, 150 DPI. Papel branco 150g; fita-cola (para unir as 2 laudas) 3M ref. 201E, 50mm; embalamento enrolado individualmente. Entrega até à sexta-feira anterior ao dia em que a campanha começa. Quantidades requeridas: +10% além da quantidade contratada. Aconselha-se que a produção seja sempre feita na Pinkplate (Parque Empresarial Primóvel - Ed. D1, Albarraque, 2635-395 Rio de Mouro; Tel. 21 9251800). Cartazes entregues à unidade e identificados. Envio via WeTransfer/Hightail/Dropbox ou FTP do cliente (com utilizador e password); CD/DVD sempre com prova de cor.</t>
+        </is>
+      </c>
+      <c r="M510" t="inlineStr"/>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr"/>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>Flashes</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>Arte final: 370x270mm + 5mm de bleed (frente e verso).</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr"/>
+      <c r="I511" t="inlineStr"/>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>PDF (qualidade de impressão), JPEG (visualização) e ficheiro editável</t>
+        </is>
+      </c>
+      <c r="K511" t="inlineStr"/>
+      <c r="L511" t="inlineStr">
+        <is>
+          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Deve ser deixado 20mm no topo para o encaixe — esta área deve estar livre de informação relevante e ser um prolongamento do fundo (não deixar a branco, a menos que o fundo da criatividade o seja). Papel auto-extinguível ou PVC auto-extinguível (FLAMSTOP), 180g/m2, espessura máxima 0,8mm. Cartazes entregues já dobrados e com as duas faces coladas integralmente. Quantidades requeridas: +15% que o número de posições. Prazo de entrega: até 5 dias úteis antes do início da campanha.</t>
+        </is>
+      </c>
+      <c r="M511" t="inlineStr"/>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr"/>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>Backlight 4x3</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>Arte final: 403x300mm + 1mm de bleed.</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr"/>
+      <c r="I512" t="inlineStr"/>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>PDF (qualidade de impressão), JPEG (visualização) e ficheiro editável</t>
+        </is>
+      </c>
+      <c r="K512" t="inlineStr"/>
+      <c r="L512" t="inlineStr">
+        <is>
+          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Produção em tela backlight no formato pretendido, com duas possibilidades: lona rígida para campanhas anuais (reutilizável) ou tela flexível para campanhas de curta duração (não reutilizável); telas acabadas com uma nervura à volta para fixação e tensionamento nos painéis PRISMAFLEX. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica PRISMAFLEX (Av. Dom Vicente Afonso Valente, 61, 2625-207 Póvoa de Santa Iria; Tel. +351 210 119 500; geral@prismaflex.pt).</t>
+        </is>
+      </c>
+      <c r="M512" t="inlineStr"/>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr"/>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>Backlight 8x3</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>Arte final: 803x286mm + 1mm de bleed.</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr"/>
+      <c r="I513" t="inlineStr"/>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>PDF (qualidade de impressão), JPEG (visualização) e ficheiro editável</t>
+        </is>
+      </c>
+      <c r="K513" t="inlineStr"/>
+      <c r="L513" t="inlineStr">
+        <is>
+          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Produção em tela backlight no formato pretendido, com duas possibilidades: lona rígida para campanhas anuais (reutilizável) ou tela flexível para campanhas de curta duração (não reutilizável); telas acabadas com uma nervura à volta para fixação e tensionamento nos painéis PRISMAFLEX. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica PRISMAFLEX (Av. Dom Vicente Afonso Valente, 61, 2625-207 Póvoa de Santa Iria; Tel. +351 210 119 500; geral@prismaflex.pt).</t>
+        </is>
+      </c>
+      <c r="M513" t="inlineStr"/>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr"/>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>Backlight 10x5</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>Arte final: 966x481mm + 1mm de bleed.</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr"/>
+      <c r="I514" t="inlineStr"/>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>PDF (qualidade de impressão), JPEG (visualização) e ficheiro editável</t>
+        </is>
+      </c>
+      <c r="K514" t="inlineStr"/>
+      <c r="L514" t="inlineStr">
+        <is>
+          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Produção em tela backlight no formato pretendido, com duas possibilidades: lona rígida para campanhas anuais (reutilizável) ou tela flexível para campanhas de curta duração (não reutilizável); telas acabadas com uma nervura à volta para fixação e tensionamento nos painéis PRISMAFLEX. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica PRISMAFLEX (Av. Dom Vicente Afonso Valente, 61, 2625-207 Póvoa de Santa Iria; Tel. +351 210 119 500; geral@prismaflex.pt).</t>
+        </is>
+      </c>
+      <c r="M514" t="inlineStr"/>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr"/>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>Backlight 12x5</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>Arte final: 1211x481mm + 1mm de bleed.</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr"/>
+      <c r="I515" t="inlineStr"/>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>PDF (qualidade de impressão), JPEG (visualização) e ficheiro editável</t>
+        </is>
+      </c>
+      <c r="K515" t="inlineStr"/>
+      <c r="L515" t="inlineStr">
+        <is>
+          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Produção em tela backlight no formato pretendido, com duas possibilidades: lona rígida para campanhas anuais (reutilizável) ou tela flexível para campanhas de curta duração (não reutilizável); telas acabadas com uma nervura à volta para fixação e tensionamento nos painéis PRISMAFLEX. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica PRISMAFLEX (Av. Dom Vicente Afonso Valente, 61, 2625-207 Póvoa de Santa Iria; Tel. +351 210 119 500; geral@prismaflex.pt).</t>
+        </is>
+      </c>
+      <c r="M515" t="inlineStr"/>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr"/>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>Autocarro - Lateral Direita</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>Arte final: 434x118mm + 3mm de bleed. Medida real: 2170x588mm. Área visível: 2150x568mm.</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr"/>
+      <c r="I516" t="inlineStr"/>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>PDF (qualidade de impressão), JPEG (visualização) e ficheiro editável</t>
+        </is>
+      </c>
+      <c r="K516" t="inlineStr"/>
+      <c r="L516" t="inlineStr">
+        <is>
+          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Material obrigatório: PPA 3,5mm | 650g (impressão direta). 2 folhas (corte vertical central), com colagem em sistema de encosto, usando fita-cola 3M ref. 8959 — também permitido em uma só folha no formato total. Prazo de entrega: até 2 dias úteis antes do início da campanha. Quantidades necessárias: +5% que o número de faces, e +5% por cada semana extra de afixação. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica Pinkplate (Parque Empresarial Primóvel - Ed. D1, Albarraque, 2635-395 Rio de Mouro; Tel. 21 9251800).</t>
+        </is>
+      </c>
+      <c r="M516" t="inlineStr"/>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr"/>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>Autocarro - Lateral Esquerda</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>Arte final: 548x150mm + 3mm de bleed. Medida real: 2740x750mm. Área visível: 2720x730mm.</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr"/>
+      <c r="I517" t="inlineStr"/>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>PDF (qualidade de impressão), JPEG (visualização) e ficheiro editável</t>
+        </is>
+      </c>
+      <c r="K517" t="inlineStr"/>
+      <c r="L517" t="inlineStr">
+        <is>
+          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Material obrigatório: PPA 3,5mm | 650g (impressão direta). 2 folhas (corte vertical central), com colagem em sistema de encosto, usando fita-cola 3M ref. 8959 — também permitido em uma só folha no formato total. Prazo de entrega: até 2 dias úteis antes do início da campanha. Quantidades necessárias: +5% que o número de faces, e +5% por cada semana extra de afixação. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica Pinkplate (Parque Empresarial Primóvel - Ed. D1, Albarraque, 2635-395 Rio de Mouro; Tel. 21 9251800).</t>
+        </is>
+      </c>
+      <c r="M517" t="inlineStr"/>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr"/>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>Autocarro - Lateral Esquerda + Esquerda Especial</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>Dimensões Lateral Esquerda — Arte final: 548x150mm + 3mm de bleed, Medida real: 2740x750mm, Área visível: 2720x730mm. Dimensões Esquerda Especial — Arte final: 434x118mm + 3mm de bleed, Medida real: 2170x588mm, Área visível: 2150x568mm.</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr"/>
+      <c r="I518" t="inlineStr"/>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>PDF (qualidade de impressão), JPEG (visualização) e ficheiro editável</t>
+        </is>
+      </c>
+      <c r="K518" t="inlineStr"/>
+      <c r="L518" t="inlineStr">
+        <is>
+          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Material obrigatório: PPA 3,5mm | 650g (impressão direta). 2 folhas (corte vertical central), com colagem em sistema de encosto, usando fita-cola 3M ref. 8959 — também permitido em uma só folha no formato total. Prazo de entrega: até 2 dias úteis antes do início da campanha. Quantidades necessárias: +5% que o número de faces, e +5% por cada semana extra de afixação. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica Pinkplate (Parque Empresarial Primóvel - Ed. D1, Albarraque, 2635-395 Rio de Mouro; Tel. 21 9251800).</t>
+        </is>
+      </c>
+      <c r="M518" t="inlineStr"/>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr"/>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>Autocarro - Retaguarda</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>Arte final: 300x96mm + 1mm de bleed. Medida real: 1500x478mm. Área visível: 2150x568mm.</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr"/>
+      <c r="I519" t="inlineStr"/>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>PDF (qualidade de impressão), JPEG (visualização) e ficheiro editável</t>
+        </is>
+      </c>
+      <c r="K519" t="inlineStr"/>
+      <c r="L519" t="inlineStr">
+        <is>
+          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Material obrigatório: PPA 3,5mm | 650g (impressão direta). 2 folhas (corte vertical central), com colagem em sistema de encosto, usando fita-cola 3M ref. 8959 — também permitido em uma só folha no formato total. Prazo de entrega: até 2 dias úteis antes do início da campanha. Quantidades necessárias: +5% que o número de faces, e +5% por cada semana extra de afixação. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica Pinkplate (Parque Empresarial Primóvel - Ed. D1, Albarraque, 2635-395 Rio de Mouro; Tel. 21 9251800).</t>
+        </is>
+      </c>
+      <c r="M519" t="inlineStr"/>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr"/>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>3 Ecrãs</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>1920x1080px.</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr"/>
+      <c r="J520" t="inlineStr">
+        <is>
+          <t>Vídeo: MP4/MOV; Imagem: qualquer formato; Web: HTML/URL — codec H264</t>
+        </is>
+      </c>
+      <c r="K520" t="inlineStr"/>
+      <c r="L520" t="inlineStr">
+        <is>
+          <t>Duração: 10 segundos (obrigatório). Bitrate máx. 6 Mbps. Framerate 30 frames/s. Tamanho máximo: 100MB. Existe uma separação real de 2,5cm (medida real) na junção entre os três ecrãs, que divide e corta a imagem total — deve ser tido em conta para evitar que frases ou elementos relevantes fiquem deformados (zonas de quebra).</t>
+        </is>
+      </c>
+      <c r="M520" t="inlineStr"/>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr"/>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>4x3 Digital</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>1536x1152px (na proporção 4x3, até 3840x2880px).</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>4:3</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr"/>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>Vídeo: MP4/MOV; Imagem: qualquer formato; Web: HTML/URL — codec H264</t>
+        </is>
+      </c>
+      <c r="K521" t="inlineStr"/>
+      <c r="L521" t="inlineStr">
+        <is>
+          <t>Duração: 10 segundos. Bitrate máximo 6 Mbps. Framerate 30 frames/s. Tamanho máximo: 100MB. Compressão nativa.</t>
+        </is>
+      </c>
+      <c r="M521" t="inlineStr"/>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr"/>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>Tomi PhotoFun</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>1080x810px.</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>4:3</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr"/>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>PNG</t>
+        </is>
+      </c>
+      <c r="K522" t="inlineStr"/>
+      <c r="L522" t="inlineStr">
+        <is>
+          <t>Profundidade de cor: 8 bits ou superior. Deve ter sempre um espaço vazio de conteúdo de 125x125px para o logótipo TOMI no canto da moldura. Por ser impossível tirar uma fotografia sem o efeito de espelho com uma câmara frontal, é sempre necessário o envio da moldura espelhada.</t>
+        </is>
+      </c>
+      <c r="M522" t="inlineStr"/>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr"/>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>Tomi Sport TV</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>1080x1920px.</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr"/>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>MP4 (sem fundo), codec H264</t>
+        </is>
+      </c>
+      <c r="K523" t="inlineStr"/>
+      <c r="L523" t="inlineStr">
+        <is>
+          <t>Duração: múltiplos de 5 segundos. Bitrate máximo 6 Mbps. Tamanho máximo: 100MB.</t>
+        </is>
+      </c>
+      <c r="M523" t="inlineStr"/>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr"/>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>LED Galp</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>840x336px.</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr"/>
+      <c r="I524" t="inlineStr"/>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>Vídeo: MP4/MOV; Imagem: qualquer formato; Web: HTML/URL — codec H264</t>
+        </is>
+      </c>
+      <c r="K524" t="inlineStr"/>
+      <c r="L524" t="inlineStr">
+        <is>
+          <t>Duração: 10 segundos (obrigatório). Bitrate máximo 6 Mbps. Framerate 30 frames/s. Tamanho máximo: 100MB.</t>
+        </is>
+      </c>
+      <c r="M524" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M524"/>
+  <dimension ref="A1:M529"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="18.08984375" customWidth="1" style="2" min="1" max="1"/>
@@ -25984,7 +25984,6 @@
           <t>MOP</t>
         </is>
       </c>
-      <c r="E510" t="inlineStr"/>
       <c r="F510" t="inlineStr">
         <is>
           <t>4Plus</t>
@@ -25995,20 +25994,16 @@
           <t>Arte final: 394x140mm. Medida real: 4000x1500mm. Área visível: 3860x1360mm.</t>
         </is>
       </c>
-      <c r="H510" t="inlineStr"/>
-      <c r="I510" t="inlineStr"/>
       <c r="J510" t="inlineStr">
         <is>
           <t>PDF (qualidade de impressão), JPEG (visualização) e ficheiro editável</t>
         </is>
       </c>
-      <c r="K510" t="inlineStr"/>
       <c r="L510" t="inlineStr">
         <is>
           <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Imagens a 100%, 150 DPI. Papel branco 150g; fita-cola (para unir as 2 laudas) 3M ref. 201E, 50mm; embalamento enrolado individualmente. Entrega até à sexta-feira anterior ao dia em que a campanha começa. Quantidades requeridas: +10% além da quantidade contratada. Aconselha-se que a produção seja sempre feita na Pinkplate (Parque Empresarial Primóvel - Ed. D1, Albarraque, 2635-395 Rio de Mouro; Tel. 21 9251800). Cartazes entregues à unidade e identificados. Envio via WeTransfer/Hightail/Dropbox ou FTP do cliente (com utilizador e password); CD/DVD sempre com prova de cor.</t>
         </is>
       </c>
-      <c r="M510" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -26031,7 +26026,6 @@
           <t>MOP</t>
         </is>
       </c>
-      <c r="E511" t="inlineStr"/>
       <c r="F511" t="inlineStr">
         <is>
           <t>Flashes</t>
@@ -26042,20 +26036,16 @@
           <t>Arte final: 370x270mm + 5mm de bleed (frente e verso).</t>
         </is>
       </c>
-      <c r="H511" t="inlineStr"/>
-      <c r="I511" t="inlineStr"/>
       <c r="J511" t="inlineStr">
         <is>
           <t>PDF (qualidade de impressão), JPEG (visualização) e ficheiro editável</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr"/>
       <c r="L511" t="inlineStr">
         <is>
           <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Deve ser deixado 20mm no topo para o encaixe — esta área deve estar livre de informação relevante e ser um prolongamento do fundo (não deixar a branco, a menos que o fundo da criatividade o seja). Papel auto-extinguível ou PVC auto-extinguível (FLAMSTOP), 180g/m2, espessura máxima 0,8mm. Cartazes entregues já dobrados e com as duas faces coladas integralmente. Quantidades requeridas: +15% que o número de posições. Prazo de entrega: até 5 dias úteis antes do início da campanha.</t>
         </is>
       </c>
-      <c r="M511" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -26078,7 +26068,6 @@
           <t>MOP</t>
         </is>
       </c>
-      <c r="E512" t="inlineStr"/>
       <c r="F512" t="inlineStr">
         <is>
           <t>Backlight 4x3</t>
@@ -26089,20 +26078,16 @@
           <t>Arte final: 403x300mm + 1mm de bleed.</t>
         </is>
       </c>
-      <c r="H512" t="inlineStr"/>
-      <c r="I512" t="inlineStr"/>
       <c r="J512" t="inlineStr">
         <is>
           <t>PDF (qualidade de impressão), JPEG (visualização) e ficheiro editável</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr"/>
       <c r="L512" t="inlineStr">
         <is>
           <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Produção em tela backlight no formato pretendido, com duas possibilidades: lona rígida para campanhas anuais (reutilizável) ou tela flexível para campanhas de curta duração (não reutilizável); telas acabadas com uma nervura à volta para fixação e tensionamento nos painéis PRISMAFLEX. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica PRISMAFLEX (Av. Dom Vicente Afonso Valente, 61, 2625-207 Póvoa de Santa Iria; Tel. +351 210 119 500; geral@prismaflex.pt).</t>
         </is>
       </c>
-      <c r="M512" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -26125,7 +26110,6 @@
           <t>MOP</t>
         </is>
       </c>
-      <c r="E513" t="inlineStr"/>
       <c r="F513" t="inlineStr">
         <is>
           <t>Backlight 8x3</t>
@@ -26136,20 +26120,16 @@
           <t>Arte final: 803x286mm + 1mm de bleed.</t>
         </is>
       </c>
-      <c r="H513" t="inlineStr"/>
-      <c r="I513" t="inlineStr"/>
       <c r="J513" t="inlineStr">
         <is>
           <t>PDF (qualidade de impressão), JPEG (visualização) e ficheiro editável</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
       <c r="L513" t="inlineStr">
         <is>
           <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Produção em tela backlight no formato pretendido, com duas possibilidades: lona rígida para campanhas anuais (reutilizável) ou tela flexível para campanhas de curta duração (não reutilizável); telas acabadas com uma nervura à volta para fixação e tensionamento nos painéis PRISMAFLEX. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica PRISMAFLEX (Av. Dom Vicente Afonso Valente, 61, 2625-207 Póvoa de Santa Iria; Tel. +351 210 119 500; geral@prismaflex.pt).</t>
         </is>
       </c>
-      <c r="M513" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -26172,7 +26152,6 @@
           <t>MOP</t>
         </is>
       </c>
-      <c r="E514" t="inlineStr"/>
       <c r="F514" t="inlineStr">
         <is>
           <t>Backlight 10x5</t>
@@ -26183,20 +26162,16 @@
           <t>Arte final: 966x481mm + 1mm de bleed.</t>
         </is>
       </c>
-      <c r="H514" t="inlineStr"/>
-      <c r="I514" t="inlineStr"/>
       <c r="J514" t="inlineStr">
         <is>
           <t>PDF (qualidade de impressão), JPEG (visualização) e ficheiro editável</t>
         </is>
       </c>
-      <c r="K514" t="inlineStr"/>
       <c r="L514" t="inlineStr">
         <is>
           <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Produção em tela backlight no formato pretendido, com duas possibilidades: lona rígida para campanhas anuais (reutilizável) ou tela flexível para campanhas de curta duração (não reutilizável); telas acabadas com uma nervura à volta para fixação e tensionamento nos painéis PRISMAFLEX. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica PRISMAFLEX (Av. Dom Vicente Afonso Valente, 61, 2625-207 Póvoa de Santa Iria; Tel. +351 210 119 500; geral@prismaflex.pt).</t>
         </is>
       </c>
-      <c r="M514" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -26219,7 +26194,6 @@
           <t>MOP</t>
         </is>
       </c>
-      <c r="E515" t="inlineStr"/>
       <c r="F515" t="inlineStr">
         <is>
           <t>Backlight 12x5</t>
@@ -26230,20 +26204,16 @@
           <t>Arte final: 1211x481mm + 1mm de bleed.</t>
         </is>
       </c>
-      <c r="H515" t="inlineStr"/>
-      <c r="I515" t="inlineStr"/>
       <c r="J515" t="inlineStr">
         <is>
           <t>PDF (qualidade de impressão), JPEG (visualização) e ficheiro editável</t>
         </is>
       </c>
-      <c r="K515" t="inlineStr"/>
       <c r="L515" t="inlineStr">
         <is>
           <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Produção em tela backlight no formato pretendido, com duas possibilidades: lona rígida para campanhas anuais (reutilizável) ou tela flexível para campanhas de curta duração (não reutilizável); telas acabadas com uma nervura à volta para fixação e tensionamento nos painéis PRISMAFLEX. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica PRISMAFLEX (Av. Dom Vicente Afonso Valente, 61, 2625-207 Póvoa de Santa Iria; Tel. +351 210 119 500; geral@prismaflex.pt).</t>
         </is>
       </c>
-      <c r="M515" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -26266,7 +26236,6 @@
           <t>MOP</t>
         </is>
       </c>
-      <c r="E516" t="inlineStr"/>
       <c r="F516" t="inlineStr">
         <is>
           <t>Autocarro - Lateral Direita</t>
@@ -26277,20 +26246,16 @@
           <t>Arte final: 434x118mm + 3mm de bleed. Medida real: 2170x588mm. Área visível: 2150x568mm.</t>
         </is>
       </c>
-      <c r="H516" t="inlineStr"/>
-      <c r="I516" t="inlineStr"/>
       <c r="J516" t="inlineStr">
         <is>
           <t>PDF (qualidade de impressão), JPEG (visualização) e ficheiro editável</t>
         </is>
       </c>
-      <c r="K516" t="inlineStr"/>
       <c r="L516" t="inlineStr">
         <is>
           <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Material obrigatório: PPA 3,5mm | 650g (impressão direta). 2 folhas (corte vertical central), com colagem em sistema de encosto, usando fita-cola 3M ref. 8959 — também permitido em uma só folha no formato total. Prazo de entrega: até 2 dias úteis antes do início da campanha. Quantidades necessárias: +5% que o número de faces, e +5% por cada semana extra de afixação. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica Pinkplate (Parque Empresarial Primóvel - Ed. D1, Albarraque, 2635-395 Rio de Mouro; Tel. 21 9251800).</t>
         </is>
       </c>
-      <c r="M516" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -26313,7 +26278,6 @@
           <t>MOP</t>
         </is>
       </c>
-      <c r="E517" t="inlineStr"/>
       <c r="F517" t="inlineStr">
         <is>
           <t>Autocarro - Lateral Esquerda</t>
@@ -26324,20 +26288,16 @@
           <t>Arte final: 548x150mm + 3mm de bleed. Medida real: 2740x750mm. Área visível: 2720x730mm.</t>
         </is>
       </c>
-      <c r="H517" t="inlineStr"/>
-      <c r="I517" t="inlineStr"/>
       <c r="J517" t="inlineStr">
         <is>
           <t>PDF (qualidade de impressão), JPEG (visualização) e ficheiro editável</t>
         </is>
       </c>
-      <c r="K517" t="inlineStr"/>
       <c r="L517" t="inlineStr">
         <is>
           <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Material obrigatório: PPA 3,5mm | 650g (impressão direta). 2 folhas (corte vertical central), com colagem em sistema de encosto, usando fita-cola 3M ref. 8959 — também permitido em uma só folha no formato total. Prazo de entrega: até 2 dias úteis antes do início da campanha. Quantidades necessárias: +5% que o número de faces, e +5% por cada semana extra de afixação. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica Pinkplate (Parque Empresarial Primóvel - Ed. D1, Albarraque, 2635-395 Rio de Mouro; Tel. 21 9251800).</t>
         </is>
       </c>
-      <c r="M517" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -26360,7 +26320,6 @@
           <t>MOP</t>
         </is>
       </c>
-      <c r="E518" t="inlineStr"/>
       <c r="F518" t="inlineStr">
         <is>
           <t>Autocarro - Lateral Esquerda + Esquerda Especial</t>
@@ -26371,20 +26330,16 @@
           <t>Dimensões Lateral Esquerda — Arte final: 548x150mm + 3mm de bleed, Medida real: 2740x750mm, Área visível: 2720x730mm. Dimensões Esquerda Especial — Arte final: 434x118mm + 3mm de bleed, Medida real: 2170x588mm, Área visível: 2150x568mm.</t>
         </is>
       </c>
-      <c r="H518" t="inlineStr"/>
-      <c r="I518" t="inlineStr"/>
       <c r="J518" t="inlineStr">
         <is>
           <t>PDF (qualidade de impressão), JPEG (visualização) e ficheiro editável</t>
         </is>
       </c>
-      <c r="K518" t="inlineStr"/>
       <c r="L518" t="inlineStr">
         <is>
           <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Material obrigatório: PPA 3,5mm | 650g (impressão direta). 2 folhas (corte vertical central), com colagem em sistema de encosto, usando fita-cola 3M ref. 8959 — também permitido em uma só folha no formato total. Prazo de entrega: até 2 dias úteis antes do início da campanha. Quantidades necessárias: +5% que o número de faces, e +5% por cada semana extra de afixação. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica Pinkplate (Parque Empresarial Primóvel - Ed. D1, Albarraque, 2635-395 Rio de Mouro; Tel. 21 9251800).</t>
         </is>
       </c>
-      <c r="M518" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -26407,7 +26362,6 @@
           <t>MOP</t>
         </is>
       </c>
-      <c r="E519" t="inlineStr"/>
       <c r="F519" t="inlineStr">
         <is>
           <t>Autocarro - Retaguarda</t>
@@ -26418,20 +26372,16 @@
           <t>Arte final: 300x96mm + 1mm de bleed. Medida real: 1500x478mm. Área visível: 2150x568mm.</t>
         </is>
       </c>
-      <c r="H519" t="inlineStr"/>
-      <c r="I519" t="inlineStr"/>
       <c r="J519" t="inlineStr">
         <is>
           <t>PDF (qualidade de impressão), JPEG (visualização) e ficheiro editável</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr"/>
       <c r="L519" t="inlineStr">
         <is>
           <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Material obrigatório: PPA 3,5mm | 650g (impressão direta). 2 folhas (corte vertical central), com colagem em sistema de encosto, usando fita-cola 3M ref. 8959 — também permitido em uma só folha no formato total. Prazo de entrega: até 2 dias úteis antes do início da campanha. Quantidades necessárias: +5% que o número de faces, e +5% por cada semana extra de afixação. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica Pinkplate (Parque Empresarial Primóvel - Ed. D1, Albarraque, 2635-395 Rio de Mouro; Tel. 21 9251800).</t>
         </is>
       </c>
-      <c r="M519" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -26454,7 +26404,6 @@
           <t>MOP</t>
         </is>
       </c>
-      <c r="E520" t="inlineStr"/>
       <c r="F520" t="inlineStr">
         <is>
           <t>3 Ecrãs</t>
@@ -26470,19 +26419,16 @@
           <t>16:9</t>
         </is>
       </c>
-      <c r="I520" t="inlineStr"/>
       <c r="J520" t="inlineStr">
         <is>
           <t>Vídeo: MP4/MOV; Imagem: qualquer formato; Web: HTML/URL — codec H264</t>
         </is>
       </c>
-      <c r="K520" t="inlineStr"/>
       <c r="L520" t="inlineStr">
         <is>
           <t>Duração: 10 segundos (obrigatório). Bitrate máx. 6 Mbps. Framerate 30 frames/s. Tamanho máximo: 100MB. Existe uma separação real de 2,5cm (medida real) na junção entre os três ecrãs, que divide e corta a imagem total — deve ser tido em conta para evitar que frases ou elementos relevantes fiquem deformados (zonas de quebra).</t>
         </is>
       </c>
-      <c r="M520" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -26505,7 +26451,6 @@
           <t>MOP</t>
         </is>
       </c>
-      <c r="E521" t="inlineStr"/>
       <c r="F521" t="inlineStr">
         <is>
           <t>4x3 Digital</t>
@@ -26521,19 +26466,16 @@
           <t>4:3</t>
         </is>
       </c>
-      <c r="I521" t="inlineStr"/>
       <c r="J521" t="inlineStr">
         <is>
           <t>Vídeo: MP4/MOV; Imagem: qualquer formato; Web: HTML/URL — codec H264</t>
         </is>
       </c>
-      <c r="K521" t="inlineStr"/>
       <c r="L521" t="inlineStr">
         <is>
           <t>Duração: 10 segundos. Bitrate máximo 6 Mbps. Framerate 30 frames/s. Tamanho máximo: 100MB. Compressão nativa.</t>
         </is>
       </c>
-      <c r="M521" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -26556,7 +26498,6 @@
           <t>MOP</t>
         </is>
       </c>
-      <c r="E522" t="inlineStr"/>
       <c r="F522" t="inlineStr">
         <is>
           <t>Tomi PhotoFun</t>
@@ -26572,19 +26513,16 @@
           <t>4:3</t>
         </is>
       </c>
-      <c r="I522" t="inlineStr"/>
       <c r="J522" t="inlineStr">
         <is>
           <t>PNG</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr"/>
       <c r="L522" t="inlineStr">
         <is>
           <t>Profundidade de cor: 8 bits ou superior. Deve ter sempre um espaço vazio de conteúdo de 125x125px para o logótipo TOMI no canto da moldura. Por ser impossível tirar uma fotografia sem o efeito de espelho com uma câmara frontal, é sempre necessário o envio da moldura espelhada.</t>
         </is>
       </c>
-      <c r="M522" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -26607,7 +26545,6 @@
           <t>MOP</t>
         </is>
       </c>
-      <c r="E523" t="inlineStr"/>
       <c r="F523" t="inlineStr">
         <is>
           <t>Tomi Sport TV</t>
@@ -26623,19 +26560,16 @@
           <t>9:16</t>
         </is>
       </c>
-      <c r="I523" t="inlineStr"/>
       <c r="J523" t="inlineStr">
         <is>
           <t>MP4 (sem fundo), codec H264</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr"/>
       <c r="L523" t="inlineStr">
         <is>
           <t>Duração: múltiplos de 5 segundos. Bitrate máximo 6 Mbps. Tamanho máximo: 100MB.</t>
         </is>
       </c>
-      <c r="M523" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -26658,7 +26592,6 @@
           <t>MOP</t>
         </is>
       </c>
-      <c r="E524" t="inlineStr"/>
       <c r="F524" t="inlineStr">
         <is>
           <t>LED Galp</t>
@@ -26669,20 +26602,221 @@
           <t>840x336px.</t>
         </is>
       </c>
-      <c r="H524" t="inlineStr"/>
-      <c r="I524" t="inlineStr"/>
       <c r="J524" t="inlineStr">
         <is>
           <t>Vídeo: MP4/MOV; Imagem: qualquer formato; Web: HTML/URL — codec H264</t>
         </is>
       </c>
-      <c r="K524" t="inlineStr"/>
       <c r="L524" t="inlineStr">
         <is>
           <t>Duração: 10 segundos (obrigatório). Bitrate máximo 6 Mbps. Framerate 30 frames/s. Tamanho máximo: 100MB.</t>
         </is>
       </c>
-      <c r="M524" t="inlineStr"/>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>Ecrã Fracionado / Split Screen</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>480x1080px (25% de um ecrã de 1920x1080px), 25 fps</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>QuickTime (.MOV), ProRes 4444 (com canal Alpha) ou ProRes 422 (sem Alpha), 1080i entrelaçado (Upper/odd Field First), 25 fps</t>
+        </is>
+      </c>
+      <c r="L525" t="inlineStr">
+        <is>
+          <t>Conteúdo publicitário que ocupa no máximo 25% do ecrã, transmitido em simultâneo com programas de entretenimento, desporto e magazine. Duração 10″, com entrada e saída incluídas nesses 10″. Sem áudio. Tem de manter a palavra "PUBLICIDADE" com leitura garantida e dentro da Safe Area durante todo o tempo em que está no ar. Na TVI entra pela direita do ecrã. Safe Area geral: 96px horizontais / 54px verticais a partir da margem; Title Safe Area: 192px horizontais / 108px verticais — nenhuma informação relevante deve ficar fora destas áreas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>CNN Portugal</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>Ecrã Fracionado / Split Screen</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>480x1080px (25% de um ecrã de 1920x1080px), 25 fps</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>QuickTime (.MOV), ProRes 4444 (com canal Alpha) ou ProRes 422 (sem Alpha), 1080i entrelaçado (Upper/odd Field First), 25 fps</t>
+        </is>
+      </c>
+      <c r="L526" t="inlineStr">
+        <is>
+          <t>Conteúdo publicitário que ocupa no máximo 25% do ecrã, transmitido em simultâneo com programas de entretenimento, desporto e magazine. Duração 10″, com entrada e saída incluídas nesses 10″. Sem áudio. Tem de manter a palavra "PUBLICIDADE" com leitura garantida e dentro da Safe Area durante todo o tempo em que está no ar. Na CNN Portugal entra pela esquerda do ecrã. Safe Area geral: 96px horizontais / 54px verticais a partir da margem; Title Safe Area: 192px horizontais / 108px verticais — nenhuma informação relevante deve ficar fora destas áreas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>TVI/CNN Portugal</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>Telepromoção</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>1920x1080px (plasma de estúdio; a zona útil do plasma tem 220px de altura a partir da base do ecrã) e oráculo 1920x1080px</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>Imagens/grafismos: JPEG, PNG, PSD, AI/EPS (Illustrator versão CC), TIFF ou TGA, todos em resolução HD; ficheiros 3D: C4D (formato ideal), FBX ou OBJ. Vídeo: Formato de vídeo genérico (aplicável salvo indicação em contrário): wrapper MXF OP1a (.MXF), XDCAM HD 4:2:2, 1080i, 25 fps, entrelaçado (Upper/odd Field First), MPEG2 @ 50Mbps, perfil 4:2:2@HL, 1920x1080px, aspect ratio 16:9. Áudio: 8 canais @ 24 bits, PGM nos primeiros dois canais, 48.0 KHz, PCM não comprimido (.wav ou .aiff depois de desembrulhado), nível de referência -20dBFS, loudness -23 LUFS (EBU R.128).</t>
+        </is>
+      </c>
+      <c r="L527" t="inlineStr">
+        <is>
+          <t>Materiais a fornecer para produção de grafismos, ou grafismos já finalizados — usados no plasma existente no estúdio (para passar vídeos, fotografias ou grafismos) e/ou no oráculo. Devem ser enquadrados dentro das áreas de segurança indicadas para os logos e textos não correrem o risco de serem cortados ou distorcidos (Safe Area geral: 96px horizontais / 54px verticais a partir da margem; Title Safe Area: 192px horizontais / 108px verticais — nenhuma informação relevante deve ficar fora destas áreas. No plasma de estúdio, a zona útil começa a 220px da base do ecrã; no oráculo aplica-se a Title Safe Area). Os guiões para telepromoções de 60″ de duração devem ter entre 730 e 800 caracteres sem espaçamento. Fontes de letra em formato TT, para PC; referências de cor em RGB. Todos os materiais devem ser fornecidos com pelo menos uma semana de antecedência relativamente à data de realização da telepromoção, nos formatos indicados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>Clearspot</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>Clearspot</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>Especificações por confirmar</t>
+        </is>
+      </c>
+      <c r="L528" t="inlineStr">
+        <is>
+          <t>Concessionária adicionada à base para já sem formatos associados — as especificações técnicas de Clearspot ainda não foram fornecidas. Atualizar esta linha (e acrescentar as linhas de formato que fizerem falta) assim que a informação chegar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>CS Outdoors</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>CS Outdoors</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>Especificações por confirmar</t>
+        </is>
+      </c>
+      <c r="L529" t="inlineStr">
+        <is>
+          <t>Concessionária adicionada à base para já sem formatos associados — as especificações técnicas de CS Outdoors ainda não foram fornecidas. Atualizar esta linha (e acrescentar as linhas de formato que fizerem falta) assim que a informação chegar.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M529"/>
+  <dimension ref="A1:M528"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="18.08984375" customWidth="1" style="2" min="1" max="1"/>
@@ -25845,12 +25845,12 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>GoFastWay</t>
+          <t>TV</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>GoFastWay</t>
+          <t>TV</t>
         </is>
       </c>
       <c r="F507" t="inlineStr">
@@ -25892,12 +25892,12 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>GoFastWay</t>
+          <t>TV</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>GoFastWay</t>
+          <t>TV</t>
         </is>
       </c>
       <c r="F508" t="inlineStr">
@@ -26626,12 +26626,12 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>TVI</t>
+          <t>TV</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>TVI</t>
+          <t>TV</t>
         </is>
       </c>
       <c r="F525" t="inlineStr">
@@ -26656,7 +26656,7 @@
       </c>
       <c r="L525" t="inlineStr">
         <is>
-          <t>Conteúdo publicitário que ocupa no máximo 25% do ecrã, transmitido em simultâneo com programas de entretenimento, desporto e magazine. Duração 10″, com entrada e saída incluídas nesses 10″. Sem áudio. Tem de manter a palavra "PUBLICIDADE" com leitura garantida e dentro da Safe Area durante todo o tempo em que está no ar. Na TVI entra pela direita do ecrã. Safe Area geral: 96px horizontais / 54px verticais a partir da margem; Title Safe Area: 192px horizontais / 108px verticais — nenhuma informação relevante deve ficar fora destas áreas.</t>
+          <t>Conteúdo publicitário que ocupa no máximo 25% do ecrã, transmitido em simultâneo com programas de entretenimento, desporto e magazine. Duração 10″, com entrada e saída incluídas nesses 10″. Sem áudio. Tem de manter a palavra "PUBLICIDADE" com leitura garantida e dentro da Safe Area durante todo o tempo em que está no ar. Entra pela direita do ecrã na TVI e pela esquerda na CNN Portugal. Safe Area geral: 96px horizontais / 54px verticais a partir da margem; Title Safe Area: 192px horizontais / 108px verticais — nenhuma informação relevante deve ficar fora destas áreas.</t>
         </is>
       </c>
     </row>
@@ -26673,22 +26673,22 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>TVI</t>
+          <t>TV</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>CNN Portugal</t>
+          <t>TV</t>
         </is>
       </c>
       <c r="F526" t="inlineStr">
         <is>
-          <t>Ecrã Fracionado / Split Screen</t>
+          <t>Telepromoção</t>
         </is>
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>480x1080px (25% de um ecrã de 1920x1080px), 25 fps</t>
+          <t>1920x1080px (plasma de estúdio; a zona útil do plasma tem 220px de altura a partir da base do ecrã) e oráculo 1920x1080px</t>
         </is>
       </c>
       <c r="H526" t="inlineStr">
@@ -26698,59 +26698,44 @@
       </c>
       <c r="J526" t="inlineStr">
         <is>
-          <t>QuickTime (.MOV), ProRes 4444 (com canal Alpha) ou ProRes 422 (sem Alpha), 1080i entrelaçado (Upper/odd Field First), 25 fps</t>
+          <t>Imagens/grafismos: JPEG, PNG, PSD, AI/EPS (Illustrator versão CC), TIFF ou TGA, todos em resolução HD; ficheiros 3D: C4D (formato ideal), FBX ou OBJ. Vídeo: Formato de vídeo genérico (aplicável salvo indicação em contrário): wrapper MXF OP1a (.MXF), XDCAM HD 4:2:2, 1080i, 25 fps, entrelaçado (Upper/odd Field First), MPEG2 @ 50Mbps, perfil 4:2:2@HL, 1920x1080px, aspect ratio 16:9. Áudio: 8 canais @ 24 bits, PGM nos primeiros dois canais, 48.0 KHz, PCM não comprimido (.wav ou .aiff depois de desembrulhado), nível de referência -20dBFS, loudness -23 LUFS (EBU R.128).</t>
         </is>
       </c>
       <c r="L526" t="inlineStr">
         <is>
-          <t>Conteúdo publicitário que ocupa no máximo 25% do ecrã, transmitido em simultâneo com programas de entretenimento, desporto e magazine. Duração 10″, com entrada e saída incluídas nesses 10″. Sem áudio. Tem de manter a palavra "PUBLICIDADE" com leitura garantida e dentro da Safe Area durante todo o tempo em que está no ar. Na CNN Portugal entra pela esquerda do ecrã. Safe Area geral: 96px horizontais / 54px verticais a partir da margem; Title Safe Area: 192px horizontais / 108px verticais — nenhuma informação relevante deve ficar fora destas áreas.</t>
+          <t>Materiais a fornecer para produção de grafismos, ou grafismos já finalizados — usados no plasma existente no estúdio (para passar vídeos, fotografias ou grafismos) e/ou no oráculo. Devem ser enquadrados dentro das áreas de segurança indicadas para os logos e textos não correrem o risco de serem cortados ou distorcidos (Safe Area geral: 96px horizontais / 54px verticais a partir da margem; Title Safe Area: 192px horizontais / 108px verticais — nenhuma informação relevante deve ficar fora destas áreas. No plasma de estúdio, a zona útil começa a 220px da base do ecrã; no oráculo aplica-se a Title Safe Area). Os guiões para telepromoções de 60″ de duração devem ter entre 730 e 800 caracteres sem espaçamento. Fontes de letra em formato TT, para PC; referências de cor em RGB. Todos os materiais devem ser fornecidos com pelo menos uma semana de antecedência relativamente à data de realização da telepromoção, nos formatos indicados.</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>TV</t>
+          <t>OOH</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>TV</t>
+          <t>OOH</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>TVI</t>
+          <t>Clearspot</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>TVI/CNN Portugal</t>
+          <t>Clearspot</t>
         </is>
       </c>
       <c r="F527" t="inlineStr">
         <is>
-          <t>Telepromoção</t>
-        </is>
-      </c>
-      <c r="G527" t="inlineStr">
-        <is>
-          <t>1920x1080px (plasma de estúdio; a zona útil do plasma tem 220px de altura a partir da base do ecrã) e oráculo 1920x1080px</t>
-        </is>
-      </c>
-      <c r="H527" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
-      <c r="J527" t="inlineStr">
-        <is>
-          <t>Imagens/grafismos: JPEG, PNG, PSD, AI/EPS (Illustrator versão CC), TIFF ou TGA, todos em resolução HD; ficheiros 3D: C4D (formato ideal), FBX ou OBJ. Vídeo: Formato de vídeo genérico (aplicável salvo indicação em contrário): wrapper MXF OP1a (.MXF), XDCAM HD 4:2:2, 1080i, 25 fps, entrelaçado (Upper/odd Field First), MPEG2 @ 50Mbps, perfil 4:2:2@HL, 1920x1080px, aspect ratio 16:9. Áudio: 8 canais @ 24 bits, PGM nos primeiros dois canais, 48.0 KHz, PCM não comprimido (.wav ou .aiff depois de desembrulhado), nível de referência -20dBFS, loudness -23 LUFS (EBU R.128).</t>
+          <t>Especificações por confirmar</t>
         </is>
       </c>
       <c r="L527" t="inlineStr">
         <is>
-          <t>Materiais a fornecer para produção de grafismos, ou grafismos já finalizados — usados no plasma existente no estúdio (para passar vídeos, fotografias ou grafismos) e/ou no oráculo. Devem ser enquadrados dentro das áreas de segurança indicadas para os logos e textos não correrem o risco de serem cortados ou distorcidos (Safe Area geral: 96px horizontais / 54px verticais a partir da margem; Title Safe Area: 192px horizontais / 108px verticais — nenhuma informação relevante deve ficar fora destas áreas. No plasma de estúdio, a zona útil começa a 220px da base do ecrã; no oráculo aplica-se a Title Safe Area). Os guiões para telepromoções de 60″ de duração devem ter entre 730 e 800 caracteres sem espaçamento. Fontes de letra em formato TT, para PC; referências de cor em RGB. Todos os materiais devem ser fornecidos com pelo menos uma semana de antecedência relativamente à data de realização da telepromoção, nos formatos indicados.</t>
+          <t>Concessionária adicionada à base para já sem formatos associados — as especificações técnicas de Clearspot ainda não foram fornecidas. Atualizar esta linha (e acrescentar as linhas de formato que fizerem falta) assim que a informação chegar.</t>
         </is>
       </c>
     </row>
@@ -26767,12 +26752,12 @@
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>Clearspot</t>
+          <t>CS Outdoors</t>
         </is>
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>Clearspot</t>
+          <t>CS Outdoors</t>
         </is>
       </c>
       <c r="F528" t="inlineStr">
@@ -26781,38 +26766,6 @@
         </is>
       </c>
       <c r="L528" t="inlineStr">
-        <is>
-          <t>Concessionária adicionada à base para já sem formatos associados — as especificações técnicas de Clearspot ainda não foram fornecidas. Atualizar esta linha (e acrescentar as linhas de formato que fizerem falta) assim que a informação chegar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="529">
-      <c r="A529" t="inlineStr">
-        <is>
-          <t>OOH</t>
-        </is>
-      </c>
-      <c r="B529" t="inlineStr">
-        <is>
-          <t>OOH</t>
-        </is>
-      </c>
-      <c r="C529" t="inlineStr">
-        <is>
-          <t>CS Outdoors</t>
-        </is>
-      </c>
-      <c r="D529" t="inlineStr">
-        <is>
-          <t>CS Outdoors</t>
-        </is>
-      </c>
-      <c r="F529" t="inlineStr">
-        <is>
-          <t>Especificações por confirmar</t>
-        </is>
-      </c>
-      <c r="L529" t="inlineStr">
         <is>
           <t>Concessionária adicionada à base para já sem formatos associados — as especificações técnicas de CS Outdoors ainda não foram fornecidas. Atualizar esta linha (e acrescentar as linhas de formato que fizerem falta) assim que a informação chegar.</t>
         </is>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -25954,7 +25954,7 @@
       </c>
       <c r="J509" t="inlineStr">
         <is>
-          <t>MP4 (áudio AAC)</t>
+          <t>MP3</t>
         </is>
       </c>
       <c r="L509" t="inlineStr">

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M528"/>
+  <dimension ref="A1:M532"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="18.08984375" customWidth="1" style="2" min="1" max="1"/>
@@ -19846,32 +19846,32 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>BIG Outdoors</t>
+          <t>DreamMedia</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>BIG Outdoors</t>
+          <t>DreamMedia</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Monoposte 10x5</t>
+          <t>Mupi Papel</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>Área de mancha publicitária: 10000x5000mm.</t>
+          <t>Área total: 118,5x175cm. Área de mancha publicitária: 116x171cm.</t>
         </is>
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>Ficheiro fechado: JPG, TIFF ou PDF, a 10% do tamanho real, a 300 dpi. Formato editável: textos convertidos em curvas (outlines) ou fontes fornecidas.</t>
+          <t>Ficheiro fechado: JPG, TIFF ou PDF, a 10% do tamanho real, a 300 dpi. Formato editável: textos convertidos em curvas (outlines) ou fontes fornecidas. Ficheiros prontos para impressão em CMYK — não se aceita Pantone.</t>
         </is>
       </c>
       <c r="L365" t="inlineStr">
         <is>
-          <t>Bleed: 10cm a toda a volta (não deve conter informação importante). Ficheiros fornecidos em CMYK prontos para impressão — ficheiros em RGB são convertidos para CMYK, podendo as cores sofrer alterações. Importante: a arte final não deve conter letras de tamanho inferior a 30cm (110 pontos); dar maior destaque ao produto, logótipo, telefone e site para melhores resultados de comunicação.</t>
+          <t>Papel: Couché mate (COM) ou Sunrise, entre 130 e 140 g/m². Densidade até 117µm. Prazo de entrega: até 5 dias úteis antes do início da campanha. Quantidades requeridas: mais 10% além da quantidade contratada. A arte final não deve conter elementos de informação relevante junto às margens de corte.</t>
         </is>
       </c>
     </row>
@@ -19888,32 +19888,32 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>BIG Outdoors</t>
+          <t>DreamMedia</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>BIG Outdoors</t>
+          <t>DreamMedia</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Monoposte 11x5</t>
+          <t>Carris Metropolitana</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>Área de mancha publicitária: 11000x5000mm.</t>
+          <t>3 medidas obrigatórias, para adaptação a todos os tamanhos de autocarro: 1590x535mm, 1440x640mm, 2210x640mm.</t>
         </is>
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>Ficheiro fechado: JPG, TIFF ou PDF, a 10% do tamanho real, a 300 dpi. Formato editável: textos convertidos em curvas (outlines) ou fontes fornecidas.</t>
+          <t>Material obrigatório: PPA 3,5mm - 650g (impressão direta), alvéolos na vertical. Placas superiores a 200cm de comprimento fornecidas em 2 folhas com colagem em sistema de encosto (fita cola 3M ref.ª 8959) — também permitido numa só folha. Escala: tamanho real. Resolução: 300 dpi. Cores: CMYK — não se aceita Pantone (ficheiros em RGB são convertidos). Fontes convertidas em curvas (outlines). Formato: PDF editável, gravado em versão anterior à utilizada para o criar. Imagens incorporadas a 300dpi no ficheiro final.</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
         <is>
-          <t>Bleed: 10cm a toda a volta (não deve conter informação importante). Ficheiros fornecidos em CMYK prontos para impressão — ficheiros em RGB são convertidos para CMYK, podendo as cores sofrer alterações. Importante: a arte final não deve conter letras de tamanho inferior a 30cm (110 pontos); dar maior destaque ao produto, logótipo, telefone e site para melhores resultados de comunicação.</t>
+          <t>Margem de segurança de 40mm a toda a volta (textos, logótipos e imagens críticas). Sangria de 5mm a toda a volta para corte e ajuste. Elementos de fundo (cores, imagens contínuas ou texturas) devem ocupar a área total com sangria. Entrega das artes finais: 6 dias úteis antes do 1º dia de implementação — é obrigatório fornecer as 3 medidas. Implementação: Áreas 1 e 2 entram à quarta-feira; Áreas 3 e 4 entram à quinta-feira.</t>
         </is>
       </c>
     </row>
@@ -19930,22 +19930,22 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>BIG Outdoors</t>
+          <t>DreamMedia</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>BIG Outdoors</t>
+          <t>DreamMedia</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>Monoposte 12x5</t>
+          <t>Citie Premium</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>Área de mancha publicitária: 12000x5000mm.</t>
+          <t>2,40x1,70m.</t>
         </is>
       </c>
       <c r="J367" t="inlineStr">
@@ -19955,7 +19955,7 @@
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t>Bleed: 10cm a toda a volta (não deve conter informação importante). Ficheiros fornecidos em CMYK prontos para impressão — ficheiros em RGB são convertidos para CMYK, podendo as cores sofrer alterações. Importante: a arte final não deve conter letras de tamanho inferior a 30cm (110 pontos); dar maior destaque ao produto, logótipo, telefone e site para melhores resultados de comunicação.</t>
+          <t>Bleed: 10cm a toda a volta (não deve conter informação importante). Ficheiros fornecidos em CMYK, prontos para impressão — ficheiros em RGB são convertidos para CMYK, podendo as cores sofrer alterações.</t>
         </is>
       </c>
     </row>
@@ -19972,32 +19972,37 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>JCDecaux</t>
+          <t>DreamMedia</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>JCDecaux</t>
+          <t>DreamMedia</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>Mupi Papel</t>
+          <t>Power Street</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>Área total: 1185x1750mm. Área visível: 1160x1710mm.</t>
+          <t>1080x1920px (Full HD).</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>9:16</t>
         </is>
       </c>
       <c r="J368" t="inlineStr">
         <is>
-          <t>Papel, gramagem 130g, verso do cartaz com fundo branco. Ficheiro: Illustrator, Photoshop, PDF, EPS ou TIFF.</t>
+          <t>Vídeo pronto: .MOV ou .MP4 (MP4 preferencial), RGB, 30fps ou 60fps. Materiais abertos para produção também aceites: Adobe Photoshop (1080x1920px, layers abertos, RGB, 72dpi, fontes em curvas) ou Adobe Illustrator/After Effects (1080x1920px, fontes em curvas, imagens rasterizadas no ficheiro).</t>
         </is>
       </c>
       <c r="L368" t="inlineStr">
         <is>
-          <t>Prazo: 7 dias úteis após aprovação da Arte Final. Se enviar PDF, atenção a cores/perfis embebidos/resolução de imagens; enviar fontes; texto convertido em curvas, aberto e editável. Impressão offset: CMYK, mín. 300 dpi, máx. 400 dpi. Impressão digital: CMYK, mín. 150 dpi, máx. 200 dpi. Ficheiro na medida indicada + 3cm de bleed (3mm se a AF for elaborada à escala de 10%); respeitar área de segurança virtual para evitar corte de elementos na afixação; sempre que possível, enviar com prova de cor. Após receção, a JCDecaux envia um JPG para validação final antes de imprimir; após aprovação, declina responsabilidade por desformatações/falhas na imagem. Critérios de qualidade: opacidade ≥88%, brancura 91-93 ISO, absorção de água (cobb60) 15-30g/m², absorção de água (cobb300) &lt;70g/m², distensão máx. ±2%/m, resistência à rutura por tração (húmido) &gt;0,6kN/m — materiais fora destes requisitos podem não ser afixados. Especificações ambientais: papel com certificação PEFC/FSC (ou equivalente); tintas conformes REACH/GreenGuard, isentas de metais pesados; papel reciclado, sem cloro (ECF/TCF).</t>
+          <t>Duração: 10″. Em anúncios/vídeos com textos sobrepostos, enviar também as imagens/vídeos limpos, para a inclusão dos textos ser aplicada e editada à parte. Margem de segurança: 30px. Prazo de entrega: 72 horas antes do início da campanha. Enviar para digital@dreammedia.pt (via WeTransfer/Dropbox/Google Drive se superior a 15Mb).</t>
         </is>
       </c>
     </row>
@@ -20014,32 +20019,32 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>JCDecaux</t>
+          <t>BIG Outdoors</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>JCDecaux</t>
+          <t>BIG Outdoors</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>Impressão Senior</t>
+          <t>Monoposte 10x5</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>Área visível: 3020x2230mm. Área total: 3200x2350mm.</t>
+          <t>Área de mancha publicitária: 10000x5000mm.</t>
         </is>
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>Papel, gramagem 150g, verso do cartaz com fundo branco. Ficheiro: Illustrator, Photoshop, PDF, EPS ou TIFF.</t>
+          <t>Ficheiro fechado: JPG, TIFF ou PDF, a 10% do tamanho real, a 300 dpi. Formato editável: textos convertidos em curvas (outlines) ou fontes fornecidas.</t>
         </is>
       </c>
       <c r="L369" t="inlineStr">
         <is>
-          <t>Impressão em 1, 2 ou 4 folhas, entregues alceadas por ordem de colagem (a começar na folha 1, com o verso para baixo). Impressão em 2 folhas: folha 1 3200x1200mm (aparada 3130x1150mm) + folha 2 idêntica, margem de sobreposição 25mm/35mm. Impressão em 4 folhas: 1600x1200mm por folha (aparada 1530x1175mm), aparadas à medida sem margem entre si. Prazo: 7 dias úteis após aprovação da Arte Final. Ficheiro: Illustrator/Photoshop (incluir fontes e respetivos links) ou PDF (cores/perfis embebidos/resolução de imagens, texto em curvas); impressão offset CMYK 300-400 dpi, digital CMYK 150-200 dpi; medida indicada + 3cm de bleed (3mm à escala de 10%); respeitar área de segurança virtual; enviar com prova de cor sempre que possível. Entrega nas instalações da JCDecaux 5 dias úteis antes do início da campanha, com impressão da campanha e guia de transporte certificada; horário de entrega 07h-12h e 13h30-16h (Portão 2), Beco da Aviação nº1, Granja do Alpriate, Vialonga. Após receção, a JCDecaux envia JPG para validação; após aprovação, declina responsabilidade por falhas na imagem. Critérios de qualidade: opacidade ≥88%, brancura 91-93 ISO, absorção água (cobb60) 15-30g/m², (cobb300) &lt;70g/m², distensão máx. ±2%/m, resistência à rutura (húmido) &gt;0,6kN/m.</t>
+          <t>Bleed: 10cm a toda a volta (não deve conter informação importante). Ficheiros fornecidos em CMYK prontos para impressão — ficheiros em RGB são convertidos para CMYK, podendo as cores sofrer alterações. Importante: a arte final não deve conter letras de tamanho inferior a 30cm (110 pontos); dar maior destaque ao produto, logótipo, telefone e site para melhores resultados de comunicação.</t>
         </is>
       </c>
     </row>
@@ -20056,37 +20061,32 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>JCDecaux</t>
+          <t>BIG Outdoors</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>JCDecaux</t>
+          <t>BIG Outdoors</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>Mupi Digital</t>
+          <t>Monoposte 11x5</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>1080x1920px.</t>
-        </is>
-      </c>
-      <c r="H370" t="inlineStr">
-        <is>
-          <t>9:16</t>
+          <t>Área de mancha publicitária: 11000x5000mm.</t>
         </is>
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000.</t>
+          <t>Ficheiro fechado: JPG, TIFF ou PDF, a 10% do tamanho real, a 300 dpi. Formato editável: textos convertidos em curvas (outlines) ou fontes fornecidas.</t>
         </is>
       </c>
       <c r="L370" t="inlineStr">
         <is>
-          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Após envio, a JCDecaux declina responsabilidade por falhas no vídeo apresentado. Alterações ao vídeo carecem de aprovação final do cliente; a JCDecaux não se responsabiliza por atraso na entrega (sem compensação de airing).</t>
+          <t>Bleed: 10cm a toda a volta (não deve conter informação importante). Ficheiros fornecidos em CMYK prontos para impressão — ficheiros em RGB são convertidos para CMYK, podendo as cores sofrer alterações. Importante: a arte final não deve conter letras de tamanho inferior a 30cm (110 pontos); dar maior destaque ao produto, logótipo, telefone e site para melhores resultados de comunicação.</t>
         </is>
       </c>
     </row>
@@ -20103,37 +20103,32 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>JCDecaux</t>
+          <t>BIG Outdoors</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>JCDecaux</t>
+          <t>BIG Outdoors</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>Mupi Digital (Shopping)</t>
+          <t>Monoposte 12x5</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>Ficheiro entregue em 1920x1080px (paisagem, para ecrãs de 63''), rodado automaticamente pelo sistema para exibição vertical 1080x1920px.</t>
-        </is>
-      </c>
-      <c r="H371" t="inlineStr">
-        <is>
-          <t>16:9 (ficheiro) / 9:16 (exibição)</t>
+          <t>Área de mancha publicitária: 12000x5000mm.</t>
         </is>
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>Ficheiro nativo (compressão nativa), bitrate máx. 20.000.</t>
+          <t>Ficheiro fechado: JPG, TIFF ou PDF, a 10% do tamanho real, a 300 dpi. Formato editável: textos convertidos em curvas (outlines) ou fontes fornecidas.</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t>Duração do spot: 10 segundos, dentro de um loop de 60 segundos com outros anunciantes. Enviar o vídeo 2 dias antes do início da campanha, por e-mail para o contacto JCDecaux. Alterações carecem de aprovação final do cliente; a JCDecaux declina responsabilidade por falhas no vídeo após o envio, e não se responsabiliza por atraso na entrega.</t>
+          <t>Bleed: 10cm a toda a volta (não deve conter informação importante). Ficheiros fornecidos em CMYK prontos para impressão — ficheiros em RGB são convertidos para CMYK, podendo as cores sofrer alterações. Importante: a arte final não deve conter letras de tamanho inferior a 30cm (110 pontos); dar maior destaque ao produto, logótipo, telefone e site para melhores resultados de comunicação.</t>
         </is>
       </c>
     </row>
@@ -20160,22 +20155,22 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>Painel 8x3 - Papel</t>
+          <t>Mupi Papel</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>Área total: 8000x3000mm. Área visível: 7500x2750mm.</t>
+          <t>Área total: 1185x1750mm. Área visível: 1160x1710mm.</t>
         </is>
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>Papel, gramagem entre 120g e 170g, verso do cartaz com fundo azul. Ficheiro: Illustrator, Photoshop, PDF, EPS ou TIFF.</t>
+          <t>Papel, gramagem 130g, verso do cartaz com fundo branco. Ficheiro: Illustrator, Photoshop, PDF, EPS ou TIFF.</t>
         </is>
       </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t>Prazo: 7 dias úteis após aprovação da Arte Final. Impressão em 12, 14 ou 16 folhas, entregues alceadas (a começar na folha 1, verso para baixo), numeradas no canto superior direito. Impressão em 14 folhas: folhas superiores 1-6 (997mm cada) + folha 7 (997mm), folhas inferiores 9-13 (1135mm cada) + folha 14 (1135mm); margem de sobreposição 25mm à direita nas folhas superiores (exceto a última) e 25mm à direita + no topo nas inferiores (exceto a última, só no topo); áreas de sobreposição isentas de impressão. Impressão em 16 folhas: superiores 1-7 (997mm) + folha 8 (997mm), inferiores 9-15 (997mm) + folha 16 (997mm), mesmas regras de margem. Se PDF: cores/perfis embebidos/resolução de imagens, texto em curvas; impressão offset CMYK 300-400 dpi, digital CMYK 150-200 dpi; medida indicada + 3cm de bleed (3mm à escala de 10%); área de segurança virtual; prova de cor recomendada. Entrega nas instalações JCDecaux, Portão 1, Beco da Aviação nº1, Granja do Alpriate, Vialonga, 07h-12h/13h30-16h. Após receção, JCDecaux envia JPG para validação; após aprovação, declina responsabilidade por falhas na imagem.</t>
+          <t>Prazo: 7 dias úteis após aprovação da Arte Final. Se enviar PDF, atenção a cores/perfis embebidos/resolução de imagens; enviar fontes; texto convertido em curvas, aberto e editável. Impressão offset: CMYK, mín. 300 dpi, máx. 400 dpi. Impressão digital: CMYK, mín. 150 dpi, máx. 200 dpi. Ficheiro na medida indicada + 3cm de bleed (3mm se a AF for elaborada à escala de 10%); respeitar área de segurança virtual para evitar corte de elementos na afixação; sempre que possível, enviar com prova de cor. Após receção, a JCDecaux envia um JPG para validação final antes de imprimir; após aprovação, declina responsabilidade por desformatações/falhas na imagem. Critérios de qualidade: opacidade ≥88%, brancura 91-93 ISO, absorção de água (cobb60) 15-30g/m², absorção de água (cobb300) &lt;70g/m², distensão máx. ±2%/m, resistência à rutura por tração (húmido) &gt;0,6kN/m — materiais fora destes requisitos podem não ser afixados. Especificações ambientais: papel com certificação PEFC/FSC (ou equivalente); tintas conformes REACH/GreenGuard, isentas de metais pesados; papel reciclado, sem cloro (ECF/TCF).</t>
         </is>
       </c>
     </row>
@@ -20202,22 +20197,22 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>Painel 8x3 - Vinil</t>
+          <t>Impressão Senior</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>Área total: 8000x3000mm. Área visível: 8000x3000mm (sem margem).</t>
+          <t>Área visível: 3020x2230mm. Área total: 3200x2350mm.</t>
         </is>
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>Vinil PVC branco ou transparente, superfície brilhante ou mate, polyacrylate removível e transparente; base em papel revestido a silicone 135g/m². Ficheiro: Illustrator, Photoshop, PDF, EPS ou TIFF.</t>
+          <t>Papel, gramagem 150g, verso do cartaz com fundo branco. Ficheiro: Illustrator, Photoshop, PDF, EPS ou TIFF.</t>
         </is>
       </c>
       <c r="L373" t="inlineStr">
         <is>
-          <t>Uso recomendado: outdoors de curta e média duração. Método de impressão: tintas de base solvente, UV ou látex. Prazo: 7 dias úteis após aprovação da Arte Final. Impressão em 8 folhas de 1000mm cada, enroladas por ordem (folha 1 a 8), numeradas no canto superior direito; margem de sobreposição 25mm à direita em todas as folhas (áreas de sobreposição isentas de impressão). Se PDF: cores/perfis embebidos/resolução de imagens, texto em curvas; impressão offset CMYK 300-400 dpi, digital CMYK 150-200 dpi; medida indicada + 5cm de bleed (5mm à escala de 10%); área de segurança virtual; prova de cor recomendada. Entrega nas instalações JCDecaux, Portão 1, Beco da Aviação nº1, Granja do Alpriate, Vialonga, 5 dias úteis antes do início da campanha, com impressão da campanha e guia de transporte certificada, 07h-12h/13h30-16h. Após receção, JCDecaux envia JPG para validação; após aprovação, declina responsabilidade por falhas na imagem.</t>
+          <t>Impressão em 1, 2 ou 4 folhas, entregues alceadas por ordem de colagem (a começar na folha 1, com o verso para baixo). Impressão em 2 folhas: folha 1 3200x1200mm (aparada 3130x1150mm) + folha 2 idêntica, margem de sobreposição 25mm/35mm. Impressão em 4 folhas: 1600x1200mm por folha (aparada 1530x1175mm), aparadas à medida sem margem entre si. Prazo: 7 dias úteis após aprovação da Arte Final. Ficheiro: Illustrator/Photoshop (incluir fontes e respetivos links) ou PDF (cores/perfis embebidos/resolução de imagens, texto em curvas); impressão offset CMYK 300-400 dpi, digital CMYK 150-200 dpi; medida indicada + 3cm de bleed (3mm à escala de 10%); respeitar área de segurança virtual; enviar com prova de cor sempre que possível. Entrega nas instalações da JCDecaux 5 dias úteis antes do início da campanha, com impressão da campanha e guia de transporte certificada; horário de entrega 07h-12h e 13h30-16h (Portão 2), Beco da Aviação nº1, Granja do Alpriate, Vialonga. Após receção, a JCDecaux envia JPG para validação; após aprovação, declina responsabilidade por falhas na imagem. Critérios de qualidade: opacidade ≥88%, brancura 91-93 ISO, absorção água (cobb60) 15-30g/m², (cobb300) &lt;70g/m², distensão máx. ±2%/m, resistência à rutura (húmido) &gt;0,6kN/m.</t>
         </is>
       </c>
     </row>
@@ -20244,17 +20239,17 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>Premium LED 6m²</t>
+          <t>Mupi Digital</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>328x492px.</t>
+          <t>1080x1920px.</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>2:3</t>
+          <t>9:16</t>
         </is>
       </c>
       <c r="J374" t="inlineStr">
@@ -20264,7 +20259,7 @@
       </c>
       <c r="L374" t="inlineStr">
         <is>
-          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 4 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
+          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Após envio, a JCDecaux declina responsabilidade por falhas no vídeo apresentado. Alterações ao vídeo carecem de aprovação final do cliente; a JCDecaux não se responsabiliza por atraso na entrega (sem compensação de airing).</t>
         </is>
       </c>
     </row>
@@ -20291,27 +20286,27 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>Premium LED 8m²</t>
+          <t>Mupi Digital (Shopping)</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>370x656px.</t>
+          <t>Ficheiro entregue em 1920x1080px (paisagem, para ecrãs de 63''), rodado automaticamente pelo sistema para exibição vertical 1080x1920px.</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>9:16</t>
+          <t>16:9 (ficheiro) / 9:16 (exibição)</t>
         </is>
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000.</t>
+          <t>Ficheiro nativo (compressão nativa), bitrate máx. 20.000.</t>
         </is>
       </c>
       <c r="L375" t="inlineStr">
         <is>
-          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
+          <t>Duração do spot: 10 segundos, dentro de um loop de 60 segundos com outros anunciantes. Enviar o vídeo 2 dias antes do início da campanha, por e-mail para o contacto JCDecaux. Alterações carecem de aprovação final do cliente; a JCDecaux declina responsabilidade por falhas no vídeo após o envio, e não se responsabiliza por atraso na entrega.</t>
         </is>
       </c>
     </row>
@@ -20338,27 +20333,22 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>Premium LED 12m²</t>
+          <t>Painel 8x3 - Papel</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>1520x800px.</t>
-        </is>
-      </c>
-      <c r="H376" t="inlineStr">
-        <is>
-          <t>1.91:1</t>
+          <t>Área total: 8000x3000mm. Área visível: 7500x2750mm.</t>
         </is>
       </c>
       <c r="J376" t="inlineStr">
         <is>
-          <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000.</t>
+          <t>Papel, gramagem entre 120g e 170g, verso do cartaz com fundo azul. Ficheiro: Illustrator, Photoshop, PDF, EPS ou TIFF.</t>
         </is>
       </c>
       <c r="L376" t="inlineStr">
         <is>
-          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
+          <t>Prazo: 7 dias úteis após aprovação da Arte Final. Impressão em 12, 14 ou 16 folhas, entregues alceadas (a começar na folha 1, verso para baixo), numeradas no canto superior direito. Impressão em 14 folhas: folhas superiores 1-6 (997mm cada) + folha 7 (997mm), folhas inferiores 9-13 (1135mm cada) + folha 14 (1135mm); margem de sobreposição 25mm à direita nas folhas superiores (exceto a última) e 25mm à direita + no topo nas inferiores (exceto a última, só no topo); áreas de sobreposição isentas de impressão. Impressão em 16 folhas: superiores 1-7 (997mm) + folha 8 (997mm), inferiores 9-15 (997mm) + folha 16 (997mm), mesmas regras de margem. Se PDF: cores/perfis embebidos/resolução de imagens, texto em curvas; impressão offset CMYK 300-400 dpi, digital CMYK 150-200 dpi; medida indicada + 3cm de bleed (3mm à escala de 10%); área de segurança virtual; prova de cor recomendada. Entrega nas instalações JCDecaux, Portão 1, Beco da Aviação nº1, Granja do Alpriate, Vialonga, 07h-12h/13h30-16h. Após receção, JCDecaux envia JPG para validação; após aprovação, declina responsabilidade por falhas na imagem.</t>
         </is>
       </c>
     </row>
@@ -20385,27 +20375,22 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>Premium LED 15m²</t>
+          <t>Painel 8x3 - Vinil</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>720x1296px.</t>
-        </is>
-      </c>
-      <c r="H377" t="inlineStr">
-        <is>
-          <t>9:16</t>
+          <t>Área total: 8000x3000mm. Área visível: 8000x3000mm (sem margem).</t>
         </is>
       </c>
       <c r="J377" t="inlineStr">
         <is>
-          <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000.</t>
+          <t>Vinil PVC branco ou transparente, superfície brilhante ou mate, polyacrylate removível e transparente; base em papel revestido a silicone 135g/m². Ficheiro: Illustrator, Photoshop, PDF, EPS ou TIFF.</t>
         </is>
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
+          <t>Uso recomendado: outdoors de curta e média duração. Método de impressão: tintas de base solvente, UV ou látex. Prazo: 7 dias úteis após aprovação da Arte Final. Impressão em 8 folhas de 1000mm cada, enroladas por ordem (folha 1 a 8), numeradas no canto superior direito; margem de sobreposição 25mm à direita em todas as folhas (áreas de sobreposição isentas de impressão). Se PDF: cores/perfis embebidos/resolução de imagens, texto em curvas; impressão offset CMYK 300-400 dpi, digital CMYK 150-200 dpi; medida indicada + 5cm de bleed (5mm à escala de 10%); área de segurança virtual; prova de cor recomendada. Entrega nas instalações JCDecaux, Portão 1, Beco da Aviação nº1, Granja do Alpriate, Vialonga, 5 dias úteis antes do início da campanha, com impressão da campanha e guia de transporte certificada, 07h-12h/13h30-16h. Após receção, JCDecaux envia JPG para validação; após aprovação, declina responsabilidade por falhas na imagem.</t>
         </is>
       </c>
     </row>
@@ -20432,17 +20417,17 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>Premium LED 18m²</t>
+          <t>Premium LED 6m²</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>640x1152px.</t>
+          <t>328x492px.</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>9:16</t>
+          <t>2:3</t>
         </is>
       </c>
       <c r="J378" t="inlineStr">
@@ -20452,7 +20437,7 @@
       </c>
       <c r="L378" t="inlineStr">
         <is>
-          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
+          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 4 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
         </is>
       </c>
     </row>
@@ -20479,12 +20464,17 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>Premium LED 22m²</t>
+          <t>Premium LED 8m²</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>1248x800px.</t>
+          <t>370x656px.</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>9:16</t>
         </is>
       </c>
       <c r="J379" t="inlineStr">
@@ -20494,7 +20484,7 @@
       </c>
       <c r="L379" t="inlineStr">
         <is>
-          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. Vídeo em estilo "Subtle Motion" recomendado: movimento lento e gradual dos elementos criativos (slow motion sem cortes bruscos; fundos deslocados/ampliados lentamente em vez de intermitentes; texto a desvanecer gradualmente em vez de deslizar/pulsar; luzes a brilhar em vez de piscar); marca visível em pelo menos 80% da criatividade. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
+          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
         </is>
       </c>
     </row>
@@ -20521,12 +20511,17 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>Premium LED 25m²</t>
+          <t>Premium LED 12m²</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>480x810px.</t>
+          <t>1520x800px.</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>1.91:1</t>
         </is>
       </c>
       <c r="J380" t="inlineStr">
@@ -20563,12 +20558,17 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>Premium LED 37m²</t>
+          <t>Premium LED 15m²</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>480x738px.</t>
+          <t>720x1296px.</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>9:16</t>
         </is>
       </c>
       <c r="J381" t="inlineStr">
@@ -20578,7 +20578,7 @@
       </c>
       <c r="L381" t="inlineStr">
         <is>
-          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 16,7%. Vídeo em estilo "Subtle Motion" recomendado (ver formato "Premium LED 22m²" para guidelines completas). A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
+          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
         </is>
       </c>
     </row>
@@ -20595,200 +20595,205 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Táxi Advertising</t>
+          <t>JCDecaux</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>Táxi Advertising</t>
+          <t>JCDecaux</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>Decoração de Táxi</t>
+          <t>Premium LED 18m²</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>Manter o tamanho original do template (ficheiros vetoriais reais fornecidos pelo fornecedor, com o desenho do lado esquerdo e do lado direito do táxi).</t>
+          <t>640x1152px.</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>9:16</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>Ficheiros de trabalho em Illustrator (vetoriais). Entrega: JPG ou PDF.</t>
+          <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000.</t>
         </is>
       </c>
       <c r="L382" t="inlineStr">
         <is>
-          <t>O texto deve manter-se dentro da linha amarela de segurança (para não ser cortado). O fundo atrás do texto deve ultrapassar a linha branca em pelo menos 50mm de bleed. Impressão em CMYK, resolução 150 pixels/polegada. É obrigatório enviar também um PDF com a maqueta da decoração do táxi, para orientação da colagem do vinil.</t>
+          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Imprensa</t>
+          <t>OOH</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Imprensa</t>
+          <t>OOH</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Correio da Manhã</t>
+          <t>JCDecaux</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>Correio da Manhã</t>
+          <t>JCDecaux</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>Página</t>
+          <t>Premium LED 22m²</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>257x320mm (80 módulos, 5 col. x 16 mód.)</t>
+          <t>1248x800px.</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+          <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000.</t>
         </is>
       </c>
       <c r="L383" t="inlineStr">
         <is>
-          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 colunas x 16 módulos); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. Vídeo em estilo "Subtle Motion" recomendado: movimento lento e gradual dos elementos criativos (slow motion sem cortes bruscos; fundos deslocados/ampliados lentamente em vez de intermitentes; texto a desvanecer gradualmente em vez de deslizar/pulsar; luzes a brilhar em vez de piscar); marca visível em pelo menos 80% da criatividade. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Imprensa</t>
+          <t>OOH</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Imprensa</t>
+          <t>OOH</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Correio da Manhã</t>
+          <t>JCDecaux</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>Correio da Manhã</t>
+          <t>JCDecaux</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>Meia Página</t>
+          <t>Premium LED 25m²</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>204x240mm (48 módulos, 4 col. x 12 mód.)</t>
+          <t>480x810px.</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+          <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000.</t>
         </is>
       </c>
       <c r="L384" t="inlineStr">
         <is>
-          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 colunas x 16 módulos); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Imprensa</t>
+          <t>OOH</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Imprensa</t>
+          <t>OOH</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Correio da Manhã</t>
+          <t>JCDecaux</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Correio da Manhã</t>
+          <t>JCDecaux</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>1/2 Página Alto (3 Col.)</t>
+          <t>Premium LED 37m²</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>153x320mm (48 módulos, 3 col. x 16 mód.)</t>
+          <t>480x738px.</t>
         </is>
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+          <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000.</t>
         </is>
       </c>
       <c r="L385" t="inlineStr">
         <is>
-          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 colunas x 16 módulos); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 16,7%. Vídeo em estilo "Subtle Motion" recomendado (ver formato "Premium LED 22m²" para guidelines completas). A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Imprensa</t>
+          <t>OOH</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Imprensa</t>
+          <t>OOH</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Correio da Manhã</t>
+          <t>Táxi Advertising</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>Correio da Manhã</t>
+          <t>Táxi Advertising</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>1/3 Página Alto (2 Col.)</t>
+          <t>Decoração de Táxi</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>100x320mm (32 módulos, 2 col. x 16 mód.)</t>
+          <t>Manter o tamanho original do template (ficheiros vetoriais reais fornecidos pelo fornecedor, com o desenho do lado esquerdo e do lado direito do táxi).</t>
         </is>
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+          <t>Ficheiros de trabalho em Illustrator (vetoriais). Entrega: JPG ou PDF.</t>
         </is>
       </c>
       <c r="L386" t="inlineStr">
         <is>
-          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 colunas x 16 módulos); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>O texto deve manter-se dentro da linha amarela de segurança (para não ser cortado). O fundo atrás do texto deve ultrapassar a linha branca em pelo menos 50mm de bleed. Impressão em CMYK, resolução 150 pixels/polegada. É obrigatório enviar também um PDF com a maqueta da decoração do táxi, para orientação da colagem do vinil.</t>
         </is>
       </c>
     </row>
@@ -20815,12 +20820,12 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>1/2 Página Baixo</t>
+          <t>Página</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>257x160mm (40 módulos, 5 col. x 8 mód.)</t>
+          <t>257x320mm (80 módulos, 5 col. x 16 mód.)</t>
         </is>
       </c>
       <c r="J387" t="inlineStr">
@@ -20857,12 +20862,12 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>1/4 Página (3 Col.)</t>
+          <t>Meia Página</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>153x160mm (24 módulos, 3 col. x 8 mód.)</t>
+          <t>204x240mm (48 módulos, 4 col. x 12 mód.)</t>
         </is>
       </c>
       <c r="J388" t="inlineStr">
@@ -20899,12 +20904,12 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>1/4 Página (2 Col.)</t>
+          <t>1/2 Página Alto (3 Col.)</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>100x160mm (16 módulos, 2 col. x 8 mód.)</t>
+          <t>153x320mm (48 módulos, 3 col. x 16 mód.)</t>
         </is>
       </c>
       <c r="J389" t="inlineStr">
@@ -20941,12 +20946,12 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>Rodapé</t>
+          <t>1/3 Página Alto (2 Col.)</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>257x61mm (15 módulos, 5 col. x 3 mód.)</t>
+          <t>100x320mm (32 módulos, 2 col. x 16 mód.)</t>
         </is>
       </c>
       <c r="J390" t="inlineStr">
@@ -20978,17 +20983,17 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Mais Sport</t>
+          <t>Correio da Manhã</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>Página</t>
+          <t>1/2 Página Baixo</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>257x320mm (80 módulos, 5 col. x 16 mód.)</t>
+          <t>257x160mm (40 módulos, 5 col. x 8 mód.)</t>
         </is>
       </c>
       <c r="J391" t="inlineStr">
@@ -20998,7 +21003,7 @@
       </c>
       <c r="L391" t="inlineStr">
         <is>
-          <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 257x320mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 colunas x 16 módulos); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -21020,17 +21025,17 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>Boa Onda</t>
+          <t>Correio da Manhã</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>Página Dupla</t>
+          <t>1/4 Página (3 Col.)</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>400x295mm (+3mm bleed)</t>
+          <t>153x160mm (24 módulos, 3 col. x 8 mód.)</t>
         </is>
       </c>
       <c r="J392" t="inlineStr">
@@ -21040,7 +21045,7 @@
       </c>
       <c r="L392" t="inlineStr">
         <is>
-          <t>Periodicidade semanal (sexta-feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 colunas x 16 módulos); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -21062,17 +21067,17 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>Boa Onda</t>
+          <t>Correio da Manhã</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>Página</t>
+          <t>1/4 Página (2 Col.)</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>200x295mm (+3mm bleed)</t>
+          <t>100x160mm (16 módulos, 2 col. x 8 mód.)</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
@@ -21082,7 +21087,7 @@
       </c>
       <c r="L393" t="inlineStr">
         <is>
-          <t>Periodicidade semanal (sexta-feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 colunas x 16 módulos); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -21104,17 +21109,17 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>Boa Onda</t>
+          <t>Correio da Manhã</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>1/2 Página Dupla</t>
+          <t>Rodapé</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>400x147mm (+3mm bleed)</t>
+          <t>257x61mm (15 módulos, 5 col. x 3 mód.)</t>
         </is>
       </c>
       <c r="J394" t="inlineStr">
@@ -21124,7 +21129,7 @@
       </c>
       <c r="L394" t="inlineStr">
         <is>
-          <t>Periodicidade semanal (sexta-feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 colunas x 16 módulos); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -21146,17 +21151,17 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>Boa Onda</t>
+          <t>Mais Sport</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>1/2 Página Alto</t>
+          <t>Página</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>100x295mm (+3mm bleed)</t>
+          <t>257x320mm (80 módulos, 5 col. x 16 mód.)</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
@@ -21166,7 +21171,7 @@
       </c>
       <c r="L395" t="inlineStr">
         <is>
-          <t>Periodicidade semanal (sexta-feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 257x320mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -21193,12 +21198,12 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>1/2 Página Baixo</t>
+          <t>Página Dupla</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>200x147mm (+3mm bleed)</t>
+          <t>400x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J396" t="inlineStr">
@@ -21235,12 +21240,12 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>1/3 Página Alto</t>
+          <t>Página</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>72x295mm (+3mm bleed)</t>
+          <t>200x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
@@ -21277,12 +21282,12 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>1/3 Página Baixo</t>
+          <t>1/2 Página Dupla</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>200x105mm (+3mm bleed)</t>
+          <t>400x147mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
@@ -21319,12 +21324,12 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>1/4 Página</t>
+          <t>1/2 Página Alto</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>100x147mm (+3mm bleed)</t>
+          <t>100x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J399" t="inlineStr">
@@ -21361,12 +21366,12 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>Rodapé</t>
+          <t>1/2 Página Baixo</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>200x78mm (+3mm bleed)</t>
+          <t>200x147mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J400" t="inlineStr">
@@ -21398,17 +21403,17 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>VIDAS</t>
+          <t>Boa Onda</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>Página Dupla</t>
+          <t>1/3 Página Alto</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>400x295mm (+3mm bleed)</t>
+          <t>72x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J401" t="inlineStr">
@@ -21418,7 +21423,7 @@
       </c>
       <c r="L401" t="inlineStr">
         <is>
-          <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Periodicidade semanal (sexta-feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -21440,17 +21445,17 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>VIDAS</t>
+          <t>Boa Onda</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>Página</t>
+          <t>1/3 Página Baixo</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>200x295mm (+3mm bleed)</t>
+          <t>200x105mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J402" t="inlineStr">
@@ -21460,7 +21465,7 @@
       </c>
       <c r="L402" t="inlineStr">
         <is>
-          <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Periodicidade semanal (sexta-feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -21482,17 +21487,17 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>VIDAS</t>
+          <t>Boa Onda</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>1/2 Página Dupla</t>
+          <t>1/4 Página</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>400x147mm (+3mm bleed)</t>
+          <t>100x147mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J403" t="inlineStr">
@@ -21502,7 +21507,7 @@
       </c>
       <c r="L403" t="inlineStr">
         <is>
-          <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Periodicidade semanal (sexta-feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -21524,17 +21529,17 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>VIDAS</t>
+          <t>Boa Onda</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>1/2 Página Alto</t>
+          <t>Rodapé</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>100x295mm (+3mm bleed)</t>
+          <t>200x78mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J404" t="inlineStr">
@@ -21544,7 +21549,7 @@
       </c>
       <c r="L404" t="inlineStr">
         <is>
-          <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Periodicidade semanal (sexta-feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -21571,12 +21576,12 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>1/2 Página Baixo</t>
+          <t>Página Dupla</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>200x147mm (+3mm bleed)</t>
+          <t>400x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J405" t="inlineStr">
@@ -21613,12 +21618,12 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>1/3 Página Alto</t>
+          <t>Página</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>72x295mm (+3mm bleed)</t>
+          <t>200x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J406" t="inlineStr">
@@ -21655,12 +21660,12 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>1/3 Página Baixo</t>
+          <t>1/2 Página Dupla</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>200x105mm (+3mm bleed)</t>
+          <t>400x147mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J407" t="inlineStr">
@@ -21697,12 +21702,12 @@
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>1/4 Página</t>
+          <t>1/2 Página Alto</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>100x147mm (+3mm bleed)</t>
+          <t>100x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
@@ -21739,12 +21744,12 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>Rodapé</t>
+          <t>1/2 Página Baixo</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>200x78mm (+3mm bleed)</t>
+          <t>200x147mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J409" t="inlineStr">
@@ -21776,17 +21781,17 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>Domingo</t>
+          <t>VIDAS</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>Página Dupla</t>
+          <t>1/3 Página Alto</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>400x295mm (+3mm bleed)</t>
+          <t>72x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J410" t="inlineStr">
@@ -21796,7 +21801,7 @@
       </c>
       <c r="L410" t="inlineStr">
         <is>
-          <t>Periodicidade semanal (domingo); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -21818,17 +21823,17 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Domingo</t>
+          <t>VIDAS</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>Página</t>
+          <t>1/3 Página Baixo</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>200x295mm (+3mm bleed)</t>
+          <t>200x105mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J411" t="inlineStr">
@@ -21838,7 +21843,7 @@
       </c>
       <c r="L411" t="inlineStr">
         <is>
-          <t>Periodicidade semanal (domingo); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -21860,17 +21865,17 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>Domingo</t>
+          <t>VIDAS</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>1/2 Página Dupla</t>
+          <t>1/4 Página</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>400x147mm (+3mm bleed)</t>
+          <t>100x147mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J412" t="inlineStr">
@@ -21880,7 +21885,7 @@
       </c>
       <c r="L412" t="inlineStr">
         <is>
-          <t>Periodicidade semanal (domingo); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -21902,17 +21907,17 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Domingo</t>
+          <t>VIDAS</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>1/2 Página Alto</t>
+          <t>Rodapé</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>100x295mm (+3mm bleed)</t>
+          <t>200x78mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J413" t="inlineStr">
@@ -21922,7 +21927,7 @@
       </c>
       <c r="L413" t="inlineStr">
         <is>
-          <t>Periodicidade semanal (domingo); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -21949,12 +21954,12 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>1/2 Página Baixo</t>
+          <t>Página Dupla</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>200x147mm (+3mm bleed)</t>
+          <t>400x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J414" t="inlineStr">
@@ -21991,12 +21996,12 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>1/3 Página Alto</t>
+          <t>Página</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>72x295mm (+3mm bleed)</t>
+          <t>200x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J415" t="inlineStr">
@@ -22033,12 +22038,12 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>1/3 Página Baixo</t>
+          <t>1/2 Página Dupla</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>200x105mm (+3mm bleed)</t>
+          <t>400x147mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J416" t="inlineStr">
@@ -22075,12 +22080,12 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>1/4 Página</t>
+          <t>1/2 Página Alto</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>100x147mm (+3mm bleed)</t>
+          <t>100x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J417" t="inlineStr">
@@ -22117,12 +22122,12 @@
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>Rodapé</t>
+          <t>1/2 Página Baixo</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>200x78mm (+3mm bleed)</t>
+          <t>200x147mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J418" t="inlineStr">
@@ -22149,32 +22154,32 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Destak</t>
+          <t>Correio da Manhã</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>Destak</t>
+          <t>Domingo</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>Capa Falsa</t>
+          <t>1/3 Página Alto</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>210x280mm | 230x300mm (corte)</t>
+          <t>72x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
       <c r="L419" t="inlineStr">
         <is>
-          <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Periodicidade semanal (domingo); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -22191,32 +22196,32 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Destak</t>
+          <t>Correio da Manhã</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>Destak</t>
+          <t>Domingo</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>Rodapé 1ª Página</t>
+          <t>1/3 Página Baixo</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>210x42mm</t>
+          <t>200x105mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J420" t="inlineStr">
         <is>
-          <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
       <c r="L420" t="inlineStr">
         <is>
-          <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Periodicidade semanal (domingo); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -22233,32 +22238,32 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Destak</t>
+          <t>Correio da Manhã</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>Destak</t>
+          <t>Domingo</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>Janela Premium</t>
+          <t>1/4 Página</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>49,5x78,5mm</t>
+          <t>100x147mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J421" t="inlineStr">
         <is>
-          <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
       <c r="L421" t="inlineStr">
         <is>
-          <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Periodicidade semanal (domingo); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -22275,32 +22280,32 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Destak</t>
+          <t>Correio da Manhã</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>Destak</t>
+          <t>Domingo</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>Página Dupla</t>
+          <t>Rodapé</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>440x280mm | 460x300mm (corte)</t>
+          <t>200x78mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
       <c r="L422" t="inlineStr">
         <is>
-          <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Periodicidade semanal (domingo); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -22327,7 +22332,7 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>Página</t>
+          <t>Capa Falsa</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
@@ -22369,12 +22374,12 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>Contracapa</t>
+          <t>Rodapé 1ª Página</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>210x280mm | 230x300mm (corte)</t>
+          <t>210x42mm</t>
         </is>
       </c>
       <c r="J424" t="inlineStr">
@@ -22411,12 +22416,12 @@
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>1/2 Página Alto</t>
+          <t>Janela Premium</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>103x280mm</t>
+          <t>49,5x78,5mm</t>
         </is>
       </c>
       <c r="J425" t="inlineStr">
@@ -22453,12 +22458,12 @@
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>1/2 Página Baixo</t>
+          <t>Página Dupla</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>210x138mm</t>
+          <t>440x280mm | 460x300mm (corte)</t>
         </is>
       </c>
       <c r="J426" t="inlineStr">
@@ -22495,12 +22500,12 @@
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>3/4 Página</t>
+          <t>Página</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>103x138mm</t>
+          <t>210x280mm | 230x300mm (corte)</t>
         </is>
       </c>
       <c r="J427" t="inlineStr">
@@ -22537,12 +22542,12 @@
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>Rodapé</t>
+          <t>Contracapa</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>210x42mm</t>
+          <t>210x280mm | 230x300mm (corte)</t>
         </is>
       </c>
       <c r="J428" t="inlineStr">
@@ -22569,32 +22574,32 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Jornal de Negócios</t>
+          <t>Destak</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>Jornal de Negócios</t>
+          <t>Destak</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>Página</t>
+          <t>1/2 Página Alto</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>257x320mm (80 módulos, 5 col. x 16 mód.)</t>
+          <t>103x280mm</t>
         </is>
       </c>
       <c r="J429" t="inlineStr">
         <is>
-          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+          <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
         </is>
       </c>
       <c r="L429" t="inlineStr">
         <is>
-          <t>Periodicidade diária (2ª feira a 6ª feira); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -22611,32 +22616,32 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Jornal de Negócios</t>
+          <t>Destak</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>Jornal de Negócios</t>
+          <t>Destak</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>Meia Página</t>
+          <t>1/2 Página Baixo</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>204x240mm (48 módulos, 4 col. x 12 mód.)</t>
+          <t>210x138mm</t>
         </is>
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+          <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
         </is>
       </c>
       <c r="L430" t="inlineStr">
         <is>
-          <t>Periodicidade diária (2ª feira a 6ª feira); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -22653,32 +22658,32 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Jornal de Negócios</t>
+          <t>Destak</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>Jornal de Negócios</t>
+          <t>Destak</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>1/2 Página Alto (3 Col.)</t>
+          <t>3/4 Página</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>153x320mm (48 módulos, 3 col. x 16 mód.)</t>
+          <t>103x138mm</t>
         </is>
       </c>
       <c r="J431" t="inlineStr">
         <is>
-          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+          <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
         </is>
       </c>
       <c r="L431" t="inlineStr">
         <is>
-          <t>Periodicidade diária (2ª feira a 6ª feira); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -22695,32 +22700,32 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Jornal de Negócios</t>
+          <t>Destak</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>Jornal de Negócios</t>
+          <t>Destak</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>1/3 Página Alto (2 Col.)</t>
+          <t>Rodapé</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>100x320mm (32 módulos, 2 col. x 16 mód.)</t>
+          <t>210x42mm</t>
         </is>
       </c>
       <c r="J432" t="inlineStr">
         <is>
-          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+          <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
         </is>
       </c>
       <c r="L432" t="inlineStr">
         <is>
-          <t>Periodicidade diária (2ª feira a 6ª feira); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -22747,12 +22752,12 @@
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>1/2 Página Baixo</t>
+          <t>Página</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>257x160mm (40 módulos, 5 col. x 8 mód.)</t>
+          <t>257x320mm (80 módulos, 5 col. x 16 mód.)</t>
         </is>
       </c>
       <c r="J433" t="inlineStr">
@@ -22789,12 +22794,12 @@
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>1/4 Página (3 Col.)</t>
+          <t>Meia Página</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>153x160mm (24 módulos, 3 col. x 8 mód.)</t>
+          <t>204x240mm (48 módulos, 4 col. x 12 mód.)</t>
         </is>
       </c>
       <c r="J434" t="inlineStr">
@@ -22831,12 +22836,12 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>1/4 Página (2 Col.)</t>
+          <t>1/2 Página Alto (3 Col.)</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>100x160mm (16 módulos, 2 col. x 8 mód.)</t>
+          <t>153x320mm (48 módulos, 3 col. x 16 mód.)</t>
         </is>
       </c>
       <c r="J435" t="inlineStr">
@@ -22873,12 +22878,12 @@
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>Rodapé</t>
+          <t>1/3 Página Alto (2 Col.)</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>257x61mm (15 módulos, 5 col. x 3 mód.)</t>
+          <t>100x320mm (32 módulos, 2 col. x 16 mód.)</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
@@ -22915,12 +22920,12 @@
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>Janela de Primeira Página</t>
+          <t>1/2 Página Baixo</t>
         </is>
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>55x96mm</t>
+          <t>257x160mm (40 módulos, 5 col. x 8 mód.)</t>
         </is>
       </c>
       <c r="J437" t="inlineStr">
@@ -22930,7 +22935,7 @@
       </c>
       <c r="L437" t="inlineStr">
         <is>
-          <t>Formato especial na 1ª página ou última página do 1º Caderno. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Periodicidade diária (2ª feira a 6ª feira); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -22957,12 +22962,12 @@
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>Orelha de Primeira Página</t>
+          <t>1/4 Página (3 Col.)</t>
         </is>
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>55x45mm</t>
+          <t>153x160mm (24 módulos, 3 col. x 8 mód.)</t>
         </is>
       </c>
       <c r="J438" t="inlineStr">
@@ -22972,7 +22977,7 @@
       </c>
       <c r="L438" t="inlineStr">
         <is>
-          <t>Formato especial na 1ª página ou última página do 1º Caderno. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Periodicidade diária (2ª feira a 6ª feira); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -22999,12 +23004,12 @@
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>Rodapé de Primeira Página</t>
+          <t>1/4 Página (2 Col.)</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>195x25mm</t>
+          <t>100x160mm (16 módulos, 2 col. x 8 mód.)</t>
         </is>
       </c>
       <c r="J439" t="inlineStr">
@@ -23014,7 +23019,7 @@
       </c>
       <c r="L439" t="inlineStr">
         <is>
-          <t>Formato especial na 1ª página ou última página do 1º Caderno. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Periodicidade diária (2ª feira a 6ª feira); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -23041,12 +23046,12 @@
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>Home Page (Quadrado 2ª Página)</t>
+          <t>Rodapé</t>
         </is>
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>150x130mm</t>
+          <t>257x61mm (15 módulos, 5 col. x 3 mód.)</t>
         </is>
       </c>
       <c r="J440" t="inlineStr">
@@ -23056,7 +23061,7 @@
       </c>
       <c r="L440" t="inlineStr">
         <is>
-          <t>Formato especial na 1ª página ou última página do 1º Caderno. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Periodicidade diária (2ª feira a 6ª feira); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -23083,12 +23088,12 @@
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>Rodapé Última Página</t>
+          <t>Janela de Primeira Página</t>
         </is>
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>205x61mm</t>
+          <t>55x96mm</t>
         </is>
       </c>
       <c r="J441" t="inlineStr">
@@ -23115,22 +23120,22 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Record</t>
+          <t>Jornal de Negócios</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>Record</t>
+          <t>Jornal de Negócios</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>Página</t>
+          <t>Orelha de Primeira Página</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>257x320mm (80 módulos, 5 col. x 16 mód.)</t>
+          <t>55x45mm</t>
         </is>
       </c>
       <c r="J442" t="inlineStr">
@@ -23140,7 +23145,7 @@
       </c>
       <c r="L442" t="inlineStr">
         <is>
-          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Formato especial na 1ª página ou última página do 1º Caderno. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -23157,22 +23162,22 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Record</t>
+          <t>Jornal de Negócios</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>Record</t>
+          <t>Jornal de Negócios</t>
         </is>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>Meia Página</t>
+          <t>Rodapé de Primeira Página</t>
         </is>
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>204x240mm (48 módulos, 4 col. x 12 mód.)</t>
+          <t>195x25mm</t>
         </is>
       </c>
       <c r="J443" t="inlineStr">
@@ -23182,7 +23187,7 @@
       </c>
       <c r="L443" t="inlineStr">
         <is>
-          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Formato especial na 1ª página ou última página do 1º Caderno. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -23199,22 +23204,22 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Record</t>
+          <t>Jornal de Negócios</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>Record</t>
+          <t>Jornal de Negócios</t>
         </is>
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>1/2 Página Alto (3 Col.)</t>
+          <t>Home Page (Quadrado 2ª Página)</t>
         </is>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>153x320mm (48 módulos, 3 col. x 16 mód.)</t>
+          <t>150x130mm</t>
         </is>
       </c>
       <c r="J444" t="inlineStr">
@@ -23224,7 +23229,7 @@
       </c>
       <c r="L444" t="inlineStr">
         <is>
-          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Formato especial na 1ª página ou última página do 1º Caderno. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -23241,22 +23246,22 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Record</t>
+          <t>Jornal de Negócios</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>Record</t>
+          <t>Jornal de Negócios</t>
         </is>
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>1/3 Página Alto (2 Col.)</t>
+          <t>Rodapé Última Página</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>100x320mm (32 módulos, 2 col. x 16 mód.)</t>
+          <t>205x61mm</t>
         </is>
       </c>
       <c r="J445" t="inlineStr">
@@ -23266,7 +23271,7 @@
       </c>
       <c r="L445" t="inlineStr">
         <is>
-          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Formato especial na 1ª página ou última página do 1º Caderno. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -23293,12 +23298,12 @@
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>1/2 Página Baixo</t>
+          <t>Página</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>257x160mm (40 módulos, 5 col. x 8 mód.)</t>
+          <t>257x320mm (80 módulos, 5 col. x 16 mód.)</t>
         </is>
       </c>
       <c r="J446" t="inlineStr">
@@ -23335,12 +23340,12 @@
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>1/4 Página (3 Col.)</t>
+          <t>Meia Página</t>
         </is>
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>153x160mm (24 módulos, 3 col. x 8 mód.)</t>
+          <t>204x240mm (48 módulos, 4 col. x 12 mód.)</t>
         </is>
       </c>
       <c r="J447" t="inlineStr">
@@ -23377,12 +23382,12 @@
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>1/4 Página (2 Col.)</t>
+          <t>1/2 Página Alto (3 Col.)</t>
         </is>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>100x160mm (16 módulos, 2 col. x 8 mód.)</t>
+          <t>153x320mm (48 módulos, 3 col. x 16 mód.)</t>
         </is>
       </c>
       <c r="J448" t="inlineStr">
@@ -23419,12 +23424,12 @@
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>Rodapé</t>
+          <t>1/3 Página Alto (2 Col.)</t>
         </is>
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>257x61mm (15 módulos, 5 col. x 3 mód.)</t>
+          <t>100x320mm (32 módulos, 2 col. x 16 mód.)</t>
         </is>
       </c>
       <c r="J449" t="inlineStr">
@@ -23451,22 +23456,22 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Sábado</t>
+          <t>Record</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>Sábado</t>
+          <t>Record</t>
         </is>
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>Página Dupla</t>
+          <t>1/2 Página Baixo</t>
         </is>
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>410x275mm (+3mm bleed)</t>
+          <t>257x160mm (40 módulos, 5 col. x 8 mód.)</t>
         </is>
       </c>
       <c r="J450" t="inlineStr">
@@ -23476,7 +23481,7 @@
       </c>
       <c r="L450" t="inlineStr">
         <is>
-          <t>Periodicidade semanal (5ª feira); distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -23493,22 +23498,22 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Sábado</t>
+          <t>Record</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>Sábado</t>
+          <t>Record</t>
         </is>
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>Página</t>
+          <t>1/4 Página (3 Col.)</t>
         </is>
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>205x275mm (+3mm bleed)</t>
+          <t>153x160mm (24 módulos, 3 col. x 8 mód.)</t>
         </is>
       </c>
       <c r="J451" t="inlineStr">
@@ -23518,7 +23523,7 @@
       </c>
       <c r="L451" t="inlineStr">
         <is>
-          <t>Periodicidade semanal (5ª feira); distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -23535,22 +23540,22 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Sábado</t>
+          <t>Record</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>Sábado</t>
+          <t>Record</t>
         </is>
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>1/2 Página Dupla</t>
+          <t>1/4 Página (2 Col.)</t>
         </is>
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>410x137mm (+3mm bleed)</t>
+          <t>100x160mm (16 módulos, 2 col. x 8 mód.)</t>
         </is>
       </c>
       <c r="J452" t="inlineStr">
@@ -23560,7 +23565,7 @@
       </c>
       <c r="L452" t="inlineStr">
         <is>
-          <t>Periodicidade semanal (5ª feira); distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -23577,22 +23582,22 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Sábado</t>
+          <t>Record</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>Sábado</t>
+          <t>Record</t>
         </is>
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>1/2 Página Alto</t>
+          <t>Rodapé</t>
         </is>
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>102x275mm (+3mm bleed)</t>
+          <t>257x61mm (15 módulos, 5 col. x 3 mód.)</t>
         </is>
       </c>
       <c r="J453" t="inlineStr">
@@ -23602,7 +23607,7 @@
       </c>
       <c r="L453" t="inlineStr">
         <is>
-          <t>Periodicidade semanal (5ª feira); distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -23629,12 +23634,12 @@
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>1/2 Página Baixo</t>
+          <t>Página Dupla</t>
         </is>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>205x137mm (+3mm bleed)</t>
+          <t>410x275mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J454" t="inlineStr">
@@ -23671,12 +23676,12 @@
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>1/3 Página Alto</t>
+          <t>Página</t>
         </is>
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>72x275mm (+3mm bleed)</t>
+          <t>205x275mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J455" t="inlineStr">
@@ -23713,12 +23718,12 @@
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>1/3 Página Baixo</t>
+          <t>1/2 Página Dupla</t>
         </is>
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>205x91mm (+3mm bleed)</t>
+          <t>410x137mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J456" t="inlineStr">
@@ -23750,17 +23755,17 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>Sábado Viajante</t>
+          <t>Sábado</t>
         </is>
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>Página Dupla</t>
+          <t>1/2 Página Alto</t>
         </is>
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>410x275mm (+3mm bleed)</t>
+          <t>102x275mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J457" t="inlineStr">
@@ -23770,7 +23775,7 @@
       </c>
       <c r="L457" t="inlineStr">
         <is>
-          <t>Periodicidade trimestral; distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Periodicidade semanal (5ª feira); distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -23792,17 +23797,17 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>Sábado Viajante</t>
+          <t>Sábado</t>
         </is>
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>Página</t>
+          <t>1/2 Página Baixo</t>
         </is>
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>205x275mm (+3mm bleed)</t>
+          <t>205x137mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J458" t="inlineStr">
@@ -23812,7 +23817,7 @@
       </c>
       <c r="L458" t="inlineStr">
         <is>
-          <t>Periodicidade trimestral; distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Periodicidade semanal (5ª feira); distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -23834,17 +23839,17 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>Sábado Viajante</t>
+          <t>Sábado</t>
         </is>
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>1/2 Página Dupla</t>
+          <t>1/3 Página Alto</t>
         </is>
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>410x137mm (+3mm bleed)</t>
+          <t>72x275mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J459" t="inlineStr">
@@ -23854,7 +23859,7 @@
       </c>
       <c r="L459" t="inlineStr">
         <is>
-          <t>Periodicidade trimestral; distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Periodicidade semanal (5ª feira); distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -23876,17 +23881,17 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>Sábado Viajante</t>
+          <t>Sábado</t>
         </is>
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>1/2 Página Alto</t>
+          <t>1/3 Página Baixo</t>
         </is>
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>102x275mm (+3mm bleed)</t>
+          <t>205x91mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J460" t="inlineStr">
@@ -23896,7 +23901,7 @@
       </c>
       <c r="L460" t="inlineStr">
         <is>
-          <t>Periodicidade trimestral; distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Periodicidade semanal (5ª feira); distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -23923,12 +23928,12 @@
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t>1/2 Página Baixo</t>
+          <t>Página Dupla</t>
         </is>
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>205x137mm (+3mm bleed)</t>
+          <t>410x275mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J461" t="inlineStr">
@@ -23965,12 +23970,12 @@
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>1/3 Página Alto</t>
+          <t>Página</t>
         </is>
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>72x275mm (+3mm bleed)</t>
+          <t>205x275mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J462" t="inlineStr">
@@ -24007,12 +24012,12 @@
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>1/3 Página Baixo</t>
+          <t>1/2 Página Dupla</t>
         </is>
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>205x91mm (+3mm bleed)</t>
+          <t>410x137mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J463" t="inlineStr">
@@ -24039,22 +24044,22 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>TV Guia</t>
+          <t>Sábado</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>TV Guia</t>
+          <t>Sábado Viajante</t>
         </is>
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>Página Dupla</t>
+          <t>1/2 Página Alto</t>
         </is>
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>400x295mm (+3mm bleed)</t>
+          <t>102x275mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J464" t="inlineStr">
@@ -24064,7 +24069,7 @@
       </c>
       <c r="L464" t="inlineStr">
         <is>
-          <t>Periodicidade semanal (6ª feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo LWC 57g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Periodicidade trimestral; distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -24081,22 +24086,22 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>TV Guia</t>
+          <t>Sábado</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>TV Guia</t>
+          <t>Sábado Viajante</t>
         </is>
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>Página</t>
+          <t>1/2 Página Baixo</t>
         </is>
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>200x295mm (+3mm bleed)</t>
+          <t>205x137mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J465" t="inlineStr">
@@ -24106,7 +24111,7 @@
       </c>
       <c r="L465" t="inlineStr">
         <is>
-          <t>Periodicidade semanal (6ª feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo LWC 57g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Periodicidade trimestral; distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -24123,22 +24128,22 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>TV Guia</t>
+          <t>Sábado</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>TV Guia</t>
+          <t>Sábado Viajante</t>
         </is>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>1/2 Página Dupla</t>
+          <t>1/3 Página Alto</t>
         </is>
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>400x147mm (+3mm bleed)</t>
+          <t>72x275mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J466" t="inlineStr">
@@ -24148,7 +24153,7 @@
       </c>
       <c r="L466" t="inlineStr">
         <is>
-          <t>Periodicidade semanal (6ª feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo LWC 57g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Periodicidade trimestral; distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -24165,22 +24170,22 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>TV Guia</t>
+          <t>Sábado</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>TV Guia</t>
+          <t>Sábado Viajante</t>
         </is>
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>1/2 Página Alto</t>
+          <t>1/3 Página Baixo</t>
         </is>
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>100x295mm (+3mm bleed)</t>
+          <t>205x91mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J467" t="inlineStr">
@@ -24190,7 +24195,7 @@
       </c>
       <c r="L467" t="inlineStr">
         <is>
-          <t>Periodicidade semanal (6ª feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo LWC 57g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Periodicidade trimestral; distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -24217,12 +24222,12 @@
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>1/2 Página Baixo</t>
+          <t>Página Dupla</t>
         </is>
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>200x147mm (+3mm bleed)</t>
+          <t>400x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J468" t="inlineStr">
@@ -24259,12 +24264,12 @@
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>1/3 Página Alto</t>
+          <t>Página</t>
         </is>
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>72x295mm (+3mm bleed)</t>
+          <t>200x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J469" t="inlineStr">
@@ -24301,12 +24306,12 @@
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>1/3 Página Baixo</t>
+          <t>1/2 Página Dupla</t>
         </is>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>200x105mm (+3mm bleed)</t>
+          <t>400x147mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J470" t="inlineStr">
@@ -24333,32 +24338,32 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Expresso</t>
+          <t>TV Guia</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>Expresso</t>
+          <t>TV Guia</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>Página Dupla</t>
+          <t>1/2 Página Alto</t>
         </is>
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>548x408mm</t>
+          <t>100x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J471" t="inlineStr">
         <is>
-          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
       <c r="L471" t="inlineStr">
         <is>
-          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Periodicidade semanal (6ª feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo LWC 57g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -24375,32 +24380,32 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Expresso</t>
+          <t>TV Guia</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>Expresso</t>
+          <t>TV Guia</t>
         </is>
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>Página</t>
+          <t>1/2 Página Baixo</t>
         </is>
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>264x408mm</t>
+          <t>200x147mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J472" t="inlineStr">
         <is>
-          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
       <c r="L472" t="inlineStr">
         <is>
-          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Periodicidade semanal (6ª feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo LWC 57g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -24417,32 +24422,32 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Expresso</t>
+          <t>TV Guia</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>Expresso</t>
+          <t>TV Guia</t>
         </is>
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>1/2 Página Baixo</t>
+          <t>1/3 Página Alto</t>
         </is>
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>264x201,8mm</t>
+          <t>72x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J473" t="inlineStr">
         <is>
-          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
       <c r="L473" t="inlineStr">
         <is>
-          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Periodicidade semanal (6ª feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo LWC 57g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -24459,32 +24464,32 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Expresso</t>
+          <t>TV Guia</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>Expresso</t>
+          <t>TV Guia</t>
         </is>
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>1/2 Página Alto</t>
+          <t>1/3 Página Baixo</t>
         </is>
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>130x408mm</t>
+          <t>200x105mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J474" t="inlineStr">
         <is>
-          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
       <c r="L474" t="inlineStr">
         <is>
-          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Periodicidade semanal (6ª feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo LWC 57g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -24511,12 +24516,12 @@
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>1/2 Página Dupla</t>
+          <t>Página Dupla</t>
         </is>
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>548x201,8mm</t>
+          <t>548x408mm</t>
         </is>
       </c>
       <c r="J475" t="inlineStr">
@@ -24553,12 +24558,12 @@
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>Júnior Page</t>
+          <t>Página</t>
         </is>
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>174,8x277mm</t>
+          <t>264x408mm</t>
         </is>
       </c>
       <c r="J476" t="inlineStr">
@@ -24595,12 +24600,12 @@
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>1/4 Página</t>
+          <t>1/2 Página Baixo</t>
         </is>
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>130x201,8mm</t>
+          <t>264x201,8mm</t>
         </is>
       </c>
       <c r="J477" t="inlineStr">
@@ -24637,12 +24642,12 @@
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>1/4 Página Landscape</t>
+          <t>1/2 Página Alto</t>
         </is>
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>264x92,2mm</t>
+          <t>130x408mm</t>
         </is>
       </c>
       <c r="J478" t="inlineStr">
@@ -24679,12 +24684,12 @@
       </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>1/8 Página</t>
+          <t>1/2 Página Dupla</t>
         </is>
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>130x101mm</t>
+          <t>548x201,8mm</t>
         </is>
       </c>
       <c r="J479" t="inlineStr">
@@ -24721,12 +24726,12 @@
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>Orelha de Capa</t>
+          <t>Júnior Page</t>
         </is>
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>450x60mm</t>
+          <t>174,8x277mm</t>
         </is>
       </c>
       <c r="J480" t="inlineStr">
@@ -24736,7 +24741,7 @@
       </c>
       <c r="L480" t="inlineStr">
         <is>
-          <t>Formato especial de capa do 1º Caderno. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -24763,12 +24768,12 @@
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>Sanca de Capa</t>
+          <t>1/4 Página</t>
         </is>
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>240x264mm</t>
+          <t>130x201,8mm</t>
         </is>
       </c>
       <c r="J481" t="inlineStr">
@@ -24778,7 +24783,7 @@
       </c>
       <c r="L481" t="inlineStr">
         <is>
-          <t>Formato especial de capa do 1º Caderno. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -24805,22 +24810,22 @@
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t>Saco Expresso</t>
+          <t>1/4 Página Landscape</t>
         </is>
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>450x360mm (área útil do cliente: 450x278mm)</t>
+          <t>264x92,2mm</t>
         </is>
       </c>
       <c r="J482" t="inlineStr">
         <is>
-          <t>PDF em alta definição (elementos de desenho em vetorial, imagens à parte + JPEG para visualização)</t>
+          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
       <c r="L482" t="inlineStr">
         <is>
-          <t>Saco em papel liso impresso a CMYK + 2 cores; a tarja com a informação é sempre na cor do Expresso (Pantone 315C).</t>
+          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -24842,17 +24847,17 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>Expresso Economia</t>
+          <t>Expresso</t>
         </is>
       </c>
       <c r="F483" t="inlineStr">
         <is>
-          <t>Página Dupla</t>
+          <t>1/8 Página</t>
         </is>
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>548x408mm</t>
+          <t>130x101mm</t>
         </is>
       </c>
       <c r="J483" t="inlineStr">
@@ -24884,17 +24889,17 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>Expresso Economia</t>
+          <t>Expresso</t>
         </is>
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t>Página</t>
+          <t>Orelha de Capa</t>
         </is>
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>264x408mm</t>
+          <t>450x60mm</t>
         </is>
       </c>
       <c r="J484" t="inlineStr">
@@ -24904,7 +24909,7 @@
       </c>
       <c r="L484" t="inlineStr">
         <is>
-          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Formato especial de capa do 1º Caderno. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -24926,17 +24931,17 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>Expresso Economia</t>
+          <t>Expresso</t>
         </is>
       </c>
       <c r="F485" t="inlineStr">
         <is>
-          <t>1/2 Página Baixo</t>
+          <t>Sanca de Capa</t>
         </is>
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>264x201,8mm</t>
+          <t>240x264mm</t>
         </is>
       </c>
       <c r="J485" t="inlineStr">
@@ -24946,7 +24951,7 @@
       </c>
       <c r="L485" t="inlineStr">
         <is>
-          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Formato especial de capa do 1º Caderno. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -24968,27 +24973,27 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>Expresso Economia</t>
+          <t>Expresso</t>
         </is>
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>1/2 Página Alto</t>
+          <t>Saco Expresso</t>
         </is>
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>130x408mm</t>
+          <t>450x360mm (área útil do cliente: 450x278mm)</t>
         </is>
       </c>
       <c r="J486" t="inlineStr">
         <is>
-          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
+          <t>PDF em alta definição (elementos de desenho em vetorial, imagens à parte + JPEG para visualização)</t>
         </is>
       </c>
       <c r="L486" t="inlineStr">
         <is>
-          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Saco em papel liso impresso a CMYK + 2 cores; a tarja com a informação é sempre na cor do Expresso (Pantone 315C).</t>
         </is>
       </c>
     </row>
@@ -25015,12 +25020,12 @@
       </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>1/2 Página Dupla</t>
+          <t>Página Dupla</t>
         </is>
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>548x201,8mm</t>
+          <t>548x408mm</t>
         </is>
       </c>
       <c r="J487" t="inlineStr">
@@ -25057,12 +25062,12 @@
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>Júnior Page</t>
+          <t>Página</t>
         </is>
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>174,8x277mm</t>
+          <t>264x408mm</t>
         </is>
       </c>
       <c r="J488" t="inlineStr">
@@ -25099,12 +25104,12 @@
       </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t>1/4 Página</t>
+          <t>1/2 Página Baixo</t>
         </is>
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>130x201,8mm</t>
+          <t>264x201,8mm</t>
         </is>
       </c>
       <c r="J489" t="inlineStr">
@@ -25141,12 +25146,12 @@
       </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t>1/4 Página Landscape</t>
+          <t>1/2 Página Alto</t>
         </is>
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>264x92,2mm</t>
+          <t>130x408mm</t>
         </is>
       </c>
       <c r="J490" t="inlineStr">
@@ -25183,12 +25188,12 @@
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>1/8 Página</t>
+          <t>1/2 Página Dupla</t>
         </is>
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>130x101mm</t>
+          <t>548x201,8mm</t>
         </is>
       </c>
       <c r="J491" t="inlineStr">
@@ -25225,12 +25230,12 @@
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>Orelha (Janela na Primeira Página)</t>
+          <t>Júnior Page</t>
         </is>
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>41x32mm</t>
+          <t>174,8x277mm</t>
         </is>
       </c>
       <c r="J492" t="inlineStr">
@@ -25267,12 +25272,12 @@
       </c>
       <c r="F493" t="inlineStr">
         <is>
-          <t>Orelha Grande (Janela na Primeira Página)</t>
+          <t>1/4 Página</t>
         </is>
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>41x87mm</t>
+          <t>130x201,8mm</t>
         </is>
       </c>
       <c r="J493" t="inlineStr">
@@ -25304,17 +25309,17 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>Revista E</t>
+          <t>Expresso Economia</t>
         </is>
       </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>Página Dupla</t>
+          <t>1/4 Página Landscape</t>
         </is>
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>530x337mm</t>
+          <t>264x92,2mm</t>
         </is>
       </c>
       <c r="J494" t="inlineStr">
@@ -25324,7 +25329,7 @@
       </c>
       <c r="L494" t="inlineStr">
         <is>
-          <t>Impressão offset quadricromia — papel jornal melhorado 55g, capa couché mate 130g, lombada colada; localização obrigatória: +30%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -25346,17 +25351,17 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>Revista E</t>
+          <t>Expresso Economia</t>
         </is>
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>Página</t>
+          <t>1/8 Página</t>
         </is>
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>265x337mm</t>
+          <t>130x101mm</t>
         </is>
       </c>
       <c r="J495" t="inlineStr">
@@ -25366,7 +25371,7 @@
       </c>
       <c r="L495" t="inlineStr">
         <is>
-          <t>Impressão offset quadricromia — papel jornal melhorado 55g, capa couché mate 130g, lombada colada; localização obrigatória: +30%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -25388,17 +25393,17 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>Revista E</t>
+          <t>Expresso Economia</t>
         </is>
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>1/2 Página Baixo</t>
+          <t>Orelha (Janela na Primeira Página)</t>
         </is>
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>265x167mm</t>
+          <t>41x32mm</t>
         </is>
       </c>
       <c r="J496" t="inlineStr">
@@ -25408,7 +25413,7 @@
       </c>
       <c r="L496" t="inlineStr">
         <is>
-          <t>Impressão offset quadricromia — papel jornal melhorado 55g, capa couché mate 130g, lombada colada; localização obrigatória: +30%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -25430,17 +25435,17 @@
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>Revista E</t>
+          <t>Expresso Economia</t>
         </is>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>1/2 Página Alto</t>
+          <t>Orelha Grande (Janela na Primeira Página)</t>
         </is>
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>130x337mm</t>
+          <t>41x87mm</t>
         </is>
       </c>
       <c r="J497" t="inlineStr">
@@ -25450,7 +25455,7 @@
       </c>
       <c r="L497" t="inlineStr">
         <is>
-          <t>Impressão offset quadricromia — papel jornal melhorado 55g, capa couché mate 130g, lombada colada; localização obrigatória: +30%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -25477,12 +25482,12 @@
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>1/3 Página Alto</t>
+          <t>Página Dupla</t>
         </is>
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>90x337mm</t>
+          <t>530x337mm</t>
         </is>
       </c>
       <c r="J498" t="inlineStr">
@@ -25519,12 +25524,12 @@
       </c>
       <c r="F499" t="inlineStr">
         <is>
-          <t>Rodapé</t>
+          <t>Página</t>
         </is>
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>265x108mm</t>
+          <t>265x337mm</t>
         </is>
       </c>
       <c r="J499" t="inlineStr">
@@ -25561,12 +25566,12 @@
       </c>
       <c r="F500" t="inlineStr">
         <is>
-          <t>1/4 Página</t>
+          <t>1/2 Página Baixo</t>
         </is>
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>115x147mm</t>
+          <t>265x167mm</t>
         </is>
       </c>
       <c r="J500" t="inlineStr">
@@ -25603,12 +25608,12 @@
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>1/6 Página</t>
+          <t>1/2 Página Alto</t>
         </is>
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>75x147mm</t>
+          <t>130x337mm</t>
         </is>
       </c>
       <c r="J501" t="inlineStr">
@@ -25645,12 +25650,12 @@
       </c>
       <c r="F502" t="inlineStr">
         <is>
-          <t>1/8 Página</t>
+          <t>1/3 Página Alto</t>
         </is>
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>115x71mm</t>
+          <t>90x337mm</t>
         </is>
       </c>
       <c r="J502" t="inlineStr">
@@ -25677,32 +25682,32 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Attitude</t>
+          <t>Expresso</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>Attitude</t>
+          <t>Revista E</t>
         </is>
       </c>
       <c r="F503" t="inlineStr">
         <is>
-          <t>Página (Par/Ímpar)</t>
+          <t>Rodapé</t>
         </is>
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>215x278mm (+3mm bleed)</t>
+          <t>265x108mm</t>
         </is>
       </c>
       <c r="J503" t="inlineStr">
         <is>
-          <t>PDF, EPS ou TIFF em alta resolução de 400 DPI (mínimo 300 DPI), CMYK, sem atribuição de perfil final</t>
+          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
       <c r="L503" t="inlineStr">
         <is>
-          <t>Periodicidade bimestral (janeiro, março, maio, julho, setembro, novembro); revista bilingue (português + inglês); distribuição em Portugal e mais 22 países; páginas duplas com desvio de 6mm ao centro (3mm para a esquerda e 3mm para a direita) para garantir o acerto central. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Impressão offset quadricromia — papel jornal melhorado 55g, capa couché mate 130g, lombada colada; localização obrigatória: +30%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -25719,32 +25724,32 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Attitude</t>
+          <t>Expresso</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>Attitude</t>
+          <t>Revista E</t>
         </is>
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>1/2 Página Vertical</t>
+          <t>1/4 Página</t>
         </is>
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>106,25x278mm (+3mm bleed)</t>
+          <t>115x147mm</t>
         </is>
       </c>
       <c r="J504" t="inlineStr">
         <is>
-          <t>PDF, EPS ou TIFF em alta resolução de 400 DPI (mínimo 300 DPI), CMYK, sem atribuição de perfil final</t>
+          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
       <c r="L504" t="inlineStr">
         <is>
-          <t>Periodicidade bimestral (janeiro, março, maio, julho, setembro, novembro); revista bilingue (português + inglês); distribuição em Portugal e mais 22 países; páginas duplas com desvio de 6mm ao centro (3mm para a esquerda e 3mm para a direita) para garantir o acerto central. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Impressão offset quadricromia — papel jornal melhorado 55g, capa couché mate 130g, lombada colada; localização obrigatória: +30%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -25761,32 +25766,32 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Attitude</t>
+          <t>Expresso</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>Attitude</t>
+          <t>Revista E</t>
         </is>
       </c>
       <c r="F505" t="inlineStr">
         <is>
-          <t>1/2 Página Horizontal</t>
+          <t>1/6 Página</t>
         </is>
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>215x143mm (+3mm bleed)</t>
+          <t>75x147mm</t>
         </is>
       </c>
       <c r="J505" t="inlineStr">
         <is>
-          <t>PDF, EPS ou TIFF em alta resolução de 400 DPI (mínimo 300 DPI), CMYK, sem atribuição de perfil final</t>
+          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
       <c r="L505" t="inlineStr">
         <is>
-          <t>Periodicidade bimestral (janeiro, março, maio, julho, setembro, novembro); revista bilingue (português + inglês); distribuição em Portugal e mais 22 países; páginas duplas com desvio de 6mm ao centro (3mm para a esquerda e 3mm para a direita) para garantir o acerto central. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Impressão offset quadricromia — papel jornal melhorado 55g, capa couché mate 130g, lombada colada; localização obrigatória: +30%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
@@ -25803,331 +25808,331 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Attitude</t>
+          <t>Expresso</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>Attitude</t>
+          <t>Revista E</t>
         </is>
       </c>
       <c r="F506" t="inlineStr">
         <is>
-          <t>Página Dupla</t>
+          <t>1/8 Página</t>
         </is>
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>430x278mm (+3mm bleed, +6mm massa central)</t>
+          <t>115x71mm</t>
         </is>
       </c>
       <c r="J506" t="inlineStr">
         <is>
-          <t>PDF, EPS ou TIFF em alta resolução de 400 DPI (mínimo 300 DPI), CMYK, sem atribuição de perfil final</t>
+          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
       <c r="L506" t="inlineStr">
         <is>
-          <t>Periodicidade bimestral (janeiro, março, maio, julho, setembro, novembro); revista bilingue (português + inglês); distribuição em Portugal e mais 22 países; páginas duplas com desvio de 6mm ao centro (3mm para a esquerda e 3mm para a direita) para garantir o acerto central. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
+          <t>Impressão offset quadricromia — papel jornal melhorado 55g, capa couché mate 130g, lombada colada; localização obrigatória: +30%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>TV</t>
+          <t>Imprensa</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>TV</t>
+          <t>Imprensa</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>TV</t>
+          <t>Attitude</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>TV</t>
+          <t>Attitude</t>
         </is>
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>Spot TV (SD — IMX50)</t>
+          <t>Página (Par/Ímpar)</t>
         </is>
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>720x576px, 25 fps</t>
-        </is>
-      </c>
-      <c r="H507" t="inlineStr">
-        <is>
-          <t>16:9</t>
+          <t>215x278mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J507" t="inlineStr">
         <is>
-          <t>MXF (OP-1a), codec IMX50, 50 Mb/s (CBR), croma 4:2:2, entrelaçado (Interlaced UFF, 16:9FHA), extensão .mxf</t>
+          <t>PDF, EPS ou TIFF em alta resolução de 400 DPI (mínimo 300 DPI), CMYK, sem atribuição de perfil final</t>
         </is>
       </c>
       <c r="L507" t="inlineStr">
         <is>
-          <t>Estrutura obrigatória do ficheiro: o conteúdo publicitário deve começar no primeiro frame de vídeo e terminar no último — pre-roll e post-roll de 0 frames, duração do ficheiro = duração do spot x 25 frames. Áudio: PCM, 2 canais (stereo), 24 bit, 48 KHz, peak level -3dB TP máx., loudness (integrado) -23 LUFS. Nomenclatura sugerida para o ficheiro: &lt;Pub ID&gt;_&lt;Nome do Spot&gt;_&lt;Duração&gt;.mxf (ex.: PUB-2015-000345_Fiat 500X Sport Edition_30.mxf) — não é obrigatória, mas recomendada sempre que possível. Entrega exclusivamente por utilizador registado através do Portal GoFastWay (www.gofastway.tv). Todos os ficheiros passam por controlo automático de qualidade (conformidade técnica com estas specs + análise subjetiva de vídeo e áudio); em caso de inconsistência, a GoFastWay pode pedir a entrega de um novo ficheiro corrigido.</t>
+          <t>Periodicidade bimestral (janeiro, março, maio, julho, setembro, novembro); revista bilingue (português + inglês); distribuição em Portugal e mais 22 países; páginas duplas com desvio de 6mm ao centro (3mm para a esquerda e 3mm para a direita) para garantir o acerto central. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>TV</t>
+          <t>Imprensa</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>TV</t>
+          <t>Imprensa</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>TV</t>
+          <t>Attitude</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>TV</t>
+          <t>Attitude</t>
         </is>
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>Spot TV (HD — XDCAM HD422)</t>
+          <t>1/2 Página Vertical</t>
         </is>
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>1920x1080px, 25 fps</t>
-        </is>
-      </c>
-      <c r="H508" t="inlineStr">
-        <is>
-          <t>16:9</t>
+          <t>106,25x278mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J508" t="inlineStr">
         <is>
-          <t>MXF (OP-1a), codec XDCAM HD422, 50 Mb/s mín. (CBR), croma 4:2:2, entrelaçado (Interlaced UFF), extensão .mxf</t>
+          <t>PDF, EPS ou TIFF em alta resolução de 400 DPI (mínimo 300 DPI), CMYK, sem atribuição de perfil final</t>
         </is>
       </c>
       <c r="L508" t="inlineStr">
         <is>
-          <t>Estrutura obrigatória do ficheiro: o conteúdo publicitário deve começar no primeiro frame de vídeo e terminar no último — pre-roll e post-roll de 0 frames, duração do ficheiro = duração do spot x 25 frames. Áudio: PCM, 2 canais (stereo), 24 bit, 48 KHz, peak level -3dB TP máx., loudness (integrado) -23 LUFS. Nomenclatura sugerida para o ficheiro: &lt;Pub ID&gt;_&lt;Nome do Spot&gt;_&lt;Duração&gt;.mxf (ex.: PUB-2015-000345_Fiat 500X Sport Edition_30.mxf) — não é obrigatória, mas recomendada sempre que possível. Entrega exclusivamente por utilizador registado através do Portal GoFastWay (www.gofastway.tv). Todos os ficheiros passam por controlo automático de qualidade (conformidade técnica com estas specs + análise subjetiva de vídeo e áudio); em caso de inconsistência, a GoFastWay pode pedir a entrega de um novo ficheiro corrigido.</t>
+          <t>Periodicidade bimestral (janeiro, março, maio, julho, setembro, novembro); revista bilingue (português + inglês); distribuição em Portugal e mais 22 países; páginas duplas com desvio de 6mm ao centro (3mm para a esquerda e 3mm para a direita) para garantir o acerto central. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>Rádio</t>
+          <t>Imprensa</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Rádio</t>
+          <t>Imprensa</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Rádio</t>
+          <t>Attitude</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>Rádio</t>
+          <t>Attitude</t>
         </is>
       </c>
       <c r="F509" t="inlineStr">
         <is>
-          <t>Spot Rádio</t>
+          <t>1/2 Página Horizontal</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>215x143mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J509" t="inlineStr">
         <is>
-          <t>MP3</t>
+          <t>PDF, EPS ou TIFF em alta resolução de 400 DPI (mínimo 300 DPI), CMYK, sem atribuição de perfil final</t>
         </is>
       </c>
       <c r="L509" t="inlineStr">
         <is>
-          <t>Não foi indicada nenhuma plataforma de distribuição nem rádio específica — specs genéricas de entrega, a confirmar sempre junto da rádio ou da central de meios antes de entregar. Áudio AAC, 2 canais (stereo) ou mono consoante o spot, 48 KHz, bit rate mínimo recomendado 320 kbps (CBR), loudness (integrado) -23 LUFS e peak level -3dB TP máx. — o mesmo padrão de loudness broadcast já usado para TV.</t>
+          <t>Periodicidade bimestral (janeiro, março, maio, julho, setembro, novembro); revista bilingue (português + inglês); distribuição em Portugal e mais 22 países; páginas duplas com desvio de 6mm ao centro (3mm para a esquerda e 3mm para a direita) para garantir o acerto central. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>Imprensa</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>Imprensa</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>MOP</t>
+          <t>Attitude</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>MOP</t>
+          <t>Attitude</t>
         </is>
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>4Plus</t>
+          <t>Página Dupla</t>
         </is>
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>Arte final: 394x140mm. Medida real: 4000x1500mm. Área visível: 3860x1360mm.</t>
+          <t>430x278mm (+3mm bleed, +6mm massa central)</t>
         </is>
       </c>
       <c r="J510" t="inlineStr">
         <is>
-          <t>PDF (qualidade de impressão), JPEG (visualização) e ficheiro editável</t>
+          <t>PDF, EPS ou TIFF em alta resolução de 400 DPI (mínimo 300 DPI), CMYK, sem atribuição de perfil final</t>
         </is>
       </c>
       <c r="L510" t="inlineStr">
         <is>
-          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Imagens a 100%, 150 DPI. Papel branco 150g; fita-cola (para unir as 2 laudas) 3M ref. 201E, 50mm; embalamento enrolado individualmente. Entrega até à sexta-feira anterior ao dia em que a campanha começa. Quantidades requeridas: +10% além da quantidade contratada. Aconselha-se que a produção seja sempre feita na Pinkplate (Parque Empresarial Primóvel - Ed. D1, Albarraque, 2635-395 Rio de Mouro; Tel. 21 9251800). Cartazes entregues à unidade e identificados. Envio via WeTransfer/Hightail/Dropbox ou FTP do cliente (com utilizador e password); CD/DVD sempre com prova de cor.</t>
+          <t>Periodicidade bimestral (janeiro, março, maio, julho, setembro, novembro); revista bilingue (português + inglês); distribuição em Portugal e mais 22 países; páginas duplas com desvio de 6mm ao centro (3mm para a esquerda e 3mm para a direita) para garantir o acerto central. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>TV</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>TV</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>MOP</t>
+          <t>TV</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>MOP</t>
+          <t>TV</t>
         </is>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>Flashes</t>
+          <t>Spot TV (SD — IMX50)</t>
         </is>
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>Arte final: 370x270mm + 5mm de bleed (frente e verso).</t>
+          <t>720x576px, 25 fps</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>16:9</t>
         </is>
       </c>
       <c r="J511" t="inlineStr">
         <is>
-          <t>PDF (qualidade de impressão), JPEG (visualização) e ficheiro editável</t>
+          <t>MXF (OP-1a), codec IMX50, 50 Mb/s (CBR), croma 4:2:2, entrelaçado (Interlaced UFF, 16:9FHA), extensão .mxf</t>
         </is>
       </c>
       <c r="L511" t="inlineStr">
         <is>
-          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Deve ser deixado 20mm no topo para o encaixe — esta área deve estar livre de informação relevante e ser um prolongamento do fundo (não deixar a branco, a menos que o fundo da criatividade o seja). Papel auto-extinguível ou PVC auto-extinguível (FLAMSTOP), 180g/m2, espessura máxima 0,8mm. Cartazes entregues já dobrados e com as duas faces coladas integralmente. Quantidades requeridas: +15% que o número de posições. Prazo de entrega: até 5 dias úteis antes do início da campanha.</t>
+          <t>Estrutura obrigatória do ficheiro: o conteúdo publicitário deve começar no primeiro frame de vídeo e terminar no último — pre-roll e post-roll de 0 frames, duração do ficheiro = duração do spot x 25 frames. Áudio: PCM, 2 canais (stereo), 24 bit, 48 KHz, peak level -3dB TP máx., loudness (integrado) -23 LUFS. Nomenclatura sugerida para o ficheiro: &lt;Pub ID&gt;_&lt;Nome do Spot&gt;_&lt;Duração&gt;.mxf (ex.: PUB-2015-000345_Fiat 500X Sport Edition_30.mxf) — não é obrigatória, mas recomendada sempre que possível. Entrega exclusivamente por utilizador registado através do Portal GoFastWay (www.gofastway.tv). Todos os ficheiros passam por controlo automático de qualidade (conformidade técnica com estas specs + análise subjetiva de vídeo e áudio); em caso de inconsistência, a GoFastWay pode pedir a entrega de um novo ficheiro corrigido.</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>TV</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>TV</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>MOP</t>
+          <t>TV</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>MOP</t>
+          <t>TV</t>
         </is>
       </c>
       <c r="F512" t="inlineStr">
         <is>
-          <t>Backlight 4x3</t>
+          <t>Spot TV (HD — XDCAM HD422)</t>
         </is>
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>Arte final: 403x300mm + 1mm de bleed.</t>
+          <t>1920x1080px, 25 fps</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>16:9</t>
         </is>
       </c>
       <c r="J512" t="inlineStr">
         <is>
-          <t>PDF (qualidade de impressão), JPEG (visualização) e ficheiro editável</t>
+          <t>MXF (OP-1a), codec XDCAM HD422, 50 Mb/s mín. (CBR), croma 4:2:2, entrelaçado (Interlaced UFF), extensão .mxf</t>
         </is>
       </c>
       <c r="L512" t="inlineStr">
         <is>
-          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Produção em tela backlight no formato pretendido, com duas possibilidades: lona rígida para campanhas anuais (reutilizável) ou tela flexível para campanhas de curta duração (não reutilizável); telas acabadas com uma nervura à volta para fixação e tensionamento nos painéis PRISMAFLEX. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica PRISMAFLEX (Av. Dom Vicente Afonso Valente, 61, 2625-207 Póvoa de Santa Iria; Tel. +351 210 119 500; geral@prismaflex.pt).</t>
+          <t>Estrutura obrigatória do ficheiro: o conteúdo publicitário deve começar no primeiro frame de vídeo e terminar no último — pre-roll e post-roll de 0 frames, duração do ficheiro = duração do spot x 25 frames. Áudio: PCM, 2 canais (stereo), 24 bit, 48 KHz, peak level -3dB TP máx., loudness (integrado) -23 LUFS. Nomenclatura sugerida para o ficheiro: &lt;Pub ID&gt;_&lt;Nome do Spot&gt;_&lt;Duração&gt;.mxf (ex.: PUB-2015-000345_Fiat 500X Sport Edition_30.mxf) — não é obrigatória, mas recomendada sempre que possível. Entrega exclusivamente por utilizador registado através do Portal GoFastWay (www.gofastway.tv). Todos os ficheiros passam por controlo automático de qualidade (conformidade técnica com estas specs + análise subjetiva de vídeo e áudio); em caso de inconsistência, a GoFastWay pode pedir a entrega de um novo ficheiro corrigido.</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>Rádio</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>Rádio</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>MOP</t>
+          <t>Rádio</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>MOP</t>
+          <t>Rádio</t>
         </is>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>Backlight 8x3</t>
-        </is>
-      </c>
-      <c r="G513" t="inlineStr">
-        <is>
-          <t>Arte final: 803x286mm + 1mm de bleed.</t>
+          <t>Spot Rádio</t>
         </is>
       </c>
       <c r="J513" t="inlineStr">
         <is>
-          <t>PDF (qualidade de impressão), JPEG (visualização) e ficheiro editável</t>
+          <t>MP3</t>
         </is>
       </c>
       <c r="L513" t="inlineStr">
         <is>
-          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Produção em tela backlight no formato pretendido, com duas possibilidades: lona rígida para campanhas anuais (reutilizável) ou tela flexível para campanhas de curta duração (não reutilizável); telas acabadas com uma nervura à volta para fixação e tensionamento nos painéis PRISMAFLEX. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica PRISMAFLEX (Av. Dom Vicente Afonso Valente, 61, 2625-207 Póvoa de Santa Iria; Tel. +351 210 119 500; geral@prismaflex.pt).</t>
+          <t>Não foi indicada nenhuma plataforma de distribuição nem rádio específica — specs genéricas de entrega, a confirmar sempre junto da rádio ou da central de meios antes de entregar. Áudio AAC, 2 canais (stereo) ou mono consoante o spot, 48 KHz, bit rate mínimo recomendado 320 kbps (CBR), loudness (integrado) -23 LUFS e peak level -3dB TP máx. — o mesmo padrão de loudness broadcast já usado para TV.</t>
         </is>
       </c>
     </row>
@@ -26154,12 +26159,12 @@
       </c>
       <c r="F514" t="inlineStr">
         <is>
-          <t>Backlight 10x5</t>
+          <t>4Plus</t>
         </is>
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>Arte final: 966x481mm + 1mm de bleed.</t>
+          <t>Arte final: 394x140mm. Medida real: 4000x1500mm. Área visível: 3860x1360mm.</t>
         </is>
       </c>
       <c r="J514" t="inlineStr">
@@ -26169,7 +26174,7 @@
       </c>
       <c r="L514" t="inlineStr">
         <is>
-          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Produção em tela backlight no formato pretendido, com duas possibilidades: lona rígida para campanhas anuais (reutilizável) ou tela flexível para campanhas de curta duração (não reutilizável); telas acabadas com uma nervura à volta para fixação e tensionamento nos painéis PRISMAFLEX. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica PRISMAFLEX (Av. Dom Vicente Afonso Valente, 61, 2625-207 Póvoa de Santa Iria; Tel. +351 210 119 500; geral@prismaflex.pt).</t>
+          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Imagens a 100%, 150 DPI. Papel branco 150g; fita-cola (para unir as 2 laudas) 3M ref. 201E, 50mm; embalamento enrolado individualmente. Entrega até à sexta-feira anterior ao dia em que a campanha começa. Quantidades requeridas: +10% além da quantidade contratada. Aconselha-se que a produção seja sempre feita na Pinkplate (Parque Empresarial Primóvel - Ed. D1, Albarraque, 2635-395 Rio de Mouro; Tel. 21 9251800). Cartazes entregues à unidade e identificados. Envio via WeTransfer/Hightail/Dropbox ou FTP do cliente (com utilizador e password); CD/DVD sempre com prova de cor.</t>
         </is>
       </c>
     </row>
@@ -26196,12 +26201,12 @@
       </c>
       <c r="F515" t="inlineStr">
         <is>
-          <t>Backlight 12x5</t>
+          <t>Flashes</t>
         </is>
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>Arte final: 1211x481mm + 1mm de bleed.</t>
+          <t>Arte final: 370x270mm + 5mm de bleed (frente e verso).</t>
         </is>
       </c>
       <c r="J515" t="inlineStr">
@@ -26211,7 +26216,7 @@
       </c>
       <c r="L515" t="inlineStr">
         <is>
-          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Produção em tela backlight no formato pretendido, com duas possibilidades: lona rígida para campanhas anuais (reutilizável) ou tela flexível para campanhas de curta duração (não reutilizável); telas acabadas com uma nervura à volta para fixação e tensionamento nos painéis PRISMAFLEX. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica PRISMAFLEX (Av. Dom Vicente Afonso Valente, 61, 2625-207 Póvoa de Santa Iria; Tel. +351 210 119 500; geral@prismaflex.pt).</t>
+          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Deve ser deixado 20mm no topo para o encaixe — esta área deve estar livre de informação relevante e ser um prolongamento do fundo (não deixar a branco, a menos que o fundo da criatividade o seja). Papel auto-extinguível ou PVC auto-extinguível (FLAMSTOP), 180g/m2, espessura máxima 0,8mm. Cartazes entregues já dobrados e com as duas faces coladas integralmente. Quantidades requeridas: +15% que o número de posições. Prazo de entrega: até 5 dias úteis antes do início da campanha.</t>
         </is>
       </c>
     </row>
@@ -26238,12 +26243,12 @@
       </c>
       <c r="F516" t="inlineStr">
         <is>
-          <t>Autocarro - Lateral Direita</t>
+          <t>Backlight 4x3</t>
         </is>
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>Arte final: 434x118mm + 3mm de bleed. Medida real: 2170x588mm. Área visível: 2150x568mm.</t>
+          <t>Arte final: 403x300mm + 1mm de bleed.</t>
         </is>
       </c>
       <c r="J516" t="inlineStr">
@@ -26253,7 +26258,7 @@
       </c>
       <c r="L516" t="inlineStr">
         <is>
-          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Material obrigatório: PPA 3,5mm | 650g (impressão direta). 2 folhas (corte vertical central), com colagem em sistema de encosto, usando fita-cola 3M ref. 8959 — também permitido em uma só folha no formato total. Prazo de entrega: até 2 dias úteis antes do início da campanha. Quantidades necessárias: +5% que o número de faces, e +5% por cada semana extra de afixação. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica Pinkplate (Parque Empresarial Primóvel - Ed. D1, Albarraque, 2635-395 Rio de Mouro; Tel. 21 9251800).</t>
+          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Produção em tela backlight no formato pretendido, com duas possibilidades: lona rígida para campanhas anuais (reutilizável) ou tela flexível para campanhas de curta duração (não reutilizável); telas acabadas com uma nervura à volta para fixação e tensionamento nos painéis PRISMAFLEX. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica PRISMAFLEX (Av. Dom Vicente Afonso Valente, 61, 2625-207 Póvoa de Santa Iria; Tel. +351 210 119 500; geral@prismaflex.pt).</t>
         </is>
       </c>
     </row>
@@ -26280,12 +26285,12 @@
       </c>
       <c r="F517" t="inlineStr">
         <is>
-          <t>Autocarro - Lateral Esquerda</t>
+          <t>Backlight 8x3</t>
         </is>
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>Arte final: 548x150mm + 3mm de bleed. Medida real: 2740x750mm. Área visível: 2720x730mm.</t>
+          <t>Arte final: 803x286mm + 1mm de bleed.</t>
         </is>
       </c>
       <c r="J517" t="inlineStr">
@@ -26295,7 +26300,7 @@
       </c>
       <c r="L517" t="inlineStr">
         <is>
-          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Material obrigatório: PPA 3,5mm | 650g (impressão direta). 2 folhas (corte vertical central), com colagem em sistema de encosto, usando fita-cola 3M ref. 8959 — também permitido em uma só folha no formato total. Prazo de entrega: até 2 dias úteis antes do início da campanha. Quantidades necessárias: +5% que o número de faces, e +5% por cada semana extra de afixação. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica Pinkplate (Parque Empresarial Primóvel - Ed. D1, Albarraque, 2635-395 Rio de Mouro; Tel. 21 9251800).</t>
+          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Produção em tela backlight no formato pretendido, com duas possibilidades: lona rígida para campanhas anuais (reutilizável) ou tela flexível para campanhas de curta duração (não reutilizável); telas acabadas com uma nervura à volta para fixação e tensionamento nos painéis PRISMAFLEX. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica PRISMAFLEX (Av. Dom Vicente Afonso Valente, 61, 2625-207 Póvoa de Santa Iria; Tel. +351 210 119 500; geral@prismaflex.pt).</t>
         </is>
       </c>
     </row>
@@ -26322,12 +26327,12 @@
       </c>
       <c r="F518" t="inlineStr">
         <is>
-          <t>Autocarro - Lateral Esquerda + Esquerda Especial</t>
+          <t>Backlight 10x5</t>
         </is>
       </c>
       <c r="G518" t="inlineStr">
         <is>
-          <t>Dimensões Lateral Esquerda — Arte final: 548x150mm + 3mm de bleed, Medida real: 2740x750mm, Área visível: 2720x730mm. Dimensões Esquerda Especial — Arte final: 434x118mm + 3mm de bleed, Medida real: 2170x588mm, Área visível: 2150x568mm.</t>
+          <t>Arte final: 966x481mm + 1mm de bleed.</t>
         </is>
       </c>
       <c r="J518" t="inlineStr">
@@ -26337,7 +26342,7 @@
       </c>
       <c r="L518" t="inlineStr">
         <is>
-          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Material obrigatório: PPA 3,5mm | 650g (impressão direta). 2 folhas (corte vertical central), com colagem em sistema de encosto, usando fita-cola 3M ref. 8959 — também permitido em uma só folha no formato total. Prazo de entrega: até 2 dias úteis antes do início da campanha. Quantidades necessárias: +5% que o número de faces, e +5% por cada semana extra de afixação. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica Pinkplate (Parque Empresarial Primóvel - Ed. D1, Albarraque, 2635-395 Rio de Mouro; Tel. 21 9251800).</t>
+          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Produção em tela backlight no formato pretendido, com duas possibilidades: lona rígida para campanhas anuais (reutilizável) ou tela flexível para campanhas de curta duração (não reutilizável); telas acabadas com uma nervura à volta para fixação e tensionamento nos painéis PRISMAFLEX. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica PRISMAFLEX (Av. Dom Vicente Afonso Valente, 61, 2625-207 Póvoa de Santa Iria; Tel. +351 210 119 500; geral@prismaflex.pt).</t>
         </is>
       </c>
     </row>
@@ -26364,12 +26369,12 @@
       </c>
       <c r="F519" t="inlineStr">
         <is>
-          <t>Autocarro - Retaguarda</t>
+          <t>Backlight 12x5</t>
         </is>
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>Arte final: 300x96mm + 1mm de bleed. Medida real: 1500x478mm. Área visível: 2150x568mm.</t>
+          <t>Arte final: 1211x481mm + 1mm de bleed.</t>
         </is>
       </c>
       <c r="J519" t="inlineStr">
@@ -26379,7 +26384,7 @@
       </c>
       <c r="L519" t="inlineStr">
         <is>
-          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Material obrigatório: PPA 3,5mm | 650g (impressão direta). 2 folhas (corte vertical central), com colagem em sistema de encosto, usando fita-cola 3M ref. 8959 — também permitido em uma só folha no formato total. Prazo de entrega: até 2 dias úteis antes do início da campanha. Quantidades necessárias: +5% que o número de faces, e +5% por cada semana extra de afixação. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica Pinkplate (Parque Empresarial Primóvel - Ed. D1, Albarraque, 2635-395 Rio de Mouro; Tel. 21 9251800).</t>
+          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Produção em tela backlight no formato pretendido, com duas possibilidades: lona rígida para campanhas anuais (reutilizável) ou tela flexível para campanhas de curta duração (não reutilizável); telas acabadas com uma nervura à volta para fixação e tensionamento nos painéis PRISMAFLEX. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica PRISMAFLEX (Av. Dom Vicente Afonso Valente, 61, 2625-207 Póvoa de Santa Iria; Tel. +351 210 119 500; geral@prismaflex.pt).</t>
         </is>
       </c>
     </row>
@@ -26406,27 +26411,22 @@
       </c>
       <c r="F520" t="inlineStr">
         <is>
-          <t>3 Ecrãs</t>
+          <t>Autocarro - Lateral Direita</t>
         </is>
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>1920x1080px.</t>
-        </is>
-      </c>
-      <c r="H520" t="inlineStr">
-        <is>
-          <t>16:9</t>
+          <t>Arte final: 434x118mm + 3mm de bleed. Medida real: 2170x588mm. Área visível: 2150x568mm.</t>
         </is>
       </c>
       <c r="J520" t="inlineStr">
         <is>
-          <t>Vídeo: MP4/MOV; Imagem: qualquer formato; Web: HTML/URL — codec H264</t>
+          <t>PDF (qualidade de impressão), JPEG (visualização) e ficheiro editável</t>
         </is>
       </c>
       <c r="L520" t="inlineStr">
         <is>
-          <t>Duração: 10 segundos (obrigatório). Bitrate máx. 6 Mbps. Framerate 30 frames/s. Tamanho máximo: 100MB. Existe uma separação real de 2,5cm (medida real) na junção entre os três ecrãs, que divide e corta a imagem total — deve ser tido em conta para evitar que frases ou elementos relevantes fiquem deformados (zonas de quebra).</t>
+          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Material obrigatório: PPA 3,5mm | 650g (impressão direta). 2 folhas (corte vertical central), com colagem em sistema de encosto, usando fita-cola 3M ref. 8959 — também permitido em uma só folha no formato total. Prazo de entrega: até 2 dias úteis antes do início da campanha. Quantidades necessárias: +5% que o número de faces, e +5% por cada semana extra de afixação. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica Pinkplate (Parque Empresarial Primóvel - Ed. D1, Albarraque, 2635-395 Rio de Mouro; Tel. 21 9251800).</t>
         </is>
       </c>
     </row>
@@ -26453,27 +26453,22 @@
       </c>
       <c r="F521" t="inlineStr">
         <is>
-          <t>4x3 Digital</t>
+          <t>Autocarro - Lateral Esquerda</t>
         </is>
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>1536x1152px (na proporção 4x3, até 3840x2880px).</t>
-        </is>
-      </c>
-      <c r="H521" t="inlineStr">
-        <is>
-          <t>4:3</t>
+          <t>Arte final: 548x150mm + 3mm de bleed. Medida real: 2740x750mm. Área visível: 2720x730mm.</t>
         </is>
       </c>
       <c r="J521" t="inlineStr">
         <is>
-          <t>Vídeo: MP4/MOV; Imagem: qualquer formato; Web: HTML/URL — codec H264</t>
+          <t>PDF (qualidade de impressão), JPEG (visualização) e ficheiro editável</t>
         </is>
       </c>
       <c r="L521" t="inlineStr">
         <is>
-          <t>Duração: 10 segundos. Bitrate máximo 6 Mbps. Framerate 30 frames/s. Tamanho máximo: 100MB. Compressão nativa.</t>
+          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Material obrigatório: PPA 3,5mm | 650g (impressão direta). 2 folhas (corte vertical central), com colagem em sistema de encosto, usando fita-cola 3M ref. 8959 — também permitido em uma só folha no formato total. Prazo de entrega: até 2 dias úteis antes do início da campanha. Quantidades necessárias: +5% que o número de faces, e +5% por cada semana extra de afixação. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica Pinkplate (Parque Empresarial Primóvel - Ed. D1, Albarraque, 2635-395 Rio de Mouro; Tel. 21 9251800).</t>
         </is>
       </c>
     </row>
@@ -26500,27 +26495,22 @@
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>Tomi PhotoFun</t>
+          <t>Autocarro - Lateral Esquerda + Esquerda Especial</t>
         </is>
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>1080x810px.</t>
-        </is>
-      </c>
-      <c r="H522" t="inlineStr">
-        <is>
-          <t>4:3</t>
+          <t>Dimensões Lateral Esquerda — Arte final: 548x150mm + 3mm de bleed, Medida real: 2740x750mm, Área visível: 2720x730mm. Dimensões Esquerda Especial — Arte final: 434x118mm + 3mm de bleed, Medida real: 2170x588mm, Área visível: 2150x568mm.</t>
         </is>
       </c>
       <c r="J522" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>PDF (qualidade de impressão), JPEG (visualização) e ficheiro editável</t>
         </is>
       </c>
       <c r="L522" t="inlineStr">
         <is>
-          <t>Profundidade de cor: 8 bits ou superior. Deve ter sempre um espaço vazio de conteúdo de 125x125px para o logótipo TOMI no canto da moldura. Por ser impossível tirar uma fotografia sem o efeito de espelho com uma câmara frontal, é sempre necessário o envio da moldura espelhada.</t>
+          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Material obrigatório: PPA 3,5mm | 650g (impressão direta). 2 folhas (corte vertical central), com colagem em sistema de encosto, usando fita-cola 3M ref. 8959 — também permitido em uma só folha no formato total. Prazo de entrega: até 2 dias úteis antes do início da campanha. Quantidades necessárias: +5% que o número de faces, e +5% por cada semana extra de afixação. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica Pinkplate (Parque Empresarial Primóvel - Ed. D1, Albarraque, 2635-395 Rio de Mouro; Tel. 21 9251800).</t>
         </is>
       </c>
     </row>
@@ -26547,27 +26537,22 @@
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>Tomi Sport TV</t>
+          <t>Autocarro - Retaguarda</t>
         </is>
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>1080x1920px.</t>
-        </is>
-      </c>
-      <c r="H523" t="inlineStr">
-        <is>
-          <t>9:16</t>
+          <t>Arte final: 300x96mm + 1mm de bleed. Medida real: 1500x478mm. Área visível: 2150x568mm.</t>
         </is>
       </c>
       <c r="J523" t="inlineStr">
         <is>
-          <t>MP4 (sem fundo), codec H264</t>
+          <t>PDF (qualidade de impressão), JPEG (visualização) e ficheiro editável</t>
         </is>
       </c>
       <c r="L523" t="inlineStr">
         <is>
-          <t>Duração: múltiplos de 5 segundos. Bitrate máximo 6 Mbps. Tamanho máximo: 100MB.</t>
+          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Material obrigatório: PPA 3,5mm | 650g (impressão direta). 2 folhas (corte vertical central), com colagem em sistema de encosto, usando fita-cola 3M ref. 8959 — também permitido em uma só folha no formato total. Prazo de entrega: até 2 dias úteis antes do início da campanha. Quantidades necessárias: +5% que o número de faces, e +5% por cada semana extra de afixação. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica Pinkplate (Parque Empresarial Primóvel - Ed. D1, Albarraque, 2635-395 Rio de Mouro; Tel. 21 9251800).</t>
         </is>
       </c>
     </row>
@@ -26594,12 +26579,17 @@
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>LED Galp</t>
+          <t>3 Ecrãs</t>
         </is>
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>840x336px.</t>
+          <t>1920x1080px.</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>16:9</t>
         </is>
       </c>
       <c r="J524" t="inlineStr">
@@ -26609,101 +26599,101 @@
       </c>
       <c r="L524" t="inlineStr">
         <is>
-          <t>Duração: 10 segundos (obrigatório). Bitrate máximo 6 Mbps. Framerate 30 frames/s. Tamanho máximo: 100MB.</t>
+          <t>Duração: 10 segundos (obrigatório). Bitrate máx. 6 Mbps. Framerate 30 frames/s. Tamanho máximo: 100MB. Existe uma separação real de 2,5cm (medida real) na junção entre os três ecrãs, que divide e corta a imagem total — deve ser tido em conta para evitar que frases ou elementos relevantes fiquem deformados (zonas de quebra).</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>TV</t>
+          <t>OOH</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>TV</t>
+          <t>OOH</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>TV</t>
+          <t>MOP</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>TV</t>
+          <t>MOP</t>
         </is>
       </c>
       <c r="F525" t="inlineStr">
         <is>
-          <t>Ecrã Fracionado / Split Screen</t>
+          <t>4x3 Digital</t>
         </is>
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>480x1080px (25% de um ecrã de 1920x1080px), 25 fps</t>
+          <t>1536x1152px (na proporção 4x3, até 3840x2880px).</t>
         </is>
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>16:9</t>
+          <t>4:3</t>
         </is>
       </c>
       <c r="J525" t="inlineStr">
         <is>
-          <t>QuickTime (.MOV), ProRes 4444 (com canal Alpha) ou ProRes 422 (sem Alpha), 1080i entrelaçado (Upper/odd Field First), 25 fps</t>
+          <t>Vídeo: MP4/MOV; Imagem: qualquer formato; Web: HTML/URL — codec H264</t>
         </is>
       </c>
       <c r="L525" t="inlineStr">
         <is>
-          <t>Conteúdo publicitário que ocupa no máximo 25% do ecrã, transmitido em simultâneo com programas de entretenimento, desporto e magazine. Duração 10″, com entrada e saída incluídas nesses 10″. Sem áudio. Tem de manter a palavra "PUBLICIDADE" com leitura garantida e dentro da Safe Area durante todo o tempo em que está no ar. Entra pela direita do ecrã na TVI e pela esquerda na CNN Portugal. Safe Area geral: 96px horizontais / 54px verticais a partir da margem; Title Safe Area: 192px horizontais / 108px verticais — nenhuma informação relevante deve ficar fora destas áreas.</t>
+          <t>Duração: 10 segundos. Bitrate máximo 6 Mbps. Framerate 30 frames/s. Tamanho máximo: 100MB. Compressão nativa.</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>TV</t>
+          <t>OOH</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>TV</t>
+          <t>OOH</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>TV</t>
+          <t>MOP</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>TV</t>
+          <t>MOP</t>
         </is>
       </c>
       <c r="F526" t="inlineStr">
         <is>
-          <t>Telepromoção</t>
+          <t>Tomi PhotoFun</t>
         </is>
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>1920x1080px (plasma de estúdio; a zona útil do plasma tem 220px de altura a partir da base do ecrã) e oráculo 1920x1080px</t>
+          <t>1080x810px.</t>
         </is>
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t>16:9</t>
+          <t>4:3</t>
         </is>
       </c>
       <c r="J526" t="inlineStr">
         <is>
-          <t>Imagens/grafismos: JPEG, PNG, PSD, AI/EPS (Illustrator versão CC), TIFF ou TGA, todos em resolução HD; ficheiros 3D: C4D (formato ideal), FBX ou OBJ. Vídeo: Formato de vídeo genérico (aplicável salvo indicação em contrário): wrapper MXF OP1a (.MXF), XDCAM HD 4:2:2, 1080i, 25 fps, entrelaçado (Upper/odd Field First), MPEG2 @ 50Mbps, perfil 4:2:2@HL, 1920x1080px, aspect ratio 16:9. Áudio: 8 canais @ 24 bits, PGM nos primeiros dois canais, 48.0 KHz, PCM não comprimido (.wav ou .aiff depois de desembrulhado), nível de referência -20dBFS, loudness -23 LUFS (EBU R.128).</t>
+          <t>PNG</t>
         </is>
       </c>
       <c r="L526" t="inlineStr">
         <is>
-          <t>Materiais a fornecer para produção de grafismos, ou grafismos já finalizados — usados no plasma existente no estúdio (para passar vídeos, fotografias ou grafismos) e/ou no oráculo. Devem ser enquadrados dentro das áreas de segurança indicadas para os logos e textos não correrem o risco de serem cortados ou distorcidos (Safe Area geral: 96px horizontais / 54px verticais a partir da margem; Title Safe Area: 192px horizontais / 108px verticais — nenhuma informação relevante deve ficar fora destas áreas. No plasma de estúdio, a zona útil começa a 220px da base do ecrã; no oráculo aplica-se a Title Safe Area). Os guiões para telepromoções de 60″ de duração devem ter entre 730 e 800 caracteres sem espaçamento. Fontes de letra em formato TT, para PC; referências de cor em RGB. Todos os materiais devem ser fornecidos com pelo menos uma semana de antecedência relativamente à data de realização da telepromoção, nos formatos indicados.</t>
+          <t>Profundidade de cor: 8 bits ou superior. Deve ter sempre um espaço vazio de conteúdo de 125x125px para o logótipo TOMI no canto da moldura. Por ser impossível tirar uma fotografia sem o efeito de espelho com uma câmara frontal, é sempre necessário o envio da moldura espelhada.</t>
         </is>
       </c>
     </row>
@@ -26720,22 +26710,37 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Clearspot</t>
+          <t>MOP</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>Clearspot</t>
+          <t>MOP</t>
         </is>
       </c>
       <c r="F527" t="inlineStr">
         <is>
-          <t>Especificações por confirmar</t>
+          <t>Tomi Sport TV</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>1080x1920px.</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>MP4 (sem fundo), codec H264</t>
         </is>
       </c>
       <c r="L527" t="inlineStr">
         <is>
-          <t>Concessionária adicionada à base para já sem formatos associados — as especificações técnicas de Clearspot ainda não foram fornecidas. Atualizar esta linha (e acrescentar as linhas de formato que fizerem falta) assim que a informação chegar.</t>
+          <t>Duração: múltiplos de 5 segundos. Bitrate máximo 6 Mbps. Tamanho máximo: 100MB.</t>
         </is>
       </c>
     </row>
@@ -26752,20 +26757,188 @@
       </c>
       <c r="C528" t="inlineStr">
         <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>LED Galp</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>840x336px.</t>
+        </is>
+      </c>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>Vídeo: MP4/MOV; Imagem: qualquer formato; Web: HTML/URL — codec H264</t>
+        </is>
+      </c>
+      <c r="L528" t="inlineStr">
+        <is>
+          <t>Duração: 10 segundos (obrigatório). Bitrate máximo 6 Mbps. Framerate 30 frames/s. Tamanho máximo: 100MB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>Ecrã Fracionado / Split Screen</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>480x1080px (25% de um ecrã de 1920x1080px), 25 fps</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>QuickTime (.MOV), ProRes 4444 (com canal Alpha) ou ProRes 422 (sem Alpha), 1080i entrelaçado (Upper/odd Field First), 25 fps</t>
+        </is>
+      </c>
+      <c r="L529" t="inlineStr">
+        <is>
+          <t>Conteúdo publicitário que ocupa no máximo 25% do ecrã, transmitido em simultâneo com programas de entretenimento, desporto e magazine. Duração 10″, com entrada e saída incluídas nesses 10″. Sem áudio. Tem de manter a palavra "PUBLICIDADE" com leitura garantida e dentro da Safe Area durante todo o tempo em que está no ar. Entra pela direita do ecrã na TVI e pela esquerda na CNN Portugal. Safe Area geral: 96px horizontais / 54px verticais a partir da margem; Title Safe Area: 192px horizontais / 108px verticais — nenhuma informação relevante deve ficar fora destas áreas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>Telepromoção</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>1920x1080px (plasma de estúdio; a zona útil do plasma tem 220px de altura a partir da base do ecrã) e oráculo 1920x1080px</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>Imagens/grafismos: JPEG, PNG, PSD, AI/EPS (Illustrator versão CC), TIFF ou TGA, todos em resolução HD; ficheiros 3D: C4D (formato ideal), FBX ou OBJ. Vídeo: Formato de vídeo genérico (aplicável salvo indicação em contrário): wrapper MXF OP1a (.MXF), XDCAM HD 4:2:2, 1080i, 25 fps, entrelaçado (Upper/odd Field First), MPEG2 @ 50Mbps, perfil 4:2:2@HL, 1920x1080px, aspect ratio 16:9. Áudio: 8 canais @ 24 bits, PGM nos primeiros dois canais, 48.0 KHz, PCM não comprimido (.wav ou .aiff depois de desembrulhado), nível de referência -20dBFS, loudness -23 LUFS (EBU R.128).</t>
+        </is>
+      </c>
+      <c r="L530" t="inlineStr">
+        <is>
+          <t>Materiais a fornecer para produção de grafismos, ou grafismos já finalizados — usados no plasma existente no estúdio (para passar vídeos, fotografias ou grafismos) e/ou no oráculo. Devem ser enquadrados dentro das áreas de segurança indicadas para os logos e textos não correrem o risco de serem cortados ou distorcidos (Safe Area geral: 96px horizontais / 54px verticais a partir da margem; Title Safe Area: 192px horizontais / 108px verticais — nenhuma informação relevante deve ficar fora destas áreas. No plasma de estúdio, a zona útil começa a 220px da base do ecrã; no oráculo aplica-se a Title Safe Area). Os guiões para telepromoções de 60″ de duração devem ter entre 730 e 800 caracteres sem espaçamento. Fontes de letra em formato TT, para PC; referências de cor em RGB. Todos os materiais devem ser fornecidos com pelo menos uma semana de antecedência relativamente à data de realização da telepromoção, nos formatos indicados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>Clearspot</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>Clearspot</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>Especificações por confirmar</t>
+        </is>
+      </c>
+      <c r="L531" t="inlineStr">
+        <is>
+          <t>Concessionária adicionada à base para já sem formatos associados — as especificações técnicas de Clearspot ainda não foram fornecidas. Atualizar esta linha (e acrescentar as linhas de formato que fizerem falta) assim que a informação chegar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
           <t>CS Outdoors</t>
         </is>
       </c>
-      <c r="D528" t="inlineStr">
+      <c r="D532" t="inlineStr">
         <is>
           <t>CS Outdoors</t>
         </is>
       </c>
-      <c r="F528" t="inlineStr">
+      <c r="F532" t="inlineStr">
         <is>
           <t>Especificações por confirmar</t>
         </is>
       </c>
-      <c r="L528" t="inlineStr">
+      <c r="L532" t="inlineStr">
         <is>
           <t>Concessionária adicionada à base para já sem formatos associados — as especificações técnicas de CS Outdoors ainda não foram fornecidas. Atualizar esta linha (e acrescentar as linhas de formato que fizerem falta) assim que a informação chegar.</t>
         </is>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M532"/>
+  <dimension ref="A1:M534"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="18.08984375" customWidth="1" style="2" min="1" max="1"/>
@@ -26944,6 +26944,100 @@
         </is>
       </c>
     </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>CINEMA</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>Cinema</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>VS2.0</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>VS2.0</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>Publicidade Cinema 2D</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>Formato de imagem preferencial: FLAT 1.85 — 1998x1080px.</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>1.85:1</t>
+        </is>
+      </c>
+      <c r="J533" t="inlineStr">
+        <is>
+          <t>Ficheiros DATA: sequência de ficheiros DPX 10-bit a 24fps, ou sequência de ficheiros TIFF em RGB. Ficheiros vídeo: QuickTime ProRes a 25fps ou 24fps, com áudio 5.1 ou 2.0 sincronizado à imagem.</t>
+        </is>
+      </c>
+      <c r="L533" t="inlineStr">
+        <is>
+          <t>Áudio: 6 canais (5.1) ou 2 canais (estéreo); ficheiros WAV a 24-bit; sampling 48KHz; nível de referência -20dBFS; velocidade 24fps. Masterização em Dolby Digital Cinema (VS2.0, certified partner). Dúvidas: bruno.figueiredo@vs2.pt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>CINEMA</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Cinema</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>VS2.0</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>VS2.0</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>Publicidade Cinema 3D</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>Formato de imagem: FLAT 1.85 — 1998x1080px, ou SCOPE 2.39 — 2048x858px (maior exploração do ecrã).</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>1.85:1 (FLAT) ou 2.39:1 (SCOPE)</t>
+        </is>
+      </c>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>Ficheiros DATA: dois ficheiros separados (Left eye + Right eye) em sequência, no formato TIFF RGB 16-bit data, ou ficheiros DPX 10-bit — ambos a 24fps.</t>
+        </is>
+      </c>
+      <c r="L534" t="inlineStr">
+        <is>
+          <t>Áudio: 6 canais (5.1) ou 2 canais (estéreo); ficheiros WAV a 24-bit; sampling 48KHz; nível de referência -20dBFS; velocidade 24fps. Masterização em Dolby Digital Cinema (VS2.0, certified partner). Dúvidas: bruno.figueiredo@vs2.pt.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M534"/>
+  <dimension ref="A1:M537"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="18.08984375" customWidth="1" style="2" min="1" max="1"/>
@@ -27038,6 +27038,132 @@
         </is>
       </c>
     </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>3D Lab</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>3D Lab</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>Grande Formato</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>Escala 1:10.</t>
+        </is>
+      </c>
+      <c r="J535" t="inlineStr">
+        <is>
+          <t>TIFF ou JPEG — aconselhável também o envio em PDF editável.</t>
+        </is>
+      </c>
+      <c r="L535" t="inlineStr">
+        <is>
+          <t>Cor: modo CMYK. Fontes convertidas em curvas (ficheiros vetoriais) ou fonte enviada junto com o ficheiro. Resolução: 450 dpi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>3D Lab</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>3D Lab</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>Rede Highway</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>10,15x5,15m. Escala 1:10.</t>
+        </is>
+      </c>
+      <c r="J536" t="inlineStr">
+        <is>
+          <t>TIFF ou JPEG — aconselhável também o envio em PDF editável.</t>
+        </is>
+      </c>
+      <c r="L536" t="inlineStr">
+        <is>
+          <t>Cor: modo CMYK. Fontes convertidas em curvas (ficheiros vetoriais) ou fonte enviada junto com o ficheiro. Resolução: 450 dpi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>3D Lab</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>3D Lab</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>Rede LED</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>Escala 1:10.</t>
+        </is>
+      </c>
+      <c r="J537" t="inlineStr">
+        <is>
+          <t>TIFF ou JPEG — aconselhável também o envio em PDF editável.</t>
+        </is>
+      </c>
+      <c r="L537" t="inlineStr">
+        <is>
+          <t>Cor: modo RGB. Fontes convertidas em curvas (ficheiros vetoriais) ou fonte enviada junto com o ficheiro. Resolução: 100 dpi.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M537"/>
+  <dimension ref="A1:M544"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="18.08984375" customWidth="1" style="2" min="1" max="1"/>
@@ -27164,6 +27164,310 @@
         </is>
       </c>
     </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>Unimidia</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>Unimidia</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>Mupi Digital | Universidades</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>Tamanho total: 1080x1920px. Área visível: 1080x1920px.</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>Máx. 10MB (vídeo produzido pelo cliente).</t>
+        </is>
+      </c>
+      <c r="J538" t="inlineStr">
+        <is>
+          <t>Produzido pela Unimidia (material por camadas): .psd, .ai ou .indd, fotografias/imagens com resolução superior a 150dpi, texto convertido em curvas — sujeito a apresentação de orçamento. Produzido pelo cliente (vídeo pronto): .avi, .mp4, .mov, .mpeg, .mpg ou .jpeg, resolução 1080x1920px, 25 frames por segundo, em formato vertical.</t>
+        </is>
+      </c>
+      <c r="L538" t="inlineStr">
+        <is>
+          <t>Duração máxima: 10 segundos. Criatividade tem de estar em português. A emissão do material só se inicia após validação da criatividade pela Unimidia. Data de entrega: 15 dias antes do início da campanha se produzido pela Unimidia (sujeito a orçamento), ou 2 dias úteis antes se produzido pelo cliente. Ficheiros enviados por email para universidades@unimidia.pt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>Spreading</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>Spreading</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>Táxi Açores - Lateral Direita</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>Cortante: 1650x750mm. Área visível variável consoante o ano/modelo da viatura.</t>
+        </is>
+      </c>
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>InDesign CS3, Illustrator CS3, Photoshop CS3 ou PDF. Ficheiros EPS ou TIFF.</t>
+        </is>
+      </c>
+      <c r="L539" t="inlineStr">
+        <is>
+          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido. Considerar uma margem de segurança sobre os limites visíveis, para evitar perda de informação vital.</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>Spreading</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>Spreading</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>Táxi Açores - Lateral Esquerda</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>Cortante: 1650x750mm. Área visível variável consoante o ano/modelo da viatura.</t>
+        </is>
+      </c>
+      <c r="J540" t="inlineStr">
+        <is>
+          <t>InDesign CS3, Illustrator CS3, Photoshop CS3 ou PDF. Ficheiros EPS ou TIFF.</t>
+        </is>
+      </c>
+      <c r="L540" t="inlineStr">
+        <is>
+          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido. Considerar uma margem de segurança sobre os limites visíveis, para evitar perda de informação vital.</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>Spreading</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>Spreading</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>Táxi Doorcover - Lateral Direita</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>Cortante: 2200x750mm. Área visível variável consoante o ano/modelo da viatura.</t>
+        </is>
+      </c>
+      <c r="J541" t="inlineStr">
+        <is>
+          <t>InDesign CS3, Illustrator CS3, Photoshop CS3 ou PDF. Ficheiros EPS ou TIFF.</t>
+        </is>
+      </c>
+      <c r="L541" t="inlineStr">
+        <is>
+          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido. Margem de segurança de 5 a 10cm sobre os limites visíveis; considerar a mesma margem junto aos puxadores das portas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>Spreading</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>Spreading</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>Táxi Doorcover - Lateral Esquerda</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>Cortante: 2200x750mm. Área visível variável consoante o ano/modelo da viatura.</t>
+        </is>
+      </c>
+      <c r="J542" t="inlineStr">
+        <is>
+          <t>InDesign CS3, Illustrator CS3, Photoshop CS3 ou PDF. Ficheiros EPS ou TIFF.</t>
+        </is>
+      </c>
+      <c r="L542" t="inlineStr">
+        <is>
+          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido. Margem de segurança de 5 a 10cm sobre os limites visíveis; considerar a mesma margem junto aos puxadores das portas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>Spreading</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>Spreading</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>Táxi Indoor - Flyer</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>Altura (sem margem): 20cm. Largura (sem margem): 10cm.</t>
+        </is>
+      </c>
+      <c r="J543" t="inlineStr">
+        <is>
+          <t>InDesign CS3, Illustrator CS3, Photoshop CS3 ou PDF. Ficheiros PDF, EPS ou TIFF.</t>
+        </is>
+      </c>
+      <c r="L543" t="inlineStr">
+        <is>
+          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>Spreading</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>Spreading</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>Táxi Indoor - Banner</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>Impressão: 34x12,6cm (largura x altura). Área visível: 37,5x15cm (largura x altura).</t>
+        </is>
+      </c>
+      <c r="J544" t="inlineStr">
+        <is>
+          <t>InDesign CS3, Illustrator CS3, Photoshop CS3 ou PDF. Ficheiros PDF, EPS ou TIFF.</t>
+        </is>
+      </c>
+      <c r="L544" t="inlineStr">
+        <is>
+          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M544"/>
+  <dimension ref="A1:M547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="18.08984375" customWidth="1" style="2" min="1" max="1"/>
@@ -27468,6 +27468,147 @@
         </is>
       </c>
     </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>Shine Care</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Shine Care</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>Mupi Digital</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>1080x1920px.</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
+      <c r="J545" t="inlineStr">
+        <is>
+          <t>MP4.</t>
+        </is>
+      </c>
+      <c r="L545" t="inlineStr">
+        <is>
+          <t>Duração: 10 segundos. Frame rate: 30 frames por segundo. Rede de mupis digitais em hospitais e clínicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>Media Play</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>Media Play</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>Ecrã Horizontal</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>1920x1080px.</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="J546" t="inlineStr">
+        <is>
+          <t>Vídeo: MP4, codec H.264, frame rate constante até 30fps, bitrate até 3000 Kbps (recomendado 1500-2500 Kbps para vídeo com imagem real; cerca de 600 Kbps para animações ou imagens estáticas), encoder profile Baseline ou Main, encoder level entre 3.0 e 4.2 (recomendado 3.2). Estático: JPEG (preferencial) ou PNG.</t>
+        </is>
+      </c>
+      <c r="L546" t="inlineStr">
+        <is>
+          <t>Duração do vídeo: 10 segundos. Aceite tanto criativo em vídeo (10 segundos) como criativo estático, consoante os materiais disponíveis do anunciante. Rede de publicidade digital em farmácias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>Media Play</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>Media Play</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>Ecrã Vertical</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>1080x1920px.</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
+      <c r="J547" t="inlineStr">
+        <is>
+          <t>Vídeo: MP4, codec H.264, frame rate constante até 30fps, bitrate até 3000 Kbps (recomendado 1500-2500 Kbps para vídeo com imagem real; cerca de 600 Kbps para animações ou imagens estáticas), encoder profile Baseline ou Main, encoder level entre 3.0 e 4.2 (recomendado 3.2). Estático: JPEG (preferencial) ou PNG.</t>
+        </is>
+      </c>
+      <c r="L547" t="inlineStr">
+        <is>
+          <t>Duração do vídeo: 10 segundos. Aceite tanto criativo em vídeo (10 segundos) como criativo estático, consoante os materiais disponíveis do anunciante. Rede de publicidade digital em farmácias.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -27177,7 +27177,7 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>Unimidia</t>
+          <t>Unimidia/Spreading</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
@@ -27229,7 +27229,7 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>Spreading</t>
+          <t>Unimidia/Spreading</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
@@ -27271,7 +27271,7 @@
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>Spreading</t>
+          <t>Unimidia/Spreading</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
@@ -27313,7 +27313,7 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Spreading</t>
+          <t>Unimidia/Spreading</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
@@ -27355,7 +27355,7 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Spreading</t>
+          <t>Unimidia/Spreading</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
@@ -27397,7 +27397,7 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Spreading</t>
+          <t>Unimidia/Spreading</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
@@ -27439,7 +27439,7 @@
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>Spreading</t>
+          <t>Unimidia/Spreading</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M547"/>
+  <dimension ref="A1:M550"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="18.08984375" customWidth="1" style="2" min="1" max="1"/>
@@ -27609,6 +27609,127 @@
         </is>
       </c>
     </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>Tequilha</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>Tequilha</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>Mupis Digitais</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>Mupi de pé (estrutura autónoma): 202cm de altura total, 73cm de largura. Ecrã de 50″, com 107cm de altura visível, posicionado a 83,5cm do chão; margens de 11cm (topo) e 7cm (laterais do ecrã).</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
+      <c r="J548" t="inlineStr">
+        <is>
+          <t>Conteúdo: 1080x1920px, MP4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>Tequilha</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>Tequilha</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>Mupis Tradicionais</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>80cm (largura) x 120cm (altura). Área total = área visível.</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>Tequilha</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>Tequilha</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>Ecrãs de Cinema Universidades</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>Ecrã de 50″.</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="J550" t="inlineStr">
+        <is>
+          <t>Conteúdo: 1920x1080px, MP4.</t>
+        </is>
+      </c>
+      <c r="L550" t="inlineStr">
+        <is>
+          <t>Estes ecrãs passam trailers de filmes; entre os trailers, passam spots de TV dos parceiros, incluindo a Tequilha.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -26957,12 +26957,12 @@
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>VS2.0</t>
+          <t>NOS Publicidade</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>VS2.0</t>
+          <t>NOS Publicidade</t>
         </is>
       </c>
       <c r="F533" t="inlineStr">
@@ -27004,12 +27004,12 @@
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>VS2.0</t>
+          <t>NOS Publicidade</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>VS2.0</t>
+          <t>NOS Publicidade</t>
         </is>
       </c>
       <c r="F534" t="inlineStr">

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M550"/>
+  <dimension ref="A1:M552"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="18.08984375" customWidth="1" style="2" min="1" max="1"/>
@@ -27730,6 +27730,90 @@
         </is>
       </c>
     </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>Unimidia/Spreading</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>Spreading</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>Táxi Doorcover Madeira - Lateral Direita</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>Escala 1/10. Área visível variável consoante o ano/modelo da viatura (táxis da Madeira).</t>
+        </is>
+      </c>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>InDesign CS3, Illustrator CS3, Photoshop CS3 ou PDF. Ficheiros EPS ou TIFF.</t>
+        </is>
+      </c>
+      <c r="L551" t="inlineStr">
+        <is>
+          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido. Margem de segurança de 5 a 10cm sobre os limites visíveis; considerar a mesma margem junto aos puxadores das portas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>Unimidia/Spreading</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>Spreading</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>Táxi Doorcover Madeira - Lateral Esquerda</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>Escala 1/10. Área visível variável consoante o ano/modelo da viatura (táxis da Madeira).</t>
+        </is>
+      </c>
+      <c r="J552" t="inlineStr">
+        <is>
+          <t>InDesign CS3, Illustrator CS3, Photoshop CS3 ou PDF. Ficheiros EPS ou TIFF.</t>
+        </is>
+      </c>
+      <c r="L552" t="inlineStr">
+        <is>
+          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido. Margem de segurança de 5 a 10cm sobre os limites visíveis; considerar a mesma margem junto aos puxadores das portas.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -13208,7 +13208,7 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>MP4, MOV (upload via YouTube)</t>
+          <t>MP4, MOV (enviar o link do vídeo carregado no canal de YouTube)</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
@@ -13265,7 +13265,7 @@
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>MP4, MOV (enviar o link do vídeo carregado no canal de YouTube)</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
@@ -13322,7 +13322,7 @@
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>MP4, MOV (enviar o link do vídeo carregado no canal de YouTube)</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
@@ -13379,7 +13379,7 @@
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>MP4, MOV (enviar o link do vídeo carregado no canal de YouTube)</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
@@ -13436,7 +13436,7 @@
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>MP4, MOV (enviar o link do vídeo carregado no canal de YouTube)</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>MP4, MOV (enviar o link do vídeo carregado no canal de YouTube)</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
@@ -13555,7 +13555,7 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>MP4, MOV (enviar o link do vídeo carregado no canal de YouTube)</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
@@ -13897,7 +13897,7 @@
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>MP4, MOV (enviar o link do vídeo carregado no canal de YouTube)</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
@@ -13954,7 +13954,7 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>MP4, MOV (upload via YouTube)</t>
+          <t>MP4, MOV (enviar o link do vídeo carregado no canal de YouTube)</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
@@ -14011,7 +14011,7 @@
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>MP4, MOV (upload via YouTube)</t>
+          <t>MP4, MOV (enviar o link do vídeo carregado no canal de YouTube)</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
@@ -14068,7 +14068,7 @@
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>MP4, MOV (enviar o link do vídeo carregado no canal de YouTube)</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
@@ -14125,7 +14125,7 @@
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>MP4, MOV (upload via YouTube)</t>
+          <t>MP4, MOV (enviar o link do vídeo carregado no canal de YouTube)</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
@@ -14182,7 +14182,7 @@
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>MP4, MOV (enviar o link do vídeo carregado no canal de YouTube)</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
@@ -14239,7 +14239,7 @@
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>MP4, MOV (enviar o link do vídeo carregado no canal de YouTube)</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
@@ -14752,7 +14752,7 @@
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>MP4, MOV (enviar o link do vídeo carregado no canal de YouTube)</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M552"/>
+  <dimension ref="A1:M554"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="18.08984375" customWidth="1" style="2" min="1" max="1"/>
@@ -27814,6 +27814,70 @@
         </is>
       </c>
     </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>Rádio</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Rádio</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>Rádio</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>Rádio</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>Live Copies</t>
+        </is>
+      </c>
+      <c r="L553" t="inlineStr">
+        <is>
+          <t>Briefing da campanha, fornecido pela agência, para a rádio produzir o guião de conversa entre os animadores (live read).</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>Rádio</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>Rádio</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>Rádio</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>Rádio</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>Referência</t>
+        </is>
+      </c>
+      <c r="L554" t="inlineStr">
+        <is>
+          <t>Frase de 5 segundos, com uma frase quase tipo slogan da marca.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -27842,7 +27842,7 @@
       </c>
       <c r="L553" t="inlineStr">
         <is>
-          <t>Briefing da campanha, fornecido pela agência, para a rádio produzir o guião de conversa entre os animadores (live read).</t>
+          <t>Formato de "live read": a agência não entrega um ficheiro de áudio pronto a emitir — entrega um briefing da campanha (conceito, mensagens-chave e tom de comunicação), e é a própria rádio quem escreve o guião e produz a conversa entre os animadores, lida em direto ou gravada com a voz da estação. Por não haver ficheiro de áudio a entregar, não tem Tipo de Ficheiro nem Peso — o que se entrega é o briefing escrito.</t>
         </is>
       </c>
     </row>
@@ -27874,7 +27874,7 @@
       </c>
       <c r="L554" t="inlineStr">
         <is>
-          <t>Frase de 5 segundos, com uma frase quase tipo slogan da marca.</t>
+          <t>Frase curta, com a duração de 5 segundos, com um texto quase ao estilo de um slogan da marca, lida pelos animadores da rádio em antena. Tal como o Live Copies, não é um ficheiro de áudio entregue pela agência — o que se fornece é o texto da frase, para a rádio gravar ou ler; por isso não tem Tipo de Ficheiro nem Peso.</t>
         </is>
       </c>
     </row>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -27842,7 +27842,7 @@
       </c>
       <c r="L553" t="inlineStr">
         <is>
-          <t>Formato de "live read": a agência não entrega um ficheiro de áudio pronto a emitir — entrega um briefing da campanha (conceito, mensagens-chave e tom de comunicação), e é a própria rádio quem escreve o guião e produz a conversa entre os animadores, lida em direto ou gravada com a voz da estação. Por não haver ficheiro de áudio a entregar, não tem Tipo de Ficheiro nem Peso — o que se entrega é o briefing escrito.</t>
+          <t>É necessário fornecer um briefing da campanha, incluindo o conceito, as mensagens-chave e o tom de comunicação. A partir desse briefing, a própria rádio desenvolve o guião e produz a conversa entre os animadores, que pode ser realizada em direto ou previamente gravada, sempre com as vozes da estação.</t>
         </is>
       </c>
     </row>
@@ -27874,7 +27874,7 @@
       </c>
       <c r="L554" t="inlineStr">
         <is>
-          <t>Frase curta, com a duração de 5 segundos, com um texto quase ao estilo de um slogan da marca, lida pelos animadores da rádio em antena. Tal como o Live Copies, não é um ficheiro de áudio entregue pela agência — o que se fornece é o texto da frase, para a rádio gravar ou ler; por isso não tem Tipo de Ficheiro nem Peso.</t>
+          <t>É necessário fornecer uma frase curta, com cerca de 5 segundos de duração e uma construção próxima de um slogan de marca, para ser lida em antena pelos animadores da rádio.</t>
         </is>
       </c>
     </row>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -26130,11 +26130,6 @@
           <t>MP3</t>
         </is>
       </c>
-      <c r="L513" t="inlineStr">
-        <is>
-          <t>Não foi indicada nenhuma plataforma de distribuição nem rádio específica — specs genéricas de entrega, a confirmar sempre junto da rádio ou da central de meios antes de entregar. Áudio AAC, 2 canais (stereo) ou mono consoante o spot, 48 KHz, bit rate mínimo recomendado 320 kbps (CBR), loudness (integrado) -23 LUFS e peak level -3dB TP máx. — o mesmo padrão de loudness broadcast já usado para TV.</t>
-        </is>
-      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M554"/>
+  <dimension ref="A1:M580"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="18.08984375" customWidth="1" style="2" min="1" max="1"/>
@@ -27873,6 +27873,1644 @@
         </is>
       </c>
     </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Conversacional</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="J555" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Mensagens + botões de resposta.</t>
+        </is>
+      </c>
+      <c r="L555" t="inlineStr">
+        <is>
+          <t>Chat / conversa simulada. Imagens necessárias: 0 (usa avatar do logo). Substituível por asset real: Avatar do chat (círculo) → foto/ícone da marca 96x96 PNG. Emoji 👋 → ícone próprio. Specs do asset: Avatar opcional (círculo, 96x96). Bolhas de chat geradas por CSS. Sem imagens de fundo. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="M555" t="inlineStr"/>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Audiências Game</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="J556" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>3 labels de audiência (ex: Jovens/Famílias/Profissionais) + enunciado.</t>
+        </is>
+      </c>
+      <c r="L556" t="inlineStr">
+        <is>
+          <t>Drag &amp; drop de mensagens para audiências. Imagens necessárias: 0–3 (ícones de audiência opcionais). Substituível por asset real: Emojis das audiências (👥) → ícones da marca 128x128 PNG transparente. Bins → cores da marca. Specs do asset: Ícones 1:1 PNG transparente 128x128 (opcional; caso contrário emoji). Bins e cartões gerados por CSS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="M556" t="inlineStr"/>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Scratch</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="J557" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Pergunta topo + mensagem revelada + CTA.</t>
+        </is>
+      </c>
+      <c r="L557" t="inlineStr">
+        <is>
+          <t>Raspadinha (scratch-to-reveal). Imagens necessárias: 1 imagem-prémio/revelação (recomendado). Substituível por asset real: Camada revelada → imagem real do cliente 300x300. Emojis ✨🔎 → ícones próprios. Specs do asset: Imagem de revelação 300x300 (JPG/PNG). Camada de raspar é CSS/canvas. Imagem por baixo é o asset do cliente. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="M557" t="inlineStr"/>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Slider Relevância</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="J558" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>2 labels extremos + enunciado + conclusão.</t>
+        </is>
+      </c>
+      <c r="L558" t="inlineStr">
+        <is>
+          <t>Slider comparativo (relevante vs genérico). Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícones/emojis dos extremos → ícones 96x96 PNG (opcional). Totalmente CSS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="M558" t="inlineStr"/>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Catch Sinais</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Enunciado + mensagem final.</t>
+        </is>
+      </c>
+      <c r="L559" t="inlineStr">
+        <is>
+          <t>Apanhar itens que caem (jogo). Imagens necessárias: 0–4 (ícones dos itens, opcional). Substituível por asset real: Itens que caem (emoji) → ícones 96x96 PNG transparente da marca. Specs do asset: Ícones 96x96 PNG transparente (opcional; senão emoji). Física/posições por JS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="M559" t="inlineStr"/>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Puzzle Logo</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="J560" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Instrução + mensagem final.</t>
+        </is>
+      </c>
+      <c r="L560" t="inlineStr">
+        <is>
+          <t>Puzzle de peças que monta o logótipo. Imagens necessárias: 1 logótipo (obrigatório). Substituível por asset real: Já usa imagem real (logótipo). Fundo das peças → cor/textura da marca (opcional). Specs do asset: Logótipo 240x240 PNG (fundo sólido ou transparente). A imagem é fatiada em peças por CSS. Entregar logo em alta resolução. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome).</t>
+        </is>
+      </c>
+      <c r="M560" t="inlineStr"/>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Ligações</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Instrução + mensagem final.</t>
+        </is>
+      </c>
+      <c r="L561" t="inlineStr">
+        <is>
+          <t>Jogo da memória (pares). Imagens necessárias: 0–6 (faces das cartas, opcional). Substituível por asset real: Faces das cartas (emoji) → imagens/ícones 128x128 (produtos, símbolos da marca). Specs do asset: Ícones/faces 128x128 (opcional; senão emoji). Cartas geradas por CSS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="M561" t="inlineStr"/>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Roda Havas</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>6 labels de segmento + enunciado + resultado.</t>
+        </is>
+      </c>
+      <c r="L562" t="inlineStr">
+        <is>
+          <t>Roda da sorte / estratégia. Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Emojis dos segmentos → ícones 64x64 PNG. Cores dos segmentos → paleta da marca. Segmentos e cores por CSS. Emojis por segmento. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="M562" t="inlineStr"/>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Hold Ligação</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="J563" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Instrução + mensagem ao completar.</t>
+        </is>
+      </c>
+      <c r="L563" t="inlineStr">
+        <is>
+          <t>Press-and-hold para carregar. Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícone central (emoji) → ícone/logo 96x96 PNG (opcional). Totalmente CSS/JS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="M563" t="inlineStr"/>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Swipe Briefing</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="J564" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>N afirmações (texto) + resultado.</t>
+        </is>
+      </c>
+      <c r="L564" t="inlineStr">
+        <is>
+          <t>Swipe cards (claro/vago). Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ilustrações das cartas → imagens 260x300 (opcional; senão CSS). Cartas por CSS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="M564" t="inlineStr"/>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Calculadora Contactos</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>Labels dos campos + enunciado + resultado.</t>
+        </is>
+      </c>
+      <c r="L565" t="inlineStr">
+        <is>
+          <t>Calculadora interativa. Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícones dos campos (emoji) → ícones 48x48 PNG (opcional). Inputs e cálculo por JS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="M565" t="inlineStr"/>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Tap Sinais</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="J566" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>Enunciado + mensagem final.</t>
+        </is>
+      </c>
+      <c r="L566" t="inlineStr">
+        <is>
+          <t>Tap rápido em alvos. Imagens necessárias: 0–4 (ícones-alvo, opcional). Substituível por asset real: Alvos (emoji) → ícones 96x96 PNG transparente da marca. Specs do asset: Ícones 96x96 PNG (opcional). Alvos por CSS/JS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="M566" t="inlineStr"/>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Procura na Estratégia</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="J567" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Enunciado + itens a encontrar (labels) + final.</t>
+        </is>
+      </c>
+      <c r="L567" t="inlineStr">
+        <is>
+          <t>Encontra itens (procura visual). Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Itens a encontrar (emoji) → ícones/mini-imagens 64x64 PNG. Grelha por CSS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="M567" t="inlineStr"/>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Método Havas</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="J568" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Instrução + mensagem final.</t>
+        </is>
+      </c>
+      <c r="L568" t="inlineStr">
+        <is>
+          <t>Simon (sequência de memória). Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Pads (cor) → cores da marca. Ícones por pad 64x64 PNG (opcional). Pads e sequência por JS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="M568" t="inlineStr"/>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Palavra</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="J569" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>Palavra-alvo + pista + mensagem final.</t>
+        </is>
+      </c>
+      <c r="L569" t="inlineStr">
+        <is>
+          <t>Anagrama / ordenar letras. Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícone/pista (emoji) → ícone 96x96 PNG (opcional). Letras por CSS. Definir palavra-chave da campanha. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="M569" t="inlineStr"/>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Da Marca à Pessoa</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="J570" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Labels do percurso + mensagem final.</t>
+        </is>
+      </c>
+      <c r="L570" t="inlineStr">
+        <is>
+          <t>Percurso animado marca→pessoa. Imagens necessárias: 0–1 (logótipo no início, opcional). Substituível por asset real: Início do percurso → logótipo 128x128. Fim → foto/ícone 'pessoa' 128x128 (opcional). Specs do asset: Logótipo 128x128 (opcional). Trajeto por CSS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="M570" t="inlineStr"/>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Slot Havas</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Enunciado + linha de prémio + resultado.</t>
+        </is>
+      </c>
+      <c r="L571" t="inlineStr">
+        <is>
+          <t>Slot machine (3 rolos). Imagens necessárias: 0–3 (símbolos dos rolos, opcional). Substituível por asset real: Símbolos dos rolos (emoji) → 3+ ícones 96x96 PNG transparente (produtos/marca). Specs do asset: Símbolos 96x96 PNG transparente (opcional; senão emoji). Rolos e símbolos por CSS/emoji. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="M571" t="inlineStr"/>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Verdade/Mito</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="J572" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>5 afirmações + feedback por afirmação + resultado.</t>
+        </is>
+      </c>
+      <c r="L572" t="inlineStr">
+        <is>
+          <t>Quiz verdadeiro/falso (5 afirmações). Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícone das cartas (emoji) → ícone 96x96 PNG (opcional). Verde/vermelho mantêm-se (funcional). Semáforo verde/vermelho é funcional (manter). Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="M572" t="inlineStr"/>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Diferenças</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="J573" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>Enunciado + mensagem final.</t>
+        </is>
+      </c>
+      <c r="L573" t="inlineStr">
+        <is>
+          <t>Descobre as diferenças. Imagens necessárias: 2 imagens (A e B) — obrigatório se usado. Substituível por asset real: Já usa 2 imagens reais. Cliente envia o par 300x300 (senão versão ilustrada). Specs do asset: 2 imagens 300x300 quase idênticas (JPG/PNG). Se sem imagens do cliente, usa versão ilustrada. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome).</t>
+        </is>
+      </c>
+      <c r="M573" t="inlineStr"/>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Enche o Mapa</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="J574" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Enunciado + label + mensagem final.</t>
+        </is>
+      </c>
+      <c r="L574" t="inlineStr">
+        <is>
+          <t>Preencher barra/mapa por toques. Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícone/label (emoji) → ícone 96x96 PNG (opcional). Barra por CSS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="M574" t="inlineStr"/>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Configurador</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="J575" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>6 labels de opção + enunciado + resumo.</t>
+        </is>
+      </c>
+      <c r="L575" t="inlineStr">
+        <is>
+          <t>Seletor de opções (configurar seleção). Imagens necessárias: 0–6 (ícones das opções, opcional). Substituível por asset real: Ícones das opções (emoji) → ícones 96x96 PNG transparente. Cores por opção → paleta da marca. Specs do asset: Ícones 96x96 (opcional; senão emoji). Cores por opção configuráveis. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="M575" t="inlineStr"/>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Countdown</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="J576" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Título + subtítulo + CTA.</t>
+        </is>
+      </c>
+      <c r="L576" t="inlineStr">
+        <is>
+          <t>Contagem decrescente para data-alvo. Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícone/fundo (emoji/CSS) → imagem de fundo 300x600 ou ícone 96x96 (opcional). Definir data-alvo por campanha (JS). Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="M576" t="inlineStr"/>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Estimativa</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="J577" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Pergunta + valor de referência + resultado.</t>
+        </is>
+      </c>
+      <c r="L577" t="inlineStr">
+        <is>
+          <t>Adivinha o número (slider). Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícone do enunciado (emoji) → ícone 96x96 PNG (opcional). Slider por CSS/JS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="M577" t="inlineStr"/>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Ranking</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="J578" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>4 itens (labels) + enunciado + confirmação.</t>
+        </is>
+      </c>
+      <c r="L578" t="inlineStr">
+        <is>
+          <t>Ordenar prioridades (drag). Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Emojis dos itens (🎯👥…) → ícones 48x48 PNG da marca (opcional). Itens arrastáveis por JS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="M578" t="inlineStr"/>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Carrossel Produtos</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="J579" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>Por slide: título + subtítulo + 3 bullets + CTA.</t>
+        </is>
+      </c>
+      <c r="L579" t="inlineStr">
+        <is>
+          <t>Carrossel de produtos/cards. Imagens necessárias: 1 por slide (recomendado 3–5). Substituível por asset real: Já usa imagens reais (1 por slide). Cliente envia 3–5 imagens 300x300. Specs do asset: Imagens de produto 300x300 (JPG/PNG), fundo neutro. Nº de slides configurável. Peso soma todas as imagens. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="M579" t="inlineStr"/>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Parallax</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="J580" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Título + subtítulo + CTA.</t>
+        </is>
+      </c>
+      <c r="L580" t="inlineStr">
+        <is>
+          <t>Cena com camadas parallax. Imagens necessárias: 1–4 camadas (opcional). Substituível por asset real: Camadas ilustradas (CSS) → 1–4 PNG transparentes 420x420 da marca (produto/cena). Specs do asset: Camadas PNG transparente 420x420 (opcional; senão ilustração). Auto-scroll ping-pong. Sem leitura de scroll do host. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="M580" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -27901,7 +27901,7 @@
       </c>
       <c r="F555" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Conversacional</t>
+          <t>Prog - Displ.AI+ - Conversacional</t>
         </is>
       </c>
       <c r="G555" t="inlineStr">
@@ -27934,7 +27934,6 @@
           <t>Chat / conversa simulada. Imagens necessárias: 0 (usa avatar do logo). Substituível por asset real: Avatar do chat (círculo) → foto/ícone da marca 96x96 PNG. Emoji 👋 → ícone próprio. Specs do asset: Avatar opcional (círculo, 96x96). Bolhas de chat geradas por CSS. Sem imagens de fundo. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
-      <c r="M555" t="inlineStr"/>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
@@ -27964,7 +27963,7 @@
       </c>
       <c r="F556" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Audiências Game</t>
+          <t>Prog - Displ.AI+ - Audiências Game</t>
         </is>
       </c>
       <c r="G556" t="inlineStr">
@@ -27997,7 +27996,6 @@
           <t>Drag &amp; drop de mensagens para audiências. Imagens necessárias: 0–3 (ícones de audiência opcionais). Substituível por asset real: Emojis das audiências (👥) → ícones da marca 128x128 PNG transparente. Bins → cores da marca. Specs do asset: Ícones 1:1 PNG transparente 128x128 (opcional; caso contrário emoji). Bins e cartões gerados por CSS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
-      <c r="M556" t="inlineStr"/>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
@@ -28027,7 +28025,7 @@
       </c>
       <c r="F557" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Scratch</t>
+          <t>Prog - Displ.AI+ - Scratch</t>
         </is>
       </c>
       <c r="G557" t="inlineStr">
@@ -28060,7 +28058,6 @@
           <t>Raspadinha (scratch-to-reveal). Imagens necessárias: 1 imagem-prémio/revelação (recomendado). Substituível por asset real: Camada revelada → imagem real do cliente 300x300. Emojis ✨🔎 → ícones próprios. Specs do asset: Imagem de revelação 300x300 (JPG/PNG). Camada de raspar é CSS/canvas. Imagem por baixo é o asset do cliente. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
-      <c r="M557" t="inlineStr"/>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
@@ -28090,7 +28087,7 @@
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Slider Relevância</t>
+          <t>Prog - Displ.AI+ - Slider Relevância</t>
         </is>
       </c>
       <c r="G558" t="inlineStr">
@@ -28123,7 +28120,6 @@
           <t>Slider comparativo (relevante vs genérico). Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícones/emojis dos extremos → ícones 96x96 PNG (opcional). Totalmente CSS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
-      <c r="M558" t="inlineStr"/>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
@@ -28153,7 +28149,7 @@
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Catch Sinais</t>
+          <t>Prog - Displ.AI+ - Catch Sinais</t>
         </is>
       </c>
       <c r="G559" t="inlineStr">
@@ -28186,7 +28182,6 @@
           <t>Apanhar itens que caem (jogo). Imagens necessárias: 0–4 (ícones dos itens, opcional). Substituível por asset real: Itens que caem (emoji) → ícones 96x96 PNG transparente da marca. Specs do asset: Ícones 96x96 PNG transparente (opcional; senão emoji). Física/posições por JS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
-      <c r="M559" t="inlineStr"/>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
@@ -28216,7 +28211,7 @@
       </c>
       <c r="F560" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Puzzle Logo</t>
+          <t>Prog - Displ.AI+ - Puzzle Logo</t>
         </is>
       </c>
       <c r="G560" t="inlineStr">
@@ -28249,7 +28244,6 @@
           <t>Puzzle de peças que monta o logótipo. Imagens necessárias: 1 logótipo (obrigatório). Substituível por asset real: Já usa imagem real (logótipo). Fundo das peças → cor/textura da marca (opcional). Specs do asset: Logótipo 240x240 PNG (fundo sólido ou transparente). A imagem é fatiada em peças por CSS. Entregar logo em alta resolução. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome).</t>
         </is>
       </c>
-      <c r="M560" t="inlineStr"/>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
@@ -28279,7 +28273,7 @@
       </c>
       <c r="F561" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Ligações</t>
+          <t>Prog - Displ.AI+ - Ligações</t>
         </is>
       </c>
       <c r="G561" t="inlineStr">
@@ -28312,7 +28306,6 @@
           <t>Jogo da memória (pares). Imagens necessárias: 0–6 (faces das cartas, opcional). Substituível por asset real: Faces das cartas (emoji) → imagens/ícones 128x128 (produtos, símbolos da marca). Specs do asset: Ícones/faces 128x128 (opcional; senão emoji). Cartas geradas por CSS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
-      <c r="M561" t="inlineStr"/>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
@@ -28342,7 +28335,7 @@
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Roda Havas</t>
+          <t>Prog - Displ.AI+ - Roda Havas</t>
         </is>
       </c>
       <c r="G562" t="inlineStr">
@@ -28375,7 +28368,6 @@
           <t>Roda da sorte / estratégia. Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Emojis dos segmentos → ícones 64x64 PNG. Cores dos segmentos → paleta da marca. Segmentos e cores por CSS. Emojis por segmento. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
-      <c r="M562" t="inlineStr"/>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
@@ -28405,7 +28397,7 @@
       </c>
       <c r="F563" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Hold Ligação</t>
+          <t>Prog - Displ.AI+ - Hold Ligação</t>
         </is>
       </c>
       <c r="G563" t="inlineStr">
@@ -28438,7 +28430,6 @@
           <t>Press-and-hold para carregar. Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícone central (emoji) → ícone/logo 96x96 PNG (opcional). Totalmente CSS/JS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
-      <c r="M563" t="inlineStr"/>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
@@ -28468,7 +28459,7 @@
       </c>
       <c r="F564" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Swipe Briefing</t>
+          <t>Prog - Displ.AI+ - Swipe Briefing</t>
         </is>
       </c>
       <c r="G564" t="inlineStr">
@@ -28501,7 +28492,6 @@
           <t>Swipe cards (claro/vago). Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ilustrações das cartas → imagens 260x300 (opcional; senão CSS). Cartas por CSS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
-      <c r="M564" t="inlineStr"/>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
@@ -28531,7 +28521,7 @@
       </c>
       <c r="F565" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Calculadora Contactos</t>
+          <t>Prog - Displ.AI+ - Calculadora Contactos</t>
         </is>
       </c>
       <c r="G565" t="inlineStr">
@@ -28564,7 +28554,6 @@
           <t>Calculadora interativa. Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícones dos campos (emoji) → ícones 48x48 PNG (opcional). Inputs e cálculo por JS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
-      <c r="M565" t="inlineStr"/>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
@@ -28594,7 +28583,7 @@
       </c>
       <c r="F566" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Tap Sinais</t>
+          <t>Prog - Displ.AI+ - Tap Sinais</t>
         </is>
       </c>
       <c r="G566" t="inlineStr">
@@ -28627,7 +28616,6 @@
           <t>Tap rápido em alvos. Imagens necessárias: 0–4 (ícones-alvo, opcional). Substituível por asset real: Alvos (emoji) → ícones 96x96 PNG transparente da marca. Specs do asset: Ícones 96x96 PNG (opcional). Alvos por CSS/JS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
-      <c r="M566" t="inlineStr"/>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
@@ -28657,7 +28645,7 @@
       </c>
       <c r="F567" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Procura na Estratégia</t>
+          <t>Prog - Displ.AI+ - Procura na Estratégia</t>
         </is>
       </c>
       <c r="G567" t="inlineStr">
@@ -28690,7 +28678,6 @@
           <t>Encontra itens (procura visual). Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Itens a encontrar (emoji) → ícones/mini-imagens 64x64 PNG. Grelha por CSS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
-      <c r="M567" t="inlineStr"/>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
@@ -28720,7 +28707,7 @@
       </c>
       <c r="F568" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Método Havas</t>
+          <t>Prog - Displ.AI+ - Método Havas</t>
         </is>
       </c>
       <c r="G568" t="inlineStr">
@@ -28753,7 +28740,6 @@
           <t>Simon (sequência de memória). Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Pads (cor) → cores da marca. Ícones por pad 64x64 PNG (opcional). Pads e sequência por JS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
-      <c r="M568" t="inlineStr"/>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
@@ -28783,7 +28769,7 @@
       </c>
       <c r="F569" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Palavra</t>
+          <t>Prog - Displ.AI+ - Palavra</t>
         </is>
       </c>
       <c r="G569" t="inlineStr">
@@ -28816,7 +28802,6 @@
           <t>Anagrama / ordenar letras. Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícone/pista (emoji) → ícone 96x96 PNG (opcional). Letras por CSS. Definir palavra-chave da campanha. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
-      <c r="M569" t="inlineStr"/>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
@@ -28846,7 +28831,7 @@
       </c>
       <c r="F570" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Da Marca à Pessoa</t>
+          <t>Prog - Displ.AI+ - Da Marca à Pessoa</t>
         </is>
       </c>
       <c r="G570" t="inlineStr">
@@ -28879,7 +28864,6 @@
           <t>Percurso animado marca→pessoa. Imagens necessárias: 0–1 (logótipo no início, opcional). Substituível por asset real: Início do percurso → logótipo 128x128. Fim → foto/ícone 'pessoa' 128x128 (opcional). Specs do asset: Logótipo 128x128 (opcional). Trajeto por CSS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
-      <c r="M570" t="inlineStr"/>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
@@ -28909,7 +28893,7 @@
       </c>
       <c r="F571" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Slot Havas</t>
+          <t>Prog - Displ.AI+ - Slot Havas</t>
         </is>
       </c>
       <c r="G571" t="inlineStr">
@@ -28942,7 +28926,6 @@
           <t>Slot machine (3 rolos). Imagens necessárias: 0–3 (símbolos dos rolos, opcional). Substituível por asset real: Símbolos dos rolos (emoji) → 3+ ícones 96x96 PNG transparente (produtos/marca). Specs do asset: Símbolos 96x96 PNG transparente (opcional; senão emoji). Rolos e símbolos por CSS/emoji. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
-      <c r="M571" t="inlineStr"/>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
@@ -28972,7 +28955,7 @@
       </c>
       <c r="F572" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Verdade/Mito</t>
+          <t>Prog - Displ.AI+ - Verdade/Mito</t>
         </is>
       </c>
       <c r="G572" t="inlineStr">
@@ -29005,7 +28988,6 @@
           <t>Quiz verdadeiro/falso (5 afirmações). Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícone das cartas (emoji) → ícone 96x96 PNG (opcional). Verde/vermelho mantêm-se (funcional). Semáforo verde/vermelho é funcional (manter). Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
-      <c r="M572" t="inlineStr"/>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
@@ -29035,7 +29017,7 @@
       </c>
       <c r="F573" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Diferenças</t>
+          <t>Prog - Displ.AI+ - Diferenças</t>
         </is>
       </c>
       <c r="G573" t="inlineStr">
@@ -29068,7 +29050,6 @@
           <t>Descobre as diferenças. Imagens necessárias: 2 imagens (A e B) — obrigatório se usado. Substituível por asset real: Já usa 2 imagens reais. Cliente envia o par 300x300 (senão versão ilustrada). Specs do asset: 2 imagens 300x300 quase idênticas (JPG/PNG). Se sem imagens do cliente, usa versão ilustrada. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome).</t>
         </is>
       </c>
-      <c r="M573" t="inlineStr"/>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
@@ -29098,7 +29079,7 @@
       </c>
       <c r="F574" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Enche o Mapa</t>
+          <t>Prog - Displ.AI+ - Enche o Mapa</t>
         </is>
       </c>
       <c r="G574" t="inlineStr">
@@ -29131,7 +29112,6 @@
           <t>Preencher barra/mapa por toques. Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícone/label (emoji) → ícone 96x96 PNG (opcional). Barra por CSS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
-      <c r="M574" t="inlineStr"/>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
@@ -29161,7 +29141,7 @@
       </c>
       <c r="F575" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Configurador</t>
+          <t>Prog - Displ.AI+ - Configurador</t>
         </is>
       </c>
       <c r="G575" t="inlineStr">
@@ -29194,7 +29174,6 @@
           <t>Seletor de opções (configurar seleção). Imagens necessárias: 0–6 (ícones das opções, opcional). Substituível por asset real: Ícones das opções (emoji) → ícones 96x96 PNG transparente. Cores por opção → paleta da marca. Specs do asset: Ícones 96x96 (opcional; senão emoji). Cores por opção configuráveis. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
-      <c r="M575" t="inlineStr"/>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
@@ -29224,7 +29203,7 @@
       </c>
       <c r="F576" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Countdown</t>
+          <t>Prog - Displ.AI+ - Countdown</t>
         </is>
       </c>
       <c r="G576" t="inlineStr">
@@ -29257,7 +29236,6 @@
           <t>Contagem decrescente para data-alvo. Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícone/fundo (emoji/CSS) → imagem de fundo 300x600 ou ícone 96x96 (opcional). Definir data-alvo por campanha (JS). Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
-      <c r="M576" t="inlineStr"/>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
@@ -29287,7 +29265,7 @@
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Estimativa</t>
+          <t>Prog - Displ.AI+ - Estimativa</t>
         </is>
       </c>
       <c r="G577" t="inlineStr">
@@ -29320,7 +29298,6 @@
           <t>Adivinha o número (slider). Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícone do enunciado (emoji) → ícone 96x96 PNG (opcional). Slider por CSS/JS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
-      <c r="M577" t="inlineStr"/>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
@@ -29350,7 +29327,7 @@
       </c>
       <c r="F578" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Ranking</t>
+          <t>Prog - Displ.AI+ - Ranking</t>
         </is>
       </c>
       <c r="G578" t="inlineStr">
@@ -29383,7 +29360,6 @@
           <t>Ordenar prioridades (drag). Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Emojis dos itens (🎯👥…) → ícones 48x48 PNG da marca (opcional). Itens arrastáveis por JS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
-      <c r="M578" t="inlineStr"/>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
@@ -29413,7 +29389,7 @@
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Carrossel Produtos</t>
+          <t>Prog - Displ.AI+ - Carrossel Produtos</t>
         </is>
       </c>
       <c r="G579" t="inlineStr">
@@ -29446,7 +29422,6 @@
           <t>Carrossel de produtos/cards. Imagens necessárias: 1 por slide (recomendado 3–5). Substituível por asset real: Já usa imagens reais (1 por slide). Cliente envia 3–5 imagens 300x300. Specs do asset: Imagens de produto 300x300 (JPG/PNG), fundo neutro. Nº de slides configurável. Peso soma todas as imagens. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
-      <c r="M579" t="inlineStr"/>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
@@ -29476,7 +29451,7 @@
       </c>
       <c r="F580" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Parallax</t>
+          <t>Prog - Displ.AI+ - Parallax</t>
         </is>
       </c>
       <c r="G580" t="inlineStr">
@@ -29509,7 +29484,6 @@
           <t>Cena com camadas parallax. Imagens necessárias: 1–4 camadas (opcional). Substituível por asset real: Camadas ilustradas (CSS) → 1–4 PNG transparentes 420x420 da marca (produto/cena). Specs do asset: Camadas PNG transparente 420x420 (opcional; senão ilustração). Auto-scroll ping-pong. Sem leitura de scroll do host. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
-      <c r="M580" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Base Formatos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Base Formatos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -65,7 +65,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -78,6 +78,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -444,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M580"/>
+  <dimension ref="A1:M581"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="18.08984375" customWidth="1" style="2" min="1" max="1"/>
@@ -29485,6 +29488,83 @@
         </is>
       </c>
     </row>
+    <row r="581">
+      <c r="A581" s="5" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B581" s="5" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C581" s="5" t="inlineStr">
+        <is>
+          <t>Genérico</t>
+        </is>
+      </c>
+      <c r="D581" s="5" t="inlineStr">
+        <is>
+          <t>Genérico</t>
+        </is>
+      </c>
+      <c r="E581" s="5" t="inlineStr">
+        <is>
+          <t>Branded Content</t>
+        </is>
+      </c>
+      <c r="F581" s="5" t="inlineStr">
+        <is>
+          <t>Branded Content</t>
+        </is>
+      </c>
+      <c r="G581" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H581" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I581" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J581" s="5" t="inlineStr">
+        <is>
+          <t>Envio de Briefing a detalhar principais mensagens de comunicação + URLs destino dos artigos (caso se aplique) + editáveis da campanha para utilização pelo meio + Imagens estáticas formato 9:16 e 1:1 + MREC (300x250) + Halfpage (300x600) + Outros elementos/imagens considerados importantes</t>
+        </is>
+      </c>
+      <c r="K581" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L581" s="5" t="inlineStr">
+        <is>
+          <t>É necessário enviar:
+ - data da publicação?
+- qual o produto ou serviço a comunicar?
+- qual a mensagem a passar?
+- objectivo da comunicação?
+- alvo?
+- mini-briefing: explicação do produto e pontos/temas a destacar
+- PR ou documento com informação do produto
+- imagens em alta qualidade (jpeg)
+- vídeos a associar (mp4).
+Para a publicação e destaque dos artigos:
+- link do site (ou tags)
+- link do perfil de facebook da marca
+- link do perfil de instagram da marca
+- logotipo (jpeg pu png) com fundo transparente</t>
+        </is>
+      </c>
+      <c r="M581" s="5" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -24150,11 +24150,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L455" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 colunas x 16 módulos); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -24192,11 +24187,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L456" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 colunas x 16 módulos); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -24234,11 +24224,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L457" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 colunas x 16 módulos); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -24276,11 +24261,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L458" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 colunas x 16 módulos); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -24318,11 +24298,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L459" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 colunas x 16 módulos); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -24360,11 +24335,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L460" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 colunas x 16 módulos); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -24402,11 +24372,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L461" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 colunas x 16 módulos); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -24444,11 +24409,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L462" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 colunas x 16 módulos); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -24486,11 +24446,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L463" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 257x320mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -24528,11 +24483,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L464" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (sexta-feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -24570,11 +24520,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L465" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (sexta-feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -24612,11 +24557,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L466" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (sexta-feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -24654,11 +24594,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L467" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (sexta-feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -24696,11 +24631,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L468" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (sexta-feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -24738,11 +24668,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L469" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (sexta-feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -24780,11 +24705,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L470" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (sexta-feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -24822,11 +24742,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L471" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (sexta-feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -24864,11 +24779,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L472" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (sexta-feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -24906,11 +24816,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L473" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -24948,11 +24853,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L474" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -24990,11 +24890,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L475" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -25032,11 +24927,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L476" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -25074,11 +24964,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L477" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -25116,11 +25001,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L478" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -25158,11 +25038,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L479" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -25200,11 +25075,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L480" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -25242,11 +25112,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L481" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -25284,11 +25149,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L482" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (domingo); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -25326,11 +25186,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L483" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (domingo); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -25368,11 +25223,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L484" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (domingo); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -25410,11 +25260,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L485" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (domingo); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -25452,11 +25297,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L486" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (domingo); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -25494,11 +25334,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L487" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (domingo); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -25536,11 +25371,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L488" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (domingo); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -25578,11 +25408,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L489" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (domingo); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -25620,11 +25445,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L490" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (domingo); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -25662,11 +25482,6 @@
           <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
         </is>
       </c>
-      <c r="L491" t="inlineStr">
-        <is>
-          <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -25704,11 +25519,6 @@
           <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
         </is>
       </c>
-      <c r="L492" t="inlineStr">
-        <is>
-          <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -25746,11 +25556,6 @@
           <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
         </is>
       </c>
-      <c r="L493" t="inlineStr">
-        <is>
-          <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -25788,11 +25593,6 @@
           <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
         </is>
       </c>
-      <c r="L494" t="inlineStr">
-        <is>
-          <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -25830,11 +25630,6 @@
           <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
         </is>
       </c>
-      <c r="L495" t="inlineStr">
-        <is>
-          <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -25872,11 +25667,6 @@
           <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
         </is>
       </c>
-      <c r="L496" t="inlineStr">
-        <is>
-          <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -25914,11 +25704,6 @@
           <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
         </is>
       </c>
-      <c r="L497" t="inlineStr">
-        <is>
-          <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -25956,11 +25741,6 @@
           <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
         </is>
       </c>
-      <c r="L498" t="inlineStr">
-        <is>
-          <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -25998,11 +25778,6 @@
           <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
         </is>
       </c>
-      <c r="L499" t="inlineStr">
-        <is>
-          <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -26040,11 +25815,6 @@
           <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
         </is>
       </c>
-      <c r="L500" t="inlineStr">
-        <is>
-          <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -26082,11 +25852,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L501" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a 6ª feira); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -26124,11 +25889,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L502" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a 6ª feira); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -26166,11 +25926,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L503" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a 6ª feira); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -26208,11 +25963,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L504" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a 6ª feira); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -26250,11 +26000,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L505" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a 6ª feira); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -26292,11 +26037,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L506" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a 6ª feira); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -26334,11 +26074,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L507" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a 6ª feira); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -26376,11 +26111,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L508" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a 6ª feira); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -26418,11 +26148,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L509" t="inlineStr">
-        <is>
-          <t>Formato especial na 1ª página ou última página do 1º Caderno. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -26460,11 +26185,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L510" t="inlineStr">
-        <is>
-          <t>Formato especial na 1ª página ou última página do 1º Caderno. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -26502,11 +26222,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L511" t="inlineStr">
-        <is>
-          <t>Formato especial na 1ª página ou última página do 1º Caderno. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -26544,11 +26259,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L512" t="inlineStr">
-        <is>
-          <t>Formato especial na 1ª página ou última página do 1º Caderno. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -26586,11 +26296,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L513" t="inlineStr">
-        <is>
-          <t>Formato especial na 1ª página ou última página do 1º Caderno. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -26628,11 +26333,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L514" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -26670,11 +26370,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L515" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -26712,11 +26407,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L516" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -26754,11 +26444,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L517" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -26796,11 +26481,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L518" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -26838,11 +26518,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L519" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -26880,11 +26555,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L520" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -26922,11 +26592,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L521" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -26964,11 +26629,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L522" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (5ª feira); distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -27006,11 +26666,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L523" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (5ª feira); distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -27048,11 +26703,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L524" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (5ª feira); distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -27090,11 +26740,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L525" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (5ª feira); distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -27132,11 +26777,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L526" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (5ª feira); distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -27174,11 +26814,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L527" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (5ª feira); distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -27216,11 +26851,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L528" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (5ª feira); distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -27258,11 +26888,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L529" t="inlineStr">
-        <is>
-          <t>Periodicidade trimestral; distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -27300,11 +26925,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L530" t="inlineStr">
-        <is>
-          <t>Periodicidade trimestral; distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -27342,11 +26962,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L531" t="inlineStr">
-        <is>
-          <t>Periodicidade trimestral; distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -27384,11 +26999,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L532" t="inlineStr">
-        <is>
-          <t>Periodicidade trimestral; distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -27426,11 +27036,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L533" t="inlineStr">
-        <is>
-          <t>Periodicidade trimestral; distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -27468,11 +27073,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L534" t="inlineStr">
-        <is>
-          <t>Periodicidade trimestral; distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -27510,11 +27110,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L535" t="inlineStr">
-        <is>
-          <t>Periodicidade trimestral; distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -27552,11 +27147,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L536" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (6ª feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo LWC 57g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -27594,11 +27184,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L537" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (6ª feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo LWC 57g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -27636,11 +27221,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L538" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (6ª feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo LWC 57g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -27678,11 +27258,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L539" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (6ª feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo LWC 57g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -27720,11 +27295,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L540" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (6ª feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo LWC 57g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -27762,11 +27332,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L541" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (6ª feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo LWC 57g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -27804,11 +27369,6 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="L542" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (6ª feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo LWC 57g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -27846,11 +27406,6 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="L543" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
@@ -27888,11 +27443,6 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="L544" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
@@ -27930,11 +27480,6 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="L545" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
@@ -27972,11 +27517,6 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="L546" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
@@ -28014,11 +27554,6 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="L547" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
@@ -28056,11 +27591,6 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="L548" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -28098,11 +27628,6 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="L549" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
@@ -28140,11 +27665,6 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="L550" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
@@ -28182,11 +27702,6 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="L551" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
@@ -28224,11 +27739,6 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="L552" t="inlineStr">
-        <is>
-          <t>Formato especial de capa do 1º Caderno. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
@@ -28266,11 +27776,6 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="L553" t="inlineStr">
-        <is>
-          <t>Formato especial de capa do 1º Caderno. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
@@ -28308,11 +27813,6 @@
           <t>PDF em alta definição (elementos de desenho em vetorial, imagens à parte + JPEG para visualização)</t>
         </is>
       </c>
-      <c r="L554" t="inlineStr">
-        <is>
-          <t>Saco em papel liso impresso a CMYK + 2 cores; a tarja com a informação é sempre na cor do Expresso (Pantone 315C).</t>
-        </is>
-      </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
@@ -28350,11 +27850,6 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="L555" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
@@ -28392,11 +27887,6 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="L556" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
@@ -28434,11 +27924,6 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="L557" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
@@ -28476,11 +27961,6 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="L558" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
@@ -28518,11 +27998,6 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="L559" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
@@ -28560,11 +28035,6 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="L560" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
@@ -28602,11 +28072,6 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="L561" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
@@ -28644,11 +28109,6 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="L562" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
@@ -28686,11 +28146,6 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="L563" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
@@ -28728,11 +28183,6 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="L564" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
@@ -28770,11 +28220,6 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="L565" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
@@ -28812,11 +28257,6 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="L566" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia — papel jornal melhorado 55g, capa couché mate 130g, lombada colada; localização obrigatória: +30%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
@@ -28854,11 +28294,6 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="L567" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia — papel jornal melhorado 55g, capa couché mate 130g, lombada colada; localização obrigatória: +30%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
@@ -28896,11 +28331,6 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="L568" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia — papel jornal melhorado 55g, capa couché mate 130g, lombada colada; localização obrigatória: +30%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
@@ -28938,11 +28368,6 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="L569" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia — papel jornal melhorado 55g, capa couché mate 130g, lombada colada; localização obrigatória: +30%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
@@ -28980,11 +28405,6 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="L570" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia — papel jornal melhorado 55g, capa couché mate 130g, lombada colada; localização obrigatória: +30%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
@@ -29022,11 +28442,6 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="L571" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia — papel jornal melhorado 55g, capa couché mate 130g, lombada colada; localização obrigatória: +30%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
@@ -29064,11 +28479,6 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="L572" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia — papel jornal melhorado 55g, capa couché mate 130g, lombada colada; localização obrigatória: +30%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
@@ -29106,11 +28516,6 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="L573" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia — papel jornal melhorado 55g, capa couché mate 130g, lombada colada; localização obrigatória: +30%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
@@ -29148,11 +28553,6 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="L574" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia — papel jornal melhorado 55g, capa couché mate 130g, lombada colada; localização obrigatória: +30%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
@@ -29190,11 +28590,6 @@
           <t>PDF, EPS ou TIFF em alta resolução de 400 DPI (mínimo 300 DPI), CMYK, sem atribuição de perfil final</t>
         </is>
       </c>
-      <c r="L575" t="inlineStr">
-        <is>
-          <t>Periodicidade bimestral (janeiro, março, maio, julho, setembro, novembro); revista bilingue (português + inglês); distribuição em Portugal e mais 22 países; páginas duplas com desvio de 6mm ao centro (3mm para a esquerda e 3mm para a direita) para garantir o acerto central. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
@@ -29232,11 +28627,6 @@
           <t>PDF, EPS ou TIFF em alta resolução de 400 DPI (mínimo 300 DPI), CMYK, sem atribuição de perfil final</t>
         </is>
       </c>
-      <c r="L576" t="inlineStr">
-        <is>
-          <t>Periodicidade bimestral (janeiro, março, maio, julho, setembro, novembro); revista bilingue (português + inglês); distribuição em Portugal e mais 22 países; páginas duplas com desvio de 6mm ao centro (3mm para a esquerda e 3mm para a direita) para garantir o acerto central. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
@@ -29274,11 +28664,6 @@
           <t>PDF, EPS ou TIFF em alta resolução de 400 DPI (mínimo 300 DPI), CMYK, sem atribuição de perfil final</t>
         </is>
       </c>
-      <c r="L577" t="inlineStr">
-        <is>
-          <t>Periodicidade bimestral (janeiro, março, maio, julho, setembro, novembro); revista bilingue (português + inglês); distribuição em Portugal e mais 22 países; páginas duplas com desvio de 6mm ao centro (3mm para a esquerda e 3mm para a direita) para garantir o acerto central. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
@@ -29314,11 +28699,6 @@
       <c r="J578" t="inlineStr">
         <is>
           <t>PDF, EPS ou TIFF em alta resolução de 400 DPI (mínimo 300 DPI), CMYK, sem atribuição de perfil final</t>
-        </is>
-      </c>
-      <c r="L578" t="inlineStr">
-        <is>
-          <t>Periodicidade bimestral (janeiro, março, maio, julho, setembro, novembro); revista bilingue (português + inglês); distribuição em Portugal e mais 22 países; páginas duplas com desvio de 6mm ao centro (3mm para a esquerda e 3mm para a direita) para garantir o acerto central. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
         </is>
       </c>
     </row>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -504,11 +504,6 @@
           <t>Impresa</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Billboard</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>Billboard</t>
@@ -556,11 +551,6 @@
           <t>Impresa</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Cubo</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>Cubo</t>
@@ -608,11 +598,6 @@
           <t>Impresa</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Floor Ad</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>Floor Ad</t>
@@ -660,11 +645,6 @@
           <t>Impresa</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Halfpage</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>Halfpage</t>
@@ -717,11 +697,6 @@
           <t>Impresa</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Header XL</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>Header XL</t>
@@ -764,11 +739,6 @@
           <t>Impresa</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>Hero</t>
@@ -816,11 +786,6 @@
           <t>Impresa</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Mrec</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>In-Article</t>
@@ -873,11 +838,6 @@
           <t>Impresa</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Interscroller</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>Interscroller</t>
@@ -930,11 +890,6 @@
           <t>Impresa</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>Interstitial</t>
@@ -987,11 +942,6 @@
           <t>Impresa</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Mrec</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>Mrec</t>
@@ -1039,11 +989,6 @@
           <t>Impresa</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Mrec</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>Mrec Video</t>
@@ -1091,11 +1036,6 @@
           <t>Impresa</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>Push Down</t>
@@ -1148,11 +1088,6 @@
           <t>Impresa</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Open Door</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>Open Door</t>
@@ -1205,11 +1140,6 @@
           <t>Impresa</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>Video In Stream</t>
@@ -1262,11 +1192,6 @@
           <t>Impresa</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>Video Outstream</t>
@@ -1319,11 +1244,6 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Billboard</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>Billboard</t>
@@ -1371,11 +1291,6 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Billboard</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>Billboard XL</t>
@@ -1428,11 +1343,6 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Carousel</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>Carrossel In Content</t>
@@ -1485,11 +1395,6 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Carousel</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>Carrossel Top</t>
@@ -1542,11 +1447,6 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>Dossier</t>
@@ -1599,11 +1499,6 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>Full Frame</t>
@@ -1656,11 +1551,6 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Halfpage</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>Halfpage</t>
@@ -1713,11 +1603,6 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Interscroller</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>Insterscroll</t>
@@ -1770,11 +1655,6 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>Intro</t>
@@ -1827,11 +1707,6 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>Intro/Splash</t>
@@ -1879,11 +1754,6 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>L Frame</t>
@@ -1936,11 +1806,6 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Leaderboard</t>
-        </is>
-      </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>Leaderboard</t>
@@ -1988,11 +1853,6 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Billboard</t>
-        </is>
-      </c>
       <c r="F29" t="inlineStr">
         <is>
           <t>Mega Billboard</t>
@@ -2040,11 +1900,6 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Mrec</t>
-        </is>
-      </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>Mrec</t>
@@ -2092,11 +1947,6 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
       <c r="F31" t="inlineStr">
         <is>
           <t>Native</t>
@@ -2149,11 +1999,6 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Open Door</t>
-        </is>
-      </c>
       <c r="F32" t="inlineStr">
         <is>
           <t>Open Door</t>
@@ -2206,11 +2051,6 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
       <c r="F33" t="inlineStr">
         <is>
           <t>Outstream</t>
@@ -2253,11 +2093,6 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Peel Off</t>
-        </is>
-      </c>
       <c r="F34" t="inlineStr">
         <is>
           <t>Page Flip</t>
@@ -2300,11 +2135,6 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
       <c r="F35" t="inlineStr">
         <is>
           <t>Pop In</t>
@@ -2352,11 +2182,6 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Single Image</t>
-        </is>
-      </c>
       <c r="F36" t="inlineStr">
         <is>
           <t>Post Social Media</t>
@@ -2404,11 +2229,6 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Pre-Roll</t>
-        </is>
-      </c>
       <c r="F37" t="inlineStr">
         <is>
           <t>Pre Roll</t>
@@ -2461,11 +2281,6 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Pre-Roll</t>
-        </is>
-      </c>
       <c r="F38" t="inlineStr">
         <is>
           <t>Pre Roll Vertical</t>
@@ -2518,11 +2333,6 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F39" t="inlineStr">
         <is>
           <t>Push Down</t>
@@ -2575,11 +2385,6 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Vertical Video</t>
-        </is>
-      </c>
       <c r="F40" t="inlineStr">
         <is>
           <t>Reel Social Media</t>
@@ -2632,11 +2437,6 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F41" t="inlineStr">
         <is>
           <t>Side Frame</t>
@@ -2684,11 +2484,6 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Single Image</t>
-        </is>
-      </c>
       <c r="F42" t="inlineStr">
         <is>
           <t>Social Card</t>
@@ -2726,11 +2521,6 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
       <c r="F43" t="inlineStr">
         <is>
           <t>Splash</t>
@@ -2778,11 +2568,6 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
       <c r="F44" t="inlineStr">
         <is>
           <t>Story Social Media</t>
@@ -2835,11 +2620,6 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Takeover</t>
-        </is>
-      </c>
       <c r="F45" t="inlineStr">
         <is>
           <t>Takeover</t>
@@ -2887,11 +2667,6 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
       <c r="F46" t="inlineStr">
         <is>
           <t>Ticker</t>
@@ -2944,11 +2719,6 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Vertical Video</t>
-        </is>
-      </c>
       <c r="F47" t="inlineStr">
         <is>
           <t>Vertical Video</t>
@@ -3001,11 +2771,6 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F48" t="inlineStr">
         <is>
           <t>Video Wall</t>
@@ -3048,11 +2813,6 @@
           <t>Media Livre</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Peel Off</t>
-        </is>
-      </c>
       <c r="F49" t="inlineStr">
         <is>
           <t>Corner Ad</t>
@@ -3100,11 +2860,6 @@
           <t>Media Livre</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Floor Ad</t>
-        </is>
-      </c>
       <c r="F50" t="inlineStr">
         <is>
           <t>Floor Ad</t>
@@ -3152,11 +2907,6 @@
           <t>Media Livre</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Halfpage</t>
-        </is>
-      </c>
       <c r="F51" t="inlineStr">
         <is>
           <t>Halfpage</t>
@@ -3209,11 +2959,6 @@
           <t>Media Livre</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
       <c r="F52" t="inlineStr">
         <is>
           <t>In Content</t>
@@ -3266,11 +3011,6 @@
           <t>Media Livre</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
       <c r="F53" t="inlineStr">
         <is>
           <t>Intro</t>
@@ -3323,11 +3063,6 @@
           <t>Media Livre</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
       <c r="F54" t="inlineStr">
         <is>
           <t>Layer</t>
@@ -3375,11 +3110,6 @@
           <t>Media Livre</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Leaderboard</t>
-        </is>
-      </c>
       <c r="F55" t="inlineStr">
         <is>
           <t>Leaderboard</t>
@@ -3427,11 +3157,6 @@
           <t>Media Livre</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Header XL</t>
-        </is>
-      </c>
       <c r="F56" t="inlineStr">
         <is>
           <t>Masthead</t>
@@ -3479,11 +3204,6 @@
           <t>Media Livre</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Sticky Banner</t>
-        </is>
-      </c>
       <c r="F57" t="inlineStr">
         <is>
           <t>Masthead Sticky Companion</t>
@@ -3531,11 +3251,6 @@
           <t>Media Livre</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F58" t="inlineStr">
         <is>
           <t>Moldura</t>
@@ -3578,11 +3293,6 @@
           <t>Media Livre</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Mrec</t>
-        </is>
-      </c>
       <c r="F59" t="inlineStr">
         <is>
           <t>Mrec</t>
@@ -3630,11 +3340,6 @@
           <t>Media Livre</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Open Door</t>
-        </is>
-      </c>
       <c r="F60" t="inlineStr">
         <is>
           <t>Open Door</t>
@@ -3687,11 +3392,6 @@
           <t>Media Livre</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Peel Off</t>
-        </is>
-      </c>
       <c r="F61" t="inlineStr">
         <is>
           <t>Peel Off</t>
@@ -3739,11 +3439,6 @@
           <t>Media Livre</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Pre-Roll</t>
-        </is>
-      </c>
       <c r="F62" t="inlineStr">
         <is>
           <t>Pre Roll</t>
@@ -3796,11 +3491,6 @@
           <t>Media Livre</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F63" t="inlineStr">
         <is>
           <t>Showcase Rich Media</t>
@@ -3833,11 +3523,6 @@
           <t>Media Livre</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
       <c r="F64" t="inlineStr">
         <is>
           <t>Sideticker</t>
@@ -3870,11 +3555,6 @@
           <t>Media Livre</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
       <c r="F65" t="inlineStr">
         <is>
           <t>Slash</t>
@@ -3907,11 +3587,6 @@
           <t>Media Livre</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F66" t="inlineStr">
         <is>
           <t>Topo Extensivel</t>
@@ -3944,11 +3619,6 @@
           <t>Observador</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Audio Ad</t>
-        </is>
-      </c>
       <c r="F67" t="inlineStr">
         <is>
           <t>Audio Ad</t>
@@ -3991,11 +3661,6 @@
           <t>Observador</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Newsletter Banner</t>
-        </is>
-      </c>
       <c r="F68" t="inlineStr">
         <is>
           <t>Banner Newsletter</t>
@@ -4043,11 +3708,6 @@
           <t>Observador</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Carousel</t>
-        </is>
-      </c>
       <c r="F69" t="inlineStr">
         <is>
           <t>Carrossel</t>
@@ -4100,11 +3760,6 @@
           <t>Observador</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F70" t="inlineStr">
         <is>
           <t>Compare</t>
@@ -4157,11 +3812,6 @@
           <t>Observador</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Gallery</t>
-        </is>
-      </c>
       <c r="F71" t="inlineStr">
         <is>
           <t>Flipper</t>
@@ -4214,11 +3864,6 @@
           <t>Observador</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Halfpage</t>
-        </is>
-      </c>
       <c r="F72" t="inlineStr">
         <is>
           <t>Halfpage</t>
@@ -4271,11 +3916,6 @@
           <t>Observador</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Header XL</t>
-        </is>
-      </c>
       <c r="F73" t="inlineStr">
         <is>
           <t>Header XL</t>
@@ -4323,11 +3963,6 @@
           <t>Observador</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
       <c r="F74" t="inlineStr">
         <is>
           <t>Interstitial</t>
@@ -4375,11 +4010,6 @@
           <t>Observador</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
       <c r="F75" t="inlineStr">
         <is>
           <t>Intro Dynamic</t>
@@ -4427,11 +4057,6 @@
           <t>Observador</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
       <c r="F76" t="inlineStr">
         <is>
           <t>Intro Folheto</t>
@@ -4474,11 +4099,6 @@
           <t>Observador</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Billboard</t>
-        </is>
-      </c>
       <c r="F77" t="inlineStr">
         <is>
           <t>Manchete</t>
@@ -4526,11 +4146,6 @@
           <t>Observador</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Mrec</t>
-        </is>
-      </c>
       <c r="F78" t="inlineStr">
         <is>
           <t>Mrec</t>
@@ -4578,11 +4193,6 @@
           <t>Observador</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Open Door</t>
-        </is>
-      </c>
       <c r="F79" t="inlineStr">
         <is>
           <t>Open Door</t>
@@ -4625,11 +4235,6 @@
           <t>Observador</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
       <c r="F80" t="inlineStr">
         <is>
           <t>Outstream</t>
@@ -4682,11 +4287,6 @@
           <t>Observador</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Peel Off</t>
-        </is>
-      </c>
       <c r="F81" t="inlineStr">
         <is>
           <t>Peel Off</t>
@@ -4739,11 +4339,6 @@
           <t>Observador</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Pre-Roll</t>
-        </is>
-      </c>
       <c r="F82" t="inlineStr">
         <is>
           <t>Pre-Roll</t>
@@ -4796,11 +4391,6 @@
           <t>Observador</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Skin</t>
-        </is>
-      </c>
       <c r="F83" t="inlineStr">
         <is>
           <t>Skin</t>
@@ -4848,11 +4438,6 @@
           <t>Observador</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Sticky Banner</t>
-        </is>
-      </c>
       <c r="F84" t="inlineStr">
         <is>
           <t>Sticky Dynamic</t>
@@ -4900,11 +4485,6 @@
           <t>Observador</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Floor Ad</t>
-        </is>
-      </c>
       <c r="F85" t="inlineStr">
         <is>
           <t>Sticky Footer</t>
@@ -4952,11 +4532,6 @@
           <t>Observador</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
       <c r="F86" t="inlineStr">
         <is>
           <t>Sticky Intro</t>
@@ -5009,11 +4584,6 @@
           <t>Observador</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Twin Ad</t>
-        </is>
-      </c>
       <c r="F87" t="inlineStr">
         <is>
           <t>Twin Ad</t>
@@ -5066,11 +4636,6 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Gallery</t>
-        </is>
-      </c>
       <c r="F88" t="inlineStr">
         <is>
           <t>Ad Selector</t>
@@ -5123,11 +4688,6 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Leaderboard</t>
-        </is>
-      </c>
       <c r="F89" t="inlineStr">
         <is>
           <t>Barra Topo</t>
@@ -5175,11 +4735,6 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F90" t="inlineStr">
         <is>
           <t>Barra Topo Extensivel</t>
@@ -5227,11 +4782,6 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Billboard</t>
-        </is>
-      </c>
       <c r="F91" t="inlineStr">
         <is>
           <t>Billboard</t>
@@ -5279,11 +4829,6 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Cubo</t>
-        </is>
-      </c>
       <c r="F92" t="inlineStr">
         <is>
           <t>Cubo</t>
@@ -5331,11 +4876,6 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Floor Ad</t>
-        </is>
-      </c>
       <c r="F93" t="inlineStr">
         <is>
           <t>Floor Ad</t>
@@ -5383,11 +4923,6 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Gallery</t>
-        </is>
-      </c>
       <c r="F94" t="inlineStr">
         <is>
           <t>Gallery Flip</t>
@@ -5440,11 +4975,6 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Halfpage</t>
-        </is>
-      </c>
       <c r="F95" t="inlineStr">
         <is>
           <t>Halfpage</t>
@@ -5497,11 +5027,6 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
       <c r="F96" t="inlineStr">
         <is>
           <t>Interstitial</t>
@@ -5554,11 +5079,6 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Mrec</t>
-        </is>
-      </c>
       <c r="F97" t="inlineStr">
         <is>
           <t>Mrec</t>
@@ -5606,11 +5126,6 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Newsletter Banner</t>
-        </is>
-      </c>
       <c r="F98" t="inlineStr">
         <is>
           <t>Newsletter</t>
@@ -5658,11 +5173,6 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Open Door</t>
-        </is>
-      </c>
       <c r="F99" t="inlineStr">
         <is>
           <t>Open Door</t>
@@ -5710,11 +5220,6 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Parallax</t>
-        </is>
-      </c>
       <c r="F100" t="inlineStr">
         <is>
           <t>Parallax</t>
@@ -5767,11 +5272,6 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Halfpage</t>
-        </is>
-      </c>
       <c r="F101" t="inlineStr">
         <is>
           <t>Prisma</t>
@@ -5824,11 +5324,6 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F102" t="inlineStr">
         <is>
           <t>Scratch</t>
@@ -5881,11 +5376,6 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Catalog Ad</t>
-        </is>
-      </c>
       <c r="F103" t="inlineStr">
         <is>
           <t>Shopping Ads</t>
@@ -5938,11 +5428,6 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>Gallery</t>
-        </is>
-      </c>
       <c r="F104" t="inlineStr">
         <is>
           <t>Slide Door Video</t>
@@ -5995,11 +5480,6 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Gallery</t>
-        </is>
-      </c>
       <c r="F105" t="inlineStr">
         <is>
           <t>Slide R Video</t>
@@ -6042,11 +5522,6 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>Takeover</t>
-        </is>
-      </c>
       <c r="F106" t="inlineStr">
         <is>
           <t>Takeover XXL</t>
@@ -6094,11 +5569,6 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Gallery</t>
-        </is>
-      </c>
       <c r="F107" t="inlineStr">
         <is>
           <t>Top Header Gallery</t>
@@ -6141,11 +5611,6 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Twin Ad</t>
-        </is>
-      </c>
       <c r="F108" t="inlineStr">
         <is>
           <t>Twin Ad</t>
@@ -6193,11 +5658,6 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
       <c r="F109" t="inlineStr">
         <is>
           <t>Video Incontent</t>
@@ -6250,11 +5710,6 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Pre-Roll</t>
-        </is>
-      </c>
       <c r="F110" t="inlineStr">
         <is>
           <t>Video Pre-Roll</t>
@@ -6307,11 +5762,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Cubo</t>
-        </is>
-      </c>
       <c r="F111" t="inlineStr">
         <is>
           <t>3D Cube (Teads)</t>
@@ -6359,11 +5809,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
       <c r="F112" t="inlineStr">
         <is>
           <t>App Install Native (Outbrain)</t>
@@ -6416,11 +5861,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Audio Ad</t>
-        </is>
-      </c>
       <c r="F113" t="inlineStr">
         <is>
           <t>Audio Digital (Spotify)</t>
@@ -6463,11 +5903,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Audio Ad</t>
-        </is>
-      </c>
       <c r="F114" t="inlineStr">
         <is>
           <t>Audio Mid-Roll</t>
@@ -6510,11 +5945,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Audio Ad</t>
-        </is>
-      </c>
       <c r="F115" t="inlineStr">
         <is>
           <t>Audio Post-Roll</t>
@@ -6557,11 +5987,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Audio Ad</t>
-        </is>
-      </c>
       <c r="F116" t="inlineStr">
         <is>
           <t>Audio Pre-Roll</t>
@@ -6604,11 +6029,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>Billboard</t>
-        </is>
-      </c>
       <c r="F117" t="inlineStr">
         <is>
           <t>Billboard 1 e 2 Posição</t>
@@ -6656,11 +6076,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Billboard</t>
-        </is>
-      </c>
       <c r="F118" t="inlineStr">
         <is>
           <t>Billboard Carousel</t>
@@ -6713,11 +6128,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Billboard</t>
-        </is>
-      </c>
       <c r="F119" t="inlineStr">
         <is>
           <t>Billboard IAB</t>
@@ -6760,11 +6170,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Billboard</t>
-        </is>
-      </c>
       <c r="F120" t="inlineStr">
         <is>
           <t>Billboard Responsive</t>
@@ -6812,11 +6217,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>Branded Content</t>
-        </is>
-      </c>
       <c r="F121" t="inlineStr">
         <is>
           <t>Branded Content</t>
@@ -6849,11 +6249,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
       <c r="F122" t="inlineStr">
         <is>
           <t>Capa Falsa</t>
@@ -6906,11 +6301,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>Carousel</t>
-        </is>
-      </c>
       <c r="F123" t="inlineStr">
         <is>
           <t>Carousel (Teads)</t>
@@ -6958,11 +6348,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Carousel</t>
-        </is>
-      </c>
       <c r="F124" t="inlineStr">
         <is>
           <t>Carousel Native (Outbrain)</t>
@@ -7015,11 +6400,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>Carousel</t>
-        </is>
-      </c>
       <c r="F125" t="inlineStr">
         <is>
           <t>Carousel Performance</t>
@@ -7047,11 +6427,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
       <c r="F126" t="inlineStr">
         <is>
           <t>Clip Native (Outbrain)</t>
@@ -7079,11 +6454,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>Sticky Banner</t>
-        </is>
-      </c>
       <c r="F127" t="inlineStr">
         <is>
           <t>Companion Banner</t>
@@ -7131,11 +6501,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>Countdown</t>
-        </is>
-      </c>
       <c r="F128" t="inlineStr">
         <is>
           <t>Countdown</t>
@@ -7188,11 +6553,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>CTV</t>
-        </is>
-      </c>
       <c r="F129" t="inlineStr">
         <is>
           <t>CTV - Homescreen</t>
@@ -7220,11 +6580,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>CTV</t>
-        </is>
-      </c>
       <c r="F130" t="inlineStr">
         <is>
           <t>CTV - Pause Ad</t>
@@ -7252,11 +6607,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>CTV</t>
-        </is>
-      </c>
       <c r="F131" t="inlineStr">
         <is>
           <t>CTV - Pre-Roll</t>
@@ -7284,11 +6634,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Banner</t>
-        </is>
-      </c>
       <c r="F132" t="inlineStr">
         <is>
           <t>Display Standard (CPC Surf)</t>
@@ -7341,11 +6686,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F133" t="inlineStr">
         <is>
           <t>Drag and Drop (Teads)</t>
@@ -7393,11 +6733,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F134" t="inlineStr">
         <is>
           <t>Flip Flow (Teads)</t>
@@ -7445,11 +6780,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F135" t="inlineStr">
         <is>
           <t>Flow (Teads)</t>
@@ -7497,11 +6827,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>Halfpage</t>
-        </is>
-      </c>
       <c r="F136" t="inlineStr">
         <is>
           <t>Halfpage</t>
@@ -7554,11 +6879,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Halfpage</t>
-        </is>
-      </c>
       <c r="F137" t="inlineStr">
         <is>
           <t>Halfpage Flip</t>
@@ -7611,11 +6931,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Header XL</t>
-        </is>
-      </c>
       <c r="F138" t="inlineStr">
         <is>
           <t>Header XL</t>
@@ -7643,11 +6958,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Header XL</t>
-        </is>
-      </c>
       <c r="F139" t="inlineStr">
         <is>
           <t>Header XL Galeria</t>
@@ -7675,11 +6985,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Header XL</t>
-        </is>
-      </c>
       <c r="F140" t="inlineStr">
         <is>
           <t>Header XL Galeria Video</t>
@@ -7707,11 +7012,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>Header XL</t>
-        </is>
-      </c>
       <c r="F141" t="inlineStr">
         <is>
           <t>Header XL Navigation</t>
@@ -7739,11 +7039,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Header XL</t>
-        </is>
-      </c>
       <c r="F142" t="inlineStr">
         <is>
           <t>Header XL Video</t>
@@ -7771,11 +7066,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>Header XL</t>
-        </is>
-      </c>
       <c r="F143" t="inlineStr">
         <is>
           <t>Header XL Widget</t>
@@ -7803,11 +7093,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Header XL</t>
-        </is>
-      </c>
       <c r="F144" t="inlineStr">
         <is>
           <t>Header XL Zoom</t>
@@ -7835,11 +7120,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Open Door</t>
-        </is>
-      </c>
       <c r="F145" t="inlineStr">
         <is>
           <t>Homepage Takeover (Spotify)</t>
@@ -7892,11 +7172,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F146" t="inlineStr">
         <is>
           <t>Hover (Teads)</t>
@@ -7949,11 +7224,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>In-Feed</t>
-        </is>
-      </c>
       <c r="F147" t="inlineStr">
         <is>
           <t>In-feed Display (Spotify)</t>
@@ -8006,11 +7276,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>In-Feed</t>
-        </is>
-      </c>
       <c r="F148" t="inlineStr">
         <is>
           <t>In-feed Video (Spotify)</t>
@@ -8043,11 +7308,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F149" t="inlineStr">
         <is>
           <t>Inline Midscroll</t>
@@ -8095,11 +7355,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Interscroller</t>
-        </is>
-      </c>
       <c r="F150" t="inlineStr">
         <is>
           <t>Interscroller Display (Teads)</t>
@@ -8152,11 +7407,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>Interscroller</t>
-        </is>
-      </c>
       <c r="F151" t="inlineStr">
         <is>
           <t>Interscroller Video (Teads)</t>
@@ -8209,11 +7459,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
       <c r="F152" t="inlineStr">
         <is>
           <t>Intra</t>
@@ -8266,11 +7511,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
       <c r="F153" t="inlineStr">
         <is>
           <t>Intra Plus</t>
@@ -8318,11 +7558,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
       <c r="F154" t="inlineStr">
         <is>
           <t>Intra Plus Vídeo</t>
@@ -8370,11 +7605,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
       <c r="F155" t="inlineStr">
         <is>
           <t>Intra Vídeo</t>
@@ -8427,11 +7657,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
       <c r="F156" t="inlineStr">
         <is>
           <t>In-stream Video (Spotify)</t>
@@ -8484,11 +7709,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>Landing Page</t>
-        </is>
-      </c>
       <c r="F157" t="inlineStr">
         <is>
           <t>Landing Page</t>
@@ -8521,11 +7741,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>Leaderboard</t>
-        </is>
-      </c>
       <c r="F158" t="inlineStr">
         <is>
           <t>Leaderboard</t>
@@ -8573,11 +7788,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>Landing Page</t>
-        </is>
-      </c>
       <c r="F159" t="inlineStr">
         <is>
           <t>Microsite</t>
@@ -8610,11 +7820,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>Banner</t>
-        </is>
-      </c>
       <c r="F160" t="inlineStr">
         <is>
           <t>Mobile Banner</t>
@@ -8662,11 +7867,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>Mrec</t>
-        </is>
-      </c>
       <c r="F161" t="inlineStr">
         <is>
           <t>Mrec</t>
@@ -8714,11 +7914,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>Mrec</t>
-        </is>
-      </c>
       <c r="F162" t="inlineStr">
         <is>
           <t>Mrec Carousel</t>
@@ -8766,11 +7961,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
       <c r="F163" t="inlineStr">
         <is>
           <t>Overlay Video</t>
@@ -8823,11 +8013,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>Vertical Video</t>
-        </is>
-      </c>
       <c r="F164" t="inlineStr">
         <is>
           <t>Reel</t>
@@ -8880,11 +8065,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F165" t="inlineStr">
         <is>
           <t>Scratch (Teads)</t>
@@ -8937,11 +8117,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F166" t="inlineStr">
         <is>
           <t>Scroller (Teads)</t>
@@ -8989,11 +8164,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>Catalog Ad</t>
-        </is>
-      </c>
       <c r="F167" t="inlineStr">
         <is>
           <t>Shoppable Carousel Performance (Teads)</t>
@@ -9041,11 +8211,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>Catalog Ad</t>
-        </is>
-      </c>
       <c r="F168" t="inlineStr">
         <is>
           <t>Shoppable Display (Teads)</t>
@@ -9093,11 +8258,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>Single Image</t>
-        </is>
-      </c>
       <c r="F169" t="inlineStr">
         <is>
           <t>Single Image</t>
@@ -9145,11 +8305,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>Single Video</t>
-        </is>
-      </c>
       <c r="F170" t="inlineStr">
         <is>
           <t>Single Video</t>
@@ -9192,11 +8347,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>Skin</t>
-        </is>
-      </c>
       <c r="F171" t="inlineStr">
         <is>
           <t>Skin</t>
@@ -9234,11 +8384,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F172" t="inlineStr">
         <is>
           <t>Slider (Teads)</t>
@@ -9291,11 +8436,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F173" t="inlineStr">
         <is>
           <t>Smart6 (Teads)</t>
@@ -9348,11 +8488,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>Single Image</t>
-        </is>
-      </c>
       <c r="F174" t="inlineStr">
         <is>
           <t>Social (Teads)</t>
@@ -9390,11 +8525,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F175" t="inlineStr">
         <is>
           <t>Social Performance</t>
@@ -9432,11 +8562,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>Single Video</t>
-        </is>
-      </c>
       <c r="F176" t="inlineStr">
         <is>
           <t>Social Video</t>
@@ -9474,11 +8599,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F177" t="inlineStr">
         <is>
           <t>Spin Card (Teads)</t>
@@ -9526,11 +8646,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>Billboard</t>
-        </is>
-      </c>
       <c r="F178" t="inlineStr">
         <is>
           <t>Standard Green Ad</t>
@@ -9578,11 +8693,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
       <c r="F179" t="inlineStr">
         <is>
           <t>Standard Native (Outbrain)</t>
@@ -9635,11 +8745,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
       <c r="F180" t="inlineStr">
         <is>
           <t>Stories Display (Teads)</t>
@@ -9677,11 +8782,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
       <c r="F181" t="inlineStr">
         <is>
           <t>Stories Video (Teads)</t>
@@ -9719,11 +8819,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>Carousel</t>
-        </is>
-      </c>
       <c r="F182" t="inlineStr">
         <is>
           <t>Swipe Carousel (Teads)</t>
@@ -9776,11 +8871,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>Topscroll</t>
-        </is>
-      </c>
       <c r="F183" t="inlineStr">
         <is>
           <t>Topscroll</t>
@@ -9833,11 +8923,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>Topscroll</t>
-        </is>
-      </c>
       <c r="F184" t="inlineStr">
         <is>
           <t>Topscroll Carousel</t>
@@ -9875,11 +8960,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>Topscroll</t>
-        </is>
-      </c>
       <c r="F185" t="inlineStr">
         <is>
           <t>Topscroll Expand</t>
@@ -9927,11 +9007,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>Topscroll</t>
-        </is>
-      </c>
       <c r="F186" t="inlineStr">
         <is>
           <t>Topscroll Expand Video</t>
@@ -9979,11 +9054,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>Topscroll</t>
-        </is>
-      </c>
       <c r="F187" t="inlineStr">
         <is>
           <t>Topscroll Prismo</t>
@@ -10031,11 +9101,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>Topscroll</t>
-        </is>
-      </c>
       <c r="F188" t="inlineStr">
         <is>
           <t>Topscroll Video</t>
@@ -10073,11 +9138,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>Twin Ad</t>
-        </is>
-      </c>
       <c r="F189" t="inlineStr">
         <is>
           <t>Twin Ad</t>
@@ -10125,11 +9185,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
       <c r="F190" t="inlineStr">
         <is>
           <t>Video In-Stream Mid-Roll</t>
@@ -10182,11 +9237,6 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>Pre-Roll</t>
-        </is>
-      </c>
       <c r="F191" t="inlineStr">
         <is>
           <t>Video In-Stream Pre-Roll</t>
@@ -10239,11 +9289,6 @@
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
       <c r="F192" t="inlineStr">
         <is>
           <t>Article and Newsletter Ads</t>
@@ -10296,11 +9341,6 @@
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>Carousel</t>
-        </is>
-      </c>
       <c r="F193" t="inlineStr">
         <is>
           <t>Carousel</t>
@@ -10358,11 +9398,6 @@
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>CTV</t>
-        </is>
-      </c>
       <c r="F194" t="inlineStr">
         <is>
           <t>Connected TV Ads</t>
@@ -10415,11 +9450,6 @@
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
       <c r="F195" t="inlineStr">
         <is>
           <t>Conversation Ads</t>
@@ -10472,11 +9502,6 @@
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
       <c r="F196" t="inlineStr">
         <is>
           <t>Document Ads</t>
@@ -10529,11 +9554,6 @@
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
       <c r="F197" t="inlineStr">
         <is>
           <t>Event Ads</t>
@@ -10591,11 +9611,6 @@
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
       <c r="F198" t="inlineStr">
         <is>
           <t>Follower Ads</t>
@@ -10653,11 +9668,6 @@
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
       <c r="F199" t="inlineStr">
         <is>
           <t>Job Ads</t>
@@ -10710,11 +9720,6 @@
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
       <c r="F200" t="inlineStr">
         <is>
           <t>Lead Gen Forms</t>
@@ -10767,11 +9772,6 @@
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
       <c r="F201" t="inlineStr">
         <is>
           <t>Message Ads</t>
@@ -10824,11 +9824,6 @@
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>Single Image</t>
-        </is>
-      </c>
       <c r="F202" t="inlineStr">
         <is>
           <t>Single Image</t>
@@ -10886,11 +9881,6 @@
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>Single Video</t>
-        </is>
-      </c>
       <c r="F203" t="inlineStr">
         <is>
           <t>Single Video</t>
@@ -10948,11 +9938,6 @@
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
       <c r="F204" t="inlineStr">
         <is>
           <t>Spotlight Ads</t>
@@ -11010,11 +9995,6 @@
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
       <c r="F205" t="inlineStr">
         <is>
           <t>Text Ads</t>
@@ -11072,11 +10052,6 @@
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
       <c r="F206" t="inlineStr">
         <is>
           <t>Thought Leader Ads</t>
@@ -11129,11 +10104,6 @@
           <t>Pinterest</t>
         </is>
       </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>Carousel</t>
-        </is>
-      </c>
       <c r="F207" t="inlineStr">
         <is>
           <t>Carousel Ad</t>
@@ -11191,11 +10161,6 @@
           <t>Pinterest</t>
         </is>
       </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>Collection</t>
-        </is>
-      </c>
       <c r="F208" t="inlineStr">
         <is>
           <t>Collection</t>
@@ -11253,11 +10218,6 @@
           <t>Pinterest</t>
         </is>
       </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>Single Image</t>
-        </is>
-      </c>
       <c r="F209" t="inlineStr">
         <is>
           <t>Image Pin</t>
@@ -11315,11 +10275,6 @@
           <t>Pinterest</t>
         </is>
       </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>Single Video</t>
-        </is>
-      </c>
       <c r="F210" t="inlineStr">
         <is>
           <t>Video Ad</t>
@@ -11377,11 +10332,6 @@
           <t>Reddit</t>
         </is>
       </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>Carousel</t>
-        </is>
-      </c>
       <c r="F211" t="inlineStr">
         <is>
           <t>Carousel Ad</t>
@@ -11439,11 +10389,6 @@
           <t>Reddit</t>
         </is>
       </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
       <c r="F212" t="inlineStr">
         <is>
           <t>Free-form Ad</t>
@@ -11501,11 +10446,6 @@
           <t>Reddit</t>
         </is>
       </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>Single Image</t>
-        </is>
-      </c>
       <c r="F213" t="inlineStr">
         <is>
           <t>Image Ad</t>
@@ -11563,11 +10503,6 @@
           <t>Reddit</t>
         </is>
       </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>Catalog Ad</t>
-        </is>
-      </c>
       <c r="F214" t="inlineStr">
         <is>
           <t>Product Ad</t>
@@ -11615,11 +10550,6 @@
           <t>Reddit</t>
         </is>
       </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>Single Video</t>
-        </is>
-      </c>
       <c r="F215" t="inlineStr">
         <is>
           <t>Video Ad</t>
@@ -11677,11 +10607,6 @@
           <t>Snapchat</t>
         </is>
       </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>Branded Effects</t>
-        </is>
-      </c>
       <c r="F216" t="inlineStr">
         <is>
           <t>AR Filters</t>
@@ -11729,11 +10654,6 @@
           <t>Snapchat</t>
         </is>
       </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>Collection</t>
-        </is>
-      </c>
       <c r="F217" t="inlineStr">
         <is>
           <t>Collection</t>
@@ -11791,11 +10711,6 @@
           <t>Snapchat</t>
         </is>
       </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>Single Video</t>
-        </is>
-      </c>
       <c r="F218" t="inlineStr">
         <is>
           <t>Commercial Ad</t>
@@ -11848,11 +10763,6 @@
           <t>Snapchat</t>
         </is>
       </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>Single Image</t>
-        </is>
-      </c>
       <c r="F219" t="inlineStr">
         <is>
           <t>Single Image</t>
@@ -11910,11 +10820,6 @@
           <t>Snapchat</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>Single Video</t>
-        </is>
-      </c>
       <c r="F220" t="inlineStr">
         <is>
           <t>Single Video</t>
@@ -11972,11 +10877,6 @@
           <t>Snapchat</t>
         </is>
       </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
       <c r="F221" t="inlineStr">
         <is>
           <t>Story</t>
@@ -12034,11 +10934,6 @@
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>Branded Effects</t>
-        </is>
-      </c>
       <c r="F222" t="inlineStr">
         <is>
           <t>Branded Effect</t>
@@ -12091,11 +10986,6 @@
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>Carousel</t>
-        </is>
-      </c>
       <c r="F223" t="inlineStr">
         <is>
           <t>Carousel Ads</t>
@@ -12148,11 +11038,6 @@
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>In-Feed Video</t>
-        </is>
-      </c>
       <c r="F224" t="inlineStr">
         <is>
           <t>In-Feed (Standard Feed)</t>
@@ -12215,11 +11100,6 @@
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>In-Feed Video</t>
-        </is>
-      </c>
       <c r="F225" t="inlineStr">
         <is>
           <t>Pulse</t>
@@ -12267,11 +11147,6 @@
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>In-Feed Video</t>
-        </is>
-      </c>
       <c r="F226" t="inlineStr">
         <is>
           <t>Spark Ads</t>
@@ -12324,11 +11199,6 @@
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>In-Feed Video</t>
-        </is>
-      </c>
       <c r="F227" t="inlineStr">
         <is>
           <t>Top Feed</t>
@@ -12381,11 +11251,6 @@
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>In-Feed Video</t>
-        </is>
-      </c>
       <c r="F228" t="inlineStr">
         <is>
           <t>TopView</t>
@@ -12448,11 +11313,6 @@
           <t>X</t>
         </is>
       </c>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>Carousel</t>
-        </is>
-      </c>
       <c r="F229" t="inlineStr">
         <is>
           <t>Carousel Ad</t>
@@ -12510,11 +11370,6 @@
           <t>X</t>
         </is>
       </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>Single Image</t>
-        </is>
-      </c>
       <c r="F230" t="inlineStr">
         <is>
           <t>Image Ad</t>
@@ -12572,11 +11427,6 @@
           <t>X</t>
         </is>
       </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
       <c r="F231" t="inlineStr">
         <is>
           <t>Text Ad</t>
@@ -12629,11 +11479,6 @@
           <t>X</t>
         </is>
       </c>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t>Single Video</t>
-        </is>
-      </c>
       <c r="F232" t="inlineStr">
         <is>
           <t>Video Ad</t>
@@ -12691,11 +11536,6 @@
           <t>Google Display Network</t>
         </is>
       </c>
-      <c r="E233" t="inlineStr">
-        <is>
-          <t>Mrec</t>
-        </is>
-      </c>
       <c r="F233" t="inlineStr">
         <is>
           <t>Medium Rectangle</t>
@@ -12743,11 +11583,6 @@
           <t>Google Display Network</t>
         </is>
       </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>Mrec</t>
-        </is>
-      </c>
       <c r="F234" t="inlineStr">
         <is>
           <t>Large Rectangle</t>
@@ -12795,11 +11630,6 @@
           <t>Google Display Network</t>
         </is>
       </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>Leaderboard</t>
-        </is>
-      </c>
       <c r="F235" t="inlineStr">
         <is>
           <t>Leaderboard</t>
@@ -12847,11 +11677,6 @@
           <t>Google Display Network</t>
         </is>
       </c>
-      <c r="E236" t="inlineStr">
-        <is>
-          <t>Halfpage</t>
-        </is>
-      </c>
       <c r="F236" t="inlineStr">
         <is>
           <t>Half Page</t>
@@ -12904,11 +11729,6 @@
           <t>Google Display Network</t>
         </is>
       </c>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>Banner</t>
-        </is>
-      </c>
       <c r="F237" t="inlineStr">
         <is>
           <t>Mobile Banner</t>
@@ -12956,11 +11776,6 @@
           <t>Google Display Network</t>
         </is>
       </c>
-      <c r="E238" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
       <c r="F238" t="inlineStr">
         <is>
           <t>Responsive Display Ads (imagem)</t>
@@ -13013,11 +11828,6 @@
           <t>Google Display Network</t>
         </is>
       </c>
-      <c r="E239" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F239" t="inlineStr">
         <is>
           <t>HTML5 Display</t>
@@ -13070,11 +11880,6 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="E240" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
       <c r="F240" t="inlineStr">
         <is>
           <t>Skippable In-Stream</t>
@@ -13127,11 +11932,6 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="E241" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
       <c r="F241" t="inlineStr">
         <is>
           <t>Non-skippable In-Stream (standard)</t>
@@ -13184,11 +11984,6 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="E242" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
       <c r="F242" t="inlineStr">
         <is>
           <t>Bumper</t>
@@ -13241,11 +12036,6 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="E243" t="inlineStr">
-        <is>
-          <t>CTV</t>
-        </is>
-      </c>
       <c r="F243" t="inlineStr">
         <is>
           <t>Non-skippable 30s (Connected TV)</t>
@@ -13298,11 +12088,6 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="E244" t="inlineStr">
-        <is>
-          <t>In-Feed Video</t>
-        </is>
-      </c>
       <c r="F244" t="inlineStr">
         <is>
           <t>In-Feed Video Ad (ex-Discovery)</t>
@@ -13360,11 +12145,6 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="E245" t="inlineStr">
-        <is>
-          <t>Vertical Video</t>
-        </is>
-      </c>
       <c r="F245" t="inlineStr">
         <is>
           <t>YouTube Shorts Ads</t>
@@ -13417,11 +12197,6 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="E246" t="inlineStr">
-        <is>
-          <t>Open Door</t>
-        </is>
-      </c>
       <c r="F246" t="inlineStr">
         <is>
           <t>Masthead</t>
@@ -13474,11 +12249,6 @@
           <t>Google Demand Gen</t>
         </is>
       </c>
-      <c r="E247" t="inlineStr">
-        <is>
-          <t>Single Image</t>
-        </is>
-      </c>
       <c r="F247" t="inlineStr">
         <is>
           <t>Imagem</t>
@@ -13531,11 +12301,6 @@
           <t>Google Demand Gen</t>
         </is>
       </c>
-      <c r="E248" t="inlineStr">
-        <is>
-          <t>Single Video</t>
-        </is>
-      </c>
       <c r="F248" t="inlineStr">
         <is>
           <t>Vídeo</t>
@@ -13588,11 +12353,6 @@
           <t>Google Demand Gen</t>
         </is>
       </c>
-      <c r="E249" t="inlineStr">
-        <is>
-          <t>Carousel</t>
-        </is>
-      </c>
       <c r="F249" t="inlineStr">
         <is>
           <t>Carousel</t>
@@ -13650,11 +12410,6 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>Audio Ad</t>
-        </is>
-      </c>
       <c r="F250" t="inlineStr">
         <is>
           <t>Prog - Audio Ad</t>
@@ -13702,11 +12457,6 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="E251" t="inlineStr">
-        <is>
-          <t>Banner</t>
-        </is>
-      </c>
       <c r="F251" t="inlineStr">
         <is>
           <t>Prog - Standard Banners</t>
@@ -13759,11 +12509,6 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="E252" t="inlineStr">
-        <is>
-          <t>Open Door</t>
-        </is>
-      </c>
       <c r="F252" t="inlineStr">
         <is>
           <t>Prog - YouTube Masthead</t>
@@ -13816,11 +12561,6 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
       <c r="F253" t="inlineStr">
         <is>
           <t>Prog - YouTube Select</t>
@@ -13873,11 +12613,6 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="E254" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
       <c r="F254" t="inlineStr">
         <is>
           <t>Prog - YouTube VRC Ad Sequence</t>
@@ -13930,11 +12665,6 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
       <c r="F255" t="inlineStr">
         <is>
           <t>Prog - YouTube VRC Non-Skippable</t>
@@ -13987,11 +12717,6 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="E256" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
       <c r="F256" t="inlineStr">
         <is>
           <t>Prog - YouTube VVC</t>
@@ -14044,11 +12769,6 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="E257" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
       <c r="F257" t="inlineStr">
         <is>
           <t>Prog - YouTube VRC Efficient Reach</t>
@@ -14101,11 +12821,6 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="E258" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
       <c r="F258" t="inlineStr">
         <is>
           <t>Prog - YouTube VRC Target Frequency</t>
@@ -14158,11 +12873,6 @@
           <t>Google App Campaigns</t>
         </is>
       </c>
-      <c r="E259" t="inlineStr">
-        <is>
-          <t>Single Image</t>
-        </is>
-      </c>
       <c r="F259" t="inlineStr">
         <is>
           <t>Imagem</t>
@@ -14215,11 +12925,6 @@
           <t>Google App Campaigns</t>
         </is>
       </c>
-      <c r="E260" t="inlineStr">
-        <is>
-          <t>Single Video</t>
-        </is>
-      </c>
       <c r="F260" t="inlineStr">
         <is>
           <t>Vídeo</t>
@@ -14272,11 +12977,6 @@
           <t>Google Performance Max</t>
         </is>
       </c>
-      <c r="E261" t="inlineStr">
-        <is>
-          <t>Single Image</t>
-        </is>
-      </c>
       <c r="F261" t="inlineStr">
         <is>
           <t>Imagem</t>
@@ -14329,11 +13029,6 @@
           <t>Google Performance Max</t>
         </is>
       </c>
-      <c r="E262" t="inlineStr">
-        <is>
-          <t>Logo</t>
-        </is>
-      </c>
       <c r="F262" t="inlineStr">
         <is>
           <t>Logo</t>
@@ -14386,11 +13081,6 @@
           <t>Google Performance Max</t>
         </is>
       </c>
-      <c r="E263" t="inlineStr">
-        <is>
-          <t>Single Video</t>
-        </is>
-      </c>
       <c r="F263" t="inlineStr">
         <is>
           <t>Vídeo</t>
@@ -14443,11 +13133,6 @@
           <t>Google Search</t>
         </is>
       </c>
-      <c r="E264" t="inlineStr">
-        <is>
-          <t>Logo</t>
-        </is>
-      </c>
       <c r="F264" t="inlineStr">
         <is>
           <t>Business Information (Logo)</t>
@@ -14500,11 +13185,6 @@
           <t>Google Search</t>
         </is>
       </c>
-      <c r="E265" t="inlineStr">
-        <is>
-          <t>Ad Assets</t>
-        </is>
-      </c>
       <c r="F265" t="inlineStr">
         <is>
           <t>Ad Assets (Imagens)</t>
@@ -14557,11 +13237,6 @@
           <t>Google Search</t>
         </is>
       </c>
-      <c r="E266" t="inlineStr">
-        <is>
-          <t>Responsive Search Ad</t>
-        </is>
-      </c>
       <c r="F266" t="inlineStr">
         <is>
           <t>Responsive Search Ads</t>
@@ -14614,11 +13289,6 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="E267" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
       <c r="F267" t="inlineStr">
         <is>
           <t>Video Action Campaigns</t>
@@ -14676,11 +13346,6 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="E268" t="inlineStr">
-        <is>
-          <t>Thumbnail</t>
-        </is>
-      </c>
       <c r="F268" t="inlineStr">
         <is>
           <t>Thumbnail (vídeo)</t>
@@ -14733,11 +13398,6 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>Companion Banner</t>
-        </is>
-      </c>
       <c r="F269" t="inlineStr">
         <is>
           <t>Companion Banner</t>
@@ -14790,11 +13450,6 @@
           <t>Facebook</t>
         </is>
       </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>Single Image</t>
-        </is>
-      </c>
       <c r="F270" t="inlineStr">
         <is>
           <t>Single Image</t>
@@ -14852,11 +13507,6 @@
           <t>Facebook</t>
         </is>
       </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>Single Video</t>
-        </is>
-      </c>
       <c r="F271" t="inlineStr">
         <is>
           <t>Single Video</t>
@@ -14914,11 +13564,6 @@
           <t>Facebook</t>
         </is>
       </c>
-      <c r="E272" t="inlineStr">
-        <is>
-          <t>Carousel</t>
-        </is>
-      </c>
       <c r="F272" t="inlineStr">
         <is>
           <t>Carousel</t>
@@ -14976,11 +13621,6 @@
           <t>Facebook</t>
         </is>
       </c>
-      <c r="E273" t="inlineStr">
-        <is>
-          <t>Collection</t>
-        </is>
-      </c>
       <c r="F273" t="inlineStr">
         <is>
           <t>Collection</t>
@@ -15038,11 +13678,6 @@
           <t>Instagram</t>
         </is>
       </c>
-      <c r="E274" t="inlineStr">
-        <is>
-          <t>Single Image</t>
-        </is>
-      </c>
       <c r="F274" t="inlineStr">
         <is>
           <t>Single Image</t>
@@ -15100,11 +13735,6 @@
           <t>Instagram</t>
         </is>
       </c>
-      <c r="E275" t="inlineStr">
-        <is>
-          <t>Single Video</t>
-        </is>
-      </c>
       <c r="F275" t="inlineStr">
         <is>
           <t>Single Video</t>
@@ -15162,11 +13792,6 @@
           <t>Instagram</t>
         </is>
       </c>
-      <c r="E276" t="inlineStr">
-        <is>
-          <t>Carousel</t>
-        </is>
-      </c>
       <c r="F276" t="inlineStr">
         <is>
           <t>Carousel</t>
@@ -15224,11 +13849,6 @@
           <t>Instagram</t>
         </is>
       </c>
-      <c r="E277" t="inlineStr">
-        <is>
-          <t>Collection</t>
-        </is>
-      </c>
       <c r="F277" t="inlineStr">
         <is>
           <t>Collection</t>
@@ -15286,11 +13906,6 @@
           <t>Pinterest</t>
         </is>
       </c>
-      <c r="E278" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
       <c r="F278" t="inlineStr">
         <is>
           <t>Idea Ad</t>
@@ -15348,11 +13963,6 @@
           <t>Pinterest</t>
         </is>
       </c>
-      <c r="E279" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
       <c r="F279" t="inlineStr">
         <is>
           <t>Showcase Ad</t>
@@ -15410,11 +14020,6 @@
           <t>Pinterest</t>
         </is>
       </c>
-      <c r="E280" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
       <c r="F280" t="inlineStr">
         <is>
           <t>Quiz Ad</t>
@@ -15472,11 +14077,6 @@
           <t>Snapchat</t>
         </is>
       </c>
-      <c r="E281" t="inlineStr">
-        <is>
-          <t>Branded Effects</t>
-        </is>
-      </c>
       <c r="F281" t="inlineStr">
         <is>
           <t>AR Lenses</t>
@@ -15529,11 +14129,6 @@
           <t>Snapchat</t>
         </is>
       </c>
-      <c r="E282" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
       <c r="F282" t="inlineStr">
         <is>
           <t>Sponsored Snap</t>
@@ -15591,11 +14186,6 @@
           <t>X</t>
         </is>
       </c>
-      <c r="E283" t="inlineStr">
-        <is>
-          <t>Vertical Video</t>
-        </is>
-      </c>
       <c r="F283" t="inlineStr">
         <is>
           <t>Vertical Video Ad</t>
@@ -15643,11 +14233,6 @@
           <t>X</t>
         </is>
       </c>
-      <c r="E284" t="inlineStr">
-        <is>
-          <t>Single Video</t>
-        </is>
-      </c>
       <c r="F284" t="inlineStr">
         <is>
           <t>Amplify Pre-roll</t>
@@ -15710,11 +14295,6 @@
           <t>X</t>
         </is>
       </c>
-      <c r="E285" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
       <c r="F285" t="inlineStr">
         <is>
           <t>X Live</t>
@@ -15767,11 +14347,6 @@
           <t>X</t>
         </is>
       </c>
-      <c r="E286" t="inlineStr">
-        <is>
-          <t>Takeover</t>
-        </is>
-      </c>
       <c r="F286" t="inlineStr">
         <is>
           <t>Timeline Takeover</t>
@@ -15814,11 +14389,6 @@
           <t>X</t>
         </is>
       </c>
-      <c r="E287" t="inlineStr">
-        <is>
-          <t>Takeover</t>
-        </is>
-      </c>
       <c r="F287" t="inlineStr">
         <is>
           <t>Spotlight Takeover</t>
@@ -15876,11 +14446,6 @@
           <t>X</t>
         </is>
       </c>
-      <c r="E288" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
       <c r="F288" t="inlineStr">
         <is>
           <t>Branded Notifications</t>
@@ -15928,11 +14493,6 @@
           <t>X</t>
         </is>
       </c>
-      <c r="E289" t="inlineStr">
-        <is>
-          <t>Catalog Ad</t>
-        </is>
-      </c>
       <c r="F289" t="inlineStr">
         <is>
           <t>Dynamic Product Ads</t>
@@ -15975,11 +14535,6 @@
           <t>X</t>
         </is>
       </c>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
       <c r="F290" t="inlineStr">
         <is>
           <t>Conversation Button</t>
@@ -16022,11 +14577,6 @@
           <t>X</t>
         </is>
       </c>
-      <c r="E291" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
       <c r="F291" t="inlineStr">
         <is>
           <t>Polls</t>
@@ -16074,11 +14624,6 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="E292" t="inlineStr">
-        <is>
-          <t>Companion Banner</t>
-        </is>
-      </c>
       <c r="F292" t="inlineStr">
         <is>
           <t>Prog - Companion Banner (Audio)</t>
@@ -16126,11 +14671,6 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="E293" t="inlineStr">
-        <is>
-          <t>Pre-Roll</t>
-        </is>
-      </c>
       <c r="F293" t="inlineStr">
         <is>
           <t>Prog - Pre-Roll</t>
@@ -16178,11 +14718,6 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="E294" t="inlineStr">
-        <is>
-          <t>CTV</t>
-        </is>
-      </c>
       <c r="F294" t="inlineStr">
         <is>
           <t>Prog - Connected TV</t>
@@ -16230,11 +14765,6 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="E295" t="inlineStr">
-        <is>
-          <t>Companion Banner</t>
-        </is>
-      </c>
       <c r="F295" t="inlineStr">
         <is>
           <t>Prog - Companion Banner (YouTube)</t>
@@ -16339,11 +14869,6 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="E297" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
       <c r="F297" t="inlineStr">
         <is>
           <t>Prog - Rewarded Video</t>
@@ -16391,11 +14916,6 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="E298" t="inlineStr">
-        <is>
-          <t>In-Feed Video</t>
-        </is>
-      </c>
       <c r="F298" t="inlineStr">
         <is>
           <t>Prog - Outstream</t>
@@ -16480,11 +15000,6 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="E300" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
       <c r="F300" t="inlineStr">
         <is>
           <t>Window Splash Vídeo</t>
@@ -16537,11 +15052,6 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="E301" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
       <c r="F301" t="inlineStr">
         <is>
           <t>Intro Full Vídeo</t>
@@ -16594,11 +15104,6 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="E302" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
       <c r="F302" t="inlineStr">
         <is>
           <t>Splash/Intro</t>
@@ -16651,11 +15156,6 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="E303" t="inlineStr">
-        <is>
-          <t>Takeover</t>
-        </is>
-      </c>
       <c r="F303" t="inlineStr">
         <is>
           <t>Vídeo FullScreen TakeOver</t>
@@ -16708,11 +15208,6 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="E304" t="inlineStr">
-        <is>
-          <t>Takeover</t>
-        </is>
-      </c>
       <c r="F304" t="inlineStr">
         <is>
           <t>FullScreen TakeOver</t>
@@ -16765,11 +15260,6 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="E305" t="inlineStr">
-        <is>
-          <t>Takeover</t>
-        </is>
-      </c>
       <c r="F305" t="inlineStr">
         <is>
           <t>TakeOver</t>
@@ -16817,11 +15307,6 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="E306" t="inlineStr">
-        <is>
-          <t>Skin</t>
-        </is>
-      </c>
       <c r="F306" t="inlineStr">
         <is>
           <t>Skin (Imagem)</t>
@@ -16869,11 +15354,6 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="E307" t="inlineStr">
-        <is>
-          <t>Skin</t>
-        </is>
-      </c>
       <c r="F307" t="inlineStr">
         <is>
           <t>Skin Vídeo</t>
@@ -16926,11 +15406,6 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="E308" t="inlineStr">
-        <is>
-          <t>Skin</t>
-        </is>
-      </c>
       <c r="F308" t="inlineStr">
         <is>
           <t>Skin Invertida</t>
@@ -16978,11 +15453,6 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="E309" t="inlineStr">
-        <is>
-          <t>Skin</t>
-        </is>
-      </c>
       <c r="F309" t="inlineStr">
         <is>
           <t>Skin Mobile</t>
@@ -17035,11 +15505,6 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>Parallax</t>
-        </is>
-      </c>
       <c r="F310" t="inlineStr">
         <is>
           <t>Parallax</t>
@@ -17087,11 +15552,6 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="E311" t="inlineStr">
-        <is>
-          <t>Carousel</t>
-        </is>
-      </c>
       <c r="F311" t="inlineStr">
         <is>
           <t>Carrossel</t>
@@ -17134,11 +15594,6 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="E312" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F312" t="inlineStr">
         <is>
           <t>FlipBook Ad</t>
@@ -17191,11 +15646,6 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="E313" t="inlineStr">
-        <is>
-          <t>Cubo</t>
-        </is>
-      </c>
       <c r="F313" t="inlineStr">
         <is>
           <t>Mrec Cubo 3D</t>
@@ -17243,11 +15693,6 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="E314" t="inlineStr">
-        <is>
-          <t>Cubo</t>
-        </is>
-      </c>
       <c r="F314" t="inlineStr">
         <is>
           <t>Half Page Cubo 3D</t>
@@ -17295,11 +15740,6 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="E315" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
       <c r="F315" t="inlineStr">
         <is>
           <t>Ticker Expandido</t>
@@ -17352,11 +15792,6 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="E316" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
       <c r="F316" t="inlineStr">
         <is>
           <t>Spot TV</t>
@@ -17409,11 +15844,6 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="E317" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F317" t="inlineStr">
         <is>
           <t>Flip Ad</t>
@@ -17466,11 +15896,6 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="E318" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F318" t="inlineStr">
         <is>
           <t>Overslide</t>
@@ -17518,11 +15943,6 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="E319" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F319" t="inlineStr">
         <is>
           <t>Layer</t>
@@ -17575,11 +15995,6 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="E320" t="inlineStr">
-        <is>
-          <t>Peel Off</t>
-        </is>
-      </c>
       <c r="F320" t="inlineStr">
         <is>
           <t>Peel Off</t>
@@ -17632,11 +16047,6 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="E321" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F321" t="inlineStr">
         <is>
           <t>Push Down</t>
@@ -17684,11 +16094,6 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="E322" t="inlineStr">
-        <is>
-          <t>Audio Ad</t>
-        </is>
-      </c>
       <c r="F322" t="inlineStr">
         <is>
           <t>Áudio Ad</t>
@@ -17736,11 +16141,6 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="E323" t="inlineStr">
-        <is>
-          <t>Pre-Roll</t>
-        </is>
-      </c>
       <c r="F323" t="inlineStr">
         <is>
           <t>Pre-Roll</t>
@@ -17793,11 +16193,6 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="E324" t="inlineStr">
-        <is>
-          <t>In-Feed Video</t>
-        </is>
-      </c>
       <c r="F324" t="inlineStr">
         <is>
           <t>InContent Sticky</t>
@@ -17850,11 +16245,6 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="E325" t="inlineStr">
-        <is>
-          <t>In-Feed Video</t>
-        </is>
-      </c>
       <c r="F325" t="inlineStr">
         <is>
           <t>InContent</t>
@@ -17907,11 +16297,6 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="E326" t="inlineStr">
-        <is>
-          <t>Billboard</t>
-        </is>
-      </c>
       <c r="F326" t="inlineStr">
         <is>
           <t>Superboard/Billboard</t>
@@ -17959,11 +16344,6 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="E327" t="inlineStr">
-        <is>
-          <t>Mrec</t>
-        </is>
-      </c>
       <c r="F327" t="inlineStr">
         <is>
           <t>Mrec</t>
@@ -18011,11 +16391,6 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="E328" t="inlineStr">
-        <is>
-          <t>Halfpage</t>
-        </is>
-      </c>
       <c r="F328" t="inlineStr">
         <is>
           <t>Half Page</t>
@@ -18063,11 +16438,6 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="E329" t="inlineStr">
-        <is>
-          <t>Header XL</t>
-        </is>
-      </c>
       <c r="F329" t="inlineStr">
         <is>
           <t>Megapub</t>
@@ -18115,11 +16485,6 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="E330" t="inlineStr">
-        <is>
-          <t>Mrec</t>
-        </is>
-      </c>
       <c r="F330" t="inlineStr">
         <is>
           <t>Mrec Vídeo</t>
@@ -18172,11 +16537,6 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="E331" t="inlineStr">
-        <is>
-          <t>Halfpage</t>
-        </is>
-      </c>
       <c r="F331" t="inlineStr">
         <is>
           <t>Half Page Vídeo (Imagem + Vídeo)</t>
@@ -18224,11 +16584,6 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="E332" t="inlineStr">
-        <is>
-          <t>Halfpage</t>
-        </is>
-      </c>
       <c r="F332" t="inlineStr">
         <is>
           <t>Half Page Full Vídeo</t>
@@ -18281,11 +16636,6 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="E333" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
       <c r="F333" t="inlineStr">
         <is>
           <t>Social Card</t>
@@ -18328,11 +16678,6 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="E334" t="inlineStr">
-        <is>
-          <t>Gallery</t>
-        </is>
-      </c>
       <c r="F334" t="inlineStr">
         <is>
           <t>Filmstrip</t>
@@ -18380,11 +16725,6 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="E335" t="inlineStr">
-        <is>
-          <t>Newsletter Banner</t>
-        </is>
-      </c>
       <c r="F335" t="inlineStr">
         <is>
           <t>Newsletter</t>
@@ -18437,11 +16777,6 @@
           <t>WeTransfer</t>
         </is>
       </c>
-      <c r="E336" t="inlineStr">
-        <is>
-          <t>Takeover</t>
-        </is>
-      </c>
       <c r="F336" t="inlineStr">
         <is>
           <t>Static Starter</t>
@@ -18489,11 +16824,6 @@
           <t>Roblox</t>
         </is>
       </c>
-      <c r="E337" t="inlineStr">
-        <is>
-          <t>Banner</t>
-        </is>
-      </c>
       <c r="F337" t="inlineStr">
         <is>
           <t>Display Ads</t>
@@ -18541,11 +16871,6 @@
           <t>OLX</t>
         </is>
       </c>
-      <c r="E338" t="inlineStr">
-        <is>
-          <t>Leaderboard</t>
-        </is>
-      </c>
       <c r="F338" t="inlineStr">
         <is>
           <t>Homepage Leaderboard</t>
@@ -18588,11 +16913,6 @@
           <t>Azerion</t>
         </is>
       </c>
-      <c r="E339" t="inlineStr">
-        <is>
-          <t>Skin</t>
-        </is>
-      </c>
       <c r="F339" t="inlineStr">
         <is>
           <t>Skin</t>
@@ -18635,11 +16955,6 @@
           <t>Azerion</t>
         </is>
       </c>
-      <c r="E340" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
       <c r="F340" t="inlineStr">
         <is>
           <t>Native ad</t>
@@ -18692,11 +17007,6 @@
           <t>Bauer</t>
         </is>
       </c>
-      <c r="E341" t="inlineStr">
-        <is>
-          <t>Leaderboard</t>
-        </is>
-      </c>
       <c r="F341" t="inlineStr">
         <is>
           <t>Leaderboard</t>
@@ -18729,11 +17039,6 @@
           <t>Bauer</t>
         </is>
       </c>
-      <c r="E342" t="inlineStr">
-        <is>
-          <t>Leaderboard</t>
-        </is>
-      </c>
       <c r="F342" t="inlineStr">
         <is>
           <t>Mobile Leaderboard</t>
@@ -18766,11 +17071,6 @@
           <t>Bauer</t>
         </is>
       </c>
-      <c r="E343" t="inlineStr">
-        <is>
-          <t>Mrec</t>
-        </is>
-      </c>
       <c r="F343" t="inlineStr">
         <is>
           <t>MREC (mpu)</t>
@@ -18818,11 +17118,6 @@
           <t>Bauer</t>
         </is>
       </c>
-      <c r="E344" t="inlineStr">
-        <is>
-          <t>Billboard</t>
-        </is>
-      </c>
       <c r="F344" t="inlineStr">
         <is>
           <t>Billboard (desktop)</t>
@@ -18870,11 +17165,6 @@
           <t>Bauer</t>
         </is>
       </c>
-      <c r="E345" t="inlineStr">
-        <is>
-          <t>Billboard</t>
-        </is>
-      </c>
       <c r="F345" t="inlineStr">
         <is>
           <t>Mobile Billboard</t>
@@ -18907,11 +17197,6 @@
           <t>Bauer</t>
         </is>
       </c>
-      <c r="E346" t="inlineStr">
-        <is>
-          <t>Halfpage</t>
-        </is>
-      </c>
       <c r="F346" t="inlineStr">
         <is>
           <t>Halfpage (double mpu)</t>
@@ -18959,11 +17244,6 @@
           <t>Bauer</t>
         </is>
       </c>
-      <c r="E347" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
       <c r="F347" t="inlineStr">
         <is>
           <t>Native</t>
@@ -19001,11 +17281,6 @@
           <t>Bauer</t>
         </is>
       </c>
-      <c r="E348" t="inlineStr">
-        <is>
-          <t>Interscroller</t>
-        </is>
-      </c>
       <c r="F348" t="inlineStr">
         <is>
           <t>Mobile Interscroller</t>
@@ -19043,11 +17318,6 @@
           <t>Bauer</t>
         </is>
       </c>
-      <c r="E349" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F349" t="inlineStr">
         <is>
           <t>Socially Inspired Rich Media</t>
@@ -19085,11 +17355,6 @@
           <t>Bauer</t>
         </is>
       </c>
-      <c r="E350" t="inlineStr">
-        <is>
-          <t>Takeover</t>
-        </is>
-      </c>
       <c r="F350" t="inlineStr">
         <is>
           <t>Standard Takeover</t>
@@ -19132,11 +17397,6 @@
           <t>Bauer</t>
         </is>
       </c>
-      <c r="E351" t="inlineStr">
-        <is>
-          <t>Takeover</t>
-        </is>
-      </c>
       <c r="F351" t="inlineStr">
         <is>
           <t>Hero Takeover</t>
@@ -19179,11 +17439,6 @@
           <t>Bauer</t>
         </is>
       </c>
-      <c r="E352" t="inlineStr">
-        <is>
-          <t>In-Feed Video</t>
-        </is>
-      </c>
       <c r="F352" t="inlineStr">
         <is>
           <t>In-Article Video</t>
@@ -19231,11 +17486,6 @@
           <t>Bauer</t>
         </is>
       </c>
-      <c r="E353" t="inlineStr">
-        <is>
-          <t>Pre-Roll</t>
-        </is>
-      </c>
       <c r="F353" t="inlineStr">
         <is>
           <t>Radio Player Pre-Roll</t>
@@ -19283,11 +17533,6 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="E354" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F354" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Conversacional</t>
@@ -19345,11 +17590,6 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="E355" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F355" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Audiências Game</t>
@@ -19407,11 +17647,6 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="E356" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F356" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Scratch</t>
@@ -19469,11 +17704,6 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="E357" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F357" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Slider Relevância</t>
@@ -19531,11 +17761,6 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="E358" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F358" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Catch Sinais</t>
@@ -19593,11 +17818,6 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="E359" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F359" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Puzzle Logo</t>
@@ -19655,11 +17875,6 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="E360" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F360" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Ligações</t>
@@ -19717,11 +17932,6 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="E361" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F361" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Roda Havas</t>
@@ -19779,11 +17989,6 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="E362" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F362" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Hold Ligação</t>
@@ -19841,11 +18046,6 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="E363" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F363" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Swipe Briefing</t>
@@ -19903,11 +18103,6 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="E364" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F364" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Calculadora Contactos</t>
@@ -19965,11 +18160,6 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="E365" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F365" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Tap Sinais</t>
@@ -20027,11 +18217,6 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="E366" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F366" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Procura na Estratégia</t>
@@ -20089,11 +18274,6 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="E367" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F367" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Método Havas</t>
@@ -20151,11 +18331,6 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="E368" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F368" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Palavra</t>
@@ -20213,11 +18388,6 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="E369" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F369" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Da Marca à Pessoa</t>
@@ -20275,11 +18445,6 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="E370" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F370" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Slot Havas</t>
@@ -20337,11 +18502,6 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="E371" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F371" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Verdade/Mito</t>
@@ -20399,11 +18559,6 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="E372" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F372" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Diferenças</t>
@@ -20461,11 +18616,6 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="E373" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F373" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Enche o Mapa</t>
@@ -20523,11 +18673,6 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="E374" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F374" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Configurador</t>
@@ -20585,11 +18730,6 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="E375" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F375" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Countdown</t>
@@ -20647,11 +18787,6 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="E376" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F376" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Estimativa</t>
@@ -20709,11 +18844,6 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="E377" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F377" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Ranking</t>
@@ -20771,11 +18901,6 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="E378" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F378" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Carrossel Produtos</t>
@@ -20833,11 +18958,6 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="E379" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
       <c r="F379" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Parallax</t>
@@ -28721,11 +26841,6 @@
       <c r="D579" t="inlineStr">
         <is>
           <t>Genérico</t>
-        </is>
-      </c>
-      <c r="E579" t="inlineStr">
-        <is>
-          <t>Branded Content</t>
         </is>
       </c>
       <c r="F579" t="inlineStr">

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M579"/>
+  <dimension ref="A1:M578"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21879,12 +21879,12 @@
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>Spot TV (SD — IMX50)</t>
+          <t>Spot TV (HD — XDCAM HD422)</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>720x576px, 25 fps</t>
+          <t>1920x1080px, 25 fps</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
@@ -21894,7 +21894,7 @@
       </c>
       <c r="J446" t="inlineStr">
         <is>
-          <t>MXF (OP-1a), codec IMX50, 50 Mb/s (CBR), croma 4:2:2, entrelaçado (Interlaced UFF, 16:9FHA), extensão .mxf</t>
+          <t>MXF (OP-1a), codec XDCAM HD422, 50 Mb/s mín. (CBR), croma 4:2:2, entrelaçado (Interlaced UFF), extensão .mxf</t>
         </is>
       </c>
       <c r="L446" t="inlineStr">
@@ -21926,12 +21926,12 @@
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>Spot TV (HD — XDCAM HD422)</t>
+          <t>Ecrã Fracionado / Split Screen</t>
         </is>
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>1920x1080px, 25 fps</t>
+          <t>480x1080px (25% de um ecrã de 1920x1080px), 25 fps</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
@@ -21941,12 +21941,12 @@
       </c>
       <c r="J447" t="inlineStr">
         <is>
-          <t>MXF (OP-1a), codec XDCAM HD422, 50 Mb/s mín. (CBR), croma 4:2:2, entrelaçado (Interlaced UFF), extensão .mxf</t>
+          <t>QuickTime (.MOV), ProRes 4444 (com canal Alpha) ou ProRes 422 (sem Alpha), 1080i entrelaçado (Upper/odd Field First), 25 fps</t>
         </is>
       </c>
       <c r="L447" t="inlineStr">
         <is>
-          <t>Estrutura obrigatória do ficheiro: o conteúdo publicitário deve começar no primeiro frame de vídeo e terminar no último — pre-roll e post-roll de 0 frames, duração do ficheiro = duração do spot x 25 frames. Áudio: PCM, 2 canais (stereo), 24 bit, 48 KHz, peak level -3dB TP máx., loudness (integrado) -23 LUFS. Nomenclatura sugerida para o ficheiro: &lt;Pub ID&gt;_&lt;Nome do Spot&gt;_&lt;Duração&gt;.mxf (ex.: PUB-2015-000345_Fiat 500X Sport Edition_30.mxf) — não é obrigatória, mas recomendada sempre que possível. Entrega exclusivamente por utilizador registado através do Portal GoFastWay (www.gofastway.tv). Todos os ficheiros passam por controlo automático de qualidade (conformidade técnica com estas specs + análise subjetiva de vídeo e áudio); em caso de inconsistência, a GoFastWay pode pedir a entrega de um novo ficheiro corrigido.</t>
+          <t>Conteúdo publicitário que ocupa no máximo 25% do ecrã, transmitido em simultâneo com programas de entretenimento, desporto e magazine. Duração 10″, com entrada e saída incluídas nesses 10″. Sem áudio. Tem de manter a palavra "PUBLICIDADE" com leitura garantida e dentro da Safe Area durante todo o tempo em que está no ar. Entra pela direita do ecrã na TVI e pela esquerda na CNN Portugal. Safe Area geral: 96px horizontais / 54px verticais a partir da margem; Title Safe Area: 192px horizontais / 108px verticais — nenhuma informação relevante deve ficar fora destas áreas.</t>
         </is>
       </c>
     </row>
@@ -21973,12 +21973,12 @@
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>Ecrã Fracionado / Split Screen</t>
+          <t>Telepromoção</t>
         </is>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>480x1080px (25% de um ecrã de 1920x1080px), 25 fps</t>
+          <t>1920x1080px (plasma de estúdio; a zona útil do plasma tem 220px de altura a partir da base do ecrã) e oráculo 1920x1080px</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
@@ -21988,59 +21988,44 @@
       </c>
       <c r="J448" t="inlineStr">
         <is>
-          <t>QuickTime (.MOV), ProRes 4444 (com canal Alpha) ou ProRes 422 (sem Alpha), 1080i entrelaçado (Upper/odd Field First), 25 fps</t>
+          <t>Imagens/grafismos: JPEG, PNG, PSD, AI/EPS (Illustrator versão CC), TIFF ou TGA, todos em resolução HD; ficheiros 3D: C4D (formato ideal), FBX ou OBJ. Vídeo: Formato de vídeo genérico (aplicável salvo indicação em contrário): wrapper MXF OP1a (.MXF), XDCAM HD 4:2:2, 1080i, 25 fps, entrelaçado (Upper/odd Field First), MPEG2 @ 50Mbps, perfil 4:2:2@HL, 1920x1080px, aspect ratio 16:9. Áudio: 8 canais @ 24 bits, PGM nos primeiros dois canais, 48.0 KHz, PCM não comprimido (.wav ou .aiff depois de desembrulhado), nível de referência -20dBFS, loudness -23 LUFS (EBU R.128).</t>
         </is>
       </c>
       <c r="L448" t="inlineStr">
         <is>
-          <t>Conteúdo publicitário que ocupa no máximo 25% do ecrã, transmitido em simultâneo com programas de entretenimento, desporto e magazine. Duração 10″, com entrada e saída incluídas nesses 10″. Sem áudio. Tem de manter a palavra "PUBLICIDADE" com leitura garantida e dentro da Safe Area durante todo o tempo em que está no ar. Entra pela direita do ecrã na TVI e pela esquerda na CNN Portugal. Safe Area geral: 96px horizontais / 54px verticais a partir da margem; Title Safe Area: 192px horizontais / 108px verticais — nenhuma informação relevante deve ficar fora destas áreas.</t>
+          <t>Materiais a fornecer para produção de grafismos, ou grafismos já finalizados — usados no plasma existente no estúdio (para passar vídeos, fotografias ou grafismos) e/ou no oráculo. Devem ser enquadrados dentro das áreas de segurança indicadas para os logos e textos não correrem o risco de serem cortados ou distorcidos (Safe Area geral: 96px horizontais / 54px verticais a partir da margem; Title Safe Area: 192px horizontais / 108px verticais — nenhuma informação relevante deve ficar fora destas áreas. No plasma de estúdio, a zona útil começa a 220px da base do ecrã; no oráculo aplica-se a Title Safe Area). Os guiões para telepromoções de 60″ de duração devem ter entre 730 e 800 caracteres sem espaçamento. Fontes de letra em formato TT, para PC; referências de cor em RGB. Todos os materiais devem ser fornecidos com pelo menos uma semana de antecedência relativamente à data de realização da telepromoção, nos formatos indicados.</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>TV</t>
+          <t>Rádio</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>TV</t>
+          <t>Rádio</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>TV</t>
+          <t>Rádio</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>TV</t>
+          <t>Rádio</t>
         </is>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>Telepromoção</t>
-        </is>
-      </c>
-      <c r="G449" t="inlineStr">
-        <is>
-          <t>1920x1080px (plasma de estúdio; a zona útil do plasma tem 220px de altura a partir da base do ecrã) e oráculo 1920x1080px</t>
-        </is>
-      </c>
-      <c r="H449" t="inlineStr">
-        <is>
-          <t>16:9</t>
+          <t>Spot Rádio</t>
         </is>
       </c>
       <c r="J449" t="inlineStr">
         <is>
-          <t>Imagens/grafismos: JPEG, PNG, PSD, AI/EPS (Illustrator versão CC), TIFF ou TGA, todos em resolução HD; ficheiros 3D: C4D (formato ideal), FBX ou OBJ. Vídeo: Formato de vídeo genérico (aplicável salvo indicação em contrário): wrapper MXF OP1a (.MXF), XDCAM HD 4:2:2, 1080i, 25 fps, entrelaçado (Upper/odd Field First), MPEG2 @ 50Mbps, perfil 4:2:2@HL, 1920x1080px, aspect ratio 16:9. Áudio: 8 canais @ 24 bits, PGM nos primeiros dois canais, 48.0 KHz, PCM não comprimido (.wav ou .aiff depois de desembrulhado), nível de referência -20dBFS, loudness -23 LUFS (EBU R.128).</t>
-        </is>
-      </c>
-      <c r="L449" t="inlineStr">
-        <is>
-          <t>Materiais a fornecer para produção de grafismos, ou grafismos já finalizados — usados no plasma existente no estúdio (para passar vídeos, fotografias ou grafismos) e/ou no oráculo. Devem ser enquadrados dentro das áreas de segurança indicadas para os logos e textos não correrem o risco de serem cortados ou distorcidos (Safe Area geral: 96px horizontais / 54px verticais a partir da margem; Title Safe Area: 192px horizontais / 108px verticais — nenhuma informação relevante deve ficar fora destas áreas. No plasma de estúdio, a zona útil começa a 220px da base do ecrã; no oráculo aplica-se a Title Safe Area). Os guiões para telepromoções de 60″ de duração devem ter entre 730 e 800 caracteres sem espaçamento. Fontes de letra em formato TT, para PC; referências de cor em RGB. Todos os materiais devem ser fornecidos com pelo menos uma semana de antecedência relativamente à data de realização da telepromoção, nos formatos indicados.</t>
+          <t>MP3</t>
         </is>
       </c>
     </row>
@@ -22067,12 +22052,12 @@
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>Spot Rádio</t>
-        </is>
-      </c>
-      <c r="J450" t="inlineStr">
-        <is>
-          <t>MP3</t>
+          <t>Live Copies</t>
+        </is>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>É necessário fornecer um briefing da campanha, incluindo o conceito, as mensagens-chave e o tom de comunicação. A partir desse briefing, a própria rádio desenvolve o guião e produz a conversa entre os animadores, que pode ser realizada em direto ou previamente gravada, sempre com as vozes da estação.</t>
         </is>
       </c>
     </row>
@@ -22099,44 +22084,59 @@
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>Live Copies</t>
+          <t>Referência</t>
         </is>
       </c>
       <c r="L451" t="inlineStr">
         <is>
-          <t>É necessário fornecer um briefing da campanha, incluindo o conceito, as mensagens-chave e o tom de comunicação. A partir desse briefing, a própria rádio desenvolve o guião e produz a conversa entre os animadores, que pode ser realizada em direto ou previamente gravada, sempre com as vozes da estação.</t>
+          <t>É necessário fornecer uma frase curta, com cerca de 5 segundos de duração e uma construção próxima de um slogan de marca, para ser lida em antena pelos animadores da rádio.</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Rádio</t>
+          <t>CINEMA</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Rádio</t>
+          <t>Cinema</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Rádio</t>
+          <t>NOS Publicidade</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>Rádio</t>
+          <t>NOS Publicidade</t>
         </is>
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>Referência</t>
+          <t>Publicidade Cinema 2D</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>Formato de imagem preferencial: FLAT 1.85 — 1998x1080px.</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>1.85:1</t>
+        </is>
+      </c>
+      <c r="J452" t="inlineStr">
+        <is>
+          <t>Ficheiros DATA: sequência de ficheiros DPX 10-bit a 24fps, ou sequência de ficheiros TIFF em RGB. Ficheiros vídeo: QuickTime ProRes a 25fps ou 24fps, com áudio 5.1 ou 2.0 sincronizado à imagem.</t>
         </is>
       </c>
       <c r="L452" t="inlineStr">
         <is>
-          <t>É necessário fornecer uma frase curta, com cerca de 5 segundos de duração e uma construção próxima de um slogan de marca, para ser lida em antena pelos animadores da rádio.</t>
+          <t>Áudio: 6 canais (5.1) ou 2 canais (estéreo); ficheiros WAV a 24-bit; sampling 48KHz; nível de referência -20dBFS; velocidade 24fps. Masterização em Dolby Digital Cinema (VS2.0, certified partner).</t>
         </is>
       </c>
     </row>
@@ -22163,22 +22163,22 @@
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>Publicidade Cinema 2D</t>
+          <t>Publicidade Cinema 3D</t>
         </is>
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>Formato de imagem preferencial: FLAT 1.85 — 1998x1080px.</t>
+          <t>Formato de imagem: FLAT 1.85 — 1998x1080px, ou SCOPE 2.39 — 2048x858px (maior exploração do ecrã).</t>
         </is>
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>1.85:1</t>
+          <t>1.85:1 (FLAT) ou 2.39:1 (SCOPE)</t>
         </is>
       </c>
       <c r="J453" t="inlineStr">
         <is>
-          <t>Ficheiros DATA: sequência de ficheiros DPX 10-bit a 24fps, ou sequência de ficheiros TIFF em RGB. Ficheiros vídeo: QuickTime ProRes a 25fps ou 24fps, com áudio 5.1 ou 2.0 sincronizado à imagem.</t>
+          <t>Ficheiros DATA: dois ficheiros separados (Left eye + Right eye) em sequência, no formato TIFF RGB 16-bit data, ou ficheiros DPX 10-bit — ambos a 24fps.</t>
         </is>
       </c>
       <c r="L453" t="inlineStr">
@@ -22190,47 +22190,37 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>CINEMA</t>
+          <t>Imprensa</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Cinema</t>
+          <t>Imprensa</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>NOS Publicidade</t>
+          <t>Correio da Manhã</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>NOS Publicidade</t>
+          <t>Correio da Manhã</t>
         </is>
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>Publicidade Cinema 3D</t>
+          <t>Página</t>
         </is>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>Formato de imagem: FLAT 1.85 — 1998x1080px, ou SCOPE 2.39 — 2048x858px (maior exploração do ecrã).</t>
-        </is>
-      </c>
-      <c r="H454" t="inlineStr">
-        <is>
-          <t>1.85:1 (FLAT) ou 2.39:1 (SCOPE)</t>
+          <t>257x320mm (80 módulos, 5 col. x 16 mód.)</t>
         </is>
       </c>
       <c r="J454" t="inlineStr">
         <is>
-          <t>Ficheiros DATA: dois ficheiros separados (Left eye + Right eye) em sequência, no formato TIFF RGB 16-bit data, ou ficheiros DPX 10-bit — ambos a 24fps.</t>
-        </is>
-      </c>
-      <c r="L454" t="inlineStr">
-        <is>
-          <t>Áudio: 6 canais (5.1) ou 2 canais (estéreo); ficheiros WAV a 24-bit; sampling 48KHz; nível de referência -20dBFS; velocidade 24fps. Masterização em Dolby Digital Cinema (VS2.0, certified partner).</t>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
     </row>
@@ -22257,12 +22247,12 @@
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>Página</t>
+          <t>Meia Página</t>
         </is>
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>257x320mm (80 módulos, 5 col. x 16 mód.)</t>
+          <t>204x240mm (48 módulos, 4 col. x 12 mód.)</t>
         </is>
       </c>
       <c r="J455" t="inlineStr">
@@ -22294,12 +22284,12 @@
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>Meia Página</t>
+          <t>1/2 Página Alto (3 Col.)</t>
         </is>
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>204x240mm (48 módulos, 4 col. x 12 mód.)</t>
+          <t>153x320mm (48 módulos, 3 col. x 16 mód.)</t>
         </is>
       </c>
       <c r="J456" t="inlineStr">
@@ -22331,12 +22321,12 @@
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>1/2 Página Alto (3 Col.)</t>
+          <t>1/3 Página Alto (2 Col.)</t>
         </is>
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>153x320mm (48 módulos, 3 col. x 16 mód.)</t>
+          <t>100x320mm (32 módulos, 2 col. x 16 mód.)</t>
         </is>
       </c>
       <c r="J457" t="inlineStr">
@@ -22368,12 +22358,12 @@
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>1/3 Página Alto (2 Col.)</t>
+          <t>1/2 Página Baixo</t>
         </is>
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>100x320mm (32 módulos, 2 col. x 16 mód.)</t>
+          <t>257x160mm (40 módulos, 5 col. x 8 mód.)</t>
         </is>
       </c>
       <c r="J458" t="inlineStr">
@@ -22405,12 +22395,12 @@
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>1/2 Página Baixo</t>
+          <t>1/4 Página (3 Col.)</t>
         </is>
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>257x160mm (40 módulos, 5 col. x 8 mód.)</t>
+          <t>153x160mm (24 módulos, 3 col. x 8 mód.)</t>
         </is>
       </c>
       <c r="J459" t="inlineStr">
@@ -22442,12 +22432,12 @@
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>1/4 Página (3 Col.)</t>
+          <t>1/4 Página (2 Col.)</t>
         </is>
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>153x160mm (24 módulos, 3 col. x 8 mód.)</t>
+          <t>100x160mm (16 módulos, 2 col. x 8 mód.)</t>
         </is>
       </c>
       <c r="J460" t="inlineStr">
@@ -22479,12 +22469,12 @@
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t>1/4 Página (2 Col.)</t>
+          <t>Rodapé</t>
         </is>
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>100x160mm (16 módulos, 2 col. x 8 mód.)</t>
+          <t>257x61mm (15 módulos, 5 col. x 3 mód.)</t>
         </is>
       </c>
       <c r="J461" t="inlineStr">
@@ -22511,17 +22501,17 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>Correio da Manhã</t>
+          <t>Mais Sport</t>
         </is>
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>Rodapé</t>
+          <t>Página</t>
         </is>
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>257x61mm (15 módulos, 5 col. x 3 mód.)</t>
+          <t>257x320mm (80 módulos, 5 col. x 16 mód.)</t>
         </is>
       </c>
       <c r="J462" t="inlineStr">
@@ -22548,17 +22538,17 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>Mais Sport</t>
+          <t>Boa Onda</t>
         </is>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>Página</t>
+          <t>Página Dupla</t>
         </is>
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>257x320mm (80 módulos, 5 col. x 16 mód.)</t>
+          <t>400x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J463" t="inlineStr">
@@ -22590,12 +22580,12 @@
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>Página Dupla</t>
+          <t>Página</t>
         </is>
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>400x295mm (+3mm bleed)</t>
+          <t>200x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J464" t="inlineStr">
@@ -22627,12 +22617,12 @@
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>Página</t>
+          <t>1/2 Página Dupla</t>
         </is>
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>200x295mm (+3mm bleed)</t>
+          <t>400x147mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J465" t="inlineStr">
@@ -22664,12 +22654,12 @@
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>1/2 Página Dupla</t>
+          <t>1/2 Página Alto</t>
         </is>
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>400x147mm (+3mm bleed)</t>
+          <t>100x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J466" t="inlineStr">
@@ -22701,12 +22691,12 @@
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>1/2 Página Alto</t>
+          <t>1/2 Página Baixo</t>
         </is>
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>100x295mm (+3mm bleed)</t>
+          <t>200x147mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J467" t="inlineStr">
@@ -22738,12 +22728,12 @@
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>1/2 Página Baixo</t>
+          <t>1/3 Página Alto</t>
         </is>
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>200x147mm (+3mm bleed)</t>
+          <t>72x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J468" t="inlineStr">
@@ -22775,12 +22765,12 @@
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>1/3 Página Alto</t>
+          <t>1/3 Página Baixo</t>
         </is>
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>72x295mm (+3mm bleed)</t>
+          <t>200x105mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J469" t="inlineStr">
@@ -22812,12 +22802,12 @@
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>1/3 Página Baixo</t>
+          <t>1/4 Página</t>
         </is>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>200x105mm (+3mm bleed)</t>
+          <t>100x147mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J470" t="inlineStr">
@@ -22849,12 +22839,12 @@
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>1/4 Página</t>
+          <t>Rodapé</t>
         </is>
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>100x147mm (+3mm bleed)</t>
+          <t>200x78mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J471" t="inlineStr">
@@ -22881,17 +22871,17 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>Boa Onda</t>
+          <t>VIDAS</t>
         </is>
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>Rodapé</t>
+          <t>Página Dupla</t>
         </is>
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>200x78mm (+3mm bleed)</t>
+          <t>400x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J472" t="inlineStr">
@@ -22923,12 +22913,12 @@
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>Página Dupla</t>
+          <t>Página</t>
         </is>
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>400x295mm (+3mm bleed)</t>
+          <t>200x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J473" t="inlineStr">
@@ -22960,12 +22950,12 @@
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>Página</t>
+          <t>1/2 Página Dupla</t>
         </is>
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>200x295mm (+3mm bleed)</t>
+          <t>400x147mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J474" t="inlineStr">
@@ -22997,12 +22987,12 @@
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>1/2 Página Dupla</t>
+          <t>1/2 Página Alto</t>
         </is>
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>400x147mm (+3mm bleed)</t>
+          <t>100x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J475" t="inlineStr">
@@ -23034,12 +23024,12 @@
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>1/2 Página Alto</t>
+          <t>1/2 Página Baixo</t>
         </is>
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>100x295mm (+3mm bleed)</t>
+          <t>200x147mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J476" t="inlineStr">
@@ -23071,12 +23061,12 @@
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>1/2 Página Baixo</t>
+          <t>1/3 Página Alto</t>
         </is>
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>200x147mm (+3mm bleed)</t>
+          <t>72x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J477" t="inlineStr">
@@ -23108,12 +23098,12 @@
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>1/3 Página Alto</t>
+          <t>1/3 Página Baixo</t>
         </is>
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>72x295mm (+3mm bleed)</t>
+          <t>200x105mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J478" t="inlineStr">
@@ -23145,12 +23135,12 @@
       </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>1/3 Página Baixo</t>
+          <t>1/4 Página</t>
         </is>
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>200x105mm (+3mm bleed)</t>
+          <t>100x147mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J479" t="inlineStr">
@@ -23182,12 +23172,12 @@
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>1/4 Página</t>
+          <t>Rodapé</t>
         </is>
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>100x147mm (+3mm bleed)</t>
+          <t>200x78mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J480" t="inlineStr">
@@ -23214,17 +23204,17 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>VIDAS</t>
+          <t>Domingo</t>
         </is>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>Rodapé</t>
+          <t>Página Dupla</t>
         </is>
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>200x78mm (+3mm bleed)</t>
+          <t>400x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J481" t="inlineStr">
@@ -23256,12 +23246,12 @@
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t>Página Dupla</t>
+          <t>Página</t>
         </is>
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>400x295mm (+3mm bleed)</t>
+          <t>200x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J482" t="inlineStr">
@@ -23293,12 +23283,12 @@
       </c>
       <c r="F483" t="inlineStr">
         <is>
-          <t>Página</t>
+          <t>1/2 Página Dupla</t>
         </is>
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>200x295mm (+3mm bleed)</t>
+          <t>400x147mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J483" t="inlineStr">
@@ -23330,12 +23320,12 @@
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t>1/2 Página Dupla</t>
+          <t>1/2 Página Alto</t>
         </is>
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>400x147mm (+3mm bleed)</t>
+          <t>100x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J484" t="inlineStr">
@@ -23367,12 +23357,12 @@
       </c>
       <c r="F485" t="inlineStr">
         <is>
-          <t>1/2 Página Alto</t>
+          <t>1/2 Página Baixo</t>
         </is>
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>100x295mm (+3mm bleed)</t>
+          <t>200x147mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J485" t="inlineStr">
@@ -23404,12 +23394,12 @@
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>1/2 Página Baixo</t>
+          <t>1/3 Página Alto</t>
         </is>
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>200x147mm (+3mm bleed)</t>
+          <t>72x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J486" t="inlineStr">
@@ -23441,12 +23431,12 @@
       </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>1/3 Página Alto</t>
+          <t>1/3 Página Baixo</t>
         </is>
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>72x295mm (+3mm bleed)</t>
+          <t>200x105mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J487" t="inlineStr">
@@ -23478,12 +23468,12 @@
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>1/3 Página Baixo</t>
+          <t>1/4 Página</t>
         </is>
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>200x105mm (+3mm bleed)</t>
+          <t>100x147mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J488" t="inlineStr">
@@ -23515,12 +23505,12 @@
       </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t>1/4 Página</t>
+          <t>Rodapé</t>
         </is>
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>100x147mm (+3mm bleed)</t>
+          <t>200x78mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J489" t="inlineStr">
@@ -23542,27 +23532,27 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Correio da Manhã</t>
+          <t>Destak</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>Domingo</t>
+          <t>Destak</t>
         </is>
       </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t>Rodapé</t>
+          <t>Capa Falsa</t>
         </is>
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>200x78mm (+3mm bleed)</t>
+          <t>210x280mm | 230x300mm (corte)</t>
         </is>
       </c>
       <c r="J490" t="inlineStr">
         <is>
-          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+          <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
         </is>
       </c>
     </row>
@@ -23589,12 +23579,12 @@
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>Capa Falsa</t>
+          <t>Rodapé 1ª Página</t>
         </is>
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>210x280mm | 230x300mm (corte)</t>
+          <t>210x42mm</t>
         </is>
       </c>
       <c r="J491" t="inlineStr">
@@ -23626,12 +23616,12 @@
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>Rodapé 1ª Página</t>
+          <t>Janela Premium</t>
         </is>
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>210x42mm</t>
+          <t>49,5x78,5mm</t>
         </is>
       </c>
       <c r="J492" t="inlineStr">
@@ -23663,12 +23653,12 @@
       </c>
       <c r="F493" t="inlineStr">
         <is>
-          <t>Janela Premium</t>
+          <t>Página Dupla</t>
         </is>
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>49,5x78,5mm</t>
+          <t>440x280mm | 460x300mm (corte)</t>
         </is>
       </c>
       <c r="J493" t="inlineStr">
@@ -23700,12 +23690,12 @@
       </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>Página Dupla</t>
+          <t>Página</t>
         </is>
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>440x280mm | 460x300mm (corte)</t>
+          <t>210x280mm | 230x300mm (corte)</t>
         </is>
       </c>
       <c r="J494" t="inlineStr">
@@ -23737,7 +23727,7 @@
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>Página</t>
+          <t>Contracapa</t>
         </is>
       </c>
       <c r="G495" t="inlineStr">
@@ -23774,12 +23764,12 @@
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>Contracapa</t>
+          <t>1/2 Página Alto</t>
         </is>
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>210x280mm | 230x300mm (corte)</t>
+          <t>103x280mm</t>
         </is>
       </c>
       <c r="J496" t="inlineStr">
@@ -23811,12 +23801,12 @@
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>1/2 Página Alto</t>
+          <t>1/2 Página Baixo</t>
         </is>
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>103x280mm</t>
+          <t>210x138mm</t>
         </is>
       </c>
       <c r="J497" t="inlineStr">
@@ -23848,12 +23838,12 @@
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>1/2 Página Baixo</t>
+          <t>3/4 Página</t>
         </is>
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>210x138mm</t>
+          <t>103x138mm</t>
         </is>
       </c>
       <c r="J498" t="inlineStr">
@@ -23885,12 +23875,12 @@
       </c>
       <c r="F499" t="inlineStr">
         <is>
-          <t>3/4 Página</t>
+          <t>Rodapé</t>
         </is>
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>103x138mm</t>
+          <t>210x42mm</t>
         </is>
       </c>
       <c r="J499" t="inlineStr">
@@ -23912,27 +23902,27 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Destak</t>
+          <t>Jornal de Negócios</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>Destak</t>
+          <t>Jornal de Negócios</t>
         </is>
       </c>
       <c r="F500" t="inlineStr">
         <is>
-          <t>Rodapé</t>
+          <t>Página</t>
         </is>
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>210x42mm</t>
+          <t>257x320mm (80 módulos, 5 col. x 16 mód.)</t>
         </is>
       </c>
       <c r="J500" t="inlineStr">
         <is>
-          <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
     </row>
@@ -23959,12 +23949,12 @@
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>Página</t>
+          <t>Meia Página</t>
         </is>
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>257x320mm (80 módulos, 5 col. x 16 mód.)</t>
+          <t>204x240mm (48 módulos, 4 col. x 12 mód.)</t>
         </is>
       </c>
       <c r="J501" t="inlineStr">
@@ -23996,12 +23986,12 @@
       </c>
       <c r="F502" t="inlineStr">
         <is>
-          <t>Meia Página</t>
+          <t>1/2 Página Alto (3 Col.)</t>
         </is>
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>204x240mm (48 módulos, 4 col. x 12 mód.)</t>
+          <t>153x320mm (48 módulos, 3 col. x 16 mód.)</t>
         </is>
       </c>
       <c r="J502" t="inlineStr">
@@ -24033,12 +24023,12 @@
       </c>
       <c r="F503" t="inlineStr">
         <is>
-          <t>1/2 Página Alto (3 Col.)</t>
+          <t>1/3 Página Alto (2 Col.)</t>
         </is>
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>153x320mm (48 módulos, 3 col. x 16 mód.)</t>
+          <t>100x320mm (32 módulos, 2 col. x 16 mód.)</t>
         </is>
       </c>
       <c r="J503" t="inlineStr">
@@ -24070,12 +24060,12 @@
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>1/3 Página Alto (2 Col.)</t>
+          <t>1/2 Página Baixo</t>
         </is>
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>100x320mm (32 módulos, 2 col. x 16 mód.)</t>
+          <t>257x160mm (40 módulos, 5 col. x 8 mód.)</t>
         </is>
       </c>
       <c r="J504" t="inlineStr">
@@ -24107,12 +24097,12 @@
       </c>
       <c r="F505" t="inlineStr">
         <is>
-          <t>1/2 Página Baixo</t>
+          <t>1/4 Página (3 Col.)</t>
         </is>
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>257x160mm (40 módulos, 5 col. x 8 mód.)</t>
+          <t>153x160mm (24 módulos, 3 col. x 8 mód.)</t>
         </is>
       </c>
       <c r="J505" t="inlineStr">
@@ -24144,12 +24134,12 @@
       </c>
       <c r="F506" t="inlineStr">
         <is>
-          <t>1/4 Página (3 Col.)</t>
+          <t>1/4 Página (2 Col.)</t>
         </is>
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>153x160mm (24 módulos, 3 col. x 8 mód.)</t>
+          <t>100x160mm (16 módulos, 2 col. x 8 mód.)</t>
         </is>
       </c>
       <c r="J506" t="inlineStr">
@@ -24181,12 +24171,12 @@
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>1/4 Página (2 Col.)</t>
+          <t>Rodapé</t>
         </is>
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>100x160mm (16 módulos, 2 col. x 8 mód.)</t>
+          <t>257x61mm (15 módulos, 5 col. x 3 mód.)</t>
         </is>
       </c>
       <c r="J507" t="inlineStr">
@@ -24218,12 +24208,12 @@
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>Rodapé</t>
+          <t>Janela de Primeira Página</t>
         </is>
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>257x61mm (15 módulos, 5 col. x 3 mód.)</t>
+          <t>55x96mm</t>
         </is>
       </c>
       <c r="J508" t="inlineStr">
@@ -24255,12 +24245,12 @@
       </c>
       <c r="F509" t="inlineStr">
         <is>
-          <t>Janela de Primeira Página</t>
+          <t>Orelha de Primeira Página</t>
         </is>
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>55x96mm</t>
+          <t>55x45mm</t>
         </is>
       </c>
       <c r="J509" t="inlineStr">
@@ -24292,12 +24282,12 @@
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>Orelha de Primeira Página</t>
+          <t>Rodapé de Primeira Página</t>
         </is>
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>55x45mm</t>
+          <t>195x25mm</t>
         </is>
       </c>
       <c r="J510" t="inlineStr">
@@ -24329,12 +24319,12 @@
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>Rodapé de Primeira Página</t>
+          <t>Home Page (Quadrado 2ª Página)</t>
         </is>
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>195x25mm</t>
+          <t>150x130mm</t>
         </is>
       </c>
       <c r="J511" t="inlineStr">
@@ -24366,12 +24356,12 @@
       </c>
       <c r="F512" t="inlineStr">
         <is>
-          <t>Home Page (Quadrado 2ª Página)</t>
+          <t>Rodapé Última Página</t>
         </is>
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>150x130mm</t>
+          <t>205x61mm</t>
         </is>
       </c>
       <c r="J512" t="inlineStr">
@@ -24393,22 +24383,22 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Jornal de Negócios</t>
+          <t>Record</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>Jornal de Negócios</t>
+          <t>Record</t>
         </is>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>Rodapé Última Página</t>
+          <t>Página</t>
         </is>
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>205x61mm</t>
+          <t>257x320mm (80 módulos, 5 col. x 16 mód.)</t>
         </is>
       </c>
       <c r="J513" t="inlineStr">
@@ -24440,12 +24430,12 @@
       </c>
       <c r="F514" t="inlineStr">
         <is>
-          <t>Página</t>
+          <t>Meia Página</t>
         </is>
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>257x320mm (80 módulos, 5 col. x 16 mód.)</t>
+          <t>204x240mm (48 módulos, 4 col. x 12 mód.)</t>
         </is>
       </c>
       <c r="J514" t="inlineStr">
@@ -24477,12 +24467,12 @@
       </c>
       <c r="F515" t="inlineStr">
         <is>
-          <t>Meia Página</t>
+          <t>1/2 Página Alto (3 Col.)</t>
         </is>
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>204x240mm (48 módulos, 4 col. x 12 mód.)</t>
+          <t>153x320mm (48 módulos, 3 col. x 16 mód.)</t>
         </is>
       </c>
       <c r="J515" t="inlineStr">
@@ -24514,12 +24504,12 @@
       </c>
       <c r="F516" t="inlineStr">
         <is>
-          <t>1/2 Página Alto (3 Col.)</t>
+          <t>1/3 Página Alto (2 Col.)</t>
         </is>
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>153x320mm (48 módulos, 3 col. x 16 mód.)</t>
+          <t>100x320mm (32 módulos, 2 col. x 16 mód.)</t>
         </is>
       </c>
       <c r="J516" t="inlineStr">
@@ -24551,12 +24541,12 @@
       </c>
       <c r="F517" t="inlineStr">
         <is>
-          <t>1/3 Página Alto (2 Col.)</t>
+          <t>1/2 Página Baixo</t>
         </is>
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>100x320mm (32 módulos, 2 col. x 16 mód.)</t>
+          <t>257x160mm (40 módulos, 5 col. x 8 mód.)</t>
         </is>
       </c>
       <c r="J517" t="inlineStr">
@@ -24588,12 +24578,12 @@
       </c>
       <c r="F518" t="inlineStr">
         <is>
-          <t>1/2 Página Baixo</t>
+          <t>1/4 Página (3 Col.)</t>
         </is>
       </c>
       <c r="G518" t="inlineStr">
         <is>
-          <t>257x160mm (40 módulos, 5 col. x 8 mód.)</t>
+          <t>153x160mm (24 módulos, 3 col. x 8 mód.)</t>
         </is>
       </c>
       <c r="J518" t="inlineStr">
@@ -24625,12 +24615,12 @@
       </c>
       <c r="F519" t="inlineStr">
         <is>
-          <t>1/4 Página (3 Col.)</t>
+          <t>1/4 Página (2 Col.)</t>
         </is>
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>153x160mm (24 módulos, 3 col. x 8 mód.)</t>
+          <t>100x160mm (16 módulos, 2 col. x 8 mód.)</t>
         </is>
       </c>
       <c r="J519" t="inlineStr">
@@ -24662,12 +24652,12 @@
       </c>
       <c r="F520" t="inlineStr">
         <is>
-          <t>1/4 Página (2 Col.)</t>
+          <t>Rodapé</t>
         </is>
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>100x160mm (16 módulos, 2 col. x 8 mód.)</t>
+          <t>257x61mm (15 módulos, 5 col. x 3 mód.)</t>
         </is>
       </c>
       <c r="J520" t="inlineStr">
@@ -24689,22 +24679,22 @@
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Record</t>
+          <t>Sábado</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>Record</t>
+          <t>Sábado</t>
         </is>
       </c>
       <c r="F521" t="inlineStr">
         <is>
-          <t>Rodapé</t>
+          <t>Página Dupla</t>
         </is>
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>257x61mm (15 módulos, 5 col. x 3 mód.)</t>
+          <t>410x275mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J521" t="inlineStr">
@@ -24736,12 +24726,12 @@
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>Página Dupla</t>
+          <t>Página</t>
         </is>
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>410x275mm (+3mm bleed)</t>
+          <t>205x275mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J522" t="inlineStr">
@@ -24773,12 +24763,12 @@
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>Página</t>
+          <t>1/2 Página Dupla</t>
         </is>
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>205x275mm (+3mm bleed)</t>
+          <t>410x137mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J523" t="inlineStr">
@@ -24810,12 +24800,12 @@
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>1/2 Página Dupla</t>
+          <t>1/2 Página Alto</t>
         </is>
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>410x137mm (+3mm bleed)</t>
+          <t>102x275mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J524" t="inlineStr">
@@ -24847,12 +24837,12 @@
       </c>
       <c r="F525" t="inlineStr">
         <is>
-          <t>1/2 Página Alto</t>
+          <t>1/2 Página Baixo</t>
         </is>
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>102x275mm (+3mm bleed)</t>
+          <t>205x137mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J525" t="inlineStr">
@@ -24884,12 +24874,12 @@
       </c>
       <c r="F526" t="inlineStr">
         <is>
-          <t>1/2 Página Baixo</t>
+          <t>1/3 Página Alto</t>
         </is>
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>205x137mm (+3mm bleed)</t>
+          <t>72x275mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J526" t="inlineStr">
@@ -24921,12 +24911,12 @@
       </c>
       <c r="F527" t="inlineStr">
         <is>
-          <t>1/3 Página Alto</t>
+          <t>1/3 Página Baixo</t>
         </is>
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>72x275mm (+3mm bleed)</t>
+          <t>205x91mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J527" t="inlineStr">
@@ -24953,17 +24943,17 @@
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>Sábado</t>
+          <t>Sábado Viajante</t>
         </is>
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>1/3 Página Baixo</t>
+          <t>Página Dupla</t>
         </is>
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>205x91mm (+3mm bleed)</t>
+          <t>410x275mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J528" t="inlineStr">
@@ -24995,12 +24985,12 @@
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>Página Dupla</t>
+          <t>Página</t>
         </is>
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>410x275mm (+3mm bleed)</t>
+          <t>205x275mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J529" t="inlineStr">
@@ -25032,12 +25022,12 @@
       </c>
       <c r="F530" t="inlineStr">
         <is>
-          <t>Página</t>
+          <t>1/2 Página Dupla</t>
         </is>
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>205x275mm (+3mm bleed)</t>
+          <t>410x137mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J530" t="inlineStr">
@@ -25069,12 +25059,12 @@
       </c>
       <c r="F531" t="inlineStr">
         <is>
-          <t>1/2 Página Dupla</t>
+          <t>1/2 Página Alto</t>
         </is>
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>410x137mm (+3mm bleed)</t>
+          <t>102x275mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J531" t="inlineStr">
@@ -25106,12 +25096,12 @@
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>1/2 Página Alto</t>
+          <t>1/2 Página Baixo</t>
         </is>
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>102x275mm (+3mm bleed)</t>
+          <t>205x137mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J532" t="inlineStr">
@@ -25143,12 +25133,12 @@
       </c>
       <c r="F533" t="inlineStr">
         <is>
-          <t>1/2 Página Baixo</t>
+          <t>1/3 Página Alto</t>
         </is>
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>205x137mm (+3mm bleed)</t>
+          <t>72x275mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J533" t="inlineStr">
@@ -25180,12 +25170,12 @@
       </c>
       <c r="F534" t="inlineStr">
         <is>
-          <t>1/3 Página Alto</t>
+          <t>1/3 Página Baixo</t>
         </is>
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>72x275mm (+3mm bleed)</t>
+          <t>205x91mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J534" t="inlineStr">
@@ -25207,22 +25197,22 @@
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>Sábado</t>
+          <t>TV Guia</t>
         </is>
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>Sábado Viajante</t>
+          <t>TV Guia</t>
         </is>
       </c>
       <c r="F535" t="inlineStr">
         <is>
-          <t>1/3 Página Baixo</t>
+          <t>Página Dupla</t>
         </is>
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>205x91mm (+3mm bleed)</t>
+          <t>400x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J535" t="inlineStr">
@@ -25254,12 +25244,12 @@
       </c>
       <c r="F536" t="inlineStr">
         <is>
-          <t>Página Dupla</t>
+          <t>Página</t>
         </is>
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>400x295mm (+3mm bleed)</t>
+          <t>200x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J536" t="inlineStr">
@@ -25291,12 +25281,12 @@
       </c>
       <c r="F537" t="inlineStr">
         <is>
-          <t>Página</t>
+          <t>1/2 Página Dupla</t>
         </is>
       </c>
       <c r="G537" t="inlineStr">
         <is>
-          <t>200x295mm (+3mm bleed)</t>
+          <t>400x147mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J537" t="inlineStr">
@@ -25328,12 +25318,12 @@
       </c>
       <c r="F538" t="inlineStr">
         <is>
-          <t>1/2 Página Dupla</t>
+          <t>1/2 Página Alto</t>
         </is>
       </c>
       <c r="G538" t="inlineStr">
         <is>
-          <t>400x147mm (+3mm bleed)</t>
+          <t>100x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J538" t="inlineStr">
@@ -25365,12 +25355,12 @@
       </c>
       <c r="F539" t="inlineStr">
         <is>
-          <t>1/2 Página Alto</t>
+          <t>1/2 Página Baixo</t>
         </is>
       </c>
       <c r="G539" t="inlineStr">
         <is>
-          <t>100x295mm (+3mm bleed)</t>
+          <t>200x147mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J539" t="inlineStr">
@@ -25402,12 +25392,12 @@
       </c>
       <c r="F540" t="inlineStr">
         <is>
-          <t>1/2 Página Baixo</t>
+          <t>1/3 Página Alto</t>
         </is>
       </c>
       <c r="G540" t="inlineStr">
         <is>
-          <t>200x147mm (+3mm bleed)</t>
+          <t>72x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J540" t="inlineStr">
@@ -25439,12 +25429,12 @@
       </c>
       <c r="F541" t="inlineStr">
         <is>
-          <t>1/3 Página Alto</t>
+          <t>1/3 Página Baixo</t>
         </is>
       </c>
       <c r="G541" t="inlineStr">
         <is>
-          <t>72x295mm (+3mm bleed)</t>
+          <t>200x105mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J541" t="inlineStr">
@@ -25466,27 +25456,27 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>TV Guia</t>
+          <t>Expresso</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>TV Guia</t>
+          <t>Expresso</t>
         </is>
       </c>
       <c r="F542" t="inlineStr">
         <is>
-          <t>1/3 Página Baixo</t>
+          <t>Página Dupla</t>
         </is>
       </c>
       <c r="G542" t="inlineStr">
         <is>
-          <t>200x105mm (+3mm bleed)</t>
+          <t>548x408mm</t>
         </is>
       </c>
       <c r="J542" t="inlineStr">
         <is>
-          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
     </row>
@@ -25513,12 +25503,12 @@
       </c>
       <c r="F543" t="inlineStr">
         <is>
-          <t>Página Dupla</t>
+          <t>Página</t>
         </is>
       </c>
       <c r="G543" t="inlineStr">
         <is>
-          <t>548x408mm</t>
+          <t>264x408mm</t>
         </is>
       </c>
       <c r="J543" t="inlineStr">
@@ -25550,12 +25540,12 @@
       </c>
       <c r="F544" t="inlineStr">
         <is>
-          <t>Página</t>
+          <t>1/2 Página Baixo</t>
         </is>
       </c>
       <c r="G544" t="inlineStr">
         <is>
-          <t>264x408mm</t>
+          <t>264x201,8mm</t>
         </is>
       </c>
       <c r="J544" t="inlineStr">
@@ -25587,12 +25577,12 @@
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>1/2 Página Baixo</t>
+          <t>1/2 Página Alto</t>
         </is>
       </c>
       <c r="G545" t="inlineStr">
         <is>
-          <t>264x201,8mm</t>
+          <t>130x408mm</t>
         </is>
       </c>
       <c r="J545" t="inlineStr">
@@ -25624,12 +25614,12 @@
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t>1/2 Página Alto</t>
+          <t>1/2 Página Dupla</t>
         </is>
       </c>
       <c r="G546" t="inlineStr">
         <is>
-          <t>130x408mm</t>
+          <t>548x201,8mm</t>
         </is>
       </c>
       <c r="J546" t="inlineStr">
@@ -25661,12 +25651,12 @@
       </c>
       <c r="F547" t="inlineStr">
         <is>
-          <t>1/2 Página Dupla</t>
+          <t>Júnior Page</t>
         </is>
       </c>
       <c r="G547" t="inlineStr">
         <is>
-          <t>548x201,8mm</t>
+          <t>174,8x277mm</t>
         </is>
       </c>
       <c r="J547" t="inlineStr">
@@ -25698,12 +25688,12 @@
       </c>
       <c r="F548" t="inlineStr">
         <is>
-          <t>Júnior Page</t>
+          <t>1/4 Página</t>
         </is>
       </c>
       <c r="G548" t="inlineStr">
         <is>
-          <t>174,8x277mm</t>
+          <t>130x201,8mm</t>
         </is>
       </c>
       <c r="J548" t="inlineStr">
@@ -25735,12 +25725,12 @@
       </c>
       <c r="F549" t="inlineStr">
         <is>
-          <t>1/4 Página</t>
+          <t>1/4 Página Landscape</t>
         </is>
       </c>
       <c r="G549" t="inlineStr">
         <is>
-          <t>130x201,8mm</t>
+          <t>264x92,2mm</t>
         </is>
       </c>
       <c r="J549" t="inlineStr">
@@ -25772,12 +25762,12 @@
       </c>
       <c r="F550" t="inlineStr">
         <is>
-          <t>1/4 Página Landscape</t>
+          <t>1/8 Página</t>
         </is>
       </c>
       <c r="G550" t="inlineStr">
         <is>
-          <t>264x92,2mm</t>
+          <t>130x101mm</t>
         </is>
       </c>
       <c r="J550" t="inlineStr">
@@ -25809,12 +25799,12 @@
       </c>
       <c r="F551" t="inlineStr">
         <is>
-          <t>1/8 Página</t>
+          <t>Orelha de Capa</t>
         </is>
       </c>
       <c r="G551" t="inlineStr">
         <is>
-          <t>130x101mm</t>
+          <t>450x60mm</t>
         </is>
       </c>
       <c r="J551" t="inlineStr">
@@ -25846,12 +25836,12 @@
       </c>
       <c r="F552" t="inlineStr">
         <is>
-          <t>Orelha de Capa</t>
+          <t>Sanca de Capa</t>
         </is>
       </c>
       <c r="G552" t="inlineStr">
         <is>
-          <t>450x60mm</t>
+          <t>240x264mm</t>
         </is>
       </c>
       <c r="J552" t="inlineStr">
@@ -25883,17 +25873,17 @@
       </c>
       <c r="F553" t="inlineStr">
         <is>
-          <t>Sanca de Capa</t>
+          <t>Saco Expresso</t>
         </is>
       </c>
       <c r="G553" t="inlineStr">
         <is>
-          <t>240x264mm</t>
+          <t>450x360mm (área útil do cliente: 450x278mm)</t>
         </is>
       </c>
       <c r="J553" t="inlineStr">
         <is>
-          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
+          <t>PDF em alta definição (elementos de desenho em vetorial, imagens à parte + JPEG para visualização)</t>
         </is>
       </c>
     </row>
@@ -25915,22 +25905,22 @@
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>Expresso</t>
+          <t>Expresso Economia</t>
         </is>
       </c>
       <c r="F554" t="inlineStr">
         <is>
-          <t>Saco Expresso</t>
+          <t>Página Dupla</t>
         </is>
       </c>
       <c r="G554" t="inlineStr">
         <is>
-          <t>450x360mm (área útil do cliente: 450x278mm)</t>
+          <t>548x408mm</t>
         </is>
       </c>
       <c r="J554" t="inlineStr">
         <is>
-          <t>PDF em alta definição (elementos de desenho em vetorial, imagens à parte + JPEG para visualização)</t>
+          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
     </row>
@@ -25957,12 +25947,12 @@
       </c>
       <c r="F555" t="inlineStr">
         <is>
-          <t>Página Dupla</t>
+          <t>Página</t>
         </is>
       </c>
       <c r="G555" t="inlineStr">
         <is>
-          <t>548x408mm</t>
+          <t>264x408mm</t>
         </is>
       </c>
       <c r="J555" t="inlineStr">
@@ -25994,12 +25984,12 @@
       </c>
       <c r="F556" t="inlineStr">
         <is>
-          <t>Página</t>
+          <t>1/2 Página Baixo</t>
         </is>
       </c>
       <c r="G556" t="inlineStr">
         <is>
-          <t>264x408mm</t>
+          <t>264x201,8mm</t>
         </is>
       </c>
       <c r="J556" t="inlineStr">
@@ -26031,12 +26021,12 @@
       </c>
       <c r="F557" t="inlineStr">
         <is>
-          <t>1/2 Página Baixo</t>
+          <t>1/2 Página Alto</t>
         </is>
       </c>
       <c r="G557" t="inlineStr">
         <is>
-          <t>264x201,8mm</t>
+          <t>130x408mm</t>
         </is>
       </c>
       <c r="J557" t="inlineStr">
@@ -26068,12 +26058,12 @@
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>1/2 Página Alto</t>
+          <t>1/2 Página Dupla</t>
         </is>
       </c>
       <c r="G558" t="inlineStr">
         <is>
-          <t>130x408mm</t>
+          <t>548x201,8mm</t>
         </is>
       </c>
       <c r="J558" t="inlineStr">
@@ -26105,12 +26095,12 @@
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>1/2 Página Dupla</t>
+          <t>Júnior Page</t>
         </is>
       </c>
       <c r="G559" t="inlineStr">
         <is>
-          <t>548x201,8mm</t>
+          <t>174,8x277mm</t>
         </is>
       </c>
       <c r="J559" t="inlineStr">
@@ -26142,12 +26132,12 @@
       </c>
       <c r="F560" t="inlineStr">
         <is>
-          <t>Júnior Page</t>
+          <t>1/4 Página</t>
         </is>
       </c>
       <c r="G560" t="inlineStr">
         <is>
-          <t>174,8x277mm</t>
+          <t>130x201,8mm</t>
         </is>
       </c>
       <c r="J560" t="inlineStr">
@@ -26179,12 +26169,12 @@
       </c>
       <c r="F561" t="inlineStr">
         <is>
-          <t>1/4 Página</t>
+          <t>1/4 Página Landscape</t>
         </is>
       </c>
       <c r="G561" t="inlineStr">
         <is>
-          <t>130x201,8mm</t>
+          <t>264x92,2mm</t>
         </is>
       </c>
       <c r="J561" t="inlineStr">
@@ -26216,12 +26206,12 @@
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>1/4 Página Landscape</t>
+          <t>1/8 Página</t>
         </is>
       </c>
       <c r="G562" t="inlineStr">
         <is>
-          <t>264x92,2mm</t>
+          <t>130x101mm</t>
         </is>
       </c>
       <c r="J562" t="inlineStr">
@@ -26253,12 +26243,12 @@
       </c>
       <c r="F563" t="inlineStr">
         <is>
-          <t>1/8 Página</t>
+          <t>Orelha (Janela na Primeira Página)</t>
         </is>
       </c>
       <c r="G563" t="inlineStr">
         <is>
-          <t>130x101mm</t>
+          <t>41x32mm</t>
         </is>
       </c>
       <c r="J563" t="inlineStr">
@@ -26290,12 +26280,12 @@
       </c>
       <c r="F564" t="inlineStr">
         <is>
-          <t>Orelha (Janela na Primeira Página)</t>
+          <t>Orelha Grande (Janela na Primeira Página)</t>
         </is>
       </c>
       <c r="G564" t="inlineStr">
         <is>
-          <t>41x32mm</t>
+          <t>41x87mm</t>
         </is>
       </c>
       <c r="J564" t="inlineStr">
@@ -26322,17 +26312,17 @@
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>Expresso Economia</t>
+          <t>Revista E</t>
         </is>
       </c>
       <c r="F565" t="inlineStr">
         <is>
-          <t>Orelha Grande (Janela na Primeira Página)</t>
+          <t>Página Dupla</t>
         </is>
       </c>
       <c r="G565" t="inlineStr">
         <is>
-          <t>41x87mm</t>
+          <t>530x337mm</t>
         </is>
       </c>
       <c r="J565" t="inlineStr">
@@ -26364,12 +26354,12 @@
       </c>
       <c r="F566" t="inlineStr">
         <is>
-          <t>Página Dupla</t>
+          <t>Página</t>
         </is>
       </c>
       <c r="G566" t="inlineStr">
         <is>
-          <t>530x337mm</t>
+          <t>265x337mm</t>
         </is>
       </c>
       <c r="J566" t="inlineStr">
@@ -26401,12 +26391,12 @@
       </c>
       <c r="F567" t="inlineStr">
         <is>
-          <t>Página</t>
+          <t>1/2 Página Baixo</t>
         </is>
       </c>
       <c r="G567" t="inlineStr">
         <is>
-          <t>265x337mm</t>
+          <t>265x167mm</t>
         </is>
       </c>
       <c r="J567" t="inlineStr">
@@ -26438,12 +26428,12 @@
       </c>
       <c r="F568" t="inlineStr">
         <is>
-          <t>1/2 Página Baixo</t>
+          <t>1/2 Página Alto</t>
         </is>
       </c>
       <c r="G568" t="inlineStr">
         <is>
-          <t>265x167mm</t>
+          <t>130x337mm</t>
         </is>
       </c>
       <c r="J568" t="inlineStr">
@@ -26475,12 +26465,12 @@
       </c>
       <c r="F569" t="inlineStr">
         <is>
-          <t>1/2 Página Alto</t>
+          <t>1/3 Página Alto</t>
         </is>
       </c>
       <c r="G569" t="inlineStr">
         <is>
-          <t>130x337mm</t>
+          <t>90x337mm</t>
         </is>
       </c>
       <c r="J569" t="inlineStr">
@@ -26512,12 +26502,12 @@
       </c>
       <c r="F570" t="inlineStr">
         <is>
-          <t>1/3 Página Alto</t>
+          <t>Rodapé</t>
         </is>
       </c>
       <c r="G570" t="inlineStr">
         <is>
-          <t>90x337mm</t>
+          <t>265x108mm</t>
         </is>
       </c>
       <c r="J570" t="inlineStr">
@@ -26549,12 +26539,12 @@
       </c>
       <c r="F571" t="inlineStr">
         <is>
-          <t>Rodapé</t>
+          <t>1/4 Página</t>
         </is>
       </c>
       <c r="G571" t="inlineStr">
         <is>
-          <t>265x108mm</t>
+          <t>115x147mm</t>
         </is>
       </c>
       <c r="J571" t="inlineStr">
@@ -26586,12 +26576,12 @@
       </c>
       <c r="F572" t="inlineStr">
         <is>
-          <t>1/4 Página</t>
+          <t>1/6 Página</t>
         </is>
       </c>
       <c r="G572" t="inlineStr">
         <is>
-          <t>115x147mm</t>
+          <t>75x147mm</t>
         </is>
       </c>
       <c r="J572" t="inlineStr">
@@ -26623,12 +26613,12 @@
       </c>
       <c r="F573" t="inlineStr">
         <is>
-          <t>1/6 Página</t>
+          <t>1/8 Página</t>
         </is>
       </c>
       <c r="G573" t="inlineStr">
         <is>
-          <t>75x147mm</t>
+          <t>115x71mm</t>
         </is>
       </c>
       <c r="J573" t="inlineStr">
@@ -26650,27 +26640,27 @@
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>Expresso</t>
+          <t>Attitude</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>Revista E</t>
+          <t>Attitude</t>
         </is>
       </c>
       <c r="F574" t="inlineStr">
         <is>
-          <t>1/8 Página</t>
+          <t>Página (Par/Ímpar)</t>
         </is>
       </c>
       <c r="G574" t="inlineStr">
         <is>
-          <t>115x71mm</t>
+          <t>215x278mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J574" t="inlineStr">
         <is>
-          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
+          <t>PDF, EPS ou TIFF em alta resolução de 400 DPI (mínimo 300 DPI), CMYK, sem atribuição de perfil final</t>
         </is>
       </c>
     </row>
@@ -26697,12 +26687,12 @@
       </c>
       <c r="F575" t="inlineStr">
         <is>
-          <t>Página (Par/Ímpar)</t>
+          <t>1/2 Página Vertical</t>
         </is>
       </c>
       <c r="G575" t="inlineStr">
         <is>
-          <t>215x278mm (+3mm bleed)</t>
+          <t>106,25x278mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J575" t="inlineStr">
@@ -26734,12 +26724,12 @@
       </c>
       <c r="F576" t="inlineStr">
         <is>
-          <t>1/2 Página Vertical</t>
+          <t>1/2 Página Horizontal</t>
         </is>
       </c>
       <c r="G576" t="inlineStr">
         <is>
-          <t>106,25x278mm (+3mm bleed)</t>
+          <t>215x143mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J576" t="inlineStr">
@@ -26771,12 +26761,12 @@
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>1/2 Página Horizontal</t>
+          <t>Página Dupla</t>
         </is>
       </c>
       <c r="G577" t="inlineStr">
         <is>
-          <t>215x143mm (+3mm bleed)</t>
+          <t>430x278mm (+3mm bleed, +6mm massa central)</t>
         </is>
       </c>
       <c r="J577" t="inlineStr">
@@ -26788,92 +26778,55 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>Imprensa</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Imprensa</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>Attitude</t>
+          <t>Genérico</t>
         </is>
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>Attitude</t>
+          <t>Genérico</t>
         </is>
       </c>
       <c r="F578" t="inlineStr">
         <is>
-          <t>Página Dupla</t>
+          <t>Branded Content</t>
         </is>
       </c>
       <c r="G578" t="inlineStr">
         <is>
-          <t>430x278mm (+3mm bleed, +6mm massa central)</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="J578" t="inlineStr">
         <is>
-          <t>PDF, EPS ou TIFF em alta resolução de 400 DPI (mínimo 300 DPI), CMYK, sem atribuição de perfil final</t>
-        </is>
-      </c>
-    </row>
-    <row r="579">
-      <c r="A579" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B579" t="inlineStr">
-        <is>
-          <t>Internet</t>
-        </is>
-      </c>
-      <c r="C579" t="inlineStr">
-        <is>
-          <t>Genérico</t>
-        </is>
-      </c>
-      <c r="D579" t="inlineStr">
-        <is>
-          <t>Genérico</t>
-        </is>
-      </c>
-      <c r="F579" t="inlineStr">
-        <is>
-          <t>Branded Content</t>
-        </is>
-      </c>
-      <c r="G579" t="inlineStr">
+          <t>Envio de Briefing a detalhar principais mensagens de comunicação + URLs destino dos artigos (caso se aplique) + editáveis da campanha para utilização pelo meio + Imagens estáticas formato 9:16 e 1:1 + MREC (300x250) + Halfpage (300x600) + Outros elementos/imagens considerados importantes</t>
+        </is>
+      </c>
+      <c r="K578" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H579" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I579" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J579" t="inlineStr">
-        <is>
-          <t>Envio de Briefing a detalhar principais mensagens de comunicação + URLs destino dos artigos (caso se aplique) + editáveis da campanha para utilização pelo meio + Imagens estáticas formato 9:16 e 1:1 + MREC (300x250) + Halfpage (300x600) + Outros elementos/imagens considerados importantes</t>
-        </is>
-      </c>
-      <c r="K579" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L579" t="inlineStr">
+      <c r="L578" t="inlineStr">
         <is>
           <t>É necessário enviar:
  - data da publicação?

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M578"/>
+  <dimension ref="A1:M585"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26846,6 +26846,335 @@
         </is>
       </c>
     </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>HomePage Banner</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>512x348px</t>
+        </is>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>Máx. 200KB</t>
+        </is>
+      </c>
+      <c r="J579" t="inlineStr">
+        <is>
+          <t>JPG ou PNG</t>
+        </is>
+      </c>
+      <c r="L579" t="inlineStr">
+        <is>
+          <t>Banner estático (Guapo) no fundo do ecrã principal da app, sempre com uma promoção de pelo menos 20% de desconto. Logo: altura até 150px, largura máx. 500px. Texto: Título obrigatório, máx. 40 carateres (se ocupar 2 linhas, a tagline fica limitada a 1 linha); Tagline opcional, máx. 52 carateres (se ocupar 2 linhas, o título fica limitado a 1 linha); texto "Ad" obrigatório, máx. 13 carateres. Não colocar informação nem elementos importantes nas zonas coloridas do banner — o que lá estiver é cortado ou sobreposto pela seta. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>Food Wall Banner</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>512x348px</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>Máx. 200KB</t>
+        </is>
+      </c>
+      <c r="J580" t="inlineStr">
+        <is>
+          <t>JPG ou PNG</t>
+        </is>
+      </c>
+      <c r="L580" t="inlineStr">
+        <is>
+          <t>Banner estático no meio da loja Food Wall, focado em marcas de comida, sempre com uma promoção. Logo: altura até 150px, largura máx. 500px. Várias cores de fundo sólidas disponíveis. Texto: Título obrigatório, máx. 40 carateres (se ocupar 2 linhas, a tagline fica limitada a 1 linha); Tagline opcional, máx. 52 carateres (se ocupar 2 linhas, o título fica limitado a 1 linha); texto "Ad" obrigatório, máx. 13 carateres. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>In-store Banner</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>750x266px</t>
+        </is>
+      </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>Máx. 200KB</t>
+        </is>
+      </c>
+      <c r="J581" t="inlineStr">
+        <is>
+          <t>JPG ou PNG</t>
+        </is>
+      </c>
+      <c r="L581" t="inlineStr">
+        <is>
+          <t>Banner estático em supermercados ou na parede do Glovo Market ("store wall"), a mostrar a marca de forma visual e a encaminhar para compra direta dos produtos. Fundo sólido. Deixar 30px de margem no topo e na base, para os produtos ficarem todos visíveis na zona central; atenção à seta de CTA no canto inferior direito. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>Shoppable Banner</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>750x422px</t>
+        </is>
+      </c>
+      <c r="I582" t="inlineStr">
+        <is>
+          <t>Máx. 200KB</t>
+        </is>
+      </c>
+      <c r="J582" t="inlineStr">
+        <is>
+          <t>JPG ou PNG</t>
+        </is>
+      </c>
+      <c r="L582" t="inlineStr">
+        <is>
+          <t>Banner localizado dentro de diferentes categorias das lojas (fora da categoria principal da marca), com os produtos a aparecer por baixo do banner — o utilizador pode adicioná-los diretamente ao cesto ou clicar no banner para ir à loja completa. Fundo sólido. Deixar 90px de espaço a partir da margem inferior, onde entram a palavra "Sponsored" e o botão, assim que o banner estiver na app. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>Q-commerce Store Wall Banner</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>512x348px</t>
+        </is>
+      </c>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>Máx. 200KB</t>
+        </is>
+      </c>
+      <c r="J583" t="inlineStr">
+        <is>
+          <t>JPG ou PNG</t>
+        </is>
+      </c>
+      <c r="L583" t="inlineStr">
+        <is>
+          <t>Banner estático nas paredes das lojas de Groceries e Shops (Q-commerce), a mostrar a marca de forma visual e a encaminhar para compra direta dos produtos. Logo: altura até 150px, largura máx. 500px. Várias cores de fundo sólidas disponíveis. Texto: Título obrigatório, máx. 40 carateres (se ocupar 2 linhas, a tagline fica limitada a 1 linha); Tagline opcional, máx. 52 carateres (se ocupar 2 linhas, o título fica limitado a 1 linha); texto "Ad" obrigatório, máx. 13 carateres. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>OTP Premium</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>1280x720px</t>
+        </is>
+      </c>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>Máx. 200KB</t>
+        </is>
+      </c>
+      <c r="J584" t="inlineStr">
+        <is>
+          <t>JPG ou PNG</t>
+        </is>
+      </c>
+      <c r="L584" t="inlineStr">
+        <is>
+          <t>Banner "skippable" (não endémico) que aparece depois de uma compra concluída, assim que o mapa de entrega é mostrado, no fundo do ecrã, com uma secção de texto personalizável. O utilizador pode saltar o anúncio quando quiser. Logo tem de estar incluído na própria imagem do banner. Texto: Título máx. 20 carateres; CTA máx. 10 carateres. Evitar colocar informação importante no canto superior direito — fica sobreposta pelo botão de fechar. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>OTP Standard</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>1280x720px</t>
+        </is>
+      </c>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>Máx. 200KB</t>
+        </is>
+      </c>
+      <c r="J585" t="inlineStr">
+        <is>
+          <t>JPG ou PNG</t>
+        </is>
+      </c>
+      <c r="L585" t="inlineStr">
+        <is>
+          <t>Banner (não endémico) que aparece depois de uma compra concluída, assim que o mapa de entrega é mostrado, e depois de um OTP Premium ter sido saltado ("skipped"). Logo tem de estar incluído na própria imagem do banner. Texto: Título máx. 30 carateres; sem tagline. Várias cores de fundo sólidas disponíveis. Não colocar informação importante nas zonas coloridas do banner — o que lá estiver é cortado ou sobreposto pela seta. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M585"/>
+  <dimension ref="A1:M591"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27175,6 +27175,283 @@
         </is>
       </c>
     </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>Criteo</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>Criteo</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>Criteo - Standard (Imagem)</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>320x50, 300x250, 728x90, 300x600, 160x600, 336x280, 970x250, 320x100, 320x480, 970x90, 468x60, 360x640, 120x600, 250x250, 180x150, 320x568</t>
+        </is>
+      </c>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>Máx. 500 KB</t>
+        </is>
+      </c>
+      <c r="J586" t="inlineStr">
+        <is>
+          <t>JPG ou PNG; GIF animado até 30″</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>Criteo</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>Criteo</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>Criteo - Vídeo</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>16:9, 9:16 ou 1:1</t>
+        </is>
+      </c>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>Máx. 25 MB</t>
+        </is>
+      </c>
+      <c r="J587" t="inlineStr">
+        <is>
+          <t>MP4</t>
+        </is>
+      </c>
+      <c r="L587" t="inlineStr">
+        <is>
+          <t>Duração máx. 30″. Resolução até 720p (ou inferior, se o vídeo original for de qualidade inferior).</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>Criteo</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>Criteo</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>Criteo - Rich Media / Responsivo</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>1200x628px, 1200x1200px ou 800x1200px</t>
+        </is>
+      </c>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="J588" t="inlineStr">
+        <is>
+          <t>PNG ou JPG</t>
+        </is>
+      </c>
+      <c r="L588" t="inlineStr">
+        <is>
+          <t>Engloba os formatos Adaptive, Showcase, Carousel, Cube, Slider, Scroll, Search, Story, Lead Form e Interactive Ads, e os formatos com vídeo elaborados pela equipa de criativo da Criteo a partir das mesmas imagens (Motion Video, Video with Skin, QR Video). Pode incluir vídeo em vez de, ou além da, imagem: MP4, 1:1/16:9/9:16, máx. 25 MB, máx. 30″.</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>Criteo</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>Criteo</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>Criteo - App Install</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>Imagens: 1200x628px, 1200x1200px ou 800x1200px. Logo da app: proporção 1:1.</t>
+        </is>
+      </c>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>1:1, 16:9 ou 9:16 (vídeo)</t>
+        </is>
+      </c>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>Imagem máx. 1 MB; logo da app máx. 50 KB; vídeo máx. 25 MB</t>
+        </is>
+      </c>
+      <c r="J589" t="inlineStr">
+        <is>
+          <t>PNG, JPG ou MP4</t>
+        </is>
+      </c>
+      <c r="L589" t="inlineStr">
+        <is>
+          <t>Vídeo opcional, máx. 30″.</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>Criteo</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>Criteo</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>Criteo - Hero SKU</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>Imagem de produto/branding: 1200x628px, 1200x1200px ou 800x1200px. Imagem de fundo: 300x250, 336x280, 300x600, 320x480, 160x600, 728x90, 970x250 ou 320x50px.</t>
+        </is>
+      </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="J590" t="inlineStr">
+        <is>
+          <t>PNG ou JPG</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>Criteo</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>Criteo</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>Criteo - 3.60</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>1200x628px, 1200x1200px ou 800x1200px — mín. 6 imagens do mesmo produto, em ângulos diferentes.</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>1:1, 2:3 ou 1.91:1</t>
+        </is>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="J591" t="inlineStr">
+        <is>
+          <t>PNG ou JPG</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M591"/>
+  <dimension ref="A1:M602"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27452,6 +27452,358 @@
         </is>
       </c>
     </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>Tap Tap</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>Tap Tap</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>Formato (specs a confirmar)</t>
+        </is>
+      </c>
+      <c r="L592" t="inlineStr">
+        <is>
+          <t>Specs técnicas ainda não disponíveis — substituir esta linha quando a Cláudia enviar os materiais deste fornecedor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>Shopfully</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>Shopfully</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>Formato (specs a confirmar)</t>
+        </is>
+      </c>
+      <c r="L593" t="inlineStr">
+        <is>
+          <t>Specs técnicas ainda não disponíveis — substituir esta linha quando a Cláudia enviar os materiais deste fornecedor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>RTB House</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>RTB House</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>Formato (specs a confirmar)</t>
+        </is>
+      </c>
+      <c r="L594" t="inlineStr">
+        <is>
+          <t>Specs técnicas ainda não disponíveis — substituir esta linha quando a Cláudia enviar os materiais deste fornecedor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>Formato (specs a confirmar)</t>
+        </is>
+      </c>
+      <c r="L595" t="inlineStr">
+        <is>
+          <t>Specs técnicas ainda não disponíveis — substituir esta linha quando a Cláudia enviar os materiais deste fornecedor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>Formato (specs a confirmar)</t>
+        </is>
+      </c>
+      <c r="L596" t="inlineStr">
+        <is>
+          <t>Specs técnicas ainda não disponíveis — substituir esta linha quando a Cláudia enviar os materiais deste fornecedor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>AdsMovil</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>AdsMovil</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>Formato (specs a confirmar)</t>
+        </is>
+      </c>
+      <c r="L597" t="inlineStr">
+        <is>
+          <t>Specs técnicas ainda não disponíveis — substituir esta linha quando a Cláudia enviar os materiais deste fornecedor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>Formato (specs a confirmar)</t>
+        </is>
+      </c>
+      <c r="L598" t="inlineStr">
+        <is>
+          <t>Specs técnicas ainda não disponíveis — substituir esta linha quando a Cláudia enviar os materiais deste fornecedor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>EXTE</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>EXTE</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>Formato (specs a confirmar)</t>
+        </is>
+      </c>
+      <c r="L599" t="inlineStr">
+        <is>
+          <t>Specs técnicas ainda não disponíveis — substituir esta linha quando a Cláudia enviar os materiais deste fornecedor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>Oxy</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>Oxy</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>Formato (specs a confirmar)</t>
+        </is>
+      </c>
+      <c r="L600" t="inlineStr">
+        <is>
+          <t>Specs técnicas ainda não disponíveis — substituir esta linha quando a Cláudia enviar os materiais deste fornecedor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>Suebi</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>Suebi</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>Formato (specs a confirmar)</t>
+        </is>
+      </c>
+      <c r="L601" t="inlineStr">
+        <is>
+          <t>Specs técnicas ainda não disponíveis — substituir esta linha quando a Cláudia enviar os materiais deste fornecedor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>ClickProfit</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>ClickProfit</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>Formato (specs a confirmar)</t>
+        </is>
+      </c>
+      <c r="L602" t="inlineStr">
+        <is>
+          <t>Specs técnicas ainda não disponíveis — substituir esta linha quando a Cláudia enviar os materiais deste fornecedor.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M602"/>
+  <dimension ref="A1:M608"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27790,17 +27790,269 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
+          <t>Forretas e Descontos (Homepage)</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>Moldura (barra lateral direita)</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>200x700</t>
+        </is>
+      </c>
+      <c r="J602" t="inlineStr">
+        <is>
+          <t>JPEG, GIF ou PNG + fontes usadas</t>
+        </is>
+      </c>
+      <c r="L602" t="inlineStr">
+        <is>
+          <t>O Take Over é composto por 3 peças: barra lateral direita, barra lateral esquerda e topo. Prazo de entrega dos materiais: 72h úteis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
           <t>ClickProfit</t>
         </is>
       </c>
-      <c r="F602" t="inlineStr">
-        <is>
-          <t>Formato (specs a confirmar)</t>
-        </is>
-      </c>
-      <c r="L602" t="inlineStr">
-        <is>
-          <t>Specs técnicas ainda não disponíveis — substituir esta linha quando a Cláudia enviar os materiais deste fornecedor.</t>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>Forretas e Descontos (Homepage)</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>Moldura (barra lateral esquerda)</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>200x700</t>
+        </is>
+      </c>
+      <c r="J603" t="inlineStr">
+        <is>
+          <t>JPEG, GIF ou PNG + fontes usadas</t>
+        </is>
+      </c>
+      <c r="L603" t="inlineStr">
+        <is>
+          <t>O Take Over é composto por 3 peças: barra lateral direita, barra lateral esquerda e topo. Prazo de entrega dos materiais: 72h úteis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>ClickProfit</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>Descontos (Homepage)</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>Moldura (topo)</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>940x120</t>
+        </is>
+      </c>
+      <c r="J604" t="inlineStr">
+        <is>
+          <t>JPEG, GIF ou PNG + fontes usadas</t>
+        </is>
+      </c>
+      <c r="L604" t="inlineStr">
+        <is>
+          <t>O topo tem de ter em conta os elementos fixos do site, que não serão sobrepostos. Prazo de entrega dos materiais: 72h úteis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>ClickProfit</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>Forretas (Homepage)</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>Moldura (topo)</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>1920x313</t>
+        </is>
+      </c>
+      <c r="J605" t="inlineStr">
+        <is>
+          <t>JPEG, GIF ou PNG + fontes usadas</t>
+        </is>
+      </c>
+      <c r="L605" t="inlineStr">
+        <is>
+          <t>O topo tem de ter em conta os elementos fixos do site, que não serão sobrepostos. Prazo de entrega dos materiais: 72h úteis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>ClickProfit</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>Descontos</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>Imagem Oferta e Native Ad — Cupão</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>468x351</t>
+        </is>
+      </c>
+      <c r="J606" t="inlineStr">
+        <is>
+          <t>JPEG ou PNG</t>
+        </is>
+      </c>
+      <c r="L606" t="inlineStr">
+        <is>
+          <t>Imagem identificativa da oferta. Prazo de entrega dos materiais: 72h úteis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>ClickProfit</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>ClickProfit</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>HTML (Email)</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>600 ou 700px de largura; altura ao critério do cliente</t>
+        </is>
+      </c>
+      <c r="J607" t="inlineStr">
+        <is>
+          <t>HTML + imagens em JPG ou PNG</t>
+        </is>
+      </c>
+      <c r="L607" t="inlineStr">
+        <is>
+          <t>Enviar subject e sender. Prazo de entrega dos materiais: 72h úteis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>ClickProfit</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>ClickProfit</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>SMS</t>
+        </is>
+      </c>
+      <c r="L608" t="inlineStr">
+        <is>
+          <t>Sender: máx. 11 carateres. Copy: máx. 160 carateres (inclui espaços, pontuação e o link de unsubscribe usado pela ClickProfit — bit.ly/ChB_); sobram 142 carateres para o anunciante, podendo incluir um link (que a ClickProfit converte depois em bit.ly — esse link também conta para os 142 carateres). Enviar números de telemóvel para envio de SMS de teste. Prazo de entrega dos materiais: 72h úteis.</t>
         </is>
       </c>
     </row>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M608"/>
+  <dimension ref="A1:M616"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27657,12 +27657,12 @@
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>Taboola</t>
+          <t>EXTE</t>
         </is>
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>Taboola</t>
+          <t>EXTE</t>
         </is>
       </c>
       <c r="F598" t="inlineStr">
@@ -27684,17 +27684,17 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>EXTE</t>
+          <t>Oxy</t>
         </is>
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>EXTE</t>
+          <t>Oxy</t>
         </is>
       </c>
       <c r="F599" t="inlineStr">
@@ -27721,12 +27721,12 @@
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>Oxy</t>
+          <t>Suebi</t>
         </is>
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>Oxy</t>
+          <t>Suebi</t>
         </is>
       </c>
       <c r="F600" t="inlineStr">
@@ -27753,22 +27753,32 @@
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>Suebi</t>
+          <t>ClickProfit</t>
         </is>
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>Suebi</t>
+          <t>Forretas e Descontos (Homepage)</t>
         </is>
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>Formato (specs a confirmar)</t>
+          <t>Moldura (barra lateral direita)</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>200x700</t>
+        </is>
+      </c>
+      <c r="J601" t="inlineStr">
+        <is>
+          <t>JPEG, GIF ou PNG + fontes usadas</t>
         </is>
       </c>
       <c r="L601" t="inlineStr">
         <is>
-          <t>Specs técnicas ainda não disponíveis — substituir esta linha quando a Cláudia enviar os materiais deste fornecedor.</t>
+          <t>O Take Over é composto por 3 peças: barra lateral direita, barra lateral esquerda e topo. Prazo de entrega dos materiais: 72h úteis.</t>
         </is>
       </c>
     </row>
@@ -27795,7 +27805,7 @@
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>Moldura (barra lateral direita)</t>
+          <t>Moldura (barra lateral esquerda)</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
@@ -27832,17 +27842,17 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>Forretas e Descontos (Homepage)</t>
+          <t>Descontos (Homepage)</t>
         </is>
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>Moldura (barra lateral esquerda)</t>
+          <t>Moldura (topo)</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>200x700</t>
+          <t>940x120</t>
         </is>
       </c>
       <c r="J603" t="inlineStr">
@@ -27852,7 +27862,7 @@
       </c>
       <c r="L603" t="inlineStr">
         <is>
-          <t>O Take Over é composto por 3 peças: barra lateral direita, barra lateral esquerda e topo. Prazo de entrega dos materiais: 72h úteis.</t>
+          <t>O topo tem de ter em conta os elementos fixos do site, que não serão sobrepostos. Prazo de entrega dos materiais: 72h úteis.</t>
         </is>
       </c>
     </row>
@@ -27874,7 +27884,7 @@
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>Descontos (Homepage)</t>
+          <t>Forretas (Homepage)</t>
         </is>
       </c>
       <c r="F604" t="inlineStr">
@@ -27884,7 +27894,7 @@
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>940x120</t>
+          <t>1920x313</t>
         </is>
       </c>
       <c r="J604" t="inlineStr">
@@ -27916,27 +27926,27 @@
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>Forretas (Homepage)</t>
+          <t>Descontos</t>
         </is>
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>Moldura (topo)</t>
+          <t>Imagem Oferta e Native Ad — Cupão</t>
         </is>
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>1920x313</t>
+          <t>468x351</t>
         </is>
       </c>
       <c r="J605" t="inlineStr">
         <is>
-          <t>JPEG, GIF ou PNG + fontes usadas</t>
+          <t>JPEG ou PNG</t>
         </is>
       </c>
       <c r="L605" t="inlineStr">
         <is>
-          <t>O topo tem de ter em conta os elementos fixos do site, que não serão sobrepostos. Prazo de entrega dos materiais: 72h úteis.</t>
+          <t>Imagem identificativa da oferta. Prazo de entrega dos materiais: 72h úteis.</t>
         </is>
       </c>
     </row>
@@ -27958,27 +27968,27 @@
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>Descontos</t>
+          <t>ClickProfit</t>
         </is>
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>Imagem Oferta e Native Ad — Cupão</t>
+          <t>HTML (Email)</t>
         </is>
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>468x351</t>
+          <t>600 ou 700px de largura; altura ao critério do cliente</t>
         </is>
       </c>
       <c r="J606" t="inlineStr">
         <is>
-          <t>JPEG ou PNG</t>
+          <t>HTML + imagens em JPG ou PNG</t>
         </is>
       </c>
       <c r="L606" t="inlineStr">
         <is>
-          <t>Imagem identificativa da oferta. Prazo de entrega dos materiais: 72h úteis.</t>
+          <t>Enviar subject e sender. Prazo de entrega dos materiais: 72h úteis.</t>
         </is>
       </c>
     </row>
@@ -28005,54 +28015,405 @@
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>HTML (Email)</t>
-        </is>
-      </c>
-      <c r="G607" t="inlineStr">
-        <is>
-          <t>600 ou 700px de largura; altura ao critério do cliente</t>
-        </is>
-      </c>
-      <c r="J607" t="inlineStr">
-        <is>
-          <t>HTML + imagens em JPG ou PNG</t>
+          <t>SMS</t>
         </is>
       </c>
       <c r="L607" t="inlineStr">
         <is>
-          <t>Enviar subject e sender. Prazo de entrega dos materiais: 72h úteis.</t>
+          <t>Sender: máx. 11 carateres. Copy: máx. 160 carateres (inclui espaços, pontuação e o link de unsubscribe usado pela ClickProfit — bit.ly/ChB_); sobram 142 carateres para o anunciante, podendo incluir um link (que a ClickProfit converte depois em bit.ly — esse link também conta para os 142 carateres). Enviar números de telemóvel para envio de SMS de teste. Prazo de entrega dos materiais: 72h úteis.</t>
         </is>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>INTERNET</t>
+          <t>PROGRAMÁTICO</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Programático</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>ClickProfit</t>
+          <t>Taboola</t>
         </is>
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>ClickProfit</t>
+          <t>Taboola</t>
         </is>
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>SMS</t>
+          <t>Taboola - Native Ads (Imagem)</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>1200x674 (recomendado); mín. 400x350</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>16:9 (preferencial), 4:3 ou 1:1</t>
+        </is>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>Máx. 5 MB</t>
+        </is>
+      </c>
+      <c r="J608" t="inlineStr">
+        <is>
+          <t>JPEG (preferencial), BMP, PNG, WBMP ou GIF</t>
         </is>
       </c>
       <c r="L608" t="inlineStr">
         <is>
-          <t>Sender: máx. 11 carateres. Copy: máx. 160 carateres (inclui espaços, pontuação e o link de unsubscribe usado pela ClickProfit — bit.ly/ChB_); sobram 142 carateres para o anunciante, podendo incluir um link (que a ClickProfit converte depois em bit.ly — esse link também conta para os 142 carateres). Enviar números de telemóvel para envio de SMS de teste. Prazo de entrega dos materiais: 72h úteis.</t>
+          <t>Título: 34-45 carateres (ideal), máx. 60. Descrição: 180 (ideal), máx. 250. Texto de marca: máx. 30 carateres.</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>Taboola - Motion Ads (Vídeo)</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>1067x600</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>Máx. 50 MB (GIF: máx. 5 MB)</t>
+        </is>
+      </c>
+      <c r="J609" t="inlineStr">
+        <is>
+          <t>MP4, MOV ou GIF</t>
+        </is>
+      </c>
+      <c r="L609" t="inlineStr">
+        <is>
+          <t>Duração máx. 15″. Título: 34-45 carateres (ideal), máx. 60. Texto de marca: máx. 30 carateres.</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>Taboola - Display Hosted (Imagem)</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>Tamanhos standard IAB: 300x250, 300x600, 320x50, 728x90, 970x250, 160x600 ou 250x250</t>
+        </is>
+      </c>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>Máx. 2 MB</t>
+        </is>
+      </c>
+      <c r="J610" t="inlineStr">
+        <is>
+          <t>JPEG, JPG, PNG ou GIF</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>Taboola - Display Hosted (Vídeo)</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>Tamanhos standard IAB: 300x250, 300x600, 320x50, 728x90, 970x250, 160x600 ou 250x250</t>
+        </is>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>Máx. 200 MB</t>
+        </is>
+      </c>
+      <c r="J611" t="inlineStr">
+        <is>
+          <t>MP4</t>
+        </is>
+      </c>
+      <c r="L611" t="inlineStr">
+        <is>
+          <t>Duração: 5 a 30″. Pode incluir áudio (vídeo arranca sem som; o utilizador pode ativar).</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>Taboola - Display Hosted (HTML5)</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>Tamanhos standard IAB: 300x250, 300x600, 320x50, 728x90, 970x250, 160x600 ou 250x250</t>
+        </is>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>Máx. 2 MB (ZIP comprimido)</t>
+        </is>
+      </c>
+      <c r="J612" t="inlineStr">
+        <is>
+          <t>ZIP (HTML, JS, CSS, JPG, JPEG, GIF, PNG, SVG; máx. 100 ficheiros); index.html na raiz</t>
+        </is>
+      </c>
+      <c r="L612" t="inlineStr">
+        <is>
+          <t>Tem de incluir uma imagem estática de recurso (JPG, PNG ou GIF) para browsers sem JavaScript.</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>Taboola - Display (Tag de 3ºs)</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>Tamanhos standard IAB: 300x250, 300x600, 320x50, 728x90, 970x250, 160x600 ou 250x250</t>
+        </is>
+      </c>
+      <c r="L613" t="inlineStr">
+        <is>
+          <t>Ad servers aceites: DCM e Adform. Macros de clique obrigatórias quando a tag não é reconhecida automaticamente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>Taboola - Carousel</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>1200x627</t>
+        </is>
+      </c>
+      <c r="L614" t="inlineStr">
+        <is>
+          <t>Mín. 3 e máx. 5 cartões. Por cartão: imagem, título (máx. 50 carateres), descrição (máx. 150 carateres), CTA e URL de destino (pode variar por cartão). Suporta GIF/vídeo nos cartões.</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>Taboola - Social Importer (Facebook/Instagram)</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>300x250 ou 300x600</t>
+        </is>
+      </c>
+      <c r="L615" t="inlineStr">
+        <is>
+          <t>Anúncio importado diretamente do Facebook/Instagram a partir do ID da Meta Ad Library (16 dígitos) — não editável, aparece exatamente como no social.</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>Taboola - Vertical</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>4:5, 9:16 ou 1:2</t>
+        </is>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>Máx. 5 MB</t>
+        </is>
+      </c>
+      <c r="J616" t="inlineStr">
+        <is>
+          <t>JPG ou PNG</t>
         </is>
       </c>
     </row>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M616"/>
+  <dimension ref="A1:M618"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27721,22 +27721,32 @@
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>Suebi</t>
+          <t>ClickProfit</t>
         </is>
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>Suebi</t>
+          <t>Forretas e Descontos (Homepage)</t>
         </is>
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>Formato (specs a confirmar)</t>
+          <t>Moldura (barra lateral direita)</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>200x700</t>
+        </is>
+      </c>
+      <c r="J600" t="inlineStr">
+        <is>
+          <t>JPEG, GIF ou PNG + fontes usadas</t>
         </is>
       </c>
       <c r="L600" t="inlineStr">
         <is>
-          <t>Specs técnicas ainda não disponíveis — substituir esta linha quando a Cláudia enviar os materiais deste fornecedor.</t>
+          <t>O Take Over é composto por 3 peças: barra lateral direita, barra lateral esquerda e topo. Prazo de entrega dos materiais: 72h úteis.</t>
         </is>
       </c>
     </row>
@@ -27763,7 +27773,7 @@
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>Moldura (barra lateral direita)</t>
+          <t>Moldura (barra lateral esquerda)</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
@@ -27800,17 +27810,17 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>Forretas e Descontos (Homepage)</t>
+          <t>Descontos (Homepage)</t>
         </is>
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>Moldura (barra lateral esquerda)</t>
+          <t>Moldura (topo)</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>200x700</t>
+          <t>940x120</t>
         </is>
       </c>
       <c r="J602" t="inlineStr">
@@ -27820,7 +27830,7 @@
       </c>
       <c r="L602" t="inlineStr">
         <is>
-          <t>O Take Over é composto por 3 peças: barra lateral direita, barra lateral esquerda e topo. Prazo de entrega dos materiais: 72h úteis.</t>
+          <t>O topo tem de ter em conta os elementos fixos do site, que não serão sobrepostos. Prazo de entrega dos materiais: 72h úteis.</t>
         </is>
       </c>
     </row>
@@ -27842,7 +27852,7 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>Descontos (Homepage)</t>
+          <t>Forretas (Homepage)</t>
         </is>
       </c>
       <c r="F603" t="inlineStr">
@@ -27852,7 +27862,7 @@
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>940x120</t>
+          <t>1920x313</t>
         </is>
       </c>
       <c r="J603" t="inlineStr">
@@ -27884,27 +27894,27 @@
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>Forretas (Homepage)</t>
+          <t>Descontos</t>
         </is>
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>Moldura (topo)</t>
+          <t>Imagem Oferta e Native Ad — Cupão</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>1920x313</t>
+          <t>468x351</t>
         </is>
       </c>
       <c r="J604" t="inlineStr">
         <is>
-          <t>JPEG, GIF ou PNG + fontes usadas</t>
+          <t>JPEG ou PNG</t>
         </is>
       </c>
       <c r="L604" t="inlineStr">
         <is>
-          <t>O topo tem de ter em conta os elementos fixos do site, que não serão sobrepostos. Prazo de entrega dos materiais: 72h úteis.</t>
+          <t>Imagem identificativa da oferta. Prazo de entrega dos materiais: 72h úteis.</t>
         </is>
       </c>
     </row>
@@ -27926,27 +27936,27 @@
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>Descontos</t>
+          <t>ClickProfit</t>
         </is>
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>Imagem Oferta e Native Ad — Cupão</t>
+          <t>HTML (Email)</t>
         </is>
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>468x351</t>
+          <t>600 ou 700px de largura; altura ao critério do cliente</t>
         </is>
       </c>
       <c r="J605" t="inlineStr">
         <is>
-          <t>JPEG ou PNG</t>
+          <t>HTML + imagens em JPG ou PNG</t>
         </is>
       </c>
       <c r="L605" t="inlineStr">
         <is>
-          <t>Imagem identificativa da oferta. Prazo de entrega dos materiais: 72h úteis.</t>
+          <t>Enviar subject e sender. Prazo de entrega dos materiais: 72h úteis.</t>
         </is>
       </c>
     </row>
@@ -27973,54 +27983,64 @@
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>HTML (Email)</t>
-        </is>
-      </c>
-      <c r="G606" t="inlineStr">
-        <is>
-          <t>600 ou 700px de largura; altura ao critério do cliente</t>
-        </is>
-      </c>
-      <c r="J606" t="inlineStr">
-        <is>
-          <t>HTML + imagens em JPG ou PNG</t>
+          <t>SMS</t>
         </is>
       </c>
       <c r="L606" t="inlineStr">
         <is>
-          <t>Enviar subject e sender. Prazo de entrega dos materiais: 72h úteis.</t>
+          <t>Sender: máx. 11 carateres. Copy: máx. 160 carateres (inclui espaços, pontuação e o link de unsubscribe usado pela ClickProfit — bit.ly/ChB_); sobram 142 carateres para o anunciante, podendo incluir um link (que a ClickProfit converte depois em bit.ly — esse link também conta para os 142 carateres). Enviar números de telemóvel para envio de SMS de teste. Prazo de entrega dos materiais: 72h úteis.</t>
         </is>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>INTERNET</t>
+          <t>PROGRAMÁTICO</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Programático</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>ClickProfit</t>
+          <t>Taboola</t>
         </is>
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>ClickProfit</t>
+          <t>Taboola</t>
         </is>
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>SMS</t>
+          <t>Taboola - Native Ads (Imagem)</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>1200x674 (recomendado); mín. 400x350</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>16:9 (preferencial), 4:3 ou 1:1</t>
+        </is>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>Máx. 5 MB</t>
+        </is>
+      </c>
+      <c r="J607" t="inlineStr">
+        <is>
+          <t>JPEG (preferencial), BMP, PNG, WBMP ou GIF</t>
         </is>
       </c>
       <c r="L607" t="inlineStr">
         <is>
-          <t>Sender: máx. 11 carateres. Copy: máx. 160 carateres (inclui espaços, pontuação e o link de unsubscribe usado pela ClickProfit — bit.ly/ChB_); sobram 142 carateres para o anunciante, podendo incluir um link (que a ClickProfit converte depois em bit.ly — esse link também conta para os 142 carateres). Enviar números de telemóvel para envio de SMS de teste. Prazo de entrega dos materiais: 72h úteis.</t>
+          <t>Título: 34-45 carateres (ideal), máx. 60. Descrição: 180 (ideal), máx. 250. Texto de marca: máx. 30 carateres.</t>
         </is>
       </c>
     </row>
@@ -28047,32 +28067,32 @@
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>Taboola - Native Ads (Imagem)</t>
+          <t>Taboola - Motion Ads (Vídeo)</t>
         </is>
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>1200x674 (recomendado); mín. 400x350</t>
+          <t>1067x600</t>
         </is>
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>16:9 (preferencial), 4:3 ou 1:1</t>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I608" t="inlineStr">
         <is>
-          <t>Máx. 5 MB</t>
+          <t>Máx. 50 MB (GIF: máx. 5 MB)</t>
         </is>
       </c>
       <c r="J608" t="inlineStr">
         <is>
-          <t>JPEG (preferencial), BMP, PNG, WBMP ou GIF</t>
+          <t>MP4, MOV ou GIF</t>
         </is>
       </c>
       <c r="L608" t="inlineStr">
         <is>
-          <t>Título: 34-45 carateres (ideal), máx. 60. Descrição: 180 (ideal), máx. 250. Texto de marca: máx. 30 carateres.</t>
+          <t>Duração máx. 15″. Título: 34-45 carateres (ideal), máx. 60. Texto de marca: máx. 30 carateres.</t>
         </is>
       </c>
     </row>
@@ -28099,32 +28119,22 @@
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>Taboola - Motion Ads (Vídeo)</t>
+          <t>Taboola - Display Hosted (Imagem)</t>
         </is>
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>1067x600</t>
-        </is>
-      </c>
-      <c r="H609" t="inlineStr">
-        <is>
-          <t>16:9</t>
+          <t>Tamanhos standard IAB: 300x250, 300x600, 320x50, 728x90, 970x250, 160x600 ou 250x250</t>
         </is>
       </c>
       <c r="I609" t="inlineStr">
         <is>
-          <t>Máx. 50 MB (GIF: máx. 5 MB)</t>
+          <t>Máx. 2 MB</t>
         </is>
       </c>
       <c r="J609" t="inlineStr">
         <is>
-          <t>MP4, MOV ou GIF</t>
-        </is>
-      </c>
-      <c r="L609" t="inlineStr">
-        <is>
-          <t>Duração máx. 15″. Título: 34-45 carateres (ideal), máx. 60. Texto de marca: máx. 30 carateres.</t>
+          <t>JPEG, JPG, PNG ou GIF</t>
         </is>
       </c>
     </row>
@@ -28151,7 +28161,7 @@
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>Taboola - Display Hosted (Imagem)</t>
+          <t>Taboola - Display Hosted (Vídeo)</t>
         </is>
       </c>
       <c r="G610" t="inlineStr">
@@ -28161,12 +28171,17 @@
       </c>
       <c r="I610" t="inlineStr">
         <is>
-          <t>Máx. 2 MB</t>
+          <t>Máx. 200 MB</t>
         </is>
       </c>
       <c r="J610" t="inlineStr">
         <is>
-          <t>JPEG, JPG, PNG ou GIF</t>
+          <t>MP4</t>
+        </is>
+      </c>
+      <c r="L610" t="inlineStr">
+        <is>
+          <t>Duração: 5 a 30″. Pode incluir áudio (vídeo arranca sem som; o utilizador pode ativar).</t>
         </is>
       </c>
     </row>
@@ -28193,7 +28208,7 @@
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>Taboola - Display Hosted (Vídeo)</t>
+          <t>Taboola - Display Hosted (HTML5)</t>
         </is>
       </c>
       <c r="G611" t="inlineStr">
@@ -28203,17 +28218,17 @@
       </c>
       <c r="I611" t="inlineStr">
         <is>
-          <t>Máx. 200 MB</t>
+          <t>Máx. 2 MB (ZIP comprimido)</t>
         </is>
       </c>
       <c r="J611" t="inlineStr">
         <is>
-          <t>MP4</t>
+          <t>ZIP (HTML, JS, CSS, JPG, JPEG, GIF, PNG, SVG; máx. 100 ficheiros); index.html na raiz</t>
         </is>
       </c>
       <c r="L611" t="inlineStr">
         <is>
-          <t>Duração: 5 a 30″. Pode incluir áudio (vídeo arranca sem som; o utilizador pode ativar).</t>
+          <t>Tem de incluir uma imagem estática de recurso (JPG, PNG ou GIF) para browsers sem JavaScript.</t>
         </is>
       </c>
     </row>
@@ -28240,7 +28255,7 @@
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>Taboola - Display Hosted (HTML5)</t>
+          <t>Taboola - Display (Tag de 3ºs)</t>
         </is>
       </c>
       <c r="G612" t="inlineStr">
@@ -28248,19 +28263,9 @@
           <t>Tamanhos standard IAB: 300x250, 300x600, 320x50, 728x90, 970x250, 160x600 ou 250x250</t>
         </is>
       </c>
-      <c r="I612" t="inlineStr">
-        <is>
-          <t>Máx. 2 MB (ZIP comprimido)</t>
-        </is>
-      </c>
-      <c r="J612" t="inlineStr">
-        <is>
-          <t>ZIP (HTML, JS, CSS, JPG, JPEG, GIF, PNG, SVG; máx. 100 ficheiros); index.html na raiz</t>
-        </is>
-      </c>
       <c r="L612" t="inlineStr">
         <is>
-          <t>Tem de incluir uma imagem estática de recurso (JPG, PNG ou GIF) para browsers sem JavaScript.</t>
+          <t>Ad servers aceites: DCM e Adform. Macros de clique obrigatórias quando a tag não é reconhecida automaticamente.</t>
         </is>
       </c>
     </row>
@@ -28287,17 +28292,17 @@
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>Taboola - Display (Tag de 3ºs)</t>
+          <t>Taboola - Carousel</t>
         </is>
       </c>
       <c r="G613" t="inlineStr">
         <is>
-          <t>Tamanhos standard IAB: 300x250, 300x600, 320x50, 728x90, 970x250, 160x600 ou 250x250</t>
+          <t>1200x627</t>
         </is>
       </c>
       <c r="L613" t="inlineStr">
         <is>
-          <t>Ad servers aceites: DCM e Adform. Macros de clique obrigatórias quando a tag não é reconhecida automaticamente.</t>
+          <t>Mín. 3 e máx. 5 cartões. Por cartão: imagem, título (máx. 50 carateres), descrição (máx. 150 carateres), CTA e URL de destino (pode variar por cartão). Suporta GIF/vídeo nos cartões.</t>
         </is>
       </c>
     </row>
@@ -28324,17 +28329,17 @@
       </c>
       <c r="F614" t="inlineStr">
         <is>
-          <t>Taboola - Carousel</t>
+          <t>Taboola - Social Importer (Facebook/Instagram)</t>
         </is>
       </c>
       <c r="G614" t="inlineStr">
         <is>
-          <t>1200x627</t>
+          <t>300x250 ou 300x600</t>
         </is>
       </c>
       <c r="L614" t="inlineStr">
         <is>
-          <t>Mín. 3 e máx. 5 cartões. Por cartão: imagem, título (máx. 50 carateres), descrição (máx. 150 carateres), CTA e URL de destino (pode variar por cartão). Suporta GIF/vídeo nos cartões.</t>
+          <t>Anúncio importado diretamente do Facebook/Instagram a partir do ID da Meta Ad Library (16 dígitos) — não editável, aparece exatamente como no social.</t>
         </is>
       </c>
     </row>
@@ -28361,59 +28366,133 @@
       </c>
       <c r="F615" t="inlineStr">
         <is>
-          <t>Taboola - Social Importer (Facebook/Instagram)</t>
-        </is>
-      </c>
-      <c r="G615" t="inlineStr">
-        <is>
-          <t>300x250 ou 300x600</t>
-        </is>
-      </c>
-      <c r="L615" t="inlineStr">
-        <is>
-          <t>Anúncio importado diretamente do Facebook/Instagram a partir do ID da Meta Ad Library (16 dígitos) — não editável, aparece exatamente como no social.</t>
+          <t>Taboola - Vertical</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>4:5, 9:16 ou 1:2</t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>Máx. 5 MB</t>
+        </is>
+      </c>
+      <c r="J615" t="inlineStr">
+        <is>
+          <t>JPG ou PNG</t>
         </is>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>Taboola</t>
+          <t>Suebi</t>
         </is>
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>Taboola</t>
+          <t>Suebi</t>
         </is>
       </c>
       <c r="F616" t="inlineStr">
         <is>
-          <t>Taboola - Vertical</t>
-        </is>
-      </c>
-      <c r="H616" t="inlineStr">
-        <is>
-          <t>4:5, 9:16 ou 1:2</t>
-        </is>
-      </c>
-      <c r="I616" t="inlineStr">
-        <is>
-          <t>Máx. 5 MB</t>
-        </is>
-      </c>
-      <c r="J616" t="inlineStr">
-        <is>
-          <t>JPG ou PNG</t>
+          <t>Suebi - SMS</t>
+        </is>
+      </c>
+      <c r="L616" t="inlineStr">
+        <is>
+          <t>Sender: máx. 11 carateres. Copy: máx. 160 carateres (inclui espaços, pontuação e o link de unsubscribe — Stop SMS: 91xxxxxxx); no total ~135 carateres disponíveis. Não usar o símbolo € (spam trigger), usar "EUR". Símbolos especiais (%, ?, pontuação) contam como 2 espaços.</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>Suebi</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>Suebi</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>Suebi - Email / Newsletter</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>600px de largura (imagens)</t>
+        </is>
+      </c>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>Imagens: recomendado máx. 200 KB</t>
+        </is>
+      </c>
+      <c r="L617" t="inlineStr">
+        <is>
+          <t>Usar logo da marca. Banner = imagem + proposta de valor + CTA, visíveis sem necessidade de scroll. Newsletter não deve ser muito extensa; preferir mais texto do que imagens. A Suebi pode desenvolver o HTML sem custo para o cliente, se necessário.</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>Suebi</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>Suebi</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>Suebi - Push Notification</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>Logo 1:1; imagem opcional 512x256 ou 1024x512</t>
+        </is>
+      </c>
+      <c r="L618" t="inlineStr">
+        <is>
+          <t>Sender: 30-45 carateres. Subject: 40-50 carateres. Awareness puro, com clicktracker.</t>
         </is>
       </c>
     </row>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -28408,7 +28408,7 @@
       </c>
       <c r="F616" t="inlineStr">
         <is>
-          <t>Suebi - SMS</t>
+          <t>SMS</t>
         </is>
       </c>
       <c r="L616" t="inlineStr">
@@ -28440,7 +28440,7 @@
       </c>
       <c r="F617" t="inlineStr">
         <is>
-          <t>Suebi - Email / Newsletter</t>
+          <t>Email / Newsletter</t>
         </is>
       </c>
       <c r="G617" t="inlineStr">
@@ -28482,7 +28482,7 @@
       </c>
       <c r="F618" t="inlineStr">
         <is>
-          <t>Suebi - Push Notification</t>
+          <t>Push Notification</t>
         </is>
       </c>
       <c r="G618" t="inlineStr">

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M618"/>
+  <dimension ref="A1:M610"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27460,27 +27460,37 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>Tap Tap</t>
+          <t>ClickProfit</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>Tap Tap</t>
+          <t>Forretas e Descontos (Homepage)</t>
         </is>
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>Formato (specs a confirmar)</t>
+          <t>Moldura (barra lateral direita)</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>200x700</t>
+        </is>
+      </c>
+      <c r="J592" t="inlineStr">
+        <is>
+          <t>JPEG, GIF ou PNG + fontes usadas</t>
         </is>
       </c>
       <c r="L592" t="inlineStr">
         <is>
-          <t>Specs técnicas ainda não disponíveis — substituir esta linha quando a Cláudia enviar os materiais deste fornecedor.</t>
+          <t>O Take Over é composto por 3 peças: barra lateral direita, barra lateral esquerda e topo. Prazo de entrega dos materiais: 72h úteis.</t>
         </is>
       </c>
     </row>
@@ -27497,22 +27507,32 @@
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>Shopfully</t>
+          <t>ClickProfit</t>
         </is>
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>Shopfully</t>
+          <t>Forretas e Descontos (Homepage)</t>
         </is>
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>Formato (specs a confirmar)</t>
+          <t>Moldura (barra lateral esquerda)</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>200x700</t>
+        </is>
+      </c>
+      <c r="J593" t="inlineStr">
+        <is>
+          <t>JPEG, GIF ou PNG + fontes usadas</t>
         </is>
       </c>
       <c r="L593" t="inlineStr">
         <is>
-          <t>Specs técnicas ainda não disponíveis — substituir esta linha quando a Cláudia enviar os materiais deste fornecedor.</t>
+          <t>O Take Over é composto por 3 peças: barra lateral direita, barra lateral esquerda e topo. Prazo de entrega dos materiais: 72h úteis.</t>
         </is>
       </c>
     </row>
@@ -27524,91 +27544,121 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>RTB House</t>
+          <t>ClickProfit</t>
         </is>
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>RTB House</t>
+          <t>Descontos (Homepage)</t>
         </is>
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>Formato (specs a confirmar)</t>
+          <t>Moldura (topo)</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>940x120</t>
+        </is>
+      </c>
+      <c r="J594" t="inlineStr">
+        <is>
+          <t>JPEG, GIF ou PNG + fontes usadas</t>
         </is>
       </c>
       <c r="L594" t="inlineStr">
         <is>
-          <t>Specs técnicas ainda não disponíveis — substituir esta linha quando a Cláudia enviar os materiais deste fornecedor.</t>
+          <t>O topo tem de ter em conta os elementos fixos do site, que não serão sobrepostos. Prazo de entrega dos materiais: 72h úteis.</t>
         </is>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>Endless</t>
+          <t>ClickProfit</t>
         </is>
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>Endless</t>
+          <t>Forretas (Homepage)</t>
         </is>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>Formato (specs a confirmar)</t>
+          <t>Moldura (topo)</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>1920x313</t>
+        </is>
+      </c>
+      <c r="J595" t="inlineStr">
+        <is>
+          <t>JPEG, GIF ou PNG + fontes usadas</t>
         </is>
       </c>
       <c r="L595" t="inlineStr">
         <is>
-          <t>Specs técnicas ainda não disponíveis — substituir esta linha quando a Cláudia enviar os materiais deste fornecedor.</t>
+          <t>O topo tem de ter em conta os elementos fixos do site, que não serão sobrepostos. Prazo de entrega dos materiais: 72h úteis.</t>
         </is>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>In-Store Media</t>
+          <t>ClickProfit</t>
         </is>
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>In-Store Media</t>
+          <t>Descontos</t>
         </is>
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>Formato (specs a confirmar)</t>
+          <t>Imagem Oferta e Native Ad — Cupão</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>468x351</t>
+        </is>
+      </c>
+      <c r="J596" t="inlineStr">
+        <is>
+          <t>JPEG ou PNG</t>
         </is>
       </c>
       <c r="L596" t="inlineStr">
         <is>
-          <t>Specs técnicas ainda não disponíveis — substituir esta linha quando a Cláudia enviar os materiais deste fornecedor.</t>
+          <t>Imagem identificativa da oferta. Prazo de entrega dos materiais: 72h úteis.</t>
         </is>
       </c>
     </row>
@@ -27620,27 +27670,37 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>AdsMovil</t>
+          <t>ClickProfit</t>
         </is>
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>AdsMovil</t>
+          <t>ClickProfit</t>
         </is>
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>Formato (specs a confirmar)</t>
+          <t>HTML (Email)</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>600 ou 700px de largura; altura ao critério do cliente</t>
+        </is>
+      </c>
+      <c r="J597" t="inlineStr">
+        <is>
+          <t>HTML + imagens em JPG ou PNG</t>
         </is>
       </c>
       <c r="L597" t="inlineStr">
         <is>
-          <t>Specs técnicas ainda não disponíveis — substituir esta linha quando a Cláudia enviar os materiais deste fornecedor.</t>
+          <t>Enviar subject e sender. Prazo de entrega dos materiais: 72h úteis.</t>
         </is>
       </c>
     </row>
@@ -27652,343 +27712,378 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>EXTE</t>
+          <t>ClickProfit</t>
         </is>
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>EXTE</t>
+          <t>ClickProfit</t>
         </is>
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>Formato (specs a confirmar)</t>
+          <t>SMS</t>
         </is>
       </c>
       <c r="L598" t="inlineStr">
         <is>
-          <t>Specs técnicas ainda não disponíveis — substituir esta linha quando a Cláudia enviar os materiais deste fornecedor.</t>
+          <t>Sender: máx. 11 carateres. Copy: máx. 160 carateres (inclui espaços, pontuação e o link de unsubscribe usado pela ClickProfit — bit.ly/ChB_); sobram 142 carateres para o anunciante, podendo incluir um link (que a ClickProfit converte depois em bit.ly — esse link também conta para os 142 carateres). Enviar números de telemóvel para envio de SMS de teste. Prazo de entrega dos materiais: 72h úteis.</t>
         </is>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>INTERNET</t>
+          <t>PROGRAMÁTICO</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Programático</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>Oxy</t>
+          <t>Taboola</t>
         </is>
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>Oxy</t>
+          <t>Taboola</t>
         </is>
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>Formato (specs a confirmar)</t>
+          <t>Taboola - Native Ads (Imagem)</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>1200x674 (recomendado); mín. 400x350</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>16:9 (preferencial), 4:3 ou 1:1</t>
+        </is>
+      </c>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>Máx. 5 MB</t>
+        </is>
+      </c>
+      <c r="J599" t="inlineStr">
+        <is>
+          <t>JPEG (preferencial), BMP, PNG, WBMP ou GIF</t>
         </is>
       </c>
       <c r="L599" t="inlineStr">
         <is>
-          <t>Specs técnicas ainda não disponíveis — substituir esta linha quando a Cláudia enviar os materiais deste fornecedor.</t>
+          <t>Título: 34-45 carateres (ideal), máx. 60. Descrição: 180 (ideal), máx. 250. Texto de marca: máx. 30 carateres.</t>
         </is>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>INTERNET</t>
+          <t>PROGRAMÁTICO</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Programático</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>ClickProfit</t>
+          <t>Taboola</t>
         </is>
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>Forretas e Descontos (Homepage)</t>
+          <t>Taboola</t>
         </is>
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>Moldura (barra lateral direita)</t>
+          <t>Taboola - Motion Ads (Vídeo)</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>200x700</t>
+          <t>1067x600</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>Máx. 50 MB (GIF: máx. 5 MB)</t>
         </is>
       </c>
       <c r="J600" t="inlineStr">
         <is>
-          <t>JPEG, GIF ou PNG + fontes usadas</t>
+          <t>MP4, MOV ou GIF</t>
         </is>
       </c>
       <c r="L600" t="inlineStr">
         <is>
-          <t>O Take Over é composto por 3 peças: barra lateral direita, barra lateral esquerda e topo. Prazo de entrega dos materiais: 72h úteis.</t>
+          <t>Duração máx. 15″. Título: 34-45 carateres (ideal), máx. 60. Texto de marca: máx. 30 carateres.</t>
         </is>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>INTERNET</t>
+          <t>PROGRAMÁTICO</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Programático</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>ClickProfit</t>
+          <t>Taboola</t>
         </is>
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>Forretas e Descontos (Homepage)</t>
+          <t>Taboola</t>
         </is>
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>Moldura (barra lateral esquerda)</t>
+          <t>Taboola - Display Hosted (Imagem)</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>200x700</t>
+          <t>Tamanhos standard IAB: 300x250, 300x600, 320x50, 728x90, 970x250, 160x600 ou 250x250</t>
+        </is>
+      </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>Máx. 2 MB</t>
         </is>
       </c>
       <c r="J601" t="inlineStr">
         <is>
-          <t>JPEG, GIF ou PNG + fontes usadas</t>
-        </is>
-      </c>
-      <c r="L601" t="inlineStr">
-        <is>
-          <t>O Take Over é composto por 3 peças: barra lateral direita, barra lateral esquerda e topo. Prazo de entrega dos materiais: 72h úteis.</t>
+          <t>JPEG, JPG, PNG ou GIF</t>
         </is>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>INTERNET</t>
+          <t>PROGRAMÁTICO</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Programático</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>ClickProfit</t>
+          <t>Taboola</t>
         </is>
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>Descontos (Homepage)</t>
+          <t>Taboola</t>
         </is>
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>Moldura (topo)</t>
+          <t>Taboola - Display Hosted (Vídeo)</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>940x120</t>
+          <t>Tamanhos standard IAB: 300x250, 300x600, 320x50, 728x90, 970x250, 160x600 ou 250x250</t>
+        </is>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>Máx. 200 MB</t>
         </is>
       </c>
       <c r="J602" t="inlineStr">
         <is>
-          <t>JPEG, GIF ou PNG + fontes usadas</t>
+          <t>MP4</t>
         </is>
       </c>
       <c r="L602" t="inlineStr">
         <is>
-          <t>O topo tem de ter em conta os elementos fixos do site, que não serão sobrepostos. Prazo de entrega dos materiais: 72h úteis.</t>
+          <t>Duração: 5 a 30″. Pode incluir áudio (vídeo arranca sem som; o utilizador pode ativar).</t>
         </is>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>INTERNET</t>
+          <t>PROGRAMÁTICO</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Programático</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>ClickProfit</t>
+          <t>Taboola</t>
         </is>
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>Forretas (Homepage)</t>
+          <t>Taboola</t>
         </is>
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>Moldura (topo)</t>
+          <t>Taboola - Display Hosted (HTML5)</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>1920x313</t>
+          <t>Tamanhos standard IAB: 300x250, 300x600, 320x50, 728x90, 970x250, 160x600 ou 250x250</t>
+        </is>
+      </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>Máx. 2 MB (ZIP comprimido)</t>
         </is>
       </c>
       <c r="J603" t="inlineStr">
         <is>
-          <t>JPEG, GIF ou PNG + fontes usadas</t>
+          <t>ZIP (HTML, JS, CSS, JPG, JPEG, GIF, PNG, SVG; máx. 100 ficheiros); index.html na raiz</t>
         </is>
       </c>
       <c r="L603" t="inlineStr">
         <is>
-          <t>O topo tem de ter em conta os elementos fixos do site, que não serão sobrepostos. Prazo de entrega dos materiais: 72h úteis.</t>
+          <t>Tem de incluir uma imagem estática de recurso (JPG, PNG ou GIF) para browsers sem JavaScript.</t>
         </is>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>INTERNET</t>
+          <t>PROGRAMÁTICO</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Programático</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>ClickProfit</t>
+          <t>Taboola</t>
         </is>
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>Descontos</t>
+          <t>Taboola</t>
         </is>
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>Imagem Oferta e Native Ad — Cupão</t>
+          <t>Taboola - Display (Tag de 3ºs)</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>468x351</t>
-        </is>
-      </c>
-      <c r="J604" t="inlineStr">
-        <is>
-          <t>JPEG ou PNG</t>
+          <t>Tamanhos standard IAB: 300x250, 300x600, 320x50, 728x90, 970x250, 160x600 ou 250x250</t>
         </is>
       </c>
       <c r="L604" t="inlineStr">
         <is>
-          <t>Imagem identificativa da oferta. Prazo de entrega dos materiais: 72h úteis.</t>
+          <t>Ad servers aceites: DCM e Adform. Macros de clique obrigatórias quando a tag não é reconhecida automaticamente.</t>
         </is>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>INTERNET</t>
+          <t>PROGRAMÁTICO</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Programático</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>ClickProfit</t>
+          <t>Taboola</t>
         </is>
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>ClickProfit</t>
+          <t>Taboola</t>
         </is>
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>HTML (Email)</t>
+          <t>Taboola - Carousel</t>
         </is>
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>600 ou 700px de largura; altura ao critério do cliente</t>
-        </is>
-      </c>
-      <c r="J605" t="inlineStr">
-        <is>
-          <t>HTML + imagens em JPG ou PNG</t>
+          <t>1200x627</t>
         </is>
       </c>
       <c r="L605" t="inlineStr">
         <is>
-          <t>Enviar subject e sender. Prazo de entrega dos materiais: 72h úteis.</t>
+          <t>Mín. 3 e máx. 5 cartões. Por cartão: imagem, título (máx. 50 carateres), descrição (máx. 150 carateres), CTA e URL de destino (pode variar por cartão). Suporta GIF/vídeo nos cartões.</t>
         </is>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>INTERNET</t>
+          <t>PROGRAMÁTICO</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Programático</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>ClickProfit</t>
+          <t>Taboola</t>
         </is>
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>ClickProfit</t>
+          <t>Taboola</t>
         </is>
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>SMS</t>
+          <t>Taboola - Social Importer (Facebook/Instagram)</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>300x250 ou 300x600</t>
         </is>
       </c>
       <c r="L606" t="inlineStr">
         <is>
-          <t>Sender: máx. 11 carateres. Copy: máx. 160 carateres (inclui espaços, pontuação e o link de unsubscribe usado pela ClickProfit — bit.ly/ChB_); sobram 142 carateres para o anunciante, podendo incluir um link (que a ClickProfit converte depois em bit.ly — esse link também conta para os 142 carateres). Enviar números de telemóvel para envio de SMS de teste. Prazo de entrega dos materiais: 72h úteis.</t>
+          <t>Anúncio importado diretamente do Facebook/Instagram a partir do ID da Meta Ad Library (16 dígitos) — não editável, aparece exatamente como no social.</t>
         </is>
       </c>
     </row>
@@ -28015,17 +28110,12 @@
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>Taboola - Native Ads (Imagem)</t>
-        </is>
-      </c>
-      <c r="G607" t="inlineStr">
-        <is>
-          <t>1200x674 (recomendado); mín. 400x350</t>
+          <t>Taboola - Vertical</t>
         </is>
       </c>
       <c r="H607" t="inlineStr">
         <is>
-          <t>16:9 (preferencial), 4:3 ou 1:1</t>
+          <t>4:5, 9:16 ou 1:2</t>
         </is>
       </c>
       <c r="I607" t="inlineStr">
@@ -28035,462 +28125,116 @@
       </c>
       <c r="J607" t="inlineStr">
         <is>
-          <t>JPEG (preferencial), BMP, PNG, WBMP ou GIF</t>
-        </is>
-      </c>
-      <c r="L607" t="inlineStr">
-        <is>
-          <t>Título: 34-45 carateres (ideal), máx. 60. Descrição: 180 (ideal), máx. 250. Texto de marca: máx. 30 carateres.</t>
+          <t>JPG ou PNG</t>
         </is>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>Taboola</t>
+          <t>Suebi</t>
         </is>
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>Taboola</t>
+          <t>Suebi</t>
         </is>
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>Taboola - Motion Ads (Vídeo)</t>
-        </is>
-      </c>
-      <c r="G608" t="inlineStr">
-        <is>
-          <t>1067x600</t>
-        </is>
-      </c>
-      <c r="H608" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
-      <c r="I608" t="inlineStr">
-        <is>
-          <t>Máx. 50 MB (GIF: máx. 5 MB)</t>
-        </is>
-      </c>
-      <c r="J608" t="inlineStr">
-        <is>
-          <t>MP4, MOV ou GIF</t>
+          <t>SMS</t>
         </is>
       </c>
       <c r="L608" t="inlineStr">
         <is>
-          <t>Duração máx. 15″. Título: 34-45 carateres (ideal), máx. 60. Texto de marca: máx. 30 carateres.</t>
+          <t>Sender: máx. 11 carateres. Copy: máx. 160 carateres (inclui espaços, pontuação e o link de unsubscribe — Stop SMS: 91xxxxxxx); no total ~135 carateres disponíveis. Não usar o símbolo € (spam trigger), usar "EUR". Símbolos especiais (%, ?, pontuação) contam como 2 espaços.</t>
         </is>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>Taboola</t>
+          <t>Suebi</t>
         </is>
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>Taboola</t>
+          <t>Suebi</t>
         </is>
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>Taboola - Display Hosted (Imagem)</t>
+          <t>Email / Newsletter</t>
         </is>
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>Tamanhos standard IAB: 300x250, 300x600, 320x50, 728x90, 970x250, 160x600 ou 250x250</t>
+          <t>600px de largura (imagens)</t>
         </is>
       </c>
       <c r="I609" t="inlineStr">
         <is>
-          <t>Máx. 2 MB</t>
-        </is>
-      </c>
-      <c r="J609" t="inlineStr">
-        <is>
-          <t>JPEG, JPG, PNG ou GIF</t>
+          <t>Imagens: recomendado máx. 200 KB</t>
+        </is>
+      </c>
+      <c r="L609" t="inlineStr">
+        <is>
+          <t>Usar logo da marca. Banner = imagem + proposta de valor + CTA, visíveis sem necessidade de scroll. Newsletter não deve ser muito extensa; preferir mais texto do que imagens. A Suebi pode desenvolver o HTML sem custo para o cliente, se necessário.</t>
         </is>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>Taboola</t>
+          <t>Suebi</t>
         </is>
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>Taboola</t>
+          <t>Suebi</t>
         </is>
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>Taboola - Display Hosted (Vídeo)</t>
+          <t>Push Notification</t>
         </is>
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>Tamanhos standard IAB: 300x250, 300x600, 320x50, 728x90, 970x250, 160x600 ou 250x250</t>
-        </is>
-      </c>
-      <c r="I610" t="inlineStr">
-        <is>
-          <t>Máx. 200 MB</t>
-        </is>
-      </c>
-      <c r="J610" t="inlineStr">
-        <is>
-          <t>MP4</t>
+          <t>Logo 1:1; imagem opcional 512x256 ou 1024x512</t>
         </is>
       </c>
       <c r="L610" t="inlineStr">
-        <is>
-          <t>Duração: 5 a 30″. Pode incluir áudio (vídeo arranca sem som; o utilizador pode ativar).</t>
-        </is>
-      </c>
-    </row>
-    <row r="611">
-      <c r="A611" t="inlineStr">
-        <is>
-          <t>PROGRAMÁTICO</t>
-        </is>
-      </c>
-      <c r="B611" t="inlineStr">
-        <is>
-          <t>Programático</t>
-        </is>
-      </c>
-      <c r="C611" t="inlineStr">
-        <is>
-          <t>Taboola</t>
-        </is>
-      </c>
-      <c r="D611" t="inlineStr">
-        <is>
-          <t>Taboola</t>
-        </is>
-      </c>
-      <c r="F611" t="inlineStr">
-        <is>
-          <t>Taboola - Display Hosted (HTML5)</t>
-        </is>
-      </c>
-      <c r="G611" t="inlineStr">
-        <is>
-          <t>Tamanhos standard IAB: 300x250, 300x600, 320x50, 728x90, 970x250, 160x600 ou 250x250</t>
-        </is>
-      </c>
-      <c r="I611" t="inlineStr">
-        <is>
-          <t>Máx. 2 MB (ZIP comprimido)</t>
-        </is>
-      </c>
-      <c r="J611" t="inlineStr">
-        <is>
-          <t>ZIP (HTML, JS, CSS, JPG, JPEG, GIF, PNG, SVG; máx. 100 ficheiros); index.html na raiz</t>
-        </is>
-      </c>
-      <c r="L611" t="inlineStr">
-        <is>
-          <t>Tem de incluir uma imagem estática de recurso (JPG, PNG ou GIF) para browsers sem JavaScript.</t>
-        </is>
-      </c>
-    </row>
-    <row r="612">
-      <c r="A612" t="inlineStr">
-        <is>
-          <t>PROGRAMÁTICO</t>
-        </is>
-      </c>
-      <c r="B612" t="inlineStr">
-        <is>
-          <t>Programático</t>
-        </is>
-      </c>
-      <c r="C612" t="inlineStr">
-        <is>
-          <t>Taboola</t>
-        </is>
-      </c>
-      <c r="D612" t="inlineStr">
-        <is>
-          <t>Taboola</t>
-        </is>
-      </c>
-      <c r="F612" t="inlineStr">
-        <is>
-          <t>Taboola - Display (Tag de 3ºs)</t>
-        </is>
-      </c>
-      <c r="G612" t="inlineStr">
-        <is>
-          <t>Tamanhos standard IAB: 300x250, 300x600, 320x50, 728x90, 970x250, 160x600 ou 250x250</t>
-        </is>
-      </c>
-      <c r="L612" t="inlineStr">
-        <is>
-          <t>Ad servers aceites: DCM e Adform. Macros de clique obrigatórias quando a tag não é reconhecida automaticamente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="613">
-      <c r="A613" t="inlineStr">
-        <is>
-          <t>PROGRAMÁTICO</t>
-        </is>
-      </c>
-      <c r="B613" t="inlineStr">
-        <is>
-          <t>Programático</t>
-        </is>
-      </c>
-      <c r="C613" t="inlineStr">
-        <is>
-          <t>Taboola</t>
-        </is>
-      </c>
-      <c r="D613" t="inlineStr">
-        <is>
-          <t>Taboola</t>
-        </is>
-      </c>
-      <c r="F613" t="inlineStr">
-        <is>
-          <t>Taboola - Carousel</t>
-        </is>
-      </c>
-      <c r="G613" t="inlineStr">
-        <is>
-          <t>1200x627</t>
-        </is>
-      </c>
-      <c r="L613" t="inlineStr">
-        <is>
-          <t>Mín. 3 e máx. 5 cartões. Por cartão: imagem, título (máx. 50 carateres), descrição (máx. 150 carateres), CTA e URL de destino (pode variar por cartão). Suporta GIF/vídeo nos cartões.</t>
-        </is>
-      </c>
-    </row>
-    <row r="614">
-      <c r="A614" t="inlineStr">
-        <is>
-          <t>PROGRAMÁTICO</t>
-        </is>
-      </c>
-      <c r="B614" t="inlineStr">
-        <is>
-          <t>Programático</t>
-        </is>
-      </c>
-      <c r="C614" t="inlineStr">
-        <is>
-          <t>Taboola</t>
-        </is>
-      </c>
-      <c r="D614" t="inlineStr">
-        <is>
-          <t>Taboola</t>
-        </is>
-      </c>
-      <c r="F614" t="inlineStr">
-        <is>
-          <t>Taboola - Social Importer (Facebook/Instagram)</t>
-        </is>
-      </c>
-      <c r="G614" t="inlineStr">
-        <is>
-          <t>300x250 ou 300x600</t>
-        </is>
-      </c>
-      <c r="L614" t="inlineStr">
-        <is>
-          <t>Anúncio importado diretamente do Facebook/Instagram a partir do ID da Meta Ad Library (16 dígitos) — não editável, aparece exatamente como no social.</t>
-        </is>
-      </c>
-    </row>
-    <row r="615">
-      <c r="A615" t="inlineStr">
-        <is>
-          <t>PROGRAMÁTICO</t>
-        </is>
-      </c>
-      <c r="B615" t="inlineStr">
-        <is>
-          <t>Programático</t>
-        </is>
-      </c>
-      <c r="C615" t="inlineStr">
-        <is>
-          <t>Taboola</t>
-        </is>
-      </c>
-      <c r="D615" t="inlineStr">
-        <is>
-          <t>Taboola</t>
-        </is>
-      </c>
-      <c r="F615" t="inlineStr">
-        <is>
-          <t>Taboola - Vertical</t>
-        </is>
-      </c>
-      <c r="H615" t="inlineStr">
-        <is>
-          <t>4:5, 9:16 ou 1:2</t>
-        </is>
-      </c>
-      <c r="I615" t="inlineStr">
-        <is>
-          <t>Máx. 5 MB</t>
-        </is>
-      </c>
-      <c r="J615" t="inlineStr">
-        <is>
-          <t>JPG ou PNG</t>
-        </is>
-      </c>
-    </row>
-    <row r="616">
-      <c r="A616" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B616" t="inlineStr">
-        <is>
-          <t>Internet</t>
-        </is>
-      </c>
-      <c r="C616" t="inlineStr">
-        <is>
-          <t>Suebi</t>
-        </is>
-      </c>
-      <c r="D616" t="inlineStr">
-        <is>
-          <t>Suebi</t>
-        </is>
-      </c>
-      <c r="F616" t="inlineStr">
-        <is>
-          <t>SMS</t>
-        </is>
-      </c>
-      <c r="L616" t="inlineStr">
-        <is>
-          <t>Sender: máx. 11 carateres. Copy: máx. 160 carateres (inclui espaços, pontuação e o link de unsubscribe — Stop SMS: 91xxxxxxx); no total ~135 carateres disponíveis. Não usar o símbolo € (spam trigger), usar "EUR". Símbolos especiais (%, ?, pontuação) contam como 2 espaços.</t>
-        </is>
-      </c>
-    </row>
-    <row r="617">
-      <c r="A617" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B617" t="inlineStr">
-        <is>
-          <t>Internet</t>
-        </is>
-      </c>
-      <c r="C617" t="inlineStr">
-        <is>
-          <t>Suebi</t>
-        </is>
-      </c>
-      <c r="D617" t="inlineStr">
-        <is>
-          <t>Suebi</t>
-        </is>
-      </c>
-      <c r="F617" t="inlineStr">
-        <is>
-          <t>Email / Newsletter</t>
-        </is>
-      </c>
-      <c r="G617" t="inlineStr">
-        <is>
-          <t>600px de largura (imagens)</t>
-        </is>
-      </c>
-      <c r="I617" t="inlineStr">
-        <is>
-          <t>Imagens: recomendado máx. 200 KB</t>
-        </is>
-      </c>
-      <c r="L617" t="inlineStr">
-        <is>
-          <t>Usar logo da marca. Banner = imagem + proposta de valor + CTA, visíveis sem necessidade de scroll. Newsletter não deve ser muito extensa; preferir mais texto do que imagens. A Suebi pode desenvolver o HTML sem custo para o cliente, se necessário.</t>
-        </is>
-      </c>
-    </row>
-    <row r="618">
-      <c r="A618" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B618" t="inlineStr">
-        <is>
-          <t>Internet</t>
-        </is>
-      </c>
-      <c r="C618" t="inlineStr">
-        <is>
-          <t>Suebi</t>
-        </is>
-      </c>
-      <c r="D618" t="inlineStr">
-        <is>
-          <t>Suebi</t>
-        </is>
-      </c>
-      <c r="F618" t="inlineStr">
-        <is>
-          <t>Push Notification</t>
-        </is>
-      </c>
-      <c r="G618" t="inlineStr">
-        <is>
-          <t>Logo 1:1; imagem opcional 512x256 ou 1024x512</t>
-        </is>
-      </c>
-      <c r="L618" t="inlineStr">
         <is>
           <t>Sender: 30-45 carateres. Subject: 40-50 carateres. Awareness puro, com clicktracker.</t>
         </is>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M610"/>
+  <dimension ref="A1:M611"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28240,6 +28240,48 @@
         </is>
       </c>
     </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>RTB House</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>RTB House</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>Display</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>300x600, 160x600, 336x280, 300x250, 320x50, 320x100, 970x250 ou 728x90</t>
+        </is>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="J611" t="inlineStr">
+        <is>
+          <t>PNG, JPG, JPEG, GIF ou HTML</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M565"/>
+  <dimension ref="A1:M563"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18967,22 +18967,32 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Clearspot</t>
+          <t>3D Lab</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Clearspot</t>
+          <t>3D Lab</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>Especificações por confirmar</t>
+          <t>Grande Formato</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>Escala 1:10.</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>TIFF ou JPEG — aconselhável também o envio em PDF editável.</t>
         </is>
       </c>
       <c r="L380" t="inlineStr">
         <is>
-          <t>Concessionária adicionada à base para já sem formatos associados — as especificações técnicas de Clearspot ainda não foram fornecidas. Atualizar esta linha (e acrescentar as linhas de formato que fizerem falta) assim que a informação chegar.</t>
+          <t>Cor: modo CMYK. Fontes convertidas em curvas (ficheiros vetoriais) ou fonte enviada junto com o ficheiro. Resolução: 450 dpi.</t>
         </is>
       </c>
     </row>
@@ -18999,22 +19009,32 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>CS Outdoors</t>
+          <t>3D Lab</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>CS Outdoors</t>
+          <t>3D Lab</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>Especificações por confirmar</t>
+          <t>Rede Highway</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>10,15x5,15m. Escala 1:10.</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>TIFF ou JPEG — aconselhável também o envio em PDF editável.</t>
         </is>
       </c>
       <c r="L381" t="inlineStr">
         <is>
-          <t>Concessionária adicionada à base para já sem formatos associados — as especificações técnicas de CS Outdoors ainda não foram fornecidas. Atualizar esta linha (e acrescentar as linhas de formato que fizerem falta) assim que a informação chegar.</t>
+          <t>Cor: modo CMYK. Fontes convertidas em curvas (ficheiros vetoriais) ou fonte enviada junto com o ficheiro. Resolução: 450 dpi.</t>
         </is>
       </c>
     </row>
@@ -19041,7 +19061,7 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>Grande Formato</t>
+          <t>Rede LED</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
@@ -19056,7 +19076,7 @@
       </c>
       <c r="L382" t="inlineStr">
         <is>
-          <t>Cor: modo CMYK. Fontes convertidas em curvas (ficheiros vetoriais) ou fonte enviada junto com o ficheiro. Resolução: 450 dpi.</t>
+          <t>Cor: modo RGB. Fontes convertidas em curvas (ficheiros vetoriais) ou fonte enviada junto com o ficheiro. Resolução: 100 dpi.</t>
         </is>
       </c>
     </row>
@@ -19073,32 +19093,42 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>3D Lab</t>
+          <t>Unimidia/Spreading</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>3D Lab</t>
+          <t>Unimidia</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>Rede Highway</t>
+          <t>Mupi Digital | Universidades</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>10,15x5,15m. Escala 1:10.</t>
+          <t>Tamanho total: 1080x1920px. Área visível: 1080x1920px.</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>Máx. 10MB (vídeo produzido pelo cliente).</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>TIFF ou JPEG — aconselhável também o envio em PDF editável.</t>
+          <t>Produzido pela Unimidia (material por camadas): .psd, .ai ou .indd, fotografias/imagens com resolução superior a 150dpi, texto convertido em curvas — sujeito a apresentação de orçamento. Produzido pelo cliente (vídeo pronto): .avi, .mp4, .mov, .mpeg, .mpg ou .jpeg, resolução 1080x1920px, 25 frames por segundo, em formato vertical.</t>
         </is>
       </c>
       <c r="L383" t="inlineStr">
         <is>
-          <t>Cor: modo CMYK. Fontes convertidas em curvas (ficheiros vetoriais) ou fonte enviada junto com o ficheiro. Resolução: 450 dpi.</t>
+          <t>Duração máxima: 10 segundos. Criatividade tem de estar em português. A emissão do material só se inicia após validação da criatividade pela Unimidia. Data de entrega: 15 dias antes do início da campanha se produzido pela Unimidia (sujeito a orçamento), ou 2 dias úteis antes se produzido pelo cliente. Ficheiros enviados por email para universidades@unimidia.pt.</t>
         </is>
       </c>
     </row>
@@ -19115,32 +19145,32 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>3D Lab</t>
+          <t>Unimidia/Spreading</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>3D Lab</t>
+          <t>Spreading</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>Rede LED</t>
+          <t>Táxi Açores - Lateral Direita</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>Escala 1:10.</t>
+          <t>Cortante: 1650x750mm. Área visível variável consoante o ano/modelo da viatura.</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>TIFF ou JPEG — aconselhável também o envio em PDF editável.</t>
+          <t>InDesign CS3, Illustrator CS3, Photoshop CS3 ou PDF. Ficheiros EPS ou TIFF.</t>
         </is>
       </c>
       <c r="L384" t="inlineStr">
         <is>
-          <t>Cor: modo RGB. Fontes convertidas em curvas (ficheiros vetoriais) ou fonte enviada junto com o ficheiro. Resolução: 100 dpi.</t>
+          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido. Considerar uma margem de segurança sobre os limites visíveis, para evitar perda de informação vital.</t>
         </is>
       </c>
     </row>
@@ -19162,37 +19192,27 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Unimidia</t>
+          <t>Spreading</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>Mupi Digital | Universidades</t>
+          <t>Táxi Açores - Lateral Esquerda</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>Tamanho total: 1080x1920px. Área visível: 1080x1920px.</t>
-        </is>
-      </c>
-      <c r="H385" t="inlineStr">
-        <is>
-          <t>9:16</t>
-        </is>
-      </c>
-      <c r="I385" t="inlineStr">
-        <is>
-          <t>Máx. 10MB (vídeo produzido pelo cliente).</t>
+          <t>Cortante: 1650x750mm. Área visível variável consoante o ano/modelo da viatura.</t>
         </is>
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>Produzido pela Unimidia (material por camadas): .psd, .ai ou .indd, fotografias/imagens com resolução superior a 150dpi, texto convertido em curvas — sujeito a apresentação de orçamento. Produzido pelo cliente (vídeo pronto): .avi, .mp4, .mov, .mpeg, .mpg ou .jpeg, resolução 1080x1920px, 25 frames por segundo, em formato vertical.</t>
+          <t>InDesign CS3, Illustrator CS3, Photoshop CS3 ou PDF. Ficheiros EPS ou TIFF.</t>
         </is>
       </c>
       <c r="L385" t="inlineStr">
         <is>
-          <t>Duração máxima: 10 segundos. Criatividade tem de estar em português. A emissão do material só se inicia após validação da criatividade pela Unimidia. Data de entrega: 15 dias antes do início da campanha se produzido pela Unimidia (sujeito a orçamento), ou 2 dias úteis antes se produzido pelo cliente. Ficheiros enviados por email para universidades@unimidia.pt.</t>
+          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido. Considerar uma margem de segurança sobre os limites visíveis, para evitar perda de informação vital.</t>
         </is>
       </c>
     </row>
@@ -19219,12 +19239,12 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>Táxi Açores - Lateral Direita</t>
+          <t>Táxi Doorcover - Lateral Direita</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>Cortante: 1650x750mm. Área visível variável consoante o ano/modelo da viatura.</t>
+          <t>Cortante: 2200x750mm. Área visível variável consoante o ano/modelo da viatura.</t>
         </is>
       </c>
       <c r="J386" t="inlineStr">
@@ -19234,7 +19254,7 @@
       </c>
       <c r="L386" t="inlineStr">
         <is>
-          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido. Considerar uma margem de segurança sobre os limites visíveis, para evitar perda de informação vital.</t>
+          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido. Margem de segurança de 5 a 10cm sobre os limites visíveis; considerar a mesma margem junto aos puxadores das portas.</t>
         </is>
       </c>
     </row>
@@ -19261,12 +19281,12 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>Táxi Açores - Lateral Esquerda</t>
+          <t>Táxi Doorcover - Lateral Esquerda</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Cortante: 1650x750mm. Área visível variável consoante o ano/modelo da viatura.</t>
+          <t>Cortante: 2200x750mm. Área visível variável consoante o ano/modelo da viatura.</t>
         </is>
       </c>
       <c r="J387" t="inlineStr">
@@ -19276,7 +19296,7 @@
       </c>
       <c r="L387" t="inlineStr">
         <is>
-          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido. Considerar uma margem de segurança sobre os limites visíveis, para evitar perda de informação vital.</t>
+          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido. Margem de segurança de 5 a 10cm sobre os limites visíveis; considerar a mesma margem junto aos puxadores das portas.</t>
         </is>
       </c>
     </row>
@@ -19303,22 +19323,22 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>Táxi Doorcover - Lateral Direita</t>
+          <t>Táxi Indoor - Flyer</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>Cortante: 2200x750mm. Área visível variável consoante o ano/modelo da viatura.</t>
+          <t>Altura (sem margem): 20cm. Largura (sem margem): 10cm.</t>
         </is>
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>InDesign CS3, Illustrator CS3, Photoshop CS3 ou PDF. Ficheiros EPS ou TIFF.</t>
+          <t>InDesign CS3, Illustrator CS3, Photoshop CS3 ou PDF. Ficheiros PDF, EPS ou TIFF.</t>
         </is>
       </c>
       <c r="L388" t="inlineStr">
         <is>
-          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido. Margem de segurança de 5 a 10cm sobre os limites visíveis; considerar a mesma margem junto aos puxadores das portas.</t>
+          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido.</t>
         </is>
       </c>
     </row>
@@ -19345,22 +19365,22 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>Táxi Doorcover - Lateral Esquerda</t>
+          <t>Táxi Indoor - Banner</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>Cortante: 2200x750mm. Área visível variável consoante o ano/modelo da viatura.</t>
+          <t>Impressão: 34x12,6cm (largura x altura). Área visível: 37,5x15cm (largura x altura).</t>
         </is>
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t>InDesign CS3, Illustrator CS3, Photoshop CS3 ou PDF. Ficheiros EPS ou TIFF.</t>
+          <t>InDesign CS3, Illustrator CS3, Photoshop CS3 ou PDF. Ficheiros PDF, EPS ou TIFF.</t>
         </is>
       </c>
       <c r="L389" t="inlineStr">
         <is>
-          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido. Margem de segurança de 5 a 10cm sobre os limites visíveis; considerar a mesma margem junto aos puxadores das portas.</t>
+          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido.</t>
         </is>
       </c>
     </row>
@@ -19377,32 +19397,37 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Unimidia/Spreading</t>
+          <t>Shine Care</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Spreading</t>
+          <t>Shine Care</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>Táxi Indoor - Flyer</t>
+          <t>Mupi Digital</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>Altura (sem margem): 20cm. Largura (sem margem): 10cm.</t>
+          <t>1080x1920px.</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>9:16</t>
         </is>
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>InDesign CS3, Illustrator CS3, Photoshop CS3 ou PDF. Ficheiros PDF, EPS ou TIFF.</t>
+          <t>MP4.</t>
         </is>
       </c>
       <c r="L390" t="inlineStr">
         <is>
-          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido.</t>
+          <t>Duração: 10 segundos. Frame rate: 30 frames por segundo. Rede de mupis digitais em hospitais e clínicas.</t>
         </is>
       </c>
     </row>
@@ -19419,32 +19444,37 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Unimidia/Spreading</t>
+          <t>Media Play</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Spreading</t>
+          <t>Media Play</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>Táxi Indoor - Banner</t>
+          <t>Ecrã Horizontal</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>Impressão: 34x12,6cm (largura x altura). Área visível: 37,5x15cm (largura x altura).</t>
+          <t>1920x1080px.</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>16:9</t>
         </is>
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>InDesign CS3, Illustrator CS3, Photoshop CS3 ou PDF. Ficheiros PDF, EPS ou TIFF.</t>
+          <t>Vídeo: MP4, codec H.264, frame rate constante até 30fps, bitrate até 3000 Kbps (recomendado 1500-2500 Kbps para vídeo com imagem real; cerca de 600 Kbps para animações ou imagens estáticas), encoder profile Baseline ou Main, encoder level entre 3.0 e 4.2 (recomendado 3.2). Estático: JPEG (preferencial) ou PNG.</t>
         </is>
       </c>
       <c r="L391" t="inlineStr">
         <is>
-          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido.</t>
+          <t>Duração do vídeo: 10 segundos. Aceite tanto criativo em vídeo (10 segundos) como criativo estático, consoante os materiais disponíveis do anunciante. Rede de publicidade digital em farmácias.</t>
         </is>
       </c>
     </row>
@@ -19461,17 +19491,17 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Shine Care</t>
+          <t>Media Play</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>Shine Care</t>
+          <t>Media Play</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>Mupi Digital</t>
+          <t>Ecrã Vertical</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
@@ -19486,12 +19516,12 @@
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>MP4.</t>
+          <t>Vídeo: MP4, codec H.264, frame rate constante até 30fps, bitrate até 3000 Kbps (recomendado 1500-2500 Kbps para vídeo com imagem real; cerca de 600 Kbps para animações ou imagens estáticas), encoder profile Baseline ou Main, encoder level entre 3.0 e 4.2 (recomendado 3.2). Estático: JPEG (preferencial) ou PNG.</t>
         </is>
       </c>
       <c r="L392" t="inlineStr">
         <is>
-          <t>Duração: 10 segundos. Frame rate: 30 frames por segundo. Rede de mupis digitais em hospitais e clínicas.</t>
+          <t>Duração do vídeo: 10 segundos. Aceite tanto criativo em vídeo (10 segundos) como criativo estático, consoante os materiais disponíveis do anunciante. Rede de publicidade digital em farmácias.</t>
         </is>
       </c>
     </row>
@@ -19508,37 +19538,32 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Media Play</t>
+          <t>Tequilha</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>Media Play</t>
+          <t>Tequilha</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>Ecrã Horizontal</t>
+          <t>Mupis Digitais</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>1920x1080px.</t>
+          <t>Mupi de pé (estrutura autónoma): 202cm de altura total, 73cm de largura. Ecrã de 50″, com 107cm de altura visível, posicionado a 83,5cm do chão; margens de 11cm (topo) e 7cm (laterais do ecrã).</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>16:9</t>
+          <t>9:16</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>Vídeo: MP4, codec H.264, frame rate constante até 30fps, bitrate até 3000 Kbps (recomendado 1500-2500 Kbps para vídeo com imagem real; cerca de 600 Kbps para animações ou imagens estáticas), encoder profile Baseline ou Main, encoder level entre 3.0 e 4.2 (recomendado 3.2). Estático: JPEG (preferencial) ou PNG.</t>
-        </is>
-      </c>
-      <c r="L393" t="inlineStr">
-        <is>
-          <t>Duração do vídeo: 10 segundos. Aceite tanto criativo em vídeo (10 segundos) como criativo estático, consoante os materiais disponíveis do anunciante. Rede de publicidade digital em farmácias.</t>
+          <t>Conteúdo: 1080x1920px, MP4.</t>
         </is>
       </c>
     </row>
@@ -19555,37 +19580,22 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Media Play</t>
+          <t>Tequilha</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>Media Play</t>
+          <t>Tequilha</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>Ecrã Vertical</t>
+          <t>Mupis Tradicionais</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>1080x1920px.</t>
-        </is>
-      </c>
-      <c r="H394" t="inlineStr">
-        <is>
-          <t>9:16</t>
-        </is>
-      </c>
-      <c r="J394" t="inlineStr">
-        <is>
-          <t>Vídeo: MP4, codec H.264, frame rate constante até 30fps, bitrate até 3000 Kbps (recomendado 1500-2500 Kbps para vídeo com imagem real; cerca de 600 Kbps para animações ou imagens estáticas), encoder profile Baseline ou Main, encoder level entre 3.0 e 4.2 (recomendado 3.2). Estático: JPEG (preferencial) ou PNG.</t>
-        </is>
-      </c>
-      <c r="L394" t="inlineStr">
-        <is>
-          <t>Duração do vídeo: 10 segundos. Aceite tanto criativo em vídeo (10 segundos) como criativo estático, consoante os materiais disponíveis do anunciante. Rede de publicidade digital em farmácias.</t>
+          <t>80cm (largura) x 120cm (altura). Área total = área visível.</t>
         </is>
       </c>
     </row>
@@ -19612,22 +19622,27 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>Mupis Digitais</t>
+          <t>Ecrãs de Cinema Universidades</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>Mupi de pé (estrutura autónoma): 202cm de altura total, 73cm de largura. Ecrã de 50″, com 107cm de altura visível, posicionado a 83,5cm do chão; margens de 11cm (topo) e 7cm (laterais do ecrã).</t>
+          <t>Ecrã de 50″.</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>9:16</t>
+          <t>16:9</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>Conteúdo: 1080x1920px, MP4.</t>
+          <t>Conteúdo: 1920x1080px, MP4.</t>
+        </is>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>Estes ecrãs passam trailers de filmes; entre os trailers, passam spots de TV dos parceiros, incluindo a Tequilha.</t>
         </is>
       </c>
     </row>
@@ -19644,22 +19659,32 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Tequilha</t>
+          <t>Unimidia/Spreading</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>Tequilha</t>
+          <t>Spreading</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>Mupis Tradicionais</t>
+          <t>Táxi Doorcover Madeira - Lateral Direita</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>80cm (largura) x 120cm (altura). Área total = área visível.</t>
+          <t>Escala 1/10. Área visível variável consoante o ano/modelo da viatura (táxis da Madeira).</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>InDesign CS3, Illustrator CS3, Photoshop CS3 ou PDF. Ficheiros EPS ou TIFF.</t>
+        </is>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido. Margem de segurança de 5 a 10cm sobre os limites visíveis; considerar a mesma margem junto aos puxadores das portas.</t>
         </is>
       </c>
     </row>
@@ -19676,121 +19701,126 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Tequilha</t>
+          <t>Unimidia/Spreading</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>Tequilha</t>
+          <t>Spreading</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>Ecrãs de Cinema Universidades</t>
+          <t>Táxi Doorcover Madeira - Lateral Esquerda</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>Ecrã de 50″.</t>
-        </is>
-      </c>
-      <c r="H397" t="inlineStr">
-        <is>
-          <t>16:9</t>
+          <t>Escala 1/10. Área visível variável consoante o ano/modelo da viatura (táxis da Madeira).</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>Conteúdo: 1920x1080px, MP4.</t>
+          <t>InDesign CS3, Illustrator CS3, Photoshop CS3 ou PDF. Ficheiros EPS ou TIFF.</t>
         </is>
       </c>
       <c r="L397" t="inlineStr">
         <is>
-          <t>Estes ecrãs passam trailers de filmes; entre os trailers, passam spots de TV dos parceiros, incluindo a Tequilha.</t>
+          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido. Margem de segurança de 5 a 10cm sobre os limites visíveis; considerar a mesma margem junto aos puxadores das portas.</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>TV</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>TV</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Unimidia/Spreading</t>
+          <t>TV</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Spreading</t>
+          <t>TV</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>Táxi Doorcover Madeira - Lateral Direita</t>
+          <t>Spot TV (HD — XDCAM HD422)</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>Escala 1/10. Área visível variável consoante o ano/modelo da viatura (táxis da Madeira).</t>
+          <t>1920x1080px, 25 fps</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>16:9</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>InDesign CS3, Illustrator CS3, Photoshop CS3 ou PDF. Ficheiros EPS ou TIFF.</t>
+          <t>MXF (OP-1a), codec XDCAM HD422, 50 Mb/s mín. (CBR), croma 4:2:2, entrelaçado (Interlaced UFF), extensão .mxf</t>
         </is>
       </c>
       <c r="L398" t="inlineStr">
         <is>
-          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido. Margem de segurança de 5 a 10cm sobre os limites visíveis; considerar a mesma margem junto aos puxadores das portas.</t>
+          <t>Estrutura obrigatória do ficheiro: o conteúdo publicitário deve começar no primeiro frame de vídeo e terminar no último — pre-roll e post-roll de 0 frames, duração do ficheiro = duração do spot x 25 frames. Áudio: PCM, 2 canais (stereo), 24 bit, 48 KHz, peak level -3dB TP máx., loudness (integrado) -23 LUFS. Nomenclatura sugerida para o ficheiro: &lt;Pub ID&gt;_&lt;Nome do Spot&gt;_&lt;Duração&gt;.mxf (ex.: PUB-2015-000345_Fiat 500X Sport Edition_30.mxf) — não é obrigatória, mas recomendada sempre que possível. Entrega exclusivamente por utilizador registado através do Portal GoFastWay (www.gofastway.tv). Todos os ficheiros passam por controlo automático de qualidade (conformidade técnica com estas specs + análise subjetiva de vídeo e áudio); em caso de inconsistência, a GoFastWay pode pedir a entrega de um novo ficheiro corrigido.</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>TV</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>TV</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Unimidia/Spreading</t>
+          <t>TV</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>Spreading</t>
+          <t>TV</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>Táxi Doorcover Madeira - Lateral Esquerda</t>
+          <t>Ecrã Fracionado / Split Screen</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>Escala 1/10. Área visível variável consoante o ano/modelo da viatura (táxis da Madeira).</t>
+          <t>480x1080px (25% de um ecrã de 1920x1080px), 25 fps</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>16:9</t>
         </is>
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>InDesign CS3, Illustrator CS3, Photoshop CS3 ou PDF. Ficheiros EPS ou TIFF.</t>
+          <t>QuickTime (.MOV), ProRes 4444 (com canal Alpha) ou ProRes 422 (sem Alpha), 1080i entrelaçado (Upper/odd Field First), 25 fps</t>
         </is>
       </c>
       <c r="L399" t="inlineStr">
         <is>
-          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido. Margem de segurança de 5 a 10cm sobre os limites visíveis; considerar a mesma margem junto aos puxadores das portas.</t>
+          <t>Conteúdo publicitário que ocupa no máximo 25% do ecrã, transmitido em simultâneo com programas de entretenimento, desporto e magazine. Duração 10″, com entrada e saída incluídas nesses 10″. Sem áudio. Tem de manter a palavra "PUBLICIDADE" com leitura garantida e dentro da Safe Area durante todo o tempo em que está no ar. Entra pela direita do ecrã na TVI e pela esquerda na CNN Portugal. Safe Area geral: 96px horizontais / 54px verticais a partir da margem; Title Safe Area: 192px horizontais / 108px verticais — nenhuma informação relevante deve ficar fora destas áreas.</t>
         </is>
       </c>
     </row>
@@ -19817,12 +19847,12 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>Spot TV (HD — XDCAM HD422)</t>
+          <t>Telepromoção</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>1920x1080px, 25 fps</t>
+          <t>1920x1080px (plasma de estúdio; a zona útil do plasma tem 220px de altura a partir da base do ecrã) e oráculo 1920x1080px</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
@@ -19832,106 +19862,76 @@
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>MXF (OP-1a), codec XDCAM HD422, 50 Mb/s mín. (CBR), croma 4:2:2, entrelaçado (Interlaced UFF), extensão .mxf</t>
+          <t>Imagens/grafismos: JPEG, PNG, PSD, AI/EPS (Illustrator versão CC), TIFF ou TGA, todos em resolução HD; ficheiros 3D: C4D (formato ideal), FBX ou OBJ. Vídeo: Formato de vídeo genérico (aplicável salvo indicação em contrário): wrapper MXF OP1a (.MXF), XDCAM HD 4:2:2, 1080i, 25 fps, entrelaçado (Upper/odd Field First), MPEG2 @ 50Mbps, perfil 4:2:2@HL, 1920x1080px, aspect ratio 16:9. Áudio: 8 canais @ 24 bits, PGM nos primeiros dois canais, 48.0 KHz, PCM não comprimido (.wav ou .aiff depois de desembrulhado), nível de referência -20dBFS, loudness -23 LUFS (EBU R.128).</t>
         </is>
       </c>
       <c r="L400" t="inlineStr">
         <is>
-          <t>Estrutura obrigatória do ficheiro: o conteúdo publicitário deve começar no primeiro frame de vídeo e terminar no último — pre-roll e post-roll de 0 frames, duração do ficheiro = duração do spot x 25 frames. Áudio: PCM, 2 canais (stereo), 24 bit, 48 KHz, peak level -3dB TP máx., loudness (integrado) -23 LUFS. Nomenclatura sugerida para o ficheiro: &lt;Pub ID&gt;_&lt;Nome do Spot&gt;_&lt;Duração&gt;.mxf (ex.: PUB-2015-000345_Fiat 500X Sport Edition_30.mxf) — não é obrigatória, mas recomendada sempre que possível. Entrega exclusivamente por utilizador registado através do Portal GoFastWay (www.gofastway.tv). Todos os ficheiros passam por controlo automático de qualidade (conformidade técnica com estas specs + análise subjetiva de vídeo e áudio); em caso de inconsistência, a GoFastWay pode pedir a entrega de um novo ficheiro corrigido.</t>
+          <t>Materiais a fornecer para produção de grafismos, ou grafismos já finalizados — usados no plasma existente no estúdio (para passar vídeos, fotografias ou grafismos) e/ou no oráculo. Devem ser enquadrados dentro das áreas de segurança indicadas para os logos e textos não correrem o risco de serem cortados ou distorcidos (Safe Area geral: 96px horizontais / 54px verticais a partir da margem; Title Safe Area: 192px horizontais / 108px verticais — nenhuma informação relevante deve ficar fora destas áreas. No plasma de estúdio, a zona útil começa a 220px da base do ecrã; no oráculo aplica-se a Title Safe Area). Os guiões para telepromoções de 60″ de duração devem ter entre 730 e 800 caracteres sem espaçamento. Fontes de letra em formato TT, para PC; referências de cor em RGB. Todos os materiais devem ser fornecidos com pelo menos uma semana de antecedência relativamente à data de realização da telepromoção, nos formatos indicados.</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>TV</t>
+          <t>Rádio</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>TV</t>
+          <t>Rádio</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>TV</t>
+          <t>Rádio</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>TV</t>
+          <t>Rádio</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>Ecrã Fracionado / Split Screen</t>
-        </is>
-      </c>
-      <c r="G401" t="inlineStr">
-        <is>
-          <t>480x1080px (25% de um ecrã de 1920x1080px), 25 fps</t>
-        </is>
-      </c>
-      <c r="H401" t="inlineStr">
-        <is>
-          <t>16:9</t>
+          <t>Spot Rádio</t>
         </is>
       </c>
       <c r="J401" t="inlineStr">
         <is>
-          <t>QuickTime (.MOV), ProRes 4444 (com canal Alpha) ou ProRes 422 (sem Alpha), 1080i entrelaçado (Upper/odd Field First), 25 fps</t>
-        </is>
-      </c>
-      <c r="L401" t="inlineStr">
-        <is>
-          <t>Conteúdo publicitário que ocupa no máximo 25% do ecrã, transmitido em simultâneo com programas de entretenimento, desporto e magazine. Duração 10″, com entrada e saída incluídas nesses 10″. Sem áudio. Tem de manter a palavra "PUBLICIDADE" com leitura garantida e dentro da Safe Area durante todo o tempo em que está no ar. Entra pela direita do ecrã na TVI e pela esquerda na CNN Portugal. Safe Area geral: 96px horizontais / 54px verticais a partir da margem; Title Safe Area: 192px horizontais / 108px verticais — nenhuma informação relevante deve ficar fora destas áreas.</t>
+          <t>MP3</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>TV</t>
+          <t>Rádio</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>TV</t>
+          <t>Rádio</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>TV</t>
+          <t>Rádio</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>TV</t>
+          <t>Rádio</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>Telepromoção</t>
-        </is>
-      </c>
-      <c r="G402" t="inlineStr">
-        <is>
-          <t>1920x1080px (plasma de estúdio; a zona útil do plasma tem 220px de altura a partir da base do ecrã) e oráculo 1920x1080px</t>
-        </is>
-      </c>
-      <c r="H402" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
-      <c r="J402" t="inlineStr">
-        <is>
-          <t>Imagens/grafismos: JPEG, PNG, PSD, AI/EPS (Illustrator versão CC), TIFF ou TGA, todos em resolução HD; ficheiros 3D: C4D (formato ideal), FBX ou OBJ. Vídeo: Formato de vídeo genérico (aplicável salvo indicação em contrário): wrapper MXF OP1a (.MXF), XDCAM HD 4:2:2, 1080i, 25 fps, entrelaçado (Upper/odd Field First), MPEG2 @ 50Mbps, perfil 4:2:2@HL, 1920x1080px, aspect ratio 16:9. Áudio: 8 canais @ 24 bits, PGM nos primeiros dois canais, 48.0 KHz, PCM não comprimido (.wav ou .aiff depois de desembrulhado), nível de referência -20dBFS, loudness -23 LUFS (EBU R.128).</t>
+          <t>Live Copies</t>
         </is>
       </c>
       <c r="L402" t="inlineStr">
         <is>
-          <t>Materiais a fornecer para produção de grafismos, ou grafismos já finalizados — usados no plasma existente no estúdio (para passar vídeos, fotografias ou grafismos) e/ou no oráculo. Devem ser enquadrados dentro das áreas de segurança indicadas para os logos e textos não correrem o risco de serem cortados ou distorcidos (Safe Area geral: 96px horizontais / 54px verticais a partir da margem; Title Safe Area: 192px horizontais / 108px verticais — nenhuma informação relevante deve ficar fora destas áreas. No plasma de estúdio, a zona útil começa a 220px da base do ecrã; no oráculo aplica-se a Title Safe Area). Os guiões para telepromoções de 60″ de duração devem ter entre 730 e 800 caracteres sem espaçamento. Fontes de letra em formato TT, para PC; referências de cor em RGB. Todos os materiais devem ser fornecidos com pelo menos uma semana de antecedência relativamente à data de realização da telepromoção, nos formatos indicados.</t>
+          <t>É necessário fornecer um briefing da campanha, incluindo o conceito, as mensagens-chave e o tom de comunicação. A partir desse briefing, a própria rádio desenvolve o guião e produz a conversa entre os animadores, que pode ser realizada em direto ou previamente gravada, sempre com as vozes da estação.</t>
         </is>
       </c>
     </row>
@@ -19958,170 +19958,180 @@
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>Spot Rádio</t>
-        </is>
-      </c>
-      <c r="J403" t="inlineStr">
-        <is>
-          <t>MP3</t>
+          <t>Referência</t>
+        </is>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>É necessário fornecer uma frase curta, com cerca de 5 segundos de duração e uma construção próxima de um slogan de marca, para ser lida em antena pelos animadores da rádio.</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Rádio</t>
+          <t>CINEMA</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Rádio</t>
+          <t>Cinema</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Rádio</t>
+          <t>NOS Publicidade</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>Rádio</t>
+          <t>NOS Publicidade</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>Live Copies</t>
+          <t>Publicidade Cinema 2D</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>Formato de imagem preferencial: FLAT 1.85 — 1998x1080px.</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>1.85:1</t>
+        </is>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>Ficheiros DATA: sequência de ficheiros DPX 10-bit a 24fps, ou sequência de ficheiros TIFF em RGB. Ficheiros vídeo: QuickTime ProRes a 25fps ou 24fps, com áudio 5.1 ou 2.0 sincronizado à imagem.</t>
         </is>
       </c>
       <c r="L404" t="inlineStr">
         <is>
-          <t>É necessário fornecer um briefing da campanha, incluindo o conceito, as mensagens-chave e o tom de comunicação. A partir desse briefing, a própria rádio desenvolve o guião e produz a conversa entre os animadores, que pode ser realizada em direto ou previamente gravada, sempre com as vozes da estação.</t>
+          <t>Áudio: 6 canais (5.1) ou 2 canais (estéreo); ficheiros WAV a 24-bit; sampling 48KHz; nível de referência -20dBFS; velocidade 24fps. Masterização em Dolby Digital Cinema (VS2.0, certified partner).</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Rádio</t>
+          <t>CINEMA</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Rádio</t>
+          <t>Cinema</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Rádio</t>
+          <t>NOS Publicidade</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>Rádio</t>
+          <t>NOS Publicidade</t>
         </is>
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>Referência</t>
+          <t>Publicidade Cinema 3D</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>Formato de imagem: FLAT 1.85 — 1998x1080px, ou SCOPE 2.39 — 2048x858px (maior exploração do ecrã).</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>1.85:1 (FLAT) ou 2.39:1 (SCOPE)</t>
+        </is>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>Ficheiros DATA: dois ficheiros separados (Left eye + Right eye) em sequência, no formato TIFF RGB 16-bit data, ou ficheiros DPX 10-bit — ambos a 24fps.</t>
         </is>
       </c>
       <c r="L405" t="inlineStr">
         <is>
-          <t>É necessário fornecer uma frase curta, com cerca de 5 segundos de duração e uma construção próxima de um slogan de marca, para ser lida em antena pelos animadores da rádio.</t>
+          <t>Áudio: 6 canais (5.1) ou 2 canais (estéreo); ficheiros WAV a 24-bit; sampling 48KHz; nível de referência -20dBFS; velocidade 24fps. Masterização em Dolby Digital Cinema (VS2.0, certified partner).</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>CINEMA</t>
+          <t>Imprensa</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Cinema</t>
+          <t>Imprensa</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>NOS Publicidade</t>
+          <t>Correio da Manhã</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>NOS Publicidade</t>
+          <t>Correio da Manhã</t>
         </is>
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>Publicidade Cinema 2D</t>
+          <t>Página</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>Formato de imagem preferencial: FLAT 1.85 — 1998x1080px.</t>
-        </is>
-      </c>
-      <c r="H406" t="inlineStr">
-        <is>
-          <t>1.85:1</t>
+          <t>257x320mm (80 módulos, 5 col. x 16 mód.)</t>
         </is>
       </c>
       <c r="J406" t="inlineStr">
         <is>
-          <t>Ficheiros DATA: sequência de ficheiros DPX 10-bit a 24fps, ou sequência de ficheiros TIFF em RGB. Ficheiros vídeo: QuickTime ProRes a 25fps ou 24fps, com áudio 5.1 ou 2.0 sincronizado à imagem.</t>
-        </is>
-      </c>
-      <c r="L406" t="inlineStr">
-        <is>
-          <t>Áudio: 6 canais (5.1) ou 2 canais (estéreo); ficheiros WAV a 24-bit; sampling 48KHz; nível de referência -20dBFS; velocidade 24fps. Masterização em Dolby Digital Cinema (VS2.0, certified partner).</t>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>CINEMA</t>
+          <t>Imprensa</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Cinema</t>
+          <t>Imprensa</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>NOS Publicidade</t>
+          <t>Correio da Manhã</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>NOS Publicidade</t>
+          <t>Correio da Manhã</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>Publicidade Cinema 3D</t>
+          <t>Meia Página</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>Formato de imagem: FLAT 1.85 — 1998x1080px, ou SCOPE 2.39 — 2048x858px (maior exploração do ecrã).</t>
-        </is>
-      </c>
-      <c r="H407" t="inlineStr">
-        <is>
-          <t>1.85:1 (FLAT) ou 2.39:1 (SCOPE)</t>
+          <t>204x240mm (48 módulos, 4 col. x 12 mód.)</t>
         </is>
       </c>
       <c r="J407" t="inlineStr">
         <is>
-          <t>Ficheiros DATA: dois ficheiros separados (Left eye + Right eye) em sequência, no formato TIFF RGB 16-bit data, ou ficheiros DPX 10-bit — ambos a 24fps.</t>
-        </is>
-      </c>
-      <c r="L407" t="inlineStr">
-        <is>
-          <t>Áudio: 6 canais (5.1) ou 2 canais (estéreo); ficheiros WAV a 24-bit; sampling 48KHz; nível de referência -20dBFS; velocidade 24fps. Masterização em Dolby Digital Cinema (VS2.0, certified partner).</t>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
     </row>
@@ -20148,12 +20158,12 @@
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>Página</t>
+          <t>1/2 Página Alto (3 Col.)</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>257x320mm (80 módulos, 5 col. x 16 mód.)</t>
+          <t>153x320mm (48 módulos, 3 col. x 16 mód.)</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
@@ -20185,12 +20195,12 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>Meia Página</t>
+          <t>1/3 Página Alto (2 Col.)</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>204x240mm (48 módulos, 4 col. x 12 mód.)</t>
+          <t>100x320mm (32 módulos, 2 col. x 16 mód.)</t>
         </is>
       </c>
       <c r="J409" t="inlineStr">
@@ -20222,12 +20232,12 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>1/2 Página Alto (3 Col.)</t>
+          <t>1/2 Página Baixo</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>153x320mm (48 módulos, 3 col. x 16 mód.)</t>
+          <t>257x160mm (40 módulos, 5 col. x 8 mód.)</t>
         </is>
       </c>
       <c r="J410" t="inlineStr">
@@ -20259,12 +20269,12 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>1/3 Página Alto (2 Col.)</t>
+          <t>1/4 Página (3 Col.)</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>100x320mm (32 módulos, 2 col. x 16 mód.)</t>
+          <t>153x160mm (24 módulos, 3 col. x 8 mód.)</t>
         </is>
       </c>
       <c r="J411" t="inlineStr">
@@ -20296,12 +20306,12 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>1/2 Página Baixo</t>
+          <t>1/4 Página (2 Col.)</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>257x160mm (40 módulos, 5 col. x 8 mód.)</t>
+          <t>100x160mm (16 módulos, 2 col. x 8 mód.)</t>
         </is>
       </c>
       <c r="J412" t="inlineStr">
@@ -20333,12 +20343,12 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>1/4 Página (3 Col.)</t>
+          <t>Rodapé</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>153x160mm (24 módulos, 3 col. x 8 mód.)</t>
+          <t>257x61mm (15 módulos, 5 col. x 3 mód.)</t>
         </is>
       </c>
       <c r="J413" t="inlineStr">
@@ -20365,17 +20375,17 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>Correio da Manhã</t>
+          <t>Mais Sport</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>1/4 Página (2 Col.)</t>
+          <t>Página</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>100x160mm (16 módulos, 2 col. x 8 mód.)</t>
+          <t>257x320mm (80 módulos, 5 col. x 16 mód.)</t>
         </is>
       </c>
       <c r="J414" t="inlineStr">
@@ -20402,17 +20412,17 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Correio da Manhã</t>
+          <t>Boa Onda</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>Rodapé</t>
+          <t>Página Dupla</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>257x61mm (15 módulos, 5 col. x 3 mód.)</t>
+          <t>400x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J415" t="inlineStr">
@@ -20439,7 +20449,7 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>Mais Sport</t>
+          <t>Boa Onda</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
@@ -20449,7 +20459,7 @@
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>257x320mm (80 módulos, 5 col. x 16 mód.)</t>
+          <t>200x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J416" t="inlineStr">
@@ -20481,12 +20491,12 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>Página Dupla</t>
+          <t>1/2 Página Dupla</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>400x295mm (+3mm bleed)</t>
+          <t>400x147mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J417" t="inlineStr">
@@ -20518,12 +20528,12 @@
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>Página</t>
+          <t>1/2 Página Alto</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>200x295mm (+3mm bleed)</t>
+          <t>100x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J418" t="inlineStr">
@@ -20555,12 +20565,12 @@
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>1/2 Página Dupla</t>
+          <t>1/2 Página Baixo</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>400x147mm (+3mm bleed)</t>
+          <t>200x147mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J419" t="inlineStr">
@@ -20592,12 +20602,12 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>1/2 Página Alto</t>
+          <t>1/3 Página Alto</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>100x295mm (+3mm bleed)</t>
+          <t>72x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J420" t="inlineStr">
@@ -20629,12 +20639,12 @@
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>1/2 Página Baixo</t>
+          <t>1/3 Página Baixo</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>200x147mm (+3mm bleed)</t>
+          <t>200x105mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J421" t="inlineStr">
@@ -20666,12 +20676,12 @@
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>1/3 Página Alto</t>
+          <t>1/4 Página</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>72x295mm (+3mm bleed)</t>
+          <t>100x147mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J422" t="inlineStr">
@@ -20703,12 +20713,12 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>1/3 Página Baixo</t>
+          <t>Rodapé</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>200x105mm (+3mm bleed)</t>
+          <t>200x78mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J423" t="inlineStr">
@@ -20735,17 +20745,17 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>Boa Onda</t>
+          <t>VIDAS</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>1/4 Página</t>
+          <t>Página Dupla</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>100x147mm (+3mm bleed)</t>
+          <t>400x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J424" t="inlineStr">
@@ -20772,17 +20782,17 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>Boa Onda</t>
+          <t>VIDAS</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>Rodapé</t>
+          <t>Página</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>200x78mm (+3mm bleed)</t>
+          <t>200x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J425" t="inlineStr">
@@ -20814,12 +20824,12 @@
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>Página Dupla</t>
+          <t>1/2 Página Dupla</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>400x295mm (+3mm bleed)</t>
+          <t>400x147mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J426" t="inlineStr">
@@ -20851,12 +20861,12 @@
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>Página</t>
+          <t>1/2 Página Alto</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>200x295mm (+3mm bleed)</t>
+          <t>100x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J427" t="inlineStr">
@@ -20888,12 +20898,12 @@
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>1/2 Página Dupla</t>
+          <t>1/2 Página Baixo</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>400x147mm (+3mm bleed)</t>
+          <t>200x147mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J428" t="inlineStr">
@@ -20925,12 +20935,12 @@
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>1/2 Página Alto</t>
+          <t>1/3 Página Alto</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>100x295mm (+3mm bleed)</t>
+          <t>72x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J429" t="inlineStr">
@@ -20962,12 +20972,12 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>1/2 Página Baixo</t>
+          <t>1/3 Página Baixo</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>200x147mm (+3mm bleed)</t>
+          <t>200x105mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J430" t="inlineStr">
@@ -20999,12 +21009,12 @@
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>1/3 Página Alto</t>
+          <t>1/4 Página</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>72x295mm (+3mm bleed)</t>
+          <t>100x147mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J431" t="inlineStr">
@@ -21036,12 +21046,12 @@
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>1/3 Página Baixo</t>
+          <t>Rodapé</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>200x105mm (+3mm bleed)</t>
+          <t>200x78mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J432" t="inlineStr">
@@ -21068,17 +21078,17 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>VIDAS</t>
+          <t>Domingo</t>
         </is>
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>1/4 Página</t>
+          <t>Página Dupla</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>100x147mm (+3mm bleed)</t>
+          <t>400x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J433" t="inlineStr">
@@ -21105,17 +21115,17 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>VIDAS</t>
+          <t>Domingo</t>
         </is>
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>Rodapé</t>
+          <t>Página</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>200x78mm (+3mm bleed)</t>
+          <t>200x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J434" t="inlineStr">
@@ -21147,12 +21157,12 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>Página Dupla</t>
+          <t>1/2 Página Dupla</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>400x295mm (+3mm bleed)</t>
+          <t>400x147mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J435" t="inlineStr">
@@ -21184,12 +21194,12 @@
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>Página</t>
+          <t>1/2 Página Alto</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>200x295mm (+3mm bleed)</t>
+          <t>100x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
@@ -21221,12 +21231,12 @@
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>1/2 Página Dupla</t>
+          <t>1/2 Página Baixo</t>
         </is>
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>400x147mm (+3mm bleed)</t>
+          <t>200x147mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J437" t="inlineStr">
@@ -21258,12 +21268,12 @@
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>1/2 Página Alto</t>
+          <t>1/3 Página Alto</t>
         </is>
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>100x295mm (+3mm bleed)</t>
+          <t>72x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J438" t="inlineStr">
@@ -21295,12 +21305,12 @@
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>1/2 Página Baixo</t>
+          <t>1/3 Página Baixo</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>200x147mm (+3mm bleed)</t>
+          <t>200x105mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J439" t="inlineStr">
@@ -21332,12 +21342,12 @@
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>1/3 Página Alto</t>
+          <t>1/4 Página</t>
         </is>
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>72x295mm (+3mm bleed)</t>
+          <t>100x147mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J440" t="inlineStr">
@@ -21369,12 +21379,12 @@
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>1/3 Página Baixo</t>
+          <t>Rodapé</t>
         </is>
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>200x105mm (+3mm bleed)</t>
+          <t>200x78mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J441" t="inlineStr">
@@ -21396,27 +21406,27 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Correio da Manhã</t>
+          <t>Destak</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>Domingo</t>
+          <t>Destak</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>1/4 Página</t>
+          <t>Capa Falsa</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>100x147mm (+3mm bleed)</t>
+          <t>210x280mm | 230x300mm (corte)</t>
         </is>
       </c>
       <c r="J442" t="inlineStr">
         <is>
-          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+          <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
         </is>
       </c>
     </row>
@@ -21433,27 +21443,27 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Correio da Manhã</t>
+          <t>Destak</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>Domingo</t>
+          <t>Destak</t>
         </is>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>Rodapé</t>
+          <t>Rodapé 1ª Página</t>
         </is>
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>200x78mm (+3mm bleed)</t>
+          <t>210x42mm</t>
         </is>
       </c>
       <c r="J443" t="inlineStr">
         <is>
-          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+          <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
         </is>
       </c>
     </row>
@@ -21480,12 +21490,12 @@
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>Capa Falsa</t>
+          <t>Janela Premium</t>
         </is>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>210x280mm | 230x300mm (corte)</t>
+          <t>49,5x78,5mm</t>
         </is>
       </c>
       <c r="J444" t="inlineStr">
@@ -21517,12 +21527,12 @@
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>Rodapé 1ª Página</t>
+          <t>Página Dupla</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>210x42mm</t>
+          <t>440x280mm | 460x300mm (corte)</t>
         </is>
       </c>
       <c r="J445" t="inlineStr">
@@ -21554,12 +21564,12 @@
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>Janela Premium</t>
+          <t>Página</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>49,5x78,5mm</t>
+          <t>210x280mm | 230x300mm (corte)</t>
         </is>
       </c>
       <c r="J446" t="inlineStr">
@@ -21591,12 +21601,12 @@
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>Página Dupla</t>
+          <t>Contracapa</t>
         </is>
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>440x280mm | 460x300mm (corte)</t>
+          <t>210x280mm | 230x300mm (corte)</t>
         </is>
       </c>
       <c r="J447" t="inlineStr">
@@ -21628,12 +21638,12 @@
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>Página</t>
+          <t>1/2 Página Alto</t>
         </is>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>210x280mm | 230x300mm (corte)</t>
+          <t>103x280mm</t>
         </is>
       </c>
       <c r="J448" t="inlineStr">
@@ -21665,12 +21675,12 @@
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>Contracapa</t>
+          <t>1/2 Página Baixo</t>
         </is>
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>210x280mm | 230x300mm (corte)</t>
+          <t>210x138mm</t>
         </is>
       </c>
       <c r="J449" t="inlineStr">
@@ -21702,12 +21712,12 @@
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>1/2 Página Alto</t>
+          <t>3/4 Página</t>
         </is>
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>103x280mm</t>
+          <t>103x138mm</t>
         </is>
       </c>
       <c r="J450" t="inlineStr">
@@ -21739,12 +21749,12 @@
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>1/2 Página Baixo</t>
+          <t>Rodapé</t>
         </is>
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>210x138mm</t>
+          <t>210x42mm</t>
         </is>
       </c>
       <c r="J451" t="inlineStr">
@@ -21766,27 +21776,27 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Destak</t>
+          <t>Jornal de Negócios</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>Destak</t>
+          <t>Jornal de Negócios</t>
         </is>
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>3/4 Página</t>
+          <t>Página</t>
         </is>
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>103x138mm</t>
+          <t>257x320mm (80 módulos, 5 col. x 16 mód.)</t>
         </is>
       </c>
       <c r="J452" t="inlineStr">
         <is>
-          <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
     </row>
@@ -21803,27 +21813,27 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Destak</t>
+          <t>Jornal de Negócios</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>Destak</t>
+          <t>Jornal de Negócios</t>
         </is>
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>Rodapé</t>
+          <t>Meia Página</t>
         </is>
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>210x42mm</t>
+          <t>204x240mm (48 módulos, 4 col. x 12 mód.)</t>
         </is>
       </c>
       <c r="J453" t="inlineStr">
         <is>
-          <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
+          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
     </row>
@@ -21850,12 +21860,12 @@
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>Página</t>
+          <t>1/2 Página Alto (3 Col.)</t>
         </is>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>257x320mm (80 módulos, 5 col. x 16 mód.)</t>
+          <t>153x320mm (48 módulos, 3 col. x 16 mód.)</t>
         </is>
       </c>
       <c r="J454" t="inlineStr">
@@ -21887,12 +21897,12 @@
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>Meia Página</t>
+          <t>1/3 Página Alto (2 Col.)</t>
         </is>
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>204x240mm (48 módulos, 4 col. x 12 mód.)</t>
+          <t>100x320mm (32 módulos, 2 col. x 16 mód.)</t>
         </is>
       </c>
       <c r="J455" t="inlineStr">
@@ -21924,12 +21934,12 @@
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>1/2 Página Alto (3 Col.)</t>
+          <t>1/2 Página Baixo</t>
         </is>
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>153x320mm (48 módulos, 3 col. x 16 mód.)</t>
+          <t>257x160mm (40 módulos, 5 col. x 8 mód.)</t>
         </is>
       </c>
       <c r="J456" t="inlineStr">
@@ -21961,12 +21971,12 @@
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>1/3 Página Alto (2 Col.)</t>
+          <t>1/4 Página (3 Col.)</t>
         </is>
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>100x320mm (32 módulos, 2 col. x 16 mód.)</t>
+          <t>153x160mm (24 módulos, 3 col. x 8 mód.)</t>
         </is>
       </c>
       <c r="J457" t="inlineStr">
@@ -21998,12 +22008,12 @@
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>1/2 Página Baixo</t>
+          <t>1/4 Página (2 Col.)</t>
         </is>
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>257x160mm (40 módulos, 5 col. x 8 mód.)</t>
+          <t>100x160mm (16 módulos, 2 col. x 8 mód.)</t>
         </is>
       </c>
       <c r="J458" t="inlineStr">
@@ -22035,12 +22045,12 @@
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>1/4 Página (3 Col.)</t>
+          <t>Rodapé</t>
         </is>
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>153x160mm (24 módulos, 3 col. x 8 mód.)</t>
+          <t>257x61mm (15 módulos, 5 col. x 3 mód.)</t>
         </is>
       </c>
       <c r="J459" t="inlineStr">
@@ -22072,12 +22082,12 @@
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>1/4 Página (2 Col.)</t>
+          <t>Janela de Primeira Página</t>
         </is>
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>100x160mm (16 módulos, 2 col. x 8 mód.)</t>
+          <t>55x96mm</t>
         </is>
       </c>
       <c r="J460" t="inlineStr">
@@ -22109,12 +22119,12 @@
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t>Rodapé</t>
+          <t>Orelha de Primeira Página</t>
         </is>
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>257x61mm (15 módulos, 5 col. x 3 mód.)</t>
+          <t>55x45mm</t>
         </is>
       </c>
       <c r="J461" t="inlineStr">
@@ -22146,12 +22156,12 @@
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>Janela de Primeira Página</t>
+          <t>Rodapé de Primeira Página</t>
         </is>
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>55x96mm</t>
+          <t>195x25mm</t>
         </is>
       </c>
       <c r="J462" t="inlineStr">
@@ -22183,12 +22193,12 @@
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>Orelha de Primeira Página</t>
+          <t>Home Page (Quadrado 2ª Página)</t>
         </is>
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>55x45mm</t>
+          <t>150x130mm</t>
         </is>
       </c>
       <c r="J463" t="inlineStr">
@@ -22220,12 +22230,12 @@
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>Rodapé de Primeira Página</t>
+          <t>Rodapé Última Página</t>
         </is>
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>195x25mm</t>
+          <t>205x61mm</t>
         </is>
       </c>
       <c r="J464" t="inlineStr">
@@ -22247,22 +22257,22 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Jornal de Negócios</t>
+          <t>Record</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>Jornal de Negócios</t>
+          <t>Record</t>
         </is>
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>Home Page (Quadrado 2ª Página)</t>
+          <t>Página</t>
         </is>
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>150x130mm</t>
+          <t>257x320mm (80 módulos, 5 col. x 16 mód.)</t>
         </is>
       </c>
       <c r="J465" t="inlineStr">
@@ -22284,22 +22294,22 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Jornal de Negócios</t>
+          <t>Record</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>Jornal de Negócios</t>
+          <t>Record</t>
         </is>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>Rodapé Última Página</t>
+          <t>Meia Página</t>
         </is>
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>205x61mm</t>
+          <t>204x240mm (48 módulos, 4 col. x 12 mód.)</t>
         </is>
       </c>
       <c r="J466" t="inlineStr">
@@ -22331,12 +22341,12 @@
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>Página</t>
+          <t>1/2 Página Alto (3 Col.)</t>
         </is>
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>257x320mm (80 módulos, 5 col. x 16 mód.)</t>
+          <t>153x320mm (48 módulos, 3 col. x 16 mód.)</t>
         </is>
       </c>
       <c r="J467" t="inlineStr">
@@ -22368,12 +22378,12 @@
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>Meia Página</t>
+          <t>1/3 Página Alto (2 Col.)</t>
         </is>
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>204x240mm (48 módulos, 4 col. x 12 mód.)</t>
+          <t>100x320mm (32 módulos, 2 col. x 16 mód.)</t>
         </is>
       </c>
       <c r="J468" t="inlineStr">
@@ -22405,12 +22415,12 @@
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>1/2 Página Alto (3 Col.)</t>
+          <t>1/2 Página Baixo</t>
         </is>
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>153x320mm (48 módulos, 3 col. x 16 mód.)</t>
+          <t>257x160mm (40 módulos, 5 col. x 8 mód.)</t>
         </is>
       </c>
       <c r="J469" t="inlineStr">
@@ -22442,12 +22452,12 @@
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>1/3 Página Alto (2 Col.)</t>
+          <t>1/4 Página (3 Col.)</t>
         </is>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>100x320mm (32 módulos, 2 col. x 16 mód.)</t>
+          <t>153x160mm (24 módulos, 3 col. x 8 mód.)</t>
         </is>
       </c>
       <c r="J470" t="inlineStr">
@@ -22479,12 +22489,12 @@
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>1/2 Página Baixo</t>
+          <t>1/4 Página (2 Col.)</t>
         </is>
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>257x160mm (40 módulos, 5 col. x 8 mód.)</t>
+          <t>100x160mm (16 módulos, 2 col. x 8 mód.)</t>
         </is>
       </c>
       <c r="J471" t="inlineStr">
@@ -22516,12 +22526,12 @@
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>1/4 Página (3 Col.)</t>
+          <t>Rodapé</t>
         </is>
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>153x160mm (24 módulos, 3 col. x 8 mód.)</t>
+          <t>257x61mm (15 módulos, 5 col. x 3 mód.)</t>
         </is>
       </c>
       <c r="J472" t="inlineStr">
@@ -22543,22 +22553,22 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Record</t>
+          <t>Sábado</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>Record</t>
+          <t>Sábado</t>
         </is>
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>1/4 Página (2 Col.)</t>
+          <t>Página Dupla</t>
         </is>
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>100x160mm (16 módulos, 2 col. x 8 mód.)</t>
+          <t>410x275mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J473" t="inlineStr">
@@ -22580,22 +22590,22 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Record</t>
+          <t>Sábado</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>Record</t>
+          <t>Sábado</t>
         </is>
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>Rodapé</t>
+          <t>Página</t>
         </is>
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>257x61mm (15 módulos, 5 col. x 3 mód.)</t>
+          <t>205x275mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J474" t="inlineStr">
@@ -22627,12 +22637,12 @@
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>Página Dupla</t>
+          <t>1/2 Página Dupla</t>
         </is>
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>410x275mm (+3mm bleed)</t>
+          <t>410x137mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J475" t="inlineStr">
@@ -22664,12 +22674,12 @@
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>Página</t>
+          <t>1/2 Página Alto</t>
         </is>
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>205x275mm (+3mm bleed)</t>
+          <t>102x275mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J476" t="inlineStr">
@@ -22701,12 +22711,12 @@
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>1/2 Página Dupla</t>
+          <t>1/2 Página Baixo</t>
         </is>
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>410x137mm (+3mm bleed)</t>
+          <t>205x137mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J477" t="inlineStr">
@@ -22738,12 +22748,12 @@
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>1/2 Página Alto</t>
+          <t>1/3 Página Alto</t>
         </is>
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>102x275mm (+3mm bleed)</t>
+          <t>72x275mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J478" t="inlineStr">
@@ -22775,12 +22785,12 @@
       </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>1/2 Página Baixo</t>
+          <t>1/3 Página Baixo</t>
         </is>
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>205x137mm (+3mm bleed)</t>
+          <t>205x91mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J479" t="inlineStr">
@@ -22807,17 +22817,17 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>Sábado</t>
+          <t>Sábado Viajante</t>
         </is>
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>1/3 Página Alto</t>
+          <t>Página Dupla</t>
         </is>
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>72x275mm (+3mm bleed)</t>
+          <t>410x275mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J480" t="inlineStr">
@@ -22844,17 +22854,17 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>Sábado</t>
+          <t>Sábado Viajante</t>
         </is>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>1/3 Página Baixo</t>
+          <t>Página</t>
         </is>
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>205x91mm (+3mm bleed)</t>
+          <t>205x275mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J481" t="inlineStr">
@@ -22886,12 +22896,12 @@
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t>Página Dupla</t>
+          <t>1/2 Página Dupla</t>
         </is>
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>410x275mm (+3mm bleed)</t>
+          <t>410x137mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J482" t="inlineStr">
@@ -22923,12 +22933,12 @@
       </c>
       <c r="F483" t="inlineStr">
         <is>
-          <t>Página</t>
+          <t>1/2 Página Alto</t>
         </is>
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>205x275mm (+3mm bleed)</t>
+          <t>102x275mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J483" t="inlineStr">
@@ -22960,12 +22970,12 @@
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t>1/2 Página Dupla</t>
+          <t>1/2 Página Baixo</t>
         </is>
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>410x137mm (+3mm bleed)</t>
+          <t>205x137mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J484" t="inlineStr">
@@ -22997,12 +23007,12 @@
       </c>
       <c r="F485" t="inlineStr">
         <is>
-          <t>1/2 Página Alto</t>
+          <t>1/3 Página Alto</t>
         </is>
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>102x275mm (+3mm bleed)</t>
+          <t>72x275mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J485" t="inlineStr">
@@ -23034,12 +23044,12 @@
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>1/2 Página Baixo</t>
+          <t>1/3 Página Baixo</t>
         </is>
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>205x137mm (+3mm bleed)</t>
+          <t>205x91mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J486" t="inlineStr">
@@ -23061,22 +23071,22 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Sábado</t>
+          <t>TV Guia</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>Sábado Viajante</t>
+          <t>TV Guia</t>
         </is>
       </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>1/3 Página Alto</t>
+          <t>Página Dupla</t>
         </is>
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>72x275mm (+3mm bleed)</t>
+          <t>400x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J487" t="inlineStr">
@@ -23098,22 +23108,22 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Sábado</t>
+          <t>TV Guia</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>Sábado Viajante</t>
+          <t>TV Guia</t>
         </is>
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>1/3 Página Baixo</t>
+          <t>Página</t>
         </is>
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>205x91mm (+3mm bleed)</t>
+          <t>200x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J488" t="inlineStr">
@@ -23145,12 +23155,12 @@
       </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t>Página Dupla</t>
+          <t>1/2 Página Dupla</t>
         </is>
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>400x295mm (+3mm bleed)</t>
+          <t>400x147mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J489" t="inlineStr">
@@ -23182,12 +23192,12 @@
       </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t>Página</t>
+          <t>1/2 Página Alto</t>
         </is>
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>200x295mm (+3mm bleed)</t>
+          <t>100x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J490" t="inlineStr">
@@ -23219,12 +23229,12 @@
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>1/2 Página Dupla</t>
+          <t>1/2 Página Baixo</t>
         </is>
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>400x147mm (+3mm bleed)</t>
+          <t>200x147mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J491" t="inlineStr">
@@ -23256,12 +23266,12 @@
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>1/2 Página Alto</t>
+          <t>1/3 Página Alto</t>
         </is>
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>100x295mm (+3mm bleed)</t>
+          <t>72x295mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J492" t="inlineStr">
@@ -23293,12 +23303,12 @@
       </c>
       <c r="F493" t="inlineStr">
         <is>
-          <t>1/2 Página Baixo</t>
+          <t>1/3 Página Baixo</t>
         </is>
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>200x147mm (+3mm bleed)</t>
+          <t>200x105mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J493" t="inlineStr">
@@ -23320,27 +23330,27 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>TV Guia</t>
+          <t>Expresso</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>TV Guia</t>
+          <t>Expresso</t>
         </is>
       </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>1/3 Página Alto</t>
+          <t>Página Dupla</t>
         </is>
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>72x295mm (+3mm bleed)</t>
+          <t>548x408mm</t>
         </is>
       </c>
       <c r="J494" t="inlineStr">
         <is>
-          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
     </row>
@@ -23357,27 +23367,27 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>TV Guia</t>
+          <t>Expresso</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>TV Guia</t>
+          <t>Expresso</t>
         </is>
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>1/3 Página Baixo</t>
+          <t>Página</t>
         </is>
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>200x105mm (+3mm bleed)</t>
+          <t>264x408mm</t>
         </is>
       </c>
       <c r="J495" t="inlineStr">
         <is>
-          <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
+          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
     </row>
@@ -23404,12 +23414,12 @@
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>Página Dupla</t>
+          <t>1/2 Página Baixo</t>
         </is>
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>548x408mm</t>
+          <t>264x201,8mm</t>
         </is>
       </c>
       <c r="J496" t="inlineStr">
@@ -23441,12 +23451,12 @@
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>Página</t>
+          <t>1/2 Página Alto</t>
         </is>
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>264x408mm</t>
+          <t>130x408mm</t>
         </is>
       </c>
       <c r="J497" t="inlineStr">
@@ -23478,12 +23488,12 @@
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>1/2 Página Baixo</t>
+          <t>1/2 Página Dupla</t>
         </is>
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>264x201,8mm</t>
+          <t>548x201,8mm</t>
         </is>
       </c>
       <c r="J498" t="inlineStr">
@@ -23515,12 +23525,12 @@
       </c>
       <c r="F499" t="inlineStr">
         <is>
-          <t>1/2 Página Alto</t>
+          <t>Júnior Page</t>
         </is>
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>130x408mm</t>
+          <t>174,8x277mm</t>
         </is>
       </c>
       <c r="J499" t="inlineStr">
@@ -23552,12 +23562,12 @@
       </c>
       <c r="F500" t="inlineStr">
         <is>
-          <t>1/2 Página Dupla</t>
+          <t>1/4 Página</t>
         </is>
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>548x201,8mm</t>
+          <t>130x201,8mm</t>
         </is>
       </c>
       <c r="J500" t="inlineStr">
@@ -23589,12 +23599,12 @@
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>Júnior Page</t>
+          <t>1/4 Página Landscape</t>
         </is>
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>174,8x277mm</t>
+          <t>264x92,2mm</t>
         </is>
       </c>
       <c r="J501" t="inlineStr">
@@ -23626,12 +23636,12 @@
       </c>
       <c r="F502" t="inlineStr">
         <is>
-          <t>1/4 Página</t>
+          <t>1/8 Página</t>
         </is>
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>130x201,8mm</t>
+          <t>130x101mm</t>
         </is>
       </c>
       <c r="J502" t="inlineStr">
@@ -23663,12 +23673,12 @@
       </c>
       <c r="F503" t="inlineStr">
         <is>
-          <t>1/4 Página Landscape</t>
+          <t>Orelha de Capa</t>
         </is>
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>264x92,2mm</t>
+          <t>450x60mm</t>
         </is>
       </c>
       <c r="J503" t="inlineStr">
@@ -23700,12 +23710,12 @@
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>1/8 Página</t>
+          <t>Sanca de Capa</t>
         </is>
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>130x101mm</t>
+          <t>240x264mm</t>
         </is>
       </c>
       <c r="J504" t="inlineStr">
@@ -23737,17 +23747,17 @@
       </c>
       <c r="F505" t="inlineStr">
         <is>
-          <t>Orelha de Capa</t>
+          <t>Saco Expresso</t>
         </is>
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>450x60mm</t>
+          <t>450x360mm (área útil do cliente: 450x278mm)</t>
         </is>
       </c>
       <c r="J505" t="inlineStr">
         <is>
-          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
+          <t>PDF em alta definição (elementos de desenho em vetorial, imagens à parte + JPEG para visualização)</t>
         </is>
       </c>
     </row>
@@ -23769,17 +23779,17 @@
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>Expresso</t>
+          <t>Expresso Economia</t>
         </is>
       </c>
       <c r="F506" t="inlineStr">
         <is>
-          <t>Sanca de Capa</t>
+          <t>Página Dupla</t>
         </is>
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>240x264mm</t>
+          <t>548x408mm</t>
         </is>
       </c>
       <c r="J506" t="inlineStr">
@@ -23806,22 +23816,22 @@
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>Expresso</t>
+          <t>Expresso Economia</t>
         </is>
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>Saco Expresso</t>
+          <t>Página</t>
         </is>
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>450x360mm (área útil do cliente: 450x278mm)</t>
+          <t>264x408mm</t>
         </is>
       </c>
       <c r="J507" t="inlineStr">
         <is>
-          <t>PDF em alta definição (elementos de desenho em vetorial, imagens à parte + JPEG para visualização)</t>
+          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
     </row>
@@ -23848,12 +23858,12 @@
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>Página Dupla</t>
+          <t>1/2 Página Baixo</t>
         </is>
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>548x408mm</t>
+          <t>264x201,8mm</t>
         </is>
       </c>
       <c r="J508" t="inlineStr">
@@ -23885,12 +23895,12 @@
       </c>
       <c r="F509" t="inlineStr">
         <is>
-          <t>Página</t>
+          <t>1/2 Página Alto</t>
         </is>
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>264x408mm</t>
+          <t>130x408mm</t>
         </is>
       </c>
       <c r="J509" t="inlineStr">
@@ -23922,12 +23932,12 @@
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>1/2 Página Baixo</t>
+          <t>1/2 Página Dupla</t>
         </is>
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>264x201,8mm</t>
+          <t>548x201,8mm</t>
         </is>
       </c>
       <c r="J510" t="inlineStr">
@@ -23959,12 +23969,12 @@
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>1/2 Página Alto</t>
+          <t>Júnior Page</t>
         </is>
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>130x408mm</t>
+          <t>174,8x277mm</t>
         </is>
       </c>
       <c r="J511" t="inlineStr">
@@ -23996,12 +24006,12 @@
       </c>
       <c r="F512" t="inlineStr">
         <is>
-          <t>1/2 Página Dupla</t>
+          <t>1/4 Página</t>
         </is>
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>548x201,8mm</t>
+          <t>130x201,8mm</t>
         </is>
       </c>
       <c r="J512" t="inlineStr">
@@ -24033,12 +24043,12 @@
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>Júnior Page</t>
+          <t>1/4 Página Landscape</t>
         </is>
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>174,8x277mm</t>
+          <t>264x92,2mm</t>
         </is>
       </c>
       <c r="J513" t="inlineStr">
@@ -24070,12 +24080,12 @@
       </c>
       <c r="F514" t="inlineStr">
         <is>
-          <t>1/4 Página</t>
+          <t>1/8 Página</t>
         </is>
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>130x201,8mm</t>
+          <t>130x101mm</t>
         </is>
       </c>
       <c r="J514" t="inlineStr">
@@ -24107,12 +24117,12 @@
       </c>
       <c r="F515" t="inlineStr">
         <is>
-          <t>1/4 Página Landscape</t>
+          <t>Orelha (Janela na Primeira Página)</t>
         </is>
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>264x92,2mm</t>
+          <t>41x32mm</t>
         </is>
       </c>
       <c r="J515" t="inlineStr">
@@ -24144,12 +24154,12 @@
       </c>
       <c r="F516" t="inlineStr">
         <is>
-          <t>1/8 Página</t>
+          <t>Orelha Grande (Janela na Primeira Página)</t>
         </is>
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>130x101mm</t>
+          <t>41x87mm</t>
         </is>
       </c>
       <c r="J516" t="inlineStr">
@@ -24176,17 +24186,17 @@
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>Expresso Economia</t>
+          <t>Revista E</t>
         </is>
       </c>
       <c r="F517" t="inlineStr">
         <is>
-          <t>Orelha (Janela na Primeira Página)</t>
+          <t>Página Dupla</t>
         </is>
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>41x32mm</t>
+          <t>530x337mm</t>
         </is>
       </c>
       <c r="J517" t="inlineStr">
@@ -24213,17 +24223,17 @@
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>Expresso Economia</t>
+          <t>Revista E</t>
         </is>
       </c>
       <c r="F518" t="inlineStr">
         <is>
-          <t>Orelha Grande (Janela na Primeira Página)</t>
+          <t>Página</t>
         </is>
       </c>
       <c r="G518" t="inlineStr">
         <is>
-          <t>41x87mm</t>
+          <t>265x337mm</t>
         </is>
       </c>
       <c r="J518" t="inlineStr">
@@ -24255,12 +24265,12 @@
       </c>
       <c r="F519" t="inlineStr">
         <is>
-          <t>Página Dupla</t>
+          <t>1/2 Página Baixo</t>
         </is>
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>530x337mm</t>
+          <t>265x167mm</t>
         </is>
       </c>
       <c r="J519" t="inlineStr">
@@ -24292,12 +24302,12 @@
       </c>
       <c r="F520" t="inlineStr">
         <is>
-          <t>Página</t>
+          <t>1/2 Página Alto</t>
         </is>
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>265x337mm</t>
+          <t>130x337mm</t>
         </is>
       </c>
       <c r="J520" t="inlineStr">
@@ -24329,12 +24339,12 @@
       </c>
       <c r="F521" t="inlineStr">
         <is>
-          <t>1/2 Página Baixo</t>
+          <t>1/3 Página Alto</t>
         </is>
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>265x167mm</t>
+          <t>90x337mm</t>
         </is>
       </c>
       <c r="J521" t="inlineStr">
@@ -24366,12 +24376,12 @@
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>1/2 Página Alto</t>
+          <t>Rodapé</t>
         </is>
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>130x337mm</t>
+          <t>265x108mm</t>
         </is>
       </c>
       <c r="J522" t="inlineStr">
@@ -24403,12 +24413,12 @@
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>1/3 Página Alto</t>
+          <t>1/4 Página</t>
         </is>
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>90x337mm</t>
+          <t>115x147mm</t>
         </is>
       </c>
       <c r="J523" t="inlineStr">
@@ -24440,12 +24450,12 @@
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>Rodapé</t>
+          <t>1/6 Página</t>
         </is>
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>265x108mm</t>
+          <t>75x147mm</t>
         </is>
       </c>
       <c r="J524" t="inlineStr">
@@ -24477,12 +24487,12 @@
       </c>
       <c r="F525" t="inlineStr">
         <is>
-          <t>1/4 Página</t>
+          <t>1/8 Página</t>
         </is>
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>115x147mm</t>
+          <t>115x71mm</t>
         </is>
       </c>
       <c r="J525" t="inlineStr">
@@ -24504,27 +24514,27 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Expresso</t>
+          <t>Attitude</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>Revista E</t>
+          <t>Attitude</t>
         </is>
       </c>
       <c r="F526" t="inlineStr">
         <is>
-          <t>1/6 Página</t>
+          <t>Página (Par/Ímpar)</t>
         </is>
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>75x147mm</t>
+          <t>215x278mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J526" t="inlineStr">
         <is>
-          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
+          <t>PDF, EPS ou TIFF em alta resolução de 400 DPI (mínimo 300 DPI), CMYK, sem atribuição de perfil final</t>
         </is>
       </c>
     </row>
@@ -24541,27 +24551,27 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Expresso</t>
+          <t>Attitude</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>Revista E</t>
+          <t>Attitude</t>
         </is>
       </c>
       <c r="F527" t="inlineStr">
         <is>
-          <t>1/8 Página</t>
+          <t>1/2 Página Vertical</t>
         </is>
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>115x71mm</t>
+          <t>106,25x278mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J527" t="inlineStr">
         <is>
-          <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
+          <t>PDF, EPS ou TIFF em alta resolução de 400 DPI (mínimo 300 DPI), CMYK, sem atribuição de perfil final</t>
         </is>
       </c>
     </row>
@@ -24588,12 +24598,12 @@
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>Página (Par/Ímpar)</t>
+          <t>1/2 Página Horizontal</t>
         </is>
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>215x278mm (+3mm bleed)</t>
+          <t>215x143mm (+3mm bleed)</t>
         </is>
       </c>
       <c r="J528" t="inlineStr">
@@ -24625,12 +24635,12 @@
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>1/2 Página Vertical</t>
+          <t>Página Dupla</t>
         </is>
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>106,25x278mm (+3mm bleed)</t>
+          <t>430x278mm (+3mm bleed, +6mm massa central)</t>
         </is>
       </c>
       <c r="J529" t="inlineStr">
@@ -24642,129 +24652,55 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>Imprensa</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>Imprensa</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Attitude</t>
+          <t>Genérico</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>Attitude</t>
+          <t>Genérico</t>
         </is>
       </c>
       <c r="F530" t="inlineStr">
         <is>
-          <t>1/2 Página Horizontal</t>
+          <t>Branded Content</t>
         </is>
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>215x143mm (+3mm bleed)</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="J530" t="inlineStr">
         <is>
-          <t>PDF, EPS ou TIFF em alta resolução de 400 DPI (mínimo 300 DPI), CMYK, sem atribuição de perfil final</t>
-        </is>
-      </c>
-    </row>
-    <row r="531">
-      <c r="A531" t="inlineStr">
-        <is>
-          <t>Imprensa</t>
-        </is>
-      </c>
-      <c r="B531" t="inlineStr">
-        <is>
-          <t>Imprensa</t>
-        </is>
-      </c>
-      <c r="C531" t="inlineStr">
-        <is>
-          <t>Attitude</t>
-        </is>
-      </c>
-      <c r="D531" t="inlineStr">
-        <is>
-          <t>Attitude</t>
-        </is>
-      </c>
-      <c r="F531" t="inlineStr">
-        <is>
-          <t>Página Dupla</t>
-        </is>
-      </c>
-      <c r="G531" t="inlineStr">
-        <is>
-          <t>430x278mm (+3mm bleed, +6mm massa central)</t>
-        </is>
-      </c>
-      <c r="J531" t="inlineStr">
-        <is>
-          <t>PDF, EPS ou TIFF em alta resolução de 400 DPI (mínimo 300 DPI), CMYK, sem atribuição de perfil final</t>
-        </is>
-      </c>
-    </row>
-    <row r="532">
-      <c r="A532" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B532" t="inlineStr">
-        <is>
-          <t>Internet</t>
-        </is>
-      </c>
-      <c r="C532" t="inlineStr">
-        <is>
-          <t>Genérico</t>
-        </is>
-      </c>
-      <c r="D532" t="inlineStr">
-        <is>
-          <t>Genérico</t>
-        </is>
-      </c>
-      <c r="F532" t="inlineStr">
-        <is>
-          <t>Branded Content</t>
-        </is>
-      </c>
-      <c r="G532" t="inlineStr">
+          <t>Envio de Briefing a detalhar principais mensagens de comunicação + URLs destino dos artigos (caso se aplique) + editáveis da campanha para utilização pelo meio + Imagens estáticas formato 9:16 e 1:1 + MREC (300x250) + Halfpage (300x600) + Outros elementos/imagens considerados importantes</t>
+        </is>
+      </c>
+      <c r="K530" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H532" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I532" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J532" t="inlineStr">
-        <is>
-          <t>Envio de Briefing a detalhar principais mensagens de comunicação + URLs destino dos artigos (caso se aplique) + editáveis da campanha para utilização pelo meio + Imagens estáticas formato 9:16 e 1:1 + MREC (300x250) + Halfpage (300x600) + Outros elementos/imagens considerados importantes</t>
-        </is>
-      </c>
-      <c r="K532" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L532" t="inlineStr">
+      <c r="L530" t="inlineStr">
         <is>
           <t>É necessário enviar:
  - data da publicação?
@@ -24784,6 +24720,100 @@
         </is>
       </c>
     </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>HomePage Banner</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>512x348px</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>Máx. 200KB</t>
+        </is>
+      </c>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>JPG ou PNG</t>
+        </is>
+      </c>
+      <c r="L531" t="inlineStr">
+        <is>
+          <t>Banner estático (Guapo) no fundo do ecrã principal da app, sempre com uma promoção de pelo menos 20% de desconto. Logo: altura até 150px, largura máx. 500px. Texto: Título obrigatório, máx. 40 carateres (se ocupar 2 linhas, a tagline fica limitada a 1 linha); Tagline opcional, máx. 52 carateres (se ocupar 2 linhas, o título fica limitado a 1 linha); texto "Ad" obrigatório, máx. 13 carateres. Não colocar informação nem elementos importantes nas zonas coloridas do banner — o que lá estiver é cortado ou sobreposto pela seta. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>Food Wall Banner</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>512x348px</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>Máx. 200KB</t>
+        </is>
+      </c>
+      <c r="J532" t="inlineStr">
+        <is>
+          <t>JPG ou PNG</t>
+        </is>
+      </c>
+      <c r="L532" t="inlineStr">
+        <is>
+          <t>Banner estático no meio da loja Food Wall, focado em marcas de comida, sempre com uma promoção. Logo: altura até 150px, largura máx. 500px. Várias cores de fundo sólidas disponíveis. Texto: Título obrigatório, máx. 40 carateres (se ocupar 2 linhas, a tagline fica limitada a 1 linha); Tagline opcional, máx. 52 carateres (se ocupar 2 linhas, o título fica limitado a 1 linha); texto "Ad" obrigatório, máx. 13 carateres. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
+        </is>
+      </c>
+    </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
@@ -24807,12 +24837,12 @@
       </c>
       <c r="F533" t="inlineStr">
         <is>
-          <t>HomePage Banner</t>
+          <t>In-store Banner</t>
         </is>
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>512x348px</t>
+          <t>750x266px</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
@@ -24827,7 +24857,7 @@
       </c>
       <c r="L533" t="inlineStr">
         <is>
-          <t>Banner estático (Guapo) no fundo do ecrã principal da app, sempre com uma promoção de pelo menos 20% de desconto. Logo: altura até 150px, largura máx. 500px. Texto: Título obrigatório, máx. 40 carateres (se ocupar 2 linhas, a tagline fica limitada a 1 linha); Tagline opcional, máx. 52 carateres (se ocupar 2 linhas, o título fica limitado a 1 linha); texto "Ad" obrigatório, máx. 13 carateres. Não colocar informação nem elementos importantes nas zonas coloridas do banner — o que lá estiver é cortado ou sobreposto pela seta. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
+          <t>Banner estático em supermercados ou na parede do Glovo Market ("store wall"), a mostrar a marca de forma visual e a encaminhar para compra direta dos produtos. Fundo sólido. Deixar 30px de margem no topo e na base, para os produtos ficarem todos visíveis na zona central; atenção à seta de CTA no canto inferior direito. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
         </is>
       </c>
     </row>
@@ -24854,12 +24884,12 @@
       </c>
       <c r="F534" t="inlineStr">
         <is>
-          <t>Food Wall Banner</t>
+          <t>Shoppable Banner</t>
         </is>
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>512x348px</t>
+          <t>750x422px</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
@@ -24874,7 +24904,7 @@
       </c>
       <c r="L534" t="inlineStr">
         <is>
-          <t>Banner estático no meio da loja Food Wall, focado em marcas de comida, sempre com uma promoção. Logo: altura até 150px, largura máx. 500px. Várias cores de fundo sólidas disponíveis. Texto: Título obrigatório, máx. 40 carateres (se ocupar 2 linhas, a tagline fica limitada a 1 linha); Tagline opcional, máx. 52 carateres (se ocupar 2 linhas, o título fica limitado a 1 linha); texto "Ad" obrigatório, máx. 13 carateres. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
+          <t>Banner localizado dentro de diferentes categorias das lojas (fora da categoria principal da marca), com os produtos a aparecer por baixo do banner — o utilizador pode adicioná-los diretamente ao cesto ou clicar no banner para ir à loja completa. Fundo sólido. Deixar 90px de espaço a partir da margem inferior, onde entram a palavra "Sponsored" e o botão, assim que o banner estiver na app. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
         </is>
       </c>
     </row>
@@ -24901,12 +24931,12 @@
       </c>
       <c r="F535" t="inlineStr">
         <is>
-          <t>In-store Banner</t>
+          <t>Q-commerce Store Wall Banner</t>
         </is>
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>750x266px</t>
+          <t>512x348px</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
@@ -24921,7 +24951,7 @@
       </c>
       <c r="L535" t="inlineStr">
         <is>
-          <t>Banner estático em supermercados ou na parede do Glovo Market ("store wall"), a mostrar a marca de forma visual e a encaminhar para compra direta dos produtos. Fundo sólido. Deixar 30px de margem no topo e na base, para os produtos ficarem todos visíveis na zona central; atenção à seta de CTA no canto inferior direito. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
+          <t>Banner estático nas paredes das lojas de Groceries e Shops (Q-commerce), a mostrar a marca de forma visual e a encaminhar para compra direta dos produtos. Logo: altura até 150px, largura máx. 500px. Várias cores de fundo sólidas disponíveis. Texto: Título obrigatório, máx. 40 carateres (se ocupar 2 linhas, a tagline fica limitada a 1 linha); Tagline opcional, máx. 52 carateres (se ocupar 2 linhas, o título fica limitado a 1 linha); texto "Ad" obrigatório, máx. 13 carateres. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
         </is>
       </c>
     </row>
@@ -24948,12 +24978,12 @@
       </c>
       <c r="F536" t="inlineStr">
         <is>
-          <t>Shoppable Banner</t>
+          <t>OTP Premium</t>
         </is>
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>750x422px</t>
+          <t>1280x720px</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
@@ -24968,7 +24998,7 @@
       </c>
       <c r="L536" t="inlineStr">
         <is>
-          <t>Banner localizado dentro de diferentes categorias das lojas (fora da categoria principal da marca), com os produtos a aparecer por baixo do banner — o utilizador pode adicioná-los diretamente ao cesto ou clicar no banner para ir à loja completa. Fundo sólido. Deixar 90px de espaço a partir da margem inferior, onde entram a palavra "Sponsored" e o botão, assim que o banner estiver na app. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
+          <t>Banner "skippable" (não endémico) que aparece depois de uma compra concluída, assim que o mapa de entrega é mostrado, no fundo do ecrã, com uma secção de texto personalizável. O utilizador pode saltar o anúncio quando quiser. Logo tem de estar incluído na própria imagem do banner. Texto: Título máx. 20 carateres; CTA máx. 10 carateres. Evitar colocar informação importante no canto superior direito — fica sobreposta pelo botão de fechar. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
         </is>
       </c>
     </row>
@@ -24995,12 +25025,12 @@
       </c>
       <c r="F537" t="inlineStr">
         <is>
-          <t>Q-commerce Store Wall Banner</t>
+          <t>OTP Standard</t>
         </is>
       </c>
       <c r="G537" t="inlineStr">
         <is>
-          <t>512x348px</t>
+          <t>1280x720px</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
@@ -25015,101 +25045,96 @@
       </c>
       <c r="L537" t="inlineStr">
         <is>
-          <t>Banner estático nas paredes das lojas de Groceries e Shops (Q-commerce), a mostrar a marca de forma visual e a encaminhar para compra direta dos produtos. Logo: altura até 150px, largura máx. 500px. Várias cores de fundo sólidas disponíveis. Texto: Título obrigatório, máx. 40 carateres (se ocupar 2 linhas, a tagline fica limitada a 1 linha); Tagline opcional, máx. 52 carateres (se ocupar 2 linhas, o título fica limitado a 1 linha); texto "Ad" obrigatório, máx. 13 carateres. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
+          <t>Banner (não endémico) que aparece depois de uma compra concluída, assim que o mapa de entrega é mostrado, e depois de um OTP Premium ter sido saltado ("skipped"). Logo tem de estar incluído na própria imagem do banner. Texto: Título máx. 30 carateres; sem tagline. Várias cores de fundo sólidas disponíveis. Não colocar informação importante nas zonas coloridas do banner — o que lá estiver é cortado ou sobreposto pela seta. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>INTERNET</t>
+          <t>PROGRAMÁTICO</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Programático</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>Glovo</t>
+          <t>Criteo</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>Glovo</t>
+          <t>Criteo</t>
         </is>
       </c>
       <c r="F538" t="inlineStr">
         <is>
-          <t>OTP Premium</t>
+          <t>Criteo - Standard (Imagem)</t>
         </is>
       </c>
       <c r="G538" t="inlineStr">
         <is>
-          <t>1280x720px</t>
+          <t>320x50, 300x250, 728x90, 300x600, 160x600, 336x280, 970x250, 320x100, 320x480, 970x90, 468x60, 360x640, 120x600, 250x250, 180x150, 320x568</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
         <is>
-          <t>Máx. 200KB</t>
+          <t>Máx. 500 KB</t>
         </is>
       </c>
       <c r="J538" t="inlineStr">
         <is>
-          <t>JPG ou PNG</t>
-        </is>
-      </c>
-      <c r="L538" t="inlineStr">
-        <is>
-          <t>Banner "skippable" (não endémico) que aparece depois de uma compra concluída, assim que o mapa de entrega é mostrado, no fundo do ecrã, com uma secção de texto personalizável. O utilizador pode saltar o anúncio quando quiser. Logo tem de estar incluído na própria imagem do banner. Texto: Título máx. 20 carateres; CTA máx. 10 carateres. Evitar colocar informação importante no canto superior direito — fica sobreposta pelo botão de fechar. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
+          <t>JPG ou PNG; GIF animado até 30″</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>INTERNET</t>
+          <t>PROGRAMÁTICO</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Programático</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>Glovo</t>
+          <t>Criteo</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>Glovo</t>
+          <t>Criteo</t>
         </is>
       </c>
       <c r="F539" t="inlineStr">
         <is>
-          <t>OTP Standard</t>
-        </is>
-      </c>
-      <c r="G539" t="inlineStr">
-        <is>
-          <t>1280x720px</t>
+          <t>Criteo - Vídeo</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>16:9, 9:16 ou 1:1</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
         <is>
-          <t>Máx. 200KB</t>
+          <t>Máx. 25 MB</t>
         </is>
       </c>
       <c r="J539" t="inlineStr">
         <is>
-          <t>JPG ou PNG</t>
+          <t>MP4</t>
         </is>
       </c>
       <c r="L539" t="inlineStr">
         <is>
-          <t>Banner (não endémico) que aparece depois de uma compra concluída, assim que o mapa de entrega é mostrado, e depois de um OTP Premium ter sido saltado ("skipped"). Logo tem de estar incluído na própria imagem do banner. Texto: Título máx. 30 carateres; sem tagline. Várias cores de fundo sólidas disponíveis. Não colocar informação importante nas zonas coloridas do banner — o que lá estiver é cortado ou sobreposto pela seta. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
+          <t>Duração máx. 30″. Resolução até 720p (ou inferior, se o vídeo original for de qualidade inferior).</t>
         </is>
       </c>
     </row>
@@ -25136,22 +25161,27 @@
       </c>
       <c r="F540" t="inlineStr">
         <is>
-          <t>Criteo - Standard (Imagem)</t>
+          <t>Criteo - Rich Media / Responsivo</t>
         </is>
       </c>
       <c r="G540" t="inlineStr">
         <is>
-          <t>320x50, 300x250, 728x90, 300x600, 160x600, 336x280, 970x250, 320x100, 320x480, 970x90, 468x60, 360x640, 120x600, 250x250, 180x150, 320x568</t>
+          <t>1200x628px, 1200x1200px ou 800x1200px</t>
         </is>
       </c>
       <c r="I540" t="inlineStr">
         <is>
-          <t>Máx. 500 KB</t>
+          <t>Máx. 1 MB</t>
         </is>
       </c>
       <c r="J540" t="inlineStr">
         <is>
-          <t>JPG ou PNG; GIF animado até 30″</t>
+          <t>PNG ou JPG</t>
+        </is>
+      </c>
+      <c r="L540" t="inlineStr">
+        <is>
+          <t>Engloba os formatos Adaptive, Showcase, Carousel, Cube, Slider, Scroll, Search, Story, Lead Form e Interactive Ads, e os formatos com vídeo elaborados pela equipa de criativo da Criteo a partir das mesmas imagens (Motion Video, Video with Skin, QR Video). Pode incluir vídeo em vez de, ou além da, imagem: MP4, 1:1/16:9/9:16, máx. 25 MB, máx. 30″.</t>
         </is>
       </c>
     </row>
@@ -25178,27 +25208,32 @@
       </c>
       <c r="F541" t="inlineStr">
         <is>
-          <t>Criteo - Vídeo</t>
+          <t>Criteo - App Install</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>Imagens: 1200x628px, 1200x1200px ou 800x1200px. Logo da app: proporção 1:1.</t>
         </is>
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>16:9, 9:16 ou 1:1</t>
+          <t>1:1, 16:9 ou 9:16 (vídeo)</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
         <is>
-          <t>Máx. 25 MB</t>
+          <t>Imagem máx. 1 MB; logo da app máx. 50 KB; vídeo máx. 25 MB</t>
         </is>
       </c>
       <c r="J541" t="inlineStr">
         <is>
-          <t>MP4</t>
+          <t>PNG, JPG ou MP4</t>
         </is>
       </c>
       <c r="L541" t="inlineStr">
         <is>
-          <t>Duração máx. 30″. Resolução até 720p (ou inferior, se o vídeo original for de qualidade inferior).</t>
+          <t>Vídeo opcional, máx. 30″.</t>
         </is>
       </c>
     </row>
@@ -25225,12 +25260,12 @@
       </c>
       <c r="F542" t="inlineStr">
         <is>
-          <t>Criteo - Rich Media / Responsivo</t>
+          <t>Criteo - Hero SKU</t>
         </is>
       </c>
       <c r="G542" t="inlineStr">
         <is>
-          <t>1200x628px, 1200x1200px ou 800x1200px</t>
+          <t>Imagem de produto/branding: 1200x628px, 1200x1200px ou 800x1200px. Imagem de fundo: 300x250, 336x280, 300x600, 320x480, 160x600, 728x90, 970x250 ou 320x50px.</t>
         </is>
       </c>
       <c r="I542" t="inlineStr">
@@ -25241,11 +25276,6 @@
       <c r="J542" t="inlineStr">
         <is>
           <t>PNG ou JPG</t>
-        </is>
-      </c>
-      <c r="L542" t="inlineStr">
-        <is>
-          <t>Engloba os formatos Adaptive, Showcase, Carousel, Cube, Slider, Scroll, Search, Story, Lead Form e Interactive Ads, e os formatos com vídeo elaborados pela equipa de criativo da Criteo a partir das mesmas imagens (Motion Video, Video with Skin, QR Video). Pode incluir vídeo em vez de, ou além da, imagem: MP4, 1:1/16:9/9:16, máx. 25 MB, máx. 30″.</t>
         </is>
       </c>
     </row>
@@ -25272,121 +25302,111 @@
       </c>
       <c r="F543" t="inlineStr">
         <is>
-          <t>Criteo - App Install</t>
+          <t>Criteo - 3.60</t>
         </is>
       </c>
       <c r="G543" t="inlineStr">
         <is>
-          <t>Imagens: 1200x628px, 1200x1200px ou 800x1200px. Logo da app: proporção 1:1.</t>
+          <t>1200x628px, 1200x1200px ou 800x1200px — mín. 6 imagens do mesmo produto, em ângulos diferentes.</t>
         </is>
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>1:1, 16:9 ou 9:16 (vídeo)</t>
+          <t>1:1, 2:3 ou 1.91:1</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
         <is>
-          <t>Imagem máx. 1 MB; logo da app máx. 50 KB; vídeo máx. 25 MB</t>
+          <t>Máx. 1 MB</t>
         </is>
       </c>
       <c r="J543" t="inlineStr">
         <is>
-          <t>PNG, JPG ou MP4</t>
-        </is>
-      </c>
-      <c r="L543" t="inlineStr">
-        <is>
-          <t>Vídeo opcional, máx. 30″.</t>
+          <t>PNG ou JPG</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>Criteo</t>
+          <t>ClickProfit</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>Criteo</t>
+          <t>Forretas e Descontos (Homepage)</t>
         </is>
       </c>
       <c r="F544" t="inlineStr">
         <is>
-          <t>Criteo - Hero SKU</t>
+          <t>Moldura (barra lateral direita)</t>
         </is>
       </c>
       <c r="G544" t="inlineStr">
         <is>
-          <t>Imagem de produto/branding: 1200x628px, 1200x1200px ou 800x1200px. Imagem de fundo: 300x250, 336x280, 300x600, 320x480, 160x600, 728x90, 970x250 ou 320x50px.</t>
-        </is>
-      </c>
-      <c r="I544" t="inlineStr">
-        <is>
-          <t>Máx. 1 MB</t>
+          <t>200x700</t>
         </is>
       </c>
       <c r="J544" t="inlineStr">
         <is>
-          <t>PNG ou JPG</t>
+          <t>JPEG, GIF ou PNG + fontes usadas</t>
+        </is>
+      </c>
+      <c r="L544" t="inlineStr">
+        <is>
+          <t>O Take Over é composto por 3 peças: barra lateral direita, barra lateral esquerda e topo. Prazo de entrega dos materiais: 72h úteis.</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Criteo</t>
+          <t>ClickProfit</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>Criteo</t>
+          <t>Forretas e Descontos (Homepage)</t>
         </is>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>Criteo - 3.60</t>
+          <t>Moldura (barra lateral esquerda)</t>
         </is>
       </c>
       <c r="G545" t="inlineStr">
         <is>
-          <t>1200x628px, 1200x1200px ou 800x1200px — mín. 6 imagens do mesmo produto, em ângulos diferentes.</t>
-        </is>
-      </c>
-      <c r="H545" t="inlineStr">
-        <is>
-          <t>1:1, 2:3 ou 1.91:1</t>
-        </is>
-      </c>
-      <c r="I545" t="inlineStr">
-        <is>
-          <t>Máx. 1 MB</t>
+          <t>200x700</t>
         </is>
       </c>
       <c r="J545" t="inlineStr">
         <is>
-          <t>PNG ou JPG</t>
+          <t>JPEG, GIF ou PNG + fontes usadas</t>
+        </is>
+      </c>
+      <c r="L545" t="inlineStr">
+        <is>
+          <t>O Take Over é composto por 3 peças: barra lateral direita, barra lateral esquerda e topo. Prazo de entrega dos materiais: 72h úteis.</t>
         </is>
       </c>
     </row>
@@ -25408,17 +25428,17 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>Forretas e Descontos (Homepage)</t>
+          <t>Descontos (Homepage)</t>
         </is>
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t>Moldura (barra lateral direita)</t>
+          <t>Moldura (topo)</t>
         </is>
       </c>
       <c r="G546" t="inlineStr">
         <is>
-          <t>200x700</t>
+          <t>940x120</t>
         </is>
       </c>
       <c r="J546" t="inlineStr">
@@ -25428,7 +25448,7 @@
       </c>
       <c r="L546" t="inlineStr">
         <is>
-          <t>O Take Over é composto por 3 peças: barra lateral direita, barra lateral esquerda e topo. Prazo de entrega dos materiais: 72h úteis.</t>
+          <t>O topo tem de ter em conta os elementos fixos do site, que não serão sobrepostos. Prazo de entrega dos materiais: 72h úteis.</t>
         </is>
       </c>
     </row>
@@ -25450,17 +25470,17 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>Forretas e Descontos (Homepage)</t>
+          <t>Forretas (Homepage)</t>
         </is>
       </c>
       <c r="F547" t="inlineStr">
         <is>
-          <t>Moldura (barra lateral esquerda)</t>
+          <t>Moldura (topo)</t>
         </is>
       </c>
       <c r="G547" t="inlineStr">
         <is>
-          <t>200x700</t>
+          <t>1920x313</t>
         </is>
       </c>
       <c r="J547" t="inlineStr">
@@ -25470,7 +25490,7 @@
       </c>
       <c r="L547" t="inlineStr">
         <is>
-          <t>O Take Over é composto por 3 peças: barra lateral direita, barra lateral esquerda e topo. Prazo de entrega dos materiais: 72h úteis.</t>
+          <t>O topo tem de ter em conta os elementos fixos do site, que não serão sobrepostos. Prazo de entrega dos materiais: 72h úteis.</t>
         </is>
       </c>
     </row>
@@ -25492,27 +25512,27 @@
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>Descontos (Homepage)</t>
+          <t>Descontos</t>
         </is>
       </c>
       <c r="F548" t="inlineStr">
         <is>
-          <t>Moldura (topo)</t>
+          <t>Imagem Oferta e Native Ad — Cupão</t>
         </is>
       </c>
       <c r="G548" t="inlineStr">
         <is>
-          <t>940x120</t>
+          <t>468x351</t>
         </is>
       </c>
       <c r="J548" t="inlineStr">
         <is>
-          <t>JPEG, GIF ou PNG + fontes usadas</t>
+          <t>JPEG ou PNG</t>
         </is>
       </c>
       <c r="L548" t="inlineStr">
         <is>
-          <t>O topo tem de ter em conta os elementos fixos do site, que não serão sobrepostos. Prazo de entrega dos materiais: 72h úteis.</t>
+          <t>Imagem identificativa da oferta. Prazo de entrega dos materiais: 72h úteis.</t>
         </is>
       </c>
     </row>
@@ -25534,27 +25554,27 @@
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>Forretas (Homepage)</t>
+          <t>ClickProfit</t>
         </is>
       </c>
       <c r="F549" t="inlineStr">
         <is>
-          <t>Moldura (topo)</t>
+          <t>HTML (Email)</t>
         </is>
       </c>
       <c r="G549" t="inlineStr">
         <is>
-          <t>1920x313</t>
+          <t>600 ou 700px de largura; altura ao critério do cliente</t>
         </is>
       </c>
       <c r="J549" t="inlineStr">
         <is>
-          <t>JPEG, GIF ou PNG + fontes usadas</t>
+          <t>HTML + imagens em JPG ou PNG</t>
         </is>
       </c>
       <c r="L549" t="inlineStr">
         <is>
-          <t>O topo tem de ter em conta os elementos fixos do site, que não serão sobrepostos. Prazo de entrega dos materiais: 72h úteis.</t>
+          <t>Enviar subject e sender. Prazo de entrega dos materiais: 72h úteis.</t>
         </is>
       </c>
     </row>
@@ -25576,101 +25596,121 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>Descontos</t>
+          <t>ClickProfit</t>
         </is>
       </c>
       <c r="F550" t="inlineStr">
         <is>
-          <t>Imagem Oferta e Native Ad — Cupão</t>
-        </is>
-      </c>
-      <c r="G550" t="inlineStr">
-        <is>
-          <t>468x351</t>
-        </is>
-      </c>
-      <c r="J550" t="inlineStr">
-        <is>
-          <t>JPEG ou PNG</t>
+          <t>SMS</t>
         </is>
       </c>
       <c r="L550" t="inlineStr">
         <is>
-          <t>Imagem identificativa da oferta. Prazo de entrega dos materiais: 72h úteis.</t>
+          <t>Sender: máx. 11 carateres. Copy: máx. 160 carateres (inclui espaços, pontuação e o link de unsubscribe usado pela ClickProfit — bit.ly/ChB_); sobram 142 carateres para o anunciante, podendo incluir um link (que a ClickProfit converte depois em bit.ly — esse link também conta para os 142 carateres). Enviar números de telemóvel para envio de SMS de teste. Prazo de entrega dos materiais: 72h úteis.</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>INTERNET</t>
+          <t>PROGRAMÁTICO</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Programático</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>ClickProfit</t>
+          <t>Taboola</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>ClickProfit</t>
+          <t>Taboola</t>
         </is>
       </c>
       <c r="F551" t="inlineStr">
         <is>
-          <t>HTML (Email)</t>
+          <t>Taboola - Native Ads (Imagem)</t>
         </is>
       </c>
       <c r="G551" t="inlineStr">
         <is>
-          <t>600 ou 700px de largura; altura ao critério do cliente</t>
+          <t>1200x674 (recomendado); mín. 400x350</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>16:9 (preferencial), 4:3 ou 1:1</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>Máx. 5 MB</t>
         </is>
       </c>
       <c r="J551" t="inlineStr">
         <is>
-          <t>HTML + imagens em JPG ou PNG</t>
+          <t>JPEG (preferencial), BMP, PNG, WBMP ou GIF</t>
         </is>
       </c>
       <c r="L551" t="inlineStr">
         <is>
-          <t>Enviar subject e sender. Prazo de entrega dos materiais: 72h úteis.</t>
+          <t>Título: 34-45 carateres (ideal), máx. 60. Descrição: 180 (ideal), máx. 250. Texto de marca: máx. 30 carateres.</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>INTERNET</t>
+          <t>PROGRAMÁTICO</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Programático</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>ClickProfit</t>
+          <t>Taboola</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>ClickProfit</t>
+          <t>Taboola</t>
         </is>
       </c>
       <c r="F552" t="inlineStr">
         <is>
-          <t>SMS</t>
+          <t>Taboola - Motion Ads (Vídeo)</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>1067x600</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>Máx. 50 MB (GIF: máx. 5 MB)</t>
+        </is>
+      </c>
+      <c r="J552" t="inlineStr">
+        <is>
+          <t>MP4, MOV ou GIF</t>
         </is>
       </c>
       <c r="L552" t="inlineStr">
         <is>
-          <t>Sender: máx. 11 carateres. Copy: máx. 160 carateres (inclui espaços, pontuação e o link de unsubscribe usado pela ClickProfit — bit.ly/ChB_); sobram 142 carateres para o anunciante, podendo incluir um link (que a ClickProfit converte depois em bit.ly — esse link também conta para os 142 carateres). Enviar números de telemóvel para envio de SMS de teste. Prazo de entrega dos materiais: 72h úteis.</t>
+          <t>Duração máx. 15″. Título: 34-45 carateres (ideal), máx. 60. Texto de marca: máx. 30 carateres.</t>
         </is>
       </c>
     </row>
@@ -25697,32 +25737,22 @@
       </c>
       <c r="F553" t="inlineStr">
         <is>
-          <t>Taboola - Native Ads (Imagem)</t>
+          <t>Taboola - Display Hosted (Imagem)</t>
         </is>
       </c>
       <c r="G553" t="inlineStr">
         <is>
-          <t>1200x674 (recomendado); mín. 400x350</t>
-        </is>
-      </c>
-      <c r="H553" t="inlineStr">
-        <is>
-          <t>16:9 (preferencial), 4:3 ou 1:1</t>
+          <t>Tamanhos standard IAB: 300x250, 300x600, 320x50, 728x90, 970x250, 160x600 ou 250x250</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
         <is>
-          <t>Máx. 5 MB</t>
+          <t>Máx. 2 MB</t>
         </is>
       </c>
       <c r="J553" t="inlineStr">
         <is>
-          <t>JPEG (preferencial), BMP, PNG, WBMP ou GIF</t>
-        </is>
-      </c>
-      <c r="L553" t="inlineStr">
-        <is>
-          <t>Título: 34-45 carateres (ideal), máx. 60. Descrição: 180 (ideal), máx. 250. Texto de marca: máx. 30 carateres.</t>
+          <t>JPEG, JPG, PNG ou GIF</t>
         </is>
       </c>
     </row>
@@ -25749,32 +25779,27 @@
       </c>
       <c r="F554" t="inlineStr">
         <is>
-          <t>Taboola - Motion Ads (Vídeo)</t>
+          <t>Taboola - Display Hosted (Vídeo)</t>
         </is>
       </c>
       <c r="G554" t="inlineStr">
         <is>
-          <t>1067x600</t>
-        </is>
-      </c>
-      <c r="H554" t="inlineStr">
-        <is>
-          <t>16:9</t>
+          <t>Tamanhos standard IAB: 300x250, 300x600, 320x50, 728x90, 970x250, 160x600 ou 250x250</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
         <is>
-          <t>Máx. 50 MB (GIF: máx. 5 MB)</t>
+          <t>Máx. 200 MB</t>
         </is>
       </c>
       <c r="J554" t="inlineStr">
         <is>
-          <t>MP4, MOV ou GIF</t>
+          <t>MP4</t>
         </is>
       </c>
       <c r="L554" t="inlineStr">
         <is>
-          <t>Duração máx. 15″. Título: 34-45 carateres (ideal), máx. 60. Texto de marca: máx. 30 carateres.</t>
+          <t>Duração: 5 a 30″. Pode incluir áudio (vídeo arranca sem som; o utilizador pode ativar).</t>
         </is>
       </c>
     </row>
@@ -25801,7 +25826,7 @@
       </c>
       <c r="F555" t="inlineStr">
         <is>
-          <t>Taboola - Display Hosted (Imagem)</t>
+          <t>Taboola - Display Hosted (HTML5)</t>
         </is>
       </c>
       <c r="G555" t="inlineStr">
@@ -25811,12 +25836,17 @@
       </c>
       <c r="I555" t="inlineStr">
         <is>
-          <t>Máx. 2 MB</t>
+          <t>Máx. 2 MB (ZIP comprimido)</t>
         </is>
       </c>
       <c r="J555" t="inlineStr">
         <is>
-          <t>JPEG, JPG, PNG ou GIF</t>
+          <t>ZIP (HTML, JS, CSS, JPG, JPEG, GIF, PNG, SVG; máx. 100 ficheiros); index.html na raiz</t>
+        </is>
+      </c>
+      <c r="L555" t="inlineStr">
+        <is>
+          <t>Tem de incluir uma imagem estática de recurso (JPG, PNG ou GIF) para browsers sem JavaScript.</t>
         </is>
       </c>
     </row>
@@ -25843,7 +25873,7 @@
       </c>
       <c r="F556" t="inlineStr">
         <is>
-          <t>Taboola - Display Hosted (Vídeo)</t>
+          <t>Taboola - Display (Tag de 3ºs)</t>
         </is>
       </c>
       <c r="G556" t="inlineStr">
@@ -25851,19 +25881,9 @@
           <t>Tamanhos standard IAB: 300x250, 300x600, 320x50, 728x90, 970x250, 160x600 ou 250x250</t>
         </is>
       </c>
-      <c r="I556" t="inlineStr">
-        <is>
-          <t>Máx. 200 MB</t>
-        </is>
-      </c>
-      <c r="J556" t="inlineStr">
-        <is>
-          <t>MP4</t>
-        </is>
-      </c>
       <c r="L556" t="inlineStr">
         <is>
-          <t>Duração: 5 a 30″. Pode incluir áudio (vídeo arranca sem som; o utilizador pode ativar).</t>
+          <t>Ad servers aceites: DCM e Adform. Macros de clique obrigatórias quando a tag não é reconhecida automaticamente.</t>
         </is>
       </c>
     </row>
@@ -25890,27 +25910,17 @@
       </c>
       <c r="F557" t="inlineStr">
         <is>
-          <t>Taboola - Display Hosted (HTML5)</t>
+          <t>Taboola - Carousel</t>
         </is>
       </c>
       <c r="G557" t="inlineStr">
         <is>
-          <t>Tamanhos standard IAB: 300x250, 300x600, 320x50, 728x90, 970x250, 160x600 ou 250x250</t>
-        </is>
-      </c>
-      <c r="I557" t="inlineStr">
-        <is>
-          <t>Máx. 2 MB (ZIP comprimido)</t>
-        </is>
-      </c>
-      <c r="J557" t="inlineStr">
-        <is>
-          <t>ZIP (HTML, JS, CSS, JPG, JPEG, GIF, PNG, SVG; máx. 100 ficheiros); index.html na raiz</t>
+          <t>1200x627</t>
         </is>
       </c>
       <c r="L557" t="inlineStr">
         <is>
-          <t>Tem de incluir uma imagem estática de recurso (JPG, PNG ou GIF) para browsers sem JavaScript.</t>
+          <t>Mín. 3 e máx. 5 cartões. Por cartão: imagem, título (máx. 50 carateres), descrição (máx. 150 carateres), CTA e URL de destino (pode variar por cartão). Suporta GIF/vídeo nos cartões.</t>
         </is>
       </c>
     </row>
@@ -25937,17 +25947,17 @@
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>Taboola - Display (Tag de 3ºs)</t>
+          <t>Taboola - Social Importer (Facebook/Instagram)</t>
         </is>
       </c>
       <c r="G558" t="inlineStr">
         <is>
-          <t>Tamanhos standard IAB: 300x250, 300x600, 320x50, 728x90, 970x250, 160x600 ou 250x250</t>
+          <t>300x250 ou 300x600</t>
         </is>
       </c>
       <c r="L558" t="inlineStr">
         <is>
-          <t>Ad servers aceites: DCM e Adform. Macros de clique obrigatórias quando a tag não é reconhecida automaticamente.</t>
+          <t>Anúncio importado diretamente do Facebook/Instagram a partir do ID da Meta Ad Library (16 dígitos) — não editável, aparece exatamente como no social.</t>
         </is>
       </c>
     </row>
@@ -25974,96 +25984,96 @@
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>Taboola - Carousel</t>
-        </is>
-      </c>
-      <c r="G559" t="inlineStr">
-        <is>
-          <t>1200x627</t>
-        </is>
-      </c>
-      <c r="L559" t="inlineStr">
-        <is>
-          <t>Mín. 3 e máx. 5 cartões. Por cartão: imagem, título (máx. 50 carateres), descrição (máx. 150 carateres), CTA e URL de destino (pode variar por cartão). Suporta GIF/vídeo nos cartões.</t>
+          <t>Taboola - Vertical</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>4:5, 9:16 ou 1:2</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>Máx. 5 MB</t>
+        </is>
+      </c>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>JPG ou PNG</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>Taboola</t>
+          <t>Suebi</t>
         </is>
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>Taboola</t>
+          <t>Suebi</t>
         </is>
       </c>
       <c r="F560" t="inlineStr">
         <is>
-          <t>Taboola - Social Importer (Facebook/Instagram)</t>
-        </is>
-      </c>
-      <c r="G560" t="inlineStr">
-        <is>
-          <t>300x250 ou 300x600</t>
+          <t>SMS</t>
         </is>
       </c>
       <c r="L560" t="inlineStr">
         <is>
-          <t>Anúncio importado diretamente do Facebook/Instagram a partir do ID da Meta Ad Library (16 dígitos) — não editável, aparece exatamente como no social.</t>
+          <t>Sender: máx. 11 carateres. Copy: máx. 160 carateres (inclui espaços, pontuação e o link de unsubscribe — Stop SMS: 91xxxxxxx); no total ~135 carateres disponíveis. Não usar o símbolo € (spam trigger), usar "EUR". Símbolos especiais (%, ?, pontuação) contam como 2 espaços.</t>
         </is>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>Taboola</t>
+          <t>Suebi</t>
         </is>
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>Taboola</t>
+          <t>Suebi</t>
         </is>
       </c>
       <c r="F561" t="inlineStr">
         <is>
-          <t>Taboola - Vertical</t>
-        </is>
-      </c>
-      <c r="H561" t="inlineStr">
-        <is>
-          <t>4:5, 9:16 ou 1:2</t>
+          <t>Email / Newsletter</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>600px de largura (imagens)</t>
         </is>
       </c>
       <c r="I561" t="inlineStr">
         <is>
-          <t>Máx. 5 MB</t>
-        </is>
-      </c>
-      <c r="J561" t="inlineStr">
-        <is>
-          <t>JPG ou PNG</t>
+          <t>Imagens: recomendado máx. 200 KB</t>
+        </is>
+      </c>
+      <c r="L561" t="inlineStr">
+        <is>
+          <t>Usar logo da marca. Banner = imagem + proposta de valor + CTA, visíveis sem necessidade de scroll. Newsletter não deve ser muito extensa; preferir mais texto do que imagens. A Suebi pode desenvolver o HTML sem custo para o cliente, se necessário.</t>
         </is>
       </c>
     </row>
@@ -26090,131 +26100,57 @@
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>SMS</t>
+          <t>Push Notification</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>Logo 1:1; imagem opcional 512x256 ou 1024x512</t>
         </is>
       </c>
       <c r="L562" t="inlineStr">
         <is>
-          <t>Sender: máx. 11 carateres. Copy: máx. 160 carateres (inclui espaços, pontuação e o link de unsubscribe — Stop SMS: 91xxxxxxx); no total ~135 carateres disponíveis. Não usar o símbolo € (spam trigger), usar "EUR". Símbolos especiais (%, ?, pontuação) contam como 2 espaços.</t>
+          <t>Sender: 30-45 carateres. Subject: 40-50 carateres. Awareness puro, com clicktracker.</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>INTERNET</t>
+          <t>PROGRAMÁTICO</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Programático</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>Suebi</t>
+          <t>RTB House</t>
         </is>
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>Suebi</t>
+          <t>RTB House</t>
         </is>
       </c>
       <c r="F563" t="inlineStr">
         <is>
-          <t>Email / Newsletter</t>
+          <t>Display</t>
         </is>
       </c>
       <c r="G563" t="inlineStr">
         <is>
-          <t>600px de largura (imagens)</t>
+          <t>300x600, 160x600, 336x280, 300x250, 320x50, 320x100, 970x250 ou 728x90</t>
         </is>
       </c>
       <c r="I563" t="inlineStr">
         <is>
-          <t>Imagens: recomendado máx. 200 KB</t>
-        </is>
-      </c>
-      <c r="L563" t="inlineStr">
-        <is>
-          <t>Usar logo da marca. Banner = imagem + proposta de valor + CTA, visíveis sem necessidade de scroll. Newsletter não deve ser muito extensa; preferir mais texto do que imagens. A Suebi pode desenvolver o HTML sem custo para o cliente, se necessário.</t>
-        </is>
-      </c>
-    </row>
-    <row r="564">
-      <c r="A564" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B564" t="inlineStr">
-        <is>
-          <t>Internet</t>
-        </is>
-      </c>
-      <c r="C564" t="inlineStr">
-        <is>
-          <t>Suebi</t>
-        </is>
-      </c>
-      <c r="D564" t="inlineStr">
-        <is>
-          <t>Suebi</t>
-        </is>
-      </c>
-      <c r="F564" t="inlineStr">
-        <is>
-          <t>Push Notification</t>
-        </is>
-      </c>
-      <c r="G564" t="inlineStr">
-        <is>
-          <t>Logo 1:1; imagem opcional 512x256 ou 1024x512</t>
-        </is>
-      </c>
-      <c r="L564" t="inlineStr">
-        <is>
-          <t>Sender: 30-45 carateres. Subject: 40-50 carateres. Awareness puro, com clicktracker.</t>
-        </is>
-      </c>
-    </row>
-    <row r="565">
-      <c r="A565" t="inlineStr">
-        <is>
-          <t>PROGRAMÁTICO</t>
-        </is>
-      </c>
-      <c r="B565" t="inlineStr">
-        <is>
-          <t>Programático</t>
-        </is>
-      </c>
-      <c r="C565" t="inlineStr">
-        <is>
-          <t>RTB House</t>
-        </is>
-      </c>
-      <c r="D565" t="inlineStr">
-        <is>
-          <t>RTB House</t>
-        </is>
-      </c>
-      <c r="F565" t="inlineStr">
-        <is>
-          <t>Display</t>
-        </is>
-      </c>
-      <c r="G565" t="inlineStr">
-        <is>
-          <t>300x600, 160x600, 336x280, 300x250, 320x50, 320x100, 970x250 ou 728x90</t>
-        </is>
-      </c>
-      <c r="I565" t="inlineStr">
-        <is>
           <t>Máx. 1 MB</t>
         </is>
       </c>
-      <c r="J565" t="inlineStr">
+      <c r="J563" t="inlineStr">
         <is>
           <t>PNG, JPG, JPEG, GIF ou HTML</t>
         </is>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M563"/>
+  <dimension ref="A1:M568"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26156,6 +26156,231 @@
         </is>
       </c>
     </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>Hero Header (Newsletter)</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>600x400</t>
+        </is>
+      </c>
+      <c r="L564" t="inlineStr">
+        <is>
+          <t>Canal: Newsletter. Indicar título e texto no corpo do email — curtos, diretos ao tema, a captar a curiosidade do leitor. CTA: Comprar ou Saiba mais. Colocar selo de desconto na imagem, se aplicável. Indicar SKUs a linkar e respetiva categoria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>Ledwall Vídeo (Ecospot — Parque de Estacionamento)</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>384x512, 672x672 ou 1920x1080</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>Máx. 150 MB</t>
+        </is>
+      </c>
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>MP4, codec H264 (livraria x264), bitrate &lt; 3000</t>
+        </is>
+      </c>
+      <c r="L565" t="inlineStr">
+        <is>
+          <t>Ecospots — rede de 28 lojas Continente. Objetivo: Awareness.</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>Ledwall Imagem (Ecospot — Parque de Estacionamento)</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>384x512, 672x672 ou 1920x1080</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>Máx. 2 MB</t>
+        </is>
+      </c>
+      <c r="J566" t="inlineStr">
+        <is>
+          <t>JPG e/ou PNG, modo de cor RGB, resolução 72dpi</t>
+        </is>
+      </c>
+      <c r="L566" t="inlineStr">
+        <is>
+          <t>Ecospots — rede de 28 lojas Continente. Objetivo: Awareness.</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>Image Advertising (Continente Feed)</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>Desktop: 1312x320; Tablet: 959x256; Mobile: 735x413</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB</t>
+        </is>
+      </c>
+      <c r="J567" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="L567" t="inlineStr">
+        <is>
+          <t>Localizações: Liga Portugal, Ficha de Receitas, LP Receitas, Coleção de Selos, Festival Comida CNT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>Image + Video Advertising (Continente Feed)</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>Imagem — Desktop: 743x320, Tablet: 503x256, Mobile: 503x256. Vídeo — Desktop: 569x320, Tablet: 456x256, Mobile: 735x413.</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB (imagem; peso do vídeo não indicado)</t>
+        </is>
+      </c>
+      <c r="J568" t="inlineStr">
+        <is>
+          <t>JPG/PNG (imagem; formato do vídeo não indicado)</t>
+        </is>
+      </c>
+      <c r="L568" t="inlineStr">
+        <is>
+          <t>Localizações: Liga Portugal, Ficha de Receitas, LP Receitas, Coleção de Selos, Festival Comida CNT.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M568"/>
+  <dimension ref="A1:M573"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26381,6 +26381,241 @@
         </is>
       </c>
     </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>Banner Cupão Plus (App Cartão Continente)</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>458x236</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB</t>
+        </is>
+      </c>
+      <c r="J569" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="L569" t="inlineStr">
+        <is>
+          <t>Localização: Página Cupões.</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>Banner Cupão (App Cartão Continente)</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>458x112</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB</t>
+        </is>
+      </c>
+      <c r="J570" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="L570" t="inlineStr">
+        <is>
+          <t>Localização: Página Cupões.</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>Banner Usar Cartão (App Cartão Continente)</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>458x112</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB</t>
+        </is>
+      </c>
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="L571" t="inlineStr">
+        <is>
+          <t>Localização: Página Usar Cartão.</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>Banner Destaques (App Cartão Continente)</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>660x484</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB</t>
+        </is>
+      </c>
+      <c r="J572" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="L572" t="inlineStr">
+        <is>
+          <t>Localização: Homepage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>Banner Vantagens/Folhetos (App Cartão Continente)</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>654x240</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>Máx. 250 KB</t>
+        </is>
+      </c>
+      <c r="J573" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="L573" t="inlineStr">
+        <is>
+          <t>Localização: Homepage.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -26192,6 +26192,11 @@
           <t>Canal: Newsletter. Indicar título e texto no corpo do email — curtos, diretos ao tema, a captar a curiosidade do leitor. CTA: Comprar ou Saiba mais. Colocar selo de desconto na imagem, se aplicável. Indicar SKUs a linkar e respetiva categoria.</t>
         </is>
       </c>
+      <c r="M564" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Hero-Header-397e4d8f0b1880c78e1ce86047334b9d</t>
+        </is>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
@@ -26239,6 +26244,11 @@
           <t>Ecospots — rede de 28 lojas Continente. Objetivo: Awareness.</t>
         </is>
       </c>
+      <c r="M565" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Ledwall-Video-123e4d8f0b188253b2e481717ab1e89d</t>
+        </is>
+      </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
@@ -26286,6 +26296,11 @@
           <t>Ecospots — rede de 28 lojas Continente. Objetivo: Awareness.</t>
         </is>
       </c>
+      <c r="M566" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Ledwall-179e4d8f0b18839bbee701966fbfe361</t>
+        </is>
+      </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
@@ -26333,6 +26348,11 @@
           <t>Localizações: Liga Portugal, Ficha de Receitas, LP Receitas, Coleção de Selos, Festival Comida CNT.</t>
         </is>
       </c>
+      <c r="M567" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Image-Advertising-3f3e4d8f0b1880da8163f327a16c13f2</t>
+        </is>
+      </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
@@ -26378,6 +26398,11 @@
       <c r="L568" t="inlineStr">
         <is>
           <t>Localizações: Liga Portugal, Ficha de Receitas, LP Receitas, Coleção de Selos, Festival Comida CNT.</t>
+        </is>
+      </c>
+      <c r="M568" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Image-Video-Advertising-3f7e4d8f0b1880c4b983f2a3a7e2723d</t>
         </is>
       </c>
     </row>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M573"/>
+  <dimension ref="A1:M578"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26641,6 +26641,261 @@
         </is>
       </c>
     </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>Video Ads - Auto Play (App Cartão Continente)</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>660x484</t>
+        </is>
+      </c>
+      <c r="J574" t="inlineStr">
+        <is>
+          <t>MP4</t>
+        </is>
+      </c>
+      <c r="L574" t="inlineStr">
+        <is>
+          <t>Localizações: Homepage, Plug&amp;Charge.</t>
+        </is>
+      </c>
+      <c r="M574" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Video-Ads-Auto-Play-106e4d8f0b1882a98475014f0da845d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>Banner Plug&amp;Charge (App Cartão Continente)</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>660x484</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB</t>
+        </is>
+      </c>
+      <c r="J575" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="L575" t="inlineStr">
+        <is>
+          <t>Localização: Plug&amp;Charge.</t>
+        </is>
+      </c>
+      <c r="M575" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Banner-Plug-Charge-3cee4d8f0b1880bf9363e9d7a56da35e</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>Sponsored Products Display (App Continente)</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>456x1140</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB</t>
+        </is>
+      </c>
+      <c r="J576" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="L576" t="inlineStr">
+        <is>
+          <t>Localização: Product Grid.</t>
+        </is>
+      </c>
+      <c r="M576" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Sponsored-Products-Display-90fe4d8f0b18835ca782816027b56ee2</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>Banner Ecrã Loja (App Continente)</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>345x109</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB</t>
+        </is>
+      </c>
+      <c r="J577" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="L577" t="inlineStr">
+        <is>
+          <t>Localização: Em loja.</t>
+        </is>
+      </c>
+      <c r="M577" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Banner-Ecr-Loja-3ece4d8f0b1880db8984c5d9c585137c</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>Hero Banner (App Continente)</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>1029x516</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB</t>
+        </is>
+      </c>
+      <c r="J578" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="L578" t="inlineStr">
+        <is>
+          <t>Localização: Homepage. Objetivo: Awareness.</t>
+        </is>
+      </c>
+      <c r="M578" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Hero-Banner-651e4d8f0b18836d92ca8117823842cc</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M578"/>
+  <dimension ref="A1:M581"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26896,6 +26896,162 @@
         </is>
       </c>
     </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>Banner Oportunidades (App Continente)</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>1029x772</t>
+        </is>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB</t>
+        </is>
+      </c>
+      <c r="J579" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="L579" t="inlineStr">
+        <is>
+          <t>Localização: Página Oportunidades. Objetivo: Awareness.</t>
+        </is>
+      </c>
+      <c r="M579" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Banner-Oportunidades-ecfe4d8f0b1882f6978c81988921c3c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>Top Banner (Continente Online)</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>Desktop: 1320x132; Tablet: 720x124; Mobile: 345x115</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB</t>
+        </is>
+      </c>
+      <c r="J580" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="L580" t="inlineStr">
+        <is>
+          <t>Localizações: Homepage, Folhetos, Oportunidades.</t>
+        </is>
+      </c>
+      <c r="M580" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Top-Banner-2abe4d8f0b1882fdb5b1817348bac988</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>Sponsored Products Display (Continente Online)</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>Desktop: 172x431; Mobile: 160x431</t>
+        </is>
+      </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB</t>
+        </is>
+      </c>
+      <c r="J581" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="L581" t="inlineStr">
+        <is>
+          <t>Localização: Product Grid.</t>
+        </is>
+      </c>
+      <c r="M581" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Sponsored-Products-Display-307e4d8f0b18832cb4ed81b572620cab</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M581"/>
+  <dimension ref="A1:M582"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27052,6 +27052,43 @@
         </is>
       </c>
     </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>Sponsored Products (Continente Online)</t>
+        </is>
+      </c>
+      <c r="L582" t="inlineStr">
+        <is>
+          <t>Não necessita de criatividades — enviar idealmente até 4 SKUs por posicionamento. Keyword Search (Pesquisa): produtos visíveis na zona de pesquisa, associados às keywords da campanha. Destaque Produto Categoria (Product Grid): produtos visíveis na página de categoria. Destaque Produto Homepage (Destaques): produtos visíveis na Homepage, na zona de destaques de produtos.</t>
+        </is>
+      </c>
+      <c r="M582" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Sponsored-Products-61be4d8f0b18820a9a8d81a25c6be12d</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M582"/>
+  <dimension ref="A1:M587"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27089,6 +27089,246 @@
         </is>
       </c>
     </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>Banner Pesquisa (Continente Online)</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>320x100 (Desktop, Tablet e Mobile)</t>
+        </is>
+      </c>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB</t>
+        </is>
+      </c>
+      <c r="J583" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="L583" t="inlineStr">
+        <is>
+          <t>Localização: Categoria.</t>
+        </is>
+      </c>
+      <c r="M583" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Banner-Pesquisa-e4ee4d8f0b188272a6f101cfdd8470d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>Banner Lateral (Continente Online)</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>200x200 (Desktop, Tablet e Mobile)</t>
+        </is>
+      </c>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB</t>
+        </is>
+      </c>
+      <c r="J584" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="L584" t="inlineStr">
+        <is>
+          <t>Localização: Categoria.</t>
+        </is>
+      </c>
+      <c r="M584" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Banner-Lateral-f3be4d8f0b18822aa57e01481055c040</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>Hero Banner (Continente Online)</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>Desktop: 1919x640; Mobile: 767x575</t>
+        </is>
+      </c>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>Máx. 250 KB</t>
+        </is>
+      </c>
+      <c r="J585" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="L585" t="inlineStr">
+        <is>
+          <t>Localização: Homepage.</t>
+        </is>
+      </c>
+      <c r="M585" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Hero-Banner-da2e4d8f0b1882f68c558138a2a5151d</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>Feed (Meta)</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>1080x1080</t>
+        </is>
+      </c>
+      <c r="L586" t="inlineStr">
+        <is>
+          <t>Off Site (Facebook/Instagram).</t>
+        </is>
+      </c>
+      <c r="M586" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Feed-027e4d8f0b18833694fa0199c0e3d6d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>Story (Meta)</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>1080x1920</t>
+        </is>
+      </c>
+      <c r="L587" t="inlineStr">
+        <is>
+          <t>Off Site (Facebook/Instagram).</t>
+        </is>
+      </c>
+      <c r="M587" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Story-bb5e4d8f0b188230989c0197e2ace3bf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -26159,12 +26159,12 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
@@ -26305,12 +26305,12 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
@@ -26357,12 +26357,12 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
@@ -26409,12 +26409,12 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -26456,12 +26456,12 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
@@ -26503,12 +26503,12 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -26550,12 +26550,12 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
@@ -26597,12 +26597,12 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -26644,12 +26644,12 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -26691,12 +26691,12 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
@@ -26743,12 +26743,12 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -26795,12 +26795,12 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
@@ -26847,12 +26847,12 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -26899,12 +26899,12 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
@@ -26951,12 +26951,12 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -27003,12 +27003,12 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -27055,12 +27055,12 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -27092,12 +27092,12 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -27144,12 +27144,12 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
@@ -27196,12 +27196,12 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -27248,12 +27248,12 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -27290,12 +27290,12 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M587"/>
+  <dimension ref="A1:M594"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27329,6 +27329,295 @@
         </is>
       </c>
     </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>Clearspot</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>Clearspot</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>Grandes Formatos / Empenas</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>Variável por localização (ex.: 36 m² a 216 m²)</t>
+        </is>
+      </c>
+      <c r="L588" t="inlineStr">
+        <is>
+          <t>Publicidade em fachadas/empenas de grande dimensão — medida específica por local; consultar a Clearspot para o site em concreto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>Clearspot</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>Clearspot</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>DOOH - Saldanha Square</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>3 ecrãs LED (comunicação simultânea), 3,84x2,88m cada — 864x648px (P4)</t>
+        </is>
+      </c>
+      <c r="J589" t="inlineStr">
+        <is>
+          <t>MOV/MP4, codec H264</t>
+        </is>
+      </c>
+      <c r="L589" t="inlineStr">
+        <is>
+          <t>Duração do spot: 10 segundos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>Clearspot</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>Clearspot</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>DOOH - Oeiras Valley</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>2160x504px</t>
+        </is>
+      </c>
+      <c r="J590" t="inlineStr">
+        <is>
+          <t>MOV/MP4</t>
+        </is>
+      </c>
+      <c r="L590" t="inlineStr">
+        <is>
+          <t>Duração do spot: 10 segundos. Entrada de material: quarta-feira às 06h00. Exibição 7 dias por semana.</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>Clearspot</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>Clearspot</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>Rede de Praias (50 faces)</t>
+        </is>
+      </c>
+      <c r="L591" t="inlineStr">
+        <is>
+          <t>Rede de 50 faces instalada nas principais entradas das praias. Especificações técnicas (dimensão/peso/tipo de ficheiro) não indicadas no media kit — confirmar com a Clearspot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>Awin</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>Awin</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>Logo</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>120x60 ou 88x31</t>
+        </is>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>Máx. 50 KB</t>
+        </is>
+      </c>
+      <c r="J592" t="inlineStr">
+        <is>
+          <t>GIF</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>Awin</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>Awin</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>Banner</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>300x250, 728x90, 468x60, 160x600, 120x600, 980x90 ou 250x250</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>Máx. 50 KB</t>
+        </is>
+      </c>
+      <c r="J593" t="inlineStr">
+        <is>
+          <t>GIF</t>
+        </is>
+      </c>
+      <c r="L593" t="inlineStr">
+        <is>
+          <t>Conjunto genérico de banners + conjunto específico, consoante a campanha.</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>Awin</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>Awin</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>HTML (Email)</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>500x500</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>Máx. 50 KB</t>
+        </is>
+      </c>
+      <c r="J594" t="inlineStr">
+        <is>
+          <t>HTML</t>
+        </is>
+      </c>
+      <c r="L594" t="inlineStr">
+        <is>
+          <t>Necessário em caso de ativação por email marketing, modelo CPL.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M594"/>
+  <dimension ref="A1:M602"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27618,6 +27618,392 @@
         </is>
       </c>
     </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>AdsMovil</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>AdsMovil</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>Display - Banners</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>300x250, 300x600, 320x50, 320x480, 480x320, 300x50, 728x90, 160x600 ou 320x100</t>
+        </is>
+      </c>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>Máx. 400 KB</t>
+        </is>
+      </c>
+      <c r="J595" t="inlineStr">
+        <is>
+          <t>JPG, GIF, PNG, JPEG, JS Tag, Iframe Tag ou MRAID Tag</t>
+        </is>
+      </c>
+      <c r="L595" t="inlineStr">
+        <is>
+          <t>Compra: CPM ou CPC. Recomendado um mínimo de 3 tamanhos por campanha (320x50, 320x480 e 300x600).</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>AdsMovil</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>AdsMovil</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>In-Game Display</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>300x250, 320x50 ou 728x90</t>
+        </is>
+      </c>
+      <c r="I596" t="inlineStr">
+        <is>
+          <t>Máx. 300 KB</t>
+        </is>
+      </c>
+      <c r="J596" t="inlineStr">
+        <is>
+          <t>JPG, GIF, PNG ou JPEG</t>
+        </is>
+      </c>
+      <c r="L596" t="inlineStr">
+        <is>
+          <t>Compra: CPM. Recomendado usar os 3 tamanhos por campanha.</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>AdsMovil</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>AdsMovil</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>Recomendado: 320x480. Outros: 300x250 ou 300x600.</t>
+        </is>
+      </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>HTML: máx. 1 MB. Vídeo: máx. 5 MB, até 30″.</t>
+        </is>
+      </c>
+      <c r="J597" t="inlineStr">
+        <is>
+          <t>JS Tag, iFrame Tag, MRAID Tag (in-app) ou HTML (extensão .html; .zip não suportado)</t>
+        </is>
+      </c>
+      <c r="L597" t="inlineStr">
+        <is>
+          <t>Compra: CPM ou CPC. Inclui RM Interstitial (320x480) e RM Expandable Banner (320x50 recolhido → 320x480 expandido).</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>AdsMovil</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>AdsMovil</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>Vídeo (Instream/Outstream)</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>1280x720 ou 1080x1350</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>4:3 ou 16:9</t>
+        </is>
+      </c>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>Máx. 10 MB</t>
+        </is>
+      </c>
+      <c r="J598" t="inlineStr">
+        <is>
+          <t>MP4, MOV, FLV, VAST 3.0 ou VPAID 2.0; companion asset: GIF, JPG, JPEG ou PNG</t>
+        </is>
+      </c>
+      <c r="L598" t="inlineStr">
+        <is>
+          <t>Compra: CPM ou CPCV. Duração máx. 30″ (recomendado 15-30″). Vídeos do YouTube não são aceites.</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>AdsMovil</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>AdsMovil</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>Vídeo Rewarded</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>480x320 ou 1024x768</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>4:3 ou 16:9</t>
+        </is>
+      </c>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>Máx. 10 MB</t>
+        </is>
+      </c>
+      <c r="J599" t="inlineStr">
+        <is>
+          <t>MP4, MOV, FLV ou VAST 3.0; companion asset: GIF, JPG, JPEG ou PNG</t>
+        </is>
+      </c>
+      <c r="L599" t="inlineStr">
+        <is>
+          <t>Compra: CPM ou CPCV. Duração: 15 ou 30″, não passível de ser saltado. Vídeos do YouTube não são aceites.</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>AdsMovil</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>AdsMovil</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>Áudio</t>
+        </is>
+      </c>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>Máx. 3 MB</t>
+        </is>
+      </c>
+      <c r="J600" t="inlineStr">
+        <is>
+          <t>VAST 2.0, MP3, WAV, WMA ou OGG; companion asset (300x250, máx. 50 KB): JPG, JPEG, PNG ou GIF</t>
+        </is>
+      </c>
+      <c r="L600" t="inlineStr">
+        <is>
+          <t>Compra: CPE. Duração: 15″, 30″ ou 60″. Qualidade mínima: 128 kbps / 44100 Hz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>AdsMovil</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>AdsMovil</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>Push Notifications</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>Imagem principal: 452x226 e 600x400 (ambas obrigatórias). Logo: 48x48.</t>
+        </is>
+      </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>Máx. 5 MB</t>
+        </is>
+      </c>
+      <c r="J601" t="inlineStr">
+        <is>
+          <t>JPG ou PNG</t>
+        </is>
+      </c>
+      <c r="L601" t="inlineStr">
+        <is>
+          <t>Compra: CPC (mín. 150 cliques/dia). Título: máx. 30 carateres. Subtítulo: máx. 35 carateres. Sem emojis no texto. Máx. 10 criatividades por campanha.</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>AdsMovil</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>AdsMovil</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>Connected TV</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>Resolução HD</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>4:3 ou 16:9</t>
+        </is>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>Máx. 5 MB</t>
+        </is>
+      </c>
+      <c r="J602" t="inlineStr">
+        <is>
+          <t>MP4, VAST 2.0 ou VAST 3.0</t>
+        </is>
+      </c>
+      <c r="L602" t="inlineStr">
+        <is>
+          <t>Compra: CPM. Duração: 15 ou 30″, não passível de ser saltado. Vídeos do YouTube não são suportados; dispositivos CTV não suportam VPAID.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M602"/>
+  <dimension ref="A1:M605"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28004,6 +28004,147 @@
         </is>
       </c>
     </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>Standard Banners</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>1388x1734, 720x540, 2640x600, 1760x400 ou 300x250</t>
+        </is>
+      </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB</t>
+        </is>
+      </c>
+      <c r="J603" t="inlineStr">
+        <is>
+          <t>JPG, PNG ou GIF</t>
+        </is>
+      </c>
+      <c r="L603" t="inlineStr">
+        <is>
+          <t>Ver no link as safe zones e danger zones.</t>
+        </is>
+      </c>
+      <c r="M603" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/display-studio</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>Outlook</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>Outlook</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>Native Ads</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>Logo da marca: 100x100. Imagem: 1200x627 ou 627x627.</t>
+        </is>
+      </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>Máx. 120 KB</t>
+        </is>
+      </c>
+      <c r="J604" t="inlineStr">
+        <is>
+          <t>JPG, PNG ou GIF</t>
+        </is>
+      </c>
+      <c r="L604" t="inlineStr">
+        <is>
+          <t>Short Headline (x2): máx. 30 carateres. Long Headline: máx. 90 carateres. Descrição: máx. 90 carateres. Business/Brand Name: máx. 25 carateres.</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>Open AI</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>Open AI</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>1200x1200</t>
+        </is>
+      </c>
+      <c r="J605" t="inlineStr">
+        <is>
+          <t>JPG, PNG</t>
+        </is>
+      </c>
+      <c r="L605" t="inlineStr">
+        <is>
+          <t>Título: máx. 50 carateres (recomendado 16-24). Descrição: máx. 100 carateres (recomendado 32-48).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M605"/>
+  <dimension ref="A1:M615"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28145,6 +28145,476 @@
         </is>
       </c>
     </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>Virtual Category (Icon) - Homepage</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>100x100</t>
+        </is>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="J606" t="inlineStr">
+        <is>
+          <t>JPG, PNG ou GIF</t>
+        </is>
+      </c>
+      <c r="L606" t="inlineStr">
+        <is>
+          <t>Posição: Homepage (Desktop). Texto/Copy: máx. 30 carateres.</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>Screening (Takeover) - Homepage</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>1920x1100</t>
+        </is>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="J607" t="inlineStr">
+        <is>
+          <t>JPG, PNG ou GIF</t>
+        </is>
+      </c>
+      <c r="L607" t="inlineStr">
+        <is>
+          <t>Posição: Homepage (Desktop). São necessárias duas versões para o Screening (Takeover). Ter atenção às áreas visíveis (Safe Zones).</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>Screening (Takeover) - Listing Page</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>1920x1100</t>
+        </is>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="J608" t="inlineStr">
+        <is>
+          <t>JPG, PNG ou GIF</t>
+        </is>
+      </c>
+      <c r="L608" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page (Desktop). São necessárias duas versões para o Screening (Takeover). Ter atenção às áreas visíveis (Safe Zones).</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>Full Branding - Homepage</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>2x 1920x1100, 4x 270x190</t>
+        </is>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="J609" t="inlineStr">
+        <is>
+          <t>JPG, PNG ou GIF</t>
+        </is>
+      </c>
+      <c r="L609" t="inlineStr">
+        <is>
+          <t>Posição: Homepage (Desktop). São necessárias duas versões para o Screening (Takeover). Ter atenção às áreas visíveis (Safe Zones). Título Principal: máx. 20 carateres. Título: máx. 18 carateres. Descrição: máx. 25 carateres.</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>Full Branding - Listing</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>2x 1920x1100, 4x 270x190, 1x 1237x300, 1x 1029x300</t>
+        </is>
+      </c>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="J610" t="inlineStr">
+        <is>
+          <t>JPG, PNG ou GIF</t>
+        </is>
+      </c>
+      <c r="L610" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page (Desktop). São necessárias duas versões para o Screening (Takeover). Ter atenção às áreas visíveis (Safe Zones). Título Principal: máx. 20 carateres. Título: máx. 18 carateres. Descrição: máx. 25 carateres.</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>My Account</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>890x70</t>
+        </is>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="J611" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="L611" t="inlineStr">
+        <is>
+          <t>Posição: My Account Page (Desktop).</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>Megaboard (Topboard)</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>1920x300</t>
+        </is>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="J612" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="L612" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page &amp; Ad Page (Desktop). Ter atenção às áreas visíveis (Safe Zones).</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>Skyscraper</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>160x600</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="J613" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="L613" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page (Desktop).</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>Rectangle (MREC)</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>300x250</t>
+        </is>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="J614" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="L614" t="inlineStr">
+        <is>
+          <t>Posição: Ad Page &amp; Gallery Page (Desktop).</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>Billboard</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>970x250</t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="J615" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="L615" t="inlineStr">
+        <is>
+          <t>Posição: várias páginas — Listing Page, Ad Page, Seller Page, Observed Ads (Desktop).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M615"/>
+  <dimension ref="A1:M625"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28615,6 +28615,481 @@
         </is>
       </c>
     </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>Native (In Feed)</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>210x150</t>
+        </is>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="J616" t="inlineStr">
+        <is>
+          <t>JPG, PNG ou GIF</t>
+        </is>
+      </c>
+      <c r="L616" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page (Desktop). Título: máx. 45 carateres. CTA: máx. 10 carateres.</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>Text Link / Brand Link</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>Logo: 80x80 (opcional)</t>
+        </is>
+      </c>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB (apenas se incluir logo)</t>
+        </is>
+      </c>
+      <c r="J617" t="inlineStr">
+        <is>
+          <t>JPG, PNG ou GIF (apenas se incluir logo)</t>
+        </is>
+      </c>
+      <c r="L617" t="inlineStr">
+        <is>
+          <t>Posição: Ad Page (Desktop). Texto/Copy: máx. 40 carateres.</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>Video Outstream</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>1920x1080</t>
+        </is>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>Máx. 10 MB</t>
+        </is>
+      </c>
+      <c r="J618" t="inlineStr">
+        <is>
+          <t>MP4, até 30 segundos</t>
+        </is>
+      </c>
+      <c r="L618" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page &amp; Ad Page (Desktop).</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>TopMobileBoard (Leaderboard)</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>300x100 ou 320x100</t>
+        </is>
+      </c>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="J619" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="L619" t="inlineStr">
+        <is>
+          <t>Posição: Homepage (Mobile).</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>Virtual Category (Icon) - Homepage (Mobile)</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>80x83</t>
+        </is>
+      </c>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="J620" t="inlineStr">
+        <is>
+          <t>JPG, PNG ou GIF</t>
+        </is>
+      </c>
+      <c r="L620" t="inlineStr">
+        <is>
+          <t>Posição: Homepage (Mobile). Texto/Copy: máx. 10 carateres.</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>TopMobileBoard (Anchor)</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>600x200</t>
+        </is>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="J621" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="L621" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page (Mobile).</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>Full Branding Mobile</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>1x 600x200, 3x 300x250</t>
+        </is>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="J622" t="inlineStr">
+        <is>
+          <t>JPG, PNG ou GIF</t>
+        </is>
+      </c>
+      <c r="L622" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page (Mobile).</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>Rectangle (MREC) (Mobile)</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>300x250</t>
+        </is>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="J623" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="L623" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page &amp; Ad Page (Mobile).</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>Native</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>1000x563</t>
+        </is>
+      </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="J624" t="inlineStr">
+        <is>
+          <t>JPG, PNG ou GIF</t>
+        </is>
+      </c>
+      <c r="L624" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page (Mobile). Título: máx. 25 carateres. Descrição: máx. 35 carateres.</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>Text Link / Brand Link (Mobile)</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>Logo: 80x80 (opcional)</t>
+        </is>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB (apenas se incluir logo)</t>
+        </is>
+      </c>
+      <c r="J625" t="inlineStr">
+        <is>
+          <t>JPG, PNG ou GIF (apenas se incluir logo)</t>
+        </is>
+      </c>
+      <c r="L625" t="inlineStr">
+        <is>
+          <t>Posição: Ad Page (Mobile). Texto/Copy: máx. 20 carateres.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M625"/>
+  <dimension ref="A1:M640"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29090,6 +29090,716 @@
         </is>
       </c>
     </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>Top Mobile Board (Seller/Observed Page)</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>320x100</t>
+        </is>
+      </c>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="J626" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="L626" t="inlineStr">
+        <is>
+          <t>Posição: Seller Listing Page &amp; Observed Page (Mobile).</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>Rectangle (MREC) (App)</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>300x250</t>
+        </is>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="J627" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="L627" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page &amp; Ad Page (App — Android e iOS).</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>Observed Ads (App)</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>320x100</t>
+        </is>
+      </c>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="J628" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="L628" t="inlineStr">
+        <is>
+          <t>Posição: Observed Page (App).</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>Top Mobile Board (App - Homepage)</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>320x100</t>
+        </is>
+      </c>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="J629" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="L629" t="inlineStr">
+        <is>
+          <t>Posição: Homepage (App — Android e iOS).</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>Showcase (Masthead)</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>1920x300</t>
+        </is>
+      </c>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="J630" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="L630" t="inlineStr">
+        <is>
+          <t>Posição: Homepage (Desktop). Ter atenção às áreas visíveis (Safe Zones).</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>Megaboard (Topboard)</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>1920x300</t>
+        </is>
+      </c>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="J631" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="L631" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page &amp; Ad Page (Desktop). Ter atenção às áreas visíveis (Safe Zones).</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>Native</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>Imagem: 252x152. Logo: 80x36.</t>
+        </is>
+      </c>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="J632" t="inlineStr">
+        <is>
+          <t>JPG, PNG ou GIF</t>
+        </is>
+      </c>
+      <c r="L632" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page (Desktop). Título: máx. 45 carateres. Descrição: máx. 65 carateres. CTA: máx. 10 carateres.</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>Skyscraper | Halfpage</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>160x600 ou 300x600</t>
+        </is>
+      </c>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="J633" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="L633" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page (Desktop).</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>Billboard</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>914x212</t>
+        </is>
+      </c>
+      <c r="I634" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="J634" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="L634" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page (Desktop).</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>Rectangle (MREC)</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>300x250</t>
+        </is>
+      </c>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="J635" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="L635" t="inlineStr">
+        <is>
+          <t>Posição: Ad Page &amp; Gallery Page (Desktop).</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>Halfpage</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>300x600</t>
+        </is>
+      </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="J636" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="L636" t="inlineStr">
+        <is>
+          <t>Posição: Ad Page (Desktop).</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>Video Outstream</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>1920x1080</t>
+        </is>
+      </c>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>Máx. 10 MB</t>
+        </is>
+      </c>
+      <c r="J637" t="inlineStr">
+        <is>
+          <t>MP4, até 30 segundos</t>
+        </is>
+      </c>
+      <c r="L637" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page &amp; Ad Page (Desktop).</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>Showcase (Masthead) (Mobile)</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>1080x450</t>
+        </is>
+      </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="J638" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="L638" t="inlineStr">
+        <is>
+          <t>Posição: Homepage (Mobile).</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>Full Branding Mobile</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>1x 600x200, 3x 300x250</t>
+        </is>
+      </c>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="J639" t="inlineStr">
+        <is>
+          <t>JPG, PNG ou GIF</t>
+        </is>
+      </c>
+      <c r="L639" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page (Mobile).</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>TopMobileBoard (Anchor)</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>600x200</t>
+        </is>
+      </c>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="J640" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="L640" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page (Mobile).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M640"/>
+  <dimension ref="A1:M645"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29800,6 +29800,241 @@
         </is>
       </c>
     </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>Rectangle (MREC) (Mobile)</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>300x250</t>
+        </is>
+      </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="J641" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="L641" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page &amp; Ad Page (Mobile).</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>Imovirtual</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>Imovirtual</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>Megaboard (Topboard)</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>1920x200</t>
+        </is>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="J642" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="L642" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page (Desktop). Ter atenção às áreas visíveis (Safe Zones).</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>Imovirtual</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>Imovirtual</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>Native (In List)</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>820x200</t>
+        </is>
+      </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="J643" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="L643" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page (Desktop).</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>Imovirtual</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>Imovirtual</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>Halfpage</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>300x600</t>
+        </is>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="J644" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="L644" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page &amp; Ad Page (Desktop).</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>Imovirtual</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>Imovirtual</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>Rectangle (MREC)</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>300x250</t>
+        </is>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="J645" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="L645" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page &amp; Ad Page (Desktop).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M645"/>
+  <dimension ref="A1:M648"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16309,6 +16309,11 @@
       <c r="J318" t="inlineStr">
         <is>
           <t>JPEG, JPG, PNG, GIF ou HTML5 (GWD)</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
         </is>
       </c>
     </row>
@@ -28191,6 +28196,11 @@
           <t>Posição: Homepage (Desktop). Texto/Copy: máx. 30 carateres.</t>
         </is>
       </c>
+      <c r="M606" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
@@ -28235,7 +28245,12 @@
       </c>
       <c r="L607" t="inlineStr">
         <is>
-          <t>Posição: Homepage (Desktop). São necessárias duas versões para o Screening (Takeover). Ter atenção às áreas visíveis (Safe Zones).</t>
+          <t>Posição: Homepage (Desktop). São necessárias duas versões para o Screening (Takeover). Ter atenção às áreas visíveis (Safe Zones). Existe template para download no site de specs.</t>
+        </is>
+      </c>
+      <c r="M607" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
         </is>
       </c>
     </row>
@@ -28282,7 +28297,12 @@
       </c>
       <c r="L608" t="inlineStr">
         <is>
-          <t>Posição: Listing Page (Desktop). São necessárias duas versões para o Screening (Takeover). Ter atenção às áreas visíveis (Safe Zones).</t>
+          <t>Posição: Listing Page (Desktop). São necessárias duas versões para o Screening (Takeover). Ter atenção às áreas visíveis (Safe Zones). Existe template para download no site de specs.</t>
+        </is>
+      </c>
+      <c r="M608" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
         </is>
       </c>
     </row>
@@ -28329,7 +28349,12 @@
       </c>
       <c r="L609" t="inlineStr">
         <is>
-          <t>Posição: Homepage (Desktop). São necessárias duas versões para o Screening (Takeover). Ter atenção às áreas visíveis (Safe Zones). Título Principal: máx. 20 carateres. Título: máx. 18 carateres. Descrição: máx. 25 carateres.</t>
+          <t>Posição: Homepage (Desktop). São necessárias duas versões para o Screening (Takeover). Ter atenção às áreas visíveis (Safe Zones). Título Principal: máx. 20 carateres. Título: máx. 18 carateres. Descrição: máx. 25 carateres. Existe template para download no site de specs.</t>
+        </is>
+      </c>
+      <c r="M609" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
         </is>
       </c>
     </row>
@@ -28376,7 +28401,12 @@
       </c>
       <c r="L610" t="inlineStr">
         <is>
-          <t>Posição: Listing Page (Desktop). São necessárias duas versões para o Screening (Takeover). Ter atenção às áreas visíveis (Safe Zones). Título Principal: máx. 20 carateres. Título: máx. 18 carateres. Descrição: máx. 25 carateres.</t>
+          <t>Posição: Listing Page (Desktop). São necessárias duas versões para o Screening (Takeover). Ter atenção às áreas visíveis (Safe Zones). Título Principal: máx. 20 carateres. Título: máx. 18 carateres. Descrição: máx. 25 carateres. Existe template para download no site de specs.</t>
+        </is>
+      </c>
+      <c r="M610" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
         </is>
       </c>
     </row>
@@ -28426,6 +28456,11 @@
           <t>Posição: My Account Page (Desktop).</t>
         </is>
       </c>
+      <c r="M611" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
@@ -28470,7 +28505,12 @@
       </c>
       <c r="L612" t="inlineStr">
         <is>
-          <t>Posição: Listing Page &amp; Ad Page (Desktop). Ter atenção às áreas visíveis (Safe Zones).</t>
+          <t>Posição: Listing Page &amp; Ad Page (Desktop). Ter atenção às áreas visíveis (Safe Zones). Existe template para download no site de specs.</t>
+        </is>
+      </c>
+      <c r="M612" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
         </is>
       </c>
     </row>
@@ -28520,6 +28560,11 @@
           <t>Posição: Listing Page (Desktop).</t>
         </is>
       </c>
+      <c r="M613" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
@@ -28567,6 +28612,11 @@
           <t>Posição: Ad Page &amp; Gallery Page (Desktop).</t>
         </is>
       </c>
+      <c r="M614" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
@@ -28614,6 +28664,11 @@
           <t>Posição: várias páginas — Listing Page, Ad Page, Seller Page, Observed Ads (Desktop).</t>
         </is>
       </c>
+      <c r="M615" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
@@ -28661,6 +28716,11 @@
           <t>Posição: Listing Page (Desktop). Título: máx. 45 carateres. CTA: máx. 10 carateres.</t>
         </is>
       </c>
+      <c r="M616" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
@@ -28708,6 +28768,11 @@
           <t>Posição: Ad Page (Desktop). Texto/Copy: máx. 40 carateres.</t>
         </is>
       </c>
+      <c r="M617" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
@@ -28760,6 +28825,11 @@
           <t>Posição: Listing Page &amp; Ad Page (Desktop).</t>
         </is>
       </c>
+      <c r="M618" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
@@ -28807,6 +28877,11 @@
           <t>Posição: Homepage (Mobile).</t>
         </is>
       </c>
+      <c r="M619" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
@@ -28854,6 +28929,11 @@
           <t>Posição: Homepage (Mobile). Texto/Copy: máx. 10 carateres.</t>
         </is>
       </c>
+      <c r="M620" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
@@ -28901,6 +28981,11 @@
           <t>Posição: Listing Page (Mobile).</t>
         </is>
       </c>
+      <c r="M621" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
@@ -28948,6 +29033,11 @@
           <t>Posição: Listing Page (Mobile).</t>
         </is>
       </c>
+      <c r="M622" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
@@ -28995,6 +29085,11 @@
           <t>Posição: Listing Page &amp; Ad Page (Mobile).</t>
         </is>
       </c>
+      <c r="M623" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
@@ -29042,6 +29137,11 @@
           <t>Posição: Listing Page (Mobile). Título: máx. 25 carateres. Descrição: máx. 35 carateres.</t>
         </is>
       </c>
+      <c r="M624" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
@@ -29089,6 +29189,11 @@
           <t>Posição: Ad Page (Mobile). Texto/Copy: máx. 20 carateres.</t>
         </is>
       </c>
+      <c r="M625" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
@@ -29136,6 +29241,11 @@
           <t>Posição: Seller Listing Page &amp; Observed Page (Mobile).</t>
         </is>
       </c>
+      <c r="M626" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
@@ -29183,6 +29293,11 @@
           <t>Posição: Listing Page &amp; Ad Page (App — Android e iOS).</t>
         </is>
       </c>
+      <c r="M627" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
@@ -29230,6 +29345,11 @@
           <t>Posição: Observed Page (App).</t>
         </is>
       </c>
+      <c r="M628" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
@@ -29277,6 +29397,11 @@
           <t>Posição: Homepage (App — Android e iOS).</t>
         </is>
       </c>
+      <c r="M629" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
@@ -29321,7 +29446,12 @@
       </c>
       <c r="L630" t="inlineStr">
         <is>
-          <t>Posição: Homepage (Desktop). Ter atenção às áreas visíveis (Safe Zones).</t>
+          <t>Posição: Homepage (Desktop). Ter atenção às áreas visíveis (Safe Zones). Existe template para download no site de specs.</t>
+        </is>
+      </c>
+      <c r="M630" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
         </is>
       </c>
     </row>
@@ -29368,7 +29498,12 @@
       </c>
       <c r="L631" t="inlineStr">
         <is>
-          <t>Posição: Listing Page &amp; Ad Page (Desktop). Ter atenção às áreas visíveis (Safe Zones).</t>
+          <t>Posição: Listing Page &amp; Ad Page (Desktop). Ter atenção às áreas visíveis (Safe Zones). Existe template para download no site de specs.</t>
+        </is>
+      </c>
+      <c r="M631" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
         </is>
       </c>
     </row>
@@ -29418,6 +29553,11 @@
           <t>Posição: Listing Page (Desktop). Título: máx. 45 carateres. Descrição: máx. 65 carateres. CTA: máx. 10 carateres.</t>
         </is>
       </c>
+      <c r="M632" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
@@ -29465,6 +29605,11 @@
           <t>Posição: Listing Page (Desktop).</t>
         </is>
       </c>
+      <c r="M633" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
@@ -29512,6 +29657,11 @@
           <t>Posição: Listing Page (Desktop).</t>
         </is>
       </c>
+      <c r="M634" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
@@ -29559,6 +29709,11 @@
           <t>Posição: Ad Page &amp; Gallery Page (Desktop).</t>
         </is>
       </c>
+      <c r="M635" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
@@ -29606,6 +29761,11 @@
           <t>Posição: Ad Page (Desktop).</t>
         </is>
       </c>
+      <c r="M636" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
@@ -29658,6 +29818,11 @@
           <t>Posição: Listing Page &amp; Ad Page (Desktop).</t>
         </is>
       </c>
+      <c r="M637" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
@@ -29705,6 +29870,11 @@
           <t>Posição: Homepage (Mobile).</t>
         </is>
       </c>
+      <c r="M638" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
@@ -29752,6 +29922,11 @@
           <t>Posição: Listing Page (Mobile).</t>
         </is>
       </c>
+      <c r="M639" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
@@ -29799,6 +29974,11 @@
           <t>Posição: Listing Page (Mobile).</t>
         </is>
       </c>
+      <c r="M640" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
@@ -29846,6 +30026,11 @@
           <t>Posição: Listing Page &amp; Ad Page (Mobile).</t>
         </is>
       </c>
+      <c r="M641" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
@@ -29893,6 +30078,11 @@
           <t>Posição: Listing Page (Desktop). Ter atenção às áreas visíveis (Safe Zones).</t>
         </is>
       </c>
+      <c r="M642" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
@@ -29940,6 +30130,11 @@
           <t>Posição: Listing Page (Desktop).</t>
         </is>
       </c>
+      <c r="M643" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
@@ -29987,6 +30182,11 @@
           <t>Posição: Listing Page &amp; Ad Page (Desktop).</t>
         </is>
       </c>
+      <c r="M644" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
@@ -30032,6 +30232,167 @@
       <c r="L645" t="inlineStr">
         <is>
           <t>Posição: Listing Page &amp; Ad Page (Desktop).</t>
+        </is>
+      </c>
+      <c r="M645" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>Imovirtual</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>Imovirtual</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>Text Link (Brand Link)</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>Logo: 80x80 (opcional)</t>
+        </is>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB (apenas se incluir logo)</t>
+        </is>
+      </c>
+      <c r="J646" t="inlineStr">
+        <is>
+          <t>JPG, PNG ou GIF (apenas se incluir logo)</t>
+        </is>
+      </c>
+      <c r="L646" t="inlineStr">
+        <is>
+          <t>Posição: Ad Page (Desktop). Texto/Copy: máx. 40 carateres.</t>
+        </is>
+      </c>
+      <c r="M646" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>Imovirtual</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>Imovirtual</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>Rectangle (MREC) (Mobile)</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>300x250</t>
+        </is>
+      </c>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="J647" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="L647" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page &amp; Ad Page (Mobile).</t>
+        </is>
+      </c>
+      <c r="M647" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>Imovirtual</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>Imovirtual</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>Text Link (Brand Link) (Mobile)</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>Logo: 80x80 (opcional)</t>
+        </is>
+      </c>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB (apenas se incluir logo)</t>
+        </is>
+      </c>
+      <c r="J648" t="inlineStr">
+        <is>
+          <t>JPG, PNG ou GIF (apenas se incluir logo)</t>
+        </is>
+      </c>
+      <c r="L648" t="inlineStr">
+        <is>
+          <t>Posição: Ad Page (Mobile). Texto/Copy: máx. 20 carateres.</t>
+        </is>
+      </c>
+      <c r="M648" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
         </is>
       </c>
     </row>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M648"/>
+  <dimension ref="A1:M705"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30396,6 +30396,2460 @@
         </is>
       </c>
     </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>Category Window (Higiene)</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>Largura total 133 cm (área visível 100 cm); altura 255 cm; faixas laterais 15 cm cada</t>
+        </is>
+      </c>
+      <c r="L649" t="inlineStr">
+        <is>
+          <t>Molde técnico (die-line) para a categoria Higiene — sem retalhista nem especificações de produção/impressão indicadas no documento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>Archmedia 220cm</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>Largura total 220 cm (área visível 170 cm); altura 220 cm; faixa lateral 25 cm</t>
+        </is>
+      </c>
+      <c r="L650" t="inlineStr">
+        <is>
+          <t>Molde técnico (die-line) — sem retalhista nem especificações de material/impressão.</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>Archmedia 250cm</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>Largura total 250 cm (área visível 200 cm); altura 220 cm; faixa lateral 25 cm</t>
+        </is>
+      </c>
+      <c r="L651" t="inlineStr">
+        <is>
+          <t>Molde técnico (die-line) — sem retalhista nem especificações de material/impressão.</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>Archmedia 320cm</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>Largura total 320 cm (área visível 270 cm); altura 220 cm; faixa lateral 25 cm</t>
+        </is>
+      </c>
+      <c r="L652" t="inlineStr">
+        <is>
+          <t>Molde técnico (die-line) — sem retalhista nem especificações de material/impressão.</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>Category Window (Várias Medidas)</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>Conforme indicado no documento: largura topo 1336 cm; alturas laterais 2000 cm e 2200 cm</t>
+        </is>
+      </c>
+      <c r="L653" t="inlineStr">
+        <is>
+          <t>Nome do ficheiro indica "140x255cm", mas os valores no PDF (em cm) não batem certo — possível troca de unidade (cm/mm) no documento de origem. Reportado literalmente, sem correção. Molde técnico, sem retalhista nem specs de produção.</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>Shelf Display Media Luna</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>Suporte 160x500mm; vinil base 158x100mm; vinil frontal (com luz) 291x49mm</t>
+        </is>
+      </c>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>Escala real 1:1 + 2mm de sangria</t>
+        </is>
+      </c>
+      <c r="J654" t="inlineStr">
+        <is>
+          <t>PDF qualidade de imprensa (PDF 1.4, CMYK, 300 dpi, tipografia incrustada, transparências conservadas)</t>
+        </is>
+      </c>
+      <c r="L654" t="inlineStr">
+        <is>
+          <t>Suporte metálico em meia-lua com iluminação LED interior; vinil Easy Dot; impressão digital 4/0. Só pode exibir 1 produto por suporte; marcas com mínimo de 2 linhas de facing. Contratação mínima de 2 meses. Entrega 1,5 meses antes do início da campanha. Documento da In-Store Media España.</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>Alarm Hall-Media</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>140x48x14 cms e 140x40x11 cms (segmentos 14/48/14/48 cm)</t>
+        </is>
+      </c>
+      <c r="J655" t="inlineStr">
+        <is>
+          <t>Adobe Illustrator (aberto, sem bleed); CMYK; resolução mín. 150 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="L655" t="inlineStr">
+        <is>
+          <t>Material: cartão micro canelado, corte simples; impressão digital 4/0. Criatividade em português. Não colocar informação importante entre 40 e 56 cm da base (alturas de defesas de alarme variam por loja). Entrega: 1 mês antes para validação, 2 semanas antes para Arte Final.</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>Door-Media — Pingo Doce</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>134x150 cms, 114x125 cms ou 90x100 cms</t>
+        </is>
+      </c>
+      <c r="J656" t="inlineStr">
+        <is>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="L656" t="inlineStr">
+        <is>
+          <t>Material: vinil monomérico com brilho, adesivo removível; impressão tintas low solvent 720 DPI + laminação brilho. Criatividade em português. Não colocar texto/imagem no centro onde abrem as portas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>Welcome Screen — Auchan</t>
+        </is>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>1280x256, 384x576, 384x768, 768x256 ou 960x192 px</t>
+        </is>
+      </c>
+      <c r="I657" t="inlineStr">
+        <is>
+          <t>Máx. 25 MB</t>
+        </is>
+      </c>
+      <c r="J657" t="inlineStr">
+        <is>
+          <t>MP4, codec H264, 25 fps, sem áudio</t>
+        </is>
+      </c>
+      <c r="L657" t="inlineStr">
+        <is>
+          <t>Duração 10 seg. Bitrate recomendado 10 Mbps. Emissão só após validação ISM; entrega da AF segundo indicações ISM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>Welcome Screen — Pingo Doce</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>Ecrã físico 3,00x2,00m; resolução 1532x1024 px</t>
+        </is>
+      </c>
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>Máx. 25 MB</t>
+        </is>
+      </c>
+      <c r="J658" t="inlineStr">
+        <is>
+          <t>MP4, codec H264, 25 fps, sem áudio</t>
+        </is>
+      </c>
+      <c r="L658" t="inlineStr">
+        <is>
+          <t>Duração 10 seg. Bitrate recomendado 10 Mbps. Emissão só após validação ISM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>Alarm Media (Cartão) — Auchan</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>120x52x4 cms, 105x52x4 cms ou 90x52x4 cms (segmentos 4/52/4/52cm)</t>
+        </is>
+      </c>
+      <c r="J659" t="inlineStr">
+        <is>
+          <t>Adobe Illustrator (aberto, sem bleed); CMYK; resolução mín. 150 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="L659" t="inlineStr">
+        <is>
+          <t>Material: cartão micro canelado, corte simples; impressão digital 4/0. Não colocar informação entre 40 e 56 cm da base.</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>Alarm Media (Cartão) — Pingo Doce</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>140x48x14 cms e 140x40x11 cms (segmentos 14/48/14/48cm)</t>
+        </is>
+      </c>
+      <c r="J660" t="inlineStr">
+        <is>
+          <t>Adobe Illustrator (aberto, sem bleed); CMYK; resolução mín. 150 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="L660" t="inlineStr">
+        <is>
+          <t>Material: cartão micro canelado, corte simples; impressão digital 4/0. Recomenda-se logo da marca nas laterais. Não colocar informação entre 40 e 56 cm da base (defesas variam por loja).</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>Alarm Media (Cartão) — Continente</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>140x48x14 cms e 140x40x11 cms (segmentos 14/48/14/48cm)</t>
+        </is>
+      </c>
+      <c r="J661" t="inlineStr">
+        <is>
+          <t>Adobe Illustrator (aberto, sem bleed); CMYK; resolução mín. 150 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="L661" t="inlineStr">
+        <is>
+          <t>Material: cartão micro canelado, corte simples; impressão digital 4/0. Não colocar informação entre 40 e 56 cm da base; sugere-se logo nas laterais.</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>Alarm Media (Cartão) — El Corte Inglês (Supercor)</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>140x48x14 cms</t>
+        </is>
+      </c>
+      <c r="J662" t="inlineStr">
+        <is>
+          <t>Adobe Illustrator (aberto, sem bleed); CMYK; resolução mín. 150 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="L662" t="inlineStr">
+        <is>
+          <t>Material: cartão micro canelado, corte simples; impressão digital 4/0. Não colocar informação entre 40 e 56 cm da base.</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>Alarm-Media (Papel) — El Corte Inglês (Supercor)</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>Face maior: 490x1210mm. Lateral (com logo/nome da marca): 105x1210mm.</t>
+        </is>
+      </c>
+      <c r="J663" t="inlineStr">
+        <is>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="L663" t="inlineStr">
+        <is>
+          <t>Material: white back paper 200 grs, corte simples; impressão offset 4/0, quadricromia. Pode colocar logo/nome da marca na faixa lateral.</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>Alarm-Media (Papel) — Auchan</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>104x16 cms, 106x22 cms ou 133x40 cms (CxL)</t>
+        </is>
+      </c>
+      <c r="J664" t="inlineStr">
+        <is>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="L664" t="inlineStr">
+        <is>
+          <t>Material: white back paper 150 grs, corte simples; impressão offset 4/0, quadricromia. Entrega: 1 mês antes para validação, 2 semanas antes para AF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>Alarm-Media (Papel) — Continente</t>
+        </is>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>49x121,5 cms</t>
+        </is>
+      </c>
+      <c r="J665" t="inlineStr">
+        <is>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="L665" t="inlineStr">
+        <is>
+          <t>Material: white back paper 150 grs, corte simples; impressão offset 4/0, quadricromia. Não colocar informação entre 31,5 e 47,5 cm da base (zona de defesa variável por loja). Documento da In-Store Media España.</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>Alarm-Media (Papel) — E.Leclerc</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>140x48x14 cms e 140x40x11 cms (segmentos 14/48/14/48cm)</t>
+        </is>
+      </c>
+      <c r="J666" t="inlineStr">
+        <is>
+          <t>Adobe Illustrator (aberto, sem bleed); CMYK; resolução mín. 150 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="L666" t="inlineStr">
+        <is>
+          <t>Material: cartão micro canelado, corte simples; impressão digital 4/0. Não colocar informação entre 40 e 56 cm da base; sugere-se logo nas laterais.</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>Alarm-Media (Papel) — El Corte Inglês Gaia</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>Tiras laterais 105x1210mm (x2); faces maiores 485x1210mm (x2)</t>
+        </is>
+      </c>
+      <c r="J667" t="inlineStr">
+        <is>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="L667" t="inlineStr">
+        <is>
+          <t>Material: white back paper 200 grs, corte simples; impressão offset 4/0. Nas tiras laterais colocar nome, logo ou slogan. Entrega: 10 dias antes do início da campanha. Nota: o nome do ficheiro de origem referia "Supercor Restelo", mas o conteúdo do documento identifica claramente este suporte como El Corte Inglês Gaia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>Alarm Media (Papel) — El Corte Inglês Departamental</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>Painel frontal: 490x1210mm. Lateral (logo/nome): 105x1210mm.</t>
+        </is>
+      </c>
+      <c r="J668" t="inlineStr">
+        <is>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="L668" t="inlineStr">
+        <is>
+          <t>Material: white back paper 200 grs, corte simples; impressão offset 4/0. Entrega: 10 dias úteis antes do início da campanha.</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>Alarm Walk — Auchan</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>600x100, 400x100 ou 250x100 cms; margem branco 1 cm; cantos arredondados</t>
+        </is>
+      </c>
+      <c r="J669" t="inlineStr">
+        <is>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="L669" t="inlineStr">
+        <is>
+          <t>Material: vinil de chão autocolante opaco 3M com lâmina antideslizante MSM; offset 4/0 + verniz UVI brilhante. Não são permitidos passatempos/jogos de sorte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>Alarm Walk — Continente</t>
+        </is>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>600x100, 400x100 ou 250x100 cms; margem branco 1 cm</t>
+        </is>
+      </c>
+      <c r="J670" t="inlineStr">
+        <is>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="L670" t="inlineStr">
+        <is>
+          <t>Mesmo material/impressão da versão Auchan (vinil de chão 3M, offset 4/0). Sem passatempos/jogos de sorte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>Alarm Walk — Pingo Doce</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>600x100, 400x100, 250x100 ou 180x100 cms; margem branco 1 cm</t>
+        </is>
+      </c>
+      <c r="J671" t="inlineStr">
+        <is>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="L671" t="inlineStr">
+        <is>
+          <t>Mesmo material/impressão das restantes. Tem uma variante de tamanho extra (180x100) face a Auchan/Continente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>Cart Media — Continente</t>
+        </is>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>Tamanho total 32,2x69 cms; área visível 32,2x30,5 cms (frente e verso)</t>
+        </is>
+      </c>
+      <c r="J672" t="inlineStr">
+        <is>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="L672" t="inlineStr">
+        <is>
+          <t>Material: polipropileno branco 0,5mm (PVC) 200 microns; offset UV 4/0 + verniz UV brilho. Cantos arredondados; criatividade em português.</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>Floor Media — Auchan</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>120x90 cms; margem branco 1 cm</t>
+        </is>
+      </c>
+      <c r="J673" t="inlineStr">
+        <is>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="L673" t="inlineStr">
+        <is>
+          <t>Material: vinil de chão autocolante opaco 3M, lâmina antideslizante MSM; offset 4/0. Incluir logo ISM; sem passatempos/jogos de sorte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>Floor Media 120x90 — El Corte Inglês</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>120x90 cms; margem branco 1 cm</t>
+        </is>
+      </c>
+      <c r="J674" t="inlineStr">
+        <is>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="L674" t="inlineStr">
+        <is>
+          <t>Mesmas especificações de material/impressão da versão Auchan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>Floor Media 90x60 — Continente</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>90x60 cms; margem branco 1 cm</t>
+        </is>
+      </c>
+      <c r="J675" t="inlineStr">
+        <is>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="L675" t="inlineStr">
+        <is>
+          <t>Mesma produção/material das restantes Floor Media.</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>Floor Media XXL — Continente</t>
+        </is>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>200x100 cms; margem branco 1 cm</t>
+        </is>
+      </c>
+      <c r="J676" t="inlineStr">
+        <is>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="L676" t="inlineStr">
+        <is>
+          <t>Material: vinil de chão autocolante opaco 3M; offset 4/0. Incluir logo ISM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>Floor Media — Pingo Doce</t>
+        </is>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>120x90 cms (Hipermercados) ou 90x60 cms (Supermercados); margem branco 1 cm</t>
+        </is>
+      </c>
+      <c r="J677" t="inlineStr">
+        <is>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="L677" t="inlineStr">
+        <is>
+          <t>Vinil de chão autocolante opaco 3M, lâmina antideslizante; offset 4/0. Incluir logo ISM; cantos arredondados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>Frame Media Congelados</t>
+        </is>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>7 tiras de 7x100cm (área total 7cm x várias metragens, depende do perímetro da arca)</t>
+        </is>
+      </c>
+      <c r="J678" t="inlineStr">
+        <is>
+          <t>Adobe Illustrator (aberto, sem bleed); CMYK; resolução mín. 150 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="L678" t="inlineStr">
+        <is>
+          <t>Material: vinil removível, digital 4/0. Criatividade contínua nas tiras (perímetros não uniformes, pode requerer corte). Recomenda-se só logo ou imagem do produto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>Sticker Freezer</t>
+        </is>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>16x16 cms</t>
+        </is>
+      </c>
+      <c r="J679" t="inlineStr">
+        <is>
+          <t>Adobe Illustrator (aberto, sem bleed); CMYK; resolução mín. 150 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="L679" t="inlineStr">
+        <is>
+          <t>Material: vinil removível, digital 4/0. Criatividade contínua nas tiras (arcas não uniformes, pode requerer corte). Entrega: 1 mês antes para validação, 2 semanas antes para AF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>Live Markets — Auchan</t>
+        </is>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>1080x1920 px</t>
+        </is>
+      </c>
+      <c r="I680" t="inlineStr">
+        <is>
+          <t>Máx. 25 MB</t>
+        </is>
+      </c>
+      <c r="J680" t="inlineStr">
+        <is>
+          <t>WMV ou MP4, sem áudio</t>
+        </is>
+      </c>
+      <c r="L680" t="inlineStr">
+        <is>
+          <t>Duração 10 seg. Emissão só após validação ISM; entrega até 5 dias antes do início da campanha.</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>Live Markets — Continente</t>
+        </is>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>LCDs Samsung 65"; 1080x1920 px</t>
+        </is>
+      </c>
+      <c r="I681" t="inlineStr">
+        <is>
+          <t>Máx. 25 MB</t>
+        </is>
+      </c>
+      <c r="J681" t="inlineStr">
+        <is>
+          <t>MP4, codec H264, 25 fps, sem áudio</t>
+        </is>
+      </c>
+      <c r="L681" t="inlineStr">
+        <is>
+          <t>Duração 10 seg. Criatividade em português. Entrega: 15 dias antes do início da campanha.</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>Live Markets — E.Leclerc</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>LCDs 55"; 720x1280 px</t>
+        </is>
+      </c>
+      <c r="I682" t="inlineStr">
+        <is>
+          <t>Máx. 25 MB; vídeo &lt; 4000 kbps</t>
+        </is>
+      </c>
+      <c r="J682" t="inlineStr">
+        <is>
+          <t>AVI, MOV ou MP4, 25 fps, sem áudio</t>
+        </is>
+      </c>
+      <c r="L682" t="inlineStr">
+        <is>
+          <t>Duração 10 seg. Resolução/ecrã diferentes das restantes Live Markets (720x1280 vs. 1080x1920). Entrega: 15 dias antes do início da campanha.</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>Live Markets — Pingo Doce</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>1080x1920, 1080x1634, 1080x1374, 1355x1080, 1355x982 ou 1920x1080 px</t>
+        </is>
+      </c>
+      <c r="I683" t="inlineStr">
+        <is>
+          <t>Máx. 25 MB</t>
+        </is>
+      </c>
+      <c r="J683" t="inlineStr">
+        <is>
+          <t>MP4, codec H264, 25 fps, sem áudio</t>
+        </is>
+      </c>
+      <c r="L683" t="inlineStr">
+        <is>
+          <t>Duração 10 seg. Conteúdo deve ser animado (não estático). LCDs Samsung. Entrega: 15 dias antes do início da campanha.</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>Live Matosinhos — Continente</t>
+        </is>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>Painel físico 5,76x4,8m; resolução 1008x576 px</t>
+        </is>
+      </c>
+      <c r="I684" t="inlineStr">
+        <is>
+          <t>Máx. 25 MB</t>
+        </is>
+      </c>
+      <c r="J684" t="inlineStr">
+        <is>
+          <t>MP4, codec H264, 25 fps, sem áudio</t>
+        </is>
+      </c>
+      <c r="L684" t="inlineStr">
+        <is>
+          <t>Duração 10 seg. Écran exterior/totem de grande formato em localização específica (Matosinhos). Entrega: 15 dias antes do início da campanha.</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>Mupis Digitais — Pingo Doce</t>
+        </is>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>1080x1920, 1080x1634, 1080x1374, 1355x1080, 1355x982 ou 1920x1080 px</t>
+        </is>
+      </c>
+      <c r="I685" t="inlineStr">
+        <is>
+          <t>Máx. 25 MB</t>
+        </is>
+      </c>
+      <c r="J685" t="inlineStr">
+        <is>
+          <t>MP4, codec H264, 25 fps, sem áudio</t>
+        </is>
+      </c>
+      <c r="L685" t="inlineStr">
+        <is>
+          <t>Duração 10 seg. Entrega: 15 dias antes do início da campanha.</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>Mupi (retroiluminado) — Pingo Doce</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>Tamanho total 120x176 cm; área visível 107x159 cms</t>
+        </is>
+      </c>
+      <c r="J686" t="inlineStr">
+        <is>
+          <t>Resolução 300 DPI, escala real 1:1</t>
+        </is>
+      </c>
+      <c r="L686" t="inlineStr">
+        <is>
+          <t>Material: papel especial para luz, 135 gr (mupi retroiluminado físico, distinto do digital). Arte Final em português.</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>Digital Mupis — Auchan</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>1080x1920 px</t>
+        </is>
+      </c>
+      <c r="J687" t="inlineStr">
+        <is>
+          <t>WMV ou MP4</t>
+        </is>
+      </c>
+      <c r="L687" t="inlineStr">
+        <is>
+          <t>Duração 10 seg. Filme em português ou legendado/traduzido. Entrega 5 dias antes; emissão só após validação ISM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>Passadeira Vinil</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>Total 16mts; módulos centrais 100x200cm (x7); módulos início/fim 100x100cm (x2)</t>
+        </is>
+      </c>
+      <c r="J688" t="inlineStr">
+        <is>
+          <t>Resolução 300 DPI, escala real 1:1</t>
+        </is>
+      </c>
+      <c r="L688" t="inlineStr">
+        <is>
+          <t>Material: vinil de chão removível com lâmina antideslizante; digital 4/0. Imagens início/fim iguais entre si (idem para as centrais); não usar fundo branco nem preto; incluir logo ISM no início e fim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>Stopper Digital</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>Ecrã LCD 15"; 1080x1920 px</t>
+        </is>
+      </c>
+      <c r="I689" t="inlineStr">
+        <is>
+          <t>Máx. 25 MB</t>
+        </is>
+      </c>
+      <c r="J689" t="inlineStr">
+        <is>
+          <t>MP4, codec H264, 25 fps, sem áudio</t>
+        </is>
+      </c>
+      <c r="L689" t="inlineStr">
+        <is>
+          <t>Duração 10 seg. Entrega: 15 dias antes do início da campanha.</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>Stopper-Media Max</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>Área total 20,4x40,4 cms; área visível 19,2x39,2 cms; sangria 1,2 cms</t>
+        </is>
+      </c>
+      <c r="J690" t="inlineStr">
+        <is>
+          <t>Qualquer formato suportado pelo Adobe; resolução 1080 DPI à escala real, 300 microns</t>
+        </is>
+      </c>
+      <c r="L690" t="inlineStr">
+        <is>
+          <t>Material: PVC eco branco/mate; digital 4/0. Evitar textos/logos/numeração perto do corte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>Stopper-Media Max XXL</t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>Área total 60,4x20,4 cms; área visível 59,2x19,2 cms; sangria 1,2 cms</t>
+        </is>
+      </c>
+      <c r="J691" t="inlineStr">
+        <is>
+          <t>Qualquer formato suportado pelo Adobe; resolução 1080 DPI à escala real, 300 microns</t>
+        </is>
+      </c>
+      <c r="L691" t="inlineStr">
+        <is>
+          <t>Material: PVC eco branco/mate; digital 4/0. Mesmas recomendações de corte que o Stopper-Media Max (tamanho normal).</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>Stopper Media LED 200x800</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>Tamanho total 221x800mm; área visível 200x800mm; raio de canto R=40mm</t>
+        </is>
+      </c>
+      <c r="J692" t="inlineStr">
+        <is>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução 1080 DPI à escala real, 300 microns</t>
+        </is>
+      </c>
+      <c r="L692" t="inlineStr">
+        <is>
+          <t>Material: PMMA gravado (Easydot); digital 4/4. Saída de cabo na zona superior; pinça única com peças 3D. Evitar elementos perto do corte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>Top Banner (FMCG)</t>
+        </is>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>768x216 px</t>
+        </is>
+      </c>
+      <c r="I693" t="inlineStr">
+        <is>
+          <t>Máx. 25 MB</t>
+        </is>
+      </c>
+      <c r="J693" t="inlineStr">
+        <is>
+          <t>MP4, codec H264, sem áudio</t>
+        </is>
+      </c>
+      <c r="L693" t="inlineStr">
+        <is>
+          <t>Duração 10 seg. Bitrate recomendado 10 Mbps. Entrega 5 dias antes; emissão só após validação ISM. Formato genérico, sem retalhista específico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>Mupi Papel — El Corte Inglês</t>
+        </is>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>Tamanho total 120x176 cms; área visível 107x159 cms</t>
+        </is>
+      </c>
+      <c r="J694" t="inlineStr">
+        <is>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="L694" t="inlineStr">
+        <is>
+          <t>Material: papel especial para luz, 135 gr; impressão quadricromia, Offset ou Digital. Criatividade em português. Entrega: 10 dias antes do início da campanha.</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>Elevadores — El Corte Inglês Gaia</t>
+        </is>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>Portas exteriores: largura total 99,5cm (2 painéis de 38,5cm + faixas de 5/7,5cm); altura total 209,5cm (área útil 194,5cm). Loja: 13 pisos x 3 elevadores = 39 faces.</t>
+        </is>
+      </c>
+      <c r="L695" t="inlineStr">
+        <is>
+          <t>Documento disponível é só de logística de instalação, não uma ficha técnica de produção completa — sem resolução, DPI, formato de ficheiro, peso máximo ou prazo de entrega indicados. Opções de corte do vinil: (1) criatividade única cortada em 2 partes; (2) duas criatividades separadas, uma por porta; (3) criatividade com friso central incluído. Confirmar specs de produção com a In-Store Media antes de fechar o pedido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>Mupis Digitais — El Corte Inglês</t>
+        </is>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>1080x1920 px</t>
+        </is>
+      </c>
+      <c r="I696" t="inlineStr">
+        <is>
+          <t>Máx. 25 MB</t>
+        </is>
+      </c>
+      <c r="J696" t="inlineStr">
+        <is>
+          <t>MP4 ou WMV, codec H264, sem áudio</t>
+        </is>
+      </c>
+      <c r="L696" t="inlineStr">
+        <is>
+          <t>Duração 10 seg. Material: ecrã LED; criatividade em português. Entrega: 15 dias antes do início da campanha. Nota: um dos documentos de origem indicava a nomenclatura de ficheiro "1060X3840", que não bate com a resolução declarada (1080x1920) — reportado tal como consta, sem correção.</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>Hall Media Digital — El Corte Inglês</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>666x1920 px</t>
+        </is>
+      </c>
+      <c r="I697" t="inlineStr">
+        <is>
+          <t>Máx. 25 MB</t>
+        </is>
+      </c>
+      <c r="J697" t="inlineStr">
+        <is>
+          <t>MP4, codec H264, 25 fps</t>
+        </is>
+      </c>
+      <c r="L697" t="inlineStr">
+        <is>
+          <t>Duração 10 seg. Bitrate recomendado 10 Mbps. Nomenclatura: "Anunciante"-HALL-666X1920.mp4. Criatividade em português, sem áudio. Entrega: 15 dias antes do início da campanha.</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>Live Markets (Circuito Digital) — El Corte Inglês Lisboa</t>
+        </is>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>Ecrã 42"; 1920x1080 px</t>
+        </is>
+      </c>
+      <c r="I698" t="inlineStr">
+        <is>
+          <t>Máx. 25 MB (produzido pelo cliente)</t>
+        </is>
+      </c>
+      <c r="J698" t="inlineStr">
+        <is>
+          <t>WMV ou MP4 (cliente); PSD/AI/INDD/PDF, imagens &gt;150dpi, texto em curvas (produção ISM)</t>
+        </is>
+      </c>
+      <c r="L698" t="inlineStr">
+        <is>
+          <t>Duração 8 a 10 seg (produzido pelo cliente). Emissão só após validação da criatividade pela ISM. Produção ISM: entrega 13 dias antes. Produzido pelo cliente: entrega 5 dias antes. Criatividade em português.</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>Live Markets (Circuito Digital) — El Corte Inglês Gaia</t>
+        </is>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>Ecrã 55"; 1920x1080 px</t>
+        </is>
+      </c>
+      <c r="I699" t="inlineStr">
+        <is>
+          <t>Máx. 25 MB (produzido pelo cliente)</t>
+        </is>
+      </c>
+      <c r="J699" t="inlineStr">
+        <is>
+          <t>WMV ou MP4 (cliente); PSD/AI/INDD/PDF, imagens &gt;150dpi, texto em curvas (produção ISM)</t>
+        </is>
+      </c>
+      <c r="L699" t="inlineStr">
+        <is>
+          <t>Duração 8 a 10 seg (produzido pelo cliente). Emissão só após validação da criatividade pela ISM. Produção ISM: entrega 13 dias antes. Produzido pelo cliente: entrega 5 dias antes. Criatividade em português.</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>Stairs Backlights — El Corte Inglês (Espanha)</t>
+        </is>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>78x108 cms</t>
+        </is>
+      </c>
+      <c r="J700" t="inlineStr">
+        <is>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:5 + 0,5cm de sangria</t>
+        </is>
+      </c>
+      <c r="L700" t="inlineStr">
+        <is>
+          <t>Material: white back paper 150 grs, corte simples; offset 4/0. Criatividade em português. Entrega: 10 dias antes do início da campanha. Atenção: o documento identifica o mercado como "In-Store Media España" — confirmar se este formato se aplica às lojas portuguesas (Gaia/Lisboa) ou se é exclusivo de Espanha antes de o usar num pedido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>Elevadores — El Corte Inglês Lisboa</t>
+        </is>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>150x220 cms</t>
+        </is>
+      </c>
+      <c r="J701" t="inlineStr">
+        <is>
+          <t>Freehand, Adobe Illustrator ou Corel Draw (paginação); PSD aceite com layers separados e AFs em aberto; CMYK (enviar pantones); resolução mín. 720 DPI à escala 1:10 ou 72 DPI à escala real</t>
+        </is>
+      </c>
+      <c r="L701" t="inlineStr">
+        <is>
+          <t>Material: vinil monomérico com brilho, adesivo removível; impressão tintas low solvent 720 DPI + laminação brilho. Textos convertidos em vetorial. Criatividade em português. Entrega: 10 dias antes do início da campanha.</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>Montra Digital — El Corte Inglês Gaia</t>
+        </is>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>1248x2212 px</t>
+        </is>
+      </c>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>Máx. 25 MB</t>
+        </is>
+      </c>
+      <c r="J702" t="inlineStr">
+        <is>
+          <t>MP4, codec H264, 25 fps</t>
+        </is>
+      </c>
+      <c r="L702" t="inlineStr">
+        <is>
+          <t>Duração 10 seg. Bitrate recomendado 10 Mbps. Nomenclatura: "Anunciante"-MONTRA.GAIA-1248X2212.mp4. Sem áudio, criatividade em português. Entrega: 15 dias antes do início da campanha.</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>Lona Gigante Digital — El Corte Inglês Lisboa</t>
+        </is>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>Ecrã físico 18,7x10,6m; resolução 1920x1080 px</t>
+        </is>
+      </c>
+      <c r="I703" t="inlineStr">
+        <is>
+          <t>Máx. 25 MB</t>
+        </is>
+      </c>
+      <c r="J703" t="inlineStr">
+        <is>
+          <t>WMV ou MP4, codec H264, 25 fps</t>
+        </is>
+      </c>
+      <c r="L703" t="inlineStr">
+        <is>
+          <t>Duração 10 seg. Material: ecrã LED de 198m². Sem áudio, criatividade em português. Entrega: 15 dias antes do início da campanha.</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>Banners de Exterior — El Corte Inglês</t>
+        </is>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>100x300 cms</t>
+        </is>
+      </c>
+      <c r="J704" t="inlineStr">
+        <is>
+          <t>Adobe Illustrator (AI); resolução mín. 300 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="L704" t="inlineStr">
+        <is>
+          <t>Material: tela blockout com ilhoses; impressão tintas UV ou low solvents. Evitar mensagens nos extremos. Criatividade em português. Entrega: 15 dias antes do início da campanha.</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>Montra Digital — El Corte Inglês Lisboa</t>
+        </is>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>Ecrã físico 400x450cm; resolução 1600x1800 px</t>
+        </is>
+      </c>
+      <c r="I705" t="inlineStr">
+        <is>
+          <t>Máx. 25 MB</t>
+        </is>
+      </c>
+      <c r="J705" t="inlineStr">
+        <is>
+          <t>MP4, codec H264, 25 fps</t>
+        </is>
+      </c>
+      <c r="L705" t="inlineStr">
+        <is>
+          <t>Duração 10 seg. Bitrate recomendado 10 Mbps. Nomenclatura: "Anunciante"-MONTRA.LISBOA-1600X1800.mp4. Sem áudio, criatividade em português. Entrega: 15 dias antes do início da campanha.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M705"/>
+  <dimension ref="A1:M710"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32850,6 +32850,216 @@
         </is>
       </c>
     </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>CSOutdoors</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>CSOutdoors</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>Outdoor 21x5</t>
+        </is>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>Área de impressão: 21x5m (escala 1:10, 210x50cm). Área de conteúdo relevante: 20,60x4,70m.</t>
+        </is>
+      </c>
+      <c r="J706" t="inlineStr">
+        <is>
+          <t>PDF, JPG, TIF, CDR ou AI</t>
+        </is>
+      </c>
+      <c r="L706" t="inlineStr">
+        <is>
+          <t>Imagem à escala 1:10. Resolução recomendada: 300dpi. Ficheiro em CMYK. Enviar fontes ou converter textos em curvas. Incluir um JPG para visualização. Enviar por email, pen ou CD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>CSOutdoors</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>CSOutdoors</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>Outdoor 32x5</t>
+        </is>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>Área de impressão: 32,12x5,04m (escala 1:10, 321,2x50,4cm). Área de conteúdo relevante: 31,8x4,8m.</t>
+        </is>
+      </c>
+      <c r="J707" t="inlineStr">
+        <is>
+          <t>PDF, JPG, TIF, CDR ou AI</t>
+        </is>
+      </c>
+      <c r="L707" t="inlineStr">
+        <is>
+          <t>Imagem à escala 1:10. Resolução recomendada: 300dpi. Ficheiro em CMYK. Enviar fontes ou converter textos em curvas. Incluir um JPG para visualização. Enviar por email, pen ou CD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>CSOutdoors</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>CSOutdoors</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>8x3 Premium</t>
+        </is>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>Área de impressão: 8,35x3m (escala 1:10, 83,5x30cm). Área de conteúdo relevante: 8,15x2,80m.</t>
+        </is>
+      </c>
+      <c r="J708" t="inlineStr">
+        <is>
+          <t>PDF, JPG, TIF, CDR ou AI</t>
+        </is>
+      </c>
+      <c r="L708" t="inlineStr">
+        <is>
+          <t>Imagem à escala 1:10. Resolução recomendada: 300dpi. Ficheiro em CMYK. Enviar fontes ou converter textos em curvas. Incluir um JPG para visualização. Enviar por email, pen ou CD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>CSOutdoors</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>CSOutdoors</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>Monoposte 10x5</t>
+        </is>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>Área de impressão: 10x5m (escala 1:10, 100x50cm). Área de conteúdo relevante: 9,80x4,80m.</t>
+        </is>
+      </c>
+      <c r="J709" t="inlineStr">
+        <is>
+          <t>PDF, JPG, TIF, CDR ou AI</t>
+        </is>
+      </c>
+      <c r="L709" t="inlineStr">
+        <is>
+          <t>Imagem à escala 1:10. Resolução recomendada: 300dpi. Ficheiro em CMYK. Enviar fontes ou converter textos em curvas. Incluir um JPG para visualização. Enviar por email, pen ou CD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>CSOutdoors</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>CSOutdoors</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>Outdoor 4x3</t>
+        </is>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>Área de impressão: 4x3m (escala 1:10, 40x30cm). Área de conteúdo relevante: 3,80x2,80m.</t>
+        </is>
+      </c>
+      <c r="J710" t="inlineStr">
+        <is>
+          <t>PDF, JPG, TIF, CDR ou AI</t>
+        </is>
+      </c>
+      <c r="L710" t="inlineStr">
+        <is>
+          <t>Imagem à escala 1:10. Resolução recomendada: 300dpi. Ficheiro em CMYK. Enviar fontes ou converter textos em curvas. Incluir um JPG para visualização. Enviar por email, pen ou CD.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M710"/>
+  <dimension ref="A1:M717"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28022,27 +28022,27 @@
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>Ogury</t>
+          <t>Outlook</t>
         </is>
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>Ogury</t>
+          <t>Outlook</t>
         </is>
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>Standard Banners</t>
+          <t>Native Ads</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>1388x1734, 720x540, 2640x600, 1760x400 ou 300x250</t>
+          <t>Logo da marca: 100x100. Imagem: 1200x627 ou 627x627.</t>
         </is>
       </c>
       <c r="I603" t="inlineStr">
         <is>
-          <t>Máx. 100 KB</t>
+          <t>Máx. 120 KB</t>
         </is>
       </c>
       <c r="J603" t="inlineStr">
@@ -28052,101 +28052,101 @@
       </c>
       <c r="L603" t="inlineStr">
         <is>
-          <t>Ver no link as safe zones e danger zones.</t>
-        </is>
-      </c>
-      <c r="M603" t="inlineStr">
-        <is>
-          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/display-studio</t>
+          <t>Short Headline (x2): máx. 30 carateres. Long Headline: máx. 90 carateres. Descrição: máx. 90 carateres. Business/Brand Name: máx. 25 carateres.</t>
         </is>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>INTERNET</t>
+          <t>PROGRAMÁTICO</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Programático</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>Outlook</t>
+          <t>Open AI</t>
         </is>
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>Outlook</t>
+          <t>Open AI</t>
         </is>
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>Native Ads</t>
+          <t>ChatGPT</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>Logo da marca: 100x100. Imagem: 1200x627 ou 627x627.</t>
-        </is>
-      </c>
-      <c r="I604" t="inlineStr">
-        <is>
-          <t>Máx. 120 KB</t>
+          <t>1200x1200</t>
         </is>
       </c>
       <c r="J604" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF</t>
+          <t>JPG, PNG</t>
         </is>
       </c>
       <c r="L604" t="inlineStr">
         <is>
-          <t>Short Headline (x2): máx. 30 carateres. Long Headline: máx. 90 carateres. Descrição: máx. 90 carateres. Business/Brand Name: máx. 25 carateres.</t>
+          <t>Título: máx. 50 carateres (recomendado 16-24). Descrição: máx. 100 carateres (recomendado 32-48).</t>
         </is>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>Open AI</t>
+          <t>OLX</t>
         </is>
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>Open AI</t>
+          <t>OLX</t>
         </is>
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Virtual Category (Icon) - Homepage</t>
         </is>
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>1200x1200</t>
+          <t>100x100</t>
+        </is>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
         </is>
       </c>
       <c r="J605" t="inlineStr">
         <is>
-          <t>JPG, PNG</t>
+          <t>JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="L605" t="inlineStr">
         <is>
-          <t>Título: máx. 50 carateres (recomendado 16-24). Descrição: máx. 100 carateres (recomendado 32-48).</t>
+          <t>Posição: Homepage (Desktop). Texto/Copy: máx. 30 carateres.</t>
+        </is>
+      </c>
+      <c r="M605" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
         </is>
       </c>
     </row>
@@ -28173,12 +28173,12 @@
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>Virtual Category (Icon) - Homepage</t>
+          <t>Screening (Takeover) - Homepage</t>
         </is>
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>100x100</t>
+          <t>1920x1100</t>
         </is>
       </c>
       <c r="I606" t="inlineStr">
@@ -28193,7 +28193,7 @@
       </c>
       <c r="L606" t="inlineStr">
         <is>
-          <t>Posição: Homepage (Desktop). Texto/Copy: máx. 30 carateres.</t>
+          <t>Posição: Homepage (Desktop). São necessárias duas versões para o Screening (Takeover). Ter atenção às áreas visíveis (Safe Zones). Existe template para download no site de specs.</t>
         </is>
       </c>
       <c r="M606" t="inlineStr">
@@ -28225,7 +28225,7 @@
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>Screening (Takeover) - Homepage</t>
+          <t>Screening (Takeover) - Listing Page</t>
         </is>
       </c>
       <c r="G607" t="inlineStr">
@@ -28245,7 +28245,7 @@
       </c>
       <c r="L607" t="inlineStr">
         <is>
-          <t>Posição: Homepage (Desktop). São necessárias duas versões para o Screening (Takeover). Ter atenção às áreas visíveis (Safe Zones). Existe template para download no site de specs.</t>
+          <t>Posição: Listing Page (Desktop). São necessárias duas versões para o Screening (Takeover). Ter atenção às áreas visíveis (Safe Zones). Existe template para download no site de specs.</t>
         </is>
       </c>
       <c r="M607" t="inlineStr">
@@ -28277,12 +28277,12 @@
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>Screening (Takeover) - Listing Page</t>
+          <t>Full Branding - Homepage</t>
         </is>
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>1920x1100</t>
+          <t>2x 1920x1100, 4x 270x190</t>
         </is>
       </c>
       <c r="I608" t="inlineStr">
@@ -28297,7 +28297,7 @@
       </c>
       <c r="L608" t="inlineStr">
         <is>
-          <t>Posição: Listing Page (Desktop). São necessárias duas versões para o Screening (Takeover). Ter atenção às áreas visíveis (Safe Zones). Existe template para download no site de specs.</t>
+          <t>Posição: Homepage (Desktop). São necessárias duas versões para o Screening (Takeover). Ter atenção às áreas visíveis (Safe Zones). Título Principal: máx. 20 carateres. Título: máx. 18 carateres. Descrição: máx. 25 carateres. Existe template para download no site de specs.</t>
         </is>
       </c>
       <c r="M608" t="inlineStr">
@@ -28329,12 +28329,12 @@
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>Full Branding - Homepage</t>
+          <t>Full Branding - Listing</t>
         </is>
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>2x 1920x1100, 4x 270x190</t>
+          <t>2x 1920x1100, 4x 270x190, 1x 1237x300, 1x 1029x300</t>
         </is>
       </c>
       <c r="I609" t="inlineStr">
@@ -28349,7 +28349,7 @@
       </c>
       <c r="L609" t="inlineStr">
         <is>
-          <t>Posição: Homepage (Desktop). São necessárias duas versões para o Screening (Takeover). Ter atenção às áreas visíveis (Safe Zones). Título Principal: máx. 20 carateres. Título: máx. 18 carateres. Descrição: máx. 25 carateres. Existe template para download no site de specs.</t>
+          <t>Posição: Listing Page (Desktop). São necessárias duas versões para o Screening (Takeover). Ter atenção às áreas visíveis (Safe Zones). Título Principal: máx. 20 carateres. Título: máx. 18 carateres. Descrição: máx. 25 carateres. Existe template para download no site de specs.</t>
         </is>
       </c>
       <c r="M609" t="inlineStr">
@@ -28381,12 +28381,12 @@
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>Full Branding - Listing</t>
+          <t>My Account</t>
         </is>
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>2x 1920x1100, 4x 270x190, 1x 1237x300, 1x 1029x300</t>
+          <t>890x70</t>
         </is>
       </c>
       <c r="I610" t="inlineStr">
@@ -28396,12 +28396,12 @@
       </c>
       <c r="J610" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF</t>
+          <t>JPG, PNG, GIF ou HTML5</t>
         </is>
       </c>
       <c r="L610" t="inlineStr">
         <is>
-          <t>Posição: Listing Page (Desktop). São necessárias duas versões para o Screening (Takeover). Ter atenção às áreas visíveis (Safe Zones). Título Principal: máx. 20 carateres. Título: máx. 18 carateres. Descrição: máx. 25 carateres. Existe template para download no site de specs.</t>
+          <t>Posição: My Account Page (Desktop).</t>
         </is>
       </c>
       <c r="M610" t="inlineStr">
@@ -28433,12 +28433,12 @@
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>My Account</t>
+          <t>Megaboard (Topboard)</t>
         </is>
       </c>
       <c r="G611" t="inlineStr">
         <is>
-          <t>890x70</t>
+          <t>1920x300</t>
         </is>
       </c>
       <c r="I611" t="inlineStr">
@@ -28453,7 +28453,7 @@
       </c>
       <c r="L611" t="inlineStr">
         <is>
-          <t>Posição: My Account Page (Desktop).</t>
+          <t>Posição: Listing Page &amp; Ad Page (Desktop). Ter atenção às áreas visíveis (Safe Zones). Existe template para download no site de specs.</t>
         </is>
       </c>
       <c r="M611" t="inlineStr">
@@ -28485,12 +28485,12 @@
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>Megaboard (Topboard)</t>
+          <t>Skyscraper</t>
         </is>
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>1920x300</t>
+          <t>160x600</t>
         </is>
       </c>
       <c r="I612" t="inlineStr">
@@ -28505,7 +28505,7 @@
       </c>
       <c r="L612" t="inlineStr">
         <is>
-          <t>Posição: Listing Page &amp; Ad Page (Desktop). Ter atenção às áreas visíveis (Safe Zones). Existe template para download no site de specs.</t>
+          <t>Posição: Listing Page (Desktop).</t>
         </is>
       </c>
       <c r="M612" t="inlineStr">
@@ -28537,12 +28537,12 @@
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>Skyscraper</t>
+          <t>Rectangle (MREC)</t>
         </is>
       </c>
       <c r="G613" t="inlineStr">
         <is>
-          <t>160x600</t>
+          <t>300x250</t>
         </is>
       </c>
       <c r="I613" t="inlineStr">
@@ -28557,7 +28557,7 @@
       </c>
       <c r="L613" t="inlineStr">
         <is>
-          <t>Posição: Listing Page (Desktop).</t>
+          <t>Posição: Ad Page &amp; Gallery Page (Desktop).</t>
         </is>
       </c>
       <c r="M613" t="inlineStr">
@@ -28589,12 +28589,12 @@
       </c>
       <c r="F614" t="inlineStr">
         <is>
-          <t>Rectangle (MREC)</t>
+          <t>Billboard</t>
         </is>
       </c>
       <c r="G614" t="inlineStr">
         <is>
-          <t>300x250</t>
+          <t>970x250</t>
         </is>
       </c>
       <c r="I614" t="inlineStr">
@@ -28609,7 +28609,7 @@
       </c>
       <c r="L614" t="inlineStr">
         <is>
-          <t>Posição: Ad Page &amp; Gallery Page (Desktop).</t>
+          <t>Posição: várias páginas — Listing Page, Ad Page, Seller Page, Observed Ads (Desktop).</t>
         </is>
       </c>
       <c r="M614" t="inlineStr">
@@ -28641,12 +28641,12 @@
       </c>
       <c r="F615" t="inlineStr">
         <is>
-          <t>Billboard</t>
+          <t>Native (In Feed)</t>
         </is>
       </c>
       <c r="G615" t="inlineStr">
         <is>
-          <t>970x250</t>
+          <t>210x150</t>
         </is>
       </c>
       <c r="I615" t="inlineStr">
@@ -28656,12 +28656,12 @@
       </c>
       <c r="J615" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF ou HTML5</t>
+          <t>JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="L615" t="inlineStr">
         <is>
-          <t>Posição: várias páginas — Listing Page, Ad Page, Seller Page, Observed Ads (Desktop).</t>
+          <t>Posição: Listing Page (Desktop). Título: máx. 45 carateres. CTA: máx. 10 carateres.</t>
         </is>
       </c>
       <c r="M615" t="inlineStr">
@@ -28693,27 +28693,27 @@
       </c>
       <c r="F616" t="inlineStr">
         <is>
-          <t>Native (In Feed)</t>
+          <t>Text Link / Brand Link</t>
         </is>
       </c>
       <c r="G616" t="inlineStr">
         <is>
-          <t>210x150</t>
+          <t>Logo: 80x80 (opcional)</t>
         </is>
       </c>
       <c r="I616" t="inlineStr">
         <is>
-          <t>Máx. 1 MB</t>
+          <t>Máx. 1 MB (apenas se incluir logo)</t>
         </is>
       </c>
       <c r="J616" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF</t>
+          <t>JPG, PNG ou GIF (apenas se incluir logo)</t>
         </is>
       </c>
       <c r="L616" t="inlineStr">
         <is>
-          <t>Posição: Listing Page (Desktop). Título: máx. 45 carateres. CTA: máx. 10 carateres.</t>
+          <t>Posição: Ad Page (Desktop). Texto/Copy: máx. 40 carateres.</t>
         </is>
       </c>
       <c r="M616" t="inlineStr">
@@ -28745,27 +28745,32 @@
       </c>
       <c r="F617" t="inlineStr">
         <is>
-          <t>Text Link / Brand Link</t>
+          <t>Video Outstream</t>
         </is>
       </c>
       <c r="G617" t="inlineStr">
         <is>
-          <t>Logo: 80x80 (opcional)</t>
+          <t>1920x1080</t>
+        </is>
+      </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I617" t="inlineStr">
         <is>
-          <t>Máx. 1 MB (apenas se incluir logo)</t>
+          <t>Máx. 10 MB</t>
         </is>
       </c>
       <c r="J617" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF (apenas se incluir logo)</t>
+          <t>MP4, até 30 segundos</t>
         </is>
       </c>
       <c r="L617" t="inlineStr">
         <is>
-          <t>Posição: Ad Page (Desktop). Texto/Copy: máx. 40 carateres.</t>
+          <t>Posição: Listing Page &amp; Ad Page (Desktop).</t>
         </is>
       </c>
       <c r="M617" t="inlineStr">
@@ -28797,32 +28802,27 @@
       </c>
       <c r="F618" t="inlineStr">
         <is>
-          <t>Video Outstream</t>
+          <t>TopMobileBoard (Leaderboard)</t>
         </is>
       </c>
       <c r="G618" t="inlineStr">
         <is>
-          <t>1920x1080</t>
-        </is>
-      </c>
-      <c r="H618" t="inlineStr">
-        <is>
-          <t>16:9</t>
+          <t>300x100 ou 320x100</t>
         </is>
       </c>
       <c r="I618" t="inlineStr">
         <is>
-          <t>Máx. 10 MB</t>
+          <t>Máx. 1 MB</t>
         </is>
       </c>
       <c r="J618" t="inlineStr">
         <is>
-          <t>MP4, até 30 segundos</t>
+          <t>JPG, PNG, GIF ou HTML5</t>
         </is>
       </c>
       <c r="L618" t="inlineStr">
         <is>
-          <t>Posição: Listing Page &amp; Ad Page (Desktop).</t>
+          <t>Posição: Homepage (Mobile).</t>
         </is>
       </c>
       <c r="M618" t="inlineStr">
@@ -28854,12 +28854,12 @@
       </c>
       <c r="F619" t="inlineStr">
         <is>
-          <t>TopMobileBoard (Leaderboard)</t>
+          <t>Virtual Category (Icon) - Homepage (Mobile)</t>
         </is>
       </c>
       <c r="G619" t="inlineStr">
         <is>
-          <t>300x100 ou 320x100</t>
+          <t>80x83</t>
         </is>
       </c>
       <c r="I619" t="inlineStr">
@@ -28869,12 +28869,12 @@
       </c>
       <c r="J619" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF ou HTML5</t>
+          <t>JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="L619" t="inlineStr">
         <is>
-          <t>Posição: Homepage (Mobile).</t>
+          <t>Posição: Homepage (Mobile). Texto/Copy: máx. 10 carateres.</t>
         </is>
       </c>
       <c r="M619" t="inlineStr">
@@ -28906,12 +28906,12 @@
       </c>
       <c r="F620" t="inlineStr">
         <is>
-          <t>Virtual Category (Icon) - Homepage (Mobile)</t>
+          <t>TopMobileBoard (Anchor)</t>
         </is>
       </c>
       <c r="G620" t="inlineStr">
         <is>
-          <t>80x83</t>
+          <t>600x200</t>
         </is>
       </c>
       <c r="I620" t="inlineStr">
@@ -28921,12 +28921,12 @@
       </c>
       <c r="J620" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF</t>
+          <t>JPG, PNG, GIF ou HTML5</t>
         </is>
       </c>
       <c r="L620" t="inlineStr">
         <is>
-          <t>Posição: Homepage (Mobile). Texto/Copy: máx. 10 carateres.</t>
+          <t>Posição: Listing Page (Mobile).</t>
         </is>
       </c>
       <c r="M620" t="inlineStr">
@@ -28958,12 +28958,12 @@
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>TopMobileBoard (Anchor)</t>
+          <t>Full Branding Mobile</t>
         </is>
       </c>
       <c r="G621" t="inlineStr">
         <is>
-          <t>600x200</t>
+          <t>1x 600x200, 3x 300x250</t>
         </is>
       </c>
       <c r="I621" t="inlineStr">
@@ -28973,7 +28973,7 @@
       </c>
       <c r="J621" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF ou HTML5</t>
+          <t>JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="L621" t="inlineStr">
@@ -29010,12 +29010,12 @@
       </c>
       <c r="F622" t="inlineStr">
         <is>
-          <t>Full Branding Mobile</t>
+          <t>Rectangle (MREC) (Mobile)</t>
         </is>
       </c>
       <c r="G622" t="inlineStr">
         <is>
-          <t>1x 600x200, 3x 300x250</t>
+          <t>300x250</t>
         </is>
       </c>
       <c r="I622" t="inlineStr">
@@ -29025,12 +29025,12 @@
       </c>
       <c r="J622" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF</t>
+          <t>JPG, PNG, GIF ou HTML5</t>
         </is>
       </c>
       <c r="L622" t="inlineStr">
         <is>
-          <t>Posição: Listing Page (Mobile).</t>
+          <t>Posição: Listing Page &amp; Ad Page (Mobile).</t>
         </is>
       </c>
       <c r="M622" t="inlineStr">
@@ -29062,12 +29062,12 @@
       </c>
       <c r="F623" t="inlineStr">
         <is>
-          <t>Rectangle (MREC) (Mobile)</t>
+          <t>Native</t>
         </is>
       </c>
       <c r="G623" t="inlineStr">
         <is>
-          <t>300x250</t>
+          <t>1000x563</t>
         </is>
       </c>
       <c r="I623" t="inlineStr">
@@ -29077,12 +29077,12 @@
       </c>
       <c r="J623" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF ou HTML5</t>
+          <t>JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="L623" t="inlineStr">
         <is>
-          <t>Posição: Listing Page &amp; Ad Page (Mobile).</t>
+          <t>Posição: Listing Page (Mobile). Título: máx. 25 carateres. Descrição: máx. 35 carateres.</t>
         </is>
       </c>
       <c r="M623" t="inlineStr">
@@ -29114,27 +29114,27 @@
       </c>
       <c r="F624" t="inlineStr">
         <is>
-          <t>Native</t>
+          <t>Text Link / Brand Link (Mobile)</t>
         </is>
       </c>
       <c r="G624" t="inlineStr">
         <is>
-          <t>1000x563</t>
+          <t>Logo: 80x80 (opcional)</t>
         </is>
       </c>
       <c r="I624" t="inlineStr">
         <is>
-          <t>Máx. 1 MB</t>
+          <t>Máx. 1 MB (apenas se incluir logo)</t>
         </is>
       </c>
       <c r="J624" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF</t>
+          <t>JPG, PNG ou GIF (apenas se incluir logo)</t>
         </is>
       </c>
       <c r="L624" t="inlineStr">
         <is>
-          <t>Posição: Listing Page (Mobile). Título: máx. 25 carateres. Descrição: máx. 35 carateres.</t>
+          <t>Posição: Ad Page (Mobile). Texto/Copy: máx. 20 carateres.</t>
         </is>
       </c>
       <c r="M624" t="inlineStr">
@@ -29166,27 +29166,27 @@
       </c>
       <c r="F625" t="inlineStr">
         <is>
-          <t>Text Link / Brand Link (Mobile)</t>
+          <t>Top Mobile Board (Seller/Observed Page)</t>
         </is>
       </c>
       <c r="G625" t="inlineStr">
         <is>
-          <t>Logo: 80x80 (opcional)</t>
+          <t>320x100</t>
         </is>
       </c>
       <c r="I625" t="inlineStr">
         <is>
-          <t>Máx. 1 MB (apenas se incluir logo)</t>
+          <t>Máx. 1 MB</t>
         </is>
       </c>
       <c r="J625" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF (apenas se incluir logo)</t>
+          <t>JPG, PNG, GIF ou HTML5</t>
         </is>
       </c>
       <c r="L625" t="inlineStr">
         <is>
-          <t>Posição: Ad Page (Mobile). Texto/Copy: máx. 20 carateres.</t>
+          <t>Posição: Seller Listing Page &amp; Observed Page (Mobile).</t>
         </is>
       </c>
       <c r="M625" t="inlineStr">
@@ -29218,12 +29218,12 @@
       </c>
       <c r="F626" t="inlineStr">
         <is>
-          <t>Top Mobile Board (Seller/Observed Page)</t>
+          <t>Rectangle (MREC) (App)</t>
         </is>
       </c>
       <c r="G626" t="inlineStr">
         <is>
-          <t>320x100</t>
+          <t>300x250</t>
         </is>
       </c>
       <c r="I626" t="inlineStr">
@@ -29238,7 +29238,7 @@
       </c>
       <c r="L626" t="inlineStr">
         <is>
-          <t>Posição: Seller Listing Page &amp; Observed Page (Mobile).</t>
+          <t>Posição: Listing Page &amp; Ad Page (App — Android e iOS).</t>
         </is>
       </c>
       <c r="M626" t="inlineStr">
@@ -29270,12 +29270,12 @@
       </c>
       <c r="F627" t="inlineStr">
         <is>
-          <t>Rectangle (MREC) (App)</t>
+          <t>Observed Ads (App)</t>
         </is>
       </c>
       <c r="G627" t="inlineStr">
         <is>
-          <t>300x250</t>
+          <t>320x100</t>
         </is>
       </c>
       <c r="I627" t="inlineStr">
@@ -29290,7 +29290,7 @@
       </c>
       <c r="L627" t="inlineStr">
         <is>
-          <t>Posição: Listing Page &amp; Ad Page (App — Android e iOS).</t>
+          <t>Posição: Observed Page (App).</t>
         </is>
       </c>
       <c r="M627" t="inlineStr">
@@ -29322,7 +29322,7 @@
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>Observed Ads (App)</t>
+          <t>Top Mobile Board (App - Homepage)</t>
         </is>
       </c>
       <c r="G628" t="inlineStr">
@@ -29342,7 +29342,7 @@
       </c>
       <c r="L628" t="inlineStr">
         <is>
-          <t>Posição: Observed Page (App).</t>
+          <t>Posição: Homepage (App — Android e iOS).</t>
         </is>
       </c>
       <c r="M628" t="inlineStr">
@@ -29364,22 +29364,22 @@
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>OLX</t>
+          <t>StandVirtual</t>
         </is>
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>OLX</t>
+          <t>StandVirtual</t>
         </is>
       </c>
       <c r="F629" t="inlineStr">
         <is>
-          <t>Top Mobile Board (App - Homepage)</t>
+          <t>Showcase (Masthead)</t>
         </is>
       </c>
       <c r="G629" t="inlineStr">
         <is>
-          <t>320x100</t>
+          <t>1920x300</t>
         </is>
       </c>
       <c r="I629" t="inlineStr">
@@ -29394,7 +29394,7 @@
       </c>
       <c r="L629" t="inlineStr">
         <is>
-          <t>Posição: Homepage (App — Android e iOS).</t>
+          <t>Posição: Homepage (Desktop). Ter atenção às áreas visíveis (Safe Zones). Existe template para download no site de specs.</t>
         </is>
       </c>
       <c r="M629" t="inlineStr">
@@ -29426,7 +29426,7 @@
       </c>
       <c r="F630" t="inlineStr">
         <is>
-          <t>Showcase (Masthead)</t>
+          <t>Megaboard (Topboard)</t>
         </is>
       </c>
       <c r="G630" t="inlineStr">
@@ -29446,7 +29446,7 @@
       </c>
       <c r="L630" t="inlineStr">
         <is>
-          <t>Posição: Homepage (Desktop). Ter atenção às áreas visíveis (Safe Zones). Existe template para download no site de specs.</t>
+          <t>Posição: Listing Page &amp; Ad Page (Desktop). Ter atenção às áreas visíveis (Safe Zones). Existe template para download no site de specs.</t>
         </is>
       </c>
       <c r="M630" t="inlineStr">
@@ -29478,12 +29478,12 @@
       </c>
       <c r="F631" t="inlineStr">
         <is>
-          <t>Megaboard (Topboard)</t>
+          <t>Native</t>
         </is>
       </c>
       <c r="G631" t="inlineStr">
         <is>
-          <t>1920x300</t>
+          <t>Imagem: 252x152. Logo: 80x36.</t>
         </is>
       </c>
       <c r="I631" t="inlineStr">
@@ -29493,12 +29493,12 @@
       </c>
       <c r="J631" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF ou HTML5</t>
+          <t>JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="L631" t="inlineStr">
         <is>
-          <t>Posição: Listing Page &amp; Ad Page (Desktop). Ter atenção às áreas visíveis (Safe Zones). Existe template para download no site de specs.</t>
+          <t>Posição: Listing Page (Desktop). Título: máx. 45 carateres. Descrição: máx. 65 carateres. CTA: máx. 10 carateres.</t>
         </is>
       </c>
       <c r="M631" t="inlineStr">
@@ -29530,12 +29530,12 @@
       </c>
       <c r="F632" t="inlineStr">
         <is>
-          <t>Native</t>
+          <t>Skyscraper | Halfpage</t>
         </is>
       </c>
       <c r="G632" t="inlineStr">
         <is>
-          <t>Imagem: 252x152. Logo: 80x36.</t>
+          <t>160x600 ou 300x600</t>
         </is>
       </c>
       <c r="I632" t="inlineStr">
@@ -29545,12 +29545,12 @@
       </c>
       <c r="J632" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF</t>
+          <t>JPG, PNG, GIF ou HTML5</t>
         </is>
       </c>
       <c r="L632" t="inlineStr">
         <is>
-          <t>Posição: Listing Page (Desktop). Título: máx. 45 carateres. Descrição: máx. 65 carateres. CTA: máx. 10 carateres.</t>
+          <t>Posição: Listing Page (Desktop).</t>
         </is>
       </c>
       <c r="M632" t="inlineStr">
@@ -29582,12 +29582,12 @@
       </c>
       <c r="F633" t="inlineStr">
         <is>
-          <t>Skyscraper | Halfpage</t>
+          <t>Billboard</t>
         </is>
       </c>
       <c r="G633" t="inlineStr">
         <is>
-          <t>160x600 ou 300x600</t>
+          <t>914x212</t>
         </is>
       </c>
       <c r="I633" t="inlineStr">
@@ -29634,12 +29634,12 @@
       </c>
       <c r="F634" t="inlineStr">
         <is>
-          <t>Billboard</t>
+          <t>Rectangle (MREC)</t>
         </is>
       </c>
       <c r="G634" t="inlineStr">
         <is>
-          <t>914x212</t>
+          <t>300x250</t>
         </is>
       </c>
       <c r="I634" t="inlineStr">
@@ -29654,7 +29654,7 @@
       </c>
       <c r="L634" t="inlineStr">
         <is>
-          <t>Posição: Listing Page (Desktop).</t>
+          <t>Posição: Ad Page &amp; Gallery Page (Desktop).</t>
         </is>
       </c>
       <c r="M634" t="inlineStr">
@@ -29686,12 +29686,12 @@
       </c>
       <c r="F635" t="inlineStr">
         <is>
-          <t>Rectangle (MREC)</t>
+          <t>Halfpage</t>
         </is>
       </c>
       <c r="G635" t="inlineStr">
         <is>
-          <t>300x250</t>
+          <t>300x600</t>
         </is>
       </c>
       <c r="I635" t="inlineStr">
@@ -29706,7 +29706,7 @@
       </c>
       <c r="L635" t="inlineStr">
         <is>
-          <t>Posição: Ad Page &amp; Gallery Page (Desktop).</t>
+          <t>Posição: Ad Page (Desktop).</t>
         </is>
       </c>
       <c r="M635" t="inlineStr">
@@ -29738,27 +29738,32 @@
       </c>
       <c r="F636" t="inlineStr">
         <is>
-          <t>Halfpage</t>
+          <t>Video Outstream</t>
         </is>
       </c>
       <c r="G636" t="inlineStr">
         <is>
-          <t>300x600</t>
+          <t>1920x1080</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I636" t="inlineStr">
         <is>
-          <t>Máx. 1 MB</t>
+          <t>Máx. 10 MB</t>
         </is>
       </c>
       <c r="J636" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF ou HTML5</t>
+          <t>MP4, até 30 segundos</t>
         </is>
       </c>
       <c r="L636" t="inlineStr">
         <is>
-          <t>Posição: Ad Page (Desktop).</t>
+          <t>Posição: Listing Page &amp; Ad Page (Desktop).</t>
         </is>
       </c>
       <c r="M636" t="inlineStr">
@@ -29790,32 +29795,27 @@
       </c>
       <c r="F637" t="inlineStr">
         <is>
-          <t>Video Outstream</t>
+          <t>Showcase (Masthead) (Mobile)</t>
         </is>
       </c>
       <c r="G637" t="inlineStr">
         <is>
-          <t>1920x1080</t>
-        </is>
-      </c>
-      <c r="H637" t="inlineStr">
-        <is>
-          <t>16:9</t>
+          <t>1080x450</t>
         </is>
       </c>
       <c r="I637" t="inlineStr">
         <is>
-          <t>Máx. 10 MB</t>
+          <t>Máx. 1 MB</t>
         </is>
       </c>
       <c r="J637" t="inlineStr">
         <is>
-          <t>MP4, até 30 segundos</t>
+          <t>JPG, PNG, GIF ou HTML5</t>
         </is>
       </c>
       <c r="L637" t="inlineStr">
         <is>
-          <t>Posição: Listing Page &amp; Ad Page (Desktop).</t>
+          <t>Posição: Homepage (Mobile).</t>
         </is>
       </c>
       <c r="M637" t="inlineStr">
@@ -29847,12 +29847,12 @@
       </c>
       <c r="F638" t="inlineStr">
         <is>
-          <t>Showcase (Masthead) (Mobile)</t>
+          <t>Full Branding Mobile</t>
         </is>
       </c>
       <c r="G638" t="inlineStr">
         <is>
-          <t>1080x450</t>
+          <t>1x 600x200, 3x 300x250</t>
         </is>
       </c>
       <c r="I638" t="inlineStr">
@@ -29862,12 +29862,12 @@
       </c>
       <c r="J638" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF ou HTML5</t>
+          <t>JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="L638" t="inlineStr">
         <is>
-          <t>Posição: Homepage (Mobile).</t>
+          <t>Posição: Listing Page (Mobile).</t>
         </is>
       </c>
       <c r="M638" t="inlineStr">
@@ -29899,12 +29899,12 @@
       </c>
       <c r="F639" t="inlineStr">
         <is>
-          <t>Full Branding Mobile</t>
+          <t>TopMobileBoard (Anchor)</t>
         </is>
       </c>
       <c r="G639" t="inlineStr">
         <is>
-          <t>1x 600x200, 3x 300x250</t>
+          <t>600x200</t>
         </is>
       </c>
       <c r="I639" t="inlineStr">
@@ -29914,7 +29914,7 @@
       </c>
       <c r="J639" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF</t>
+          <t>JPG, PNG, GIF ou HTML5</t>
         </is>
       </c>
       <c r="L639" t="inlineStr">
@@ -29951,12 +29951,12 @@
       </c>
       <c r="F640" t="inlineStr">
         <is>
-          <t>TopMobileBoard (Anchor)</t>
+          <t>Rectangle (MREC) (Mobile)</t>
         </is>
       </c>
       <c r="G640" t="inlineStr">
         <is>
-          <t>600x200</t>
+          <t>300x250</t>
         </is>
       </c>
       <c r="I640" t="inlineStr">
@@ -29971,7 +29971,7 @@
       </c>
       <c r="L640" t="inlineStr">
         <is>
-          <t>Posição: Listing Page (Mobile).</t>
+          <t>Posição: Listing Page &amp; Ad Page (Mobile).</t>
         </is>
       </c>
       <c r="M640" t="inlineStr">
@@ -29993,22 +29993,22 @@
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>StandVirtual</t>
+          <t>Imovirtual</t>
         </is>
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>StandVirtual</t>
+          <t>Imovirtual</t>
         </is>
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>Rectangle (MREC) (Mobile)</t>
+          <t>Megaboard (Topboard)</t>
         </is>
       </c>
       <c r="G641" t="inlineStr">
         <is>
-          <t>300x250</t>
+          <t>1920x200</t>
         </is>
       </c>
       <c r="I641" t="inlineStr">
@@ -30023,7 +30023,7 @@
       </c>
       <c r="L641" t="inlineStr">
         <is>
-          <t>Posição: Listing Page &amp; Ad Page (Mobile).</t>
+          <t>Posição: Listing Page (Desktop). Ter atenção às áreas visíveis (Safe Zones).</t>
         </is>
       </c>
       <c r="M641" t="inlineStr">
@@ -30055,12 +30055,12 @@
       </c>
       <c r="F642" t="inlineStr">
         <is>
-          <t>Megaboard (Topboard)</t>
+          <t>Native (In List)</t>
         </is>
       </c>
       <c r="G642" t="inlineStr">
         <is>
-          <t>1920x200</t>
+          <t>820x200</t>
         </is>
       </c>
       <c r="I642" t="inlineStr">
@@ -30075,7 +30075,7 @@
       </c>
       <c r="L642" t="inlineStr">
         <is>
-          <t>Posição: Listing Page (Desktop). Ter atenção às áreas visíveis (Safe Zones).</t>
+          <t>Posição: Listing Page (Desktop).</t>
         </is>
       </c>
       <c r="M642" t="inlineStr">
@@ -30107,12 +30107,12 @@
       </c>
       <c r="F643" t="inlineStr">
         <is>
-          <t>Native (In List)</t>
+          <t>Halfpage</t>
         </is>
       </c>
       <c r="G643" t="inlineStr">
         <is>
-          <t>820x200</t>
+          <t>300x600</t>
         </is>
       </c>
       <c r="I643" t="inlineStr">
@@ -30127,7 +30127,7 @@
       </c>
       <c r="L643" t="inlineStr">
         <is>
-          <t>Posição: Listing Page (Desktop).</t>
+          <t>Posição: Listing Page &amp; Ad Page (Desktop).</t>
         </is>
       </c>
       <c r="M643" t="inlineStr">
@@ -30159,12 +30159,12 @@
       </c>
       <c r="F644" t="inlineStr">
         <is>
-          <t>Halfpage</t>
+          <t>Rectangle (MREC)</t>
         </is>
       </c>
       <c r="G644" t="inlineStr">
         <is>
-          <t>300x600</t>
+          <t>300x250</t>
         </is>
       </c>
       <c r="I644" t="inlineStr">
@@ -30211,27 +30211,27 @@
       </c>
       <c r="F645" t="inlineStr">
         <is>
-          <t>Rectangle (MREC)</t>
+          <t>Text Link (Brand Link)</t>
         </is>
       </c>
       <c r="G645" t="inlineStr">
         <is>
-          <t>300x250</t>
+          <t>Logo: 80x80 (opcional)</t>
         </is>
       </c>
       <c r="I645" t="inlineStr">
         <is>
-          <t>Máx. 1 MB</t>
+          <t>Máx. 1 MB (apenas se incluir logo)</t>
         </is>
       </c>
       <c r="J645" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF ou HTML5</t>
+          <t>JPG, PNG ou GIF (apenas se incluir logo)</t>
         </is>
       </c>
       <c r="L645" t="inlineStr">
         <is>
-          <t>Posição: Listing Page &amp; Ad Page (Desktop).</t>
+          <t>Posição: Ad Page (Desktop). Texto/Copy: máx. 40 carateres.</t>
         </is>
       </c>
       <c r="M645" t="inlineStr">
@@ -30263,27 +30263,27 @@
       </c>
       <c r="F646" t="inlineStr">
         <is>
-          <t>Text Link (Brand Link)</t>
+          <t>Rectangle (MREC) (Mobile)</t>
         </is>
       </c>
       <c r="G646" t="inlineStr">
         <is>
-          <t>Logo: 80x80 (opcional)</t>
+          <t>300x250</t>
         </is>
       </c>
       <c r="I646" t="inlineStr">
         <is>
-          <t>Máx. 1 MB (apenas se incluir logo)</t>
+          <t>Máx. 1 MB</t>
         </is>
       </c>
       <c r="J646" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF (apenas se incluir logo)</t>
+          <t>JPG, PNG, GIF ou HTML5</t>
         </is>
       </c>
       <c r="L646" t="inlineStr">
         <is>
-          <t>Posição: Ad Page (Desktop). Texto/Copy: máx. 40 carateres.</t>
+          <t>Posição: Listing Page &amp; Ad Page (Mobile).</t>
         </is>
       </c>
       <c r="M646" t="inlineStr">
@@ -30315,27 +30315,27 @@
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>Rectangle (MREC) (Mobile)</t>
+          <t>Text Link (Brand Link) (Mobile)</t>
         </is>
       </c>
       <c r="G647" t="inlineStr">
         <is>
-          <t>300x250</t>
+          <t>Logo: 80x80 (opcional)</t>
         </is>
       </c>
       <c r="I647" t="inlineStr">
         <is>
-          <t>Máx. 1 MB</t>
+          <t>Máx. 1 MB (apenas se incluir logo)</t>
         </is>
       </c>
       <c r="J647" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF ou HTML5</t>
+          <t>JPG, PNG ou GIF (apenas se incluir logo)</t>
         </is>
       </c>
       <c r="L647" t="inlineStr">
         <is>
-          <t>Posição: Listing Page &amp; Ad Page (Mobile).</t>
+          <t>Posição: Ad Page (Mobile). Texto/Copy: máx. 20 carateres.</t>
         </is>
       </c>
       <c r="M647" t="inlineStr">
@@ -30347,52 +30347,37 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>INTERNET</t>
+          <t>OOH</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>OOH</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>Imovirtual</t>
+          <t>In-Store Media</t>
         </is>
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>Imovirtual</t>
+          <t>In-Store Media</t>
         </is>
       </c>
       <c r="F648" t="inlineStr">
         <is>
-          <t>Text Link (Brand Link) (Mobile)</t>
+          <t>Category Window (Higiene)</t>
         </is>
       </c>
       <c r="G648" t="inlineStr">
         <is>
-          <t>Logo: 80x80 (opcional)</t>
-        </is>
-      </c>
-      <c r="I648" t="inlineStr">
-        <is>
-          <t>Máx. 1 MB (apenas se incluir logo)</t>
-        </is>
-      </c>
-      <c r="J648" t="inlineStr">
-        <is>
-          <t>JPG, PNG ou GIF (apenas se incluir logo)</t>
+          <t>Largura total 133 cm (área visível 100 cm); altura 255 cm; faixas laterais 15 cm cada</t>
         </is>
       </c>
       <c r="L648" t="inlineStr">
         <is>
-          <t>Posição: Ad Page (Mobile). Texto/Copy: máx. 20 carateres.</t>
-        </is>
-      </c>
-      <c r="M648" t="inlineStr">
-        <is>
-          <t>https://formatos-publicidade-olx.netlify.app/</t>
+          <t>Molde técnico (die-line) para a categoria Higiene — sem retalhista nem especificações de produção/impressão indicadas no documento.</t>
         </is>
       </c>
     </row>
@@ -30419,17 +30404,17 @@
       </c>
       <c r="F649" t="inlineStr">
         <is>
-          <t>Category Window (Higiene)</t>
+          <t>Archmedia 220cm</t>
         </is>
       </c>
       <c r="G649" t="inlineStr">
         <is>
-          <t>Largura total 133 cm (área visível 100 cm); altura 255 cm; faixas laterais 15 cm cada</t>
+          <t>Largura total 220 cm (área visível 170 cm); altura 220 cm; faixa lateral 25 cm</t>
         </is>
       </c>
       <c r="L649" t="inlineStr">
         <is>
-          <t>Molde técnico (die-line) para a categoria Higiene — sem retalhista nem especificações de produção/impressão indicadas no documento.</t>
+          <t>Molde técnico (die-line) — sem retalhista nem especificações de material/impressão.</t>
         </is>
       </c>
     </row>
@@ -30456,12 +30441,12 @@
       </c>
       <c r="F650" t="inlineStr">
         <is>
-          <t>Archmedia 220cm</t>
+          <t>Archmedia 250cm</t>
         </is>
       </c>
       <c r="G650" t="inlineStr">
         <is>
-          <t>Largura total 220 cm (área visível 170 cm); altura 220 cm; faixa lateral 25 cm</t>
+          <t>Largura total 250 cm (área visível 200 cm); altura 220 cm; faixa lateral 25 cm</t>
         </is>
       </c>
       <c r="L650" t="inlineStr">
@@ -30493,12 +30478,12 @@
       </c>
       <c r="F651" t="inlineStr">
         <is>
-          <t>Archmedia 250cm</t>
+          <t>Archmedia 320cm</t>
         </is>
       </c>
       <c r="G651" t="inlineStr">
         <is>
-          <t>Largura total 250 cm (área visível 200 cm); altura 220 cm; faixa lateral 25 cm</t>
+          <t>Largura total 320 cm (área visível 270 cm); altura 220 cm; faixa lateral 25 cm</t>
         </is>
       </c>
       <c r="L651" t="inlineStr">
@@ -30530,17 +30515,17 @@
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>Archmedia 320cm</t>
+          <t>Category Window (Várias Medidas)</t>
         </is>
       </c>
       <c r="G652" t="inlineStr">
         <is>
-          <t>Largura total 320 cm (área visível 270 cm); altura 220 cm; faixa lateral 25 cm</t>
+          <t>Conforme indicado no documento: largura topo 1336 cm; alturas laterais 2000 cm e 2200 cm</t>
         </is>
       </c>
       <c r="L652" t="inlineStr">
         <is>
-          <t>Molde técnico (die-line) — sem retalhista nem especificações de material/impressão.</t>
+          <t>Nome do ficheiro indica "140x255cm", mas os valores no PDF (em cm) não batem certo — possível troca de unidade (cm/mm) no documento de origem. Reportado literalmente, sem correção. Molde técnico, sem retalhista nem specs de produção.</t>
         </is>
       </c>
     </row>
@@ -30567,17 +30552,27 @@
       </c>
       <c r="F653" t="inlineStr">
         <is>
-          <t>Category Window (Várias Medidas)</t>
+          <t>Shelf Display Media Luna</t>
         </is>
       </c>
       <c r="G653" t="inlineStr">
         <is>
-          <t>Conforme indicado no documento: largura topo 1336 cm; alturas laterais 2000 cm e 2200 cm</t>
+          <t>Suporte 160x500mm; vinil base 158x100mm; vinil frontal (com luz) 291x49mm</t>
+        </is>
+      </c>
+      <c r="I653" t="inlineStr">
+        <is>
+          <t>Escala real 1:1 + 2mm de sangria</t>
+        </is>
+      </c>
+      <c r="J653" t="inlineStr">
+        <is>
+          <t>PDF qualidade de imprensa (PDF 1.4, CMYK, 300 dpi, tipografia incrustada, transparências conservadas)</t>
         </is>
       </c>
       <c r="L653" t="inlineStr">
         <is>
-          <t>Nome do ficheiro indica "140x255cm", mas os valores no PDF (em cm) não batem certo — possível troca de unidade (cm/mm) no documento de origem. Reportado literalmente, sem correção. Molde técnico, sem retalhista nem specs de produção.</t>
+          <t>Suporte metálico em meia-lua com iluminação LED interior; vinil Easy Dot; impressão digital 4/0. Só pode exibir 1 produto por suporte; marcas com mínimo de 2 linhas de facing. Contratação mínima de 2 meses. Entrega 1,5 meses antes do início da campanha. Documento da In-Store Media España.</t>
         </is>
       </c>
     </row>
@@ -30604,27 +30599,22 @@
       </c>
       <c r="F654" t="inlineStr">
         <is>
-          <t>Shelf Display Media Luna</t>
+          <t>Alarm Hall-Media</t>
         </is>
       </c>
       <c r="G654" t="inlineStr">
         <is>
-          <t>Suporte 160x500mm; vinil base 158x100mm; vinil frontal (com luz) 291x49mm</t>
-        </is>
-      </c>
-      <c r="I654" t="inlineStr">
-        <is>
-          <t>Escala real 1:1 + 2mm de sangria</t>
+          <t>140x48x14 cms e 140x40x11 cms (segmentos 14/48/14/48 cm)</t>
         </is>
       </c>
       <c r="J654" t="inlineStr">
         <is>
-          <t>PDF qualidade de imprensa (PDF 1.4, CMYK, 300 dpi, tipografia incrustada, transparências conservadas)</t>
+          <t>Adobe Illustrator (aberto, sem bleed); CMYK; resolução mín. 150 DPI à escala 1:1</t>
         </is>
       </c>
       <c r="L654" t="inlineStr">
         <is>
-          <t>Suporte metálico em meia-lua com iluminação LED interior; vinil Easy Dot; impressão digital 4/0. Só pode exibir 1 produto por suporte; marcas com mínimo de 2 linhas de facing. Contratação mínima de 2 meses. Entrega 1,5 meses antes do início da campanha. Documento da In-Store Media España.</t>
+          <t>Material: cartão micro canelado, corte simples; impressão digital 4/0. Criatividade em português. Não colocar informação importante entre 40 e 56 cm da base (alturas de defesas de alarme variam por loja). Entrega: 1 mês antes para validação, 2 semanas antes para Arte Final.</t>
         </is>
       </c>
     </row>
@@ -30651,22 +30641,22 @@
       </c>
       <c r="F655" t="inlineStr">
         <is>
-          <t>Alarm Hall-Media</t>
+          <t>Door-Media — Pingo Doce</t>
         </is>
       </c>
       <c r="G655" t="inlineStr">
         <is>
-          <t>140x48x14 cms e 140x40x11 cms (segmentos 14/48/14/48 cm)</t>
+          <t>134x150 cms, 114x125 cms ou 90x100 cms</t>
         </is>
       </c>
       <c r="J655" t="inlineStr">
         <is>
-          <t>Adobe Illustrator (aberto, sem bleed); CMYK; resolução mín. 150 DPI à escala 1:1</t>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1</t>
         </is>
       </c>
       <c r="L655" t="inlineStr">
         <is>
-          <t>Material: cartão micro canelado, corte simples; impressão digital 4/0. Criatividade em português. Não colocar informação importante entre 40 e 56 cm da base (alturas de defesas de alarme variam por loja). Entrega: 1 mês antes para validação, 2 semanas antes para Arte Final.</t>
+          <t>Material: vinil monomérico com brilho, adesivo removível; impressão tintas low solvent 720 DPI + laminação brilho. Criatividade em português. Não colocar texto/imagem no centro onde abrem as portas.</t>
         </is>
       </c>
     </row>
@@ -30693,22 +30683,27 @@
       </c>
       <c r="F656" t="inlineStr">
         <is>
-          <t>Door-Media — Pingo Doce</t>
+          <t>Welcome Screen — Auchan</t>
         </is>
       </c>
       <c r="G656" t="inlineStr">
         <is>
-          <t>134x150 cms, 114x125 cms ou 90x100 cms</t>
+          <t>1280x256, 384x576, 384x768, 768x256 ou 960x192 px</t>
+        </is>
+      </c>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>Máx. 25 MB</t>
         </is>
       </c>
       <c r="J656" t="inlineStr">
         <is>
-          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1</t>
+          <t>MP4, codec H264, 25 fps, sem áudio</t>
         </is>
       </c>
       <c r="L656" t="inlineStr">
         <is>
-          <t>Material: vinil monomérico com brilho, adesivo removível; impressão tintas low solvent 720 DPI + laminação brilho. Criatividade em português. Não colocar texto/imagem no centro onde abrem as portas.</t>
+          <t>Duração 10 seg. Bitrate recomendado 10 Mbps. Emissão só após validação ISM; entrega da AF segundo indicações ISM.</t>
         </is>
       </c>
     </row>
@@ -30735,12 +30730,12 @@
       </c>
       <c r="F657" t="inlineStr">
         <is>
-          <t>Welcome Screen — Auchan</t>
+          <t>Welcome Screen — Pingo Doce</t>
         </is>
       </c>
       <c r="G657" t="inlineStr">
         <is>
-          <t>1280x256, 384x576, 384x768, 768x256 ou 960x192 px</t>
+          <t>Ecrã físico 3,00x2,00m; resolução 1532x1024 px</t>
         </is>
       </c>
       <c r="I657" t="inlineStr">
@@ -30755,7 +30750,7 @@
       </c>
       <c r="L657" t="inlineStr">
         <is>
-          <t>Duração 10 seg. Bitrate recomendado 10 Mbps. Emissão só após validação ISM; entrega da AF segundo indicações ISM.</t>
+          <t>Duração 10 seg. Bitrate recomendado 10 Mbps. Emissão só após validação ISM.</t>
         </is>
       </c>
     </row>
@@ -30782,27 +30777,22 @@
       </c>
       <c r="F658" t="inlineStr">
         <is>
-          <t>Welcome Screen — Pingo Doce</t>
+          <t>Alarm Media (Cartão) — Auchan</t>
         </is>
       </c>
       <c r="G658" t="inlineStr">
         <is>
-          <t>Ecrã físico 3,00x2,00m; resolução 1532x1024 px</t>
-        </is>
-      </c>
-      <c r="I658" t="inlineStr">
-        <is>
-          <t>Máx. 25 MB</t>
+          <t>120x52x4 cms, 105x52x4 cms ou 90x52x4 cms (segmentos 4/52/4/52cm)</t>
         </is>
       </c>
       <c r="J658" t="inlineStr">
         <is>
-          <t>MP4, codec H264, 25 fps, sem áudio</t>
+          <t>Adobe Illustrator (aberto, sem bleed); CMYK; resolução mín. 150 DPI à escala 1:1</t>
         </is>
       </c>
       <c r="L658" t="inlineStr">
         <is>
-          <t>Duração 10 seg. Bitrate recomendado 10 Mbps. Emissão só após validação ISM.</t>
+          <t>Material: cartão micro canelado, corte simples; impressão digital 4/0. Não colocar informação entre 40 e 56 cm da base.</t>
         </is>
       </c>
     </row>
@@ -30829,12 +30819,12 @@
       </c>
       <c r="F659" t="inlineStr">
         <is>
-          <t>Alarm Media (Cartão) — Auchan</t>
+          <t>Alarm Media (Cartão) — Pingo Doce</t>
         </is>
       </c>
       <c r="G659" t="inlineStr">
         <is>
-          <t>120x52x4 cms, 105x52x4 cms ou 90x52x4 cms (segmentos 4/52/4/52cm)</t>
+          <t>140x48x14 cms e 140x40x11 cms (segmentos 14/48/14/48cm)</t>
         </is>
       </c>
       <c r="J659" t="inlineStr">
@@ -30844,7 +30834,7 @@
       </c>
       <c r="L659" t="inlineStr">
         <is>
-          <t>Material: cartão micro canelado, corte simples; impressão digital 4/0. Não colocar informação entre 40 e 56 cm da base.</t>
+          <t>Material: cartão micro canelado, corte simples; impressão digital 4/0. Recomenda-se logo da marca nas laterais. Não colocar informação entre 40 e 56 cm da base (defesas variam por loja).</t>
         </is>
       </c>
     </row>
@@ -30871,7 +30861,7 @@
       </c>
       <c r="F660" t="inlineStr">
         <is>
-          <t>Alarm Media (Cartão) — Pingo Doce</t>
+          <t>Alarm Media (Cartão) — Continente</t>
         </is>
       </c>
       <c r="G660" t="inlineStr">
@@ -30886,7 +30876,7 @@
       </c>
       <c r="L660" t="inlineStr">
         <is>
-          <t>Material: cartão micro canelado, corte simples; impressão digital 4/0. Recomenda-se logo da marca nas laterais. Não colocar informação entre 40 e 56 cm da base (defesas variam por loja).</t>
+          <t>Material: cartão micro canelado, corte simples; impressão digital 4/0. Não colocar informação entre 40 e 56 cm da base; sugere-se logo nas laterais.</t>
         </is>
       </c>
     </row>
@@ -30913,12 +30903,12 @@
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>Alarm Media (Cartão) — Continente</t>
+          <t>Alarm Media (Cartão) — El Corte Inglês (Supercor)</t>
         </is>
       </c>
       <c r="G661" t="inlineStr">
         <is>
-          <t>140x48x14 cms e 140x40x11 cms (segmentos 14/48/14/48cm)</t>
+          <t>140x48x14 cms</t>
         </is>
       </c>
       <c r="J661" t="inlineStr">
@@ -30928,7 +30918,7 @@
       </c>
       <c r="L661" t="inlineStr">
         <is>
-          <t>Material: cartão micro canelado, corte simples; impressão digital 4/0. Não colocar informação entre 40 e 56 cm da base; sugere-se logo nas laterais.</t>
+          <t>Material: cartão micro canelado, corte simples; impressão digital 4/0. Não colocar informação entre 40 e 56 cm da base.</t>
         </is>
       </c>
     </row>
@@ -30955,22 +30945,22 @@
       </c>
       <c r="F662" t="inlineStr">
         <is>
-          <t>Alarm Media (Cartão) — El Corte Inglês (Supercor)</t>
+          <t>Alarm-Media (Papel) — El Corte Inglês (Supercor)</t>
         </is>
       </c>
       <c r="G662" t="inlineStr">
         <is>
-          <t>140x48x14 cms</t>
+          <t>Face maior: 490x1210mm. Lateral (com logo/nome da marca): 105x1210mm.</t>
         </is>
       </c>
       <c r="J662" t="inlineStr">
         <is>
-          <t>Adobe Illustrator (aberto, sem bleed); CMYK; resolução mín. 150 DPI à escala 1:1</t>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1</t>
         </is>
       </c>
       <c r="L662" t="inlineStr">
         <is>
-          <t>Material: cartão micro canelado, corte simples; impressão digital 4/0. Não colocar informação entre 40 e 56 cm da base.</t>
+          <t>Material: white back paper 200 grs, corte simples; impressão offset 4/0, quadricromia. Pode colocar logo/nome da marca na faixa lateral.</t>
         </is>
       </c>
     </row>
@@ -30997,12 +30987,12 @@
       </c>
       <c r="F663" t="inlineStr">
         <is>
-          <t>Alarm-Media (Papel) — El Corte Inglês (Supercor)</t>
+          <t>Alarm-Media (Papel) — Auchan</t>
         </is>
       </c>
       <c r="G663" t="inlineStr">
         <is>
-          <t>Face maior: 490x1210mm. Lateral (com logo/nome da marca): 105x1210mm.</t>
+          <t>104x16 cms, 106x22 cms ou 133x40 cms (CxL)</t>
         </is>
       </c>
       <c r="J663" t="inlineStr">
@@ -31012,7 +31002,7 @@
       </c>
       <c r="L663" t="inlineStr">
         <is>
-          <t>Material: white back paper 200 grs, corte simples; impressão offset 4/0, quadricromia. Pode colocar logo/nome da marca na faixa lateral.</t>
+          <t>Material: white back paper 150 grs, corte simples; impressão offset 4/0, quadricromia. Entrega: 1 mês antes para validação, 2 semanas antes para AF.</t>
         </is>
       </c>
     </row>
@@ -31039,12 +31029,12 @@
       </c>
       <c r="F664" t="inlineStr">
         <is>
-          <t>Alarm-Media (Papel) — Auchan</t>
+          <t>Alarm-Media (Papel) — Continente</t>
         </is>
       </c>
       <c r="G664" t="inlineStr">
         <is>
-          <t>104x16 cms, 106x22 cms ou 133x40 cms (CxL)</t>
+          <t>49x121,5 cms</t>
         </is>
       </c>
       <c r="J664" t="inlineStr">
@@ -31054,7 +31044,7 @@
       </c>
       <c r="L664" t="inlineStr">
         <is>
-          <t>Material: white back paper 150 grs, corte simples; impressão offset 4/0, quadricromia. Entrega: 1 mês antes para validação, 2 semanas antes para AF.</t>
+          <t>Material: white back paper 150 grs, corte simples; impressão offset 4/0, quadricromia. Não colocar informação entre 31,5 e 47,5 cm da base (zona de defesa variável por loja). Documento da In-Store Media España.</t>
         </is>
       </c>
     </row>
@@ -31081,22 +31071,22 @@
       </c>
       <c r="F665" t="inlineStr">
         <is>
-          <t>Alarm-Media (Papel) — Continente</t>
+          <t>Alarm-Media (Papel) — E.Leclerc</t>
         </is>
       </c>
       <c r="G665" t="inlineStr">
         <is>
-          <t>49x121,5 cms</t>
+          <t>140x48x14 cms e 140x40x11 cms (segmentos 14/48/14/48cm)</t>
         </is>
       </c>
       <c r="J665" t="inlineStr">
         <is>
-          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1</t>
+          <t>Adobe Illustrator (aberto, sem bleed); CMYK; resolução mín. 150 DPI à escala 1:1</t>
         </is>
       </c>
       <c r="L665" t="inlineStr">
         <is>
-          <t>Material: white back paper 150 grs, corte simples; impressão offset 4/0, quadricromia. Não colocar informação entre 31,5 e 47,5 cm da base (zona de defesa variável por loja). Documento da In-Store Media España.</t>
+          <t>Material: cartão micro canelado, corte simples; impressão digital 4/0. Não colocar informação entre 40 e 56 cm da base; sugere-se logo nas laterais.</t>
         </is>
       </c>
     </row>
@@ -31123,22 +31113,22 @@
       </c>
       <c r="F666" t="inlineStr">
         <is>
-          <t>Alarm-Media (Papel) — E.Leclerc</t>
+          <t>Alarm-Media (Papel) — El Corte Inglês Gaia</t>
         </is>
       </c>
       <c r="G666" t="inlineStr">
         <is>
-          <t>140x48x14 cms e 140x40x11 cms (segmentos 14/48/14/48cm)</t>
+          <t>Tiras laterais 105x1210mm (x2); faces maiores 485x1210mm (x2)</t>
         </is>
       </c>
       <c r="J666" t="inlineStr">
         <is>
-          <t>Adobe Illustrator (aberto, sem bleed); CMYK; resolução mín. 150 DPI à escala 1:1</t>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1</t>
         </is>
       </c>
       <c r="L666" t="inlineStr">
         <is>
-          <t>Material: cartão micro canelado, corte simples; impressão digital 4/0. Não colocar informação entre 40 e 56 cm da base; sugere-se logo nas laterais.</t>
+          <t>Material: white back paper 200 grs, corte simples; impressão offset 4/0. Nas tiras laterais colocar nome, logo ou slogan. Entrega: 10 dias antes do início da campanha. Nota: o nome do ficheiro de origem referia "Supercor Restelo", mas o conteúdo do documento identifica claramente este suporte como El Corte Inglês Gaia.</t>
         </is>
       </c>
     </row>
@@ -31165,12 +31155,12 @@
       </c>
       <c r="F667" t="inlineStr">
         <is>
-          <t>Alarm-Media (Papel) — El Corte Inglês Gaia</t>
+          <t>Alarm Media (Papel) — El Corte Inglês Departamental</t>
         </is>
       </c>
       <c r="G667" t="inlineStr">
         <is>
-          <t>Tiras laterais 105x1210mm (x2); faces maiores 485x1210mm (x2)</t>
+          <t>Painel frontal: 490x1210mm. Lateral (logo/nome): 105x1210mm.</t>
         </is>
       </c>
       <c r="J667" t="inlineStr">
@@ -31180,7 +31170,7 @@
       </c>
       <c r="L667" t="inlineStr">
         <is>
-          <t>Material: white back paper 200 grs, corte simples; impressão offset 4/0. Nas tiras laterais colocar nome, logo ou slogan. Entrega: 10 dias antes do início da campanha. Nota: o nome do ficheiro de origem referia "Supercor Restelo", mas o conteúdo do documento identifica claramente este suporte como El Corte Inglês Gaia.</t>
+          <t>Material: white back paper 200 grs, corte simples; impressão offset 4/0. Entrega: 10 dias úteis antes do início da campanha.</t>
         </is>
       </c>
     </row>
@@ -31207,12 +31197,12 @@
       </c>
       <c r="F668" t="inlineStr">
         <is>
-          <t>Alarm Media (Papel) — El Corte Inglês Departamental</t>
+          <t>Alarm Walk — Auchan</t>
         </is>
       </c>
       <c r="G668" t="inlineStr">
         <is>
-          <t>Painel frontal: 490x1210mm. Lateral (logo/nome): 105x1210mm.</t>
+          <t>600x100, 400x100 ou 250x100 cms; margem branco 1 cm; cantos arredondados</t>
         </is>
       </c>
       <c r="J668" t="inlineStr">
@@ -31222,7 +31212,7 @@
       </c>
       <c r="L668" t="inlineStr">
         <is>
-          <t>Material: white back paper 200 grs, corte simples; impressão offset 4/0. Entrega: 10 dias úteis antes do início da campanha.</t>
+          <t>Material: vinil de chão autocolante opaco 3M com lâmina antideslizante MSM; offset 4/0 + verniz UVI brilhante. Não são permitidos passatempos/jogos de sorte.</t>
         </is>
       </c>
     </row>
@@ -31249,12 +31239,12 @@
       </c>
       <c r="F669" t="inlineStr">
         <is>
-          <t>Alarm Walk — Auchan</t>
+          <t>Alarm Walk — Continente</t>
         </is>
       </c>
       <c r="G669" t="inlineStr">
         <is>
-          <t>600x100, 400x100 ou 250x100 cms; margem branco 1 cm; cantos arredondados</t>
+          <t>600x100, 400x100 ou 250x100 cms; margem branco 1 cm</t>
         </is>
       </c>
       <c r="J669" t="inlineStr">
@@ -31264,7 +31254,7 @@
       </c>
       <c r="L669" t="inlineStr">
         <is>
-          <t>Material: vinil de chão autocolante opaco 3M com lâmina antideslizante MSM; offset 4/0 + verniz UVI brilhante. Não são permitidos passatempos/jogos de sorte.</t>
+          <t>Mesmo material/impressão da versão Auchan (vinil de chão 3M, offset 4/0). Sem passatempos/jogos de sorte.</t>
         </is>
       </c>
     </row>
@@ -31291,12 +31281,12 @@
       </c>
       <c r="F670" t="inlineStr">
         <is>
-          <t>Alarm Walk — Continente</t>
+          <t>Alarm Walk — Pingo Doce</t>
         </is>
       </c>
       <c r="G670" t="inlineStr">
         <is>
-          <t>600x100, 400x100 ou 250x100 cms; margem branco 1 cm</t>
+          <t>600x100, 400x100, 250x100 ou 180x100 cms; margem branco 1 cm</t>
         </is>
       </c>
       <c r="J670" t="inlineStr">
@@ -31306,7 +31296,7 @@
       </c>
       <c r="L670" t="inlineStr">
         <is>
-          <t>Mesmo material/impressão da versão Auchan (vinil de chão 3M, offset 4/0). Sem passatempos/jogos de sorte.</t>
+          <t>Mesmo material/impressão das restantes. Tem uma variante de tamanho extra (180x100) face a Auchan/Continente.</t>
         </is>
       </c>
     </row>
@@ -31333,12 +31323,12 @@
       </c>
       <c r="F671" t="inlineStr">
         <is>
-          <t>Alarm Walk — Pingo Doce</t>
+          <t>Cart Media — Continente</t>
         </is>
       </c>
       <c r="G671" t="inlineStr">
         <is>
-          <t>600x100, 400x100, 250x100 ou 180x100 cms; margem branco 1 cm</t>
+          <t>Tamanho total 32,2x69 cms; área visível 32,2x30,5 cms (frente e verso)</t>
         </is>
       </c>
       <c r="J671" t="inlineStr">
@@ -31348,7 +31338,7 @@
       </c>
       <c r="L671" t="inlineStr">
         <is>
-          <t>Mesmo material/impressão das restantes. Tem uma variante de tamanho extra (180x100) face a Auchan/Continente.</t>
+          <t>Material: polipropileno branco 0,5mm (PVC) 200 microns; offset UV 4/0 + verniz UV brilho. Cantos arredondados; criatividade em português.</t>
         </is>
       </c>
     </row>
@@ -31375,12 +31365,12 @@
       </c>
       <c r="F672" t="inlineStr">
         <is>
-          <t>Cart Media — Continente</t>
+          <t>Floor Media — Auchan</t>
         </is>
       </c>
       <c r="G672" t="inlineStr">
         <is>
-          <t>Tamanho total 32,2x69 cms; área visível 32,2x30,5 cms (frente e verso)</t>
+          <t>120x90 cms; margem branco 1 cm</t>
         </is>
       </c>
       <c r="J672" t="inlineStr">
@@ -31390,7 +31380,7 @@
       </c>
       <c r="L672" t="inlineStr">
         <is>
-          <t>Material: polipropileno branco 0,5mm (PVC) 200 microns; offset UV 4/0 + verniz UV brilho. Cantos arredondados; criatividade em português.</t>
+          <t>Material: vinil de chão autocolante opaco 3M, lâmina antideslizante MSM; offset 4/0. Incluir logo ISM; sem passatempos/jogos de sorte.</t>
         </is>
       </c>
     </row>
@@ -31417,7 +31407,7 @@
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>Floor Media — Auchan</t>
+          <t>Floor Media 120x90 — El Corte Inglês</t>
         </is>
       </c>
       <c r="G673" t="inlineStr">
@@ -31432,7 +31422,7 @@
       </c>
       <c r="L673" t="inlineStr">
         <is>
-          <t>Material: vinil de chão autocolante opaco 3M, lâmina antideslizante MSM; offset 4/0. Incluir logo ISM; sem passatempos/jogos de sorte.</t>
+          <t>Mesmas especificações de material/impressão da versão Auchan.</t>
         </is>
       </c>
     </row>
@@ -31459,12 +31449,12 @@
       </c>
       <c r="F674" t="inlineStr">
         <is>
-          <t>Floor Media 120x90 — El Corte Inglês</t>
+          <t>Floor Media 90x60 — Continente</t>
         </is>
       </c>
       <c r="G674" t="inlineStr">
         <is>
-          <t>120x90 cms; margem branco 1 cm</t>
+          <t>90x60 cms; margem branco 1 cm</t>
         </is>
       </c>
       <c r="J674" t="inlineStr">
@@ -31474,7 +31464,7 @@
       </c>
       <c r="L674" t="inlineStr">
         <is>
-          <t>Mesmas especificações de material/impressão da versão Auchan.</t>
+          <t>Mesma produção/material das restantes Floor Media.</t>
         </is>
       </c>
     </row>
@@ -31501,12 +31491,12 @@
       </c>
       <c r="F675" t="inlineStr">
         <is>
-          <t>Floor Media 90x60 — Continente</t>
+          <t>Floor Media XXL — Continente</t>
         </is>
       </c>
       <c r="G675" t="inlineStr">
         <is>
-          <t>90x60 cms; margem branco 1 cm</t>
+          <t>200x100 cms; margem branco 1 cm</t>
         </is>
       </c>
       <c r="J675" t="inlineStr">
@@ -31516,7 +31506,7 @@
       </c>
       <c r="L675" t="inlineStr">
         <is>
-          <t>Mesma produção/material das restantes Floor Media.</t>
+          <t>Material: vinil de chão autocolante opaco 3M; offset 4/0. Incluir logo ISM.</t>
         </is>
       </c>
     </row>
@@ -31543,12 +31533,12 @@
       </c>
       <c r="F676" t="inlineStr">
         <is>
-          <t>Floor Media XXL — Continente</t>
+          <t>Floor Media — Pingo Doce</t>
         </is>
       </c>
       <c r="G676" t="inlineStr">
         <is>
-          <t>200x100 cms; margem branco 1 cm</t>
+          <t>120x90 cms (Hipermercados) ou 90x60 cms (Supermercados); margem branco 1 cm</t>
         </is>
       </c>
       <c r="J676" t="inlineStr">
@@ -31558,7 +31548,7 @@
       </c>
       <c r="L676" t="inlineStr">
         <is>
-          <t>Material: vinil de chão autocolante opaco 3M; offset 4/0. Incluir logo ISM.</t>
+          <t>Vinil de chão autocolante opaco 3M, lâmina antideslizante; offset 4/0. Incluir logo ISM; cantos arredondados.</t>
         </is>
       </c>
     </row>
@@ -31585,22 +31575,22 @@
       </c>
       <c r="F677" t="inlineStr">
         <is>
-          <t>Floor Media — Pingo Doce</t>
+          <t>Frame Media Congelados</t>
         </is>
       </c>
       <c r="G677" t="inlineStr">
         <is>
-          <t>120x90 cms (Hipermercados) ou 90x60 cms (Supermercados); margem branco 1 cm</t>
+          <t>7 tiras de 7x100cm (área total 7cm x várias metragens, depende do perímetro da arca)</t>
         </is>
       </c>
       <c r="J677" t="inlineStr">
         <is>
-          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1</t>
+          <t>Adobe Illustrator (aberto, sem bleed); CMYK; resolução mín. 150 DPI à escala 1:1</t>
         </is>
       </c>
       <c r="L677" t="inlineStr">
         <is>
-          <t>Vinil de chão autocolante opaco 3M, lâmina antideslizante; offset 4/0. Incluir logo ISM; cantos arredondados.</t>
+          <t>Material: vinil removível, digital 4/0. Criatividade contínua nas tiras (perímetros não uniformes, pode requerer corte). Recomenda-se só logo ou imagem do produto.</t>
         </is>
       </c>
     </row>
@@ -31627,12 +31617,12 @@
       </c>
       <c r="F678" t="inlineStr">
         <is>
-          <t>Frame Media Congelados</t>
+          <t>Sticker Freezer</t>
         </is>
       </c>
       <c r="G678" t="inlineStr">
         <is>
-          <t>7 tiras de 7x100cm (área total 7cm x várias metragens, depende do perímetro da arca)</t>
+          <t>16x16 cms</t>
         </is>
       </c>
       <c r="J678" t="inlineStr">
@@ -31642,7 +31632,7 @@
       </c>
       <c r="L678" t="inlineStr">
         <is>
-          <t>Material: vinil removível, digital 4/0. Criatividade contínua nas tiras (perímetros não uniformes, pode requerer corte). Recomenda-se só logo ou imagem do produto.</t>
+          <t>Material: vinil removível, digital 4/0. Criatividade contínua nas tiras (arcas não uniformes, pode requerer corte). Entrega: 1 mês antes para validação, 2 semanas antes para AF.</t>
         </is>
       </c>
     </row>
@@ -31669,22 +31659,27 @@
       </c>
       <c r="F679" t="inlineStr">
         <is>
-          <t>Sticker Freezer</t>
+          <t>Live Markets — Auchan</t>
         </is>
       </c>
       <c r="G679" t="inlineStr">
         <is>
-          <t>16x16 cms</t>
+          <t>1080x1920 px</t>
+        </is>
+      </c>
+      <c r="I679" t="inlineStr">
+        <is>
+          <t>Máx. 25 MB</t>
         </is>
       </c>
       <c r="J679" t="inlineStr">
         <is>
-          <t>Adobe Illustrator (aberto, sem bleed); CMYK; resolução mín. 150 DPI à escala 1:1</t>
+          <t>WMV ou MP4, sem áudio</t>
         </is>
       </c>
       <c r="L679" t="inlineStr">
         <is>
-          <t>Material: vinil removível, digital 4/0. Criatividade contínua nas tiras (arcas não uniformes, pode requerer corte). Entrega: 1 mês antes para validação, 2 semanas antes para AF.</t>
+          <t>Duração 10 seg. Emissão só após validação ISM; entrega até 5 dias antes do início da campanha.</t>
         </is>
       </c>
     </row>
@@ -31711,12 +31706,12 @@
       </c>
       <c r="F680" t="inlineStr">
         <is>
-          <t>Live Markets — Auchan</t>
+          <t>Live Markets — Continente</t>
         </is>
       </c>
       <c r="G680" t="inlineStr">
         <is>
-          <t>1080x1920 px</t>
+          <t>LCDs Samsung 65"; 1080x1920 px</t>
         </is>
       </c>
       <c r="I680" t="inlineStr">
@@ -31726,12 +31721,12 @@
       </c>
       <c r="J680" t="inlineStr">
         <is>
-          <t>WMV ou MP4, sem áudio</t>
+          <t>MP4, codec H264, 25 fps, sem áudio</t>
         </is>
       </c>
       <c r="L680" t="inlineStr">
         <is>
-          <t>Duração 10 seg. Emissão só após validação ISM; entrega até 5 dias antes do início da campanha.</t>
+          <t>Duração 10 seg. Criatividade em português. Entrega: 15 dias antes do início da campanha.</t>
         </is>
       </c>
     </row>
@@ -31758,27 +31753,27 @@
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>Live Markets — Continente</t>
+          <t>Live Markets — E.Leclerc</t>
         </is>
       </c>
       <c r="G681" t="inlineStr">
         <is>
-          <t>LCDs Samsung 65"; 1080x1920 px</t>
+          <t>LCDs 55"; 720x1280 px</t>
         </is>
       </c>
       <c r="I681" t="inlineStr">
         <is>
-          <t>Máx. 25 MB</t>
+          <t>Máx. 25 MB; vídeo &lt; 4000 kbps</t>
         </is>
       </c>
       <c r="J681" t="inlineStr">
         <is>
-          <t>MP4, codec H264, 25 fps, sem áudio</t>
+          <t>AVI, MOV ou MP4, 25 fps, sem áudio</t>
         </is>
       </c>
       <c r="L681" t="inlineStr">
         <is>
-          <t>Duração 10 seg. Criatividade em português. Entrega: 15 dias antes do início da campanha.</t>
+          <t>Duração 10 seg. Resolução/ecrã diferentes das restantes Live Markets (720x1280 vs. 1080x1920). Entrega: 15 dias antes do início da campanha.</t>
         </is>
       </c>
     </row>
@@ -31805,27 +31800,27 @@
       </c>
       <c r="F682" t="inlineStr">
         <is>
-          <t>Live Markets — E.Leclerc</t>
+          <t>Live Markets — Pingo Doce</t>
         </is>
       </c>
       <c r="G682" t="inlineStr">
         <is>
-          <t>LCDs 55"; 720x1280 px</t>
+          <t>1080x1920, 1080x1634, 1080x1374, 1355x1080, 1355x982 ou 1920x1080 px</t>
         </is>
       </c>
       <c r="I682" t="inlineStr">
         <is>
-          <t>Máx. 25 MB; vídeo &lt; 4000 kbps</t>
+          <t>Máx. 25 MB</t>
         </is>
       </c>
       <c r="J682" t="inlineStr">
         <is>
-          <t>AVI, MOV ou MP4, 25 fps, sem áudio</t>
+          <t>MP4, codec H264, 25 fps, sem áudio</t>
         </is>
       </c>
       <c r="L682" t="inlineStr">
         <is>
-          <t>Duração 10 seg. Resolução/ecrã diferentes das restantes Live Markets (720x1280 vs. 1080x1920). Entrega: 15 dias antes do início da campanha.</t>
+          <t>Duração 10 seg. Conteúdo deve ser animado (não estático). LCDs Samsung. Entrega: 15 dias antes do início da campanha.</t>
         </is>
       </c>
     </row>
@@ -31852,12 +31847,12 @@
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>Live Markets — Pingo Doce</t>
+          <t>Live Matosinhos — Continente</t>
         </is>
       </c>
       <c r="G683" t="inlineStr">
         <is>
-          <t>1080x1920, 1080x1634, 1080x1374, 1355x1080, 1355x982 ou 1920x1080 px</t>
+          <t>Painel físico 5,76x4,8m; resolução 1008x576 px</t>
         </is>
       </c>
       <c r="I683" t="inlineStr">
@@ -31872,7 +31867,7 @@
       </c>
       <c r="L683" t="inlineStr">
         <is>
-          <t>Duração 10 seg. Conteúdo deve ser animado (não estático). LCDs Samsung. Entrega: 15 dias antes do início da campanha.</t>
+          <t>Duração 10 seg. Écran exterior/totem de grande formato em localização específica (Matosinhos). Entrega: 15 dias antes do início da campanha.</t>
         </is>
       </c>
     </row>
@@ -31899,12 +31894,12 @@
       </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>Live Matosinhos — Continente</t>
+          <t>Mupis Digitais — Pingo Doce</t>
         </is>
       </c>
       <c r="G684" t="inlineStr">
         <is>
-          <t>Painel físico 5,76x4,8m; resolução 1008x576 px</t>
+          <t>1080x1920, 1080x1634, 1080x1374, 1355x1080, 1355x982 ou 1920x1080 px</t>
         </is>
       </c>
       <c r="I684" t="inlineStr">
@@ -31919,7 +31914,7 @@
       </c>
       <c r="L684" t="inlineStr">
         <is>
-          <t>Duração 10 seg. Écran exterior/totem de grande formato em localização específica (Matosinhos). Entrega: 15 dias antes do início da campanha.</t>
+          <t>Duração 10 seg. Entrega: 15 dias antes do início da campanha.</t>
         </is>
       </c>
     </row>
@@ -31946,27 +31941,22 @@
       </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>Mupis Digitais — Pingo Doce</t>
+          <t>Mupi (retroiluminado) — Pingo Doce</t>
         </is>
       </c>
       <c r="G685" t="inlineStr">
         <is>
-          <t>1080x1920, 1080x1634, 1080x1374, 1355x1080, 1355x982 ou 1920x1080 px</t>
-        </is>
-      </c>
-      <c r="I685" t="inlineStr">
-        <is>
-          <t>Máx. 25 MB</t>
+          <t>Tamanho total 120x176 cm; área visível 107x159 cms</t>
         </is>
       </c>
       <c r="J685" t="inlineStr">
         <is>
-          <t>MP4, codec H264, 25 fps, sem áudio</t>
+          <t>Resolução 300 DPI, escala real 1:1</t>
         </is>
       </c>
       <c r="L685" t="inlineStr">
         <is>
-          <t>Duração 10 seg. Entrega: 15 dias antes do início da campanha.</t>
+          <t>Material: papel especial para luz, 135 gr (mupi retroiluminado físico, distinto do digital). Arte Final em português.</t>
         </is>
       </c>
     </row>
@@ -31993,22 +31983,22 @@
       </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>Mupi (retroiluminado) — Pingo Doce</t>
+          <t>Digital Mupis — Auchan</t>
         </is>
       </c>
       <c r="G686" t="inlineStr">
         <is>
-          <t>Tamanho total 120x176 cm; área visível 107x159 cms</t>
+          <t>1080x1920 px</t>
         </is>
       </c>
       <c r="J686" t="inlineStr">
         <is>
-          <t>Resolução 300 DPI, escala real 1:1</t>
+          <t>WMV ou MP4</t>
         </is>
       </c>
       <c r="L686" t="inlineStr">
         <is>
-          <t>Material: papel especial para luz, 135 gr (mupi retroiluminado físico, distinto do digital). Arte Final em português.</t>
+          <t>Duração 10 seg. Filme em português ou legendado/traduzido. Entrega 5 dias antes; emissão só após validação ISM.</t>
         </is>
       </c>
     </row>
@@ -32035,22 +32025,22 @@
       </c>
       <c r="F687" t="inlineStr">
         <is>
-          <t>Digital Mupis — Auchan</t>
+          <t>Passadeira Vinil</t>
         </is>
       </c>
       <c r="G687" t="inlineStr">
         <is>
-          <t>1080x1920 px</t>
+          <t>Total 16mts; módulos centrais 100x200cm (x7); módulos início/fim 100x100cm (x2)</t>
         </is>
       </c>
       <c r="J687" t="inlineStr">
         <is>
-          <t>WMV ou MP4</t>
+          <t>Resolução 300 DPI, escala real 1:1</t>
         </is>
       </c>
       <c r="L687" t="inlineStr">
         <is>
-          <t>Duração 10 seg. Filme em português ou legendado/traduzido. Entrega 5 dias antes; emissão só após validação ISM.</t>
+          <t>Material: vinil de chão removível com lâmina antideslizante; digital 4/0. Imagens início/fim iguais entre si (idem para as centrais); não usar fundo branco nem preto; incluir logo ISM no início e fim.</t>
         </is>
       </c>
     </row>
@@ -32077,22 +32067,27 @@
       </c>
       <c r="F688" t="inlineStr">
         <is>
-          <t>Passadeira Vinil</t>
+          <t>Stopper Digital</t>
         </is>
       </c>
       <c r="G688" t="inlineStr">
         <is>
-          <t>Total 16mts; módulos centrais 100x200cm (x7); módulos início/fim 100x100cm (x2)</t>
+          <t>Ecrã LCD 15"; 1080x1920 px</t>
+        </is>
+      </c>
+      <c r="I688" t="inlineStr">
+        <is>
+          <t>Máx. 25 MB</t>
         </is>
       </c>
       <c r="J688" t="inlineStr">
         <is>
-          <t>Resolução 300 DPI, escala real 1:1</t>
+          <t>MP4, codec H264, 25 fps, sem áudio</t>
         </is>
       </c>
       <c r="L688" t="inlineStr">
         <is>
-          <t>Material: vinil de chão removível com lâmina antideslizante; digital 4/0. Imagens início/fim iguais entre si (idem para as centrais); não usar fundo branco nem preto; incluir logo ISM no início e fim.</t>
+          <t>Duração 10 seg. Entrega: 15 dias antes do início da campanha.</t>
         </is>
       </c>
     </row>
@@ -32119,27 +32114,22 @@
       </c>
       <c r="F689" t="inlineStr">
         <is>
-          <t>Stopper Digital</t>
+          <t>Stopper-Media Max</t>
         </is>
       </c>
       <c r="G689" t="inlineStr">
         <is>
-          <t>Ecrã LCD 15"; 1080x1920 px</t>
-        </is>
-      </c>
-      <c r="I689" t="inlineStr">
-        <is>
-          <t>Máx. 25 MB</t>
+          <t>Área total 20,4x40,4 cms; área visível 19,2x39,2 cms; sangria 1,2 cms</t>
         </is>
       </c>
       <c r="J689" t="inlineStr">
         <is>
-          <t>MP4, codec H264, 25 fps, sem áudio</t>
+          <t>Qualquer formato suportado pelo Adobe; resolução 1080 DPI à escala real, 300 microns</t>
         </is>
       </c>
       <c r="L689" t="inlineStr">
         <is>
-          <t>Duração 10 seg. Entrega: 15 dias antes do início da campanha.</t>
+          <t>Material: PVC eco branco/mate; digital 4/0. Evitar textos/logos/numeração perto do corte.</t>
         </is>
       </c>
     </row>
@@ -32166,12 +32156,12 @@
       </c>
       <c r="F690" t="inlineStr">
         <is>
-          <t>Stopper-Media Max</t>
+          <t>Stopper-Media Max XXL</t>
         </is>
       </c>
       <c r="G690" t="inlineStr">
         <is>
-          <t>Área total 20,4x40,4 cms; área visível 19,2x39,2 cms; sangria 1,2 cms</t>
+          <t>Área total 60,4x20,4 cms; área visível 59,2x19,2 cms; sangria 1,2 cms</t>
         </is>
       </c>
       <c r="J690" t="inlineStr">
@@ -32181,7 +32171,7 @@
       </c>
       <c r="L690" t="inlineStr">
         <is>
-          <t>Material: PVC eco branco/mate; digital 4/0. Evitar textos/logos/numeração perto do corte.</t>
+          <t>Material: PVC eco branco/mate; digital 4/0. Mesmas recomendações de corte que o Stopper-Media Max (tamanho normal).</t>
         </is>
       </c>
     </row>
@@ -32208,22 +32198,22 @@
       </c>
       <c r="F691" t="inlineStr">
         <is>
-          <t>Stopper-Media Max XXL</t>
+          <t>Stopper Media LED 200x800</t>
         </is>
       </c>
       <c r="G691" t="inlineStr">
         <is>
-          <t>Área total 60,4x20,4 cms; área visível 59,2x19,2 cms; sangria 1,2 cms</t>
+          <t>Tamanho total 221x800mm; área visível 200x800mm; raio de canto R=40mm</t>
         </is>
       </c>
       <c r="J691" t="inlineStr">
         <is>
-          <t>Qualquer formato suportado pelo Adobe; resolução 1080 DPI à escala real, 300 microns</t>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução 1080 DPI à escala real, 300 microns</t>
         </is>
       </c>
       <c r="L691" t="inlineStr">
         <is>
-          <t>Material: PVC eco branco/mate; digital 4/0. Mesmas recomendações de corte que o Stopper-Media Max (tamanho normal).</t>
+          <t>Material: PMMA gravado (Easydot); digital 4/4. Saída de cabo na zona superior; pinça única com peças 3D. Evitar elementos perto do corte.</t>
         </is>
       </c>
     </row>
@@ -32250,22 +32240,27 @@
       </c>
       <c r="F692" t="inlineStr">
         <is>
-          <t>Stopper Media LED 200x800</t>
+          <t>Top Banner (FMCG)</t>
         </is>
       </c>
       <c r="G692" t="inlineStr">
         <is>
-          <t>Tamanho total 221x800mm; área visível 200x800mm; raio de canto R=40mm</t>
+          <t>768x216 px</t>
+        </is>
+      </c>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>Máx. 25 MB</t>
         </is>
       </c>
       <c r="J692" t="inlineStr">
         <is>
-          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução 1080 DPI à escala real, 300 microns</t>
+          <t>MP4, codec H264, sem áudio</t>
         </is>
       </c>
       <c r="L692" t="inlineStr">
         <is>
-          <t>Material: PMMA gravado (Easydot); digital 4/4. Saída de cabo na zona superior; pinça única com peças 3D. Evitar elementos perto do corte.</t>
+          <t>Duração 10 seg. Bitrate recomendado 10 Mbps. Entrega 5 dias antes; emissão só após validação ISM. Formato genérico, sem retalhista específico.</t>
         </is>
       </c>
     </row>
@@ -32292,27 +32287,22 @@
       </c>
       <c r="F693" t="inlineStr">
         <is>
-          <t>Top Banner (FMCG)</t>
+          <t>Mupi Papel — El Corte Inglês</t>
         </is>
       </c>
       <c r="G693" t="inlineStr">
         <is>
-          <t>768x216 px</t>
-        </is>
-      </c>
-      <c r="I693" t="inlineStr">
-        <is>
-          <t>Máx. 25 MB</t>
+          <t>Tamanho total 120x176 cms; área visível 107x159 cms</t>
         </is>
       </c>
       <c r="J693" t="inlineStr">
         <is>
-          <t>MP4, codec H264, sem áudio</t>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1</t>
         </is>
       </c>
       <c r="L693" t="inlineStr">
         <is>
-          <t>Duração 10 seg. Bitrate recomendado 10 Mbps. Entrega 5 dias antes; emissão só após validação ISM. Formato genérico, sem retalhista específico.</t>
+          <t>Material: papel especial para luz, 135 gr; impressão quadricromia, Offset ou Digital. Criatividade em português. Entrega: 10 dias antes do início da campanha.</t>
         </is>
       </c>
     </row>
@@ -32339,22 +32329,17 @@
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>Mupi Papel — El Corte Inglês</t>
+          <t>Elevadores — El Corte Inglês Gaia</t>
         </is>
       </c>
       <c r="G694" t="inlineStr">
         <is>
-          <t>Tamanho total 120x176 cms; área visível 107x159 cms</t>
-        </is>
-      </c>
-      <c r="J694" t="inlineStr">
-        <is>
-          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1</t>
+          <t>Portas exteriores: largura total 99,5cm (2 painéis de 38,5cm + faixas de 5/7,5cm); altura total 209,5cm (área útil 194,5cm). Loja: 13 pisos x 3 elevadores = 39 faces.</t>
         </is>
       </c>
       <c r="L694" t="inlineStr">
         <is>
-          <t>Material: papel especial para luz, 135 gr; impressão quadricromia, Offset ou Digital. Criatividade em português. Entrega: 10 dias antes do início da campanha.</t>
+          <t>Documento disponível é só de logística de instalação, não uma ficha técnica de produção completa — sem resolução, DPI, formato de ficheiro, peso máximo ou prazo de entrega indicados. Opções de corte do vinil: (1) criatividade única cortada em 2 partes; (2) duas criatividades separadas, uma por porta; (3) criatividade com friso central incluído. Confirmar specs de produção com a In-Store Media antes de fechar o pedido.</t>
         </is>
       </c>
     </row>
@@ -32381,17 +32366,27 @@
       </c>
       <c r="F695" t="inlineStr">
         <is>
-          <t>Elevadores — El Corte Inglês Gaia</t>
+          <t>Mupis Digitais — El Corte Inglês</t>
         </is>
       </c>
       <c r="G695" t="inlineStr">
         <is>
-          <t>Portas exteriores: largura total 99,5cm (2 painéis de 38,5cm + faixas de 5/7,5cm); altura total 209,5cm (área útil 194,5cm). Loja: 13 pisos x 3 elevadores = 39 faces.</t>
+          <t>1080x1920 px</t>
+        </is>
+      </c>
+      <c r="I695" t="inlineStr">
+        <is>
+          <t>Máx. 25 MB</t>
+        </is>
+      </c>
+      <c r="J695" t="inlineStr">
+        <is>
+          <t>MP4 ou WMV, codec H264, sem áudio</t>
         </is>
       </c>
       <c r="L695" t="inlineStr">
         <is>
-          <t>Documento disponível é só de logística de instalação, não uma ficha técnica de produção completa — sem resolução, DPI, formato de ficheiro, peso máximo ou prazo de entrega indicados. Opções de corte do vinil: (1) criatividade única cortada em 2 partes; (2) duas criatividades separadas, uma por porta; (3) criatividade com friso central incluído. Confirmar specs de produção com a In-Store Media antes de fechar o pedido.</t>
+          <t>Duração 10 seg. Material: ecrã LED; criatividade em português. Entrega: 15 dias antes do início da campanha. Nota: um dos documentos de origem indicava a nomenclatura de ficheiro "1060X3840", que não bate com a resolução declarada (1080x1920) — reportado tal como consta, sem correção.</t>
         </is>
       </c>
     </row>
@@ -32418,12 +32413,12 @@
       </c>
       <c r="F696" t="inlineStr">
         <is>
-          <t>Mupis Digitais — El Corte Inglês</t>
+          <t>Hall Media Digital — El Corte Inglês</t>
         </is>
       </c>
       <c r="G696" t="inlineStr">
         <is>
-          <t>1080x1920 px</t>
+          <t>666x1920 px</t>
         </is>
       </c>
       <c r="I696" t="inlineStr">
@@ -32433,12 +32428,12 @@
       </c>
       <c r="J696" t="inlineStr">
         <is>
-          <t>MP4 ou WMV, codec H264, sem áudio</t>
+          <t>MP4, codec H264, 25 fps</t>
         </is>
       </c>
       <c r="L696" t="inlineStr">
         <is>
-          <t>Duração 10 seg. Material: ecrã LED; criatividade em português. Entrega: 15 dias antes do início da campanha. Nota: um dos documentos de origem indicava a nomenclatura de ficheiro "1060X3840", que não bate com a resolução declarada (1080x1920) — reportado tal como consta, sem correção.</t>
+          <t>Duração 10 seg. Bitrate recomendado 10 Mbps. Nomenclatura: "Anunciante"-HALL-666X1920.mp4. Criatividade em português, sem áudio. Entrega: 15 dias antes do início da campanha.</t>
         </is>
       </c>
     </row>
@@ -32465,27 +32460,27 @@
       </c>
       <c r="F697" t="inlineStr">
         <is>
-          <t>Hall Media Digital — El Corte Inglês</t>
+          <t>Live Markets (Circuito Digital) — El Corte Inglês Lisboa</t>
         </is>
       </c>
       <c r="G697" t="inlineStr">
         <is>
-          <t>666x1920 px</t>
+          <t>Ecrã 42"; 1920x1080 px</t>
         </is>
       </c>
       <c r="I697" t="inlineStr">
         <is>
-          <t>Máx. 25 MB</t>
+          <t>Máx. 25 MB (produzido pelo cliente)</t>
         </is>
       </c>
       <c r="J697" t="inlineStr">
         <is>
-          <t>MP4, codec H264, 25 fps</t>
+          <t>WMV ou MP4 (cliente); PSD/AI/INDD/PDF, imagens &gt;150dpi, texto em curvas (produção ISM)</t>
         </is>
       </c>
       <c r="L697" t="inlineStr">
         <is>
-          <t>Duração 10 seg. Bitrate recomendado 10 Mbps. Nomenclatura: "Anunciante"-HALL-666X1920.mp4. Criatividade em português, sem áudio. Entrega: 15 dias antes do início da campanha.</t>
+          <t>Duração 8 a 10 seg (produzido pelo cliente). Emissão só após validação da criatividade pela ISM. Produção ISM: entrega 13 dias antes. Produzido pelo cliente: entrega 5 dias antes. Criatividade em português.</t>
         </is>
       </c>
     </row>
@@ -32512,12 +32507,12 @@
       </c>
       <c r="F698" t="inlineStr">
         <is>
-          <t>Live Markets (Circuito Digital) — El Corte Inglês Lisboa</t>
+          <t>Live Markets (Circuito Digital) — El Corte Inglês Gaia</t>
         </is>
       </c>
       <c r="G698" t="inlineStr">
         <is>
-          <t>Ecrã 42"; 1920x1080 px</t>
+          <t>Ecrã 55"; 1920x1080 px</t>
         </is>
       </c>
       <c r="I698" t="inlineStr">
@@ -32559,27 +32554,22 @@
       </c>
       <c r="F699" t="inlineStr">
         <is>
-          <t>Live Markets (Circuito Digital) — El Corte Inglês Gaia</t>
+          <t>Stairs Backlights — El Corte Inglês (Espanha)</t>
         </is>
       </c>
       <c r="G699" t="inlineStr">
         <is>
-          <t>Ecrã 55"; 1920x1080 px</t>
-        </is>
-      </c>
-      <c r="I699" t="inlineStr">
-        <is>
-          <t>Máx. 25 MB (produzido pelo cliente)</t>
+          <t>78x108 cms</t>
         </is>
       </c>
       <c r="J699" t="inlineStr">
         <is>
-          <t>WMV ou MP4 (cliente); PSD/AI/INDD/PDF, imagens &gt;150dpi, texto em curvas (produção ISM)</t>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:5 + 0,5cm de sangria</t>
         </is>
       </c>
       <c r="L699" t="inlineStr">
         <is>
-          <t>Duração 8 a 10 seg (produzido pelo cliente). Emissão só após validação da criatividade pela ISM. Produção ISM: entrega 13 dias antes. Produzido pelo cliente: entrega 5 dias antes. Criatividade em português.</t>
+          <t>Material: white back paper 150 grs, corte simples; offset 4/0. Criatividade em português. Entrega: 10 dias antes do início da campanha. Atenção: o documento identifica o mercado como "In-Store Media España" — confirmar se este formato se aplica às lojas portuguesas (Gaia/Lisboa) ou se é exclusivo de Espanha antes de o usar num pedido.</t>
         </is>
       </c>
     </row>
@@ -32606,22 +32596,22 @@
       </c>
       <c r="F700" t="inlineStr">
         <is>
-          <t>Stairs Backlights — El Corte Inglês (Espanha)</t>
+          <t>Elevadores — El Corte Inglês Lisboa</t>
         </is>
       </c>
       <c r="G700" t="inlineStr">
         <is>
-          <t>78x108 cms</t>
+          <t>150x220 cms</t>
         </is>
       </c>
       <c r="J700" t="inlineStr">
         <is>
-          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:5 + 0,5cm de sangria</t>
+          <t>Freehand, Adobe Illustrator ou Corel Draw (paginação); PSD aceite com layers separados e AFs em aberto; CMYK (enviar pantones); resolução mín. 720 DPI à escala 1:10 ou 72 DPI à escala real</t>
         </is>
       </c>
       <c r="L700" t="inlineStr">
         <is>
-          <t>Material: white back paper 150 grs, corte simples; offset 4/0. Criatividade em português. Entrega: 10 dias antes do início da campanha. Atenção: o documento identifica o mercado como "In-Store Media España" — confirmar se este formato se aplica às lojas portuguesas (Gaia/Lisboa) ou se é exclusivo de Espanha antes de o usar num pedido.</t>
+          <t>Material: vinil monomérico com brilho, adesivo removível; impressão tintas low solvent 720 DPI + laminação brilho. Textos convertidos em vetorial. Criatividade em português. Entrega: 10 dias antes do início da campanha.</t>
         </is>
       </c>
     </row>
@@ -32648,22 +32638,27 @@
       </c>
       <c r="F701" t="inlineStr">
         <is>
-          <t>Elevadores — El Corte Inglês Lisboa</t>
+          <t>Montra Digital — El Corte Inglês Gaia</t>
         </is>
       </c>
       <c r="G701" t="inlineStr">
         <is>
-          <t>150x220 cms</t>
+          <t>1248x2212 px</t>
+        </is>
+      </c>
+      <c r="I701" t="inlineStr">
+        <is>
+          <t>Máx. 25 MB</t>
         </is>
       </c>
       <c r="J701" t="inlineStr">
         <is>
-          <t>Freehand, Adobe Illustrator ou Corel Draw (paginação); PSD aceite com layers separados e AFs em aberto; CMYK (enviar pantones); resolução mín. 720 DPI à escala 1:10 ou 72 DPI à escala real</t>
+          <t>MP4, codec H264, 25 fps</t>
         </is>
       </c>
       <c r="L701" t="inlineStr">
         <is>
-          <t>Material: vinil monomérico com brilho, adesivo removível; impressão tintas low solvent 720 DPI + laminação brilho. Textos convertidos em vetorial. Criatividade em português. Entrega: 10 dias antes do início da campanha.</t>
+          <t>Duração 10 seg. Bitrate recomendado 10 Mbps. Nomenclatura: "Anunciante"-MONTRA.GAIA-1248X2212.mp4. Sem áudio, criatividade em português. Entrega: 15 dias antes do início da campanha.</t>
         </is>
       </c>
     </row>
@@ -32690,12 +32685,12 @@
       </c>
       <c r="F702" t="inlineStr">
         <is>
-          <t>Montra Digital — El Corte Inglês Gaia</t>
+          <t>Lona Gigante Digital — El Corte Inglês Lisboa</t>
         </is>
       </c>
       <c r="G702" t="inlineStr">
         <is>
-          <t>1248x2212 px</t>
+          <t>Ecrã físico 18,7x10,6m; resolução 1920x1080 px</t>
         </is>
       </c>
       <c r="I702" t="inlineStr">
@@ -32705,12 +32700,12 @@
       </c>
       <c r="J702" t="inlineStr">
         <is>
-          <t>MP4, codec H264, 25 fps</t>
+          <t>WMV ou MP4, codec H264, 25 fps</t>
         </is>
       </c>
       <c r="L702" t="inlineStr">
         <is>
-          <t>Duração 10 seg. Bitrate recomendado 10 Mbps. Nomenclatura: "Anunciante"-MONTRA.GAIA-1248X2212.mp4. Sem áudio, criatividade em português. Entrega: 15 dias antes do início da campanha.</t>
+          <t>Duração 10 seg. Material: ecrã LED de 198m². Sem áudio, criatividade em português. Entrega: 15 dias antes do início da campanha.</t>
         </is>
       </c>
     </row>
@@ -32737,27 +32732,22 @@
       </c>
       <c r="F703" t="inlineStr">
         <is>
-          <t>Lona Gigante Digital — El Corte Inglês Lisboa</t>
+          <t>Banners de Exterior — El Corte Inglês</t>
         </is>
       </c>
       <c r="G703" t="inlineStr">
         <is>
-          <t>Ecrã físico 18,7x10,6m; resolução 1920x1080 px</t>
-        </is>
-      </c>
-      <c r="I703" t="inlineStr">
-        <is>
-          <t>Máx. 25 MB</t>
+          <t>100x300 cms</t>
         </is>
       </c>
       <c r="J703" t="inlineStr">
         <is>
-          <t>WMV ou MP4, codec H264, 25 fps</t>
+          <t>Adobe Illustrator (AI); resolução mín. 300 DPI à escala 1:1</t>
         </is>
       </c>
       <c r="L703" t="inlineStr">
         <is>
-          <t>Duração 10 seg. Material: ecrã LED de 198m². Sem áudio, criatividade em português. Entrega: 15 dias antes do início da campanha.</t>
+          <t>Material: tela blockout com ilhoses; impressão tintas UV ou low solvents. Evitar mensagens nos extremos. Criatividade em português. Entrega: 15 dias antes do início da campanha.</t>
         </is>
       </c>
     </row>
@@ -32784,22 +32774,27 @@
       </c>
       <c r="F704" t="inlineStr">
         <is>
-          <t>Banners de Exterior — El Corte Inglês</t>
+          <t>Montra Digital — El Corte Inglês Lisboa</t>
         </is>
       </c>
       <c r="G704" t="inlineStr">
         <is>
-          <t>100x300 cms</t>
+          <t>Ecrã físico 400x450cm; resolução 1600x1800 px</t>
+        </is>
+      </c>
+      <c r="I704" t="inlineStr">
+        <is>
+          <t>Máx. 25 MB</t>
         </is>
       </c>
       <c r="J704" t="inlineStr">
         <is>
-          <t>Adobe Illustrator (AI); resolução mín. 300 DPI à escala 1:1</t>
+          <t>MP4, codec H264, 25 fps</t>
         </is>
       </c>
       <c r="L704" t="inlineStr">
         <is>
-          <t>Material: tela blockout com ilhoses; impressão tintas UV ou low solvents. Evitar mensagens nos extremos. Criatividade em português. Entrega: 15 dias antes do início da campanha.</t>
+          <t>Duração 10 seg. Bitrate recomendado 10 Mbps. Nomenclatura: "Anunciante"-MONTRA.LISBOA-1600X1800.mp4. Sem áudio, criatividade em português. Entrega: 15 dias antes do início da campanha.</t>
         </is>
       </c>
     </row>
@@ -32816,37 +32811,32 @@
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>In-Store Media</t>
+          <t>CSOutdoors</t>
         </is>
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>In-Store Media</t>
+          <t>CSOutdoors</t>
         </is>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>Montra Digital — El Corte Inglês Lisboa</t>
+          <t>Outdoor 21x5</t>
         </is>
       </c>
       <c r="G705" t="inlineStr">
         <is>
-          <t>Ecrã físico 400x450cm; resolução 1600x1800 px</t>
-        </is>
-      </c>
-      <c r="I705" t="inlineStr">
-        <is>
-          <t>Máx. 25 MB</t>
+          <t>Área de impressão: 21x5m (escala 1:10, 210x50cm). Área de conteúdo relevante: 20,60x4,70m.</t>
         </is>
       </c>
       <c r="J705" t="inlineStr">
         <is>
-          <t>MP4, codec H264, 25 fps</t>
+          <t>PDF, JPG, TIF, CDR ou AI</t>
         </is>
       </c>
       <c r="L705" t="inlineStr">
         <is>
-          <t>Duração 10 seg. Bitrate recomendado 10 Mbps. Nomenclatura: "Anunciante"-MONTRA.LISBOA-1600X1800.mp4. Sem áudio, criatividade em português. Entrega: 15 dias antes do início da campanha.</t>
+          <t>Imagem à escala 1:10. Resolução recomendada: 300dpi. Ficheiro em CMYK. Enviar fontes ou converter textos em curvas. Incluir um JPG para visualização. Enviar por email, pen ou CD.</t>
         </is>
       </c>
     </row>
@@ -32873,12 +32863,12 @@
       </c>
       <c r="F706" t="inlineStr">
         <is>
-          <t>Outdoor 21x5</t>
+          <t>Outdoor 32x5</t>
         </is>
       </c>
       <c r="G706" t="inlineStr">
         <is>
-          <t>Área de impressão: 21x5m (escala 1:10, 210x50cm). Área de conteúdo relevante: 20,60x4,70m.</t>
+          <t>Área de impressão: 32,12x5,04m (escala 1:10, 321,2x50,4cm). Área de conteúdo relevante: 31,8x4,8m.</t>
         </is>
       </c>
       <c r="J706" t="inlineStr">
@@ -32915,12 +32905,12 @@
       </c>
       <c r="F707" t="inlineStr">
         <is>
-          <t>Outdoor 32x5</t>
+          <t>8x3 Premium</t>
         </is>
       </c>
       <c r="G707" t="inlineStr">
         <is>
-          <t>Área de impressão: 32,12x5,04m (escala 1:10, 321,2x50,4cm). Área de conteúdo relevante: 31,8x4,8m.</t>
+          <t>Área de impressão: 8,35x3m (escala 1:10, 83,5x30cm). Área de conteúdo relevante: 8,15x2,80m.</t>
         </is>
       </c>
       <c r="J707" t="inlineStr">
@@ -32957,12 +32947,12 @@
       </c>
       <c r="F708" t="inlineStr">
         <is>
-          <t>8x3 Premium</t>
+          <t>Monoposte 10x5</t>
         </is>
       </c>
       <c r="G708" t="inlineStr">
         <is>
-          <t>Área de impressão: 8,35x3m (escala 1:10, 83,5x30cm). Área de conteúdo relevante: 8,15x2,80m.</t>
+          <t>Área de impressão: 10x5m (escala 1:10, 100x50cm). Área de conteúdo relevante: 9,80x4,80m.</t>
         </is>
       </c>
       <c r="J708" t="inlineStr">
@@ -32999,12 +32989,12 @@
       </c>
       <c r="F709" t="inlineStr">
         <is>
-          <t>Monoposte 10x5</t>
+          <t>Outdoor 4x3</t>
         </is>
       </c>
       <c r="G709" t="inlineStr">
         <is>
-          <t>Área de impressão: 10x5m (escala 1:10, 100x50cm). Área de conteúdo relevante: 9,80x4,80m.</t>
+          <t>Área de impressão: 4x3m (escala 1:10, 40x30cm). Área de conteúdo relevante: 3,80x2,80m.</t>
         </is>
       </c>
       <c r="J709" t="inlineStr">
@@ -33021,42 +33011,426 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>CSOutdoors</t>
+          <t>Ogury</t>
         </is>
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>CSOutdoors</t>
+          <t>Ogury</t>
         </is>
       </c>
       <c r="F710" t="inlineStr">
         <is>
-          <t>Outdoor 4x3</t>
+          <t>Display Creatives - Image - Full Screen</t>
         </is>
       </c>
       <c r="G710" t="inlineStr">
         <is>
-          <t>Área de impressão: 4x3m (escala 1:10, 40x30cm). Área de conteúdo relevante: 3,80x2,80m.</t>
+          <t>1388x1734 (recomendado, mobile portrait). Safe zone: 780x1734. Danger zone: 304x1734 (cada lado).</t>
+        </is>
+      </c>
+      <c r="I710" t="inlineStr">
+        <is>
+          <t>Ideal: 100 KB. Máx.: 2 MB.</t>
         </is>
       </c>
       <c r="J710" t="inlineStr">
         <is>
-          <t>PDF, JPG, TIF, CDR ou AI</t>
+          <t>PNG, JPEG, GIF ou HTML5 (managed only)</t>
         </is>
       </c>
       <c r="L710" t="inlineStr">
         <is>
-          <t>Imagem à escala 1:10. Resolução recomendada: 300dpi. Ficheiro em CMYK. Enviar fontes ou converter textos em curvas. Incluir um JPG para visualização. Enviar por email, pen ou CD.</t>
+          <t>Não colocar elementos importantes nas danger zones (laterais) — usar essa área só para elementos gráficos decorativos. CTA: máx. 2-3 palavras com verbo de ação (ex.: "Compre agora", "Descubra"). Template Photoshop disponível (Mobile + IAB, com safe areas). Para redimensionamento pela equipa de design da Ogury, enviar: ficheiro PSD por camadas em alta resolução, logos em vetorial (PSD/AI/EPS/SVG), copy da campanha, fontes e brand guidelines. Prazos: criação inicial mín. 2 dias úteis; revisões mín. 1-2 dias úteis; máx. 2 revisões por criatividade. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto de pixel/click/viewability por conjunto de criatividades multi-formato).</t>
+        </is>
+      </c>
+      <c r="M710" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/display-creatives/image-design-specifications#full-screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>Display Creatives - Image - Thumbnail</t>
+        </is>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>720x540 (ratio 1,3, mobile portrait). Safe zone: 648x540. Danger zone: 36x540 (cada lado).</t>
+        </is>
+      </c>
+      <c r="I711" t="inlineStr">
+        <is>
+          <t>Ideal: 50 KB. Máx.: 2 MB.</t>
+        </is>
+      </c>
+      <c r="J711" t="inlineStr">
+        <is>
+          <t>PNG, JPEG, GIF ou HTML5 (managed only)</t>
+        </is>
+      </c>
+      <c r="L711" t="inlineStr">
+        <is>
+          <t>Só elementos necessários (logo, headline, CTA); texto legível e conciso. Não colocar elementos importantes nas danger zones. CTA: máx. 2-3 palavras com verbo de ação. Template Photoshop disponível (Mobile + IAB, com safe areas). Para redimensionamento pela equipa de design da Ogury, enviar: ficheiro PSD por camadas em alta resolução, logos em vetorial (PSD/AI/EPS/SVG), copy da campanha, fontes e brand guidelines. Prazos: criação inicial mín. 2 dias úteis; revisões mín. 1-2 dias úteis; máx. 2 revisões por criatividade. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto de pixel/click/viewability por conjunto de criatividades multi-formato).</t>
+        </is>
+      </c>
+      <c r="M711" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/display-creatives/image-design-specifications#thumbnail</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>Display Creatives - Image - Header</t>
+        </is>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>2640x600 (mobile portrait). Safe zone: 1060x600. Danger zone: 789x600 (cada lado).</t>
+        </is>
+      </c>
+      <c r="I712" t="inlineStr">
+        <is>
+          <t>Ideal: 50 KB. Máx.: 2 MB.</t>
+        </is>
+      </c>
+      <c r="J712" t="inlineStr">
+        <is>
+          <t>PNG, JPEG, GIF ou HTML5 (managed only)</t>
+        </is>
+      </c>
+      <c r="L712" t="inlineStr">
+        <is>
+          <t>Não colocar elementos importantes nas danger zones. CTA: máx. 2-3 palavras com verbo de ação. Template Photoshop disponível (Mobile + IAB, com safe areas). Para redimensionamento pela equipa de design da Ogury, enviar: ficheiro PSD por camadas em alta resolução, logos em vetorial (PSD/AI/EPS/SVG), copy da campanha, fontes e brand guidelines. Prazos: criação inicial mín. 2 dias úteis; revisões mín. 1-2 dias úteis; máx. 2 revisões por criatividade. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto de pixel/click/viewability por conjunto de criatividades multi-formato).</t>
+        </is>
+      </c>
+      <c r="M712" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/display-creatives/image-design-specifications#header</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>Display Creatives - Image - Footer</t>
+        </is>
+      </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>1760x400 (mobile portrait). Safe zone: 1280x400. Danger zone: 240x400 (cada lado).</t>
+        </is>
+      </c>
+      <c r="I713" t="inlineStr">
+        <is>
+          <t>Ideal: 50 KB. Máx.: 2 MB.</t>
+        </is>
+      </c>
+      <c r="J713" t="inlineStr">
+        <is>
+          <t>PNG, JPEG, GIF ou HTML5 (managed only)</t>
+        </is>
+      </c>
+      <c r="L713" t="inlineStr">
+        <is>
+          <t>Não colocar elementos importantes nas danger zones. CTA: máx. 2-3 palavras com verbo de ação. Template Photoshop disponível (Mobile + IAB, com safe areas). Para redimensionamento pela equipa de design da Ogury, enviar: ficheiro PSD por camadas em alta resolução, logos em vetorial (PSD/AI/EPS/SVG), copy da campanha, fontes e brand guidelines. Prazos: criação inicial mín. 2 dias úteis; revisões mín. 1-2 dias úteis; máx. 2 revisões por criatividade. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto de pixel/click/viewability por conjunto de criatividades multi-formato).</t>
+        </is>
+      </c>
+      <c r="M713" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/display-creatives/image-design-specifications#footer</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>Display Creatives - Image - Reveal</t>
+        </is>
+      </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>1388x1734 (mobile portrait). Safe zone: 780x1734. Danger zone: 304x1734 (cada lado).</t>
+        </is>
+      </c>
+      <c r="I714" t="inlineStr">
+        <is>
+          <t>Ideal: 100 KB. Máx.: 2 MB.</t>
+        </is>
+      </c>
+      <c r="J714" t="inlineStr">
+        <is>
+          <t>PNG, JPEG, GIF ou HTML5 (managed only)</t>
+        </is>
+      </c>
+      <c r="L714" t="inlineStr">
+        <is>
+          <t>Unidade criativa dinâmica in-article, pensada para visibilidade máxima durante o scroll em conteúdo mobile web. Não colocar elementos importantes nas danger zones. CTA: máx. 2-3 palavras com verbo de ação. Template Photoshop disponível (Mobile + IAB, com safe areas). Para redimensionamento pela equipa de design da Ogury, enviar: ficheiro PSD por camadas em alta resolução, logos em vetorial (PSD/AI/EPS/SVG), copy da campanha, fontes e brand guidelines. Prazos: criação inicial mín. 2 dias úteis; revisões mín. 1-2 dias úteis; máx. 2 revisões por criatividade. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto de pixel/click/viewability por conjunto de criatividades multi-formato).</t>
+        </is>
+      </c>
+      <c r="M714" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/display-creatives/image-design-specifications#reveal</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>Display Creatives - Image - In-Article MPU</t>
+        </is>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>300x250 (ratio 1:2)</t>
+        </is>
+      </c>
+      <c r="I715" t="inlineStr">
+        <is>
+          <t>Ideal: 100 KB. Máx.: 2 MB.</t>
+        </is>
+      </c>
+      <c r="J715" t="inlineStr">
+        <is>
+          <t>PNG, JPEG, GIF ou HTML5 (managed only)</t>
+        </is>
+      </c>
+      <c r="L715" t="inlineStr">
+        <is>
+          <t>Unidade in-article, pensada para consideração e tráfego qualificado. Incluído só nalguns pacotes — confirmar na recomendação de media. CTA: máx. 2-3 palavras com verbo de ação. Template Photoshop disponível (Mobile + IAB, com safe areas). Para redimensionamento pela equipa de design da Ogury, enviar: ficheiro PSD por camadas em alta resolução, logos em vetorial (PSD/AI/EPS/SVG), copy da campanha, fontes e brand guidelines. Prazos: criação inicial mín. 2 dias úteis; revisões mín. 1-2 dias úteis; máx. 2 revisões por criatividade. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto de pixel/click/viewability por conjunto de criatividades multi-formato).</t>
+        </is>
+      </c>
+      <c r="M715" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/display-creatives/image-design-specifications#in-article-mpu</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>Video Creatives - Horizontal Video</t>
+        </is>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>16:9. Recomendado: 1024x576px.</t>
+        </is>
+      </c>
+      <c r="H716" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I716" t="inlineStr">
+        <is>
+          <t>Máx.: 40 MB (MP4) ou 3 MB (VAST/VPAID).</t>
+        </is>
+      </c>
+      <c r="J716" t="inlineStr">
+        <is>
+          <t>MP4, VAST tag ou VPAID (legacy)</t>
+        </is>
+      </c>
+      <c r="L716" t="inlineStr">
+        <is>
+          <t>Formato: MP4, VAST tag ou VPAID (legacy apenas; VAST preferencial). Recomendado: compliance VAST 4.1 + OM SDK. Safe area: margem de segurança de 10% em cima/baixo (para overlays de UI). Som: deve ser compreensível sem áudio (autoplay mudo). Branding: logo/mensagem clara nos primeiros 5 segundos. Duração máxima: até 30s (recomendado 15s para melhor experiência mobile). Pixels de medição e trackers de terceiros (ex.: IAS, DoubleVerify) devem vir embrulhados em VAST tags. Personalização: nome da marca/produto e texto de CTA (máx. 30 carateres; "Visit website" por defeito). Funcionalidades opcionais, de valor acrescentado — confirmar disponibilidade com a equipa Ogury: Top &amp; Bottom Skins (imagens estáticas JPG/PNG, 768x450px cada, sobrepostas ao vídeo, sem tracking próprio); Bottom Skin isolado (JPG/PNG, 768x930px, sem tracking próprio); End Card (imagem estática a seguir ao vídeo, JPG/PNG, 16:9 ou 9:16, recomendado 1024x576 ou 576x1024px, máx. 250 KB). Templates Photoshop disponíveis para as skins/end card (com safe areas). Prazos de design: criação inicial mín. 2 dias úteis; revisões mín. 1-2 dias úteis; máx. 2 revisões por criativo.</t>
+        </is>
+      </c>
+      <c r="M716" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/video-studio/horizontal-video-specs</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>Video Creatives - Vertical Video</t>
+        </is>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>9:16. Recomendado: 576x1024px.</t>
+        </is>
+      </c>
+      <c r="H717" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
+      <c r="I717" t="inlineStr">
+        <is>
+          <t>Máx.: 40 MB (MP4) ou 3 MB (VAST/VPAID).</t>
+        </is>
+      </c>
+      <c r="J717" t="inlineStr">
+        <is>
+          <t>MP4, VAST tag ou VPAID (legacy)</t>
+        </is>
+      </c>
+      <c r="L717" t="inlineStr">
+        <is>
+          <t>Formato: MP4, VAST tag ou VPAID (legacy apenas; VAST preferencial). Recomendado: compliance VAST 4.1 + OM SDK. Safe area: margem de segurança de 10% em cima/baixo (para overlays de UI). Som: deve ser compreensível sem áudio (autoplay mudo). Branding: logo/mensagem clara nos primeiros 5 segundos. Duração máxima: até 30s (recomendado 15s para melhor experiência mobile). Pixels de medição e trackers de terceiros (ex.: IAS, DoubleVerify) devem vir embrulhados em VAST tags. Personalização: heading ("Choose your ad" por defeito), nomes de produto/feature, cor de fundo (branco por defeito) — formato interativo tipo "video chooser". Funcionalidades opcionais, de valor acrescentado — confirmar disponibilidade com a equipa Ogury: End Card (imagem estática a seguir ao vídeo, JPG/PNG, 16:9 ou 9:16, recomendado 1024x576 ou 576x1024px, máx. 250 KB, com opção de end card multi-CTA, sem tracking próprio); Video Chooser Image (specs não detalhadas nos materiais enviados — confirmar com a equipa Ogury). Template Photoshop disponível para o End Card (com safe areas). Prazos de design: criação inicial mín. 2 dias úteis; revisões mín. 1-2 dias úteis; máx. 2 revisões por criativo.</t>
+        </is>
+      </c>
+      <c r="M717" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/video-studio/vertical-video-specs</t>
         </is>
       </c>
     </row>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M717"/>
+  <dimension ref="A1:M731"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33434,6 +33434,749 @@
         </is>
       </c>
     </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>Rich Media &amp; Engagement Studio - Brand Spotlight</t>
+        </is>
+      </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>Variável — disponível nos formatos próprios Ogury (ver página de tamanhos suportados) e nos formatos IAB standard: 970x250, 300x600, 320x480, 160x600, 336x280, 300x250.</t>
+        </is>
+      </c>
+      <c r="J718" t="inlineStr">
+        <is>
+          <t>PSD (camadas), AI, INDD, Figma ou XD</t>
+        </is>
+      </c>
+      <c r="K718" t="inlineStr">
+        <is>
+          <t>Máximo 2–4 palavras (10 a 20 carateres incl. espaços). Evitar pontuação e quebras de linha.</t>
+        </is>
+      </c>
+      <c r="L718" t="inlineStr">
+        <is>
+          <t>Carrossel rich media interativo para mostrar vários produtos, features ou mensagens de marca numa experiência deslizável (swipe). Disponível para campanhas CPE e CPM. Casos de uso: product showcase (vários produtos/variações); storytelling sequencial (mensagem revelada passo a passo); 3D Brand Spotlight (transição em cubo 3D); multi-CTA (vários CTAs rastreados individualmente, na mesma slide ou em slides diferentes, cada um com destino próprio); vídeo (no root da criatividade, visível durante o swipe, ou integrado numa slide específica). Boas práticas: limitar a ~5-6 slides; manter o CTA visível; mensagem concisa por slide; consistência visual entre slides. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+        </is>
+      </c>
+      <c r="M718" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/rich-media-and-engagement-studio/brand-spotlight-design-specifications</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>Rich Media &amp; Engagement Studio - Product Galore</t>
+        </is>
+      </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>Variável — disponível nos formatos próprios Ogury (ver página de tamanhos suportados) e nos formatos IAB standard: 970x250, 300x600, 320x480, 160x600, 336x280, 300x250.</t>
+        </is>
+      </c>
+      <c r="J719" t="inlineStr">
+        <is>
+          <t>PSD (camadas), AI, INDD, Figma ou XD</t>
+        </is>
+      </c>
+      <c r="K719" t="inlineStr">
+        <is>
+          <t>Máximo 2–4 palavras (10 a 20 carateres incl. espaços). Evitar pontuação e quebras de linha.</t>
+        </is>
+      </c>
+      <c r="L719" t="inlineStr">
+        <is>
+          <t>Carrossel rich media interativo com navegação em camadas: o utilizador interage com elementos no ecrã de entrada para aceder a vistas de detalhe dedicadas. Para campanhas CPE e CPM. Casos de uso: product showcase (vários produtos, cada um com vista de detalhe); variações e opções (cores, estilos, configurações); product deep dive (um produto, várias camadas de informação); com vídeo (no ecrã de entrada ou dentro de uma vista de detalhe); com carrossel (carrossel dentro da vista de detalhe, para ângulos/features/variações adicionais). Boas práticas: limitar o nº de elementos interativos no ecrã de entrada; elementos clicáveis claramente identificáveis; botão de voltar sempre visível quando necessário; mensagem concisa por ecrã. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+        </is>
+      </c>
+      <c r="M719" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/rich-media-and-engagement-studio/product-galore-design-specification</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>Rich Media &amp; Engagement Studio - Pick &amp; Choose</t>
+        </is>
+      </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>Variável — disponível nos formatos próprios Ogury (ver página de tamanhos suportados) e nos formatos IAB standard: 970x250, 300x600, 320x480, 160x600, 336x280, 300x250.</t>
+        </is>
+      </c>
+      <c r="J720" t="inlineStr">
+        <is>
+          <t>PSD (camadas), AI, INDD, Figma ou XD</t>
+        </is>
+      </c>
+      <c r="K720" t="inlineStr">
+        <is>
+          <t>Máximo 2–4 palavras (10 a 20 carateres incl. espaços). Evitar pontuação e quebras de linha.</t>
+        </is>
+      </c>
+      <c r="L720" t="inlineStr">
+        <is>
+          <t>Formato interativo que permite ao utilizador explorar produtos, variantes, features ou configurações diferentes dentro de uma única criatividade: ao tocar numa opção seletora, o visual principal e o conteúdo associado atualizam-se instantaneamente. Para campanhas CPE e CPM. Casos de uso: seleção de produto (navegar vários produtos, cada seleção atualiza o visual/conteúdo); personalização de variante (cores, estilos, sabores, acabamentos — ideal para automóvel, moda, beleza, alimentação, mobiliário, eletrónica de consumo). Boas práticas: limitar o nº de opções selecionáveis; destacar claramente a opção selecionada; cada seleção deve gerar uma mudança visual percetível; CTA sempre visível; consistência visual entre variantes; seletores suficientemente grandes para toque em mobile. Assets visuais adicionais: uma imagem por opção selecionável; thumbnails de produto, ícones, amostras de cor ou seletores. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+        </is>
+      </c>
+      <c r="M720" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/rich-media-and-engagement-studio/pick-and-choose-design-specification</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>Rich Media &amp; Engagement Studio - Drag &amp; Drop</t>
+        </is>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>Variável — disponível nos formatos próprios Ogury (ver página de tamanhos suportados) e nos formatos IAB standard: 970x250, 300x600, 320x480, 160x600, 336x280, 300x250.</t>
+        </is>
+      </c>
+      <c r="J721" t="inlineStr">
+        <is>
+          <t>PSD (camadas), AI, INDD, Figma ou XD</t>
+        </is>
+      </c>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>Máximo 2–4 palavras (10 a 20 carateres incl. espaços). Evitar pontuação e quebras de linha.</t>
+        </is>
+      </c>
+      <c r="L721" t="inlineStr">
+        <is>
+          <t>Formato interativo em que o utilizador arrasta um ou mais elementos para áreas-alvo predefinidas para completar uma ação; ao concluir, revela conteúdo/novo ecrã. Para campanhas CPE e CPM. Casos de uso: product reveal (arrastar elemento(s) para revelar produto/oferta/mensagem); demonstração de uso do produto; receitas/ingredientes (arrastar ingredientes para uma tigela/prato/copo); desafio gamificado (ex.: marcar golo, colocar um item, fazer correspondências) antes de desbloquear o passo seguinte. Boas práticas: interação intuitiva, elementos arrastáveis e zonas de largada claramente identificáveis; pistas visuais/animações/copy instrucional; elementos fáceis de manipular em mobile; limitar o nº de ações necessárias; recompensar interações bem-sucedidas; progressão clara (nº de ações em falta). Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+        </is>
+      </c>
+      <c r="M721" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/rich-media-and-engagement-studio/drag-and-drop-design-specifications</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>Rich Media &amp; Engagement Studio - Hotspots</t>
+        </is>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>Variável — disponível nos formatos próprios Ogury (ver página de tamanhos suportados) e nos formatos IAB standard: 970x250, 300x600, 320x480, 160x600, 336x280, 300x250.</t>
+        </is>
+      </c>
+      <c r="J722" t="inlineStr">
+        <is>
+          <t>PSD (camadas), AI, INDD, Figma ou XD</t>
+        </is>
+      </c>
+      <c r="K722" t="inlineStr">
+        <is>
+          <t>Máximo 2–4 palavras (10 a 20 carateres incl. espaços). Evitar pontuação e quebras de linha.</t>
+        </is>
+      </c>
+      <c r="L722" t="inlineStr">
+        <is>
+          <t>Formato interativo com hotspots clicáveis sobre elementos-chave de um visual; ao tocar, revela conteúdo adicional (informação de produto, features, preço, imagem, vídeo ou CTA). Para campanhas CPE e CPM. Casos de uso: informação de produto (hotspots numa imagem, cada um revela info/preço/CTA); product deep dive (hotspots ligados a componentes/funcionalidades específicas). Boas práticas: limitar o nº de hotspots por ecrã; posicionar em áreas relevantes do visual; garantir visibilidade clara (contraste/espaçamento); conteúdo de cada hotspot conciso; evitar sobreposição de áreas; consistência visual entre o conteúdo dos hotspots; áreas de toque suficientemente grandes em mobile. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+        </is>
+      </c>
+      <c r="M722" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/rich-media-and-engagement-studio/hotspots-design-specification</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>Rich Media &amp; Engagement Studio - Comparison Slider</t>
+        </is>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>Variável — disponível nos formatos próprios Ogury (ver página de tamanhos suportados) e nos formatos IAB standard: 970x250, 300x600, 320x480, 160x600, 336x280, 300x250.</t>
+        </is>
+      </c>
+      <c r="J723" t="inlineStr">
+        <is>
+          <t>PSD (camadas), AI, INDD, Figma ou XD</t>
+        </is>
+      </c>
+      <c r="K723" t="inlineStr">
+        <is>
+          <t>Máximo 2–4 palavras (10 a 20 carateres incl. espaços). Evitar pontuação e quebras de linha.</t>
+        </is>
+      </c>
+      <c r="L723" t="inlineStr">
+        <is>
+          <t>Formato interativo que permite comparar dois visuais arrastando um slider pelo ecrã — revela progressivamente uma imagem enquanto esconde a outra, criando uma experiência "antes e depois". Para campanhas CPE e CPM. Casos de uso: antes e depois (transformação visual: skincare, tratamentos de beleza, fitness, remodelações); personalização de produto (cores, estilos, sabores, acabamentos, variações); impacto de produto/serviço (ex.: produtos de limpeza, tintas, jardinagem, restauro); comparação de features (ex.: standard vs. premium, modelo antigo vs. novo); melhoria de performance (ex.: desporto, nutrição, saúde e bem-estar). Boas práticas: visuais altamente contrastados; imagens perfeitamente alinhadas; pista de interação clara (setas, labels, animação subtil); foco numa única mensagem-chave; branding e CTA sempre visíveis; otimizar para leitura em mobile. Assets visuais adicionais: uma imagem por opção selecionável; thumbnails, ícones, amostras de cor ou seletores. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+        </is>
+      </c>
+      <c r="M723" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/rich-media-and-engagement-studio/comparison-slider-design-specification</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>Rich Media &amp; Engagement Studio - Puzzle</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>Variável — disponível nos formatos próprios Ogury (ver página de tamanhos suportados) e nos formatos IAB standard: 970x250, 300x600, 320x480, 160x600, 336x280, 300x250.</t>
+        </is>
+      </c>
+      <c r="J724" t="inlineStr">
+        <is>
+          <t>PSD (camadas), AI, INDD, Figma ou XD</t>
+        </is>
+      </c>
+      <c r="L724" t="inlineStr">
+        <is>
+          <t>Formato interativo em que o utilizador reconstrói uma imagem para desbloquear conteúdo adicional; ao completar o puzzle, mostra um ecrã de revelação final. Para campanhas CPE e CPM. Casos de uso: revelação de produto (produto, embalagem ou visual hero); desbloqueio de oferta (promoção, desconto, conteúdo exclusivo); engagement gamificado; storytelling de marca; teaser de evento/lançamento. Boas práticas: usar uma imagem visualmente apelativa e facilmente reconhecível; desafio simples e intuitivo (resolúvel em poucos segundos); revelação final com valor; branding consistente em todos os ecrãs; CTA apelativo; otimizar para interação em mobile. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+        </is>
+      </c>
+      <c r="M724" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/rich-media-and-engagement-studio/puzzle-design-specification</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>Rich Media &amp; Engagement Studio - Tap to Reveal</t>
+        </is>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>Variável — disponível nos formatos próprios Ogury (ver página de tamanhos suportados) e nos formatos IAB standard: 970x250, 300x600, 320x480, 160x600, 336x280, 300x250.</t>
+        </is>
+      </c>
+      <c r="J725" t="inlineStr">
+        <is>
+          <t>PSD (camadas), AI, INDD, Figma ou XD</t>
+        </is>
+      </c>
+      <c r="K725" t="inlineStr">
+        <is>
+          <t>Máximo 2–4 palavras (10 a 20 carateres incl. espaços). Evitar pontuação e quebras de linha.</t>
+        </is>
+      </c>
+      <c r="L725" t="inlineStr">
+        <is>
+          <t>Formato interativo com uma interação simples de toque que desbloqueia conteúdo adicional: começa com um visual teaser e revela uma segunda camada de conteúdo (imagem, vídeo, slideshow, animação ou mensagem promocional). Para campanhas CPE e CPM. Casos de uso: slideshow reveal; video reveal; offer reveal (promoção/oferta exclusiva/mensagem-chave); transformação criativa (mudança de universo visual, ex. campanhas sazonais/lançamentos); antes e depois (estado transformado — beleza, fitness, automóvel, melhoria de casa). Boas práticas: tornar a interação óbvia; forte contraste entre teaser e conteúdo revelado; primeiro ecrã simples e focado; usar a revelação para a mensagem-chave; transições suaves; otimizar para mobile; consistência visual entre ecrãs. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+        </is>
+      </c>
+      <c r="M725" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/rich-media-and-engagement-studio/tap-to-reveal-design-specification</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>Rich Media &amp; Engagement Studio - Tap to Map</t>
+        </is>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>Formatos próprios Ogury: Fullscreen e In-Article apenas. Formatos IAB standard: 970x250, 300x600, 300x250, 336x280, 320x480.</t>
+        </is>
+      </c>
+      <c r="J726" t="inlineStr">
+        <is>
+          <t>PSD (camadas), AI, INDD, Figma ou XD</t>
+        </is>
+      </c>
+      <c r="K726" t="inlineStr">
+        <is>
+          <t>Máximo 2–4 palavras (10 a 20 carateres incl. espaços). Evitar pontuação e quebras de linha.</t>
+        </is>
+      </c>
+      <c r="L726" t="inlineStr">
+        <is>
+          <t>Combina uma criatividade de marca com um localizador de lojas integrado: o utilizador interage com um visual promocional e depois toca num CTA para aceder a um mapa interativo dentro do próprio anúncio, mostrando lojas, pontos de venda, postos de carregamento, concessionários ou outras localizações físicas próximas. Casos de uso: localizador de loja; localizações de evento; rede de agências/balcões/serviço; rede de postos de carregamento EV. Boas práticas: CTA forte orientado a localização (ex.: "Find a Store"); introdução concisa antes de passar ao mapa; informação de localização completa. Mapa: é obrigatório um ficheiro .CSV de localizações preenchido, usando o template fornecido pela Ogury, sem alterar os nomes das colunas (caso contrário a integração do mapa falha). Campos obrigatórios: nome da localização, morada, cidade, código postal, estado/região (se aplicável), país, latitude, longitude, report label. Campos opcionais: telefone, email, URL, horário de funcionamento. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+        </is>
+      </c>
+      <c r="M726" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/rich-media-and-engagement-studio/tap-to-map-design-specification</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>Rich Media &amp; Engagement Studio - Site Scroller</t>
+        </is>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>Variável — disponível nos formatos próprios Ogury (ver página de tamanhos suportados) e nos formatos IAB standard: 970x250, 300x600, 320x480, 160x600, 336x280, 300x250.</t>
+        </is>
+      </c>
+      <c r="J727" t="inlineStr">
+        <is>
+          <t>PSD (camadas), AI, INDD, Figma ou XD</t>
+        </is>
+      </c>
+      <c r="K727" t="inlineStr">
+        <is>
+          <t>Máximo 2–4 palavras (10 a 20 carateres incl. espaços). Evitar pontuação e quebras de linha.</t>
+        </is>
+      </c>
+      <c r="L727" t="inlineStr">
+        <is>
+          <t>Experiência imersiva multi-página que permite navegação vertical por conteúdo de marca através de swipe (cima/baixo), replicando a navegação num site/landing page, com produtos, features, storytelling ou conteúdo promocional distribuídos por várias páginas dentro do mesmo anúncio. Casos de uso: product showcase (features/benefícios/configurações em páginas dedicadas); storytelling (jornada narrativa sequencial); promoção de evento/campanha (vários aspetos de um lançamento/evento em páginas diferentes); com carrossel (carrossel integrado para visibilidade adicional de produto). Boas práticas: limitar a 4-5 páginas no máximo; hierarquia visual clara (uma mensagem-chave por página); incentivar o scroll (setas/indicadores direcionais); consistência visual; fluxo narrativo lógico; terminar com um CTA forte. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+        </is>
+      </c>
+      <c r="M727" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/rich-media-and-engagement-studio/site-scroller-design-specifications</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>Rich Media &amp; Engagement Studio - 360°</t>
+        </is>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>Creative (PNG): 1080x1920. Brand Logo (PNG). Vista 360°: 8+ imagens (PNG).</t>
+        </is>
+      </c>
+      <c r="H728" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
+      <c r="J728" t="inlineStr">
+        <is>
+          <t>PNG (creative, logo e imagens da vista 360°)</t>
+        </is>
+      </c>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>CTA: "Buy Now" ou "Learn More" por defeito; customizado máx. 3 palavras.</t>
+        </is>
+      </c>
+      <c r="L728" t="inlineStr">
+        <is>
+          <t>Mostra o produto a partir de todos os ângulos. Unidade construída à medida pela equipa de Design da Ogury (não é self-service). Template Photoshop disponível, com safe areas e danger zones oficiais. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2-3 dias úteis consoante a complexidade; máx. 2 revisões por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking. Formatos próprios Ogury e IAB disponíveis para este template: confirmar com a equipa Ogury. Faturação baseada em medição 1P.</t>
+        </is>
+      </c>
+      <c r="M728" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/rich-media-and-engagement-studio/360-specs</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>Rich Media &amp; Engagement Studio - Quiz</t>
+        </is>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>Variável — disponível nos formatos próprios Ogury (ver página de tamanhos suportados) e nos formatos IAB standard: 970x250, 300x600, 320x480, 160x600, 336x280, 300x250.</t>
+        </is>
+      </c>
+      <c r="J729" t="inlineStr">
+        <is>
+          <t>PSD (camadas), AI, INDD, Figma ou XD</t>
+        </is>
+      </c>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>Pergunta/afirmação inicial; opções de resposta (recomendado 1-2 palavras cada); ecrã(s) de resultado (um ecrã partilhado ou dois ecrãs dedicados, um por resposta); texto de CTA para o(s) ecrã(s) final/finais.</t>
+        </is>
+      </c>
+      <c r="L729" t="inlineStr">
+        <is>
+          <t>Carrossel rich media interativo com navegação em camadas (entrada + vista de detalhe), orientado a pergunta/resposta. Para campanhas CPE e CPM. Casos de uso: sondagem de preferência (escolha entre duas opções/preferências/opiniões/produtos, cada resposta rastreada individualmente, podendo revelar conteúdo dedicado); awareness &amp; educação (pergunta verdadeiro/falso, revela a resposta certa + conteúdo educativo — ideal para awareness, saúde, informação pública, sustentabilidade, educação financeira/de marca); recomendação de produto (guia o utilizador para o produto/solução mais relevante consoante a resposta). Boas práticas: perguntas curtas e fáceis de perceber; opções de resposta claras e distintas; labels de resposta curtos; ambas as opções igualmente visíveis; resultado relevante para a escolha do utilizador; foco numa única pergunta; consistência visual entre ecrãs. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+        </is>
+      </c>
+      <c r="M729" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/rich-media-and-engagement-studio/quiz-design-specification</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>Rich Media &amp; Engagement Studio - Social Display</t>
+        </is>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>Logo: 256x256px. Imagem: 950x1000px.</t>
+        </is>
+      </c>
+      <c r="I730" t="inlineStr">
+        <is>
+          <t>Logo: máx. 100 KB. Imagem: máx. 400 KB.</t>
+        </is>
+      </c>
+      <c r="J730" t="inlineStr">
+        <is>
+          <t>Logo: PNG. Imagem: JPEG (pode incluir texto).</t>
+        </is>
+      </c>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>Nome da marca, texto superior (máx. 85 carateres recomendado), texto inferior (máx. 50 carateres), domínio da marca, CTA ("Discover" por defeito).</t>
+        </is>
+      </c>
+      <c r="L730" t="inlineStr">
+        <is>
+          <t>Reaproveita os assets da marca para emular a experiência social (Facebook, Instagram, TikTok, Twitter, LinkedIn, Pinterest ou Snapchat — escolher um layout) dentro de apps não-sociais, gerando alcance incremental. Unidade construída à medida pela equipa de Design da Ogury (não é self-service). Template Photoshop disponível, com safe areas e danger zones oficiais. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2-3 dias úteis consoante a complexidade; máx. 2 revisões por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking. Formatos próprios Ogury e IAB disponíveis para este template: confirmar com a equipa Ogury.</t>
+        </is>
+      </c>
+      <c r="M730" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/rich-media-and-engagement-studio/social-display-specs</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>Rich Media &amp; Engagement Studio - Social Carousel</t>
+        </is>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>Logo: 256x256px. Carrossel de imagens (máx. 5): 750x1000px cada.</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr">
+        <is>
+          <t>3:4</t>
+        </is>
+      </c>
+      <c r="I731" t="inlineStr">
+        <is>
+          <t>Logo: máx. 100 KB. Cada imagem do carrossel: máx. 100 KB.</t>
+        </is>
+      </c>
+      <c r="J731" t="inlineStr">
+        <is>
+          <t>Logo: PNG. Imagens do carrossel: JPEG (podem incluir texto).</t>
+        </is>
+      </c>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>Nome da marca, texto superior (máx. 85 carateres recomendado), texto inferior (máx. 50 carateres), domínio da marca.</t>
+        </is>
+      </c>
+      <c r="L731" t="inlineStr">
+        <is>
+          <t>Reaproveita os assets da marca para emular a experiência de carrossel social (Facebook ou Instagram — escolher um layout) dentro de apps não-sociais, gerando alcance incremental. Unidade construída à medida pela equipa de Design da Ogury (não é self-service). Template Photoshop disponível, com safe areas e danger zones oficiais. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2-3 dias úteis consoante a complexidade; máx. 2 revisões por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking. Formatos próprios Ogury e IAB disponíveis para este template: confirmar com a equipa Ogury. Faturação baseada em medição 1P.</t>
+        </is>
+      </c>
+      <c r="M731" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/rich-media-and-engagement-studio/social-carousel-specs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M731"/>
+  <dimension ref="A1:M737"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34177,6 +34177,318 @@
         </is>
       </c>
     </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>Display Creatives - Slideshow</t>
+        </is>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>Formatos próprios Ogury: Fullscreen, Header, Footer, Thumbnail, In-article Reveal. Formatos IAB standard: 970x250, 300x600, 320x480, 160x600, 336x280, 300x250, 120x600, 728x90, 320x100, 300x100, 320x50, 300x50.</t>
+        </is>
+      </c>
+      <c r="J732" t="inlineStr">
+        <is>
+          <t>PSD (camadas), AI, INDD, Figma ou XD</t>
+        </is>
+      </c>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>Máximo 2–4 palavras (10 a 20 carateres incl. espaços). Evitar pontuação e quebras de linha.</t>
+        </is>
+      </c>
+      <c r="L732" t="inlineStr">
+        <is>
+          <t>Anima o storytelling: liga narrativa com transições suaves e mensagens sequenciais, ideal para destacar várias features de produto ou mensagens-chave numa única criatividade. Casos de uso: visual animado único (estático melhorado com movimento subtil); storytelling sequencial (multi-ecrã); multi-CTA (vários CTAs rastreados individualmente, na mesma tela ou em telas diferentes, cada um com destino próprio); Slideshow com vídeo (vídeo visível durante toda a experiência); Slideshow para vídeo (sequência de slideshow seguida de um ecrã de vídeo dedicado); Slideshow com animação Lottie (elementos animados leves — neve, partículas, efeitos de fundo — sem aumentar o peso do ficheiro); Slideshow com disclaimer legal scrollável (texto legal extenso numa área com scroll automático/manual). Boas práticas: limitar a ~5-6 capítulos; manter o CTA visível; mensagem concisa por ecrã; consistência visual entre capítulos. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+        </is>
+      </c>
+      <c r="M732" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/display-creatives/slideshow-design-specifications</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>Display Creatives - Pop</t>
+        </is>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>Formatos próprios Ogury: Full Screen, Thumbnail, Header, Footer, In-article Reveal. Formatos IAB standard: tamanhos a confirmar na página de formatos e tamanhos suportados.</t>
+        </is>
+      </c>
+      <c r="J733" t="inlineStr">
+        <is>
+          <t>PSD (camadas), AI, INDD, Figma ou XD</t>
+        </is>
+      </c>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>Máximo 2–4 palavras (10 a 20 carateres incl. espaços). Evitar pontuação e quebras de linha.</t>
+        </is>
+      </c>
+      <c r="L733" t="inlineStr">
+        <is>
+          <t>Efeito de expansão rápido e chamativo, que dá impacto visual instantâneo e atrai naturalmente a atenção para elementos-chave, mantendo a experiência fluida e não intrusiva. Casos de uso: destaque de produto (efeito pop subtil); ênfase de CTA; revelação de oferta (promoções/descontos/mensagens-chave); reforço do visual principal. Boas práticas: aplicar o efeito pop a produtos, logos ou CTAs para maximizar o impacto; layout limpo (sem sobrecarregar); uma mensagem de cada vez; contraste visual forte; alinhado com a marca; a animação deve reforçar a mensagem, não distrair. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+        </is>
+      </c>
+      <c r="M733" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/display-creatives/pop-design-specifications</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>Display Creatives - Glide</t>
+        </is>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>Formatos próprios Ogury: Full Screen, Thumbnail, Header, Footer, In-article Reveal. Formatos IAB standard: tamanhos a confirmar na página de formatos e tamanhos suportados.</t>
+        </is>
+      </c>
+      <c r="J734" t="inlineStr">
+        <is>
+          <t>PSD (camadas), AI, INDD, Figma ou XD</t>
+        </is>
+      </c>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>Máximo 2–4 palavras (10 a 20 carateres incl. espaços). Evitar pontuação e quebras de linha.</t>
+        </is>
+      </c>
+      <c r="L734" t="inlineStr">
+        <is>
+          <t>Efeito de revelação horizontal: um segundo visual desliza suavemente sobre o primeiro, criando uma transição clara e envolvente — ideal para mostrar contrastes, detalhes de produto ou mensagens-chave de forma dinâmica mas controlada. Casos de uso: revelação de cor (preto e branco para cor); revelação de detalhe de produto (vista global para vista de pormenor); comparação visual. Boas práticas: usar dois visuais complementares; layout limpo; foco numa única ideia; contraste forte; visuais alinhados entre si (estilo/composição); alinhado com a marca. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+        </is>
+      </c>
+      <c r="M734" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/display-creatives/glide-design-specifications</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>Display Creatives - Shift</t>
+        </is>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>Formatos próprios Ogury: Full Screen, Thumbnail, Header, Footer, In-article Reveal. Formatos IAB standard: tamanhos a confirmar na página de formatos e tamanhos suportados.</t>
+        </is>
+      </c>
+      <c r="J735" t="inlineStr">
+        <is>
+          <t>PSD (camadas), AI, INDD, Figma ou XD</t>
+        </is>
+      </c>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>Máximo 2–4 palavras (10 a 20 carateres incl. espaços). Evitar pontuação e quebras de linha.</t>
+        </is>
+      </c>
+      <c r="L735" t="inlineStr">
+        <is>
+          <t>Transição vertical suave entre dois visuais, trazendo o conteúdo para o ecrã de forma natural e guiando a atenção do utilizador — ideal para mostrar duas mensagens/visuais complementares, com uma experiência limpa e premium. Casos de uso: antes/depois; foco de produto (dois ângulos/features complementares); transição de mensagem; marca e produto; tease &amp; reveal; destaque duplo (dois elementos com igual visibilidade). Boas práticas: dois visuais complementares; mensagem simples (uma ideia); continuidade visual (cor/estilo/composição); guiar o olhar do utilizador de um visual para o outro; ambos os visuais com valor standalone forte; alinhado com a marca. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+        </is>
+      </c>
+      <c r="M735" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/display-creatives/shift-design-specifications</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>Display Creatives - Rise</t>
+        </is>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>Formatos próprios Ogury: Full Screen, Thumbnail, Header, Footer, In-article Reveal. Formatos IAB standard: tamanhos a confirmar na página de formatos e tamanhos suportados.</t>
+        </is>
+      </c>
+      <c r="J736" t="inlineStr">
+        <is>
+          <t>PSD (camadas), AI, INDD, Figma ou XD</t>
+        </is>
+      </c>
+      <c r="K736" t="inlineStr">
+        <is>
+          <t>Máximo 2–4 palavras (10 a 20 carateres incl. espaços). Evitar pontuação e quebras de linha.</t>
+        </is>
+      </c>
+      <c r="L736" t="inlineStr">
+        <is>
+          <t>Combina uma transição vertical com um efeito de revelação limpo, introduzindo visuais ou mensagens com clareza e impacto, numa experiência fluida e fácil de seguir. Casos de uso: introdução visual; destaque de produto (revelação suave); revelação de mensagem (estruturada, fácil de ler); marca e mensagem; foco em elemento-chave. Boas práticas: visuais simples e claros; foco numa única mensagem; visuais consistentes entre si; guiar a atenção naturalmente; a revelação deve acrescentar valor real; alinhado com a marca. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+        </is>
+      </c>
+      <c r="M736" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/display-creatives/rise-design-specifications</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>Display Creatives - Unfold</t>
+        </is>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>Formatos próprios Ogury: Full Screen, Thumbnail, Header, Footer, In-article Reveal. Formatos IAB standard: tamanhos a confirmar na página de formatos e tamanhos suportados.</t>
+        </is>
+      </c>
+      <c r="J737" t="inlineStr">
+        <is>
+          <t>PSD (camadas), AI, INDD, Figma ou XD</t>
+        </is>
+      </c>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>Máximo 2–4 palavras (10 a 20 carateres incl. espaços). Evitar pontuação e quebras de linha.</t>
+        </is>
+      </c>
+      <c r="L737" t="inlineStr">
+        <is>
+          <t>Efeito de revelação a partir do centro: os visuais dividem-se e desdobram-se para introduzir novo conteúdo, criando uma transição dinâmica que mantém o utilizador envolvido — ideal para revelar progressivamente vários visuais de forma fluida e estruturada. Casos de uso: storytelling sequencial; showcase de produto (produtos/variações diferentes); destaque de coleção (ex. moda, beleza, automóvel); breakdown de features; revelação de campanha (mensagens-chave progressivas); progressão visual (evolução de um visual para outro). Boas práticas: limitar a 5 ecrãs no máximo; estilo consistente entre todos os visuais; foco numa ideia principal; visuais fortes (impacto imediato em cada ecrã); layout limpo (sem clutter); alinhado com a marca. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+        </is>
+      </c>
+      <c r="M737" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/display-creatives/unfold-design-specifications</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -19758,7 +19758,7 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>Spot TV (HD — XDCAM HD422)</t>
+          <t>Spot</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M737"/>
+  <dimension ref="A1:M749"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34489,6 +34489,595 @@
         </is>
       </c>
     </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>Paid Social</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>Interactive Add-on - Super Like</t>
+        </is>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>Ícone: 196x196px (mín. 160x160px) — área de output 200x200px, o visual não pode ultrapassar esta área. Cartão pop-up (opcional): 620x788px, com a área do botão CTA a 620x168px na base.</t>
+        </is>
+      </c>
+      <c r="I738" t="inlineStr">
+        <is>
+          <t>Ícone: máx. 50 KB. Cartão pop-up: máx. 3 MB.</t>
+        </is>
+      </c>
+      <c r="J738" t="inlineStr">
+        <is>
+          <t>Ícone: PNG. Cartão pop-up: JPG, JPEG ou PNG.</t>
+        </is>
+      </c>
+      <c r="L738" t="inlineStr">
+        <is>
+          <t>Add-on interativo: ícones em forma de coração (ou personalizados) flutuam pelo ecrã quando a audiência dá like ou toca duas vezes no anúncio. Pode incluir-se opcionalmente um cartão pop-up personalizado, que aparece depois da animação — ao clicar, leva à landing page do anúncio. Imagem do ícone: fornecer uma única imagem estática (é redimensionada automaticamente); design rico e preenchido com cor de fundo, evitando formas ocas, sombra, dispersão de elementos, formas finas ou efeito 3D; se retangular, cantos arredondados a 24px; deixar 2px de margem à volta da área válida; evitar que o elemento principal fique demasiado pequeno em relação à área efetiva (vermelha). Cartão pop-up: evitar design totalmente branco ou transparente.</t>
+        </is>
+      </c>
+      <c r="M738" t="inlineStr">
+        <is>
+          <t>https://ads.tiktok.com/resources/help/article/tiktok-interactive-add-on-super-like</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>Paid Social</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>Interactive Add-on - Pop-out Showcase</t>
+        </is>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>Elemento pop-out: 448x448px.</t>
+        </is>
+      </c>
+      <c r="I739" t="inlineStr">
+        <is>
+          <t>Elemento pop-out: 100 KB a 500 KB.</t>
+        </is>
+      </c>
+      <c r="J739" t="inlineStr">
+        <is>
+          <t>Elemento pop-out: PNG. Vídeo do anúncio: ver specs gerais do In-Feed.</t>
+        </is>
+      </c>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>CTA do elemento pop-out: até 27 carateres EN ou até 13 CN/JP/KR. Carateres half-width ocupam 1 espaço, full-width ocupam 2. Não suporta emojis nem carateres especiais ({ }, @, #). Não suporta links na legenda do anúncio. Evitar código de barras, código de ações, ID de Facebook/Instagram/WhatsApp/Messenger ou outra informação de redes sociais.</t>
+        </is>
+      </c>
+      <c r="L739" t="inlineStr">
+        <is>
+          <t>O vídeo do anúncio toca normalmente e o botão CTA aparece; depois, um elemento pop-out salta para o centro do ecrã, minimiza-se e desloca-se para o canto esquerdo. O vídeo do anúncio tem de ter mín. 8 segundos (recomendado 15s+). O elemento pop-out tem de ser o mesmo produto/SKU/cor do anúncio, e só pode aparecer enquanto o produto está visível no ecrã; só pode ser definido a partir dos 3 segundos de anúncio e até, no mínimo, 5 segundos antes do fim. Sem limitação de ângulo de entrada (o elemento gira até 0° no sentido que corresponde ao ângulo de entrada). Posição do elemento: entre X 125-515, Y 200-710 (ver ferramenta de pré-visualização da TikTok). O elemento ajusta automaticamente o tamanho para não sobrepor a legenda do anúncio.</t>
+        </is>
+      </c>
+      <c r="M739" t="inlineStr">
+        <is>
+          <t>https://ads.tiktok.com/resources/help/article/tiktok-interactive-add-on-pop-out-showcase</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>Paid Social</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>Interactive Add-on - Display Card</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>Upload recomendado: 1920x1080px (qualquer tamanho é aceite — a plataforma permite recortar/redimensionar). Tamanho final de apresentação: 750x421px.</t>
+        </is>
+      </c>
+      <c r="I740" t="inlineStr">
+        <is>
+          <t>Sem limite de tamanho de ficheiro.</t>
+        </is>
+      </c>
+      <c r="J740" t="inlineStr">
+        <is>
+          <t>JPG, JPEG ou PNG.</t>
+        </is>
+      </c>
+      <c r="L740" t="inlineStr">
+        <is>
+          <t>Card interativo que aparece dentro do anúncio in-feed, para destacar mensagens importantes, ofertas exclusivas ou direcionar para o site/app. O popup do card aparece automaticamente ao fim de alguns segundos — o momento é calculado pela plataforma consoante o objetivo, indústria e comportamento da audiência, não é configurável. Forma do card: sempre retangular. Evitar design transparente no meio do card (a margem pode ser transparente). Incluir um botão CTA claramente visível. A cor deve destacar-se do vídeo. Evitar material com pixels baixos, mosaico ou serrilhado nos contornos. As safe zones variam consoante o formato do anúncio (vertical/quadrado/horizontal) e o comprimento da legenda (legendas mais longas reduzem a safe zone) — descarregar os ficheiros de safe zone correspondentes e usar a ferramenta de pré-visualização para confirmar. Existe versão Standard LTR (esquerda para a direita, todas as regiões exceto árabe) e versão árabe RTL (direita para a esquerda).</t>
+        </is>
+      </c>
+      <c r="M740" t="inlineStr">
+        <is>
+          <t>https://ads.tiktok.com/resources/help/article/tiktok-interactive-add-on-display-card</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>Paid Social</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>Interactive Add-on - Gesture</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>Cartão: 620x788px, com a área do botão CTA a 620x168px na base.</t>
+        </is>
+      </c>
+      <c r="I741" t="inlineStr">
+        <is>
+          <t>Cartão: máx. 3 MB. Música de fundo: máx. 100 KB.</t>
+        </is>
+      </c>
+      <c r="J741" t="inlineStr">
+        <is>
+          <t>Cartão: JPG, JPEG, PNG ou GIF. Música de fundo: MP3.</t>
+        </is>
+      </c>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>Texto de orientação do gesto: até 27 carateres EN ou até 13 CN/JP/KR. Carateres half-width ocupam 1 espaço, full-width ocupam 2. Não suporta emojis nem carateres especiais ({ }, @, #). Não suporta links na legenda do anúncio. Evitar código de barras, código de ações, ID de Facebook/Instagram/WhatsApp/Messenger ou outra informação de redes sociais.</t>
+        </is>
+      </c>
+      <c r="L741" t="inlineStr">
+        <is>
+          <t>Convida a audiência a tocar ou deslizar no anúncio para desbloquear recompensas ou mais informação. Música de fundo do pop-up obrigatória: 6 segundos, idealmente consistente com a música do próprio vídeo do anúncio. Momento do pop-up: em Reach &amp; Frequency, a partir dos 3 segundos de anúncio e até 5 segundos antes do fim; em Auction Reach, a partir dos 6 segundos e até 5 segundos antes do fim. Posição, comprimento e ângulo do gesto configuram-se na ferramenta de pré-visualização (o ângulo tem de respeitar a zona marcada a vermelho). Vídeo do anúncio: mín. 8 segundos (recomendado 15s+). Gestos suportados: clique, deslize reto ou deslize curvo. O URL do cartão usa sempre o mesmo URL do botão CTA do anúncio (não se insere em separado).</t>
+        </is>
+      </c>
+      <c r="M741" t="inlineStr">
+        <is>
+          <t>https://ads.tiktok.com/resources/help/article/tiktok-interactive-add-on-gesture</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>Paid Social</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>Interactive Add-on - Gift Code Sticker</t>
+        </is>
+      </c>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>Nome do código: até 10 carateres CN/JP/KR ou até 20 noutras línguas. Código: até 10 carateres CN/JP/KR ou até 21 noutras línguas.</t>
+        </is>
+      </c>
+      <c r="L742" t="inlineStr">
+        <is>
+          <t>Adiciona um código promocional exclusivo ao vídeo do anúncio. Elementos do sticker: título, código, botão de copiar e botão CTA. Cor do sticker: cinzento ou azul (sem personalização de cor). Os anúncios com Gift Code Sticker têm de incluir URL (pode ser o mesmo da página de destino do anúncio). Garantir que o sticker fica dentro da safe zone.</t>
+        </is>
+      </c>
+      <c r="M742" t="inlineStr">
+        <is>
+          <t>https://ads.tiktok.com/resources/help/article/tiktok-interactive-add-on-gift-code-sticker</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>Paid Social</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>Interactive Add-on - Countdown Sticker</t>
+        </is>
+      </c>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>Título: até 54 carateres EN ou até 27 carateres CN/JP/KR. Não suporta hashtag (#).</t>
+        </is>
+      </c>
+      <c r="L743" t="inlineStr">
+        <is>
+          <t>Adiciona um temporizador de contagem decrescente ao vídeo do anúncio. Tamanho, ângulo e posição ajustam-se no TikTok Ads Manager. Cor do sticker: laranja, preto, azul ou rosa (sem personalização de cor). O título mostra-se na língua em que foi escrito (não é traduzido automaticamente) — sugerir frases como "termina em"/"começa em". O CTA é o mesmo escolhido no Ads Manager, traduzido automaticamente para a língua do utilizador (suporta Dynamic CTA). Os anúncios com Countdown Sticker têm de incluir URL (pode ser o mesmo da página de destino). O tempo é traduzido e calculado automaticamente consoante o fuso horário do utilizador. Garantir que o sticker fica dentro da safe zone (azul).</t>
+        </is>
+      </c>
+      <c r="M743" t="inlineStr">
+        <is>
+          <t>https://ads.tiktok.com/resources/help/article/tiktok-interactive-add-on-countdown-sticker</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>Paid Social</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>Interactive Add-on - Voting Sticker</t>
+        </is>
+      </c>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>Título: até 65 carateres EN ou até 32 CN/JP/KR. Opção A e Opção B: até 16 carateres EN ou até 8 CN/JP/KR cada.</t>
+        </is>
+      </c>
+      <c r="L744" t="inlineStr">
+        <is>
+          <t>Adiciona um tópico de votação com duas opções ao vídeo do anúncio, para aumentar o engagement e recolher informação relevante. Elementos: título, texto da opção A e texto da opção B. Cor do texto: título sempre a branco (sem personalização); opções A/B disponíveis em vermelho, azul claro ou azul escuro. Garantir que o sticker fica dentro da safe zone.</t>
+        </is>
+      </c>
+      <c r="M744" t="inlineStr">
+        <is>
+          <t>https://ads.tiktok.com/resources/help/article/tiktok-interactive-add-on-voting-sticker</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>Paid Social</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>Interactive Add-on - Download Card</t>
+        </is>
+      </c>
+      <c r="L745" t="inlineStr">
+        <is>
+          <t>Mostra elementos da app promovida (avaliação, nº de reviews, indústria) dentro do anúncio in-feed — é um elemento clicável que leva à loja de download da app. Cada elemento-chave (texto, logos) tem de ficar dentro da safe zone, sob pena de ser cortado/tapado. O tamanho da safe zone depende do formato do anúncio (vertical/quadrado/horizontal) e do comprimento da legenda — legendas mais longas reduzem a safe zone; descarregar os ficheiros de safe zone correspondentes ao formato usado. Existe versão Standard LTR (esquerda para a direita, todas as regiões exceto árabe) e versão árabe RTL (direita para a esquerda). Confirmar sempre na ferramenta de pré-visualização.</t>
+        </is>
+      </c>
+      <c r="M745" t="inlineStr">
+        <is>
+          <t>https://ads.tiktok.com/resources/help/article/tiktok-interactive-add-on-download-card-ad-specifications</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>Paid Social</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>Interactive Add-on - Story Selection</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>Vídeo principal: mín. 5s (6s em anúncios 6s Focused View), máx. 60s (recomendado &lt;10s). Sub-vídeo A e sub-vídeo B: máx. 30s cada. Imagem de capa dos sub-vídeos (opcional): 144x192px.</t>
+        </is>
+      </c>
+      <c r="J746" t="inlineStr">
+        <is>
+          <t>Vídeos: MP4, MOV, MPEG ou 3GP. Imagens de capa: PNG ou JPG.</t>
+        </is>
+      </c>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>Tópico de seleção: até 40 carateres EN ou até 20 CN/KR/JP.</t>
+        </is>
+      </c>
+      <c r="L746" t="inlineStr">
+        <is>
+          <t>Função de seleção de história para anúncios in-feed: a audiência escolhe o próximo vídeo que quer ver. Criativos: vídeo principal (obrigatório), tópico de seleção em texto (obrigatório), sub-vídeo A (obrigatório) + imagem de capa (opcional — se não for fornecida, a plataforma usa a imagem do primeiro segundo do sub-vídeo, mas fornecer uma melhora a experiência), sub-vídeo B (obrigatório) + imagem de capa (opcional, mesma regra). Deixar o texto afastado das margens e evitar cobrir elementos-chave com o botão Play.</t>
+        </is>
+      </c>
+      <c r="M746" t="inlineStr">
+        <is>
+          <t>https://ads.tiktok.com/resources/help/article/about-tiktok-interactive-add-on-story-selection?lang=en</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>LiftMedia</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>LiftMedia</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>Ecrã Digital - Canal Executivo (Horizontal)</t>
+        </is>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>1280x720px (horizontal)</t>
+        </is>
+      </c>
+      <c r="H747" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I747" t="inlineStr">
+        <is>
+          <t>Máx.: 3 MB.</t>
+        </is>
+      </c>
+      <c r="J747" t="inlineStr">
+        <is>
+          <t>MP4, WMV ou AVI</t>
+        </is>
+      </c>
+      <c r="L747" t="inlineStr">
+        <is>
+          <t>Ecrã digital instalado no interior de elevadores de edifícios de escritórios (Canal Executivo). Duração recomendada: 10 segundos. Sem áudio. Taxa de frames: 30 FPS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>LiftMedia</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>LiftMedia</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>Ecrã Digital - Canal Executivo (Vertical)</t>
+        </is>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>720x1280px (vertical)</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
+      <c r="I748" t="inlineStr">
+        <is>
+          <t>Máx.: 3 MB.</t>
+        </is>
+      </c>
+      <c r="J748" t="inlineStr">
+        <is>
+          <t>MP4, WMV ou AVI</t>
+        </is>
+      </c>
+      <c r="L748" t="inlineStr">
+        <is>
+          <t>Ecrã digital instalado no interior de elevadores de edifícios de escritórios (Canal Executivo). Duração recomendada: 10 segundos. Sem áudio. Taxa de frames: 30 FPS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>LiftMedia</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>LiftMedia</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>Ecrã Digital - Canal Residencial</t>
+        </is>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>960x540px</t>
+        </is>
+      </c>
+      <c r="H749" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I749" t="inlineStr">
+        <is>
+          <t>Máx.: 400 KB.</t>
+        </is>
+      </c>
+      <c r="J749" t="inlineStr">
+        <is>
+          <t>MP4 ou JPG</t>
+        </is>
+      </c>
+      <c r="L749" t="inlineStr">
+        <is>
+          <t>Ecrã digital instalado no interior de elevadores de edifícios residenciais (Canal Residencial), rede com 868 ecrãs em 578 edifícios em Portugal. Duração: 10 segundos. Sem áudio. Taxa de frames: 30 FPS.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M755"/>
+  <dimension ref="A1:M756"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35400,6 +35400,48 @@
         </is>
       </c>
     </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>Kwanko</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>Kwanko</t>
+        </is>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>Display Digital</t>
+        </is>
+      </c>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>Sem especificações obrigatórias — qualquer dimensão é aceite.</t>
+        </is>
+      </c>
+      <c r="I756" t="inlineStr">
+        <is>
+          <t>Sem limite de peso.</t>
+        </is>
+      </c>
+      <c r="L756" t="inlineStr">
+        <is>
+          <t>Confirmado diretamente pela Kwanko: "Do nosso lado não temos limite de peso nem tamanho nos nossos formatos digitais. Não há especificações requeridas."</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M756"/>
+  <dimension ref="A1:M762"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35442,6 +35442,243 @@
         </is>
       </c>
     </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>GirodMedias</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>GirodMedias</t>
+        </is>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>Mupi Digital</t>
+        </is>
+      </c>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>1080x1920 píxeis (ecrã de 75″).</t>
+        </is>
+      </c>
+      <c r="H757" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
+      <c r="J757" t="inlineStr">
+        <is>
+          <t>MP4, orientação vertical.</t>
+        </is>
+      </c>
+      <c r="L757" t="inlineStr">
+        <is>
+          <t>Duração do anúncio: 10 segundos, em loop a cada 1 minuto. Prazo de envio dos ficheiros: 7 dias antes do início da campanha. Formato Retail Media.</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>GirodMedias</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>GirodMedias</t>
+        </is>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>Mupi</t>
+        </is>
+      </c>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>Painel publicitário: 1,40x2,56m (2m²). Dimensão do corte: 1185x1750mm. Área visível: 1147x1697mm. Altura do pé: 550mm.</t>
+        </is>
+      </c>
+      <c r="L758" t="inlineStr">
+        <is>
+          <t>Mupi de 2 faces com vidro temperado "securit" de 8mm; estrutura em aço galvanizado com tratamento anticorrosivo; quadro em alumínio com tratamento polyester; iluminado. Nota: a GirodMedias não indicou especificações de ficheiro (tipo, resolução, bleed) para este formato — confirmar diretamente com o fornecedor antes de produzir a arte final.</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>GirodMedias</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>GirodMedias</t>
+        </is>
+      </c>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>Outdoor 4x3</t>
+        </is>
+      </c>
+      <c r="G759" t="inlineStr">
+        <is>
+          <t>Painel publicitário: 4x3m (12m²), composto por 4 módulos de alumínio de 3x1m cada.</t>
+        </is>
+      </c>
+      <c r="L759" t="inlineStr">
+        <is>
+          <t>Módulos fixos a 2 vigas de ferro I 120-IPN, distanciadas 2,60m entre si, chumbadas ao solo; moldura de alumínio de 10cm, branca. Nota: a GirodMedias não indicou especificações de ficheiro (tipo, resolução, bleed) para este formato — confirmar diretamente com o fornecedor antes de produzir a arte final.</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>GirodMedias</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>GirodMedias</t>
+        </is>
+      </c>
+      <c r="F760" t="inlineStr">
+        <is>
+          <t>Outdoor 8x3</t>
+        </is>
+      </c>
+      <c r="G760" t="inlineStr">
+        <is>
+          <t>Painel publicitário: 8x3m (24m²), composto por 8 módulos de alumínio de 3x1m cada.</t>
+        </is>
+      </c>
+      <c r="L760" t="inlineStr">
+        <is>
+          <t>Módulos fixos a 4 vigas de ferro I 120-IPN, distanciadas 2,40m entre si, chumbadas ao solo; moldura de alumínio de 10cm, branca. Nota: a GirodMedias não indicou especificações de ficheiro (tipo, resolução, bleed) para este formato — confirmar diretamente com o fornecedor antes de produzir a arte final.</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>GirodMedias</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>GirodMedias</t>
+        </is>
+      </c>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>Monoposte 10x5</t>
+        </is>
+      </c>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>Área publicitária: 10x5m. Produção de 2 telas impressas digitalmente ao formato 10,40x5,40m.</t>
+        </is>
+      </c>
+      <c r="L761" t="inlineStr">
+        <is>
+          <t>Iluminação por 8 projetores LED de 100W (4 por face). Nota: a GirodMedias não indicou especificações de ficheiro (tipo, resolução, bleed) para este formato — confirmar diretamente com o fornecedor antes de produzir a arte final.</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>Fuel</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>Fuel</t>
+        </is>
+      </c>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>Mupi Papel</t>
+        </is>
+      </c>
+      <c r="G762" t="inlineStr">
+        <is>
+          <t>234x348mm + 1mm de bleed.</t>
+        </is>
+      </c>
+      <c r="J762" t="inlineStr">
+        <is>
+          <t>PDF.</t>
+        </is>
+      </c>
+      <c r="L762" t="inlineStr">
+        <is>
+          <t>CMYK, 300 dpi. Margem de segurança: 10mm. Miras de corte. Textos e logótipos convertidos em curvas.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M762"/>
+  <dimension ref="A1:N762"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,6 +480,11 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>Link</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Imagem</t>
         </is>
       </c>
     </row>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N762"/>
+  <dimension ref="A1:N771"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35408,42 +35408,47 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>INTERNET</t>
+          <t>OOH</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>OOH</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>Kwanko</t>
+          <t>GirodMedias</t>
         </is>
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>Kwanko</t>
+          <t>GirodMedias</t>
         </is>
       </c>
       <c r="F756" t="inlineStr">
         <is>
-          <t>Display Digital</t>
+          <t>Mupi Digital</t>
         </is>
       </c>
       <c r="G756" t="inlineStr">
         <is>
-          <t>Sem especificações obrigatórias — qualquer dimensão é aceite.</t>
-        </is>
-      </c>
-      <c r="I756" t="inlineStr">
-        <is>
-          <t>Sem limite de peso.</t>
+          <t>1080x1920 píxeis (ecrã de 75″).</t>
+        </is>
+      </c>
+      <c r="H756" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
+      <c r="J756" t="inlineStr">
+        <is>
+          <t>MP4, orientação vertical.</t>
         </is>
       </c>
       <c r="L756" t="inlineStr">
         <is>
-          <t>Confirmado diretamente pela Kwanko: "Do nosso lado não temos limite de peso nem tamanho nos nossos formatos digitais. Não há especificações requeridas."</t>
+          <t>Duração do anúncio: 10 segundos, em loop a cada 1 minuto. Prazo de envio dos ficheiros: 7 dias antes do início da campanha. Formato Retail Media.</t>
         </is>
       </c>
     </row>
@@ -35470,27 +35475,17 @@
       </c>
       <c r="F757" t="inlineStr">
         <is>
-          <t>Mupi Digital</t>
+          <t>Mupi</t>
         </is>
       </c>
       <c r="G757" t="inlineStr">
         <is>
-          <t>1080x1920 píxeis (ecrã de 75″).</t>
-        </is>
-      </c>
-      <c r="H757" t="inlineStr">
-        <is>
-          <t>9:16</t>
-        </is>
-      </c>
-      <c r="J757" t="inlineStr">
-        <is>
-          <t>MP4, orientação vertical.</t>
+          <t>Painel publicitário: 1,40x2,56m (2m²). Dimensão do corte: 1185x1750mm. Área visível: 1147x1697mm. Altura do pé: 550mm.</t>
         </is>
       </c>
       <c r="L757" t="inlineStr">
         <is>
-          <t>Duração do anúncio: 10 segundos, em loop a cada 1 minuto. Prazo de envio dos ficheiros: 7 dias antes do início da campanha. Formato Retail Media.</t>
+          <t>Mupi de 2 faces com vidro temperado "securit" de 8mm; estrutura em aço galvanizado com tratamento anticorrosivo; quadro em alumínio com tratamento polyester; iluminado. Nota: a GirodMedias não indicou especificações de ficheiro (tipo, resolução, bleed) para este formato — confirmar diretamente com o fornecedor antes de produzir a arte final.</t>
         </is>
       </c>
     </row>
@@ -35517,17 +35512,17 @@
       </c>
       <c r="F758" t="inlineStr">
         <is>
-          <t>Mupi</t>
+          <t>Outdoor 4x3</t>
         </is>
       </c>
       <c r="G758" t="inlineStr">
         <is>
-          <t>Painel publicitário: 1,40x2,56m (2m²). Dimensão do corte: 1185x1750mm. Área visível: 1147x1697mm. Altura do pé: 550mm.</t>
+          <t>Painel publicitário: 4x3m (12m²), composto por 4 módulos de alumínio de 3x1m cada.</t>
         </is>
       </c>
       <c r="L758" t="inlineStr">
         <is>
-          <t>Mupi de 2 faces com vidro temperado "securit" de 8mm; estrutura em aço galvanizado com tratamento anticorrosivo; quadro em alumínio com tratamento polyester; iluminado. Nota: a GirodMedias não indicou especificações de ficheiro (tipo, resolução, bleed) para este formato — confirmar diretamente com o fornecedor antes de produzir a arte final.</t>
+          <t>Módulos fixos a 2 vigas de ferro I 120-IPN, distanciadas 2,60m entre si, chumbadas ao solo; moldura de alumínio de 10cm, branca. Nota: a GirodMedias não indicou especificações de ficheiro (tipo, resolução, bleed) para este formato — confirmar diretamente com o fornecedor antes de produzir a arte final.</t>
         </is>
       </c>
     </row>
@@ -35554,17 +35549,17 @@
       </c>
       <c r="F759" t="inlineStr">
         <is>
-          <t>Outdoor 4x3</t>
+          <t>Outdoor 8x3</t>
         </is>
       </c>
       <c r="G759" t="inlineStr">
         <is>
-          <t>Painel publicitário: 4x3m (12m²), composto por 4 módulos de alumínio de 3x1m cada.</t>
+          <t>Painel publicitário: 8x3m (24m²), composto por 8 módulos de alumínio de 3x1m cada.</t>
         </is>
       </c>
       <c r="L759" t="inlineStr">
         <is>
-          <t>Módulos fixos a 2 vigas de ferro I 120-IPN, distanciadas 2,60m entre si, chumbadas ao solo; moldura de alumínio de 10cm, branca. Nota: a GirodMedias não indicou especificações de ficheiro (tipo, resolução, bleed) para este formato — confirmar diretamente com o fornecedor antes de produzir a arte final.</t>
+          <t>Módulos fixos a 4 vigas de ferro I 120-IPN, distanciadas 2,40m entre si, chumbadas ao solo; moldura de alumínio de 10cm, branca. Nota: a GirodMedias não indicou especificações de ficheiro (tipo, resolução, bleed) para este formato — confirmar diretamente com o fornecedor antes de produzir a arte final.</t>
         </is>
       </c>
     </row>
@@ -35591,17 +35586,17 @@
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>Outdoor 8x3</t>
+          <t>Monoposte 10x5</t>
         </is>
       </c>
       <c r="G760" t="inlineStr">
         <is>
-          <t>Painel publicitário: 8x3m (24m²), composto por 8 módulos de alumínio de 3x1m cada.</t>
+          <t>Área publicitária: 10x5m. Produção de 2 telas impressas digitalmente ao formato 10,40x5,40m.</t>
         </is>
       </c>
       <c r="L760" t="inlineStr">
         <is>
-          <t>Módulos fixos a 4 vigas de ferro I 120-IPN, distanciadas 2,40m entre si, chumbadas ao solo; moldura de alumínio de 10cm, branca. Nota: a GirodMedias não indicou especificações de ficheiro (tipo, resolução, bleed) para este formato — confirmar diretamente com o fornecedor antes de produzir a arte final.</t>
+          <t>Iluminação por 8 projetores LED de 100W (4 por face). Nota: a GirodMedias não indicou especificações de ficheiro (tipo, resolução, bleed) para este formato — confirmar diretamente com o fornecedor antes de produzir a arte final.</t>
         </is>
       </c>
     </row>
@@ -35618,69 +35613,482 @@
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>GirodMedias</t>
+          <t>Fuel</t>
         </is>
       </c>
       <c r="D761" t="inlineStr">
         <is>
-          <t>GirodMedias</t>
+          <t>Fuel</t>
         </is>
       </c>
       <c r="F761" t="inlineStr">
         <is>
-          <t>Monoposte 10x5</t>
+          <t>Mupi Papel</t>
         </is>
       </c>
       <c r="G761" t="inlineStr">
         <is>
-          <t>Área publicitária: 10x5m. Produção de 2 telas impressas digitalmente ao formato 10,40x5,40m.</t>
+          <t>234x348mm + 1mm de bleed.</t>
+        </is>
+      </c>
+      <c r="J761" t="inlineStr">
+        <is>
+          <t>PDF.</t>
         </is>
       </c>
       <c r="L761" t="inlineStr">
         <is>
-          <t>Iluminação por 8 projetores LED de 100W (4 por face). Nota: a GirodMedias não indicou especificações de ficheiro (tipo, resolução, bleed) para este formato — confirmar diretamente com o fornecedor antes de produzir a arte final.</t>
+          <t>CMYK, 300 dpi. Margem de segurança: 10mm. Miras de corte. Textos e logótipos convertidos em curvas.</t>
         </is>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>OOH</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
         <is>
-          <t>Fuel</t>
+          <t>Kwanko</t>
         </is>
       </c>
       <c r="D762" t="inlineStr">
         <is>
-          <t>Fuel</t>
+          <t>Kwanko</t>
         </is>
       </c>
       <c r="F762" t="inlineStr">
         <is>
-          <t>Mupi Papel</t>
+          <t>Medium Rectangle</t>
         </is>
       </c>
       <c r="G762" t="inlineStr">
         <is>
-          <t>234x348mm + 1mm de bleed.</t>
+          <t>300x250px.</t>
+        </is>
+      </c>
+      <c r="I762" t="inlineStr">
+        <is>
+          <t>Máx. 150 KB.</t>
         </is>
       </c>
       <c r="J762" t="inlineStr">
         <is>
-          <t>PDF.</t>
+          <t>JPG, PNG, GIF, HTML5.</t>
         </is>
       </c>
       <c r="L762" t="inlineStr">
         <is>
-          <t>CMYK, 300 dpi. Margem de segurança: 10mm. Miras de corte. Textos e logótipos convertidos em curvas.</t>
+          <t>Formato TOP 4 (foco da Kwanko, para máxima cobertura na rede). Ficheiro HTML5: entregar sempre em .ZIP (com o ficheiro index e os respetivos assets). As hiperligações devem ser inseridas como variáveis genéricas (clickTags), preparadas para receber os links de tracking dinâmico da plataforma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>Kwanko</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>Kwanko</t>
+        </is>
+      </c>
+      <c r="F763" t="inlineStr">
+        <is>
+          <t>Leaderboard</t>
+        </is>
+      </c>
+      <c r="G763" t="inlineStr">
+        <is>
+          <t>728x90px.</t>
+        </is>
+      </c>
+      <c r="I763" t="inlineStr">
+        <is>
+          <t>Máx. 150 KB.</t>
+        </is>
+      </c>
+      <c r="J763" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF, HTML5.</t>
+        </is>
+      </c>
+      <c r="L763" t="inlineStr">
+        <is>
+          <t>Formato TOP 4 (foco da Kwanko, para máxima cobertura na rede). Ficheiro HTML5: entregar sempre em .ZIP (com o ficheiro index e os respetivos assets). As hiperligações devem ser inseridas como variáveis genéricas (clickTags), preparadas para receber os links de tracking dinâmico da plataforma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>Kwanko</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>Kwanko</t>
+        </is>
+      </c>
+      <c r="F764" t="inlineStr">
+        <is>
+          <t>Wide Skyscraper</t>
+        </is>
+      </c>
+      <c r="G764" t="inlineStr">
+        <is>
+          <t>160x600px.</t>
+        </is>
+      </c>
+      <c r="I764" t="inlineStr">
+        <is>
+          <t>Máx. 150 KB.</t>
+        </is>
+      </c>
+      <c r="J764" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF, HTML5.</t>
+        </is>
+      </c>
+      <c r="L764" t="inlineStr">
+        <is>
+          <t>Formato TOP 4 (foco da Kwanko, para máxima cobertura na rede). Ficheiro HTML5: entregar sempre em .ZIP (com o ficheiro index e os respetivos assets). As hiperligações devem ser inseridas como variáveis genéricas (clickTags), preparadas para receber os links de tracking dinâmico da plataforma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>Kwanko</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>Kwanko</t>
+        </is>
+      </c>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>Mobile Banner</t>
+        </is>
+      </c>
+      <c r="G765" t="inlineStr">
+        <is>
+          <t>320x50px.</t>
+        </is>
+      </c>
+      <c r="I765" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB.</t>
+        </is>
+      </c>
+      <c r="J765" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF, HTML5.</t>
+        </is>
+      </c>
+      <c r="L765" t="inlineStr">
+        <is>
+          <t>Formato TOP 4 (foco da Kwanko, para máxima cobertura na rede). Ficheiro HTML5: entregar sempre em .ZIP (com o ficheiro index e os respetivos assets). As hiperligações devem ser inseridas como variáveis genéricas (clickTags), preparadas para receber os links de tracking dinâmico da plataforma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>Kwanko</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>Kwanko</t>
+        </is>
+      </c>
+      <c r="F766" t="inlineStr">
+        <is>
+          <t>Half Page</t>
+        </is>
+      </c>
+      <c r="G766" t="inlineStr">
+        <is>
+          <t>300x600px.</t>
+        </is>
+      </c>
+      <c r="I766" t="inlineStr">
+        <is>
+          <t>Máx. 200 KB.</t>
+        </is>
+      </c>
+      <c r="J766" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF, HTML5.</t>
+        </is>
+      </c>
+      <c r="L766" t="inlineStr">
+        <is>
+          <t>Ficheiro HTML5: entregar sempre em .ZIP (com o ficheiro index e os respetivos assets). As hiperligações devem ser inseridas como variáveis genéricas (clickTags), preparadas para receber os links de tracking dinâmico da plataforma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>Kwanko</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>Kwanko</t>
+        </is>
+      </c>
+      <c r="F767" t="inlineStr">
+        <is>
+          <t>Billboard</t>
+        </is>
+      </c>
+      <c r="G767" t="inlineStr">
+        <is>
+          <t>970x250px.</t>
+        </is>
+      </c>
+      <c r="I767" t="inlineStr">
+        <is>
+          <t>Máx. 200 KB.</t>
+        </is>
+      </c>
+      <c r="J767" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF, HTML5.</t>
+        </is>
+      </c>
+      <c r="L767" t="inlineStr">
+        <is>
+          <t>Ficheiro HTML5: entregar sempre em .ZIP (com o ficheiro index e os respetivos assets). As hiperligações devem ser inseridas como variáveis genéricas (clickTags), preparadas para receber os links de tracking dinâmico da plataforma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>Kwanko</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>Kwanko</t>
+        </is>
+      </c>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>Kit de Email Marketing</t>
+        </is>
+      </c>
+      <c r="G768" t="inlineStr">
+        <is>
+          <t>Largura máxima: 600px.</t>
+        </is>
+      </c>
+      <c r="I768" t="inlineStr">
+        <is>
+          <t>Código fonte: máx. 100 KB (para evitar corte por limite de peso em clientes como o Gmail).</t>
+        </is>
+      </c>
+      <c r="J768" t="inlineStr">
+        <is>
+          <t>HTML estático.</t>
+        </is>
+      </c>
+      <c r="L768" t="inlineStr">
+        <is>
+          <t>Apenas código HTML estático — não incluir Javascript, iframes, Flash ou formulários embebidos. O CSS deve estar sempre declarado inline (dentro das tags) e nunca na secção head. Imagens alojadas num servidor público e fiável, com URLs absolutos e completos (ex.: https://www.dominio.pt/assets/header.jpg).</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>Kwanko</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>Kwanko</t>
+        </is>
+      </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>Native Ads</t>
+        </is>
+      </c>
+      <c r="G769" t="inlineStr">
+        <is>
+          <t>Imagem principal: 1200x628px ou 600x600px.</t>
+        </is>
+      </c>
+      <c r="I769" t="inlineStr">
+        <is>
+          <t>Imagem principal: até 250 KB.</t>
+        </is>
+      </c>
+      <c r="J769" t="inlineStr">
+        <is>
+          <t>JPG, PNG (imagem principal).</t>
+        </is>
+      </c>
+      <c r="K769" t="inlineStr">
+        <is>
+          <t>Título do anúncio: 50 a 60 caracteres, de forma impactante. Copy/Descrição: 90 a 100 caracteres, com o contexto da campanha e o benefício direto para o utilizador. Call to Action: texto claro e direto (ex.: "Saber Mais", "Comprar Agora", "Registe-se Aqui").</t>
+        </is>
+      </c>
+      <c r="L769" t="inlineStr">
+        <is>
+          <t>A imagem principal deve estar visualmente limpa, sem texto sobreposto nem logótipos intrusivos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>Kwanko</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>Kwanko</t>
+        </is>
+      </c>
+      <c r="F770" t="inlineStr">
+        <is>
+          <t>Catálogo/Feed de Produtos</t>
+        </is>
+      </c>
+      <c r="J770" t="inlineStr">
+        <is>
+          <t>XML (preferencial) ou CSV, via URL dinâmico.</t>
+        </is>
+      </c>
+      <c r="L770" t="inlineStr">
+        <is>
+          <t>Sincronização/atualização no mínimo diária. Campos obrigatórios: ID único, Título do Produto, Preço de Venda, Preço Anterior (se aplicável), URL da página de produto, URL da imagem em boa resolução, e Categoria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>Kwanko</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>Kwanko</t>
+        </is>
+      </c>
+      <c r="F771" t="inlineStr">
+        <is>
+          <t>Vouchers e Códigos Promocionais</t>
+        </is>
+      </c>
+      <c r="L771" t="inlineStr">
+        <is>
+          <t>Ao partilhar materiais para campanhas baseadas em Códigos de Desconto (Cupões), é obrigatório indicar à Kwanko: o código exato (em formato de texto copiável); a mecânica exata do desconto (ex.: -10€ diretos, 20% desconto no carrinho, Oferta de Portes); a data de início e de expiração rigorosas da campanha; e as regras de exclusão (produtos ou marcas não abrangidos pela promoção).</t>
         </is>
       </c>
     </row>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -36078,7 +36078,7 @@
       </c>
       <c r="L771" t="inlineStr">
         <is>
-          <t>Segmentação para qualificação dos clicks incluída. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Segmentação para qualificação dos clicks incluída. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="M771" t="inlineStr">
@@ -36130,7 +36130,7 @@
       </c>
       <c r="L772" t="inlineStr">
         <is>
-          <t>Segmentação para qualificação dos clicks incluída. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Segmentação para qualificação dos clicks incluída. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="M772" t="inlineStr">
@@ -36182,7 +36182,7 @@
       </c>
       <c r="L773" t="inlineStr">
         <is>
-          <t>Segmentação para qualificação dos clicks incluída. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Segmentação para qualificação dos clicks incluída. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="M773" t="inlineStr">
@@ -36234,7 +36234,7 @@
       </c>
       <c r="L774" t="inlineStr">
         <is>
-          <t>Segmentação para qualificação dos clicks incluída. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Segmentação para qualificação dos clicks incluída. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="M774" t="inlineStr">
@@ -36328,7 +36328,7 @@
       </c>
       <c r="L776" t="inlineStr">
         <is>
-          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="M776" t="inlineStr">
@@ -36380,7 +36380,7 @@
       </c>
       <c r="L777" t="inlineStr">
         <is>
-          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="M777" t="inlineStr">
@@ -36432,7 +36432,7 @@
       </c>
       <c r="L778" t="inlineStr">
         <is>
-          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="M778" t="inlineStr">
@@ -36484,7 +36484,7 @@
       </c>
       <c r="L779" t="inlineStr">
         <is>
-          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="M779" t="inlineStr">
@@ -36536,7 +36536,7 @@
       </c>
       <c r="L780" t="inlineStr">
         <is>
-          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="M780" t="inlineStr">
@@ -36588,7 +36588,7 @@
       </c>
       <c r="L781" t="inlineStr">
         <is>
-          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="M781" t="inlineStr">
@@ -36640,7 +36640,7 @@
       </c>
       <c r="L782" t="inlineStr">
         <is>
-          <t>Formato da família Display da Azerion (não vinha nomeado no ratecard, só na página de specs). Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Formato da família Display da Azerion (não vinha nomeado no ratecard, só na página de specs). Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="M782" t="inlineStr">
@@ -36692,7 +36692,7 @@
       </c>
       <c r="L783" t="inlineStr">
         <is>
-          <t>Formato da família Display da Azerion (não vinha nomeado no ratecard, só na página de specs). Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Formato da família Display da Azerion (não vinha nomeado no ratecard, só na página de specs). Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="M783" t="inlineStr">
@@ -36744,7 +36744,7 @@
       </c>
       <c r="L784" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="M784" t="inlineStr">
@@ -36796,7 +36796,7 @@
       </c>
       <c r="L785" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, 4 imagens de produto. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, 4 imagens de produto.</t>
         </is>
       </c>
       <c r="M785" t="inlineStr">
@@ -36848,7 +36848,7 @@
       </c>
       <c r="L786" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="M786" t="inlineStr">
@@ -36900,7 +36900,7 @@
       </c>
       <c r="L787" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="M787" t="inlineStr">
@@ -36952,7 +36952,7 @@
       </c>
       <c r="L788" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="M788" t="inlineStr">
@@ -37004,7 +37004,7 @@
       </c>
       <c r="L789" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="M789" t="inlineStr">
@@ -37056,7 +37056,7 @@
       </c>
       <c r="L790" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="M790" t="inlineStr">
@@ -37108,7 +37108,7 @@
       </c>
       <c r="L791" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="M791" t="inlineStr">
@@ -37160,7 +37160,7 @@
       </c>
       <c r="L792" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="M792" t="inlineStr">
@@ -37212,7 +37212,7 @@
       </c>
       <c r="L793" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="M793" t="inlineStr">
@@ -37264,7 +37264,7 @@
       </c>
       <c r="L794" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="M794" t="inlineStr">
@@ -37316,7 +37316,7 @@
       </c>
       <c r="L795" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="M795" t="inlineStr">
@@ -37368,7 +37368,7 @@
       </c>
       <c r="L796" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto em diferentes cores. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto em diferentes cores.</t>
         </is>
       </c>
       <c r="M796" t="inlineStr">
@@ -37420,7 +37420,7 @@
       </c>
       <c r="L797" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens 360°. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens 360°.</t>
         </is>
       </c>
       <c r="M797" t="inlineStr">
@@ -37472,7 +37472,7 @@
       </c>
       <c r="L798" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="M798" t="inlineStr">
@@ -37524,7 +37524,7 @@
       </c>
       <c r="L799" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="M799" t="inlineStr">
@@ -37576,7 +37576,7 @@
       </c>
       <c r="L800" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, 2 imagens no mínimo — pode conter vídeo. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, 2 imagens no mínimo — pode conter vídeo.</t>
         </is>
       </c>
       <c r="M800" t="inlineStr">
@@ -37628,7 +37628,7 @@
       </c>
       <c r="L801" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="M801" t="inlineStr">
@@ -37680,7 +37680,7 @@
       </c>
       <c r="L802" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, 2 imagens no mínimo. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, 2 imagens no mínimo.</t>
         </is>
       </c>
       <c r="M802" t="inlineStr">
@@ -37732,7 +37732,7 @@
       </c>
       <c r="L803" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, 2 imagens no mínimo. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, 2 imagens no mínimo.</t>
         </is>
       </c>
       <c r="M803" t="inlineStr">
@@ -37784,7 +37784,7 @@
       </c>
       <c r="L804" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="M804" t="inlineStr">
@@ -37836,7 +37836,7 @@
       </c>
       <c r="L805" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="M805" t="inlineStr">
@@ -37888,7 +37888,7 @@
       </c>
       <c r="L806" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, data. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, data.</t>
         </is>
       </c>
       <c r="M806" t="inlineStr">
@@ -37940,7 +37940,7 @@
       </c>
       <c r="L807" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, perguntas e respostas (máx. 3 perguntas). Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, perguntas e respostas (máx. 3 perguntas).</t>
         </is>
       </c>
       <c r="M807" t="inlineStr">
@@ -37992,7 +37992,7 @@
       </c>
       <c r="L808" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, pode conter vídeo. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, pode conter vídeo.</t>
         </is>
       </c>
       <c r="M808" t="inlineStr">
@@ -38044,7 +38044,7 @@
       </c>
       <c r="L809" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, playlist, música ou episódio do Spotify. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, playlist, música ou episódio do Spotify.</t>
         </is>
       </c>
       <c r="M809" t="inlineStr">
@@ -38096,7 +38096,7 @@
       </c>
       <c r="L810" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="M810" t="inlineStr">
@@ -38148,7 +38148,7 @@
       </c>
       <c r="L811" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="M811" t="inlineStr">
@@ -38200,7 +38200,7 @@
       </c>
       <c r="L812" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="M812" t="inlineStr">
@@ -38252,7 +38252,7 @@
       </c>
       <c r="L813" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, formulário (por omissão: Google Forms). Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, formulário (por omissão: Google Forms).</t>
         </is>
       </c>
       <c r="M813" t="inlineStr">
@@ -38304,7 +38304,7 @@
       </c>
       <c r="L814" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, áudios em formato MP3. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, áudios em formato MP3.</t>
         </is>
       </c>
       <c r="M814" t="inlineStr">
@@ -38356,7 +38356,7 @@
       </c>
       <c r="L815" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localizações. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localizações.</t>
         </is>
       </c>
       <c r="M815" t="inlineStr">
@@ -38408,7 +38408,7 @@
       </c>
       <c r="L816" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localizações. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localizações.</t>
         </is>
       </c>
       <c r="M816" t="inlineStr">
@@ -38460,7 +38460,7 @@
       </c>
       <c r="L817" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="M817" t="inlineStr">
@@ -38512,7 +38512,7 @@
       </c>
       <c r="L818" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localização. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localização.</t>
         </is>
       </c>
       <c r="M818" t="inlineStr">
@@ -38564,7 +38564,7 @@
       </c>
       <c r="L819" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="M819" t="inlineStr">
@@ -38616,7 +38616,7 @@
       </c>
       <c r="L820" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localizações. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localizações.</t>
         </is>
       </c>
       <c r="M820" t="inlineStr">
@@ -38668,7 +38668,7 @@
       </c>
       <c r="L821" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localizações. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localizações.</t>
         </is>
       </c>
       <c r="M821" t="inlineStr">
@@ -38720,7 +38720,7 @@
       </c>
       <c r="L822" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, data. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, data.</t>
         </is>
       </c>
       <c r="M822" t="inlineStr">
@@ -38772,7 +38772,7 @@
       </c>
       <c r="L823" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, nº de telefone. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, nº de telefone.</t>
         </is>
       </c>
       <c r="M823" t="inlineStr">
@@ -38824,7 +38824,7 @@
       </c>
       <c r="L824" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, nº de telefone. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, nº de telefone.</t>
         </is>
       </c>
       <c r="M824" t="inlineStr">
@@ -38876,7 +38876,7 @@
       </c>
       <c r="L825" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="M825" t="inlineStr">
@@ -38928,7 +38928,7 @@
       </c>
       <c r="L826" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, formulário (por omissão: Google Forms). Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, formulário (por omissão: Google Forms).</t>
         </is>
       </c>
       <c r="M826" t="inlineStr">
@@ -38980,7 +38980,7 @@
       </c>
       <c r="L827" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="M827" t="inlineStr">
@@ -39032,7 +39032,7 @@
       </c>
       <c r="L828" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas dos diferentes produtos da campanha, logótipo, copy, data de início/fim, detalhes da promoção e produtos associados. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas dos diferentes produtos da campanha, logótipo, copy, data de início/fim, detalhes da promoção e produtos associados.</t>
         </is>
       </c>
       <c r="M828" t="inlineStr">
@@ -39084,7 +39084,7 @@
       </c>
       <c r="L829" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas dos diferentes produtos da campanha, logótipo, copy, data de início/fim, detalhes da promoção, produtos associados e localização. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas dos diferentes produtos da campanha, logótipo, copy, data de início/fim, detalhes da promoção, produtos associados e localização.</t>
         </is>
       </c>
       <c r="M829" t="inlineStr">
@@ -39136,7 +39136,7 @@
       </c>
       <c r="L830" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas dos diferentes produtos da campanha, logótipo, copy, data de início/fim, detalhes da promoção, produtos associados e localização. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas dos diferentes produtos da campanha, logótipo, copy, data de início/fim, detalhes da promoção, produtos associados e localização.</t>
         </is>
       </c>
       <c r="M830" t="inlineStr">
@@ -39188,7 +39188,7 @@
       </c>
       <c r="L831" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas dos diferentes produtos da campanha, logótipo, copy, data de início/fim e localização. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas dos diferentes produtos da campanha, logótipo, copy, data de início/fim e localização.</t>
         </is>
       </c>
       <c r="M831" t="inlineStr">
@@ -39240,7 +39240,7 @@
       </c>
       <c r="L832" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="M832" t="inlineStr">
@@ -39287,7 +39287,7 @@
       </c>
       <c r="L833" t="inlineStr">
         <is>
-          <t>Peso máximo não indicado na página de specs (só nos outros formatos da galeria). Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas. Jogo com 3 ecrãs obrigatórios: ecrã de jogar (com URL), ecrã do jogo em si (sem URL), e ecrã de fim de jogo (com URL).</t>
+          <t>Peso máximo não indicado na página de specs (só nos outros formatos da galeria). Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Jogo com 3 ecrãs obrigatórios: ecrã de jogar (com URL), ecrã do jogo em si (sem URL), e ecrã de fim de jogo (com URL).</t>
         </is>
       </c>
       <c r="M833" t="inlineStr">
@@ -39339,7 +39339,7 @@
       </c>
       <c r="L834" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="M834" t="inlineStr">
@@ -39391,7 +39391,7 @@
       </c>
       <c r="L835" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="M835" t="inlineStr">
@@ -39443,7 +39443,7 @@
       </c>
       <c r="L836" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="M836" t="inlineStr">
@@ -39495,7 +39495,7 @@
       </c>
       <c r="L837" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="M837" t="inlineStr">
@@ -39547,7 +39547,7 @@
       </c>
       <c r="L838" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="M838" t="inlineStr">
@@ -39599,7 +39599,7 @@
       </c>
       <c r="L839" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="M839" t="inlineStr">
@@ -39651,7 +39651,7 @@
       </c>
       <c r="L840" t="inlineStr">
         <is>
-          <t>Sem redirecionamento (redirect) disponível. Material necessário: ficheiro PSD em camadas, logótipo, texto e copy. Definição (Azerion): formato publicitário digital que se integra naturalmente no conteúdo/design da plataforma onde aparece, imitando o seu estilo visual para não interromper a experiência do utilizador.</t>
+          <t>Sem redirecionamento (redirect) disponível. Material necessário: ficheiro PSD em camadas, logótipo, texto e copy.</t>
         </is>
       </c>
       <c r="M840" t="inlineStr">
@@ -39703,7 +39703,7 @@
       </c>
       <c r="L841" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="M841" t="inlineStr">
@@ -39755,7 +39755,7 @@
       </c>
       <c r="L842" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="M842" t="inlineStr">
@@ -39807,7 +39807,7 @@
       </c>
       <c r="L843" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="M843" t="inlineStr">
@@ -39859,7 +39859,7 @@
       </c>
       <c r="L844" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de exibição (dwell time): máx. 30 seg. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="M844" t="inlineStr">
@@ -39911,7 +39911,7 @@
       </c>
       <c r="L845" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de exibição (dwell time): máx. 30 seg. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="M845" t="inlineStr">
@@ -39963,7 +39963,7 @@
       </c>
       <c r="L846" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="M846" t="inlineStr">
@@ -40015,7 +40015,7 @@
       </c>
       <c r="L847" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="M847" t="inlineStr">
@@ -40067,7 +40067,7 @@
       </c>
       <c r="L848" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de exibição (dwell time): máx. 30 seg. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="M848" t="inlineStr">
@@ -40119,7 +40119,7 @@
       </c>
       <c r="L849" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="M849" t="inlineStr">
@@ -40171,7 +40171,7 @@
       </c>
       <c r="L850" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de exibição (dwell time): máx. 30 seg. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="M850" t="inlineStr">
@@ -40223,7 +40223,7 @@
       </c>
       <c r="L851" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo, lista de músicas. Tempo de exibição (dwell time): máx. 30 seg. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo, lista de músicas. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="M851" t="inlineStr">
@@ -40275,7 +40275,7 @@
       </c>
       <c r="L852" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="M852" t="inlineStr">
@@ -40327,7 +40327,7 @@
       </c>
       <c r="L853" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="M853" t="inlineStr">
@@ -40379,7 +40379,7 @@
       </c>
       <c r="L854" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="M854" t="inlineStr">
@@ -40431,7 +40431,7 @@
       </c>
       <c r="L855" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="M855" t="inlineStr">
@@ -40483,7 +40483,7 @@
       </c>
       <c r="L856" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="M856" t="inlineStr">
@@ -40535,7 +40535,7 @@
       </c>
       <c r="L857" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="M857" t="inlineStr">
@@ -40587,7 +40587,7 @@
       </c>
       <c r="L858" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="M858" t="inlineStr">
@@ -40639,7 +40639,7 @@
       </c>
       <c r="L859" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="M859" t="inlineStr">
@@ -40691,7 +40691,7 @@
       </c>
       <c r="L860" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo (se aplicável). Tempo de exibição (dwell time): máx. 30 seg. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas. Formato de wallpaper de alto impacto, com ação especial totalmente à medida da marca — disponibilidade a confirmar com a equipa comercial da Azerion.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo (se aplicável). Tempo de exibição (dwell time): máx. 30 seg. Formato de wallpaper de alto impacto, com ação especial totalmente à medida da marca — disponibilidade a confirmar com a equipa comercial da Azerion.</t>
         </is>
       </c>
       <c r="M860" t="inlineStr">

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -36073,12 +36073,12 @@
       </c>
       <c r="J771" t="inlineStr">
         <is>
-          <t>JPEG, GIF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L771" t="inlineStr">
         <is>
-          <t>Segmentação para qualificação dos clicks incluída. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Segmentação para qualificação dos clicks incluída. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: JPEG, GIF.</t>
         </is>
       </c>
       <c r="M771" t="inlineStr">
@@ -36125,12 +36125,12 @@
       </c>
       <c r="J772" t="inlineStr">
         <is>
-          <t>JPEG, GIF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L772" t="inlineStr">
         <is>
-          <t>Segmentação para qualificação dos clicks incluída. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Segmentação para qualificação dos clicks incluída. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: JPEG, GIF.</t>
         </is>
       </c>
       <c r="M772" t="inlineStr">
@@ -36177,12 +36177,12 @@
       </c>
       <c r="J773" t="inlineStr">
         <is>
-          <t>JPEG, GIF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L773" t="inlineStr">
         <is>
-          <t>Segmentação para qualificação dos clicks incluída. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Segmentação para qualificação dos clicks incluída. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: JPEG, GIF.</t>
         </is>
       </c>
       <c r="M773" t="inlineStr">
@@ -36229,12 +36229,12 @@
       </c>
       <c r="J774" t="inlineStr">
         <is>
-          <t>JPEG, GIF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L774" t="inlineStr">
         <is>
-          <t>Segmentação para qualificação dos clicks incluída. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Segmentação para qualificação dos clicks incluída. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: JPEG, GIF.</t>
         </is>
       </c>
       <c r="M774" t="inlineStr">
@@ -36323,12 +36323,12 @@
       </c>
       <c r="J776" t="inlineStr">
         <is>
-          <t>JPEG, GIF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L776" t="inlineStr">
         <is>
-          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: JPEG, GIF.</t>
         </is>
       </c>
       <c r="M776" t="inlineStr">
@@ -36375,12 +36375,12 @@
       </c>
       <c r="J777" t="inlineStr">
         <is>
-          <t>JPEG, GIF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L777" t="inlineStr">
         <is>
-          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: JPEG, GIF.</t>
         </is>
       </c>
       <c r="M777" t="inlineStr">
@@ -36427,12 +36427,12 @@
       </c>
       <c r="J778" t="inlineStr">
         <is>
-          <t>JPEG, GIF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L778" t="inlineStr">
         <is>
-          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: JPEG, GIF.</t>
         </is>
       </c>
       <c r="M778" t="inlineStr">
@@ -36479,12 +36479,12 @@
       </c>
       <c r="J779" t="inlineStr">
         <is>
-          <t>JPEG, GIF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L779" t="inlineStr">
         <is>
-          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: JPEG, GIF.</t>
         </is>
       </c>
       <c r="M779" t="inlineStr">
@@ -36531,12 +36531,12 @@
       </c>
       <c r="J780" t="inlineStr">
         <is>
-          <t>JPEG, GIF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L780" t="inlineStr">
         <is>
-          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: JPEG, GIF.</t>
         </is>
       </c>
       <c r="M780" t="inlineStr">
@@ -36583,12 +36583,12 @@
       </c>
       <c r="J781" t="inlineStr">
         <is>
-          <t>JPEG, GIF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L781" t="inlineStr">
         <is>
-          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: JPEG, GIF.</t>
         </is>
       </c>
       <c r="M781" t="inlineStr">
@@ -36635,12 +36635,12 @@
       </c>
       <c r="J782" t="inlineStr">
         <is>
-          <t>JPEG, GIF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L782" t="inlineStr">
         <is>
-          <t>Formato da família Display da Azerion (não vinha nomeado no ratecard, só na página de specs). Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Formato da família Display da Azerion (não vinha nomeado no ratecard, só na página de specs). Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: JPEG, GIF.</t>
         </is>
       </c>
       <c r="M782" t="inlineStr">
@@ -36687,12 +36687,12 @@
       </c>
       <c r="J783" t="inlineStr">
         <is>
-          <t>JPEG, GIF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L783" t="inlineStr">
         <is>
-          <t>Formato da família Display da Azerion (não vinha nomeado no ratecard, só na página de specs). Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Formato da família Display da Azerion (não vinha nomeado no ratecard, só na página de specs). Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: JPEG, GIF.</t>
         </is>
       </c>
       <c r="M783" t="inlineStr">
@@ -36739,12 +36739,12 @@
       </c>
       <c r="J784" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L784" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M784" t="inlineStr">
@@ -36791,12 +36791,12 @@
       </c>
       <c r="J785" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L785" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, 4 imagens de produto.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, 4 imagens de produto. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M785" t="inlineStr">
@@ -36843,12 +36843,12 @@
       </c>
       <c r="J786" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L786" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M786" t="inlineStr">
@@ -36895,12 +36895,12 @@
       </c>
       <c r="J787" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L787" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M787" t="inlineStr">
@@ -36947,12 +36947,12 @@
       </c>
       <c r="J788" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L788" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M788" t="inlineStr">
@@ -36999,12 +36999,12 @@
       </c>
       <c r="J789" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L789" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M789" t="inlineStr">
@@ -37051,12 +37051,12 @@
       </c>
       <c r="J790" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L790" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M790" t="inlineStr">
@@ -37103,12 +37103,12 @@
       </c>
       <c r="J791" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L791" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M791" t="inlineStr">
@@ -37155,12 +37155,12 @@
       </c>
       <c r="J792" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L792" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M792" t="inlineStr">
@@ -37207,12 +37207,12 @@
       </c>
       <c r="J793" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L793" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M793" t="inlineStr">
@@ -37259,12 +37259,12 @@
       </c>
       <c r="J794" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L794" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M794" t="inlineStr">
@@ -37311,12 +37311,12 @@
       </c>
       <c r="J795" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L795" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M795" t="inlineStr">
@@ -37363,12 +37363,12 @@
       </c>
       <c r="J796" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L796" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto em diferentes cores.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto em diferentes cores. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M796" t="inlineStr">
@@ -37415,12 +37415,12 @@
       </c>
       <c r="J797" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L797" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens 360°.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens 360°. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M797" t="inlineStr">
@@ -37467,12 +37467,12 @@
       </c>
       <c r="J798" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L798" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M798" t="inlineStr">
@@ -37519,12 +37519,12 @@
       </c>
       <c r="J799" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L799" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M799" t="inlineStr">
@@ -37571,12 +37571,12 @@
       </c>
       <c r="J800" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L800" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, 2 imagens no mínimo — pode conter vídeo.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, 2 imagens no mínimo — pode conter vídeo. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M800" t="inlineStr">
@@ -37623,12 +37623,12 @@
       </c>
       <c r="J801" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L801" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M801" t="inlineStr">
@@ -37675,12 +37675,12 @@
       </c>
       <c r="J802" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L802" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, 2 imagens no mínimo.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, 2 imagens no mínimo. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M802" t="inlineStr">
@@ -37727,12 +37727,12 @@
       </c>
       <c r="J803" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L803" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, 2 imagens no mínimo.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, 2 imagens no mínimo. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M803" t="inlineStr">
@@ -37779,12 +37779,12 @@
       </c>
       <c r="J804" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L804" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M804" t="inlineStr">
@@ -37831,12 +37831,12 @@
       </c>
       <c r="J805" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L805" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M805" t="inlineStr">
@@ -37883,12 +37883,12 @@
       </c>
       <c r="J806" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L806" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, data.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, data. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M806" t="inlineStr">
@@ -37935,12 +37935,12 @@
       </c>
       <c r="J807" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L807" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, perguntas e respostas (máx. 3 perguntas).</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, perguntas e respostas (máx. 3 perguntas). Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M807" t="inlineStr">
@@ -37987,12 +37987,12 @@
       </c>
       <c r="J808" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L808" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, pode conter vídeo.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, pode conter vídeo. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M808" t="inlineStr">
@@ -38039,12 +38039,12 @@
       </c>
       <c r="J809" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L809" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, playlist, música ou episódio do Spotify.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, playlist, música ou episódio do Spotify. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M809" t="inlineStr">
@@ -38091,12 +38091,12 @@
       </c>
       <c r="J810" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L810" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M810" t="inlineStr">
@@ -38143,12 +38143,12 @@
       </c>
       <c r="J811" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L811" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M811" t="inlineStr">
@@ -38195,12 +38195,12 @@
       </c>
       <c r="J812" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L812" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M812" t="inlineStr">
@@ -38247,12 +38247,12 @@
       </c>
       <c r="J813" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L813" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, formulário (por omissão: Google Forms).</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, formulário (por omissão: Google Forms). Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M813" t="inlineStr">
@@ -38299,12 +38299,12 @@
       </c>
       <c r="J814" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L814" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, áudios em formato MP3.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, áudios em formato MP3. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M814" t="inlineStr">
@@ -38351,12 +38351,12 @@
       </c>
       <c r="J815" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L815" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localizações.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localizações. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M815" t="inlineStr">
@@ -38403,12 +38403,12 @@
       </c>
       <c r="J816" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L816" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localizações.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localizações. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M816" t="inlineStr">
@@ -38455,12 +38455,12 @@
       </c>
       <c r="J817" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L817" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M817" t="inlineStr">
@@ -38507,12 +38507,12 @@
       </c>
       <c r="J818" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L818" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localização.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localização. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M818" t="inlineStr">
@@ -38559,12 +38559,12 @@
       </c>
       <c r="J819" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L819" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M819" t="inlineStr">
@@ -38611,12 +38611,12 @@
       </c>
       <c r="J820" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L820" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localizações.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localizações. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M820" t="inlineStr">
@@ -38663,12 +38663,12 @@
       </c>
       <c r="J821" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L821" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localizações.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localizações. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M821" t="inlineStr">
@@ -38715,12 +38715,12 @@
       </c>
       <c r="J822" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L822" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, data.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, data. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M822" t="inlineStr">
@@ -38767,12 +38767,12 @@
       </c>
       <c r="J823" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L823" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, nº de telefone.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, nº de telefone. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M823" t="inlineStr">
@@ -38819,12 +38819,12 @@
       </c>
       <c r="J824" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L824" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, nº de telefone.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, nº de telefone. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M824" t="inlineStr">
@@ -38871,12 +38871,12 @@
       </c>
       <c r="J825" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L825" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M825" t="inlineStr">
@@ -38923,12 +38923,12 @@
       </c>
       <c r="J826" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L826" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, formulário (por omissão: Google Forms).</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, formulário (por omissão: Google Forms). Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M826" t="inlineStr">
@@ -38975,12 +38975,12 @@
       </c>
       <c r="J827" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L827" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M827" t="inlineStr">
@@ -39027,12 +39027,12 @@
       </c>
       <c r="J828" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L828" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas dos diferentes produtos da campanha, logótipo, copy, data de início/fim, detalhes da promoção e produtos associados.</t>
+          <t>Material necessário: ficheiro PSD em camadas dos diferentes produtos da campanha, logótipo, copy, data de início/fim, detalhes da promoção e produtos associados. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M828" t="inlineStr">
@@ -39079,12 +39079,12 @@
       </c>
       <c r="J829" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L829" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas dos diferentes produtos da campanha, logótipo, copy, data de início/fim, detalhes da promoção, produtos associados e localização.</t>
+          <t>Material necessário: ficheiro PSD em camadas dos diferentes produtos da campanha, logótipo, copy, data de início/fim, detalhes da promoção, produtos associados e localização. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M829" t="inlineStr">
@@ -39131,12 +39131,12 @@
       </c>
       <c r="J830" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L830" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas dos diferentes produtos da campanha, logótipo, copy, data de início/fim, detalhes da promoção, produtos associados e localização.</t>
+          <t>Material necessário: ficheiro PSD em camadas dos diferentes produtos da campanha, logótipo, copy, data de início/fim, detalhes da promoção, produtos associados e localização. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M830" t="inlineStr">
@@ -39183,12 +39183,12 @@
       </c>
       <c r="J831" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L831" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas dos diferentes produtos da campanha, logótipo, copy, data de início/fim e localização.</t>
+          <t>Material necessário: ficheiro PSD em camadas dos diferentes produtos da campanha, logótipo, copy, data de início/fim e localização. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M831" t="inlineStr">
@@ -39235,12 +39235,12 @@
       </c>
       <c r="J832" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L832" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M832" t="inlineStr">
@@ -39282,12 +39282,12 @@
       </c>
       <c r="J833" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L833" t="inlineStr">
         <is>
-          <t>Peso máximo não indicado na página de specs (só nos outros formatos da galeria). Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Jogo com 3 ecrãs obrigatórios: ecrã de jogar (com URL), ecrã do jogo em si (sem URL), e ecrã de fim de jogo (com URL).</t>
+          <t>Peso máximo não indicado na página de specs (só nos outros formatos da galeria). Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Jogo com 3 ecrãs obrigatórios: ecrã de jogar (com URL), ecrã do jogo em si (sem URL), e ecrã de fim de jogo (com URL). Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M833" t="inlineStr">
@@ -39334,12 +39334,12 @@
       </c>
       <c r="J834" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L834" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M834" t="inlineStr">
@@ -39386,12 +39386,12 @@
       </c>
       <c r="J835" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L835" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M835" t="inlineStr">
@@ -39438,12 +39438,12 @@
       </c>
       <c r="J836" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L836" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M836" t="inlineStr">
@@ -39490,12 +39490,12 @@
       </c>
       <c r="J837" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L837" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M837" t="inlineStr">
@@ -39542,12 +39542,12 @@
       </c>
       <c r="J838" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L838" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M838" t="inlineStr">
@@ -39594,12 +39594,12 @@
       </c>
       <c r="J839" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L839" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="M839" t="inlineStr">
@@ -39641,7 +39641,7 @@
       </c>
       <c r="J840" t="inlineStr">
         <is>
-          <t>JPEG, PNG (estático).</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="K840" t="inlineStr">
@@ -39651,7 +39651,7 @@
       </c>
       <c r="L840" t="inlineStr">
         <is>
-          <t>Sem redirecionamento (redirect) disponível. Material necessário: ficheiro PSD em camadas, logótipo, texto e copy.</t>
+          <t>Sem redirecionamento (redirect) disponível. Material necessário: ficheiro PSD em camadas, logótipo, texto e copy. Formato final do anúncio: JPEG, PNG (estático).</t>
         </is>
       </c>
       <c r="M840" t="inlineStr">
@@ -39698,12 +39698,12 @@
       </c>
       <c r="J841" t="inlineStr">
         <is>
-          <t>JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L841" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
         </is>
       </c>
       <c r="M841" t="inlineStr">
@@ -39750,12 +39750,12 @@
       </c>
       <c r="J842" t="inlineStr">
         <is>
-          <t>JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L842" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
         </is>
       </c>
       <c r="M842" t="inlineStr">
@@ -39802,12 +39802,12 @@
       </c>
       <c r="J843" t="inlineStr">
         <is>
-          <t>JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L843" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
         </is>
       </c>
       <c r="M843" t="inlineStr">
@@ -39854,12 +39854,12 @@
       </c>
       <c r="J844" t="inlineStr">
         <is>
-          <t>JPEG, PNG.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L844" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de exibição (dwell time): máx. 30 seg.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG.</t>
         </is>
       </c>
       <c r="M844" t="inlineStr">
@@ -39906,12 +39906,12 @@
       </c>
       <c r="J845" t="inlineStr">
         <is>
-          <t>JPEG, PNG.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L845" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de exibição (dwell time): máx. 30 seg.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG.</t>
         </is>
       </c>
       <c r="M845" t="inlineStr">
@@ -39958,12 +39958,12 @@
       </c>
       <c r="J846" t="inlineStr">
         <is>
-          <t>JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L846" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
         </is>
       </c>
       <c r="M846" t="inlineStr">
@@ -40010,12 +40010,12 @@
       </c>
       <c r="J847" t="inlineStr">
         <is>
-          <t>JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L847" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
         </is>
       </c>
       <c r="M847" t="inlineStr">
@@ -40062,12 +40062,12 @@
       </c>
       <c r="J848" t="inlineStr">
         <is>
-          <t>JPEG, PNG.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L848" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de exibição (dwell time): máx. 30 seg.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG.</t>
         </is>
       </c>
       <c r="M848" t="inlineStr">
@@ -40114,12 +40114,12 @@
       </c>
       <c r="J849" t="inlineStr">
         <is>
-          <t>JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L849" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
         </is>
       </c>
       <c r="M849" t="inlineStr">
@@ -40166,12 +40166,12 @@
       </c>
       <c r="J850" t="inlineStr">
         <is>
-          <t>JPEG, PNG.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L850" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de exibição (dwell time): máx. 30 seg.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG.</t>
         </is>
       </c>
       <c r="M850" t="inlineStr">
@@ -40218,12 +40218,12 @@
       </c>
       <c r="J851" t="inlineStr">
         <is>
-          <t>JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L851" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo, lista de músicas. Tempo de exibição (dwell time): máx. 30 seg.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo, lista de músicas. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
         </is>
       </c>
       <c r="M851" t="inlineStr">
@@ -40270,12 +40270,12 @@
       </c>
       <c r="J852" t="inlineStr">
         <is>
-          <t>JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L852" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
         </is>
       </c>
       <c r="M852" t="inlineStr">
@@ -40322,12 +40322,12 @@
       </c>
       <c r="J853" t="inlineStr">
         <is>
-          <t>JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L853" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
         </is>
       </c>
       <c r="M853" t="inlineStr">
@@ -40374,12 +40374,12 @@
       </c>
       <c r="J854" t="inlineStr">
         <is>
-          <t>JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L854" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
         </is>
       </c>
       <c r="M854" t="inlineStr">
@@ -40426,12 +40426,12 @@
       </c>
       <c r="J855" t="inlineStr">
         <is>
-          <t>JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L855" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
         </is>
       </c>
       <c r="M855" t="inlineStr">
@@ -40478,12 +40478,12 @@
       </c>
       <c r="J856" t="inlineStr">
         <is>
-          <t>JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L856" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
         </is>
       </c>
       <c r="M856" t="inlineStr">
@@ -40530,12 +40530,12 @@
       </c>
       <c r="J857" t="inlineStr">
         <is>
-          <t>JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L857" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
         </is>
       </c>
       <c r="M857" t="inlineStr">
@@ -40582,12 +40582,12 @@
       </c>
       <c r="J858" t="inlineStr">
         <is>
-          <t>JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L858" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
         </is>
       </c>
       <c r="M858" t="inlineStr">
@@ -40634,12 +40634,12 @@
       </c>
       <c r="J859" t="inlineStr">
         <is>
-          <t>JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L859" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
         </is>
       </c>
       <c r="M859" t="inlineStr">
@@ -40686,12 +40686,12 @@
       </c>
       <c r="J860" t="inlineStr">
         <is>
-          <t>JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L860" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo (se aplicável). Tempo de exibição (dwell time): máx. 30 seg. Formato de wallpaper de alto impacto, com ação especial totalmente à medida da marca — disponibilidade a confirmar com a equipa comercial da Azerion.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo (se aplicável). Tempo de exibição (dwell time): máx. 30 seg. Formato de wallpaper de alto impacto, com ação especial totalmente à medida da marca — disponibilidade a confirmar com a equipa comercial da Azerion. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
         </is>
       </c>
       <c r="M860" t="inlineStr">
@@ -40817,12 +40817,12 @@
       </c>
       <c r="J863" t="inlineStr">
         <is>
-          <t>JPEG, TIFF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L863" t="inlineStr">
         <is>
-          <t>Wallpaper de WeTransfer com elementos gráficos estáticos e/ou copy, desenhado para captar a atenção do utilizador, reforçar a mensagem de marca e motivar ações que impulsionem a conversão. Disponível em diferentes opções consoante objetivos e orçamento. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view</t>
+          <t>Wallpaper de WeTransfer com elementos gráficos estáticos e/ou copy, desenhado para captar a atenção do utilizador, reforçar a mensagem de marca e motivar ações que impulsionem a conversão. Disponível em diferentes opções consoante objetivos e orçamento. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view Formato final do anúncio: JPEG, TIFF.</t>
         </is>
       </c>
       <c r="M863" t="inlineStr">
@@ -40864,12 +40864,12 @@
       </c>
       <c r="J864" t="inlineStr">
         <is>
-          <t>JPEG, TIFF; vídeo MP4, MOV (H.264 ou ProRes).</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L864" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view Formato final do anúncio: JPEG, TIFF; vídeo MP4, MOV (H.264 ou ProRes).</t>
         </is>
       </c>
       <c r="M864" t="inlineStr">
@@ -40911,12 +40911,12 @@
       </c>
       <c r="J865" t="inlineStr">
         <is>
-          <t>JPEG, TIFF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L865" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view Formato final do anúncio: JPEG, TIFF.</t>
         </is>
       </c>
       <c r="M865" t="inlineStr">
@@ -40958,12 +40958,12 @@
       </c>
       <c r="J866" t="inlineStr">
         <is>
-          <t>JPEG, TIFF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L866" t="inlineStr">
         <is>
-          <t>Wallpaper de WeTransfer com vídeo de uma só cena (1 a 4 segundos) com movimento em loop contínuo. Permite incluir um botão de play que ativa o vídeo completo em ecrã inteiro, captando a atenção do utilizador e potenciando o engagement com a marca. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view</t>
+          <t>Wallpaper de WeTransfer com vídeo de uma só cena (1 a 4 segundos) com movimento em loop contínuo. Permite incluir um botão de play que ativa o vídeo completo em ecrã inteiro, captando a atenção do utilizador e potenciando o engagement com a marca. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view Formato final do anúncio: JPEG, TIFF.</t>
         </is>
       </c>
       <c r="M866" t="inlineStr">
@@ -41005,12 +41005,12 @@
       </c>
       <c r="J867" t="inlineStr">
         <is>
-          <t>JPEG, TIFF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L867" t="inlineStr">
         <is>
-          <t>Wallpaper de WeTransfer interativo que, através de um slider, revela uma imagem. O logótipo e o CTA mantêm-se fixos por cima das imagens, assegurando a visibilidade da marca e potenciando a interação do utilizador. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view</t>
+          <t>Wallpaper de WeTransfer interativo que, através de um slider, revela uma imagem. O logótipo e o CTA mantêm-se fixos por cima das imagens, assegurando a visibilidade da marca e potenciando a interação do utilizador. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view Formato final do anúncio: JPEG, TIFF.</t>
         </is>
       </c>
       <c r="M867" t="inlineStr">
@@ -41052,12 +41052,12 @@
       </c>
       <c r="J868" t="inlineStr">
         <is>
-          <t>JPEG, TIFF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L868" t="inlineStr">
         <is>
-          <t>Wallpaper de WeTransfer em que o cursor se transforma num elemento gráfico ou num call to action sobre um fundo estático. Pode ainda incluir um botão de play que, ao clicar, reproduz um vídeo em modo CTP, captando a atenção do utilizador e potenciando a interação com a marca. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view</t>
+          <t>Wallpaper de WeTransfer em que o cursor se transforma num elemento gráfico ou num call to action sobre um fundo estático. Pode ainda incluir um botão de play que, ao clicar, reproduz um vídeo em modo CTP, captando a atenção do utilizador e potenciando a interação com a marca. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view Formato final do anúncio: JPEG, TIFF.</t>
         </is>
       </c>
       <c r="M868" t="inlineStr">
@@ -41099,12 +41099,12 @@
       </c>
       <c r="J869" t="inlineStr">
         <is>
-          <t>JPEG, TIFF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L869" t="inlineStr">
         <is>
-          <t>Wallpaper de WeTransfer animado, com imagens em forma de acordeão. O utilizador pode interagir com elas para as visualizar todas, aumentando a participação e o engagement com a marca. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view</t>
+          <t>Wallpaper de WeTransfer animado, com imagens em forma de acordeão. O utilizador pode interagir com elas para as visualizar todas, aumentando a participação e o engagement com a marca. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view Formato final do anúncio: JPEG, TIFF.</t>
         </is>
       </c>
       <c r="M869" t="inlineStr">
@@ -41146,12 +41146,12 @@
       </c>
       <c r="J870" t="inlineStr">
         <is>
-          <t>JPEG, TIFF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L870" t="inlineStr">
         <is>
-          <t>Wallpaper de WeTransfer interativo, com um jogo de raspadinha com duas imagens a ecrã inteiro. Permite ao utilizador descobrir conteúdo ou prémios, captando atenção e potenciando a interação com a marca. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view</t>
+          <t>Wallpaper de WeTransfer interativo, com um jogo de raspadinha com duas imagens a ecrã inteiro. Permite ao utilizador descobrir conteúdo ou prémios, captando atenção e potenciando a interação com a marca. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view Formato final do anúncio: JPEG, TIFF.</t>
         </is>
       </c>
       <c r="M870" t="inlineStr">
@@ -41193,12 +41193,12 @@
       </c>
       <c r="J871" t="inlineStr">
         <is>
-          <t>JPEG, TIFF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L871" t="inlineStr">
         <is>
-          <t>Wallpaper de WeTransfer com vídeo ou animação exclusiva que reflete a identidade da marca. Gera alto impacto visual e reforça o reconhecimento de marca, aumentando o engagement do utilizador. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view</t>
+          <t>Wallpaper de WeTransfer com vídeo ou animação exclusiva que reflete a identidade da marca. Gera alto impacto visual e reforça o reconhecimento de marca, aumentando o engagement do utilizador. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view Formato final do anúncio: JPEG, TIFF.</t>
         </is>
       </c>
       <c r="M871" t="inlineStr">
@@ -41240,12 +41240,12 @@
       </c>
       <c r="J872" t="inlineStr">
         <is>
-          <t>JPEG, TIFF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L872" t="inlineStr">
         <is>
-          <t>Wallpaper de WeTransfer em que o rato se transforma numa luz que ilumina a imagem de fundo. Fomenta a interação ativa do utilizador e destaca produtos ou mensagens-chave de forma apelativa. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view</t>
+          <t>Wallpaper de WeTransfer em que o rato se transforma numa luz que ilumina a imagem de fundo. Fomenta a interação ativa do utilizador e destaca produtos ou mensagens-chave de forma apelativa. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view Formato final do anúncio: JPEG, TIFF.</t>
         </is>
       </c>
       <c r="M872" t="inlineStr">
@@ -41287,12 +41287,12 @@
       </c>
       <c r="J873" t="inlineStr">
         <is>
-          <t>JPEG, TIFF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L873" t="inlineStr">
         <is>
-          <t>Wallpaper de WeTransfer que permite explorar várias imagens deslizando-as horizontalmente. Aumenta a participação do utilizador e oferece múltiplas oportunidades de conversão dentro do mesmo anúncio. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view</t>
+          <t>Wallpaper de WeTransfer que permite explorar várias imagens deslizando-as horizontalmente. Aumenta a participação do utilizador e oferece múltiplas oportunidades de conversão dentro do mesmo anúncio. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view Formato final do anúncio: JPEG, TIFF.</t>
         </is>
       </c>
       <c r="M873" t="inlineStr">
@@ -41334,12 +41334,12 @@
       </c>
       <c r="J874" t="inlineStr">
         <is>
-          <t>JPEG, TIFF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L874" t="inlineStr">
         <is>
-          <t>Wallpaper de WeTransfer com temporizador que mostra o tempo restante para um evento ou oferta. Gera urgência e motiva o utilizador a interagir ou realizar uma ação imediata. Material necessário: ficheiro PSD em camadas, logótipo, tipografia, copy e data. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view</t>
+          <t>Wallpaper de WeTransfer com temporizador que mostra o tempo restante para um evento ou oferta. Gera urgência e motiva o utilizador a interagir ou realizar uma ação imediata. Material necessário: ficheiro PSD em camadas, logótipo, tipografia, copy e data. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view Formato final do anúncio: JPEG, TIFF.</t>
         </is>
       </c>
       <c r="M874" t="inlineStr">
@@ -41381,12 +41381,12 @@
       </c>
       <c r="J875" t="inlineStr">
         <is>
-          <t>JPEG, TIFF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L875" t="inlineStr">
         <is>
-          <t>Wallpaper de WeTransfer com imagem interativa que inclui pontos clicáveis (hotspots) para revelar informação, produtos ou links. Melhora a exploração do conteúdo e aumenta a interação direta com a marca. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view</t>
+          <t>Wallpaper de WeTransfer com imagem interativa que inclui pontos clicáveis (hotspots) para revelar informação, produtos ou links. Melhora a exploração do conteúdo e aumenta a interação direta com a marca. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view Formato final do anúncio: JPEG, TIFF.</t>
         </is>
       </c>
       <c r="M875" t="inlineStr">
@@ -41428,12 +41428,12 @@
       </c>
       <c r="J876" t="inlineStr">
         <is>
-          <t>JPEG, TIFF; vídeo MP4, MOV (H.264 ou ProRes).</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L876" t="inlineStr">
         <is>
-          <t>24h de WeTransfer em exclusividade para a marca — campanha de um dia de duração, com inventário destinado a publicidade exclusiva para o anunciante, por país. Composto por 3 wallpapers; a campanha tem de conter uma destas opções: 2 criatividades Static + 1 criatividade Click to Play, ou 3 criatividades Static. As imagens iniciais de cada formato têm de ser bem diferentes entre si — se forem parecidas, a WeTransfer pode pedir uma criatividade adicional para otimizar melhor a campanha. Material necessário: ficheiro PSD em camadas, logótipo, vídeo (se houver) e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view</t>
+          <t>24h de WeTransfer em exclusividade para a marca — campanha de um dia de duração, com inventário destinado a publicidade exclusiva para o anunciante, por país. Composto por 3 wallpapers; a campanha tem de conter uma destas opções: 2 criatividades Static + 1 criatividade Click to Play, ou 3 criatividades Static. As imagens iniciais de cada formato têm de ser bem diferentes entre si — se forem parecidas, a WeTransfer pode pedir uma criatividade adicional para otimizar melhor a campanha. Material necessário: ficheiro PSD em camadas, logótipo, vídeo (se houver) e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view Formato final do anúncio: JPEG, TIFF; vídeo MP4, MOV (H.264 ou ProRes).</t>
         </is>
       </c>
       <c r="M876" t="inlineStr">
@@ -41475,12 +41475,12 @@
       </c>
       <c r="J877" t="inlineStr">
         <is>
-          <t>JPEG, TIFF; vídeo MP4, MOV (H.264 ou ProRes).</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="L877" t="inlineStr">
         <is>
-          <t>Formato publicitário wallpaper da WeTransfer com ação personalizada e exclusiva, onde a marca pode dar largas à imaginação — disponibilidade a confirmar com a equipa comercial. Material necessário: ficheiro PSD em camadas, logótipo, vídeo (se houver) e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view</t>
+          <t>Formato publicitário wallpaper da WeTransfer com ação personalizada e exclusiva, onde a marca pode dar largas à imaginação — disponibilidade a confirmar com a equipa comercial. Material necessário: ficheiro PSD em camadas, logótipo, vídeo (se houver) e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view Formato final do anúncio: JPEG, TIFF; vídeo MP4, MOV (H.264 ou ProRes).</t>
         </is>
       </c>
       <c r="M877" t="inlineStr">

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -32717,7 +32717,7 @@
       </c>
       <c r="L703" t="inlineStr">
         <is>
-          <t>Não colocar elementos importantes nas danger zones (laterais) — usar essa área só para elementos gráficos decorativos. CTA: máx. 2-3 palavras com verbo de ação (ex.: "Compre agora", "Descubra"). Template Photoshop disponível (Mobile + IAB, com safe areas). Para redimensionamento pela equipa de design da Ogury, enviar: ficheiro PSD por camadas em alta resolução, logos em vetorial (PSD/AI/EPS/SVG), copy da campanha, fontes e brand guidelines. Prazos: criação inicial mín. 2 dias úteis; revisões mín. 1-2 dias úteis; máx. 2 revisões por criatividade. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto de pixel/click/viewability por conjunto de criatividades multi-formato).</t>
+          <t>Não colocar elementos importantes nas danger zones (laterais) — usar essa área só para elementos gráficos decorativos. CTA: máx. 2-3 palavras com verbo de ação (ex.: "Compre agora", "Descubra").</t>
         </is>
       </c>
       <c r="M703" t="inlineStr">
@@ -32769,7 +32769,7 @@
       </c>
       <c r="L704" t="inlineStr">
         <is>
-          <t>Só elementos necessários (logo, headline, CTA); texto legível e conciso. Não colocar elementos importantes nas danger zones. CTA: máx. 2-3 palavras com verbo de ação. Template Photoshop disponível (Mobile + IAB, com safe areas). Para redimensionamento pela equipa de design da Ogury, enviar: ficheiro PSD por camadas em alta resolução, logos em vetorial (PSD/AI/EPS/SVG), copy da campanha, fontes e brand guidelines. Prazos: criação inicial mín. 2 dias úteis; revisões mín. 1-2 dias úteis; máx. 2 revisões por criatividade. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto de pixel/click/viewability por conjunto de criatividades multi-formato).</t>
+          <t>Só elementos necessários (logo, headline, CTA); texto legível e conciso. Não colocar elementos importantes nas danger zones. CTA: máx. 2-3 palavras com verbo de ação.</t>
         </is>
       </c>
       <c r="M704" t="inlineStr">
@@ -32821,7 +32821,7 @@
       </c>
       <c r="L705" t="inlineStr">
         <is>
-          <t>Não colocar elementos importantes nas danger zones. CTA: máx. 2-3 palavras com verbo de ação. Template Photoshop disponível (Mobile + IAB, com safe areas). Para redimensionamento pela equipa de design da Ogury, enviar: ficheiro PSD por camadas em alta resolução, logos em vetorial (PSD/AI/EPS/SVG), copy da campanha, fontes e brand guidelines. Prazos: criação inicial mín. 2 dias úteis; revisões mín. 1-2 dias úteis; máx. 2 revisões por criatividade. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto de pixel/click/viewability por conjunto de criatividades multi-formato).</t>
+          <t>Não colocar elementos importantes nas danger zones. CTA: máx. 2-3 palavras com verbo de ação.</t>
         </is>
       </c>
       <c r="M705" t="inlineStr">
@@ -32873,7 +32873,7 @@
       </c>
       <c r="L706" t="inlineStr">
         <is>
-          <t>Não colocar elementos importantes nas danger zones. CTA: máx. 2-3 palavras com verbo de ação. Template Photoshop disponível (Mobile + IAB, com safe areas). Para redimensionamento pela equipa de design da Ogury, enviar: ficheiro PSD por camadas em alta resolução, logos em vetorial (PSD/AI/EPS/SVG), copy da campanha, fontes e brand guidelines. Prazos: criação inicial mín. 2 dias úteis; revisões mín. 1-2 dias úteis; máx. 2 revisões por criatividade. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto de pixel/click/viewability por conjunto de criatividades multi-formato).</t>
+          <t>Não colocar elementos importantes nas danger zones. CTA: máx. 2-3 palavras com verbo de ação.</t>
         </is>
       </c>
       <c r="M706" t="inlineStr">
@@ -32925,7 +32925,7 @@
       </c>
       <c r="L707" t="inlineStr">
         <is>
-          <t>Unidade criativa dinâmica in-article, pensada para visibilidade máxima durante o scroll em conteúdo mobile web. Não colocar elementos importantes nas danger zones. CTA: máx. 2-3 palavras com verbo de ação. Template Photoshop disponível (Mobile + IAB, com safe areas). Para redimensionamento pela equipa de design da Ogury, enviar: ficheiro PSD por camadas em alta resolução, logos em vetorial (PSD/AI/EPS/SVG), copy da campanha, fontes e brand guidelines. Prazos: criação inicial mín. 2 dias úteis; revisões mín. 1-2 dias úteis; máx. 2 revisões por criatividade. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto de pixel/click/viewability por conjunto de criatividades multi-formato).</t>
+          <t>Unidade criativa dinâmica in-article, pensada para visibilidade máxima durante o scroll em conteúdo mobile web. Não colocar elementos importantes nas danger zones. CTA: máx. 2-3 palavras com verbo de ação.</t>
         </is>
       </c>
       <c r="M707" t="inlineStr">
@@ -32977,7 +32977,7 @@
       </c>
       <c r="L708" t="inlineStr">
         <is>
-          <t>Unidade in-article, pensada para consideração e tráfego qualificado. Incluído só nalguns pacotes — confirmar na recomendação de media. CTA: máx. 2-3 palavras com verbo de ação. Template Photoshop disponível (Mobile + IAB, com safe areas). Para redimensionamento pela equipa de design da Ogury, enviar: ficheiro PSD por camadas em alta resolução, logos em vetorial (PSD/AI/EPS/SVG), copy da campanha, fontes e brand guidelines. Prazos: criação inicial mín. 2 dias úteis; revisões mín. 1-2 dias úteis; máx. 2 revisões por criatividade. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto de pixel/click/viewability por conjunto de criatividades multi-formato).</t>
+          <t>Unidade in-article, pensada para consideração e tráfego qualificado. Incluído só nalguns pacotes — confirmar na recomendação de media. CTA: máx. 2-3 palavras com verbo de ação.</t>
         </is>
       </c>
       <c r="M708" t="inlineStr">
@@ -33024,7 +33024,7 @@
       </c>
       <c r="I709" t="inlineStr">
         <is>
-          <t>Máx.: 40 MB (MP4) ou 3 MB (VAST/VPAID).</t>
+          <t>Máx.: 40 MB (MP4) ou 3 MB (VAST/VPAID). Duração máxima: 30 seg (recomendado 15 seg).</t>
         </is>
       </c>
       <c r="J709" t="inlineStr">
@@ -33034,7 +33034,7 @@
       </c>
       <c r="L709" t="inlineStr">
         <is>
-          <t>Formato: MP4, VAST tag ou VPAID (legacy apenas; VAST preferencial). Recomendado: compliance VAST 4.1 + OM SDK. Safe area: margem de segurança de 10% em cima/baixo (para overlays de UI). Som: deve ser compreensível sem áudio (autoplay mudo). Branding: logo/mensagem clara nos primeiros 5 segundos. Duração máxima: até 30s (recomendado 15s para melhor experiência mobile). Pixels de medição e trackers de terceiros (ex.: IAS, DoubleVerify) devem vir embrulhados em VAST tags. Personalização: nome da marca/produto e texto de CTA (máx. 30 carateres; "Visit website" por defeito). Funcionalidades opcionais, de valor acrescentado — confirmar disponibilidade com a equipa Ogury: Top &amp; Bottom Skins (imagens estáticas JPG/PNG, 768x450px cada, sobrepostas ao vídeo, sem tracking próprio); Bottom Skin isolado (JPG/PNG, 768x930px, sem tracking próprio); End Card (imagem estática a seguir ao vídeo, JPG/PNG, 16:9 ou 9:16, recomendado 1024x576 ou 576x1024px, máx. 250 KB). Templates Photoshop disponíveis para as skins/end card (com safe areas). Prazos de design: criação inicial mín. 2 dias úteis; revisões mín. 1-2 dias úteis; máx. 2 revisões por criativo.</t>
+          <t>Safe area: margem de 10% em cima/baixo (para overlays de UI). Som opcional — tem de ser compreensível sem áudio (autoplay mudo). Branding/mensagem clara nos primeiros 5 segundos. Tracking de terceiros (ex.: IAS, DoubleVerify) só embrulhado em VAST tags. CTA personalizável: máx. 30 carateres ("Visit website" por defeito). Opcional: skins e end card disponíveis — confirmar specs com a equipa Ogury.</t>
         </is>
       </c>
       <c r="M709" t="inlineStr">
@@ -33081,7 +33081,7 @@
       </c>
       <c r="I710" t="inlineStr">
         <is>
-          <t>Máx.: 40 MB (MP4) ou 3 MB (VAST/VPAID).</t>
+          <t>Máx.: 40 MB (MP4) ou 3 MB (VAST/VPAID). Duração máxima: 30 seg (recomendado 15 seg).</t>
         </is>
       </c>
       <c r="J710" t="inlineStr">
@@ -33091,7 +33091,7 @@
       </c>
       <c r="L710" t="inlineStr">
         <is>
-          <t>Formato: MP4, VAST tag ou VPAID (legacy apenas; VAST preferencial). Recomendado: compliance VAST 4.1 + OM SDK. Safe area: margem de segurança de 10% em cima/baixo (para overlays de UI). Som: deve ser compreensível sem áudio (autoplay mudo). Branding: logo/mensagem clara nos primeiros 5 segundos. Duração máxima: até 30s (recomendado 15s para melhor experiência mobile). Pixels de medição e trackers de terceiros (ex.: IAS, DoubleVerify) devem vir embrulhados em VAST tags. Personalização: heading ("Choose your ad" por defeito), nomes de produto/feature, cor de fundo (branco por defeito) — formato interativo tipo "video chooser". Funcionalidades opcionais, de valor acrescentado — confirmar disponibilidade com a equipa Ogury: End Card (imagem estática a seguir ao vídeo, JPG/PNG, 16:9 ou 9:16, recomendado 1024x576 ou 576x1024px, máx. 250 KB, com opção de end card multi-CTA, sem tracking próprio); Video Chooser Image (specs não detalhadas nos materiais enviados — confirmar com a equipa Ogury). Template Photoshop disponível para o End Card (com safe areas). Prazos de design: criação inicial mín. 2 dias úteis; revisões mín. 1-2 dias úteis; máx. 2 revisões por criativo.</t>
+          <t>Safe area: margem de 10% em cima/baixo (para overlays de UI). Som opcional — tem de ser compreensível sem áudio (autoplay mudo). Branding/mensagem clara nos primeiros 5 segundos. Tracking de terceiros (ex.: IAS, DoubleVerify) só embrulhado em VAST tags. Formato "video chooser": heading, nomes de produto/feature e cor de fundo personalizáveis. Opcional: end card disponível — confirmar specs com a equipa Ogury.</t>
         </is>
       </c>
       <c r="M710" t="inlineStr">
@@ -33143,7 +33143,7 @@
       </c>
       <c r="L711" t="inlineStr">
         <is>
-          <t>Carrossel rich media interativo para mostrar vários produtos, features ou mensagens de marca numa experiência deslizável (swipe). Disponível para campanhas CPE e CPM. Casos de uso: product showcase (vários produtos/variações); storytelling sequencial (mensagem revelada passo a passo); 3D Brand Spotlight (transição em cubo 3D); multi-CTA (vários CTAs rastreados individualmente, na mesma slide ou em slides diferentes, cada um com destino próprio); vídeo (no root da criatividade, visível durante o swipe, ou integrado numa slide específica). Boas práticas: limitar a ~5-6 slides; manter o CTA visível; mensagem concisa por slide; consistência visual entre slides. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+          <t>Carrossel rich media interativo para mostrar vários produtos, features ou mensagens de marca numa experiência deslizável (swipe). Disponível para campanhas CPE e CPM.</t>
         </is>
       </c>
       <c r="M711" t="inlineStr">
@@ -33195,7 +33195,7 @@
       </c>
       <c r="L712" t="inlineStr">
         <is>
-          <t>Carrossel rich media interativo com navegação em camadas: o utilizador interage com elementos no ecrã de entrada para aceder a vistas de detalhe dedicadas. Para campanhas CPE e CPM. Casos de uso: product showcase (vários produtos, cada um com vista de detalhe); variações e opções (cores, estilos, configurações); product deep dive (um produto, várias camadas de informação); com vídeo (no ecrã de entrada ou dentro de uma vista de detalhe); com carrossel (carrossel dentro da vista de detalhe, para ângulos/features/variações adicionais). Boas práticas: limitar o nº de elementos interativos no ecrã de entrada; elementos clicáveis claramente identificáveis; botão de voltar sempre visível quando necessário; mensagem concisa por ecrã. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+          <t>Carrossel rich media interativo com navegação em camadas: o utilizador interage com elementos no ecrã de entrada para aceder a vistas de detalhe dedicadas. Para campanhas CPE e CPM.</t>
         </is>
       </c>
       <c r="M712" t="inlineStr">
@@ -33247,7 +33247,7 @@
       </c>
       <c r="L713" t="inlineStr">
         <is>
-          <t>Formato interativo que permite ao utilizador explorar produtos, variantes, features ou configurações diferentes dentro de uma única criatividade: ao tocar numa opção seletora, o visual principal e o conteúdo associado atualizam-se instantaneamente. Para campanhas CPE e CPM. Casos de uso: seleção de produto (navegar vários produtos, cada seleção atualiza o visual/conteúdo); personalização de variante (cores, estilos, sabores, acabamentos — ideal para automóvel, moda, beleza, alimentação, mobiliário, eletrónica de consumo). Boas práticas: limitar o nº de opções selecionáveis; destacar claramente a opção selecionada; cada seleção deve gerar uma mudança visual percetível; CTA sempre visível; consistência visual entre variantes; seletores suficientemente grandes para toque em mobile. Assets visuais adicionais: uma imagem por opção selecionável; thumbnails de produto, ícones, amostras de cor ou seletores. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+          <t>Formato interativo que permite ao utilizador explorar produtos, variantes, features ou configurações diferentes dentro de uma única criatividade: ao tocar numa opção seletora, o visual principal e o conteúdo associado atualizam-se instantaneamente. Para campanhas CPE e CPM.</t>
         </is>
       </c>
       <c r="M713" t="inlineStr">
@@ -33299,7 +33299,7 @@
       </c>
       <c r="L714" t="inlineStr">
         <is>
-          <t>Formato interativo em que o utilizador arrasta um ou mais elementos para áreas-alvo predefinidas para completar uma ação; ao concluir, revela conteúdo/novo ecrã. Para campanhas CPE e CPM. Casos de uso: product reveal (arrastar elemento(s) para revelar produto/oferta/mensagem); demonstração de uso do produto; receitas/ingredientes (arrastar ingredientes para uma tigela/prato/copo); desafio gamificado (ex.: marcar golo, colocar um item, fazer correspondências) antes de desbloquear o passo seguinte. Boas práticas: interação intuitiva, elementos arrastáveis e zonas de largada claramente identificáveis; pistas visuais/animações/copy instrucional; elementos fáceis de manipular em mobile; limitar o nº de ações necessárias; recompensar interações bem-sucedidas; progressão clara (nº de ações em falta). Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+          <t>Formato interativo em que o utilizador arrasta um ou mais elementos para áreas-alvo predefinidas para completar uma ação; ao concluir, revela conteúdo/novo ecrã. Para campanhas CPE e CPM.</t>
         </is>
       </c>
       <c r="M714" t="inlineStr">
@@ -33351,7 +33351,7 @@
       </c>
       <c r="L715" t="inlineStr">
         <is>
-          <t>Formato interativo com hotspots clicáveis sobre elementos-chave de um visual; ao tocar, revela conteúdo adicional (informação de produto, features, preço, imagem, vídeo ou CTA). Para campanhas CPE e CPM. Casos de uso: informação de produto (hotspots numa imagem, cada um revela info/preço/CTA); product deep dive (hotspots ligados a componentes/funcionalidades específicas). Boas práticas: limitar o nº de hotspots por ecrã; posicionar em áreas relevantes do visual; garantir visibilidade clara (contraste/espaçamento); conteúdo de cada hotspot conciso; evitar sobreposição de áreas; consistência visual entre o conteúdo dos hotspots; áreas de toque suficientemente grandes em mobile. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+          <t>Formato interativo com hotspots clicáveis sobre elementos-chave de um visual; ao tocar, revela conteúdo adicional (informação de produto, features, preço, imagem, vídeo ou CTA). Para campanhas CPE e CPM.</t>
         </is>
       </c>
       <c r="M715" t="inlineStr">
@@ -33403,7 +33403,7 @@
       </c>
       <c r="L716" t="inlineStr">
         <is>
-          <t>Formato interativo que permite comparar dois visuais arrastando um slider pelo ecrã — revela progressivamente uma imagem enquanto esconde a outra, criando uma experiência "antes e depois". Para campanhas CPE e CPM. Casos de uso: antes e depois (transformação visual: skincare, tratamentos de beleza, fitness, remodelações); personalização de produto (cores, estilos, sabores, acabamentos, variações); impacto de produto/serviço (ex.: produtos de limpeza, tintas, jardinagem, restauro); comparação de features (ex.: standard vs. premium, modelo antigo vs. novo); melhoria de performance (ex.: desporto, nutrição, saúde e bem-estar). Boas práticas: visuais altamente contrastados; imagens perfeitamente alinhadas; pista de interação clara (setas, labels, animação subtil); foco numa única mensagem-chave; branding e CTA sempre visíveis; otimizar para leitura em mobile. Assets visuais adicionais: uma imagem por opção selecionável; thumbnails, ícones, amostras de cor ou seletores. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+          <t>Formato interativo que permite comparar dois visuais arrastando um slider pelo ecrã — revela progressivamente uma imagem enquanto esconde a outra, criando uma experiência "antes e depois". Para campanhas CPE e CPM.</t>
         </is>
       </c>
       <c r="M716" t="inlineStr">
@@ -33450,7 +33450,7 @@
       </c>
       <c r="L717" t="inlineStr">
         <is>
-          <t>Formato interativo em que o utilizador reconstrói uma imagem para desbloquear conteúdo adicional; ao completar o puzzle, mostra um ecrã de revelação final. Para campanhas CPE e CPM. Casos de uso: revelação de produto (produto, embalagem ou visual hero); desbloqueio de oferta (promoção, desconto, conteúdo exclusivo); engagement gamificado; storytelling de marca; teaser de evento/lançamento. Boas práticas: usar uma imagem visualmente apelativa e facilmente reconhecível; desafio simples e intuitivo (resolúvel em poucos segundos); revelação final com valor; branding consistente em todos os ecrãs; CTA apelativo; otimizar para interação em mobile. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+          <t>Formato interativo em que o utilizador reconstrói uma imagem para desbloquear conteúdo adicional; ao completar o puzzle, mostra um ecrã de revelação final. Para campanhas CPE e CPM.</t>
         </is>
       </c>
       <c r="M717" t="inlineStr">
@@ -33502,7 +33502,7 @@
       </c>
       <c r="L718" t="inlineStr">
         <is>
-          <t>Formato interativo com uma interação simples de toque que desbloqueia conteúdo adicional: começa com um visual teaser e revela uma segunda camada de conteúdo (imagem, vídeo, slideshow, animação ou mensagem promocional). Para campanhas CPE e CPM. Casos de uso: slideshow reveal; video reveal; offer reveal (promoção/oferta exclusiva/mensagem-chave); transformação criativa (mudança de universo visual, ex. campanhas sazonais/lançamentos); antes e depois (estado transformado — beleza, fitness, automóvel, melhoria de casa). Boas práticas: tornar a interação óbvia; forte contraste entre teaser e conteúdo revelado; primeiro ecrã simples e focado; usar a revelação para a mensagem-chave; transições suaves; otimizar para mobile; consistência visual entre ecrãs. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+          <t>Formato interativo com uma interação simples de toque que desbloqueia conteúdo adicional: começa com um visual teaser e revela uma segunda camada de conteúdo (imagem, vídeo, slideshow, animação ou mensagem promocional). Para campanhas CPE e CPM.</t>
         </is>
       </c>
       <c r="M718" t="inlineStr">
@@ -33554,7 +33554,7 @@
       </c>
       <c r="L719" t="inlineStr">
         <is>
-          <t>Combina uma criatividade de marca com um localizador de lojas integrado: o utilizador interage com um visual promocional e depois toca num CTA para aceder a um mapa interativo dentro do próprio anúncio, mostrando lojas, pontos de venda, postos de carregamento, concessionários ou outras localizações físicas próximas. Casos de uso: localizador de loja; localizações de evento; rede de agências/balcões/serviço; rede de postos de carregamento EV. Boas práticas: CTA forte orientado a localização (ex.: "Find a Store"); introdução concisa antes de passar ao mapa; informação de localização completa. Mapa: é obrigatório um ficheiro .CSV de localizações preenchido, usando o template fornecido pela Ogury, sem alterar os nomes das colunas (caso contrário a integração do mapa falha). Campos obrigatórios: nome da localização, morada, cidade, código postal, estado/região (se aplicável), país, latitude, longitude, report label. Campos opcionais: telefone, email, URL, horário de funcionamento. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+          <t>Combina uma criatividade de marca com um localizador de lojas integrado: o utilizador interage com um visual promocional e depois toca num CTA para aceder a um mapa interativo dentro do próprio anúncio, mostrando lojas, pontos de venda, postos de carregamento, concessionários ou outras localizações físicas próximas. Mapa: é obrigatório um ficheiro .CSV de localizações preenchido, usando o template fornecido pela Ogury, sem alterar os nomes das colunas (caso contrário a integração do mapa falha). Campos obrigatórios: nome da localização, morada, cidade, código postal, estado/região (se aplicável), país, latitude, longitude, report label. Campos opcionais: telefone, email, URL, horário de funcionamento.</t>
         </is>
       </c>
       <c r="M719" t="inlineStr">
@@ -33606,7 +33606,7 @@
       </c>
       <c r="L720" t="inlineStr">
         <is>
-          <t>Experiência imersiva multi-página que permite navegação vertical por conteúdo de marca através de swipe (cima/baixo), replicando a navegação num site/landing page, com produtos, features, storytelling ou conteúdo promocional distribuídos por várias páginas dentro do mesmo anúncio. Casos de uso: product showcase (features/benefícios/configurações em páginas dedicadas); storytelling (jornada narrativa sequencial); promoção de evento/campanha (vários aspetos de um lançamento/evento em páginas diferentes); com carrossel (carrossel integrado para visibilidade adicional de produto). Boas práticas: limitar a 4-5 páginas no máximo; hierarquia visual clara (uma mensagem-chave por página); incentivar o scroll (setas/indicadores direcionais); consistência visual; fluxo narrativo lógico; terminar com um CTA forte. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+          <t>Experiência imersiva multi-página que permite navegação vertical por conteúdo de marca através de swipe (cima/baixo), replicando a navegação num site/landing page, com produtos, features, storytelling ou conteúdo promocional distribuídos por várias páginas dentro do mesmo anúncio.</t>
         </is>
       </c>
       <c r="M720" t="inlineStr">
@@ -33663,7 +33663,7 @@
       </c>
       <c r="L721" t="inlineStr">
         <is>
-          <t>Mostra o produto a partir de todos os ângulos. Unidade construída à medida pela equipa de Design da Ogury (não é self-service). Template Photoshop disponível, com safe areas e danger zones oficiais. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2-3 dias úteis consoante a complexidade; máx. 2 revisões por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking. Formatos próprios Ogury e IAB disponíveis para este template: confirmar com a equipa Ogury. Faturação baseada em medição 1P.</t>
+          <t>Mostra o produto a partir de todos os ângulos. Unidade construída à medida pela equipa de Design da Ogury (não é self-service).</t>
         </is>
       </c>
       <c r="M721" t="inlineStr">
@@ -33715,7 +33715,7 @@
       </c>
       <c r="L722" t="inlineStr">
         <is>
-          <t>Carrossel rich media interativo com navegação em camadas (entrada + vista de detalhe), orientado a pergunta/resposta. Para campanhas CPE e CPM. Casos de uso: sondagem de preferência (escolha entre duas opções/preferências/opiniões/produtos, cada resposta rastreada individualmente, podendo revelar conteúdo dedicado); awareness &amp; educação (pergunta verdadeiro/falso, revela a resposta certa + conteúdo educativo — ideal para awareness, saúde, informação pública, sustentabilidade, educação financeira/de marca); recomendação de produto (guia o utilizador para o produto/solução mais relevante consoante a resposta). Boas práticas: perguntas curtas e fáceis de perceber; opções de resposta claras e distintas; labels de resposta curtos; ambas as opções igualmente visíveis; resultado relevante para a escolha do utilizador; foco numa única pergunta; consistência visual entre ecrãs. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+          <t>Carrossel rich media interativo com navegação em camadas (entrada + vista de detalhe), orientado a pergunta/resposta. Para campanhas CPE e CPM.</t>
         </is>
       </c>
       <c r="M722" t="inlineStr">
@@ -33772,7 +33772,7 @@
       </c>
       <c r="L723" t="inlineStr">
         <is>
-          <t>Reaproveita os assets da marca para emular a experiência social (Facebook, Instagram, TikTok, Twitter, LinkedIn, Pinterest ou Snapchat — escolher um layout) dentro de apps não-sociais, gerando alcance incremental. Unidade construída à medida pela equipa de Design da Ogury (não é self-service). Template Photoshop disponível, com safe areas e danger zones oficiais. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2-3 dias úteis consoante a complexidade; máx. 2 revisões por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking. Formatos próprios Ogury e IAB disponíveis para este template: confirmar com a equipa Ogury.</t>
+          <t>Reaproveita os assets da marca para emular a experiência social (Facebook, Instagram, TikTok, Twitter, LinkedIn, Pinterest ou Snapchat — escolher um layout) dentro de apps não-sociais, gerando alcance incremental. Unidade construída à medida pela equipa de Design da Ogury (não é self-service).</t>
         </is>
       </c>
       <c r="M723" t="inlineStr">
@@ -33834,7 +33834,7 @@
       </c>
       <c r="L724" t="inlineStr">
         <is>
-          <t>Reaproveita os assets da marca para emular a experiência de carrossel social (Facebook ou Instagram — escolher um layout) dentro de apps não-sociais, gerando alcance incremental. Unidade construída à medida pela equipa de Design da Ogury (não é self-service). Template Photoshop disponível, com safe areas e danger zones oficiais. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2-3 dias úteis consoante a complexidade; máx. 2 revisões por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking. Formatos próprios Ogury e IAB disponíveis para este template: confirmar com a equipa Ogury. Faturação baseada em medição 1P.</t>
+          <t>Reaproveita os assets da marca para emular a experiência de carrossel social (Facebook ou Instagram — escolher um layout) dentro de apps não-sociais, gerando alcance incremental. Unidade construída à medida pela equipa de Design da Ogury (não é self-service).</t>
         </is>
       </c>
       <c r="M724" t="inlineStr">
@@ -33886,7 +33886,7 @@
       </c>
       <c r="L725" t="inlineStr">
         <is>
-          <t>Anima o storytelling: liga narrativa com transições suaves e mensagens sequenciais, ideal para destacar várias features de produto ou mensagens-chave numa única criatividade. Casos de uso: visual animado único (estático melhorado com movimento subtil); storytelling sequencial (multi-ecrã); multi-CTA (vários CTAs rastreados individualmente, na mesma tela ou em telas diferentes, cada um com destino próprio); Slideshow com vídeo (vídeo visível durante toda a experiência); Slideshow para vídeo (sequência de slideshow seguida de um ecrã de vídeo dedicado); Slideshow com animação Lottie (elementos animados leves — neve, partículas, efeitos de fundo — sem aumentar o peso do ficheiro); Slideshow com disclaimer legal scrollável (texto legal extenso numa área com scroll automático/manual). Boas práticas: limitar a ~5-6 capítulos; manter o CTA visível; mensagem concisa por ecrã; consistência visual entre capítulos. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+          <t>Anima o storytelling: liga narrativa com transições suaves e mensagens sequenciais, ideal para destacar várias features de produto ou mensagens-chave numa única criatividade.</t>
         </is>
       </c>
       <c r="M725" t="inlineStr">
@@ -33938,7 +33938,7 @@
       </c>
       <c r="L726" t="inlineStr">
         <is>
-          <t>Efeito de expansão rápido e chamativo, que dá impacto visual instantâneo e atrai naturalmente a atenção para elementos-chave, mantendo a experiência fluida e não intrusiva. Casos de uso: destaque de produto (efeito pop subtil); ênfase de CTA; revelação de oferta (promoções/descontos/mensagens-chave); reforço do visual principal. Boas práticas: aplicar o efeito pop a produtos, logos ou CTAs para maximizar o impacto; layout limpo (sem sobrecarregar); uma mensagem de cada vez; contraste visual forte; alinhado com a marca; a animação deve reforçar a mensagem, não distrair. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+          <t>Efeito de expansão rápido e chamativo, que dá impacto visual instantâneo e atrai naturalmente a atenção para elementos-chave, mantendo a experiência fluida e não intrusiva.</t>
         </is>
       </c>
       <c r="M726" t="inlineStr">
@@ -33990,7 +33990,7 @@
       </c>
       <c r="L727" t="inlineStr">
         <is>
-          <t>Efeito de revelação horizontal: um segundo visual desliza suavemente sobre o primeiro, criando uma transição clara e envolvente — ideal para mostrar contrastes, detalhes de produto ou mensagens-chave de forma dinâmica mas controlada. Casos de uso: revelação de cor (preto e branco para cor); revelação de detalhe de produto (vista global para vista de pormenor); comparação visual. Boas práticas: usar dois visuais complementares; layout limpo; foco numa única ideia; contraste forte; visuais alinhados entre si (estilo/composição); alinhado com a marca. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+          <t>Efeito de revelação horizontal: um segundo visual desliza suavemente sobre o primeiro, criando uma transição clara e envolvente — ideal para mostrar contrastes, detalhes de produto ou mensagens-chave de forma dinâmica mas controlada.</t>
         </is>
       </c>
       <c r="M727" t="inlineStr">
@@ -34042,7 +34042,7 @@
       </c>
       <c r="L728" t="inlineStr">
         <is>
-          <t>Transição vertical suave entre dois visuais, trazendo o conteúdo para o ecrã de forma natural e guiando a atenção do utilizador — ideal para mostrar duas mensagens/visuais complementares, com uma experiência limpa e premium. Casos de uso: antes/depois; foco de produto (dois ângulos/features complementares); transição de mensagem; marca e produto; tease &amp; reveal; destaque duplo (dois elementos com igual visibilidade). Boas práticas: dois visuais complementares; mensagem simples (uma ideia); continuidade visual (cor/estilo/composição); guiar o olhar do utilizador de um visual para o outro; ambos os visuais com valor standalone forte; alinhado com a marca. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+          <t>Transição vertical suave entre dois visuais, trazendo o conteúdo para o ecrã de forma natural e guiando a atenção do utilizador — ideal para mostrar duas mensagens/visuais complementares, com uma experiência limpa e premium.</t>
         </is>
       </c>
       <c r="M728" t="inlineStr">
@@ -34094,7 +34094,7 @@
       </c>
       <c r="L729" t="inlineStr">
         <is>
-          <t>Combina uma transição vertical com um efeito de revelação limpo, introduzindo visuais ou mensagens com clareza e impacto, numa experiência fluida e fácil de seguir. Casos de uso: introdução visual; destaque de produto (revelação suave); revelação de mensagem (estruturada, fácil de ler); marca e mensagem; foco em elemento-chave. Boas práticas: visuais simples e claros; foco numa única mensagem; visuais consistentes entre si; guiar a atenção naturalmente; a revelação deve acrescentar valor real; alinhado com a marca. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+          <t>Combina uma transição vertical com um efeito de revelação limpo, introduzindo visuais ou mensagens com clareza e impacto, numa experiência fluida e fácil de seguir.</t>
         </is>
       </c>
       <c r="M729" t="inlineStr">
@@ -34146,7 +34146,7 @@
       </c>
       <c r="L730" t="inlineStr">
         <is>
-          <t>Efeito de revelação a partir do centro: os visuais dividem-se e desdobram-se para introduzir novo conteúdo, criando uma transição dinâmica que mantém o utilizador envolvido — ideal para revelar progressivamente vários visuais de forma fluida e estruturada. Casos de uso: storytelling sequencial; showcase de produto (produtos/variações diferentes); destaque de coleção (ex. moda, beleza, automóvel); breakdown de features; revelação de campanha (mensagens-chave progressivas); progressão visual (evolução de um visual para outro). Boas práticas: limitar a 5 ecrãs no máximo; estilo consistente entre todos os visuais; foco numa ideia principal; visuais fortes (impacto imediato em cada ecrã); layout limpo (sem clutter); alinhado com a marca. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+          <t>Efeito de revelação a partir do centro: os visuais dividem-se e desdobram-se para introduzir novo conteúdo, criando uma transição dinâmica que mantém o utilizador envolvido — ideal para revelar progressivamente vários visuais de forma fluida e estruturada.</t>
         </is>
       </c>
       <c r="M730" t="inlineStr">

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -9395,7 +9395,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Hero: pode diferir dos secundários; Secundários: mín. 3 recomendado, máx. 24, todos com o mesmo rácio entre si; Hero em vídeo: duração mín. 4s, máx. 15min.</t>
+          <t>Hero: pode diferir dos secundários; Secundários: mín. 3 recomendado, máx. 24, todos com o mesmo rácio entre si.</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Imagem: 10 MB; Vídeo: até 2 GB</t>
+          <t>Imagem: 10 MB; Vídeo: até 2 GB. Hero em vídeo: duração mín. 4s, máx. 15min.</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Recomendado 1000x1500. Pins com rácio superior ao recomendado podem ficar cortados no feed.</t>
+          <t>Recomendado 1000x1500.</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -9473,6 +9473,11 @@
       <c r="K185" t="inlineStr">
         <is>
           <t>Título: até 100c (só os primeiros 40c podem mostrar no feed; 30c para chinês/japonês/coreano/árabe); Descrição: até 800c.</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>Pins com rácio superior ao recomendado podem ficar cortados no feed.</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -9509,7 +9514,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Duração: mín. 4s, máx. 15min (recomendado 6-15s para ads).</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -9519,7 +9524,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Até 2 GB</t>
+          <t>Até 2 GB. Duração: mín. 4s, máx. 15min (recomendado 6-15s para ads).</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -10547,12 +10552,12 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2 a 6 slides (imagens ou vídeos). Image Carousels: 800x800 recomendado; Video Carousels: 800x450 recomendado. Rácio único em todos os slides do carrossel; conteúdo misto tem de manter o mesmo rácio entre asset de imagem e de vídeo.</t>
+          <t>Image Carousels: 800x800 recomendado; Video Carousels: 800x450 recomendado.</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>1:1, 1.91:1, 4:5, 2:3, 16:9 ou 9:16 (rácio único por carrossel)</t>
+          <t>1:1, 1.91:1, 4:5, 2:3, 16:9 ou 9:16.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -10568,6 +10573,11 @@
       <c r="K205" t="inlineStr">
         <is>
           <t>1 destino (Carousel de destino único) ou até 6 destinos únicos (Carousel multi-destino).</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>2 a 6 slides (imagens ou vídeos). Rácio único em todos os slides do carrossel; conteúdo misto tem de manter o mesmo rácio entre asset de imagem e de vídeo.</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
@@ -10713,7 +10723,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>1200x1200 ou 1920x1080 recomendado. Duração recomendada ≤15s (até 2:20 suportado; alguns anunciantes elegíveis para até 10min, recomendado não ultrapassar 9:55). Bitrate: 1080p 6.000-10.000k (recomendado 6.000k); 720p 5.000-8.000k (recomendado 5.000k). Frame rate: 29,97 ou 30 FPS (até 60 FPS aceite, não fazer upsample). Thumbnail: rácio 